--- a/6node_spain/output_all.xlsx
+++ b/6node_spain/output_all.xlsx
@@ -460,19 +460,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4841603241809979</v>
+        <v>1.391031980694962</v>
       </c>
       <c r="C2" t="n">
+        <v>0.1357915304721569</v>
+      </c>
+      <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.003642472676483447</v>
-      </c>
       <c r="E2" t="n">
-        <v>1.317547585021377e-06</v>
+        <v>0.07461260996186911</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04825809057082037</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -532,13 +532,13 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1.096859523003464</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4395457243847766</v>
+        <v>0.9602409412334014</v>
       </c>
     </row>
   </sheetData>
@@ -628,13 +628,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1.448378918720291</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8069333896388119</v>
+        <v>0.8700077157713119</v>
       </c>
     </row>
     <row r="4">
@@ -656,10 +656,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3.622506309480824e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.2263192170913441</v>
       </c>
     </row>
     <row r="5">
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1.448378918720291</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -684,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006070787794139079</v>
+        <v>0.3797202862854819</v>
       </c>
     </row>
     <row r="6">
@@ -700,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>3.622506309480824e-10</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1.708905370183168e-06</v>
+        <v>0.1243543495741979</v>
       </c>
     </row>
     <row r="7">
@@ -722,16 +722,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8069333896388119</v>
+        <v>0.8700077157713119</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.2263192170913441</v>
       </c>
       <c r="E7" t="n">
-        <v>0.006070787794139079</v>
+        <v>0.3797202862854819</v>
       </c>
       <c r="F7" t="n">
-        <v>1.708905370183168e-06</v>
+        <v>0.1243543495741979</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.1525911632724586</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1577996507498847</v>
+        <v>0.1750426713701295</v>
       </c>
     </row>
     <row r="4">
@@ -855,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.2974497558473439</v>
       </c>
     </row>
     <row r="5">
@@ -868,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.1510158417849385</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -880,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002620441398158313</v>
+        <v>0.1648651746285813</v>
       </c>
     </row>
     <row r="6">
@@ -905,7 +905,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2.282118921086119e-06</v>
+        <v>0.232243468841142</v>
       </c>
     </row>
     <row r="7">
@@ -918,16 +918,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1638523178181806</v>
+        <v>0.1766599629615699</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.2888833065891823</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002655070250249774</v>
+        <v>0.166077538485157</v>
       </c>
       <c r="F7" t="n">
-        <v>2.28280647621386e-06</v>
+        <v>0.2323170723070234</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1020,13 +1020,13 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.8474088367275414</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8422003492501153</v>
+        <v>0.8249573286298706</v>
       </c>
     </row>
     <row r="4">
@@ -1051,7 +1051,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.7025502441526561</v>
       </c>
     </row>
     <row r="5">
@@ -1064,7 +1064,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0.8489841582150615</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -1076,7 +1076,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9973795586018417</v>
+        <v>0.8351348253714187</v>
       </c>
     </row>
     <row r="6">
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9999977178810789</v>
+        <v>0.767756531158858</v>
       </c>
     </row>
     <row r="7">
@@ -1114,16 +1114,16 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8361476821818195</v>
+        <v>0.8233400370384301</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0.7111166934108177</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9973449297497502</v>
+        <v>0.8339224615148431</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9999977171935238</v>
+        <v>0.7676829276929766</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1146,22 +1146,22 @@
     <row r="1">
       <c r="D1" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -1178,17 +1178,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -1198,32 +1198,32 @@
         <v/>
       </c>
       <c r="F2" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1577996507498847</v>
+        <v/>
       </c>
       <c r="H2" t="n">
-        <v>6.817476050451102e-09</v>
+        <v/>
       </c>
       <c r="I2" t="n">
-        <v>2.830301694229122e-09</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -1236,29 +1236,29 @@
         <v/>
       </c>
       <c r="G3" t="n">
-        <v>0.002620441398158313</v>
+        <v/>
       </c>
       <c r="H3" t="n">
-        <v>5.596219586238009e-09</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1.178573108250142e-09</v>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1271,33 +1271,33 @@
         <v/>
       </c>
       <c r="G4" t="n">
-        <v>2.282118921086119e-06</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>7.366509862981758e-09</v>
+        <v>1.127819096249323e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>2.965719357035209e-09</v>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.1638523178181806</v>
+        <v/>
       </c>
       <c r="E5" t="n">
         <v/>
@@ -1309,61 +1309,61 @@
         <v/>
       </c>
       <c r="H5" t="n">
-        <v>-3.665631481645959e-09</v>
+        <v>-1.127819096249323e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>2.147717353150931e-09</v>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v/>
       </c>
       <c r="E6" t="n">
-        <v>0.002655070250249774</v>
+        <v/>
       </c>
       <c r="F6" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v/>
       </c>
       <c r="H6" t="n">
-        <v>2.565524301888539e-10</v>
+        <v/>
       </c>
       <c r="I6" t="n">
-        <v>5.748783882499443e-09</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1373,16 +1373,16 @@
         <v/>
       </c>
       <c r="F7" t="n">
-        <v>2.28280647621386e-06</v>
+        <v/>
       </c>
       <c r="G7" t="n">
         <v/>
       </c>
       <c r="H7" t="n">
-        <v>5.527905447157694e-10</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>2.075128092554811e-10</v>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -1393,28 +1393,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>i3</t>
-        </is>
+          <t>i2</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v/>
       </c>
       <c r="E8" t="n">
-        <v>-1.540526656265304e-09</v>
+        <v/>
       </c>
       <c r="F8" t="n">
-        <v>8.321032695465486e-10</v>
+        <v/>
       </c>
       <c r="G8" t="n">
-        <v>1.099880099118007e-09</v>
+        <v/>
       </c>
       <c r="H8" t="n">
-        <v>2.154280319178363e-09</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.398609351486063e-09</v>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -1425,28 +1428,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>i4</t>
-        </is>
+          <t>i5</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v/>
       </c>
       <c r="E9" t="n">
-        <v>8.646847675150142e-10</v>
+        <v/>
       </c>
       <c r="F9" t="n">
-        <v>1.228226815956655e-09</v>
+        <v/>
       </c>
       <c r="G9" t="n">
-        <v>4.054727494642555e-09</v>
+        <v/>
       </c>
       <c r="H9" t="n">
-        <v>1.198155906363433e-09</v>
+        <v>1.000000000112782</v>
       </c>
       <c r="I9" t="n">
-        <v>1.214694885309319e-09</v>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -1457,28 +1463,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>i5</t>
-        </is>
+          <t>i6</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v/>
       </c>
       <c r="E10" t="n">
-        <v>-1.616830828672188e-09</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.577414800637724e-09</v>
+        <v/>
       </c>
       <c r="G10" t="n">
-        <v>6.421786889266428e-10</v>
+        <v/>
       </c>
       <c r="H10" t="n">
-        <v>6.236276371934655e-09</v>
+        <v/>
       </c>
       <c r="I10" t="n">
-        <v>-1.508406574029532e-09</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1489,28 +1498,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>i6</t>
-        </is>
+          <t>i3</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v/>
       </c>
       <c r="E11" t="n">
-        <v>1.135368305901628e-10</v>
+        <v/>
       </c>
       <c r="F11" t="n">
-        <v>5.37474416069381e-10</v>
+        <v/>
       </c>
       <c r="G11" t="n">
-        <v>-2.949786889018343e-10</v>
+        <v/>
       </c>
       <c r="H11" t="n">
-        <v>-1.093204520859941e-09</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>3.24644397682959e-09</v>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -1521,28 +1533,31 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>i1</t>
-        </is>
+          <t>i6</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v/>
       </c>
       <c r="E12" t="n">
-        <v>-4.396328601602161e-10</v>
+        <v/>
       </c>
       <c r="F12" t="n">
-        <v>-1.167485197223249e-10</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>7.139950790830691e-11</v>
+        <v/>
       </c>
       <c r="H12" t="n">
-        <v>2.665911296991115e-10</v>
+        <v>1.127819096249323e-10</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.529027607904855e-10</v>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -1553,28 +1568,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>i2</t>
-        </is>
+          <t>i3</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v/>
       </c>
       <c r="E13" t="n">
-        <v>-1.163905461398964e-09</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.230956419230798e-09</v>
+        <v/>
       </c>
       <c r="G13" t="n">
-        <v>1.304836131624464e-09</v>
+        <v/>
       </c>
       <c r="H13" t="n">
-        <v>2.124048432904297e-09</v>
+        <v>1.127819096249323e-10</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.174045041169948e-09</v>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -1585,7 +1603,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1593,95 +1611,104 @@
           <t>i4</t>
         </is>
       </c>
+      <c r="D14" t="n">
+        <v/>
+      </c>
       <c r="E14" t="n">
-        <v>-1.26475405824601e-09</v>
+        <v/>
       </c>
       <c r="F14" t="n">
-        <v>-1.2024822982828e-09</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>1.473879016555495e-09</v>
+        <v/>
       </c>
       <c r="H14" t="n">
-        <v>5.613424494015786e-10</v>
+        <v/>
       </c>
       <c r="I14" t="n">
-        <v>-1.191184553941645e-09</v>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>i5</t>
-        </is>
+          <t>i3</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v/>
       </c>
       <c r="E15" t="n">
-        <v>-2.071924983225628e-09</v>
+        <v/>
       </c>
       <c r="F15" t="n">
-        <v>-2.063511952596438e-09</v>
+        <v/>
       </c>
       <c r="G15" t="n">
-        <v>-3.083752635716617e-11</v>
+        <v/>
       </c>
       <c r="H15" t="n">
-        <v>4.846306366728068e-09</v>
+        <v>1.000000000018537</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.033154925539279e-09</v>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>i6</t>
-        </is>
+          <t>i4</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v/>
       </c>
       <c r="E16" t="n">
-        <v>-2.004164777970988e-09</v>
+        <v/>
       </c>
       <c r="F16" t="n">
-        <v>-1.969626786033537e-09</v>
+        <v/>
       </c>
       <c r="G16" t="n">
-        <v>-1.210616763216238e-09</v>
+        <v/>
       </c>
       <c r="H16" t="n">
-        <v>-1.405160815615033e-09</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.53873735688485e-09</v>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1689,189 +1716,204 @@
           <t>i1</t>
         </is>
       </c>
+      <c r="D17" t="n">
+        <v/>
+      </c>
       <c r="E17" t="n">
-        <v>-4.724675297185319e-11</v>
+        <v/>
       </c>
       <c r="F17" t="n">
-        <v>-1.561782112042403e-10</v>
+        <v/>
       </c>
       <c r="G17" t="n">
-        <v>-2.267868883204978e-10</v>
+        <v/>
       </c>
       <c r="H17" t="n">
-        <v>6.837935819482741e-10</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>6.623155209973572e-11</v>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>i2</t>
-        </is>
+          <t>i3</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v/>
       </c>
       <c r="E18" t="n">
-        <v>3.96267762965037e-09</v>
+        <v/>
       </c>
       <c r="F18" t="n">
-        <v>3.064012903563065e-09</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>1.140207391872835e-09</v>
+        <v/>
       </c>
       <c r="H18" t="n">
-        <v>1.506734145426344e-09</v>
+        <v/>
       </c>
       <c r="I18" t="n">
-        <v>2.672847095489885e-09</v>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>i3</t>
-        </is>
+          <t>i4</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v/>
       </c>
       <c r="E19" t="n">
-        <v>-1.80941523157539e-09</v>
+        <v/>
       </c>
       <c r="F19" t="n">
-        <v>-4.926583149189702e-10</v>
+        <v/>
       </c>
       <c r="G19" t="n">
-        <v>-6.673875495286984e-10</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>3.85525032083327e-10</v>
+        <v/>
       </c>
       <c r="I19" t="n">
-        <v>-1.808208544240411e-09</v>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.001</v>
+        <v/>
       </c>
       <c r="E20" t="n">
-        <v>-1.547791752175428e-09</v>
+        <v/>
       </c>
       <c r="F20" t="n">
-        <v>-1.622844298693807e-09</v>
+        <v/>
       </c>
       <c r="G20" t="n">
-        <v>-1.784325850708744e-10</v>
+        <v/>
       </c>
       <c r="H20" t="n">
-        <v>6.403519909940914e-09</v>
+        <v/>
       </c>
       <c r="I20" t="n">
-        <v>-1.557513358848837e-09</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>i6</t>
-        </is>
+          <t>i1</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v/>
       </c>
       <c r="E21" t="n">
-        <v>-2.065204762494256e-10</v>
+        <v/>
       </c>
       <c r="F21" t="n">
-        <v>-2.262262088416467e-10</v>
+        <v/>
       </c>
       <c r="G21" t="n">
-        <v>-3.46875094413485e-10</v>
+        <v/>
       </c>
       <c r="H21" t="n">
-        <v>-2.906515676321505e-10</v>
+        <v>1.000000000018537</v>
       </c>
       <c r="I21" t="n">
-        <v>1.855573199452468e-09</v>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>i1</t>
-        </is>
+          <t>i5</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>3.357731737727292e-10</v>
+        <v/>
       </c>
       <c r="F22" t="n">
-        <v>1.054278819974756e-10</v>
+        <v/>
       </c>
       <c r="G22" t="n">
-        <v>6.474112309682117e-10</v>
+        <v/>
       </c>
       <c r="H22" t="n">
-        <v>-3.660075936380125e-10</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>6.775563771352101e-10</v>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1881,66 +1923,72 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>i2</t>
-        </is>
+          <t>i4</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.163014144236405e-09</v>
+        <v/>
       </c>
       <c r="F23" t="n">
-        <v>-1.434112557374666e-09</v>
+        <v/>
       </c>
       <c r="G23" t="n">
-        <v>9.544560123046437e-10</v>
+        <v/>
       </c>
       <c r="H23" t="n">
-        <v>-1.965188158830178e-10</v>
+        <v/>
       </c>
       <c r="I23" t="n">
-        <v>-1.167142613843355e-09</v>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>i3</t>
-        </is>
+          <t>i1</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.032801212604987e-09</v>
+        <v/>
       </c>
       <c r="F24" t="n">
-        <v>-1.153451380416827e-09</v>
+        <v/>
       </c>
       <c r="G24" t="n">
-        <v>5.218360889760483e-11</v>
+        <v>-4.867070237402924e-10</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.886282819472016e-10</v>
+        <v/>
       </c>
       <c r="I24" t="n">
-        <v>-1.973283442526023e-09</v>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1948,31 +1996,34 @@
           <t>i4</t>
         </is>
       </c>
+      <c r="D25" t="n">
+        <v/>
+      </c>
       <c r="E25" t="n">
-        <v>-1.311469245759843e-09</v>
+        <v/>
       </c>
       <c r="F25" t="n">
-        <v>-1.468505904814819e-09</v>
+        <v/>
       </c>
       <c r="G25" t="n">
-        <v>2.188321091322729e-09</v>
+        <v>4.867070237402924e-10</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.132296213938081e-10</v>
+        <v/>
       </c>
       <c r="I25" t="n">
-        <v>-1.194367921268162e-09</v>
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1981,33 +2032,33 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.001</v>
+        <v/>
       </c>
       <c r="E26" t="n">
-        <v>-2.052880167249722e-09</v>
+        <v/>
       </c>
       <c r="F26" t="n">
-        <v>-2.127188363264693e-09</v>
+        <v/>
       </c>
       <c r="G26" t="n">
-        <v>-1.071518072488511e-09</v>
+        <v>-2.469527914385539e-10</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.66700936320385e-09</v>
+        <v/>
       </c>
       <c r="I26" t="n">
-        <v>-1.578925082255712e-09</v>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2015,31 +2066,34 @@
           <t>i1</t>
         </is>
       </c>
+      <c r="D27" t="n">
+        <v/>
+      </c>
       <c r="E27" t="n">
-        <v>2.640345596637907e-10</v>
+        <v/>
       </c>
       <c r="F27" t="n">
-        <v>1.92096189116141e-10</v>
+        <v/>
       </c>
       <c r="G27" t="n">
-        <v>-8.474121685562734e-10</v>
+        <v>4.867070237402924e-10</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.137167685884881e-09</v>
+        <v/>
       </c>
       <c r="I27" t="n">
-        <v>-6.983980329337451e-10</v>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2048,351 +2102,378 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.001</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>-5.133091285505394e-10</v>
+        <v/>
       </c>
       <c r="F28" t="n">
-        <v>-7.751453362680458e-10</v>
+        <v/>
       </c>
       <c r="G28" t="n">
-        <v>-7.492955678538552e-10</v>
+        <v/>
       </c>
       <c r="H28" t="n">
-        <v>-1.203441191536455e-09</v>
+        <v/>
       </c>
       <c r="I28" t="n">
-        <v>-1.400325388799697e-09</v>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>i3</t>
-        </is>
+          <t>i4</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v/>
       </c>
       <c r="E29" t="n">
-        <v>-1.903097951962925e-09</v>
+        <v/>
       </c>
       <c r="F29" t="n">
-        <v>-7.050025890844306e-10</v>
+        <v/>
       </c>
       <c r="G29" t="n">
-        <v>-1.238472812946618e-09</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.354269092435472e-09</v>
+        <v/>
       </c>
       <c r="I29" t="n">
-        <v>-2.188496408412235e-09</v>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>i4</t>
-        </is>
+          <t>i5</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v/>
       </c>
       <c r="E30" t="n">
-        <v>7.712827910022733e-10</v>
+        <v/>
       </c>
       <c r="F30" t="n">
-        <v>6.233133117967003e-10</v>
+        <v/>
       </c>
       <c r="G30" t="n">
-        <v>1.449497686939017e-09</v>
+        <v/>
       </c>
       <c r="H30" t="n">
-        <v>-2.238574954982443e-10</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>-5.659318231238907e-10</v>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>i5</t>
-        </is>
+          <t>i6</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v/>
       </c>
       <c r="E31" t="n">
-        <v>-2.040733810603018e-09</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.100796938638713e-09</v>
+        <v/>
       </c>
       <c r="G31" t="n">
-        <v>-1.175094005414122e-09</v>
+        <v/>
       </c>
       <c r="H31" t="n">
-        <v>-2.807383717139525e-10</v>
+        <v/>
       </c>
       <c r="I31" t="n">
-        <v>-2.284805177374418e-09</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-2.419885971957669e-09</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>0.001</v>
+        <v/>
       </c>
       <c r="F32" t="n">
-        <v>-2.352302897913032e-09</v>
+        <v/>
       </c>
       <c r="G32" t="n">
-        <v>-1.172829465251633e-09</v>
+        <v/>
       </c>
       <c r="H32" t="n">
-        <v>-6.513125804935464e-10</v>
+        <v/>
       </c>
       <c r="I32" t="n">
-        <v>-7.661748538634911e-10</v>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-2.501524836706534e-09</v>
+        <v/>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.738854040368341e-09</v>
+        <v/>
       </c>
       <c r="G33" t="n">
-        <v>-8.990341346952133e-10</v>
+        <v/>
       </c>
       <c r="H33" t="n">
-        <v>-3.751850628436884e-10</v>
+        <v/>
       </c>
       <c r="I33" t="n">
-        <v>2.464192803611214e-09</v>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-2.488093517211574e-09</v>
+        <v/>
+      </c>
+      <c r="E34" t="n">
+        <v/>
       </c>
       <c r="F34" t="n">
-        <v>-2.420462543825888e-09</v>
+        <v/>
       </c>
       <c r="G34" t="n">
-        <v>-1.151614428875823e-10</v>
+        <v>-2.469527914385539e-10</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.407631399051692e-10</v>
+        <v/>
       </c>
       <c r="I34" t="n">
-        <v>2.959974524790955e-09</v>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-2.431224815803919e-09</v>
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v/>
       </c>
       <c r="F35" t="n">
-        <v>-2.367977287155535e-09</v>
+        <v/>
       </c>
       <c r="G35" t="n">
-        <v>-7.010134046896337e-10</v>
+        <v/>
       </c>
       <c r="H35" t="n">
-        <v>1.880292788770005e-09</v>
+        <v/>
       </c>
       <c r="I35" t="n">
-        <v>2.707639664821667e-09</v>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-2.523063825562498e-09</v>
+        <v/>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>-2.440781456834349e-09</v>
+        <v/>
       </c>
       <c r="G36" t="n">
-        <v>-9.683651180126252e-10</v>
+        <v/>
       </c>
       <c r="H36" t="n">
-        <v>-1.162033227703898e-09</v>
+        <v/>
       </c>
       <c r="I36" t="n">
-        <v>5.268643492622008e-09</v>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>9.827715337137867e-11</v>
+        <v/>
+      </c>
+      <c r="E37" t="n">
+        <v/>
       </c>
       <c r="F37" t="n">
-        <v>-2.042041668675031e-09</v>
+        <v/>
       </c>
       <c r="G37" t="n">
-        <v>-5.72804477430469e-11</v>
+        <v/>
       </c>
       <c r="H37" t="n">
-        <v>1.347501788730898e-09</v>
+        <v/>
       </c>
       <c r="I37" t="n">
-        <v>2.913043388693489e-09</v>
+        <v>-2.751516060051469e-10</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-3.682710255016126e-10</v>
+        <v/>
+      </c>
+      <c r="E38" t="n">
+        <v/>
       </c>
       <c r="F38" t="n">
-        <v>8.771507267652966e-09</v>
+        <v>3.261399125969135e-10</v>
       </c>
       <c r="G38" t="n">
-        <v>2.694127621934633e-09</v>
+        <v/>
       </c>
       <c r="H38" t="n">
-        <v>4.675457462064443e-09</v>
+        <v/>
       </c>
       <c r="I38" t="n">
-        <v>6.864528812391089e-09</v>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2402,32 +2483,32 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>5.792565328242931e-09</v>
+        <v/>
       </c>
       <c r="E39" t="n">
-        <v>0.001</v>
+        <v/>
       </c>
       <c r="F39" t="n">
-        <v>6.040325240704062e-09</v>
+        <v/>
       </c>
       <c r="G39" t="n">
-        <v>0.00224549493985743</v>
+        <v/>
       </c>
       <c r="H39" t="n">
-        <v>6.171549125163005e-09</v>
+        <v/>
       </c>
       <c r="I39" t="n">
-        <v>2.960982963403987e-08</v>
+        <v>-2.751516060051469e-10</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2437,29 +2518,32 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-4.634817827336546e-10</v>
+        <v/>
+      </c>
+      <c r="E40" t="n">
+        <v/>
       </c>
       <c r="F40" t="n">
-        <v>-8.349456614057914e-10</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>2.368102976216512e-09</v>
+        <v/>
       </c>
       <c r="H40" t="n">
-        <v>1.865059241150054e-08</v>
+        <v/>
       </c>
       <c r="I40" t="n">
-        <v>6.511638399970573e-09</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2473,25 +2557,28 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>3.387042417162516e-09</v>
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v/>
       </c>
       <c r="F41" t="n">
-        <v>3.992711619608079e-09</v>
+        <v/>
       </c>
       <c r="G41" t="n">
-        <v>7.163558463436893e-09</v>
+        <v/>
       </c>
       <c r="H41" t="n">
-        <v>8.319435535926024e-10</v>
+        <v/>
       </c>
       <c r="I41" t="n">
-        <v>0.1532015092863475</v>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2501,157 +2588,172 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-1.377782836599738e-09</v>
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v/>
       </c>
       <c r="F42" t="n">
-        <v>-2.427174662419592e-09</v>
+        <v/>
       </c>
       <c r="G42" t="n">
-        <v>-9.603578231254719e-10</v>
+        <v/>
       </c>
       <c r="H42" t="n">
-        <v>-2.143459680665359e-10</v>
+        <v/>
       </c>
       <c r="I42" t="n">
-        <v>2.275421967353421e-09</v>
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-1.271774988826973e-09</v>
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v/>
       </c>
       <c r="F43" t="n">
-        <v>-1.380984677646053e-09</v>
+        <v/>
       </c>
       <c r="G43" t="n">
-        <v>-5.759777530391644e-11</v>
+        <v/>
       </c>
       <c r="H43" t="n">
-        <v>6.655971594454851e-10</v>
+        <v/>
       </c>
       <c r="I43" t="n">
-        <v>-1.729140447863482e-10</v>
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-1.411087582889077e-09</v>
+        <v/>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>-1.538743787006392e-09</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>2.311212441367774e-09</v>
+        <v/>
       </c>
       <c r="H44" t="n">
-        <v>7.132613542888384e-10</v>
+        <v/>
       </c>
       <c r="I44" t="n">
-        <v>7.569113917417068e-09</v>
+        <v>-2.751516060051469e-10</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>-2.01041705697229e-09</v>
+        <v/>
+      </c>
+      <c r="E45" t="n">
+        <v/>
       </c>
       <c r="F45" t="n">
-        <v>-2.175427062765426e-09</v>
+        <v/>
       </c>
       <c r="G45" t="n">
-        <v>-4.130555339398348e-10</v>
+        <v/>
       </c>
       <c r="H45" t="n">
-        <v>2.913218209364548e-09</v>
+        <v/>
       </c>
       <c r="I45" t="n">
-        <v>3.323156680391281e-09</v>
+        <v>2.751516060051469e-10</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>-2.049717630791665e-09</v>
+        <v/>
+      </c>
+      <c r="E46" t="n">
+        <v/>
       </c>
       <c r="F46" t="n">
-        <v>-2.149935545913493e-09</v>
+        <v/>
       </c>
       <c r="G46" t="n">
-        <v>-6.027615715098455e-10</v>
+        <v/>
       </c>
       <c r="H46" t="n">
-        <v>-1.108461698348912e-09</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>8.107898056053387e-09</v>
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2661,66 +2763,72 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-9.016295411360952e-10</v>
+        <v/>
+      </c>
+      <c r="E47" t="n">
+        <v/>
       </c>
       <c r="F47" t="n">
-        <v>-2.311119772603295e-09</v>
+        <v/>
       </c>
       <c r="G47" t="n">
-        <v>-1.21569378097212e-09</v>
+        <v/>
       </c>
       <c r="H47" t="n">
-        <v>8.882685071157354e-11</v>
+        <v/>
       </c>
       <c r="I47" t="n">
-        <v>2.50212574645386e-09</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>5.183607805426625e-09</v>
+        <v/>
+      </c>
+      <c r="E48" t="n">
+        <v/>
       </c>
       <c r="F48" t="n">
-        <v>5.42744582622913e-09</v>
+        <v>3.261399125969135e-10</v>
       </c>
       <c r="G48" t="n">
-        <v>1.291583719108656e-09</v>
+        <v/>
       </c>
       <c r="H48" t="n">
-        <v>1.431782807403952e-09</v>
+        <v/>
       </c>
       <c r="I48" t="n">
-        <v>1.030072471729933e-09</v>
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2729,65 +2837,68 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-1.579212509194256e-09</v>
+        <v>0.9999999999237215</v>
+      </c>
+      <c r="E49" t="n">
+        <v/>
       </c>
       <c r="F49" t="n">
-        <v>1.335196576226077e-10</v>
+        <v/>
       </c>
       <c r="G49" t="n">
-        <v>-6.719103092613803e-10</v>
+        <v/>
       </c>
       <c r="H49" t="n">
-        <v>2.675834715213529e-10</v>
+        <v/>
       </c>
       <c r="I49" t="n">
-        <v>4.671012185358833e-09</v>
+        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-1.230048315379362e-09</v>
+        <v/>
       </c>
       <c r="E50" t="n">
-        <v>0.001</v>
+        <v>4.778789306492098e-10</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.532428392724448e-09</v>
+        <v/>
       </c>
       <c r="G50" t="n">
-        <v>-2.719053201264582e-10</v>
+        <v/>
       </c>
       <c r="H50" t="n">
-        <v>5.021373624237705e-09</v>
+        <v/>
       </c>
       <c r="I50" t="n">
-        <v>5.547403029086671e-09</v>
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2796,30 +2907,33 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>-2.058613582280863e-11</v>
+        <v/>
+      </c>
+      <c r="E51" t="n">
+        <v/>
       </c>
       <c r="F51" t="n">
-        <v>-2.492253374845467e-10</v>
+        <v/>
       </c>
       <c r="G51" t="n">
-        <v>8.162241454169429e-10</v>
+        <v/>
       </c>
       <c r="H51" t="n">
-        <v>4.779198827738646e-10</v>
+        <v/>
       </c>
       <c r="I51" t="n">
-        <v>4.550254377371384e-08</v>
+        <v>-2.099990461856482e-09</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2828,30 +2942,33 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>-1.054332083748754e-09</v>
+        <v>1</v>
+      </c>
+      <c r="E52" t="n">
+        <v/>
       </c>
       <c r="F52" t="n">
-        <v>-2.345287527237345e-09</v>
+        <v/>
       </c>
       <c r="G52" t="n">
-        <v>-7.139726884818778e-10</v>
+        <v/>
       </c>
       <c r="H52" t="n">
-        <v>-6.567034817598232e-10</v>
+        <v/>
       </c>
       <c r="I52" t="n">
-        <v>2.829904820522029e-09</v>
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2860,89 +2977,98 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>-1.29556769045374e-09</v>
+        <v>1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>3.716836127293384e-10</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.501821331022072e-09</v>
+        <v/>
       </c>
       <c r="G53" t="n">
-        <v>-1.219606754626629e-10</v>
+        <v/>
       </c>
       <c r="H53" t="n">
-        <v>-4.728006820686186e-10</v>
+        <v/>
       </c>
       <c r="I53" t="n">
-        <v>-1.296591425387369e-10</v>
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-2.00402920512181e-09</v>
+        <v/>
+      </c>
+      <c r="E54" t="n">
+        <v>-3.716836127293384e-10</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.107069711284717e-09</v>
+        <v/>
       </c>
       <c r="G54" t="n">
-        <v>-3.903966657516019e-10</v>
+        <v/>
       </c>
       <c r="H54" t="n">
-        <v>-5.374164593282896e-10</v>
+        <v/>
       </c>
       <c r="I54" t="n">
-        <v>3.622184250683014e-09</v>
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-1.489530938725664e-09</v>
+        <v/>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>-1.693588222413684e-09</v>
+        <v/>
       </c>
       <c r="G55" t="n">
-        <v>2.25537237877518e-09</v>
+        <v/>
       </c>
       <c r="H55" t="n">
-        <v>-8.773802538776289e-11</v>
+        <v/>
       </c>
       <c r="I55" t="n">
-        <v>7.124072037286067e-09</v>
+        <v>2.099990461856482e-09</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2952,163 +3078,172 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-2.115235924455916e-09</v>
+        <v/>
       </c>
       <c r="E56" t="n">
-        <v>0.001</v>
+        <v>4.778789306492098e-10</v>
       </c>
       <c r="F56" t="n">
-        <v>-2.253631919208821e-09</v>
+        <v/>
       </c>
       <c r="G56" t="n">
-        <v>-6.593496371654788e-10</v>
+        <v/>
       </c>
       <c r="H56" t="n">
-        <v>-1.426884704581745e-09</v>
+        <v/>
       </c>
       <c r="I56" t="n">
-        <v>7.375197702631705e-09</v>
+        <v>-2.099990461856482e-09</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>-6.821936697396365e-10</v>
+        <v/>
       </c>
       <c r="E57" t="n">
-        <v>0.001</v>
+        <v>-4.778789306492098e-10</v>
       </c>
       <c r="F57" t="n">
-        <v>-2.19475459514547e-09</v>
+        <v/>
       </c>
       <c r="G57" t="n">
-        <v>-9.090988252959258e-10</v>
+        <v/>
       </c>
       <c r="H57" t="n">
-        <v>-1.014280411827543e-09</v>
+        <v/>
       </c>
       <c r="I57" t="n">
-        <v>2.113779708961972e-09</v>
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>-1.963790532676462e-10</v>
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
       </c>
       <c r="F58" t="n">
-        <v>-1.923369653474422e-10</v>
+        <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>6.080501800903544e-11</v>
+        <v/>
       </c>
       <c r="H58" t="n">
-        <v>-9.732668096558262e-10</v>
+        <v/>
       </c>
       <c r="I58" t="n">
-        <v>3.908253513227156e-11</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>-1.667742519375345e-09</v>
+        <v/>
+      </c>
+      <c r="E59" t="n">
+        <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>1.96187934306381e-10</v>
+        <v/>
       </c>
       <c r="G59" t="n">
-        <v>-4.553467746260311e-10</v>
+        <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v>-1.061170354779543e-09</v>
+        <v/>
       </c>
       <c r="I59" t="n">
-        <v>3.480758524409835e-09</v>
+        <v>2.099990461856482e-09</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1.048278014667139e-09</v>
+        <v/>
+      </c>
+      <c r="E60" t="n">
+        <v/>
       </c>
       <c r="F60" t="n">
-        <v>1.080661293416019e-09</v>
+        <v/>
       </c>
       <c r="G60" t="n">
-        <v>7.665382869509477e-09</v>
+        <v/>
       </c>
       <c r="H60" t="n">
-        <v>6.311773223778381e-10</v>
+        <v/>
       </c>
       <c r="I60" t="n">
-        <v>1.199016709278056e-08</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3118,29 +3253,32 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>-1.823523871776955e-09</v>
+        <v/>
+      </c>
+      <c r="E61" t="n">
+        <v>0.9999999996283164</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.990620307076405e-09</v>
+        <v/>
       </c>
       <c r="G61" t="n">
-        <v>-6.124360054838748e-10</v>
+        <v/>
       </c>
       <c r="H61" t="n">
-        <v>3.002405964190082e-11</v>
+        <v/>
       </c>
       <c r="I61" t="n">
-        <v>2.731861894344402e-09</v>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3154,25 +3292,28 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>-2.631876356718475e-09</v>
+        <v/>
       </c>
       <c r="E62" t="n">
-        <v>-2.287170525293462e-09</v>
+        <v/>
+      </c>
+      <c r="F62" t="n">
+        <v/>
       </c>
       <c r="G62" t="n">
-        <v>9.773839788779385e-09</v>
+        <v>1.904637672416955e-08</v>
       </c>
       <c r="H62" t="n">
-        <v>-3.438546475302525e-10</v>
+        <v/>
       </c>
       <c r="I62" t="n">
-        <v>3.784637074232417e-08</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3186,28 +3327,28 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>-2.115143837507362e-09</v>
+        <v/>
       </c>
       <c r="E63" t="n">
-        <v>-1.487851447909596e-09</v>
+        <v/>
       </c>
       <c r="F63" t="n">
-        <v>0.001</v>
+        <v/>
       </c>
       <c r="G63" t="n">
-        <v>-3.405139072916252e-10</v>
+        <v>1.482092409297515e-08</v>
       </c>
       <c r="H63" t="n">
-        <v>-2.669947755424258e-10</v>
+        <v/>
       </c>
       <c r="I63" t="n">
-        <v>-1.996696470422265e-11</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3221,89 +3362,98 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>-2.635873871128442e-09</v>
+        <v/>
       </c>
       <c r="E64" t="n">
-        <v>-2.389544543879656e-09</v>
+        <v/>
+      </c>
+      <c r="F64" t="n">
+        <v>-1.811128153445419e-10</v>
       </c>
       <c r="G64" t="n">
-        <v>1.060768705423592e-08</v>
+        <v/>
       </c>
       <c r="H64" t="n">
-        <v>-9.631825077615566e-11</v>
+        <v/>
       </c>
       <c r="I64" t="n">
-        <v>3.81214735556068e-08</v>
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>-2.584438119748789e-09</v>
+        <v/>
       </c>
       <c r="E65" t="n">
-        <v>-2.370922853293845e-09</v>
+        <v/>
+      </c>
+      <c r="F65" t="n">
+        <v>-1.811128153445419e-10</v>
       </c>
       <c r="G65" t="n">
-        <v>8.420441667361283e-09</v>
+        <v/>
       </c>
       <c r="H65" t="n">
-        <v>2.484932617143855e-09</v>
+        <v/>
       </c>
       <c r="I65" t="n">
-        <v>3.462254873345113e-08</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>-2.625297892708317e-09</v>
+        <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>-2.378409511436147e-09</v>
+        <v/>
+      </c>
+      <c r="F66" t="n">
+        <v/>
       </c>
       <c r="G66" t="n">
-        <v>9.864949885941748e-09</v>
+        <v>1.482092409297515e-08</v>
       </c>
       <c r="H66" t="n">
-        <v>-1.367673939296192e-09</v>
+        <v/>
       </c>
       <c r="I66" t="n">
-        <v>6.430784210687281e-08</v>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3313,66 +3463,72 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>-9.328974015199582e-10</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>-2.470665954500859e-09</v>
+        <v/>
+      </c>
+      <c r="F67" t="n">
+        <v/>
       </c>
       <c r="G67" t="n">
-        <v>6.285518526508099e-09</v>
+        <v/>
       </c>
       <c r="H67" t="n">
-        <v>9.624638580047827e-11</v>
+        <v/>
       </c>
       <c r="I67" t="n">
-        <v>3.053095659851355e-08</v>
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2.738233297784522e-09</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.532323436683267e-09</v>
+        <v/>
+      </c>
+      <c r="F68" t="n">
+        <v/>
       </c>
       <c r="G68" t="n">
-        <v>-3.356922951091626e-10</v>
+        <v>-4.225452631194397e-09</v>
       </c>
       <c r="H68" t="n">
-        <v>2.07328142098286e-09</v>
+        <v/>
       </c>
       <c r="I68" t="n">
-        <v>9.653245311682512e-11</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3381,30 +3537,33 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1.152401341045947e-09</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>1.784350862685129e-10</v>
+        <v/>
+      </c>
+      <c r="F69" t="n">
+        <v/>
       </c>
       <c r="G69" t="n">
-        <v>8.471013675177908e-08</v>
+        <v/>
       </c>
       <c r="H69" t="n">
-        <v>1.675317628509956e-09</v>
+        <v/>
       </c>
       <c r="I69" t="n">
-        <v>9.805159001162094e-08</v>
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3413,225 +3572,243 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>-1.402818432416195e-09</v>
+        <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.842073284309171e-09</v>
+        <v/>
+      </c>
+      <c r="F70" t="n">
+        <v/>
       </c>
       <c r="G70" t="n">
-        <v>1.19952630643385e-08</v>
+        <v>3.38673008171447e-08</v>
       </c>
       <c r="H70" t="n">
-        <v>6.404602484904017e-09</v>
+        <v/>
       </c>
       <c r="I70" t="n">
-        <v>4.502902085540498e-08</v>
+        <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1.001429995154315e-09</v>
+        <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.306787908526409e-11</v>
+        <v/>
+      </c>
+      <c r="F71" t="n">
+        <v/>
       </c>
       <c r="G71" t="n">
-        <v>2.3740842125893e-08</v>
+        <v/>
       </c>
       <c r="H71" t="n">
-        <v>-8.18257607746153e-10</v>
+        <v/>
       </c>
       <c r="I71" t="n">
-        <v>1.041531053387687e-06</v>
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>-7.040958170727577e-10</v>
+        <v/>
       </c>
       <c r="E72" t="n">
-        <v>-1.341129821989001e-09</v>
+        <v/>
+      </c>
+      <c r="F72" t="n">
+        <v>-1.811128153445419e-10</v>
       </c>
       <c r="G72" t="n">
-        <v>1.212781054846027e-08</v>
+        <v/>
       </c>
       <c r="H72" t="n">
-        <v>2.554319113288552e-09</v>
+        <v/>
       </c>
       <c r="I72" t="n">
-        <v>6.171844032690427e-08</v>
+        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>4.304265815948877e-09</v>
+        <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>1.434061503954947e-08</v>
+        <v/>
+      </c>
+      <c r="F73" t="n">
+        <v/>
       </c>
       <c r="G73" t="n">
-        <v>6.217486603195452e-08</v>
+        <v/>
       </c>
       <c r="H73" t="n">
-        <v>1.029241847430505e-08</v>
+        <v/>
       </c>
       <c r="I73" t="n">
-        <v>9.564412236309595e-07</v>
+        <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>4.395995110523724e-09</v>
+        <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>6.396766779207312e-09</v>
+        <v/>
       </c>
       <c r="F74" t="n">
-        <v>0.001</v>
+        <v/>
       </c>
       <c r="G74" t="n">
-        <v>4.343793830820923e-05</v>
+        <v/>
       </c>
       <c r="H74" t="n">
-        <v>5.237458664803053e-09</v>
+        <v/>
       </c>
       <c r="I74" t="n">
-        <v>5.425379457387429e-07</v>
+        <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>-1.624140235659063e-10</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>-2.889580833996713e-10</v>
+        <v/>
+      </c>
+      <c r="F75" t="n">
+        <v/>
       </c>
       <c r="G75" t="n">
-        <v>1.853646096703117e-08</v>
+        <v/>
       </c>
       <c r="H75" t="n">
-        <v>-1.811526244799593e-09</v>
+        <v/>
       </c>
       <c r="I75" t="n">
-        <v>9.221520440616795e-08</v>
+        <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1.051289102909028e-10</v>
+        <v/>
       </c>
       <c r="E76" t="n">
-        <v>3.811113117056199e-10</v>
+        <v/>
+      </c>
+      <c r="F76" t="n">
+        <v/>
       </c>
       <c r="G76" t="n">
-        <v>2.382495846322989e-08</v>
+        <v>-6.77346016342894e-08</v>
       </c>
       <c r="H76" t="n">
-        <v>-3.609060150042505e-10</v>
+        <v/>
       </c>
       <c r="I76" t="n">
-        <v>5.725066290334078e-07</v>
+        <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3640,30 +3817,33 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>-9.749580460899368e-10</v>
+        <v/>
       </c>
       <c r="E77" t="n">
-        <v>-2.38463778480189e-09</v>
+        <v/>
+      </c>
+      <c r="F77" t="n">
+        <v/>
       </c>
       <c r="G77" t="n">
-        <v>5.193298131845918e-09</v>
+        <v>3.38673008171447e-08</v>
       </c>
       <c r="H77" t="n">
-        <v>-4.099130917745893e-11</v>
+        <v/>
       </c>
       <c r="I77" t="n">
-        <v>3.016111997417425e-08</v>
+        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3672,30 +3852,33 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>3.412037156909342e-09</v>
+        <v/>
       </c>
       <c r="E78" t="n">
-        <v>6.583369641154007e-09</v>
+        <v>1</v>
+      </c>
+      <c r="F78" t="n">
+        <v/>
       </c>
       <c r="G78" t="n">
-        <v>2.161150798906071e-08</v>
+        <v/>
       </c>
       <c r="H78" t="n">
-        <v>1.292012793129952e-09</v>
+        <v/>
       </c>
       <c r="I78" t="n">
-        <v>1.298460411358062e-07</v>
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3704,156 +3887,138 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>4.369534843368405e-10</v>
+        <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>5.127256058136178e-10</v>
+        <v/>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
       </c>
       <c r="G79" t="n">
-        <v>2.160069948621438e-10</v>
+        <v/>
       </c>
       <c r="H79" t="n">
-        <v>1.189672981324364e-10</v>
+        <v/>
       </c>
       <c r="I79" t="n">
-        <v>3.540653928071976e-11</v>
+        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>-1.433573162497539e-09</v>
+        <v/>
       </c>
       <c r="E80" t="n">
-        <v>-1.651227479492252e-09</v>
+        <v/>
       </c>
       <c r="F80" t="n">
-        <v>0.001</v>
+        <v/>
       </c>
       <c r="G80" t="n">
-        <v>9.107758958774035e-09</v>
+        <v>1</v>
       </c>
       <c r="H80" t="n">
-        <v>5.098454465853442e-09</v>
+        <v/>
       </c>
       <c r="I80" t="n">
-        <v>4.389711093255708e-08</v>
+        <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>8.569828426785249e-11</v>
+        <v/>
       </c>
       <c r="E81" t="n">
-        <v>-8.268625367966698e-11</v>
+        <v/>
+      </c>
+      <c r="F81" t="n">
+        <v/>
       </c>
       <c r="G81" t="n">
-        <v>1.486195893928572e-08</v>
+        <v>-1.016019024514341e-07</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.081135507565191e-10</v>
+        <v>1</v>
       </c>
       <c r="I81" t="n">
-        <v>5.716370187734083e-07</v>
+        <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>-1.144976207895416e-09</v>
-      </c>
-      <c r="E82" t="n">
-        <v>-2.380720494183074e-09</v>
-      </c>
-      <c r="G82" t="n">
-        <v>7.184597226984613e-09</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-8.666677225518909e-10</v>
-      </c>
-      <c r="I82" t="n">
-        <v>3.395377090288282e-08</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>-1.645440384332685e-09</v>
-      </c>
-      <c r="E83" t="n">
-        <v>-1.350652140542181e-09</v>
-      </c>
-      <c r="G83" t="n">
-        <v>1.708099288378726e-08</v>
-      </c>
-      <c r="H83" t="n">
-        <v>-5.5802766510101e-10</v>
-      </c>
-      <c r="I83" t="n">
-        <v>6.188177481766155e-08</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3863,96 +4028,57 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>-9.557657838990758e-10</v>
-      </c>
-      <c r="E84" t="n">
-        <v>-7.306271521393815e-10</v>
-      </c>
-      <c r="G84" t="n">
-        <v>-3.563786016042888e-10</v>
-      </c>
-      <c r="H84" t="n">
-        <v>-5.662341764291614e-10</v>
-      </c>
-      <c r="I84" t="n">
-        <v>3.78031397516662e-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>i4</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>-1.69299871359458e-09</v>
+          <t>i2</t>
+        </is>
       </c>
       <c r="E85" t="n">
-        <v>-1.6473153104049e-09</v>
-      </c>
-      <c r="G85" t="n">
-        <v>2.239014954092432e-08</v>
-      </c>
-      <c r="H85" t="n">
-        <v>-4.17742431741503e-10</v>
-      </c>
-      <c r="I85" t="n">
-        <v>6.05116014534763e-08</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>-2.188857970132695e-09</v>
-      </c>
-      <c r="E86" t="n">
-        <v>-2.189604757415947e-09</v>
+          <t>i3</t>
+        </is>
       </c>
       <c r="F86" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="G86" t="n">
-        <v>1.06535988463539e-08</v>
-      </c>
-      <c r="H86" t="n">
-        <v>-1.71354658456293e-09</v>
-      </c>
-      <c r="I86" t="n">
-        <v>7.930943562958284e-08</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3962,32 +4088,20 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>-8.968225070056816e-10</v>
-      </c>
-      <c r="E87" t="n">
-        <v>-2.336744826379925e-09</v>
-      </c>
-      <c r="F87" t="n">
-        <v>0.001</v>
+        <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>7.535180055217757e-09</v>
-      </c>
-      <c r="H87" t="n">
-        <v>-1.332815463344029e-09</v>
-      </c>
-      <c r="I87" t="n">
-        <v>1.851398037105388e-08</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3997,23 +4111,11 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>i2</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>-8.826374317024207e-10</v>
-      </c>
-      <c r="E88" t="n">
-        <v>-3.766699994193902e-10</v>
-      </c>
-      <c r="G88" t="n">
-        <v>1.575486147982359e-08</v>
+          <t>i5</t>
+        </is>
       </c>
       <c r="H88" t="n">
-        <v>-1.251358642344008e-09</v>
-      </c>
-      <c r="I88" t="n">
-        <v>2.922374297959627e-08</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -8268,7 +8370,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>2.738168111972305</v>
+        <v>1.65297629265167</v>
       </c>
     </row>
   </sheetData>
@@ -8287,7 +8389,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>0.2091415</v>
+        <v>7608.812000000034</v>
       </c>
     </row>
   </sheetData>

--- a/6node_spain/output_all.xlsx
+++ b/6node_spain/output_all.xlsx
@@ -460,16 +460,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.391031980694962</v>
+        <v>1.406382439326014</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1357915304721569</v>
+        <v>0.5296187857592148</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07461260996186911</v>
+        <v>0.07461260976955639</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -532,13 +532,13 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1.096859523003464</v>
+        <v>1.506037194355334</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9602409412334014</v>
+        <v>0.9602409416628575</v>
       </c>
     </row>
   </sheetData>
@@ -628,13 +628,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1.448378918720291</v>
+        <v>1.473962980448705</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8700077157713119</v>
+        <v>0.8700077517613194</v>
       </c>
     </row>
     <row r="4">
@@ -653,10 +653,10 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
+        <v>0.656378759174014</v>
+      </c>
+      <c r="F4" t="n">
         <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3.622506309480824e-10</v>
       </c>
       <c r="G4" t="n">
         <v>0.2263192170913441</v>
@@ -672,10 +672,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>1.448378918720291</v>
+        <v>1.473962980448705</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.656378759174014</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -684,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3797202862854819</v>
+        <v>0.3797202509695052</v>
       </c>
     </row>
     <row r="6">
@@ -700,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>3.622506309480824e-10</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1243543495741979</v>
+        <v>0.1243543496159273</v>
       </c>
     </row>
     <row r="7">
@@ -722,16 +722,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8700077157713119</v>
+        <v>0.8700077517613194</v>
       </c>
       <c r="D7" t="n">
         <v>0.2263192170913441</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3797202862854819</v>
+        <v>0.3797202509695052</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1243543495741979</v>
+        <v>0.1243543496159273</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1525911632724586</v>
+        <v>0.1552865226773181</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1750426713701295</v>
+        <v>0.1750426786111998</v>
       </c>
     </row>
     <row r="4">
@@ -849,7 +849,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.1831886571542683</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -865,13 +865,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>-2.324848983848287e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1510158417849385</v>
+        <v>0.1536833748236048</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.1816113132018588</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -880,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1648651746285813</v>
+        <v>0.1648651592952561</v>
       </c>
     </row>
     <row r="6">
@@ -896,7 +896,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>9.103758557183757e-11</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -905,7 +905,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.232243468841142</v>
+        <v>0.2322434689190756</v>
       </c>
     </row>
     <row r="7">
@@ -918,16 +918,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1766599629615699</v>
+        <v>0.1766599702695435</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2888833065891823</v>
+        <v>0.2888833059334618</v>
       </c>
       <c r="E7" t="n">
-        <v>0.166077538485157</v>
+        <v>0.1660775230390755</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2323170723070234</v>
+        <v>0.2323170723849818</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1020,13 +1020,13 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8474088367275414</v>
+        <v>0.8447134773226819</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8249573286298706</v>
+        <v>0.8249573213888002</v>
       </c>
     </row>
     <row r="4">
@@ -1045,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0.8168113428457316</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>1.000000000232485</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8489841582150615</v>
+        <v>0.8463166251763952</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0.8183886867981411</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -1076,7 +1076,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8351348253714187</v>
+        <v>0.835134840704744</v>
       </c>
     </row>
     <row r="6">
@@ -1092,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0.9999999999089624</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.767756531158858</v>
+        <v>0.7677565310809243</v>
       </c>
     </row>
     <row r="7">
@@ -1114,16 +1114,16 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8233400370384301</v>
+        <v>0.8233400297304565</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7111166934108177</v>
+        <v>0.7111166940665381</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8339224615148431</v>
+        <v>0.8339224769609246</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7676829276929766</v>
+        <v>0.7676829276150182</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1195,19 +1195,19 @@
         <v/>
       </c>
       <c r="E2" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G2" t="n">
         <v/>
       </c>
       <c r="H2" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -1233,13 +1233,13 @@
         <v/>
       </c>
       <c r="F3" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v/>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I3" t="n">
         <v/>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1271,13 +1271,13 @@
         <v/>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H4" t="n">
-        <v>1.127819096249323e-10</v>
+        <v/>
       </c>
       <c r="I4" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1306,10 +1306,10 @@
         <v/>
       </c>
       <c r="G5" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.127819096249323e-10</v>
+        <v/>
       </c>
       <c r="I5" t="n">
         <v/>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1338,13 +1338,13 @@
         <v/>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G6" t="n">
         <v/>
       </c>
       <c r="H6" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1379,7 +1379,7 @@
         <v/>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>1.173088512049844e-10</v>
       </c>
       <c r="I7" t="n">
         <v/>
@@ -1393,19 +1393,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v/>
       </c>
       <c r="E8" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v/>
@@ -1414,7 +1414,7 @@
         <v/>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I8" t="n">
         <v/>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1449,10 +1449,10 @@
         <v/>
       </c>
       <c r="H9" t="n">
-        <v>1.000000000112782</v>
+        <v/>
       </c>
       <c r="I9" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1475,7 +1475,7 @@
         <v/>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F10" t="n">
         <v/>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1519,7 +1519,7 @@
         <v/>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>1.173088512049844e-10</v>
       </c>
       <c r="I11" t="n">
         <v/>
@@ -1533,28 +1533,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v/>
       </c>
       <c r="E12" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G12" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>1.127819096249323e-10</v>
+        <v/>
       </c>
       <c r="I12" t="n">
         <v/>
@@ -1563,33 +1563,33 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v/>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F13" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
         <v/>
       </c>
       <c r="H13" t="n">
-        <v>1.127819096249323e-10</v>
+        <v/>
       </c>
       <c r="I13" t="n">
         <v/>
@@ -1598,17 +1598,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1618,10 +1618,10 @@
         <v/>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G14" t="n">
-        <v/>
+        <v>1.710505649340702e-10</v>
       </c>
       <c r="H14" t="n">
         <v/>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1653,13 +1653,13 @@
         <v/>
       </c>
       <c r="F15" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v/>
+        <v>1.710505649340702e-10</v>
       </c>
       <c r="H15" t="n">
-        <v>1.000000000018537</v>
+        <v/>
       </c>
       <c r="I15" t="n">
         <v/>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1691,7 +1691,7 @@
         <v/>
       </c>
       <c r="G16" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1726,10 +1726,10 @@
         <v/>
       </c>
       <c r="G17" t="n">
-        <v/>
+        <v>-1.710505649340702e-10</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I17" t="n">
         <v/>
@@ -1748,17 +1748,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
         <v/>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G18" t="n">
         <v/>
@@ -1767,7 +1767,7 @@
         <v/>
       </c>
       <c r="I18" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1796,10 +1796,10 @@
         <v/>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H19" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
         <v/>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1834,10 +1834,10 @@
         <v/>
       </c>
       <c r="H20" t="n">
-        <v/>
+        <v>6.424589749087772e-10</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -1848,12 +1848,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1863,13 +1863,13 @@
         <v/>
       </c>
       <c r="F21" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
         <v/>
       </c>
       <c r="H21" t="n">
-        <v>1.000000000018537</v>
+        <v>1.000000000642459</v>
       </c>
       <c r="I21" t="n">
         <v/>
@@ -1888,11 +1888,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E22" t="n">
         <v/>
@@ -1904,7 +1904,7 @@
         <v/>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>-6.424589749087772e-10</v>
       </c>
       <c r="I22" t="n">
         <v/>
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1953,25 +1953,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E24" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
         <v/>
       </c>
       <c r="G24" t="n">
-        <v>-4.867070237402924e-10</v>
+        <v/>
       </c>
       <c r="H24" t="n">
         <v/>
@@ -1988,12 +1988,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -2006,10 +2006,10 @@
         <v/>
       </c>
       <c r="G25" t="n">
-        <v>4.867070237402924e-10</v>
+        <v/>
       </c>
       <c r="H25" t="n">
-        <v/>
+        <v>0.999999999961954</v>
       </c>
       <c r="I25" t="n">
         <v/>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2035,13 +2035,13 @@
         <v/>
       </c>
       <c r="E26" t="n">
-        <v/>
+        <v>-1.30242444540798e-10</v>
       </c>
       <c r="F26" t="n">
         <v/>
       </c>
       <c r="G26" t="n">
-        <v>-2.469527914385539e-10</v>
+        <v/>
       </c>
       <c r="H26" t="n">
         <v/>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2076,10 +2076,10 @@
         <v/>
       </c>
       <c r="G27" t="n">
-        <v>4.867070237402924e-10</v>
+        <v/>
       </c>
       <c r="H27" t="n">
-        <v/>
+        <v>0.999999999961954</v>
       </c>
       <c r="I27" t="n">
         <v/>
@@ -2098,14 +2098,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E28" t="n">
-        <v/>
+        <v>0.9999999998697575</v>
       </c>
       <c r="F28" t="n">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
         <v/>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v/>
+        <v>1.30242444540798e-10</v>
       </c>
       <c r="F30" t="n">
         <v/>
@@ -2184,7 +2184,7 @@
         <v/>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I30" t="n">
         <v/>
@@ -2210,7 +2210,7 @@
         <v/>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F31" t="n">
         <v/>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2280,7 +2280,7 @@
         <v/>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F33" t="n">
         <v/>
@@ -2289,7 +2289,7 @@
         <v/>
       </c>
       <c r="H33" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
         <v/>
@@ -2303,16 +2303,16 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
         <v/>
@@ -2321,7 +2321,7 @@
         <v/>
       </c>
       <c r="G34" t="n">
-        <v>-2.469527914385539e-10</v>
+        <v/>
       </c>
       <c r="H34" t="n">
         <v/>
@@ -2343,14 +2343,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E35" t="n">
-        <v/>
+        <v>-1.30242444540798e-10</v>
       </c>
       <c r="F35" t="n">
         <v/>
@@ -2368,24 +2368,24 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v/>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F36" t="n">
         <v/>
@@ -2394,7 +2394,7 @@
         <v/>
       </c>
       <c r="H36" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
         <v/>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -2429,10 +2429,10 @@
         <v/>
       </c>
       <c r="H37" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>-2.751516060051469e-10</v>
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -2458,13 +2458,13 @@
         <v/>
       </c>
       <c r="F38" t="n">
-        <v>3.261399125969135e-10</v>
+        <v/>
       </c>
       <c r="G38" t="n">
         <v/>
       </c>
       <c r="H38" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
         <v/>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
         <v/>
@@ -2502,7 +2502,7 @@
         <v/>
       </c>
       <c r="I39" t="n">
-        <v>-2.751516060051469e-10</v>
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -2528,13 +2528,13 @@
         <v/>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G40" t="n">
         <v/>
       </c>
       <c r="H40" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
         <v/>
@@ -2548,16 +2548,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E41" t="n">
         <v/>
@@ -2569,7 +2569,7 @@
         <v/>
       </c>
       <c r="H41" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
         <v/>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E43" t="n">
         <v/>
@@ -2639,7 +2639,7 @@
         <v/>
       </c>
       <c r="H43" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
         <v/>
@@ -2668,7 +2668,7 @@
         <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G44" t="n">
         <v/>
@@ -2677,7 +2677,7 @@
         <v/>
       </c>
       <c r="I44" t="n">
-        <v>-2.751516060051469e-10</v>
+        <v/>
       </c>
     </row>
     <row r="45">
@@ -2703,7 +2703,7 @@
         <v/>
       </c>
       <c r="F45" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
         <v/>
@@ -2712,7 +2712,7 @@
         <v/>
       </c>
       <c r="I45" t="n">
-        <v>2.751516060051469e-10</v>
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
         <v/>
@@ -2744,7 +2744,7 @@
         <v/>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I46" t="n">
         <v/>
@@ -2798,17 +2798,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
         <v/>
       </c>
       <c r="F48" t="n">
-        <v>3.261399125969135e-10</v>
+        <v/>
       </c>
       <c r="G48" t="n">
         <v/>
@@ -2833,11 +2833,11 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.9999999999237215</v>
+        <v/>
       </c>
       <c r="E49" t="n">
         <v/>
@@ -2849,7 +2849,7 @@
         <v/>
       </c>
       <c r="H49" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I49" t="n">
         <v/>
@@ -2858,24 +2858,24 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D50" t="n">
         <v/>
       </c>
       <c r="E50" t="n">
-        <v>4.778789306492098e-10</v>
+        <v/>
       </c>
       <c r="F50" t="n">
         <v/>
@@ -2884,7 +2884,7 @@
         <v/>
       </c>
       <c r="H50" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
         <v/>
@@ -2903,14 +2903,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D51" t="n">
         <v/>
       </c>
       <c r="E51" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
         <v/>
@@ -2922,7 +2922,7 @@
         <v/>
       </c>
       <c r="I51" t="n">
-        <v>-2.099990461856482e-09</v>
+        <v/>
       </c>
     </row>
     <row r="52">
@@ -2933,22 +2933,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E52" t="n">
-        <v/>
+        <v>0.9999999999225868</v>
       </c>
       <c r="F52" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
         <v/>
@@ -2968,22 +2968,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E53" t="n">
-        <v>3.716836127293384e-10</v>
+        <v/>
       </c>
       <c r="F53" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
         <v/>
@@ -3008,14 +3008,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D54" t="n">
         <v/>
       </c>
       <c r="E54" t="n">
-        <v>-3.716836127293384e-10</v>
+        <v>1</v>
       </c>
       <c r="F54" t="n">
         <v/>
@@ -3038,19 +3038,19 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D55" t="n">
         <v/>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F55" t="n">
         <v/>
@@ -3062,7 +3062,7 @@
         <v/>
       </c>
       <c r="I55" t="n">
-        <v>2.099990461856482e-09</v>
+        <v>-1.409024126345298e-10</v>
       </c>
     </row>
     <row r="56">
@@ -3082,10 +3082,10 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.778789306492098e-10</v>
+        <v>0.9999999999225868</v>
       </c>
       <c r="F56" t="n">
         <v/>
@@ -3097,7 +3097,7 @@
         <v/>
       </c>
       <c r="I56" t="n">
-        <v>-2.099990461856482e-09</v>
+        <v/>
       </c>
     </row>
     <row r="57">
@@ -3120,10 +3120,10 @@
         <v/>
       </c>
       <c r="E57" t="n">
-        <v>-4.778789306492098e-10</v>
+        <v/>
       </c>
       <c r="F57" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G57" t="n">
         <v/>
@@ -3152,13 +3152,13 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E58" t="n">
         <v/>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G58" t="n">
         <v/>
@@ -3167,7 +3167,7 @@
         <v/>
       </c>
       <c r="I58" t="n">
-        <v/>
+        <v>-1.409024126345298e-10</v>
       </c>
     </row>
     <row r="59">
@@ -3190,7 +3190,7 @@
         <v/>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F59" t="n">
         <v/>
@@ -3202,7 +3202,7 @@
         <v/>
       </c>
       <c r="I59" t="n">
-        <v>2.099990461856482e-09</v>
+        <v/>
       </c>
     </row>
     <row r="60">
@@ -3243,30 +3243,30 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D61" t="n">
         <v/>
       </c>
       <c r="E61" t="n">
-        <v>0.9999999996283164</v>
+        <v/>
       </c>
       <c r="F61" t="n">
         <v/>
       </c>
       <c r="G61" t="n">
-        <v/>
+        <v>1.494959298881737e-08</v>
       </c>
       <c r="H61" t="n">
         <v/>
@@ -3283,16 +3283,16 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E62" t="n">
         <v/>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="G62" t="n">
-        <v>1.904637672416955e-08</v>
+        <v/>
       </c>
       <c r="H62" t="n">
         <v/>
@@ -3318,12 +3318,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -3336,7 +3336,7 @@
         <v/>
       </c>
       <c r="G63" t="n">
-        <v>1.482092409297515e-08</v>
+        <v>-4.60113485276439e-09</v>
       </c>
       <c r="H63" t="n">
         <v/>
@@ -3353,22 +3353,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E64" t="n">
         <v/>
       </c>
       <c r="F64" t="n">
-        <v>-1.811128153445419e-10</v>
+        <v/>
       </c>
       <c r="G64" t="n">
         <v/>
@@ -3388,22 +3388,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E65" t="n">
         <v/>
       </c>
       <c r="F65" t="n">
-        <v>-1.811128153445419e-10</v>
+        <v/>
       </c>
       <c r="G65" t="n">
         <v/>
@@ -3423,16 +3423,16 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E66" t="n">
         <v/>
@@ -3441,7 +3441,7 @@
         <v/>
       </c>
       <c r="G66" t="n">
-        <v>1.482092409297515e-08</v>
+        <v>4.601134852764388e-09</v>
       </c>
       <c r="H66" t="n">
         <v/>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3476,7 +3476,7 @@
         <v/>
       </c>
       <c r="G67" t="n">
-        <v/>
+        <v>-1.034845813605298e-08</v>
       </c>
       <c r="H67" t="n">
         <v/>
@@ -3493,16 +3493,16 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E68" t="n">
         <v/>
@@ -3511,7 +3511,7 @@
         <v/>
       </c>
       <c r="G68" t="n">
-        <v>-4.225452631194397e-09</v>
+        <v>1.034845813605298e-08</v>
       </c>
       <c r="H68" t="n">
         <v/>
@@ -3528,19 +3528,19 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E69" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
         <v/>
@@ -3563,12 +3563,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -3578,10 +3578,10 @@
         <v/>
       </c>
       <c r="F70" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>3.38673008171447e-08</v>
+        <v>-4.60113485276439e-09</v>
       </c>
       <c r="H70" t="n">
         <v/>
@@ -3598,16 +3598,16 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E71" t="n">
         <v/>
@@ -3616,7 +3616,7 @@
         <v/>
       </c>
       <c r="G71" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H71" t="n">
         <v/>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -3648,13 +3648,13 @@
         <v/>
       </c>
       <c r="F72" t="n">
-        <v>-1.811128153445419e-10</v>
+        <v/>
       </c>
       <c r="G72" t="n">
-        <v/>
+        <v>-2.069691627210596e-08</v>
       </c>
       <c r="H72" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I72" t="n">
         <v/>
@@ -3679,21 +3679,6 @@
       <c r="D73" t="n">
         <v>1</v>
       </c>
-      <c r="E73" t="n">
-        <v/>
-      </c>
-      <c r="F73" t="n">
-        <v/>
-      </c>
-      <c r="G73" t="n">
-        <v/>
-      </c>
-      <c r="H73" t="n">
-        <v/>
-      </c>
-      <c r="I73" t="n">
-        <v/>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3714,21 +3699,6 @@
       <c r="D74" t="n">
         <v>1</v>
       </c>
-      <c r="E74" t="n">
-        <v/>
-      </c>
-      <c r="F74" t="n">
-        <v/>
-      </c>
-      <c r="G74" t="n">
-        <v/>
-      </c>
-      <c r="H74" t="n">
-        <v/>
-      </c>
-      <c r="I74" t="n">
-        <v/>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3749,21 +3719,6 @@
       <c r="D75" t="n">
         <v>1</v>
       </c>
-      <c r="E75" t="n">
-        <v/>
-      </c>
-      <c r="F75" t="n">
-        <v/>
-      </c>
-      <c r="G75" t="n">
-        <v/>
-      </c>
-      <c r="H75" t="n">
-        <v/>
-      </c>
-      <c r="I75" t="n">
-        <v/>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3781,24 +3736,9 @@
           <t>i4</t>
         </is>
       </c>
-      <c r="D76" t="n">
-        <v/>
-      </c>
-      <c r="E76" t="n">
-        <v/>
-      </c>
-      <c r="F76" t="n">
-        <v/>
-      </c>
       <c r="G76" t="n">
         <v>-6.77346016342894e-08</v>
       </c>
-      <c r="H76" t="n">
-        <v/>
-      </c>
-      <c r="I76" t="n">
-        <v/>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3816,24 +3756,9 @@
           <t>i1</t>
         </is>
       </c>
-      <c r="D77" t="n">
-        <v/>
-      </c>
-      <c r="E77" t="n">
-        <v/>
-      </c>
-      <c r="F77" t="n">
-        <v/>
-      </c>
       <c r="G77" t="n">
         <v>3.38673008171447e-08</v>
       </c>
-      <c r="H77" t="n">
-        <v/>
-      </c>
-      <c r="I77" t="n">
-        <v/>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3851,23 +3776,8 @@
           <t>i2</t>
         </is>
       </c>
-      <c r="D78" t="n">
-        <v/>
-      </c>
       <c r="E78" t="n">
         <v>1</v>
-      </c>
-      <c r="F78" t="n">
-        <v/>
-      </c>
-      <c r="G78" t="n">
-        <v/>
-      </c>
-      <c r="H78" t="n">
-        <v/>
-      </c>
-      <c r="I78" t="n">
-        <v/>
       </c>
     </row>
     <row r="79">
@@ -3889,20 +3799,8 @@
       <c r="D79" t="n">
         <v>1</v>
       </c>
-      <c r="E79" t="n">
-        <v/>
-      </c>
       <c r="F79" t="n">
         <v>1</v>
-      </c>
-      <c r="G79" t="n">
-        <v/>
-      </c>
-      <c r="H79" t="n">
-        <v/>
-      </c>
-      <c r="I79" t="n">
-        <v/>
       </c>
     </row>
     <row r="80">
@@ -3921,23 +3819,8 @@
           <t>i4</t>
         </is>
       </c>
-      <c r="D80" t="n">
-        <v/>
-      </c>
-      <c r="E80" t="n">
-        <v/>
-      </c>
-      <c r="F80" t="n">
-        <v/>
-      </c>
       <c r="G80" t="n">
         <v>1</v>
-      </c>
-      <c r="H80" t="n">
-        <v/>
-      </c>
-      <c r="I80" t="n">
-        <v/>
       </c>
     </row>
     <row r="81">
@@ -3956,23 +3839,11 @@
           <t>i5</t>
         </is>
       </c>
-      <c r="D81" t="n">
-        <v/>
-      </c>
-      <c r="E81" t="n">
-        <v/>
-      </c>
-      <c r="F81" t="n">
-        <v/>
-      </c>
       <c r="G81" t="n">
         <v>-1.016019024514341e-07</v>
       </c>
       <c r="H81" t="n">
         <v>1</v>
-      </c>
-      <c r="I81" t="n">
-        <v/>
       </c>
     </row>
     <row r="82">
@@ -8370,7 +8241,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>1.65297629265167</v>
+        <v>1.549048494029569</v>
       </c>
     </row>
   </sheetData>
@@ -8389,7 +8260,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>7608.812000000034</v>
+        <v>7217.391000000003</v>
       </c>
     </row>
   </sheetData>

--- a/6node_spain/output_all.xlsx
+++ b/6node_spain/output_all.xlsx
@@ -460,19 +460,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.406382439326014</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5296187857592148</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07461260976955639</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.4878048780487805</v>
       </c>
     </row>
   </sheetData>
@@ -526,19 +526,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.4878048780487805</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1.506037194355334</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9602409416628575</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -628,13 +628,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1.473962980448705</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8700077517613194</v>
+        <v>0.8130081300813008</v>
       </c>
     </row>
     <row r="4">
@@ -653,13 +653,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.656378759174014</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2263192170913441</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -672,10 +672,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>1.473962980448705</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.656378759174014</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -684,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3797202509695052</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -709,7 +709,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1243543496159273</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -722,16 +722,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8700077517613194</v>
+        <v>0.8130081300813008</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2263192170913441</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3797202509695052</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1243543496159273</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1552865226773181</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1750426786111998</v>
+        <v>0.1635745434842467</v>
       </c>
     </row>
     <row r="4">
@@ -849,13 +849,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1831886571542683</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2974497558473439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -865,13 +865,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-2.324848983848287e-10</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1536833748236048</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1816113132018588</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -880,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1648651592952561</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -896,7 +896,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>9.103758557183757e-11</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -905,7 +905,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2322434689190756</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -918,16 +918,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1766599702695435</v>
+        <v>0.1650858763020109</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2888833059334618</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1660775230390755</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2323170723849818</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1020,13 +1020,13 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8447134773226819</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8249573213888002</v>
+        <v>0.8364254565157533</v>
       </c>
     </row>
     <row r="4">
@@ -1045,13 +1045,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8168113428457316</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7025502441526561</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.000000000232485</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8463166251763952</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8183886867981411</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -1076,7 +1076,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.835134840704744</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1092,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9999999999089624</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7677565310809243</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1114,16 +1114,16 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8233400297304565</v>
+        <v>0.8349141236979891</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7111166940665381</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8339224769609246</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7676829276150182</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1195,16 +1195,16 @@
         <v/>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F2" t="n">
         <v/>
       </c>
       <c r="G2" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I2" t="n">
         <v/>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1338,13 +1338,13 @@
         <v/>
       </c>
       <c r="F6" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v/>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -1358,19 +1358,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v/>
       </c>
       <c r="E7" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v/>
@@ -1379,7 +1379,7 @@
         <v/>
       </c>
       <c r="H7" t="n">
-        <v>1.173088512049844e-10</v>
+        <v/>
       </c>
       <c r="I7" t="n">
         <v/>
@@ -1398,14 +1398,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v/>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F8" t="n">
         <v/>
@@ -1417,7 +1417,7 @@
         <v/>
       </c>
       <c r="I8" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1433,14 +1433,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v/>
       </c>
       <c r="E9" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v/>
@@ -1452,7 +1452,7 @@
         <v/>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1478,7 +1478,7 @@
         <v/>
       </c>
       <c r="F10" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v/>
@@ -1487,23 +1487,23 @@
         <v/>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1513,13 +1513,13 @@
         <v/>
       </c>
       <c r="F11" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
         <v/>
       </c>
       <c r="H11" t="n">
-        <v>1.173088512049844e-10</v>
+        <v/>
       </c>
       <c r="I11" t="n">
         <v/>
@@ -1528,33 +1528,33 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v/>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F12" t="n">
         <v/>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H12" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v/>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1603,12 +1603,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1618,13 +1618,13 @@
         <v/>
       </c>
       <c r="F14" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>1.710505649340702e-10</v>
+        <v/>
       </c>
       <c r="H14" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v/>
@@ -1643,20 +1643,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v/>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G15" t="n">
-        <v>1.710505649340702e-10</v>
+        <v/>
       </c>
       <c r="H15" t="n">
         <v/>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1691,13 +1691,13 @@
         <v/>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I16" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1726,7 +1726,7 @@
         <v/>
       </c>
       <c r="G17" t="n">
-        <v>-1.710505649340702e-10</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v/>
@@ -1743,22 +1743,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E18" t="n">
         <v/>
       </c>
       <c r="F18" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
         <v/>
@@ -1767,7 +1767,7 @@
         <v/>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1793,13 +1793,13 @@
         <v/>
       </c>
       <c r="F19" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
         <v/>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I19" t="n">
         <v/>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1828,13 +1828,13 @@
         <v/>
       </c>
       <c r="F20" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
         <v/>
       </c>
       <c r="H20" t="n">
-        <v>6.424589749087772e-10</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
         <v/>
@@ -1848,28 +1848,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v/>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G21" t="n">
         <v/>
       </c>
       <c r="H21" t="n">
-        <v>1.000000000642459</v>
+        <v/>
       </c>
       <c r="I21" t="n">
         <v/>
@@ -1883,12 +1883,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1898,13 +1898,13 @@
         <v/>
       </c>
       <c r="F22" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
         <v/>
       </c>
       <c r="H22" t="n">
-        <v>-6.424589749087772e-10</v>
+        <v/>
       </c>
       <c r="I22" t="n">
         <v/>
@@ -1923,20 +1923,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E23" t="n">
         <v/>
       </c>
       <c r="F23" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
         <v/>
@@ -1948,33 +1948,33 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v/>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F24" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
         <v/>
       </c>
       <c r="H24" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v/>
@@ -1988,16 +1988,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v/>
@@ -2006,10 +2006,10 @@
         <v/>
       </c>
       <c r="G25" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>0.999999999961954</v>
+        <v/>
       </c>
       <c r="I25" t="n">
         <v/>
@@ -2023,25 +2023,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v/>
       </c>
       <c r="E26" t="n">
-        <v>-1.30242444540798e-10</v>
+        <v/>
       </c>
       <c r="F26" t="n">
         <v/>
       </c>
       <c r="G26" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
         <v/>
@@ -2058,16 +2058,16 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
         <v/>
@@ -2079,10 +2079,10 @@
         <v/>
       </c>
       <c r="H27" t="n">
-        <v>0.999999999961954</v>
+        <v/>
       </c>
       <c r="I27" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9999999998697575</v>
+        <v/>
       </c>
       <c r="F28" t="n">
         <v/>
@@ -2128,12 +2128,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -2146,13 +2146,13 @@
         <v/>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I29" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2163,19 +2163,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>1.30242444540798e-10</v>
+        <v/>
       </c>
       <c r="F30" t="n">
         <v/>
@@ -2198,12 +2198,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -2233,16 +2233,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E32" t="n">
         <v/>
@@ -2251,13 +2251,13 @@
         <v/>
       </c>
       <c r="G32" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
         <v/>
       </c>
       <c r="I32" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -2286,10 +2286,10 @@
         <v/>
       </c>
       <c r="G33" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I33" t="n">
         <v/>
@@ -2298,17 +2298,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -2333,24 +2333,24 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.30242444540798e-10</v>
+        <v/>
       </c>
       <c r="F35" t="n">
         <v/>
@@ -2373,12 +2373,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -2394,10 +2394,10 @@
         <v/>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I36" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2408,19 +2408,19 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D37" t="n">
         <v/>
       </c>
       <c r="E37" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
         <v/>
@@ -2429,7 +2429,7 @@
         <v/>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I37" t="n">
         <v/>
@@ -2443,16 +2443,16 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
         <v/>
@@ -2464,10 +2464,10 @@
         <v/>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I38" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2478,22 +2478,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E39" t="n">
         <v/>
       </c>
       <c r="F39" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
         <v/>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -2534,10 +2534,10 @@
         <v/>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I40" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2548,16 +2548,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
         <v/>
@@ -2569,10 +2569,10 @@
         <v/>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I41" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -2633,13 +2633,13 @@
         <v/>
       </c>
       <c r="F43" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
         <v/>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I43" t="n">
         <v/>
@@ -2648,12 +2648,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2683,12 +2683,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2703,7 +2703,7 @@
         <v/>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G45" t="n">
         <v/>
@@ -2712,30 +2712,30 @@
         <v/>
       </c>
       <c r="I45" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E46" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
         <v/>
@@ -2753,12 +2753,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
         <v/>
@@ -2782,27 +2782,27 @@
         <v/>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E48" t="n">
         <v/>
@@ -2817,30 +2817,30 @@
         <v/>
       </c>
       <c r="I48" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D49" t="n">
         <v/>
       </c>
       <c r="E49" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v/>
@@ -2849,7 +2849,7 @@
         <v/>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I49" t="n">
         <v/>
@@ -2858,24 +2858,24 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D50" t="n">
         <v/>
       </c>
       <c r="E50" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
         <v/>
@@ -2884,7 +2884,7 @@
         <v/>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I50" t="n">
         <v/>
@@ -2898,12 +2898,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2933,22 +2933,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>0.9999999999225868</v>
+        <v/>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G52" t="n">
         <v/>
@@ -2963,17 +2963,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2983,10 +2983,10 @@
         <v/>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G53" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
         <v/>
@@ -2998,30 +2998,30 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D54" t="n">
         <v/>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F54" t="n">
         <v/>
       </c>
       <c r="G54" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H54" t="n">
         <v/>
@@ -3033,17 +3033,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -3056,39 +3056,39 @@
         <v/>
       </c>
       <c r="G55" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H55" t="n">
         <v/>
       </c>
       <c r="I55" t="n">
-        <v>-1.409024126345298e-10</v>
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E56" t="n">
-        <v>0.9999999999225868</v>
+        <v/>
       </c>
       <c r="F56" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
         <v/>
@@ -3103,27 +3103,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E57" t="n">
         <v/>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G57" t="n">
         <v/>
@@ -3138,21 +3138,21 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
         <v/>
@@ -3167,27 +3167,27 @@
         <v/>
       </c>
       <c r="I58" t="n">
-        <v>-1.409024126345298e-10</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
         <v/>
@@ -3196,7 +3196,7 @@
         <v/>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H59" t="n">
         <v/>
@@ -3208,17 +3208,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -3228,7 +3228,7 @@
         <v/>
       </c>
       <c r="F60" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G60" t="n">
         <v/>
@@ -3237,7 +3237,7 @@
         <v/>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="61">
@@ -3248,12 +3248,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -3266,7 +3266,7 @@
         <v/>
       </c>
       <c r="G61" t="n">
-        <v>1.494959298881737e-08</v>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
         <v/>
@@ -3283,22 +3283,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E62" t="n">
         <v/>
       </c>
       <c r="F62" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G62" t="n">
         <v/>
@@ -3318,16 +3318,16 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
         <v/>
@@ -3336,7 +3336,7 @@
         <v/>
       </c>
       <c r="G63" t="n">
-        <v>-4.60113485276439e-09</v>
+        <v/>
       </c>
       <c r="H63" t="n">
         <v/>
@@ -3353,22 +3353,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E64" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G64" t="n">
         <v/>
@@ -3399,21 +3399,6 @@
       <c r="D65" t="n">
         <v>1</v>
       </c>
-      <c r="E65" t="n">
-        <v/>
-      </c>
-      <c r="F65" t="n">
-        <v/>
-      </c>
-      <c r="G65" t="n">
-        <v/>
-      </c>
-      <c r="H65" t="n">
-        <v/>
-      </c>
-      <c r="I65" t="n">
-        <v/>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3431,24 +3416,9 @@
           <t>i1</t>
         </is>
       </c>
-      <c r="D66" t="n">
-        <v/>
-      </c>
-      <c r="E66" t="n">
-        <v/>
-      </c>
-      <c r="F66" t="n">
-        <v/>
-      </c>
       <c r="G66" t="n">
         <v>4.601134852764388e-09</v>
       </c>
-      <c r="H66" t="n">
-        <v/>
-      </c>
-      <c r="I66" t="n">
-        <v/>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3469,21 +3439,9 @@
       <c r="D67" t="n">
         <v>1</v>
       </c>
-      <c r="E67" t="n">
-        <v/>
-      </c>
-      <c r="F67" t="n">
-        <v/>
-      </c>
       <c r="G67" t="n">
         <v>-1.034845813605298e-08</v>
       </c>
-      <c r="H67" t="n">
-        <v/>
-      </c>
-      <c r="I67" t="n">
-        <v/>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3501,24 +3459,9 @@
           <t>i1</t>
         </is>
       </c>
-      <c r="D68" t="n">
-        <v/>
-      </c>
-      <c r="E68" t="n">
-        <v/>
-      </c>
-      <c r="F68" t="n">
-        <v/>
-      </c>
       <c r="G68" t="n">
         <v>1.034845813605298e-08</v>
       </c>
-      <c r="H68" t="n">
-        <v/>
-      </c>
-      <c r="I68" t="n">
-        <v/>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3536,23 +3479,8 @@
           <t>i2</t>
         </is>
       </c>
-      <c r="D69" t="n">
-        <v/>
-      </c>
       <c r="E69" t="n">
         <v>1</v>
-      </c>
-      <c r="F69" t="n">
-        <v/>
-      </c>
-      <c r="G69" t="n">
-        <v/>
-      </c>
-      <c r="H69" t="n">
-        <v/>
-      </c>
-      <c r="I69" t="n">
-        <v/>
       </c>
     </row>
     <row r="70">
@@ -3574,21 +3502,12 @@
       <c r="D70" t="n">
         <v>1</v>
       </c>
-      <c r="E70" t="n">
-        <v/>
-      </c>
       <c r="F70" t="n">
         <v>1</v>
       </c>
       <c r="G70" t="n">
         <v>-4.60113485276439e-09</v>
       </c>
-      <c r="H70" t="n">
-        <v/>
-      </c>
-      <c r="I70" t="n">
-        <v/>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3606,23 +3525,8 @@
           <t>i4</t>
         </is>
       </c>
-      <c r="D71" t="n">
-        <v/>
-      </c>
-      <c r="E71" t="n">
-        <v/>
-      </c>
-      <c r="F71" t="n">
-        <v/>
-      </c>
       <c r="G71" t="n">
         <v>1</v>
-      </c>
-      <c r="H71" t="n">
-        <v/>
-      </c>
-      <c r="I71" t="n">
-        <v/>
       </c>
     </row>
     <row r="72">
@@ -3641,23 +3545,11 @@
           <t>i5</t>
         </is>
       </c>
-      <c r="D72" t="n">
-        <v/>
-      </c>
-      <c r="E72" t="n">
-        <v/>
-      </c>
-      <c r="F72" t="n">
-        <v/>
-      </c>
       <c r="G72" t="n">
         <v>-2.069691627210596e-08</v>
       </c>
       <c r="H72" t="n">
         <v>1</v>
-      </c>
-      <c r="I72" t="n">
-        <v/>
       </c>
     </row>
     <row r="73">
@@ -8241,7 +8133,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>1.549048494029569</v>
+        <v>6.436970190190801</v>
       </c>
     </row>
   </sheetData>
@@ -8260,7 +8152,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>7217.391000000003</v>
+        <v>60.07842898368835</v>
       </c>
     </row>
   </sheetData>

--- a/6node_spain/output_all.xlsx
+++ b/6node_spain/output_all.xlsx
@@ -460,7 +460,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1.407526839642322</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -472,7 +472,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4878048780487805</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -526,7 +526,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4878048780487805</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -538,7 +538,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1.407526839642322</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8130081300813008</v>
+        <v>2.345878066070536</v>
       </c>
     </row>
     <row r="4">
@@ -722,7 +722,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8130081300813008</v>
+        <v>2.345878066070536</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -830,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1635745434842467</v>
+        <v>0.4719828984844505</v>
       </c>
     </row>
     <row r="4">
@@ -918,7 +918,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1650858763020109</v>
+        <v>0.4763437435689529</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8364254565157533</v>
+        <v>0.5280171015155495</v>
       </c>
     </row>
     <row r="4">
@@ -1114,7 +1114,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8349141236979891</v>
+        <v>0.5236562564310472</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -1188,20 +1188,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v/>
       </c>
       <c r="E2" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H2" t="n">
         <v/>
@@ -1218,22 +1218,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v/>
       </c>
       <c r="E3" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G3" t="n">
         <v/>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1268,7 +1268,7 @@
         <v/>
       </c>
       <c r="F4" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v/>
@@ -1277,7 +1277,7 @@
         <v/>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -1288,25 +1288,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v/>
       </c>
       <c r="E5" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v/>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H5" t="n">
         <v/>
@@ -1323,22 +1323,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v/>
       </c>
       <c r="E6" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G6" t="n">
         <v/>
@@ -1347,7 +1347,7 @@
         <v/>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1388,17 +1388,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1408,7 +1408,7 @@
         <v/>
       </c>
       <c r="F8" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v/>
@@ -1417,30 +1417,30 @@
         <v/>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>-5.615802685756355e-10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F9" t="n">
         <v/>
@@ -1458,17 +1458,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1478,7 +1478,7 @@
         <v/>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G10" t="n">
         <v/>
@@ -1487,7 +1487,7 @@
         <v/>
       </c>
       <c r="I10" t="n">
-        <v/>
+        <v>5.615802685756355e-10</v>
       </c>
     </row>
     <row r="11">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1513,7 +1513,7 @@
         <v/>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G11" t="n">
         <v/>
@@ -1522,7 +1522,7 @@
         <v/>
       </c>
       <c r="I11" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1533,16 +1533,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v/>
@@ -1554,7 +1554,7 @@
         <v/>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I12" t="n">
         <v/>
@@ -1568,12 +1568,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1583,7 +1583,7 @@
         <v/>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G13" t="n">
         <v/>
@@ -1592,7 +1592,7 @@
         <v/>
       </c>
       <c r="I13" t="n">
-        <v/>
+        <v>5.615802685756355e-10</v>
       </c>
     </row>
     <row r="14">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1612,19 +1612,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v/>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G14" t="n">
         <v/>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I14" t="n">
         <v/>
@@ -1633,24 +1633,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E15" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v/>
@@ -1662,23 +1662,23 @@
         <v/>
       </c>
       <c r="I15" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1694,30 +1694,30 @@
         <v/>
       </c>
       <c r="H16" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v/>
+        <v>1.667270865556533e-10</v>
       </c>
       <c r="E17" t="n">
         <v/>
@@ -1726,7 +1726,7 @@
         <v/>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H17" t="n">
         <v/>
@@ -1738,17 +1738,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1758,7 +1758,7 @@
         <v/>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G18" t="n">
         <v/>
@@ -1767,33 +1767,33 @@
         <v/>
       </c>
       <c r="I18" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v/>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G19" t="n">
         <v/>
@@ -1808,27 +1808,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G20" t="n">
         <v/>
@@ -1843,21 +1843,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>1.667270865556533e-10</v>
       </c>
       <c r="E21" t="n">
         <v/>
@@ -1878,17 +1878,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1898,32 +1898,32 @@
         <v/>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G22" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
         <v/>
       </c>
       <c r="I22" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1933,48 +1933,48 @@
         <v/>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H23" t="n">
         <v/>
       </c>
       <c r="I23" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
         <v/>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G24" t="n">
         <v/>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I24" t="n">
         <v/>
@@ -1988,16 +1988,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>1.667270865556533e-10</v>
       </c>
       <c r="E25" t="n">
         <v/>
@@ -2006,7 +2006,7 @@
         <v/>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H25" t="n">
         <v/>
@@ -2023,16 +2023,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v/>
@@ -2053,56 +2053,56 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E27" t="n">
         <v/>
       </c>
       <c r="F27" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
         <v/>
       </c>
       <c r="H27" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E28" t="n">
         <v/>
@@ -2114,7 +2114,7 @@
         <v/>
       </c>
       <c r="H28" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
         <v/>
@@ -2123,17 +2123,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -2149,30 +2149,30 @@
         <v/>
       </c>
       <c r="H29" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E30" t="n">
         <v/>
@@ -2184,7 +2184,7 @@
         <v/>
       </c>
       <c r="H30" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
         <v/>
@@ -2193,17 +2193,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -2219,26 +2219,26 @@
         <v/>
       </c>
       <c r="H31" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -2251,7 +2251,7 @@
         <v/>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H32" t="n">
         <v/>
@@ -2263,17 +2263,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -2286,13 +2286,13 @@
         <v/>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H33" t="n">
         <v/>
       </c>
       <c r="I33" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -2338,19 +2338,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E35" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
         <v/>
@@ -2359,7 +2359,7 @@
         <v/>
       </c>
       <c r="H35" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
         <v/>
@@ -2373,12 +2373,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -2413,14 +2413,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D37" t="n">
         <v/>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F37" t="n">
         <v/>
@@ -2429,7 +2429,7 @@
         <v/>
       </c>
       <c r="H37" t="n">
-        <v/>
+        <v>-3.861493182499682e-10</v>
       </c>
       <c r="I37" t="n">
         <v/>
@@ -2448,17 +2448,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E38" t="n">
         <v/>
       </c>
       <c r="F38" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
         <v/>
@@ -2467,7 +2467,7 @@
         <v/>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -2478,12 +2478,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -2493,7 +2493,7 @@
         <v/>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G39" t="n">
         <v/>
@@ -2502,7 +2502,7 @@
         <v/>
       </c>
       <c r="I39" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2518,14 +2518,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D40" t="n">
         <v/>
       </c>
       <c r="E40" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F40" t="n">
         <v/>
@@ -2537,7 +2537,7 @@
         <v/>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="41">
@@ -2548,22 +2548,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E41" t="n">
         <v/>
       </c>
       <c r="F41" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G41" t="n">
         <v/>
@@ -2572,7 +2572,7 @@
         <v/>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E42" t="n">
         <v/>
@@ -2604,7 +2604,7 @@
         <v/>
       </c>
       <c r="H42" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
         <v/>
@@ -2623,17 +2623,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D43" t="n">
         <v/>
       </c>
       <c r="E43" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G43" t="n">
         <v/>
@@ -2706,7 +2706,7 @@
         <v/>
       </c>
       <c r="G45" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
         <v/>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2735,13 +2735,13 @@
         <v/>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F46" t="n">
         <v/>
       </c>
       <c r="G46" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
         <v/>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E47" t="n">
         <v/>
@@ -2782,7 +2782,7 @@
         <v/>
       </c>
       <c r="I47" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2811,7 +2811,7 @@
         <v/>
       </c>
       <c r="G48" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
         <v/>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2893,24 +2893,24 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D51" t="n">
         <v/>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F51" t="n">
         <v/>
@@ -2919,7 +2919,7 @@
         <v/>
       </c>
       <c r="H51" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
         <v/>
@@ -2928,21 +2928,21 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E52" t="n">
         <v/>
@@ -2954,7 +2954,7 @@
         <v/>
       </c>
       <c r="H52" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I52" t="n">
         <v/>
@@ -2968,12 +2968,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -3003,12 +3003,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -3021,10 +3021,10 @@
         <v/>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H54" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
         <v/>
@@ -3038,12 +3038,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -3073,28 +3073,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
         <v/>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G56" t="n">
         <v/>
       </c>
       <c r="H56" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I56" t="n">
         <v/>
@@ -3108,19 +3108,19 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E57" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
         <v/>
@@ -3143,25 +3143,25 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E58" t="n">
         <v/>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H58" t="n">
         <v/>
@@ -3189,21 +3189,6 @@
       <c r="D59" t="n">
         <v>1</v>
       </c>
-      <c r="E59" t="n">
-        <v/>
-      </c>
-      <c r="F59" t="n">
-        <v/>
-      </c>
-      <c r="G59" t="n">
-        <v/>
-      </c>
-      <c r="H59" t="n">
-        <v/>
-      </c>
-      <c r="I59" t="n">
-        <v/>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3221,23 +3206,8 @@
           <t>i5</t>
         </is>
       </c>
-      <c r="D60" t="n">
-        <v/>
-      </c>
-      <c r="E60" t="n">
-        <v/>
-      </c>
       <c r="F60" t="n">
         <v>1</v>
-      </c>
-      <c r="G60" t="n">
-        <v/>
-      </c>
-      <c r="H60" t="n">
-        <v/>
-      </c>
-      <c r="I60" t="n">
-        <v/>
       </c>
     </row>
     <row r="61">
@@ -3256,23 +3226,8 @@
           <t>i1</t>
         </is>
       </c>
-      <c r="D61" t="n">
-        <v/>
-      </c>
-      <c r="E61" t="n">
-        <v/>
-      </c>
-      <c r="F61" t="n">
-        <v/>
-      </c>
       <c r="G61" t="n">
         <v>1</v>
-      </c>
-      <c r="H61" t="n">
-        <v/>
-      </c>
-      <c r="I61" t="n">
-        <v/>
       </c>
     </row>
     <row r="62">
@@ -3291,23 +3246,8 @@
           <t>i4</t>
         </is>
       </c>
-      <c r="D62" t="n">
-        <v/>
-      </c>
-      <c r="E62" t="n">
-        <v/>
-      </c>
       <c r="F62" t="n">
         <v>1</v>
-      </c>
-      <c r="G62" t="n">
-        <v/>
-      </c>
-      <c r="H62" t="n">
-        <v/>
-      </c>
-      <c r="I62" t="n">
-        <v/>
       </c>
     </row>
     <row r="63">
@@ -3329,21 +3269,6 @@
       <c r="D63" t="n">
         <v>1</v>
       </c>
-      <c r="E63" t="n">
-        <v/>
-      </c>
-      <c r="F63" t="n">
-        <v/>
-      </c>
-      <c r="G63" t="n">
-        <v/>
-      </c>
-      <c r="H63" t="n">
-        <v/>
-      </c>
-      <c r="I63" t="n">
-        <v/>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3361,23 +3286,11 @@
           <t>i2</t>
         </is>
       </c>
-      <c r="D64" t="n">
-        <v/>
-      </c>
       <c r="E64" t="n">
         <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>1</v>
-      </c>
-      <c r="G64" t="n">
-        <v/>
-      </c>
-      <c r="H64" t="n">
-        <v/>
-      </c>
-      <c r="I64" t="n">
-        <v/>
       </c>
     </row>
     <row r="65">
@@ -8133,7 +8046,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>6.436970190190801</v>
+        <v>2.934972515785815</v>
       </c>
     </row>
   </sheetData>
@@ -8152,7 +8065,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>60.07842898368835</v>
+        <v>63.93318581581116</v>
       </c>
     </row>
   </sheetData>

--- a/6node_spain/output_all.xlsx
+++ b/6node_spain/output_all.xlsx
@@ -460,16 +460,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.407526839642322</v>
+        <v>2.471503203273254</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.1852550364996299</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.11038009145463</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -532,13 +532,13 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1.345838955858719</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1.407526839642322</v>
+        <v>1.984583688523523</v>
       </c>
     </row>
   </sheetData>
@@ -628,13 +628,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1.773661332135592</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>2.345878066070536</v>
+        <v>2.345510673319831</v>
       </c>
     </row>
     <row r="4">
@@ -659,7 +659,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.3087583941660498</v>
       </c>
     </row>
     <row r="5">
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1.773661332135592</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -684,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.4694035942956067</v>
       </c>
     </row>
     <row r="6">
@@ -709,7 +709,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.1839668190910501</v>
       </c>
     </row>
     <row r="7">
@@ -722,16 +722,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>2.345878066070536</v>
+        <v>2.345510673319831</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.3087583941660498</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.4694035942956067</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.1839668190910501</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.1868606636176918</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4719828984844505</v>
+        <v>0.4719089802796351</v>
       </c>
     </row>
     <row r="4">
@@ -855,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.4057989866739515</v>
       </c>
     </row>
     <row r="5">
@@ -868,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.1849315504747268</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -880,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.2038034530676793</v>
       </c>
     </row>
     <row r="6">
@@ -905,7 +905,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.3435753744333946</v>
       </c>
     </row>
     <row r="7">
@@ -918,16 +918,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4763437435689529</v>
+        <v>0.4762691424032905</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.3941121164509664</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.2053021561194378</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.3436842616218094</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1020,13 +1020,13 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.8131393363823082</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5280171015155495</v>
+        <v>0.528091019720365</v>
       </c>
     </row>
     <row r="4">
@@ -1051,7 +1051,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.5942010133260485</v>
       </c>
     </row>
     <row r="5">
@@ -1064,7 +1064,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0.8150684495252731</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -1076,7 +1076,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0.7961965469323207</v>
       </c>
     </row>
     <row r="6">
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0.6564246255666054</v>
       </c>
     </row>
     <row r="7">
@@ -1114,16 +1114,16 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5236562564310472</v>
+        <v>0.5237308575967095</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0.6058878835490336</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0.7946978438805622</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0.6563157383781906</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1188,23 +1188,23 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v/>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G2" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v/>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -1233,7 +1233,7 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v/>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1268,7 +1268,7 @@
         <v/>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G4" t="n">
         <v/>
@@ -1277,7 +1277,7 @@
         <v/>
       </c>
       <c r="I4" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1288,19 +1288,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v/>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F5" t="n">
         <v/>
@@ -1312,7 +1312,7 @@
         <v/>
       </c>
       <c r="I5" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1323,25 +1323,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v/>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F6" t="n">
         <v/>
       </c>
       <c r="G6" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v/>
@@ -1358,19 +1358,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v/>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F7" t="n">
         <v/>
@@ -1382,13 +1382,13 @@
         <v/>
       </c>
       <c r="I7" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1408,36 +1408,36 @@
         <v/>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G8" t="n">
         <v/>
       </c>
       <c r="H8" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>-5.615802685756355e-10</v>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E9" t="n">
         <v/>
@@ -1452,30 +1452,30 @@
         <v/>
       </c>
       <c r="I9" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v/>
       </c>
       <c r="E10" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v/>
@@ -1487,18 +1487,18 @@
         <v/>
       </c>
       <c r="I10" t="n">
-        <v>5.615802685756355e-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1516,19 +1516,19 @@
         <v/>
       </c>
       <c r="G11" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v/>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1538,14 +1538,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E12" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
         <v/>
@@ -1557,18 +1557,18 @@
         <v/>
       </c>
       <c r="I12" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1580,10 +1580,10 @@
         <v/>
       </c>
       <c r="E13" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
         <v/>
@@ -1592,27 +1592,27 @@
         <v/>
       </c>
       <c r="I13" t="n">
-        <v>5.615802685756355e-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E14" t="n">
         <v/>
@@ -1624,7 +1624,7 @@
         <v/>
       </c>
       <c r="H14" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v/>
@@ -1633,27 +1633,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v/>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F15" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
         <v/>
@@ -1662,23 +1662,23 @@
         <v/>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1691,10 +1691,10 @@
         <v/>
       </c>
       <c r="G16" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I16" t="n">
         <v/>
@@ -1703,21 +1703,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.667270865556533e-10</v>
+        <v/>
       </c>
       <c r="E17" t="n">
         <v/>
@@ -1732,23 +1732,23 @@
         <v/>
       </c>
       <c r="I17" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1773,33 +1773,33 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E19" t="n">
         <v/>
       </c>
       <c r="F19" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
         <v/>
       </c>
       <c r="H19" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
         <v/>
@@ -1808,33 +1808,33 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F20" t="n">
         <v/>
       </c>
       <c r="G20" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I20" t="n">
         <v/>
@@ -1843,21 +1843,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1.667270865556533e-10</v>
+        <v/>
       </c>
       <c r="E21" t="n">
         <v/>
@@ -1869,7 +1869,7 @@
         <v/>
       </c>
       <c r="H21" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v/>
@@ -1878,17 +1878,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1898,32 +1898,32 @@
         <v/>
       </c>
       <c r="F22" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H22" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1936,29 +1936,29 @@
         <v/>
       </c>
       <c r="G23" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
         <v/>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1977,27 +1977,27 @@
         <v/>
       </c>
       <c r="I24" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1.667270865556533e-10</v>
+        <v/>
       </c>
       <c r="E25" t="n">
         <v/>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="H25" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v/>
@@ -2018,17 +2018,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -2041,7 +2041,7 @@
         <v/>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H26" t="n">
         <v/>
@@ -2053,12 +2053,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2067,19 +2067,19 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
         <v/>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G27" t="n">
         <v/>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I27" t="n">
         <v/>
@@ -2088,12 +2088,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2123,21 +2123,21 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
         <v/>
@@ -2149,7 +2149,7 @@
         <v/>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I29" t="n">
         <v/>
@@ -2158,21 +2158,21 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v/>
@@ -2184,7 +2184,7 @@
         <v/>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I30" t="n">
         <v/>
@@ -2193,17 +2193,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -2228,24 +2228,24 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v/>
       </c>
       <c r="E32" t="n">
-        <v/>
+        <v>1.190101944418493e-10</v>
       </c>
       <c r="F32" t="n">
         <v/>
@@ -2257,27 +2257,27 @@
         <v/>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
         <v/>
@@ -2292,27 +2292,27 @@
         <v/>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E34" t="n">
         <v/>
@@ -2324,7 +2324,7 @@
         <v/>
       </c>
       <c r="H34" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
         <v/>
@@ -2333,12 +2333,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2368,21 +2368,21 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
         <v/>
@@ -2391,29 +2391,29 @@
         <v/>
       </c>
       <c r="G36" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
         <v/>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -2429,16 +2429,16 @@
         <v/>
       </c>
       <c r="H37" t="n">
-        <v>-3.861493182499682e-10</v>
+        <v/>
       </c>
       <c r="I37" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2448,23 +2448,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v/>
       </c>
       <c r="E38" t="n">
-        <v/>
+        <v>1.190101944418493e-10</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G38" t="n">
         <v/>
       </c>
       <c r="H38" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
         <v/>
@@ -2473,21 +2473,21 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
         <v/>
@@ -2502,13 +2502,13 @@
         <v/>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2518,14 +2518,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F40" t="n">
         <v/>
@@ -2543,7 +2543,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2553,17 +2553,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D41" t="n">
         <v/>
       </c>
       <c r="E41" t="n">
-        <v/>
+        <v>1.190101944418493e-10</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G41" t="n">
         <v/>
@@ -2578,7 +2578,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2588,11 +2588,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
         <v/>
@@ -2604,7 +2604,7 @@
         <v/>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I42" t="n">
         <v/>
@@ -2618,19 +2618,19 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F43" t="n">
         <v/>
@@ -2648,24 +2648,24 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F44" t="n">
         <v/>
@@ -2683,65 +2683,65 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D45" t="n">
         <v/>
       </c>
       <c r="E45" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
         <v/>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H45" t="n">
         <v/>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
         <v/>
       </c>
       <c r="F46" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H46" t="n">
         <v/>
@@ -2753,17 +2753,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2779,26 +2779,26 @@
         <v/>
       </c>
       <c r="H47" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2811,7 +2811,7 @@
         <v/>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H48" t="n">
         <v/>
@@ -2823,24 +2823,24 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F49" t="n">
         <v/>
@@ -2863,25 +2863,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D50" t="n">
         <v/>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F50" t="n">
         <v/>
       </c>
       <c r="G50" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
         <v/>
@@ -2893,21 +2893,21 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
         <v/>
@@ -2916,10 +2916,10 @@
         <v/>
       </c>
       <c r="G51" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I51" t="n">
         <v/>
@@ -2928,33 +2928,33 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
         <v/>
       </c>
       <c r="F52" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
         <v/>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I52" t="n">
         <v/>
@@ -2963,30 +2963,30 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D53" t="n">
         <v/>
       </c>
       <c r="E53" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F53" t="n">
         <v/>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H53" t="n">
         <v/>
@@ -2998,12 +2998,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3021,10 +3021,10 @@
         <v/>
       </c>
       <c r="G54" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I54" t="n">
         <v/>
@@ -3033,7 +3033,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3047,16 +3047,16 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E55" t="n">
         <v/>
       </c>
       <c r="F55" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H55" t="n">
         <v/>
@@ -3068,21 +3068,21 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E56" t="n">
         <v/>
@@ -3094,10 +3094,10 @@
         <v/>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I56" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3108,19 +3108,19 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F57" t="n">
         <v/>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3152,16 +3152,16 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
         <v/>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H58" t="n">
         <v/>
@@ -3178,16 +3178,31 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D59" t="n">
         <v>1</v>
+      </c>
+      <c r="E59" t="n">
+        <v/>
+      </c>
+      <c r="F59" t="n">
+        <v/>
+      </c>
+      <c r="G59" t="n">
+        <v/>
+      </c>
+      <c r="H59" t="n">
+        <v/>
+      </c>
+      <c r="I59" t="n">
+        <v/>
       </c>
     </row>
     <row r="60">
@@ -3198,7 +3213,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3206,8 +3221,23 @@
           <t>i5</t>
         </is>
       </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="n">
+        <v/>
+      </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v/>
+      </c>
+      <c r="G60" t="n">
+        <v/>
+      </c>
+      <c r="H60" t="n">
+        <v>-3.140767048659399e-07</v>
+      </c>
+      <c r="I60" t="n">
+        <v/>
       </c>
     </row>
     <row r="61">
@@ -3218,16 +3248,31 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>i1</t>
-        </is>
+          <t>i2</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="n">
+        <v/>
+      </c>
+      <c r="F61" t="n">
+        <v/>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v/>
+      </c>
+      <c r="H61" t="n">
+        <v/>
+      </c>
+      <c r="I61" t="n">
+        <v/>
       </c>
     </row>
     <row r="62">
@@ -3243,11 +3288,26 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>i4</t>
-        </is>
+          <t>i2</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="n">
+        <v/>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v/>
+      </c>
+      <c r="G62" t="n">
+        <v/>
+      </c>
+      <c r="H62" t="n">
+        <v/>
+      </c>
+      <c r="I62" t="n">
+        <v/>
       </c>
     </row>
     <row r="63">
@@ -3263,11 +3323,26 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D63" t="n">
         <v>1</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" t="n">
+        <v/>
+      </c>
+      <c r="G63" t="n">
+        <v/>
+      </c>
+      <c r="H63" t="n">
+        <v/>
+      </c>
+      <c r="I63" t="n">
+        <v/>
       </c>
     </row>
     <row r="64">
@@ -3283,14 +3358,26 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>i2</t>
-        </is>
+          <t>i3</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v/>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F64" t="n">
         <v>1</v>
+      </c>
+      <c r="G64" t="n">
+        <v/>
+      </c>
+      <c r="H64" t="n">
+        <v>-3.140767048659399e-07</v>
+      </c>
+      <c r="I64" t="n">
+        <v/>
       </c>
     </row>
     <row r="65">
@@ -3301,16 +3388,31 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v/>
+      </c>
+      <c r="E65" t="n">
+        <v/>
+      </c>
+      <c r="F65" t="n">
+        <v/>
+      </c>
+      <c r="G65" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" t="n">
+        <v/>
+      </c>
+      <c r="I65" t="n">
+        <v/>
       </c>
     </row>
     <row r="66">
@@ -3321,22 +3423,37 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>i1</t>
-        </is>
+          <t>i5</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v/>
+      </c>
+      <c r="E66" t="n">
+        <v/>
+      </c>
+      <c r="F66" t="n">
+        <v/>
       </c>
       <c r="G66" t="n">
-        <v>4.601134852764388e-09</v>
+        <v/>
+      </c>
+      <c r="H66" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" t="n">
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3346,86 +3463,80 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>i4</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" t="n">
-        <v>-1.034845813605298e-08</v>
+          <t>i1</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>1.034845813605298e-08</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>i2</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
+          <t>i4</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>i3</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" t="n">
-        <v>-4.60113485276439e-09</v>
+          <t>i6</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3435,8 +3546,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>i4</t>
-        </is>
+          <t>i3</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
       </c>
       <c r="G71" t="n">
         <v>1</v>
@@ -3450,19 +3564,16 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>i5</t>
-        </is>
-      </c>
-      <c r="G72" t="n">
-        <v>-2.069691627210596e-08</v>
+          <t>i2</t>
+        </is>
       </c>
       <c r="H72" t="n">
-        <v>1</v>
+        <v>-3.587843333654428e-08</v>
       </c>
     </row>
     <row r="73">
@@ -3473,7 +3584,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3481,8 +3592,8 @@
           <t>i5</t>
         </is>
       </c>
-      <c r="D73" t="n">
-        <v>1</v>
+      <c r="H73" t="n">
+        <v>-3.587843333654428e-08</v>
       </c>
     </row>
     <row r="74">
@@ -3493,12 +3604,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3513,16 +3624,16 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>i3</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>1</v>
+          <t>i4</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>4.783791111539236e-08</v>
       </c>
     </row>
     <row r="76">
@@ -3533,16 +3644,19 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>i4</t>
-        </is>
-      </c>
-      <c r="G76" t="n">
-        <v>-6.77346016342894e-08</v>
+          <t>i5</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" t="n">
+        <v>3.026870096400883e-07</v>
       </c>
     </row>
     <row r="77">
@@ -3553,16 +3667,19 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>i1</t>
-        </is>
-      </c>
-      <c r="G77" t="n">
-        <v>3.38673008171447e-08</v>
+          <t>i2</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" t="n">
+        <v>-7.175686667308858e-08</v>
       </c>
     </row>
     <row r="78">
@@ -3573,16 +3690,16 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>i2</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>1</v>
+          <t>i4</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>3.58784333365443e-08</v>
       </c>
     </row>
     <row r="79">
@@ -3593,19 +3710,16 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>i3</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>1</v>
-      </c>
-      <c r="F79" t="n">
-        <v>1</v>
+          <t>i1</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>-7.175686667308855e-08</v>
       </c>
     </row>
     <row r="80">
@@ -3616,16 +3730,16 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>i4</t>
-        </is>
-      </c>
-      <c r="G80" t="n">
-        <v>1</v>
+          <t>i2</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>4.103223096497212e-07</v>
       </c>
     </row>
     <row r="81">
@@ -3636,19 +3750,16 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>i5</t>
-        </is>
-      </c>
-      <c r="G81" t="n">
-        <v>-1.016019024514341e-07</v>
+          <t>i3</t>
+        </is>
       </c>
       <c r="H81" t="n">
-        <v>1</v>
+        <v>-3.587843333654428e-08</v>
       </c>
     </row>
     <row r="82">
@@ -3664,11 +3775,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D82" t="n">
         <v>1</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-2.189706651881517e-07</v>
       </c>
     </row>
     <row r="83">
@@ -3679,12 +3793,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3704,7 +3818,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3719,15 +3833,15 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>i2</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
+          <t>i4</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3744,11 +3858,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>i3</t>
-        </is>
-      </c>
-      <c r="F86" t="n">
-        <v>1</v>
+          <t>i2</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="n">
+        <v>4.783791111539239e-08</v>
       </c>
     </row>
     <row r="87">
@@ -3764,13 +3881,10 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>i4</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>1</v>
-      </c>
-      <c r="G87" t="n">
+          <t>i3</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3787,17 +3901,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>i5</t>
-        </is>
-      </c>
-      <c r="H88" t="n">
+          <t>i4</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3807,23 +3921,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>-1.042772628612353e-10</v>
-      </c>
-      <c r="E89" t="n">
-        <v>1.734299307008339e-10</v>
-      </c>
-      <c r="G89" t="n">
-        <v>8.165751769004037e-10</v>
+        <v>1</v>
       </c>
       <c r="H89" t="n">
-        <v>-1.359019782310585e-09</v>
-      </c>
-      <c r="I89" t="n">
-        <v>-1.49769674661684e-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -8046,7 +8151,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>2.934972515785815</v>
+        <v>1.34481843039434</v>
       </c>
     </row>
   </sheetData>
@@ -8065,7 +8170,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>63.93318581581116</v>
+        <v>60.0634708404541</v>
       </c>
     </row>
   </sheetData>

--- a/6node_spain/output_all.xlsx
+++ b/6node_spain/output_all.xlsx
@@ -460,7 +460,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.471503203273254</v>
+        <v>2.471503174528505</v>
       </c>
       <c r="C2" t="n">
         <v>0.1852550364996299</v>
@@ -469,7 +469,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.11038009145463</v>
+        <v>0.1103801201993786</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -532,13 +532,13 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1.345838955858719</v>
+        <v>1.34583892711397</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1.984583688523523</v>
+        <v>1.984583717268271</v>
       </c>
     </row>
   </sheetData>
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1.773661332135592</v>
+        <v>1.773661284227677</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>1.773661332135592</v>
+        <v>1.773661284227677</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1839668190910501</v>
+        <v>0.1839668669989644</v>
       </c>
     </row>
     <row r="7">
@@ -731,7 +731,7 @@
         <v>0.4694035942956067</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1839668190910501</v>
+        <v>0.1839668669989644</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -824,7 +824,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1868606636176918</v>
+        <v>0.186860658570446</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -868,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1849315504747268</v>
+        <v>0.1849315454795878</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -905,7 +905,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3435753744333946</v>
+        <v>0.3435758187821139</v>
       </c>
     </row>
     <row r="7">
@@ -927,7 +927,7 @@
         <v>0.2053021561194378</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3436842616218094</v>
+        <v>0.3436843511227108</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8131393363823082</v>
+        <v>0.813139341429554</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -1064,7 +1064,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8150684495252731</v>
+        <v>0.8150684545204122</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6564246255666054</v>
+        <v>0.6564241812178861</v>
       </c>
     </row>
     <row r="7">
@@ -1123,7 +1123,7 @@
         <v>0.7946978438805622</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6563157383781906</v>
+        <v>0.6563156488772892</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1195,7 +1195,7 @@
         <v/>
       </c>
       <c r="E2" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v/>
@@ -1223,14 +1223,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v/>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1309,10 +1309,10 @@
         <v/>
       </c>
       <c r="H5" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -1338,10 +1338,10 @@
         <v/>
       </c>
       <c r="F6" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H6" t="n">
         <v/>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1376,13 +1376,13 @@
         <v/>
       </c>
       <c r="G7" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1446,7 +1446,7 @@
         <v/>
       </c>
       <c r="G9" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v/>
@@ -1468,14 +1468,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v/>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F10" t="n">
         <v/>
@@ -1484,10 +1484,10 @@
         <v/>
       </c>
       <c r="H10" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1510,13 +1510,13 @@
         <v/>
       </c>
       <c r="E11" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v/>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H11" t="n">
         <v/>
@@ -1545,10 +1545,10 @@
         <v/>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F12" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
         <v/>
@@ -1557,7 +1557,7 @@
         <v/>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -1583,7 +1583,7 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G13" t="n">
         <v/>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1624,10 +1624,10 @@
         <v/>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I14" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1653,13 +1653,13 @@
         <v/>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G15" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v/>
@@ -1673,25 +1673,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v/>
       </c>
       <c r="E16" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
         <v/>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H16" t="n">
         <v/>
@@ -1703,17 +1703,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1723,7 +1723,7 @@
         <v/>
       </c>
       <c r="F17" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
         <v/>
@@ -1732,23 +1732,23 @@
         <v/>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1758,7 +1758,7 @@
         <v/>
       </c>
       <c r="F18" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
         <v/>
@@ -1767,18 +1767,18 @@
         <v/>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1793,13 +1793,13 @@
         <v/>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G19" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I19" t="n">
         <v/>
@@ -1808,12 +1808,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1831,10 +1831,10 @@
         <v/>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H20" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
         <v/>
@@ -1848,16 +1848,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v/>
@@ -1869,10 +1869,10 @@
         <v/>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I21" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1883,28 +1883,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
         <v/>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G22" t="n">
         <v/>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I22" t="n">
         <v/>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v/>
@@ -1936,7 +1936,7 @@
         <v/>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H23" t="n">
         <v/>
@@ -1948,24 +1948,24 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E24" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
         <v/>
@@ -1977,23 +1977,23 @@
         <v/>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -2006,7 +2006,7 @@
         <v/>
       </c>
       <c r="G25" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
         <v>1</v>
@@ -2018,12 +2018,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E26" t="n">
         <v/>
@@ -2044,7 +2044,7 @@
         <v/>
       </c>
       <c r="H26" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
         <v/>
@@ -2053,24 +2053,24 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
         <v/>
@@ -2079,7 +2079,7 @@
         <v/>
       </c>
       <c r="H27" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
         <v/>
@@ -2088,12 +2088,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2111,10 +2111,10 @@
         <v/>
       </c>
       <c r="G28" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I28" t="n">
         <v/>
@@ -2123,21 +2123,21 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E29" t="n">
         <v/>
@@ -2152,18 +2152,18 @@
         <v/>
       </c>
       <c r="I29" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E30" t="n">
         <v/>
@@ -2184,7 +2184,7 @@
         <v/>
       </c>
       <c r="H30" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
         <v/>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
         <v/>
@@ -2219,7 +2219,7 @@
         <v/>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I31" t="n">
         <v/>
@@ -2233,25 +2233,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v/>
       </c>
       <c r="E32" t="n">
-        <v>1.190101944418493e-10</v>
+        <v/>
       </c>
       <c r="F32" t="n">
         <v/>
       </c>
       <c r="G32" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
         <v/>
@@ -2268,12 +2268,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2312,7 +2312,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
         <v/>
@@ -2324,7 +2324,7 @@
         <v/>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I34" t="n">
         <v/>
@@ -2333,24 +2333,24 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F35" t="n">
         <v/>
@@ -2359,7 +2359,7 @@
         <v/>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I35" t="n">
         <v/>
@@ -2368,30 +2368,30 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E36" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
         <v/>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H36" t="n">
         <v/>
@@ -2403,17 +2403,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -2423,7 +2423,7 @@
         <v/>
       </c>
       <c r="F37" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
         <v/>
@@ -2432,13 +2432,13 @@
         <v/>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2448,14 +2448,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.190101944418493e-10</v>
+        <v/>
       </c>
       <c r="F38" t="n">
         <v/>
@@ -2473,7 +2473,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E39" t="n">
         <v/>
@@ -2502,13 +2502,13 @@
         <v/>
       </c>
       <c r="I39" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2543,24 +2543,24 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D41" t="n">
         <v/>
       </c>
       <c r="E41" t="n">
-        <v>1.190101944418493e-10</v>
+        <v>1</v>
       </c>
       <c r="F41" t="n">
         <v/>
@@ -2578,24 +2578,24 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E42" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
         <v/>
@@ -2613,24 +2613,24 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E43" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
         <v/>
@@ -2648,17 +2648,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -2683,27 +2683,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F45" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
         <v/>
@@ -2718,17 +2718,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2738,7 +2738,7 @@
         <v/>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G46" t="n">
         <v/>
@@ -2753,21 +2753,21 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
         <v/>
@@ -2779,7 +2779,7 @@
         <v/>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I47" t="n">
         <v/>
@@ -2788,21 +2788,21 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
         <v/>
@@ -2817,30 +2817,30 @@
         <v/>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D49" t="n">
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v/>
@@ -2863,25 +2863,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D50" t="n">
         <v/>
       </c>
       <c r="E50" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
         <v/>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H50" t="n">
         <v/>
@@ -2898,12 +2898,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2916,7 +2916,7 @@
         <v/>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H51" t="n">
         <v/>
@@ -2938,17 +2938,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D52" t="n">
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G52" t="n">
         <v/>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -3008,20 +3008,20 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
         <v/>
       </c>
       <c r="F54" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H54" t="n">
         <v/>
@@ -3047,16 +3047,16 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E55" t="n">
         <v/>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G55" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H55" t="n">
         <v/>
@@ -3097,18 +3097,18 @@
         <v/>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0.9999996451238262</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3117,10 +3117,10 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E57" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
         <v/>
@@ -3138,17 +3138,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -3173,17 +3173,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -3208,24 +3208,24 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E60" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F60" t="n">
         <v/>
@@ -3234,7 +3234,7 @@
         <v/>
       </c>
       <c r="H60" t="n">
-        <v>-3.140767048659399e-07</v>
+        <v/>
       </c>
       <c r="I60" t="n">
         <v/>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E61" t="n">
         <v/>
@@ -3269,7 +3269,7 @@
         <v/>
       </c>
       <c r="H61" t="n">
-        <v/>
+        <v>1.993554252564312e-07</v>
       </c>
       <c r="I61" t="n">
         <v/>
@@ -3283,16 +3283,16 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E62" t="n">
         <v/>
@@ -3304,7 +3304,7 @@
         <v/>
       </c>
       <c r="H62" t="n">
-        <v/>
+        <v>-2.990331378846468e-07</v>
       </c>
       <c r="I62" t="n">
         <v/>
@@ -3318,19 +3318,19 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D63" t="n">
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F63" t="n">
         <v/>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -3368,13 +3368,13 @@
         <v/>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G64" t="n">
         <v/>
       </c>
       <c r="H64" t="n">
-        <v>-3.140767048659399e-07</v>
+        <v>2.990331378846468e-07</v>
       </c>
       <c r="I64" t="n">
         <v/>
@@ -3388,12 +3388,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -3406,10 +3406,10 @@
         <v/>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H65" t="n">
-        <v/>
+        <v>1.993554252564311e-07</v>
       </c>
       <c r="I65" t="n">
         <v/>
@@ -3423,16 +3423,16 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="E66" t="n">
         <v/>
@@ -3444,7 +3444,7 @@
         <v/>
       </c>
       <c r="H66" t="n">
-        <v>1</v>
+        <v>-2.990331378846468e-07</v>
       </c>
       <c r="I66" t="n">
         <v/>
@@ -3453,12 +3453,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3466,77 +3466,134 @@
           <t>i1</t>
         </is>
       </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v/>
+      </c>
+      <c r="G67" t="n">
+        <v/>
+      </c>
+      <c r="H67" t="n">
+        <v>-9.967771262821555e-08</v>
+      </c>
+      <c r="I67" t="n">
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>i3</t>
-        </is>
+          <t>i2</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v/>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" t="n">
+        <v/>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v/>
+      </c>
+      <c r="H68" t="n">
+        <v>1.993554252564312e-07</v>
+      </c>
+      <c r="I68" t="n">
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v/>
+      </c>
+      <c r="E69" t="n">
+        <v/>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="n">
+        <v/>
+      </c>
+      <c r="H69" t="n">
+        <v>1.993554252564311e-07</v>
+      </c>
+      <c r="I69" t="n">
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>i6</t>
-        </is>
+          <t>i4</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v/>
+      </c>
+      <c r="E70" t="n">
+        <v/>
+      </c>
+      <c r="F70" t="n">
+        <v/>
+      </c>
+      <c r="G70" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" t="n">
+        <v>-2.990331378846468e-07</v>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3546,14 +3603,26 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v/>
+      </c>
+      <c r="E71" t="n">
+        <v/>
+      </c>
+      <c r="F71" t="n">
+        <v/>
       </c>
       <c r="G71" t="n">
-        <v>1</v>
+        <v/>
+      </c>
+      <c r="H71" t="n">
+        <v>1</v>
+      </c>
+      <c r="I71" t="n">
+        <v/>
       </c>
     </row>
     <row r="72">
@@ -3564,16 +3633,16 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>i2</t>
-        </is>
-      </c>
-      <c r="H72" t="n">
-        <v>-3.587843333654428e-08</v>
+          <t>i4</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -3584,7 +3653,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3593,7 +3662,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>-3.587843333654428e-08</v>
+        <v>1.000000128926522</v>
       </c>
     </row>
     <row r="74">
@@ -3604,15 +3673,18 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3624,7 +3696,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3632,8 +3704,8 @@
           <t>i4</t>
         </is>
       </c>
-      <c r="H75" t="n">
-        <v>4.783791111539236e-08</v>
+      <c r="G75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -3644,7 +3716,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3652,11 +3724,8 @@
           <t>i5</t>
         </is>
       </c>
-      <c r="D76" t="n">
-        <v>1</v>
-      </c>
       <c r="H76" t="n">
-        <v>3.026870096400883e-07</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -3667,19 +3736,19 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>i2</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>1</v>
-      </c>
-      <c r="H77" t="n">
-        <v>-7.175686667308858e-08</v>
+          <t>i4</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -3695,11 +3764,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>i4</t>
-        </is>
-      </c>
-      <c r="H78" t="n">
-        <v>3.58784333365443e-08</v>
+          <t>i1</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -3710,16 +3779,16 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>i1</t>
-        </is>
-      </c>
-      <c r="H79" t="n">
-        <v>-7.175686667308855e-08</v>
+          <t>i4</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -3730,16 +3799,16 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>4.103223096497212e-07</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -3755,11 +3824,11 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>i3</t>
-        </is>
-      </c>
-      <c r="H81" t="n">
-        <v>-3.587843333654428e-08</v>
+          <t>i2</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -3781,9 +3850,6 @@
       <c r="D82" t="n">
         <v>1</v>
       </c>
-      <c r="H82" t="n">
-        <v>-2.189706651881517e-07</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3801,7 +3867,10 @@
           <t>i2</t>
         </is>
       </c>
-      <c r="D83" t="n">
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3833,15 +3902,15 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>i4</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
+          <t>i1</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3865,7 +3934,7 @@
         <v>1</v>
       </c>
       <c r="H86" t="n">
-        <v>4.783791111539239e-08</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -3884,7 +3953,7 @@
           <t>i3</t>
         </is>
       </c>
-      <c r="F87" t="n">
+      <c r="D87" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3901,10 +3970,10 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>i4</t>
-        </is>
-      </c>
-      <c r="G88" t="n">
+          <t>i5</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8151,7 +8220,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>1.34481843039434</v>
+        <v>1.616780471168727</v>
       </c>
     </row>
   </sheetData>
@@ -8170,7 +8239,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>60.0634708404541</v>
+        <v>60.17358303070068</v>
       </c>
     </row>
   </sheetData>

--- a/6node_spain/output_all.xlsx
+++ b/6node_spain/output_all.xlsx
@@ -457,22 +457,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>0.0001412526301437265</v>
       </c>
       <c r="B2" t="n">
-        <v>2.471503174528505</v>
+        <v>0.9329649128919539</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1852550364996299</v>
+        <v>0.1378556983081443</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1.050100798331301</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1103801201993786</v>
+        <v>0.07434178915609041</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.8459403920442028</v>
       </c>
     </row>
   </sheetData>
@@ -523,22 +523,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>2.220071449848034e-06</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.4097073999142399</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>2.47876868612077e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>1.34583892711397</v>
+        <v>0.0009996009137786224</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>2.43544164196468e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>1.984583717268271</v>
+        <v>0.1127786116306059</v>
       </c>
     </row>
   </sheetData>
@@ -597,19 +597,19 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.0002181636648008357</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>4.064371929212977e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>3.233029264942841e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1.092554890546369e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1.582521294328548e-06</v>
       </c>
     </row>
     <row r="3">
@@ -619,22 +619,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.0002181636648008357</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>5.669230804807989e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.773661284227677</v>
+        <v>1.368828954250352</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>5.181651926593764e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>2.345510673319831</v>
+        <v>0.8681733980848008</v>
       </c>
     </row>
     <row r="4">
@@ -644,22 +644,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>4.064371929212977e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>5.669230804807989e-05</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.003342225635356782</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>5.348014375516973e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3087583941660498</v>
+        <v>0.2262366487586565</v>
       </c>
     </row>
     <row r="5">
@@ -669,22 +669,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>3.233029264942841e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>1.773661284227677</v>
+        <v>1.368828954250352</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.003342225635356782</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>4.902817725195176e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4694035942956067</v>
+        <v>0.3791951598320455</v>
       </c>
     </row>
     <row r="6">
@@ -694,22 +694,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>1.092554890546369e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>5.181651926593764e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>5.348014375516973e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>4.902817725195176e-06</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1839668669989644</v>
+        <v>0.1238120553059773</v>
       </c>
     </row>
     <row r="7">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1.582521294328548e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>2.345510673319831</v>
+        <v>0.8681733980848008</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3087583941660498</v>
+        <v>0.2262366487586565</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4694035942956067</v>
+        <v>0.3791951598320455</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1839668669989644</v>
+        <v>0.1238120553059773</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -790,22 +790,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1.113819562403862e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1.125783088973265e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1.175067394498797e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>2.782525888700427e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>6.275939146149767e-08</v>
       </c>
     </row>
     <row r="3">
@@ -815,22 +815,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>1.136655958433597e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>7.756185693708062e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>0.186860658570446</v>
+        <v>0.1442050125639238</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1.128833746477653e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4719089802796351</v>
+        <v>0.1746735028859643</v>
       </c>
     </row>
     <row r="4">
@@ -840,22 +840,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1.361757255846641e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>9.7880210159218e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.0009460265365519582</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>6.319883749661415e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4057989866739515</v>
+        <v>0.2973362337248007</v>
       </c>
     </row>
     <row r="5">
@@ -865,22 +865,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1.202102644093372e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1849315454795878</v>
+        <v>0.1427162844365196</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.0009378946820528533</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>6.460285817411204e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2038034530676793</v>
+        <v>0.164636369534559</v>
       </c>
     </row>
     <row r="6">
@@ -890,22 +890,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>2.759645402417021e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1.180478916840144e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>6.442679434393028e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>6.983276534811012e-08</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3435758187821139</v>
+        <v>0.2312286427436917</v>
       </c>
     </row>
     <row r="7">
@@ -915,19 +915,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>4.006842169168578e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4762691424032905</v>
+        <v>0.1762866420917085</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3941121164509664</v>
+        <v>0.2887775527700376</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2053021561194378</v>
+        <v>0.165845921661725</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3436843511227108</v>
+        <v>0.2313018508793159</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -989,19 +989,19 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0.999988861804376</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0.9999998874216911</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.9999998824932606</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.9999972174741113</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.9999999372406085</v>
       </c>
     </row>
     <row r="3">
@@ -1011,22 +1011,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0.9999886334404157</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0.9999999224381431</v>
       </c>
       <c r="E3" t="n">
-        <v>0.813139341429554</v>
+        <v>0.8557949874360762</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.9999998871166254</v>
       </c>
       <c r="G3" t="n">
-        <v>0.528091019720365</v>
+        <v>0.8253264971140357</v>
       </c>
     </row>
     <row r="4">
@@ -1036,22 +1036,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0.9999998638242744</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0.9999999021197898</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0.999053973463448</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.9999999368011625</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5942010133260485</v>
+        <v>0.7026637662751993</v>
       </c>
     </row>
     <row r="5">
@@ -1061,22 +1061,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0.9999998797897356</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8150684545204122</v>
+        <v>0.8572837155634804</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0.9990621053179471</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.9999999353971418</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7961965469323207</v>
+        <v>0.835363630465441</v>
       </c>
     </row>
     <row r="6">
@@ -1086,22 +1086,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0.9999972403545976</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0.9999998819521083</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0.9999999355732057</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0.9999999301672347</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6564241812178861</v>
+        <v>0.7687713572563083</v>
       </c>
     </row>
     <row r="7">
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0.9999999599315783</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5237308575967095</v>
+        <v>0.8237133579082915</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6058878835490336</v>
+        <v>0.7112224472299624</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7946978438805622</v>
+        <v>0.834154078338275</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6563156488772892</v>
+        <v>0.7686981491206841</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1195,19 +1195,19 @@
         <v/>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>1.113036390693752e-05</v>
       </c>
       <c r="F2" t="n">
-        <v/>
+        <v>1.386681060049398e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>7.018923276282935e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>7.00516149576723e-09</v>
       </c>
       <c r="I2" t="n">
-        <v/>
+        <v>7.601391688857664e-09</v>
       </c>
     </row>
     <row r="3">
@@ -1230,19 +1230,19 @@
         <v/>
       </c>
       <c r="E3" t="n">
-        <v/>
+        <v>-4.289234445341601e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>9.660721926120328e-08</v>
       </c>
       <c r="G3" t="n">
-        <v/>
+        <v>6.054835936386965e-09</v>
       </c>
       <c r="H3" t="n">
-        <v/>
+        <v>5.980766152072504e-09</v>
       </c>
       <c r="I3" t="n">
-        <v/>
+        <v>6.363504824261628e-09</v>
       </c>
     </row>
     <row r="4">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v/>
+        <v>0.001</v>
       </c>
       <c r="E4" t="n">
-        <v/>
+        <v>4.106955412505385e-09</v>
       </c>
       <c r="F4" t="n">
-        <v/>
+        <v>8.494793562115414e-09</v>
       </c>
       <c r="G4" t="n">
-        <v/>
+        <v>9.800880900195733e-08</v>
       </c>
       <c r="H4" t="n">
-        <v/>
+        <v>7.549992605790588e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>8.85257550644848e-09</v>
       </c>
     </row>
     <row r="5">
@@ -1288,31 +1288,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v/>
       </c>
       <c r="E5" t="n">
-        <v/>
+        <v>6.896455753577099e-09</v>
       </c>
       <c r="F5" t="n">
-        <v/>
+        <v>5.466454988142029e-09</v>
       </c>
       <c r="G5" t="n">
-        <v/>
+        <v>7.714976254635556e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>2.761279458549696e-06</v>
       </c>
       <c r="I5" t="n">
-        <v/>
+        <v>4.8237801840849e-09</v>
       </c>
     </row>
     <row r="6">
@@ -1323,31 +1323,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v/>
       </c>
       <c r="E6" t="n">
-        <v/>
+        <v>-3.849648865250157e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>-2.210000478414463e-10</v>
       </c>
       <c r="G6" t="n">
-        <v/>
+        <v>-7.216361495681907e-10</v>
       </c>
       <c r="H6" t="n">
-        <v/>
+        <v>-1.61478523050937e-09</v>
       </c>
       <c r="I6" t="n">
-        <v/>
+        <v>3.347633139089317e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1363,26 +1363,26 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v/>
+        <v>0.001</v>
       </c>
       <c r="E7" t="n">
-        <v/>
+        <v>-1.969904035319007e-09</v>
       </c>
       <c r="F7" t="n">
-        <v/>
+        <v>1.036818421736439e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>1.101344704155611e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>1.025961254794309e-09</v>
       </c>
       <c r="I7" t="n">
-        <v/>
+        <v>1.51538115536144e-09</v>
       </c>
     </row>
     <row r="8">
@@ -1393,31 +1393,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v/>
       </c>
       <c r="E8" t="n">
-        <v/>
+        <v>-3.895269502901722e-09</v>
       </c>
       <c r="F8" t="n">
-        <v/>
+        <v>1.559421878074629e-08</v>
       </c>
       <c r="G8" t="n">
-        <v/>
+        <v>4.299687162939098e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>2.261703335089935e-09</v>
       </c>
       <c r="I8" t="n">
-        <v/>
+        <v>3.602953063878478e-09</v>
       </c>
     </row>
     <row r="9">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1440,19 +1440,19 @@
         <v/>
       </c>
       <c r="E9" t="n">
-        <v/>
+        <v>-4.091580548521304e-09</v>
       </c>
       <c r="F9" t="n">
-        <v/>
+        <v>-2.793360210584129e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>4.050306011774721e-09</v>
       </c>
       <c r="H9" t="n">
-        <v/>
+        <v>-8.36017791646727e-10</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>1.57839860554923e-10</v>
       </c>
     </row>
     <row r="10">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1475,19 +1475,19 @@
         <v/>
       </c>
       <c r="E10" t="n">
-        <v/>
+        <v>-4.327532270373517e-09</v>
       </c>
       <c r="F10" t="n">
-        <v/>
+        <v>3.061409507323717e-10</v>
       </c>
       <c r="G10" t="n">
-        <v/>
+        <v>1.928967132161557e-09</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>4.64348644632712e-09</v>
       </c>
       <c r="I10" t="n">
-        <v/>
+        <v>5.754836582035277e-10</v>
       </c>
     </row>
     <row r="11">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1510,19 +1510,19 @@
         <v/>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>-4.492015779640615e-09</v>
       </c>
       <c r="F11" t="n">
-        <v/>
+        <v>-2.295773623890641e-09</v>
       </c>
       <c r="G11" t="n">
-        <v/>
+        <v>-2.206516954764175e-09</v>
       </c>
       <c r="H11" t="n">
-        <v/>
+        <v>-2.950263612920613e-09</v>
       </c>
       <c r="I11" t="n">
-        <v/>
+        <v>1.110633525089023e-09</v>
       </c>
     </row>
     <row r="12">
@@ -1533,31 +1533,31 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v/>
       </c>
       <c r="E12" t="n">
-        <v/>
+        <v>-1.084964960148373e-09</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>-8.375368125795622e-10</v>
       </c>
       <c r="G12" t="n">
-        <v/>
+        <v>6.866342006017646e-10</v>
       </c>
       <c r="H12" t="n">
-        <v/>
+        <v>5.005992819882563e-10</v>
       </c>
       <c r="I12" t="n">
-        <v/>
+        <v>7.460584096684323e-10</v>
       </c>
     </row>
     <row r="13">
@@ -1568,31 +1568,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v/>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>-2.845980972773412e-09</v>
       </c>
       <c r="F13" t="n">
-        <v/>
+        <v>8.901214867797349e-10</v>
       </c>
       <c r="G13" t="n">
-        <v/>
+        <v>3.98879770519558e-09</v>
       </c>
       <c r="H13" t="n">
-        <v/>
+        <v>1.869001187099739e-09</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>3.026002775517072e-09</v>
       </c>
     </row>
     <row r="14">
@@ -1603,31 +1603,31 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v/>
       </c>
       <c r="E14" t="n">
-        <v/>
+        <v>-4.276987553079628e-09</v>
       </c>
       <c r="F14" t="n">
-        <v/>
+        <v>-1.280224786710368e-09</v>
       </c>
       <c r="G14" t="n">
-        <v/>
+        <v>4.204097862365146e-09</v>
       </c>
       <c r="H14" t="n">
-        <v/>
+        <v>-7.825342027222203e-10</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>1.426578238415719e-10</v>
       </c>
     </row>
     <row r="15">
@@ -1638,31 +1638,31 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v/>
       </c>
       <c r="E15" t="n">
-        <v/>
+        <v>-4.533147559210108e-09</v>
       </c>
       <c r="F15" t="n">
-        <v/>
+        <v>-9.241853398356815e-10</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>2.271487281912871e-09</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>5.34522515826243e-09</v>
       </c>
       <c r="I15" t="n">
-        <v/>
+        <v>6.109908503663567e-10</v>
       </c>
     </row>
     <row r="16">
@@ -1673,147 +1673,147 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v/>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>-4.296995018775821e-09</v>
       </c>
       <c r="F16" t="n">
-        <v/>
+        <v>-2.504739431267031e-09</v>
       </c>
       <c r="G16" t="n">
-        <v/>
+        <v>-2.079340224983505e-09</v>
       </c>
       <c r="H16" t="n">
-        <v/>
+        <v>-2.894285973391466e-09</v>
       </c>
       <c r="I16" t="n">
-        <v/>
+        <v>2.128256877219839e-09</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v/>
       </c>
       <c r="E17" t="n">
-        <v/>
+        <v>1.063360835669627e-09</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>1.430832032743528e-09</v>
       </c>
       <c r="G17" t="n">
-        <v/>
+        <v>-6.437224348221077e-10</v>
       </c>
       <c r="H17" t="n">
-        <v/>
+        <v>1.416026191480356e-09</v>
       </c>
       <c r="I17" t="n">
-        <v/>
+        <v>7.632457748622214e-10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v/>
       </c>
       <c r="E18" t="n">
-        <v/>
+        <v>-1.598417124586239e-09</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>6.040560586949836e-10</v>
       </c>
       <c r="G18" t="n">
-        <v/>
+        <v>-1.057073723153078e-09</v>
       </c>
       <c r="H18" t="n">
-        <v/>
+        <v>-7.540372435542546e-10</v>
       </c>
       <c r="I18" t="n">
-        <v/>
+        <v>-5.073797497067084e-10</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v/>
       </c>
       <c r="E19" t="n">
-        <v/>
+        <v>-3.761402756225831e-09</v>
       </c>
       <c r="F19" t="n">
-        <v/>
+        <v>4.426350876776947e-09</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>-9.461311287989981e-10</v>
       </c>
       <c r="H19" t="n">
-        <v/>
+        <v>-5.322516469655264e-10</v>
       </c>
       <c r="I19" t="n">
-        <v/>
+        <v>-3.057896966346033e-10</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1822,33 +1822,33 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v/>
+        <v>0.001</v>
       </c>
       <c r="E20" t="n">
-        <v/>
+        <v>-4.218191827466365e-09</v>
       </c>
       <c r="F20" t="n">
-        <v/>
+        <v>4.245264999038013e-10</v>
       </c>
       <c r="G20" t="n">
-        <v/>
+        <v>-3.739507894546942e-10</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>4.656335546430131e-09</v>
       </c>
       <c r="I20" t="n">
-        <v/>
+        <v>-1.658392777793136e-10</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1857,33 +1857,33 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E21" t="n">
-        <v/>
+        <v>-4.008043168218126e-09</v>
       </c>
       <c r="F21" t="n">
-        <v/>
+        <v>-1.378663850326657e-09</v>
       </c>
       <c r="G21" t="n">
-        <v/>
+        <v>-1.96768925522705e-09</v>
       </c>
       <c r="H21" t="n">
-        <v/>
+        <v>-2.117755526242572e-09</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>6.543067074369435e-09</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1892,103 +1892,103 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E22" t="n">
-        <v/>
+        <v>6.611881829346997e-09</v>
       </c>
       <c r="F22" t="n">
-        <v/>
+        <v>8.437168254666333e-11</v>
       </c>
       <c r="G22" t="n">
-        <v/>
+        <v>9.336682542369051e-10</v>
       </c>
       <c r="H22" t="n">
-        <v/>
+        <v>-4.936508318269135e-10</v>
       </c>
       <c r="I22" t="n">
-        <v/>
+        <v>1.907109634640205e-10</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E23" t="n">
-        <v/>
+        <v>-4.089044929160331e-09</v>
       </c>
       <c r="F23" t="n">
-        <v/>
+        <v>7.811879686542918e-10</v>
       </c>
       <c r="G23" t="n">
-        <v/>
+        <v>1.54184928976048e-09</v>
       </c>
       <c r="H23" t="n">
-        <v/>
+        <v>-1.031014788834865e-09</v>
       </c>
       <c r="I23" t="n">
-        <v/>
+        <v>1.825138799249094e-10</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v/>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>-4.429561358159157e-09</v>
       </c>
       <c r="F24" t="n">
-        <v/>
+        <v>4.511564581504649e-09</v>
       </c>
       <c r="G24" t="n">
-        <v/>
+        <v>2.023587597601991e-09</v>
       </c>
       <c r="H24" t="n">
-        <v/>
+        <v>-7.503881344026382e-10</v>
       </c>
       <c r="I24" t="n">
-        <v/>
+        <v>4.714333996948073e-10</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2000,65 +2000,65 @@
         <v/>
       </c>
       <c r="E25" t="n">
-        <v/>
+        <v>-4.295411622385984e-09</v>
       </c>
       <c r="F25" t="n">
-        <v/>
+        <v>-1.121765043024582e-10</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>6.881069763613266e-09</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>-1.085496821370898e-09</v>
       </c>
       <c r="I25" t="n">
-        <v/>
+        <v>1.99143813910734e-10</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v/>
+        <v>0.001</v>
       </c>
       <c r="E26" t="n">
-        <v/>
+        <v>-4.532683942203711e-09</v>
       </c>
       <c r="F26" t="n">
-        <v/>
+        <v>-2.227772233030481e-09</v>
       </c>
       <c r="G26" t="n">
-        <v/>
+        <v>-1.911424418747484e-09</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>-3.001081011893348e-09</v>
       </c>
       <c r="I26" t="n">
-        <v/>
+        <v>1.389296843413113e-09</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2067,138 +2067,138 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>-4.620354255003145e-09</v>
       </c>
       <c r="F27" t="n">
-        <v/>
+        <v>-1.71448522345802e-09</v>
       </c>
       <c r="G27" t="n">
-        <v/>
+        <v>-2.077924336239886e-09</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>-2.44893394244557e-09</v>
       </c>
       <c r="I27" t="n">
-        <v/>
+        <v>-3.215396298160228e-09</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v/>
+        <v>0.001</v>
       </c>
       <c r="E28" t="n">
-        <v/>
+        <v>-3.550121152703622e-09</v>
       </c>
       <c r="F28" t="n">
-        <v/>
+        <v>-1.78010760580055e-09</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>-2.318708491847873e-09</v>
       </c>
       <c r="H28" t="n">
-        <v/>
+        <v>-2.944241018801392e-09</v>
       </c>
       <c r="I28" t="n">
-        <v/>
+        <v>-3.340237331505456e-09</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v/>
       </c>
       <c r="E29" t="n">
-        <v/>
+        <v>-4.522919002426998e-09</v>
       </c>
       <c r="F29" t="n">
-        <v/>
+        <v>-1.58164012092429e-09</v>
       </c>
       <c r="G29" t="n">
-        <v/>
+        <v>-2.360302742968255e-09</v>
       </c>
       <c r="H29" t="n">
-        <v/>
+        <v>-2.921824254598207e-09</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>-3.478134854422212e-09</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v/>
       </c>
       <c r="E30" t="n">
-        <v/>
+        <v>-3.965669729812913e-09</v>
       </c>
       <c r="F30" t="n">
-        <v/>
+        <v>-1.31595463254479e-09</v>
       </c>
       <c r="G30" t="n">
-        <v/>
+        <v>-5.694203935219213e-11</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>-2.177626468983502e-09</v>
       </c>
       <c r="I30" t="n">
-        <v/>
+        <v>-3.024912879724147e-09</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2207,103 +2207,103 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E31" t="n">
-        <v/>
+        <v>-4.55240411862345e-09</v>
       </c>
       <c r="F31" t="n">
-        <v/>
+        <v>-2.235761604134518e-09</v>
       </c>
       <c r="G31" t="n">
-        <v/>
+        <v>-2.0727293928239e-09</v>
       </c>
       <c r="H31" t="n">
-        <v/>
+        <v>-2.085545670182372e-09</v>
       </c>
       <c r="I31" t="n">
-        <v/>
+        <v>-3.411316514366885e-09</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v/>
+        <v>-3.69317143762145e-09</v>
       </c>
       <c r="E32" t="n">
-        <v/>
+        <v>0.001</v>
       </c>
       <c r="F32" t="n">
-        <v/>
+        <v>-1.893655081590023e-10</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>-6.385396229970459e-11</v>
       </c>
       <c r="H32" t="n">
-        <v/>
+        <v>3.754763433934879e-10</v>
       </c>
       <c r="I32" t="n">
-        <v/>
+        <v>-2.286325128103791e-09</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>-4.493794384026831e-09</v>
       </c>
       <c r="E33" t="n">
         <v/>
       </c>
       <c r="F33" t="n">
-        <v/>
+        <v>1.617223316083949e-09</v>
       </c>
       <c r="G33" t="n">
-        <v/>
+        <v>8.839785627017017e-09</v>
       </c>
       <c r="H33" t="n">
-        <v/>
+        <v>6.404920111775167e-10</v>
       </c>
       <c r="I33" t="n">
-        <v/>
+        <v>-4.041504267714164e-09</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2312,488 +2312,488 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>-4.386946360132971e-09</v>
       </c>
       <c r="E34" t="n">
         <v/>
       </c>
       <c r="F34" t="n">
-        <v/>
+        <v>3.782246736562618e-10</v>
       </c>
       <c r="G34" t="n">
-        <v/>
+        <v>2.488587840183524e-08</v>
       </c>
       <c r="H34" t="n">
-        <v/>
+        <v>1.664634739930471e-09</v>
       </c>
       <c r="I34" t="n">
-        <v/>
+        <v>-3.505943046883095e-09</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>-4.454006044915851e-09</v>
       </c>
       <c r="E35" t="n">
         <v/>
       </c>
       <c r="F35" t="n">
-        <v/>
+        <v>-4.406017677567334e-10</v>
       </c>
       <c r="G35" t="n">
-        <v/>
+        <v>7.04653463982327e-09</v>
       </c>
       <c r="H35" t="n">
-        <v/>
+        <v>5.982716397258804e-09</v>
       </c>
       <c r="I35" t="n">
-        <v/>
+        <v>-3.759946460547391e-09</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v/>
+        <v>-4.639785992278809e-09</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F36" t="n">
-        <v/>
+        <v>-1.948029155466617e-09</v>
       </c>
       <c r="G36" t="n">
-        <v/>
+        <v>4.37609749664806e-09</v>
       </c>
       <c r="H36" t="n">
-        <v/>
+        <v>-1.919057893124717e-09</v>
       </c>
       <c r="I36" t="n">
-        <v/>
+        <v>-2.036205183938167e-09</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v/>
+        <v>1.135526257185091e-05</v>
       </c>
       <c r="E37" t="n">
         <v/>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>2.108405422030542e-09</v>
       </c>
       <c r="G37" t="n">
-        <v/>
+        <v>1.761952368124537e-08</v>
       </c>
       <c r="H37" t="n">
-        <v/>
+        <v>6.330403339817373e-09</v>
       </c>
       <c r="I37" t="n">
-        <v/>
+        <v>6.30970369240664e-10</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>1.59036599206093e-08</v>
       </c>
       <c r="E38" t="n">
         <v/>
       </c>
       <c r="F38" t="n">
-        <v/>
+        <v>8.014275947859846e-08</v>
       </c>
       <c r="G38" t="n">
-        <v/>
+        <v>6.007959485435506e-08</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>1.576725493155117e-08</v>
       </c>
       <c r="I38" t="n">
-        <v/>
+        <v>1.512291128900862e-08</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v/>
+        <v>-1.332877069332781e-09</v>
       </c>
       <c r="E39" t="n">
-        <v/>
+        <v>0.001</v>
       </c>
       <c r="F39" t="n">
-        <v/>
+        <v>2.908610502247928e-09</v>
       </c>
       <c r="G39" t="n">
-        <v/>
+        <v>0.1442049055471118</v>
       </c>
       <c r="H39" t="n">
-        <v/>
+        <v>4.382780873458568e-09</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>-6.906867383792801e-10</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>-7.862973688165211e-10</v>
       </c>
       <c r="E40" t="n">
         <v/>
       </c>
       <c r="F40" t="n">
-        <v/>
+        <v>3.304299259255586e-09</v>
       </c>
       <c r="G40" t="n">
-        <v/>
+        <v>2.177001407429877e-08</v>
       </c>
       <c r="H40" t="n">
-        <v/>
+        <v>8.707666082508518e-08</v>
       </c>
       <c r="I40" t="n">
-        <v/>
+        <v>1.873937549986661e-09</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v/>
+        <v>-3.702051110473355e-09</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F41" t="n">
-        <v/>
+        <v>-1.352594216621293e-09</v>
       </c>
       <c r="G41" t="n">
-        <v/>
+        <v>7.161645059499944e-09</v>
       </c>
       <c r="H41" t="n">
-        <v/>
+        <v>-1.552323718282145e-09</v>
       </c>
       <c r="I41" t="n">
-        <v/>
+        <v>0.1746734758827457</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v/>
+        <v>-2.957552998522707e-09</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F42" t="n">
-        <v/>
+        <v>-6.199813800583645e-10</v>
       </c>
       <c r="G42" t="n">
-        <v/>
+        <v>1.087686184039591e-08</v>
       </c>
       <c r="H42" t="n">
-        <v/>
+        <v>1.317043436808972e-09</v>
       </c>
       <c r="I42" t="n">
-        <v/>
+        <v>-3.771456672120116e-09</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v/>
+        <v>1.384221694230547e-08</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F43" t="n">
-        <v/>
+        <v>1.568002499243932e-09</v>
       </c>
       <c r="G43" t="n">
-        <v/>
+        <v>1.475158855464631e-09</v>
       </c>
       <c r="H43" t="n">
-        <v/>
+        <v>2.983558601003991e-09</v>
       </c>
       <c r="I43" t="n">
-        <v/>
+        <v>1.204956378199939e-08</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>-3.768685770910559e-09</v>
       </c>
       <c r="E44" t="n">
         <v/>
       </c>
       <c r="F44" t="n">
-        <v/>
+        <v>3.820120809645587e-11</v>
       </c>
       <c r="G44" t="n">
-        <v/>
+        <v>5.724184185108211e-08</v>
       </c>
       <c r="H44" t="n">
-        <v/>
+        <v>1.155134904783134e-09</v>
       </c>
       <c r="I44" t="n">
-        <v/>
+        <v>-3.717782890915769e-09</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>-4.293923484240085e-09</v>
       </c>
       <c r="E45" t="n">
         <v/>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>1.51334145712953e-10</v>
       </c>
       <c r="G45" t="n">
-        <v/>
+        <v>1.404486219529233e-08</v>
       </c>
       <c r="H45" t="n">
-        <v/>
+        <v>1.090499853159825e-08</v>
       </c>
       <c r="I45" t="n">
-        <v/>
+        <v>-3.465453772613996e-09</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>-3.939927276398467e-09</v>
       </c>
       <c r="E46" t="n">
         <v/>
       </c>
       <c r="F46" t="n">
-        <v/>
+        <v>-1.921032421224416e-09</v>
       </c>
       <c r="G46" t="n">
-        <v/>
+        <v>6.907585114480853e-09</v>
       </c>
       <c r="H46" t="n">
-        <v/>
+        <v>-2.062481712726999e-09</v>
       </c>
       <c r="I46" t="n">
-        <v/>
+        <v>-2.918667982441778e-09</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>-1.40072210495777e-09</v>
       </c>
       <c r="E47" t="n">
         <v/>
       </c>
       <c r="F47" t="n">
-        <v/>
+        <v>3.76311379864773e-10</v>
       </c>
       <c r="G47" t="n">
-        <v/>
+        <v>5.609820381921614e-09</v>
       </c>
       <c r="H47" t="n">
-        <v/>
+        <v>1.257159037549386e-09</v>
       </c>
       <c r="I47" t="n">
-        <v/>
+        <v>-3.987170560623659e-09</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2802,63 +2802,63 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>-4.131208897374992e-09</v>
       </c>
       <c r="E48" t="n">
         <v/>
       </c>
       <c r="F48" t="n">
-        <v/>
+        <v>1.826695119415328e-10</v>
       </c>
       <c r="G48" t="n">
-        <v/>
+        <v>-6.345812269477688e-10</v>
       </c>
       <c r="H48" t="n">
-        <v/>
+        <v>-3.514853244713791e-10</v>
       </c>
       <c r="I48" t="n">
-        <v/>
+        <v>-3.611689283520155e-09</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>-3.899895146543647e-09</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F49" t="n">
-        <v/>
+        <v>2.897295486536898e-09</v>
       </c>
       <c r="G49" t="n">
-        <v/>
+        <v>6.702064380566613e-09</v>
       </c>
       <c r="H49" t="n">
-        <v/>
+        <v>2.168808953373418e-10</v>
       </c>
       <c r="I49" t="n">
-        <v/>
+        <v>-4.268593110227891e-09</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2868,32 +2868,32 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v/>
+        <v>-4.035671795437813e-09</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="F50" t="n">
-        <v/>
+        <v>7.562468866420974e-10</v>
       </c>
       <c r="G50" t="n">
-        <v/>
+        <v>5.996145276190102e-09</v>
       </c>
       <c r="H50" t="n">
-        <v/>
+        <v>6.30974910414328e-09</v>
       </c>
       <c r="I50" t="n">
-        <v/>
+        <v>-3.984262348720991e-09</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2903,67 +2903,67 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>-3.821582128467596e-09</v>
       </c>
       <c r="E51" t="n">
         <v/>
       </c>
       <c r="F51" t="n">
-        <v/>
+        <v>-9.968218870142542e-10</v>
       </c>
       <c r="G51" t="n">
-        <v/>
+        <v>4.437548389296383e-09</v>
       </c>
       <c r="H51" t="n">
-        <v/>
+        <v>-1.313679986945935e-09</v>
       </c>
       <c r="I51" t="n">
-        <v/>
+        <v>-2.088078747322859e-10</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>-3.744703788468363e-09</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F52" t="n">
-        <v/>
+        <v>-5.104031753329182e-10</v>
       </c>
       <c r="G52" t="n">
-        <v/>
+        <v>7.122616624035064e-09</v>
       </c>
       <c r="H52" t="n">
-        <v/>
+        <v>-1.943479332408944e-10</v>
       </c>
       <c r="I52" t="n">
-        <v/>
+        <v>-3.654905442354816e-09</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2973,32 +2973,32 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v/>
+        <v>-1.752506341831659e-09</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F53" t="n">
-        <v/>
+        <v>2.576676727891132e-10</v>
       </c>
       <c r="G53" t="n">
-        <v/>
+        <v>1.830605164531584e-10</v>
       </c>
       <c r="H53" t="n">
-        <v/>
+        <v>-5.580310770960329e-10</v>
       </c>
       <c r="I53" t="n">
-        <v/>
+        <v>-1.43785112466897e-09</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3008,32 +3008,32 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>-4.153894763417958e-09</v>
       </c>
       <c r="E54" t="n">
         <v/>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>3.263613784712122e-09</v>
       </c>
       <c r="G54" t="n">
-        <v/>
+        <v>1.131909665277027e-08</v>
       </c>
       <c r="H54" t="n">
-        <v/>
+        <v>4.765251790851367e-11</v>
       </c>
       <c r="I54" t="n">
-        <v/>
+        <v>-3.754781619828955e-09</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3047,28 +3047,28 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v/>
+        <v>-4.010554143187793e-09</v>
       </c>
       <c r="E55" t="n">
         <v/>
       </c>
       <c r="F55" t="n">
-        <v/>
+        <v>6.987440137567641e-10</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>2.94628718730051e-08</v>
       </c>
       <c r="H55" t="n">
-        <v/>
+        <v>1.270029045652411e-10</v>
       </c>
       <c r="I55" t="n">
-        <v/>
+        <v>-3.351106073406787e-09</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3082,28 +3082,28 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v/>
+        <v>-4.34041273847125e-09</v>
       </c>
       <c r="E56" t="n">
-        <v/>
+        <v>0.001</v>
       </c>
       <c r="F56" t="n">
-        <v/>
+        <v>-1.91920018393538e-09</v>
       </c>
       <c r="G56" t="n">
-        <v/>
+        <v>4.430501545925537e-09</v>
       </c>
       <c r="H56" t="n">
-        <v/>
+        <v>-2.379900257391961e-09</v>
       </c>
       <c r="I56" t="n">
-        <v>0.9999996451238262</v>
+        <v>-1.990079925220022e-09</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3117,28 +3117,28 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v/>
+        <v>-3.495548862056048e-09</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="F57" t="n">
-        <v/>
+        <v>-1.936880688840705e-09</v>
       </c>
       <c r="G57" t="n">
-        <v/>
+        <v>3.855619675843031e-09</v>
       </c>
       <c r="H57" t="n">
-        <v/>
+        <v>-1.965996282358502e-09</v>
       </c>
       <c r="I57" t="n">
-        <v/>
+        <v>-4.847361782292492e-09</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3152,28 +3152,28 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>-4.265328259842365e-09</v>
       </c>
       <c r="E58" t="n">
         <v/>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>-1.818973580213967e-09</v>
       </c>
       <c r="G58" t="n">
-        <v/>
+        <v>-9.636691286938211e-10</v>
       </c>
       <c r="H58" t="n">
-        <v/>
+        <v>-2.449518277514357e-09</v>
       </c>
       <c r="I58" t="n">
-        <v/>
+        <v>-4.826518063344988e-09</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3187,28 +3187,28 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>-4.473948214297139e-09</v>
       </c>
       <c r="E59" t="n">
         <v/>
       </c>
       <c r="F59" t="n">
-        <v/>
+        <v>-1.59288816538954e-09</v>
       </c>
       <c r="G59" t="n">
-        <v/>
+        <v>3.605768342175373e-09</v>
       </c>
       <c r="H59" t="n">
-        <v/>
+        <v>-2.374026594550828e-09</v>
       </c>
       <c r="I59" t="n">
-        <v/>
+        <v>-4.881829824092064e-09</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3222,63 +3222,63 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v/>
+        <v>-3.790016729425227e-09</v>
       </c>
       <c r="E60" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="F60" t="n">
-        <v/>
+        <v>-8.080790197564764e-10</v>
       </c>
       <c r="G60" t="n">
-        <v/>
+        <v>1.715506768944471e-08</v>
       </c>
       <c r="H60" t="n">
-        <v/>
+        <v>-1.210929697134936e-09</v>
       </c>
       <c r="I60" t="n">
-        <v/>
+        <v>-4.795004428117606e-09</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v/>
+        <v>-4.432173081548759e-09</v>
       </c>
       <c r="E61" t="n">
         <v/>
       </c>
       <c r="F61" t="n">
-        <v/>
+        <v>-1.980856410782259e-09</v>
       </c>
       <c r="G61" t="n">
-        <v/>
+        <v>3.660591026386771e-09</v>
       </c>
       <c r="H61" t="n">
-        <v>1.993554252564312e-07</v>
+        <v>-1.226972717006471e-09</v>
       </c>
       <c r="I61" t="n">
-        <v/>
+        <v>-4.852999155062821e-09</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3288,177 +3288,177 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v/>
+        <v>-1.745691894852981e-09</v>
       </c>
       <c r="E62" t="n">
-        <v/>
+        <v>1.824899206582511e-09</v>
       </c>
       <c r="F62" t="n">
         <v/>
       </c>
       <c r="G62" t="n">
-        <v/>
+        <v>6.324066054170985e-08</v>
       </c>
       <c r="H62" t="n">
-        <v>-2.990331378846468e-07</v>
+        <v>9.069258237553507e-10</v>
       </c>
       <c r="I62" t="n">
-        <v/>
+        <v>8.688392942309089e-08</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>-1.872722264866878e-09</v>
       </c>
       <c r="E63" t="n">
-        <v/>
+        <v>-3.637604318368076e-10</v>
       </c>
       <c r="F63" t="n">
-        <v/>
+        <v>0.001</v>
       </c>
       <c r="G63" t="n">
-        <v/>
+        <v>-6.274759073109553e-11</v>
       </c>
       <c r="H63" t="n">
-        <v/>
+        <v>9.264175801956023e-11</v>
       </c>
       <c r="I63" t="n">
-        <v/>
+        <v>1.398697638894002e-10</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v/>
+        <v>-1.504875110826658e-09</v>
       </c>
       <c r="E64" t="n">
-        <v/>
+        <v>3.131056020289352e-10</v>
       </c>
       <c r="F64" t="n">
         <v/>
       </c>
       <c r="G64" t="n">
-        <v/>
+        <v>1.363452441905524e-07</v>
       </c>
       <c r="H64" t="n">
-        <v>2.990331378846468e-07</v>
+        <v>1.623256343772626e-09</v>
       </c>
       <c r="I64" t="n">
-        <v/>
+        <v>1.238323808583114e-07</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v/>
+        <v>-1.952290531625786e-09</v>
       </c>
       <c r="E65" t="n">
-        <v/>
+        <v>-5.16617473395985e-10</v>
       </c>
       <c r="F65" t="n">
         <v/>
       </c>
       <c r="G65" t="n">
-        <v/>
+        <v>4.186322014514979e-08</v>
       </c>
       <c r="H65" t="n">
-        <v>1.993554252564311e-07</v>
+        <v>5.255160403959393e-09</v>
       </c>
       <c r="I65" t="n">
-        <v/>
+        <v>8.874011374142123e-08</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>-2.779069552186397e-09</v>
       </c>
       <c r="E66" t="n">
-        <v/>
+        <v>-1.979868921441566e-09</v>
       </c>
       <c r="F66" t="n">
         <v/>
       </c>
       <c r="G66" t="n">
-        <v/>
+        <v>4.772071924828812e-08</v>
       </c>
       <c r="H66" t="n">
-        <v>-2.990331378846468e-07</v>
+        <v>-1.952766524837365e-09</v>
       </c>
       <c r="I66" t="n">
-        <v/>
+        <v>2.181651226405789e-07</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3467,339 +3467,453 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>1.229454251830606e-08</v>
       </c>
       <c r="E67" t="n">
-        <v/>
+        <v>-5.317416382734693e-10</v>
       </c>
       <c r="F67" t="n">
         <v/>
       </c>
       <c r="G67" t="n">
-        <v/>
+        <v>6.52222254290488e-08</v>
       </c>
       <c r="H67" t="n">
-        <v>-9.967771262821555e-08</v>
+        <v>1.785295172031281e-09</v>
       </c>
       <c r="I67" t="n">
-        <v/>
+        <v>1.220319858619881e-07</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v/>
+        <v>4.292216402203161e-09</v>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>1.720631318323104e-09</v>
       </c>
       <c r="F68" t="n">
         <v/>
       </c>
       <c r="G68" t="n">
-        <v/>
+        <v>2.613395211827474e-10</v>
       </c>
       <c r="H68" t="n">
-        <v>1.993554252564312e-07</v>
+        <v>2.881077197507161e-09</v>
       </c>
       <c r="I68" t="n">
-        <v/>
+        <v>3.423826563755429e-10</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v/>
+        <v>1.073273373609578e-09</v>
       </c>
       <c r="E69" t="n">
-        <v/>
+        <v>-2.20273815444345e-10</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G69" t="n">
-        <v/>
+        <v>1.371223770350843e-05</v>
       </c>
       <c r="H69" t="n">
-        <v>1.993554252564311e-07</v>
+        <v>8.762284757294595e-10</v>
       </c>
       <c r="I69" t="n">
-        <v/>
+        <v>1.492797583061999e-07</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v/>
+        <v>1.134424327497759e-09</v>
       </c>
       <c r="E70" t="n">
-        <v/>
+        <v>-1.328940074781586e-10</v>
       </c>
       <c r="F70" t="n">
         <v/>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>7.468170822076345e-08</v>
       </c>
       <c r="H70" t="n">
-        <v>-2.990331378846468e-07</v>
+        <v>7.81867088320707e-09</v>
       </c>
       <c r="I70" t="n">
-        <v/>
+        <v>1.2896005566614e-07</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v/>
+        <v>-1.894419761689235e-09</v>
       </c>
       <c r="E71" t="n">
-        <v/>
+        <v>-2.28988041442329e-09</v>
       </c>
       <c r="F71" t="n">
         <v/>
       </c>
       <c r="G71" t="n">
-        <v/>
+        <v>6.085280237815311e-08</v>
       </c>
       <c r="H71" t="n">
-        <v>1</v>
+        <v>-2.23491833009329e-09</v>
       </c>
       <c r="I71" t="n">
-        <v/>
+        <v>2.317715719771417e-07</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>i4</t>
-        </is>
+          <t>i1</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>9.863845844246635e-08</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1.777700901497717e-09</v>
+      </c>
+      <c r="F72" t="n">
+        <v/>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>9.632056000502654e-08</v>
+      </c>
+      <c r="H72" t="n">
+        <v>4.64046097564468e-09</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1.785411121299707e-07</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>i5</t>
-        </is>
+          <t>i2</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>2.079842205079652e-08</v>
+      </c>
+      <c r="E73" t="n">
+        <v>7.96538013082544e-08</v>
+      </c>
+      <c r="F73" t="n">
+        <v/>
+      </c>
+      <c r="G73" t="n">
+        <v>1.365196188793321e-05</v>
       </c>
       <c r="H73" t="n">
-        <v>1.000000128926522</v>
+        <v>1.25729063544515e-08</v>
+      </c>
+      <c r="I73" t="n">
+        <v>3.443763987641717e-07</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>6.160918635437486e-09</v>
+      </c>
+      <c r="E74" t="n">
+        <v>3.086527370266555e-09</v>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>0.001</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.0009319978586902488</v>
+      </c>
+      <c r="H74" t="n">
+        <v>3.951642417071748e-09</v>
+      </c>
+      <c r="I74" t="n">
+        <v>2.872893634895279e-07</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>i4</t>
-        </is>
+          <t>i5</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>6.137765027043009e-09</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3.579177414696797e-09</v>
+      </c>
+      <c r="F75" t="n">
+        <v/>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>1.217868087663223e-07</v>
+      </c>
+      <c r="H75" t="n">
+        <v>4.284357176839737e-08</v>
+      </c>
+      <c r="I75" t="n">
+        <v>2.338195088628347e-07</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>i5</t>
-        </is>
+          <t>i6</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>-1.112212068491488e-10</v>
+      </c>
+      <c r="E76" t="n">
+        <v>-7.614872285590392e-10</v>
+      </c>
+      <c r="F76" t="n">
+        <v/>
+      </c>
+      <c r="G76" t="n">
+        <v>1.580279614318453e-07</v>
       </c>
       <c r="H76" t="n">
-        <v>1</v>
+        <v>-1.515560220615902e-09</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.297335189195819</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>i4</t>
-        </is>
+          <t>i1</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>7.099751561689034e-09</v>
+      </c>
+      <c r="E77" t="n">
+        <v>4.223585843626621e-10</v>
       </c>
       <c r="F77" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G77" t="n">
-        <v>1</v>
+        <v>4.398576064322761e-08</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1.400119993204404e-09</v>
+      </c>
+      <c r="I77" t="n">
+        <v>9.155510342025651e-08</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>-3.400492596824471e-10</v>
+      </c>
+      <c r="E78" t="n">
+        <v>2.59521649562194e-09</v>
+      </c>
+      <c r="F78" t="n">
+        <v/>
+      </c>
+      <c r="G78" t="n">
+        <v>6.305167294373498e-08</v>
+      </c>
+      <c r="H78" t="n">
+        <v>4.785021954105795e-11</v>
+      </c>
+      <c r="I78" t="n">
+        <v>7.628855926056622e-08</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>-2.682407685965077e-10</v>
+      </c>
+      <c r="E79" t="n">
+        <v>3.478580234394867e-10</v>
+      </c>
+      <c r="F79" t="n">
+        <v/>
+      </c>
+      <c r="G79" t="n">
+        <v>-5.703918321071826e-11</v>
+      </c>
+      <c r="H79" t="n">
+        <v>-2.432198763451754e-10</v>
+      </c>
+      <c r="I79" t="n">
+        <v>1.000962648625797e-10</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3807,14 +3921,29 @@
           <t>i5</t>
         </is>
       </c>
+      <c r="D80" t="n">
+        <v>-1.600047730960581e-11</v>
+      </c>
+      <c r="E80" t="n">
+        <v>7.290908529222786e-10</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G80" t="n">
+        <v>4.58022051818766e-08</v>
+      </c>
       <c r="H80" t="n">
-        <v>1</v>
+        <v>5.641743621192259e-09</v>
+      </c>
+      <c r="I80" t="n">
+        <v>9.140268507935354e-08</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3824,37 +3953,67 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>i2</t>
-        </is>
+          <t>i6</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>-1.341642251187985e-09</v>
+      </c>
+      <c r="E81" t="n">
+        <v>-9.924834815465981e-10</v>
       </c>
       <c r="F81" t="n">
-        <v>1</v>
+        <v/>
+      </c>
+      <c r="G81" t="n">
+        <v>5.278542258284994e-08</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-1.33964473516346e-09</v>
+      </c>
+      <c r="I81" t="n">
+        <v>4.775855371909564e-07</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>4.113238331950654e-09</v>
+      </c>
+      <c r="E82" t="n">
+        <v>-4.786223674119086e-10</v>
+      </c>
+      <c r="F82" t="n">
+        <v/>
+      </c>
+      <c r="G82" t="n">
+        <v>4.210790714969312e-08</v>
+      </c>
+      <c r="H82" t="n">
+        <v>5.140523470360305e-11</v>
+      </c>
+      <c r="I82" t="n">
+        <v>9.660640433046509e-08</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3867,17 +4026,29 @@
           <t>i2</t>
         </is>
       </c>
+      <c r="D83" t="n">
+        <v>2.132975114188877e-10</v>
+      </c>
+      <c r="E83" t="n">
+        <v>2.894348477143323e-09</v>
+      </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>7.09857181154781e-08</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-3.306292779432547e-11</v>
+      </c>
+      <c r="I83" t="n">
+        <v>9.786628340932694e-08</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3891,56 +4062,98 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>2.699419000544611e-10</v>
+      </c>
+      <c r="E84" t="n">
+        <v>4.754389465353677e-10</v>
+      </c>
+      <c r="F84" t="n">
+        <v/>
+      </c>
+      <c r="G84" t="n">
+        <v>-1.456598175712066e-11</v>
+      </c>
+      <c r="H84" t="n">
+        <v>-2.323920162380037e-10</v>
+      </c>
+      <c r="I84" t="n">
+        <v>2.150823455617192e-10</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>i1</t>
-        </is>
+          <t>i4</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>5.136504213286967e-10</v>
+      </c>
+      <c r="E85" t="n">
+        <v>7.059110924852794e-10</v>
+      </c>
+      <c r="F85" t="n">
+        <v/>
       </c>
       <c r="G85" t="n">
-        <v>1</v>
+        <v>1.633259976889927e-07</v>
+      </c>
+      <c r="H85" t="n">
+        <v>2.96466885203505e-10</v>
+      </c>
+      <c r="I85" t="n">
+        <v>1.401174239588963e-07</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>i2</t>
-        </is>
+          <t>i6</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>-2.062173547855187e-09</v>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>-1.924392772894821e-09</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G86" t="n">
+        <v>4.787018217003626e-08</v>
       </c>
       <c r="H86" t="n">
-        <v>1</v>
+        <v>-2.354100782048232e-09</v>
+      </c>
+      <c r="I86" t="n">
+        <v>2.363515247202729e-07</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3950,17 +4163,32 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>-3.762979549813964e-10</v>
+      </c>
+      <c r="E87" t="n">
+        <v>-1.911937498151289e-09</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G87" t="n">
+        <v>4.147064330801392e-08</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-1.952063570869694e-09</v>
+      </c>
+      <c r="I87" t="n">
+        <v>2.902681068454876e-08</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3970,17 +4198,32 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>i5</t>
-        </is>
+          <t>i2</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>-2.025941547864877e-09</v>
+      </c>
+      <c r="E88" t="n">
+        <v>-1.086703142126318e-09</v>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v/>
+      </c>
+      <c r="G88" t="n">
+        <v>6.401583952339826e-08</v>
+      </c>
+      <c r="H88" t="n">
+        <v>-2.368266071623073e-09</v>
+      </c>
+      <c r="I88" t="n">
+        <v>2.697058361076645e-08</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3990,14 +4233,26 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>-2.421194572994772e-09</v>
+      </c>
+      <c r="E89" t="n">
+        <v>-2.180168993424828e-09</v>
+      </c>
+      <c r="F89" t="n">
+        <v/>
+      </c>
+      <c r="G89" t="n">
+        <v>-1.269876158269017e-10</v>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
+        <v>-2.498107614841147e-09</v>
+      </c>
+      <c r="I89" t="n">
+        <v>-5.462084737011546e-10</v>
       </c>
     </row>
     <row r="90">
@@ -4017,19 +4272,22 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>3.06633849802128e-10</v>
+        <v>-1.109148515322225e-09</v>
       </c>
       <c r="E90" t="n">
-        <v>4.392017178446295e-10</v>
+        <v>-7.832297744792421e-10</v>
+      </c>
+      <c r="F90" t="n">
+        <v/>
       </c>
       <c r="G90" t="n">
-        <v>4.994665630986231e-08</v>
+        <v>2.217562957671923e-07</v>
       </c>
       <c r="H90" t="n">
-        <v>-1.383859136338584e-10</v>
+        <v>-1.240744899304774e-09</v>
       </c>
       <c r="I90" t="n">
-        <v>3.635408659578188e-08</v>
+        <v>3.641305460296557e-08</v>
       </c>
     </row>
     <row r="91">
@@ -4049,19 +4307,22 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>-2.044795321417416e-09</v>
+        <v>-2.255943729072871e-09</v>
       </c>
       <c r="E91" t="n">
-        <v>-2.14573815425434e-09</v>
+        <v>-1.986073410691257e-09</v>
+      </c>
+      <c r="F91" t="n">
+        <v/>
       </c>
       <c r="G91" t="n">
-        <v>8.893035238887897e-09</v>
+        <v>4.014129682833421e-08</v>
       </c>
       <c r="H91" t="n">
-        <v>-3.869178957141516e-10</v>
+        <v>-1.33780843606449e-09</v>
       </c>
       <c r="I91" t="n">
-        <v>1.993050101577589e-08</v>
+        <v>2.82343554147192e-08</v>
       </c>
     </row>
     <row r="92">
@@ -4081,19 +4342,22 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>-1.30386461287478e-09</v>
+        <v>-5.183601438975077e-10</v>
       </c>
       <c r="E92" t="n">
-        <v>9.268435773953191e-11</v>
+        <v>1.956937938194429e-08</v>
       </c>
       <c r="F92" t="n">
-        <v>6.137062180996011e-09</v>
+        <v>8.164810384737742e-08</v>
+      </c>
+      <c r="G92" t="n">
+        <v/>
       </c>
       <c r="H92" t="n">
-        <v>1.516592115929228e-09</v>
+        <v>1.993229923602788e-09</v>
       </c>
       <c r="I92" t="n">
-        <v>1.136165254596434e-08</v>
+        <v>-1.78971812537464e-09</v>
       </c>
     </row>
     <row r="93">
@@ -4113,19 +4377,22 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>-1.29905846366312e-09</v>
+        <v>-7.211789492545289e-10</v>
       </c>
       <c r="E93" t="n">
-        <v>-5.495002941097969e-10</v>
+        <v>1.002500298038112e-08</v>
       </c>
       <c r="F93" t="n">
-        <v>1.91408562877343e-08</v>
+        <v>1.256796158359861e-07</v>
+      </c>
+      <c r="G93" t="n">
+        <v/>
       </c>
       <c r="H93" t="n">
-        <v>1.256859915212582e-09</v>
+        <v>1.64287210622647e-09</v>
       </c>
       <c r="I93" t="n">
-        <v>9.647494005612059e-09</v>
+        <v>-1.96991666986629e-09</v>
       </c>
     </row>
     <row r="94">
@@ -4145,19 +4412,22 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>-1.406632887906844e-09</v>
+        <v>-6.026713927037175e-10</v>
       </c>
       <c r="E94" t="n">
-        <v>-1.335064571275694e-09</v>
+        <v>2.495720016459382e-10</v>
       </c>
       <c r="F94" t="n">
-        <v>-8.164873291464724e-10</v>
+        <v>-1.03445467977432e-10</v>
+      </c>
+      <c r="G94" t="n">
+        <v/>
       </c>
       <c r="H94" t="n">
-        <v>1.073838251700947e-09</v>
+        <v>1.512593975183118e-09</v>
       </c>
       <c r="I94" t="n">
-        <v>-3.72198054965347e-10</v>
+        <v>2.208418522585411e-09</v>
       </c>
     </row>
     <row r="95">
@@ -4177,19 +4447,22 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>-1.127468212738432e-09</v>
+        <v>-6.16278432830002e-10</v>
       </c>
       <c r="E95" t="n">
-        <v>-3.896607025571598e-10</v>
+        <v>6.127439483402009e-09</v>
       </c>
       <c r="F95" t="n">
-        <v>6.830011421446475e-09</v>
+        <v>4.338213471896067e-08</v>
+      </c>
+      <c r="G95" t="n">
+        <v/>
       </c>
       <c r="H95" t="n">
-        <v>4.997111011133389e-09</v>
+        <v>6.889438132592771e-09</v>
       </c>
       <c r="I95" t="n">
-        <v>1.020408683027748e-08</v>
+        <v>-1.54366648389213e-09</v>
       </c>
     </row>
     <row r="96">
@@ -4209,19 +4482,22 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>-1.739072353724538e-09</v>
+        <v>-2.529038527030753e-09</v>
       </c>
       <c r="E96" t="n">
-        <v>-3.393580437793865e-10</v>
+        <v>2.386936900606571e-09</v>
       </c>
       <c r="F96" t="n">
-        <v>5.915929908804919e-09</v>
+        <v>4.381473806586608e-08</v>
+      </c>
+      <c r="G96" t="n">
+        <v/>
       </c>
       <c r="H96" t="n">
-        <v>-1.408718975382868e-09</v>
+        <v>-1.960766693680716e-09</v>
       </c>
       <c r="I96" t="n">
-        <v>1.696912359271001e-08</v>
+        <v>-1.463180564800296e-09</v>
       </c>
     </row>
     <row r="97">
@@ -4241,19 +4517,22 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>2.965047647600905e-09</v>
+        <v>5.320194612735689e-09</v>
       </c>
       <c r="E97" t="n">
-        <v>-8.654569695511916e-10</v>
+        <v>4.115781021468726e-09</v>
       </c>
       <c r="F97" t="n">
-        <v>7.889208239418551e-09</v>
+        <v>5.409934881009621e-08</v>
+      </c>
+      <c r="G97" t="n">
+        <v/>
       </c>
       <c r="H97" t="n">
-        <v>1.099361940526745e-09</v>
+        <v>1.432697660630277e-09</v>
       </c>
       <c r="I97" t="n">
-        <v>9.320522462317027e-09</v>
+        <v>-1.926265247495201e-09</v>
       </c>
     </row>
     <row r="98">
@@ -4273,19 +4552,22 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1.675942288300573e-09</v>
+        <v>3.918678349545901e-09</v>
       </c>
       <c r="E98" t="n">
-        <v>5.360170912225845e-10</v>
+        <v>1.128414211950307e-08</v>
       </c>
       <c r="F98" t="n">
-        <v>2.378510468550068e-07</v>
+        <v>1.377456619989336e-05</v>
+      </c>
+      <c r="G98" t="n">
+        <v/>
       </c>
       <c r="H98" t="n">
-        <v>3.012231979898233e-09</v>
+        <v>4.019029590646689e-09</v>
       </c>
       <c r="I98" t="n">
-        <v>1.60784665881054e-08</v>
+        <v>-6.909325537360562e-10</v>
       </c>
     </row>
     <row r="99">
@@ -4305,19 +4587,22 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1.40578956259349e-09</v>
+        <v>1.873891926548022e-10</v>
       </c>
       <c r="E99" t="n">
-        <v>6.950354979613729e-10</v>
+        <v>-5.129212838954303e-10</v>
       </c>
       <c r="F99" t="n">
-        <v>6.243392326133228e-10</v>
+        <v>7.480076549161823e-11</v>
+      </c>
+      <c r="G99" t="n">
+        <v/>
       </c>
       <c r="H99" t="n">
-        <v>-9.24528666947582e-11</v>
+        <v>-1.27667437335904e-10</v>
       </c>
       <c r="I99" t="n">
-        <v>3.008159887506722e-10</v>
+        <v>-9.549582599189155e-10</v>
       </c>
     </row>
     <row r="100">
@@ -4337,19 +4622,22 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1.178667108587444e-09</v>
+        <v>1.409807999132426e-09</v>
       </c>
       <c r="E100" t="n">
-        <v>4.564542076997899e-10</v>
+        <v>4.939626621498417e-09</v>
       </c>
       <c r="F100" t="n">
-        <v>1.378886352674374e-08</v>
+        <v>6.312445915277064e-08</v>
+      </c>
+      <c r="G100" t="n">
+        <v/>
       </c>
       <c r="H100" t="n">
-        <v>3.888878742997599e-09</v>
+        <v>5.354648602623331e-09</v>
       </c>
       <c r="I100" t="n">
-        <v>1.550021846512404e-08</v>
+        <v>-1.70323238868451e-09</v>
       </c>
     </row>
     <row r="101">
@@ -4369,19 +4657,22 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>3.360386486548932e-11</v>
+        <v>-2.375168908821785e-09</v>
       </c>
       <c r="E101" t="n">
-        <v>5.131981194196852e-09</v>
+        <v>8.514140407399728e-10</v>
       </c>
       <c r="F101" t="n">
-        <v>1.535648678917341e-08</v>
+        <v>4.647381532392683e-08</v>
+      </c>
+      <c r="G101" t="n">
+        <v/>
       </c>
       <c r="H101" t="n">
-        <v>-1.788150519759455e-09</v>
+        <v>-2.470723037566912e-09</v>
       </c>
       <c r="I101" t="n">
-        <v>2.907229767745152e-05</v>
+        <v>-2.537405309961709e-09</v>
       </c>
     </row>
     <row r="102">
@@ -4401,19 +4692,22 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1.561790820108111e-09</v>
+        <v>4.47801917193882e-09</v>
       </c>
       <c r="E102" t="n">
-        <v>-7.076318268603754e-10</v>
+        <v>6.364008273301359e-09</v>
       </c>
       <c r="F102" t="n">
-        <v>4.580776546061758e-09</v>
+        <v>4.24661516543112e-08</v>
+      </c>
+      <c r="G102" t="n">
+        <v/>
       </c>
       <c r="H102" t="n">
-        <v>8.351906815971478e-10</v>
+        <v>1.074691742417854e-09</v>
       </c>
       <c r="I102" t="n">
-        <v>9.146033295668648e-09</v>
+        <v>-2.080753145869011e-09</v>
       </c>
     </row>
     <row r="103">
@@ -4433,19 +4727,22 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>8.470599677978567e-10</v>
+        <v>4.15076880524667e-09</v>
       </c>
       <c r="E103" t="n">
-        <v>2.771404461928864e-09</v>
+        <v>6.228031569108658e-08</v>
       </c>
       <c r="F103" t="n">
-        <v>7.466792905015994e-09</v>
+        <v>1.112863571062352e-07</v>
+      </c>
+      <c r="G103" t="n">
+        <v/>
       </c>
       <c r="H103" t="n">
-        <v>2.922433439308701e-09</v>
+        <v>3.8950411969137e-09</v>
       </c>
       <c r="I103" t="n">
-        <v>2.08835132583261e-08</v>
+        <v>-6.68185534970537e-10</v>
       </c>
     </row>
     <row r="104">
@@ -4465,19 +4762,22 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>-2.105304532493867e-10</v>
+        <v>3.315204444717707e-10</v>
       </c>
       <c r="E104" t="n">
-        <v>-3.952550119430753e-10</v>
+        <v>1.347058467252457e-10</v>
       </c>
       <c r="F104" t="n">
-        <v>-2.237038983218551e-10</v>
+        <v>-6.137739052331144e-11</v>
+      </c>
+      <c r="G104" t="n">
+        <v/>
       </c>
       <c r="H104" t="n">
-        <v>3.023806654128711e-11</v>
+        <v>4.318318567769453e-11</v>
       </c>
       <c r="I104" t="n">
-        <v>-1.88836635019248e-11</v>
+        <v>-6.502513410356457e-10</v>
       </c>
     </row>
     <row r="105">
@@ -4497,19 +4797,22 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>-2.430810607148817e-11</v>
+        <v>1.849617233781028e-09</v>
       </c>
       <c r="E105" t="n">
-        <v>-1.044592315039946e-10</v>
+        <v>8.507250704791194e-09</v>
       </c>
       <c r="F105" t="n">
-        <v>5.698139733474767e-09</v>
+        <v>4.873575545860146e-08</v>
+      </c>
+      <c r="G105" t="n">
+        <v/>
       </c>
       <c r="H105" t="n">
-        <v>4.792044958092099e-09</v>
+        <v>6.610773298968857e-09</v>
       </c>
       <c r="I105" t="n">
-        <v>1.14698404446156e-08</v>
+        <v>-1.405951910711573e-09</v>
       </c>
     </row>
     <row r="106">
@@ -4529,19 +4832,22 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>-1.226458268220603e-09</v>
+        <v>-2.232824886247034e-09</v>
       </c>
       <c r="E106" t="n">
-        <v>3.39299247108195e-10</v>
+        <v>2.649098053763585e-09</v>
       </c>
       <c r="F106" t="n">
-        <v>4.863661749545312e-09</v>
+        <v>4.856822215647089e-08</v>
+      </c>
+      <c r="G106" t="n">
+        <v/>
       </c>
       <c r="H106" t="n">
-        <v>-1.745696393024311e-09</v>
+        <v>-2.413791425135983e-09</v>
       </c>
       <c r="I106" t="n">
-        <v>2.375752735031637e-08</v>
+        <v>-2.383335661330935e-09</v>
       </c>
     </row>
     <row r="107">
@@ -4561,19 +4867,22 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>7.545943415713606e-09</v>
+        <v>9.718450175264301e-08</v>
       </c>
       <c r="E107" t="n">
-        <v>-3.633362289432562e-10</v>
+        <v>1.89516609537534e-08</v>
       </c>
       <c r="F107" t="n">
-        <v>9.121663878226488e-09</v>
+        <v>1.088182734631975e-07</v>
+      </c>
+      <c r="G107" t="n">
+        <v/>
       </c>
       <c r="H107" t="n">
-        <v>6.537316418455352e-09</v>
+        <v>8.935916504950029e-09</v>
       </c>
       <c r="I107" t="n">
-        <v>1.113418146113768e-08</v>
+        <v>5.116402806164358e-09</v>
       </c>
     </row>
     <row r="108">
@@ -4593,19 +4902,22 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>7.708505055169694e-09</v>
+        <v>5.163279439471101e-09</v>
       </c>
       <c r="E108" t="n">
-        <v>0.002222468394329896</v>
+        <v>0.1427161906423875</v>
       </c>
       <c r="F108" t="n">
-        <v>2.357074920507829e-07</v>
+        <v>1.354941568586203e-05</v>
+      </c>
+      <c r="G108" t="n">
+        <v/>
       </c>
       <c r="H108" t="n">
-        <v>3.044546090215378e-09</v>
+        <v>4.126780757091951e-09</v>
       </c>
       <c r="I108" t="n">
-        <v>2.903953240407281e-05</v>
+        <v>4.075533950757324e-10</v>
       </c>
     </row>
     <row r="109">
@@ -4625,19 +4937,22 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1.523718387517107e-09</v>
+        <v>5.441042482995439e-09</v>
       </c>
       <c r="E109" t="n">
-        <v>9.813315798262166e-10</v>
+        <v>4.173351283904709e-08</v>
       </c>
       <c r="F109" t="n">
-        <v>4.322024989547144e-05</v>
+        <v>0.0009239831649658084</v>
+      </c>
+      <c r="G109" t="n">
+        <v/>
       </c>
       <c r="H109" t="n">
-        <v>3.586997408741085e-09</v>
+        <v>4.872422980796698e-09</v>
       </c>
       <c r="I109" t="n">
-        <v>1.710468522829641e-08</v>
+        <v>9.044286785229355e-10</v>
       </c>
     </row>
     <row r="110">
@@ -4657,19 +4972,22 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>3.071356440215326e-09</v>
+        <v>8.620445038867386e-09</v>
       </c>
       <c r="E110" t="n">
-        <v>1.628678110765469e-09</v>
+        <v>2.247530306209932e-08</v>
       </c>
       <c r="F110" t="n">
-        <v>2.031906558437545e-08</v>
+        <v>1.283414884840549e-07</v>
+      </c>
+      <c r="G110" t="n">
+        <v/>
       </c>
       <c r="H110" t="n">
-        <v>3.180173096048777e-08</v>
+        <v>4.576054528083475e-08</v>
       </c>
       <c r="I110" t="n">
-        <v>1.973109584246585e-08</v>
+        <v>6.440327785723372e-09</v>
       </c>
     </row>
     <row r="111">
@@ -4689,19 +5007,22 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>2.189528979405756e-09</v>
+        <v>3.027167298854047e-10</v>
       </c>
       <c r="E111" t="n">
-        <v>6.671073995782596e-09</v>
+        <v>9.394761539141645e-09</v>
       </c>
       <c r="F111" t="n">
-        <v>3.306343298658786e-08</v>
+        <v>1.244089996598997e-07</v>
+      </c>
+      <c r="G111" t="n">
+        <v/>
       </c>
       <c r="H111" t="n">
-        <v>-5.970418565458947e-11</v>
+        <v>-1.076990490422684e-10</v>
       </c>
       <c r="I111" t="n">
-        <v>6.770566791063141e-05</v>
+        <v>0.1646363579105326</v>
       </c>
     </row>
     <row r="112">
@@ -4721,19 +5042,22 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>2.666718078622364e-09</v>
+        <v>5.806605525399817e-09</v>
       </c>
       <c r="E112" t="n">
-        <v>-4.523662553596703e-10</v>
+        <v>5.804342958023104e-09</v>
       </c>
       <c r="F112" t="n">
-        <v>7.050929347170713e-09</v>
+        <v>4.136154714011575e-08</v>
+      </c>
+      <c r="G112" t="n">
+        <v/>
       </c>
       <c r="H112" t="n">
-        <v>3.343934755970646e-10</v>
+        <v>5.415582190905876e-10</v>
       </c>
       <c r="I112" t="n">
-        <v>1.032863536992836e-08</v>
+        <v>-1.485973177328646e-09</v>
       </c>
     </row>
     <row r="113">
@@ -4753,19 +5077,22 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>5.688840999321982e-10</v>
+        <v>1.862922280801448e-09</v>
       </c>
       <c r="E113" t="n">
-        <v>2.863145758572269e-09</v>
+        <v>2.355265757789159e-08</v>
       </c>
       <c r="F113" t="n">
-        <v>1.150856745422271e-08</v>
+        <v>8.926307237374403e-08</v>
+      </c>
+      <c r="G113" t="n">
+        <v/>
       </c>
       <c r="H113" t="n">
-        <v>3.281587659276954e-10</v>
+        <v>5.331644266667461e-10</v>
       </c>
       <c r="I113" t="n">
-        <v>2.164573826191544e-08</v>
+        <v>-1.49153265263732e-09</v>
       </c>
     </row>
     <row r="114">
@@ -4785,19 +5112,22 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>2.765891943229445e-11</v>
+        <v>2.217612189331901e-09</v>
       </c>
       <c r="E114" t="n">
-        <v>-2.167382650436562e-11</v>
+        <v>1.304451568644584e-08</v>
       </c>
       <c r="F114" t="n">
-        <v>3.111982664150226e-08</v>
+        <v>1.578323331759992e-07</v>
+      </c>
+      <c r="G114" t="n">
+        <v/>
       </c>
       <c r="H114" t="n">
-        <v>6.140347234767302e-10</v>
+        <v>9.404171734610423e-10</v>
       </c>
       <c r="I114" t="n">
-        <v>1.207104825470741e-08</v>
+        <v>-1.172809867857551e-09</v>
       </c>
     </row>
     <row r="115">
@@ -4817,19 +5147,22 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>3.100603030915836e-11</v>
+        <v>1.374415488568261e-09</v>
       </c>
       <c r="E115" t="n">
-        <v>-4.983897538892492e-10</v>
+        <v>3.780186751296611e-10</v>
       </c>
       <c r="F115" t="n">
-        <v>-4.179000498650203e-10</v>
+        <v>-7.379482605494779e-11</v>
+      </c>
+      <c r="G115" t="n">
+        <v/>
       </c>
       <c r="H115" t="n">
-        <v>6.612223576641505e-11</v>
+        <v>5.820909674641964e-11</v>
       </c>
       <c r="I115" t="n">
-        <v>-4.397557614585652e-11</v>
+        <v>3.283124206443669e-09</v>
       </c>
     </row>
     <row r="116">
@@ -4849,19 +5182,22 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>-1.120297002601443e-09</v>
+        <v>-2.030516485664822e-09</v>
       </c>
       <c r="E116" t="n">
-        <v>1.188674524584498e-10</v>
+        <v>2.318960703035882e-09</v>
       </c>
       <c r="F116" t="n">
-        <v>6.814647580746447e-09</v>
+        <v>4.267003711472212e-08</v>
+      </c>
+      <c r="G116" t="n">
+        <v/>
       </c>
       <c r="H116" t="n">
-        <v>-1.767078705895318e-09</v>
+        <v>-2.404694035077416e-09</v>
       </c>
       <c r="I116" t="n">
-        <v>2.190139589412906e-08</v>
+        <v>-1.537497731686834e-09</v>
       </c>
     </row>
     <row r="117">
@@ -4881,19 +5217,22 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>4.234558393631489e-10</v>
+        <v>-1.064863159356301e-09</v>
       </c>
       <c r="E117" t="n">
-        <v>-1.321079732502538e-10</v>
+        <v>3.122537541249488e-09</v>
       </c>
       <c r="F117" t="n">
-        <v>8.564794458989469e-09</v>
+        <v>4.767582593247449e-08</v>
+      </c>
+      <c r="G117" t="n">
+        <v/>
       </c>
       <c r="H117" t="n">
-        <v>-1.370580197583076e-09</v>
+        <v>-1.907496683164269e-09</v>
       </c>
       <c r="I117" t="n">
-        <v>7.880786330546732e-09</v>
+        <v>-4.181474554199748e-09</v>
       </c>
     </row>
     <row r="118">
@@ -4913,19 +5252,22 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>-5.615340379612015e-10</v>
+        <v>-2.197709136346068e-09</v>
       </c>
       <c r="E118" t="n">
-        <v>9.144543821744157e-09</v>
+        <v>7.832422199557155e-09</v>
       </c>
       <c r="F118" t="n">
-        <v>1.469003005193174e-08</v>
+        <v>1.067254047559174e-07</v>
+      </c>
+      <c r="G118" t="n">
+        <v/>
       </c>
       <c r="H118" t="n">
-        <v>-1.691861134412653e-09</v>
+        <v>-2.340230925277868e-09</v>
       </c>
       <c r="I118" t="n">
-        <v>2.007439281677167e-08</v>
+        <v>-4.270910837357531e-09</v>
       </c>
     </row>
     <row r="119">
@@ -4945,19 +5287,22 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>-9.807071712845815e-10</v>
+        <v>-2.279053303283574e-09</v>
       </c>
       <c r="E119" t="n">
-        <v>9.571830883522909e-10</v>
+        <v>3.848204944498801e-09</v>
       </c>
       <c r="F119" t="n">
-        <v>3.248558560023788e-08</v>
+        <v>1.039014076323047e-07</v>
+      </c>
+      <c r="G119" t="n">
+        <v/>
       </c>
       <c r="H119" t="n">
-        <v>-1.635913274813687e-09</v>
+        <v>-2.264843852288855e-09</v>
       </c>
       <c r="I119" t="n">
-        <v>1.033633660875952e-08</v>
+        <v>-4.259247180838187e-09</v>
       </c>
     </row>
     <row r="120">
@@ -4977,19 +5322,22 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1.803676939665575e-10</v>
+        <v>-1.290653638370529e-09</v>
       </c>
       <c r="E120" t="n">
-        <v>1.533673918052423e-09</v>
+        <v>-2.508691769970244e-10</v>
       </c>
       <c r="F120" t="n">
-        <v>8.33758195934023e-10</v>
+        <v>1.638168360038084e-10</v>
+      </c>
+      <c r="G120" t="n">
+        <v/>
       </c>
       <c r="H120" t="n">
-        <v>-1.077666555528313e-09</v>
+        <v>-1.486119716057817e-09</v>
       </c>
       <c r="I120" t="n">
-        <v>1.342431247243275e-10</v>
+        <v>-3.867410840394706e-09</v>
       </c>
     </row>
     <row r="121">
@@ -5009,19 +5357,22 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>-9.242771042957763e-10</v>
+        <v>-2.032552840534961e-09</v>
       </c>
       <c r="E121" t="n">
-        <v>4.185709908720086e-10</v>
+        <v>3.048875728469714e-09</v>
       </c>
       <c r="F121" t="n">
-        <v>9.439990707783363e-09</v>
+        <v>4.746935716404455e-08</v>
+      </c>
+      <c r="G121" t="n">
+        <v/>
       </c>
       <c r="H121" t="n">
-        <v>-9.933276173787619e-10</v>
+        <v>-1.358983063714605e-09</v>
       </c>
       <c r="I121" t="n">
-        <v>8.997600622001844e-09</v>
+        <v>-4.192166227074119e-09</v>
       </c>
     </row>
     <row r="122">
@@ -5041,19 +5392,22 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>-8.268995313958706e-10</v>
+        <v>-1.455344022728378e-09</v>
       </c>
       <c r="E122" t="n">
-        <v>9.227192932016004e-10</v>
+        <v>5.631820195857999e-09</v>
       </c>
       <c r="F122" t="n">
-        <v>2.364097259019695e-11</v>
+        <v>1.772016983651563e-09</v>
       </c>
       <c r="G122" t="n">
-        <v>1.333171061882107e-09</v>
+        <v>1.742731117832767e-09</v>
+      </c>
+      <c r="H122" t="n">
+        <v/>
       </c>
       <c r="I122" t="n">
-        <v>3.630278336951148e-08</v>
+        <v>1.247842281375548e-08</v>
       </c>
     </row>
     <row r="123">
@@ -5073,19 +5427,22 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>-9.179917977228784e-10</v>
+        <v>-1.647622088017149e-09</v>
       </c>
       <c r="E123" t="n">
-        <v>-1.583758821849265e-10</v>
+        <v>1.32893120507574e-09</v>
       </c>
       <c r="F123" t="n">
-        <v>1.978403754113159e-09</v>
+        <v>4.184507621201882e-09</v>
       </c>
       <c r="G123" t="n">
-        <v>1.048850311346532e-09</v>
+        <v>1.358631711665265e-09</v>
+      </c>
+      <c r="H123" t="n">
+        <v/>
       </c>
       <c r="I123" t="n">
-        <v>3.237831792587595e-08</v>
+        <v>1.155480714324914e-08</v>
       </c>
     </row>
     <row r="124">
@@ -5105,19 +5462,22 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>-7.643655184475427e-10</v>
+        <v>-1.337034013363635e-09</v>
       </c>
       <c r="E124" t="n">
-        <v>6.201360532143354e-11</v>
+        <v>1.315964884175658e-09</v>
       </c>
       <c r="F124" t="n">
-        <v>-7.068084525694087e-11</v>
+        <v>1.436313069612246e-09</v>
       </c>
       <c r="G124" t="n">
-        <v>6.152273057377406e-09</v>
+        <v>8.49516350450629e-09</v>
+      </c>
+      <c r="H124" t="n">
+        <v/>
       </c>
       <c r="I124" t="n">
-        <v>4.092442854884695e-08</v>
+        <v>1.764102513869354e-08</v>
       </c>
     </row>
     <row r="125">
@@ -5137,19 +5497,22 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>-8.614879729174479e-10</v>
+        <v>-1.096817994175544e-09</v>
       </c>
       <c r="E125" t="n">
-        <v>1.951905891572407e-11</v>
+        <v>6.57746945551153e-10</v>
       </c>
       <c r="F125" t="n">
-        <v>5.396061044159364e-11</v>
+        <v>7.429173236504551e-10</v>
       </c>
       <c r="G125" t="n">
-        <v>6.391334884838302e-10</v>
+        <v>8.865286879746762e-10</v>
+      </c>
+      <c r="H125" t="n">
+        <v/>
       </c>
       <c r="I125" t="n">
-        <v>5.950729089213574e-11</v>
+        <v>5.188388487249271e-10</v>
       </c>
     </row>
     <row r="126">
@@ -5169,19 +5532,22 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>-1.671029187823651e-09</v>
+        <v>-2.999959928576881e-09</v>
       </c>
       <c r="E126" t="n">
-        <v>-1.08172863608488e-09</v>
+        <v>-1.924778168774927e-09</v>
       </c>
       <c r="F126" t="n">
-        <v>-1.315399522217981e-09</v>
+        <v>-1.932531934846038e-09</v>
       </c>
       <c r="G126" t="n">
-        <v>-1.224501123375946e-09</v>
+        <v>-1.714791935452241e-09</v>
+      </c>
+      <c r="H126" t="n">
+        <v/>
       </c>
       <c r="I126" t="n">
-        <v>7.571800750578807e-08</v>
+        <v>3.715923456152328e-08</v>
       </c>
     </row>
     <row r="127">
@@ -5201,19 +5567,22 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>5.261776267198442e-09</v>
+        <v>5.076279783950605e-09</v>
       </c>
       <c r="E127" t="n">
-        <v>-7.821490254111985e-10</v>
+        <v>-4.984840439777241e-10</v>
       </c>
       <c r="F127" t="n">
-        <v>-1.856767729358548e-10</v>
+        <v>9.910250971518049e-10</v>
       </c>
       <c r="G127" t="n">
-        <v>1.75040748094353e-09</v>
+        <v>2.315658545179192e-09</v>
+      </c>
+      <c r="H127" t="n">
+        <v/>
       </c>
       <c r="I127" t="n">
-        <v>3.292666736765175e-08</v>
+        <v>1.525449529088985e-08</v>
       </c>
     </row>
     <row r="128">
@@ -5233,19 +5602,22 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>2.392435483020057e-09</v>
+        <v>2.072226909952989e-09</v>
       </c>
       <c r="E128" t="n">
-        <v>3.976153775161024e-10</v>
+        <v>1.122110105961279e-09</v>
       </c>
       <c r="F128" t="n">
-        <v>8.129947208155647e-09</v>
+        <v>1.124002376049579e-08</v>
       </c>
       <c r="G128" t="n">
-        <v>3.216291387640645e-09</v>
+        <v>4.293011529925872e-09</v>
+      </c>
+      <c r="H128" t="n">
+        <v/>
       </c>
       <c r="I128" t="n">
-        <v>4.847769639849956e-08</v>
+        <v>2.037025082835692e-08</v>
       </c>
     </row>
     <row r="129">
@@ -5265,19 +5637,22 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1.543885530060091e-09</v>
+        <v>-6.167121367642002e-10</v>
       </c>
       <c r="E129" t="n">
-        <v>6.673418435277569e-10</v>
+        <v>-1.022875792455938e-09</v>
       </c>
       <c r="F129" t="n">
-        <v>1.068628595035202e-09</v>
+        <v>1.180909993519207e-10</v>
       </c>
       <c r="G129" t="n">
-        <v>2.955106427815321e-09</v>
+        <v>4.056000639191653e-09</v>
+      </c>
+      <c r="H129" t="n">
+        <v/>
       </c>
       <c r="I129" t="n">
-        <v>6.81483298701255e-08</v>
+        <v>1.345316730219646e-08</v>
       </c>
     </row>
     <row r="130">
@@ -5297,19 +5672,22 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>8.449886086977156e-10</v>
+        <v>1.024957016863462e-09</v>
       </c>
       <c r="E130" t="n">
-        <v>-9.368991747382512e-12</v>
+        <v>-6.779924291947858e-10</v>
       </c>
       <c r="F130" t="n">
-        <v>6.7824693865784e-10</v>
+        <v>6.881120229139615e-10</v>
       </c>
       <c r="G130" t="n">
-        <v>6.287670673140974e-10</v>
+        <v>8.735297079746314e-10</v>
+      </c>
+      <c r="H130" t="n">
+        <v/>
       </c>
       <c r="I130" t="n">
-        <v>1.215181163685892e-10</v>
+        <v>6.260991339354284e-10</v>
       </c>
     </row>
     <row r="131">
@@ -5329,19 +5707,22 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>-8.419263300687622e-10</v>
+        <v>-2.8559572649411e-09</v>
       </c>
       <c r="E131" t="n">
-        <v>-8.874002462014095e-10</v>
+        <v>-2.711820730369872e-09</v>
       </c>
       <c r="F131" t="n">
-        <v>-9.548968428823256e-10</v>
+        <v>-2.381262341924954e-09</v>
       </c>
       <c r="G131" t="n">
-        <v>-1.570318588407506e-09</v>
+        <v>-2.179455218327687e-09</v>
+      </c>
+      <c r="H131" t="n">
+        <v/>
       </c>
       <c r="I131" t="n">
-        <v>2.033365443209286e-07</v>
+        <v>2.169755852449848e-08</v>
       </c>
     </row>
     <row r="132">
@@ -5361,19 +5742,22 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>4.016482914486108e-09</v>
+        <v>4.251069815647419e-09</v>
       </c>
       <c r="E132" t="n">
-        <v>-4.131371957180218e-10</v>
+        <v>7.406743646222817e-10</v>
       </c>
       <c r="F132" t="n">
-        <v>-9.126138063924808e-10</v>
+        <v>-5.236368442034786e-10</v>
       </c>
       <c r="G132" t="n">
-        <v>1.488267601149883e-09</v>
+        <v>1.960804817629001e-09</v>
+      </c>
+      <c r="H132" t="n">
+        <v/>
       </c>
       <c r="I132" t="n">
-        <v>3.222039415808706e-08</v>
+        <v>1.431488818434651e-08</v>
       </c>
     </row>
     <row r="133">
@@ -5393,19 +5777,22 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>2.252021179602235e-09</v>
+        <v>2.490697964000077e-09</v>
       </c>
       <c r="E133" t="n">
-        <v>3.670214554774358e-09</v>
+        <v>1.399805692325011e-08</v>
       </c>
       <c r="F133" t="n">
-        <v>4.268778245452066e-10</v>
+        <v>1.451079620707007e-09</v>
       </c>
       <c r="G133" t="n">
-        <v>3.34085566001223e-09</v>
+        <v>4.46145336494794e-09</v>
+      </c>
+      <c r="H133" t="n">
+        <v/>
       </c>
       <c r="I133" t="n">
-        <v>5.711093991734839e-08</v>
+        <v>2.085869131603478e-08</v>
       </c>
     </row>
     <row r="134">
@@ -5425,19 +5812,22 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>7.615018256280844e-10</v>
+        <v>-3.982868379571935e-10</v>
       </c>
       <c r="E134" t="n">
-        <v>6.365155708927153e-10</v>
+        <v>3.056832289198463e-10</v>
       </c>
       <c r="F134" t="n">
-        <v>-4.736778834466698e-10</v>
+        <v>-7.869509121785706e-10</v>
       </c>
       <c r="G134" t="n">
-        <v>3.474492940731909e-09</v>
+        <v>4.776494095842812e-09</v>
+      </c>
+      <c r="H134" t="n">
+        <v/>
       </c>
       <c r="I134" t="n">
-        <v>5.162190581847096e-08</v>
+        <v>1.450482917718643e-08</v>
       </c>
     </row>
     <row r="135">
@@ -5457,19 +5847,22 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>4.741062099995739e-10</v>
+        <v>1.711000141714675e-09</v>
       </c>
       <c r="E135" t="n">
-        <v>1.665095002502813e-10</v>
+        <v>1.047427219791475e-09</v>
       </c>
       <c r="F135" t="n">
-        <v>-3.967379444078212e-10</v>
+        <v>-3.200887172569846e-10</v>
       </c>
       <c r="G135" t="n">
-        <v>9.43711915603646e-10</v>
+        <v>1.319185715658186e-09</v>
+      </c>
+      <c r="H135" t="n">
+        <v/>
       </c>
       <c r="I135" t="n">
-        <v>8.809994576948275e-11</v>
+        <v>8.159266634592474e-10</v>
       </c>
     </row>
     <row r="136">
@@ -5489,19 +5882,22 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>-1.233814934565804e-09</v>
+        <v>-2.752461024733442e-09</v>
       </c>
       <c r="E136" t="n">
-        <v>-1.155644168817951e-09</v>
+        <v>-2.221088758476061e-09</v>
       </c>
       <c r="F136" t="n">
-        <v>-1.696751698267802e-09</v>
+        <v>-2.598824597259993e-09</v>
       </c>
       <c r="G136" t="n">
-        <v>-1.509087058276944e-09</v>
+        <v>-2.096710838180109e-09</v>
+      </c>
+      <c r="H136" t="n">
+        <v/>
       </c>
       <c r="I136" t="n">
-        <v>7.67134446768697e-08</v>
+        <v>2.494837912972528e-08</v>
       </c>
     </row>
     <row r="137">
@@ -5521,19 +5917,22 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>5.57068705305956e-09</v>
+        <v>5.326127597837684e-09</v>
       </c>
       <c r="E137" t="n">
-        <v>-1.003323868417836e-10</v>
+        <v>1.737707126797457e-09</v>
       </c>
       <c r="F137" t="n">
-        <v>4.258730426186267e-11</v>
+        <v>1.673500809258403e-09</v>
       </c>
       <c r="G137" t="n">
-        <v>-1.187444217162589e-11</v>
+        <v>4.925838395010888e-11</v>
+      </c>
+      <c r="H137" t="n">
+        <v/>
       </c>
       <c r="I137" t="n">
-        <v>3.044775727236785e-08</v>
+        <v>1.239915931453239e-08</v>
       </c>
     </row>
     <row r="138">
@@ -5553,19 +5952,22 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1.749922527469445e-09</v>
+        <v>-7.096233761559455e-10</v>
       </c>
       <c r="E138" t="n">
-        <v>6.112888784597245e-09</v>
+        <v>3.853778748298355e-09</v>
       </c>
       <c r="F138" t="n">
-        <v>2.134548710923413e-09</v>
+        <v>8.570646513941095e-10</v>
       </c>
       <c r="G138" t="n">
-        <v>-7.362036315634037e-10</v>
+        <v>-9.728051603851206e-10</v>
+      </c>
+      <c r="H138" t="n">
+        <v/>
       </c>
       <c r="I138" t="n">
-        <v>5.577245163447149e-08</v>
+        <v>8.227415607832414e-09</v>
       </c>
     </row>
     <row r="139">
@@ -5585,19 +5987,22 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>5.235050360242908e-10</v>
+        <v>-6.497889829366556e-10</v>
       </c>
       <c r="E139" t="n">
-        <v>3.142995087427095e-10</v>
+        <v>1.163710235466328e-09</v>
       </c>
       <c r="F139" t="n">
-        <v>3.156626536923459e-09</v>
+        <v>3.546939516172125e-09</v>
       </c>
       <c r="G139" t="n">
-        <v>-6.586451922983769e-10</v>
+        <v>-8.634217929087307e-10</v>
+      </c>
+      <c r="H139" t="n">
+        <v/>
       </c>
       <c r="I139" t="n">
-        <v>3.271750857340953e-08</v>
+        <v>8.636893377350368e-09</v>
       </c>
     </row>
     <row r="140">
@@ -5617,19 +6022,22 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>8.237891918626346e-10</v>
+        <v>9.345244389094555e-10</v>
       </c>
       <c r="E140" t="n">
-        <v>8.596526290428151e-10</v>
+        <v>1.112549616068346e-09</v>
       </c>
       <c r="F140" t="n">
-        <v>9.191494826792911e-10</v>
+        <v>1.054972330674204e-09</v>
       </c>
       <c r="G140" t="n">
-        <v>-5.560051917621366e-10</v>
+        <v>-8.014688162181161e-10</v>
+      </c>
+      <c r="H140" t="n">
+        <v/>
       </c>
       <c r="I140" t="n">
-        <v>8.622513854428096e-11</v>
+        <v>2.488189025776145e-10</v>
       </c>
     </row>
     <row r="141">
@@ -5649,19 +6057,22 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1.036576602914012e-11</v>
+        <v>-2.021380160307685e-09</v>
       </c>
       <c r="E141" t="n">
-        <v>4.15043247506043e-10</v>
+        <v>-1.185153322001479e-09</v>
       </c>
       <c r="F141" t="n">
-        <v>-9.291191460913792e-11</v>
+        <v>-1.238419481173668e-09</v>
       </c>
       <c r="G141" t="n">
-        <v>-1.398275867742654e-09</v>
+        <v>-1.896686794969576e-09</v>
+      </c>
+      <c r="H141" t="n">
+        <v/>
       </c>
       <c r="I141" t="n">
-        <v>3.610349212156076e-07</v>
+        <v>6.942279406286224e-08</v>
       </c>
     </row>
     <row r="142">
@@ -5681,19 +6092,22 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>-3.618383481741948e-09</v>
+        <v>2.738284934719351e-06</v>
       </c>
       <c r="E142" t="n">
-        <v>2.185660744633623e-09</v>
+        <v>6.929366579648039e-09</v>
       </c>
       <c r="F142" t="n">
-        <v>3.04046742382385e-09</v>
+        <v>5.995968007522377e-09</v>
       </c>
       <c r="G142" t="n">
-        <v>6.052115341022969e-09</v>
+        <v>8.294613608102659e-09</v>
+      </c>
+      <c r="H142" t="n">
+        <v/>
       </c>
       <c r="I142" t="n">
-        <v>7.767905322647662e-08</v>
+        <v>3.747399107779688e-08</v>
       </c>
     </row>
     <row r="143">
@@ -5713,19 +6127,22 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>7.149462664241571e-09</v>
+        <v>7.274248987642358e-09</v>
       </c>
       <c r="E143" t="n">
-        <v>1.626066083988224e-08</v>
+        <v>8.732399842451955e-08</v>
       </c>
       <c r="F143" t="n">
-        <v>7.219694421629098e-09</v>
+        <v>8.762016944948419e-09</v>
       </c>
       <c r="G143" t="n">
-        <v>4.758598442297451e-09</v>
+        <v>6.500797425346892e-09</v>
+      </c>
+      <c r="H143" t="n">
+        <v/>
       </c>
       <c r="I143" t="n">
-        <v>1.898780644011557e-07</v>
+        <v>3.04172084640501e-08</v>
       </c>
     </row>
     <row r="144">
@@ -5745,19 +6162,22 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>5.555490169691943e-09</v>
+        <v>8.445403538517495e-09</v>
       </c>
       <c r="E144" t="n">
-        <v>3.405167923815514e-09</v>
+        <v>1.243377028525282e-08</v>
       </c>
       <c r="F144" t="n">
-        <v>-1.828132392594966e-09</v>
+        <v>4.303237885912553e-08</v>
       </c>
       <c r="G144" t="n">
-        <v>5.805787701634289e-09</v>
+        <v>7.94977171881402e-09</v>
+      </c>
+      <c r="H144" t="n">
+        <v/>
       </c>
       <c r="I144" t="n">
-        <v>9.205797555229611e-08</v>
+        <v>3.542172242734508e-08</v>
       </c>
     </row>
     <row r="145">
@@ -5777,19 +6197,22 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>7.251545577496618e-09</v>
+        <v>7.321292460020358e-09</v>
       </c>
       <c r="E145" t="n">
-        <v>5.644346186594078e-09</v>
+        <v>7.351491726310172e-09</v>
       </c>
       <c r="F145" t="n">
-        <v>5.786738975415422e-09</v>
+        <v>6.424964841892185e-09</v>
       </c>
       <c r="G145" t="n">
-        <v>3.246493700957238e-08</v>
+        <v>4.711773864345821e-08</v>
+      </c>
+      <c r="H145" t="n">
+        <v/>
       </c>
       <c r="I145" t="n">
-        <v>3.010541244613815e-07</v>
+        <v>5.272734699892715e-08</v>
       </c>
     </row>
     <row r="146">
@@ -5809,19 +6232,22 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>2.1125955176311e-11</v>
+        <v>-1.668530421838129e-09</v>
       </c>
       <c r="E146" t="n">
-        <v>4.725344640260665e-11</v>
+        <v>-9.987907768552429e-10</v>
       </c>
       <c r="F146" t="n">
-        <v>-2.197474110469114e-10</v>
+        <v>-1.163116261182929e-09</v>
       </c>
       <c r="G146" t="n">
-        <v>-7.531612446963084e-10</v>
+        <v>-1.04531565801628e-09</v>
+      </c>
+      <c r="H146" t="n">
+        <v/>
       </c>
       <c r="I146" t="n">
-        <v>8.928473534192099e-07</v>
+        <v>0.2312284873984679</v>
       </c>
     </row>
     <row r="147">
@@ -5841,19 +6267,22 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>8.69043615036054e-11</v>
+        <v>-1.817840930079067e-09</v>
       </c>
       <c r="E147" t="n">
-        <v>-1.125894697452967e-09</v>
+        <v>-1.899578965227379e-09</v>
       </c>
       <c r="F147" t="n">
-        <v>-1.314839179135873e-09</v>
+        <v>-1.933634006381282e-09</v>
       </c>
       <c r="G147" t="n">
-        <v>-1.329989185230788e-09</v>
+        <v>-1.852072268334337e-09</v>
+      </c>
+      <c r="H147" t="n">
+        <v/>
       </c>
       <c r="I147" t="n">
-        <v>1.210917261632822e-08</v>
+        <v>-9.020536137163251e-11</v>
       </c>
     </row>
     <row r="148">
@@ -5873,19 +6302,22 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>-1.123347281042312e-09</v>
+        <v>-2.899185243794787e-09</v>
       </c>
       <c r="E148" t="n">
-        <v>-3.735560037205568e-11</v>
+        <v>-1.556881336993756e-09</v>
       </c>
       <c r="F148" t="n">
-        <v>-1.068512803587216e-09</v>
+        <v>-2.186188662520972e-09</v>
       </c>
       <c r="G148" t="n">
-        <v>-1.716167757322352e-09</v>
+        <v>-2.373431543798665e-09</v>
+      </c>
+      <c r="H148" t="n">
+        <v/>
       </c>
       <c r="I148" t="n">
-        <v>1.394651675109408e-08</v>
+        <v>-5.801671220640834e-10</v>
       </c>
     </row>
     <row r="149">
@@ -5905,19 +6337,22 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>-1.28314169585414e-09</v>
+        <v>-2.918199318797059e-09</v>
       </c>
       <c r="E149" t="n">
-        <v>-1.054248666392787e-09</v>
+        <v>-2.177768853658337e-09</v>
       </c>
       <c r="F149" t="n">
-        <v>-4.9072761537593e-10</v>
+        <v>-1.730058626277137e-09</v>
       </c>
       <c r="G149" t="n">
-        <v>-1.674043149102335e-09</v>
+        <v>-2.316766011598648e-09</v>
+      </c>
+      <c r="H149" t="n">
+        <v/>
       </c>
       <c r="I149" t="n">
-        <v>1.212328606646094e-08</v>
+        <v>-5.40959305319524e-10</v>
       </c>
     </row>
     <row r="150">
@@ -5937,19 +6372,22 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>-1.14297840287665e-10</v>
+        <v>-2.089399954554731e-09</v>
       </c>
       <c r="E150" t="n">
-        <v>5.913345767761111e-10</v>
+        <v>-1.267671642305711e-09</v>
       </c>
       <c r="F150" t="n">
-        <v>-1.510087216631113e-10</v>
+        <v>-1.298360172346126e-09</v>
       </c>
       <c r="G150" t="n">
-        <v>-7.952331229597591e-11</v>
+        <v>-1.129961934565409e-10</v>
+      </c>
+      <c r="H150" t="n">
+        <v/>
       </c>
       <c r="I150" t="n">
-        <v>1.83100751355586e-08</v>
+        <v>6.087126481066881e-10</v>
       </c>
     </row>
     <row r="151">
@@ -5969,19 +6407,22 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>-1.281396275603332e-09</v>
+        <v>-2.573663353445867e-09</v>
       </c>
       <c r="E151" t="n">
-        <v>-1.036311969571665e-09</v>
+        <v>-2.139730958316385e-09</v>
       </c>
       <c r="F151" t="n">
-        <v>-1.254619069282837e-09</v>
+        <v>-2.165913148670359e-09</v>
       </c>
       <c r="G151" t="n">
-        <v>-1.655620478547805e-09</v>
+        <v>-2.277694427757469e-09</v>
+      </c>
+      <c r="H151" t="n">
+        <v/>
       </c>
       <c r="I151" t="n">
-        <v>-3.553518278871307e-10</v>
+        <v>-2.272563459538408e-09</v>
       </c>
     </row>
     <row r="152">
@@ -6001,19 +6442,22 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>-2.481159538878501e-09</v>
+        <v>-2.032403299142022e-09</v>
       </c>
       <c r="E152" t="n">
-        <v>-2.962624268159566e-09</v>
+        <v>1.767612463424781e-08</v>
       </c>
       <c r="F152" t="n">
-        <v>3.12552314199634e-08</v>
+        <v>3.336673502202328e-08</v>
       </c>
       <c r="G152" t="n">
-        <v>7.252766062987849e-09</v>
+        <v>1.502704496615528e-08</v>
       </c>
       <c r="H152" t="n">
-        <v>3.467908892920796e-08</v>
+        <v>1.903086493160659e-08</v>
+      </c>
+      <c r="I152" t="n">
+        <v/>
       </c>
     </row>
     <row r="153">
@@ -6033,19 +6477,22 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>-2.50707838857256e-09</v>
+        <v>-2.129842580682795e-09</v>
       </c>
       <c r="E153" t="n">
-        <v>-3.408606218686019e-09</v>
+        <v>5.333806610294974e-09</v>
       </c>
       <c r="F153" t="n">
-        <v>6.649714697691667e-08</v>
+        <v>7.410262478772521e-08</v>
       </c>
       <c r="G153" t="n">
-        <v>6.430878072411059e-09</v>
+        <v>1.425393254482902e-08</v>
       </c>
       <c r="H153" t="n">
-        <v>3.283104497797012e-08</v>
+        <v>1.809329086825625e-08</v>
+      </c>
+      <c r="I153" t="n">
+        <v/>
       </c>
     </row>
     <row r="154">
@@ -6065,19 +6512,22 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>-2.515966580913763e-09</v>
+        <v>-2.252424716349819e-09</v>
       </c>
       <c r="E154" t="n">
-        <v>-3.470117829413024e-09</v>
+        <v>2.899381400347561e-09</v>
       </c>
       <c r="F154" t="n">
-        <v>2.737671804491979e-08</v>
+        <v>2.255234845307749e-08</v>
       </c>
       <c r="G154" t="n">
-        <v>2.103263688674112e-08</v>
+        <v>3.043637379810863e-08</v>
       </c>
       <c r="H154" t="n">
-        <v>3.154909962289431e-08</v>
+        <v>1.639337795721073e-08</v>
+      </c>
+      <c r="I154" t="n">
+        <v/>
       </c>
     </row>
     <row r="155">
@@ -6097,19 +6547,22 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>-2.431691361793436e-09</v>
+        <v>-2.232627656428985e-09</v>
       </c>
       <c r="E155" t="n">
-        <v>-3.383934143129547e-09</v>
+        <v>4.291747753510944e-09</v>
       </c>
       <c r="F155" t="n">
-        <v>3.135415147816687e-08</v>
+        <v>3.014872226077786e-08</v>
       </c>
       <c r="G155" t="n">
-        <v>7.567302549030929e-09</v>
+        <v>1.518291815508653e-08</v>
       </c>
       <c r="H155" t="n">
-        <v>8.675689939912904e-08</v>
+        <v>5.179118816277243e-08</v>
+      </c>
+      <c r="I155" t="n">
+        <v/>
       </c>
     </row>
     <row r="156">
@@ -6129,19 +6582,22 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>-2.300111541662124e-09</v>
+        <v>-1.736432517391601e-09</v>
       </c>
       <c r="E156" t="n">
-        <v>-2.633938948871904e-09</v>
+        <v>5.434663371294545e-11</v>
       </c>
       <c r="F156" t="n">
-        <v>-8.768200532747032e-11</v>
+        <v>3.550788696197008e-10</v>
       </c>
       <c r="G156" t="n">
-        <v>-9.439717346353941e-11</v>
+        <v>2.080946813497527e-10</v>
       </c>
       <c r="H156" t="n">
-        <v>-4.075227424730488e-11</v>
+        <v>3.541021140091031e-10</v>
+      </c>
+      <c r="I156" t="n">
+        <v/>
       </c>
     </row>
     <row r="157">
@@ -6161,19 +6617,22 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>-1.014882009118605e-09</v>
+        <v>1.158121509762415e-09</v>
       </c>
       <c r="E157" t="n">
-        <v>-3.569920683452351e-09</v>
+        <v>5.447087535615825e-10</v>
       </c>
       <c r="F157" t="n">
-        <v>2.799323348840179e-08</v>
+        <v>2.051376305618043e-08</v>
       </c>
       <c r="G157" t="n">
-        <v>5.695452064038471e-09</v>
+        <v>1.505615216864946e-08</v>
       </c>
       <c r="H157" t="n">
-        <v>3.333806449352818e-08</v>
+        <v>1.64184529312397e-08</v>
+      </c>
+      <c r="I157" t="n">
+        <v/>
       </c>
     </row>
     <row r="158">
@@ -6193,19 +6652,22 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>-1.207878814823014e-09</v>
+        <v>1.280971807305458e-09</v>
       </c>
       <c r="E158" t="n">
-        <v>-3.493717055096679e-09</v>
+        <v>3.209967312540542e-09</v>
       </c>
       <c r="F158" t="n">
-        <v>2.537830195375788e-07</v>
+        <v>1.192369118656629e-07</v>
       </c>
       <c r="G158" t="n">
-        <v>1.09274603392309e-08</v>
+        <v>2.544674857692036e-08</v>
       </c>
       <c r="H158" t="n">
-        <v>5.174390254822049e-08</v>
+        <v>2.668272744384879e-08</v>
+      </c>
+      <c r="I158" t="n">
+        <v/>
       </c>
     </row>
     <row r="159">
@@ -6225,19 +6687,22 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>6.257130835941594e-10</v>
+        <v>-1.665677374181226e-09</v>
       </c>
       <c r="E159" t="n">
-        <v>-3.613280864521013e-09</v>
+        <v>-3.100360284076275e-10</v>
       </c>
       <c r="F159" t="n">
-        <v>5.419977896756741e-08</v>
+        <v>1.501147594186441e-08</v>
       </c>
       <c r="G159" t="n">
-        <v>3.080159119181253e-05</v>
+        <v>2.346717804859302e-08</v>
       </c>
       <c r="H159" t="n">
-        <v>4.819808467222793e-08</v>
+        <v>1.149374681663834e-08</v>
+      </c>
+      <c r="I159" t="n">
+        <v/>
       </c>
     </row>
     <row r="160">
@@ -6257,19 +6722,22 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>-1.282394981554704e-09</v>
+        <v>-8.634323357184824e-10</v>
       </c>
       <c r="E160" t="n">
-        <v>-3.554415142222369e-09</v>
+        <v>9.91416518130039e-10</v>
       </c>
       <c r="F160" t="n">
-        <v>4.237920037227557e-08</v>
+        <v>2.421704419544731e-08</v>
       </c>
       <c r="G160" t="n">
-        <v>1.012642860302548e-08</v>
+        <v>1.70940022868162e-08</v>
       </c>
       <c r="H160" t="n">
-        <v>1.607034601175323e-07</v>
+        <v>4.379151616097291e-08</v>
+      </c>
+      <c r="I160" t="n">
+        <v/>
       </c>
     </row>
     <row r="161">
@@ -6289,19 +6757,22 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>3.167144770782603e-09</v>
+        <v>-1.201127907546831e-09</v>
       </c>
       <c r="E161" t="n">
-        <v>-3.513504772974732e-09</v>
+        <v>-1.744049870248517e-09</v>
       </c>
       <c r="F161" t="n">
-        <v>1.134164882054514e-10</v>
+        <v>-1.866944629577314e-10</v>
       </c>
       <c r="G161" t="n">
-        <v>4.341033542193107e-10</v>
+        <v>-1.842491205785316e-10</v>
       </c>
       <c r="H161" t="n">
-        <v>7.302924204645618e-11</v>
+        <v>-2.156724945170604e-10</v>
+      </c>
+      <c r="I161" t="n">
+        <v/>
       </c>
     </row>
     <row r="162">
@@ -6321,19 +6792,22 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>-1.456559105732176e-09</v>
+        <v>4.829392746757358e-10</v>
       </c>
       <c r="E162" t="n">
-        <v>-3.487880181068496e-09</v>
+        <v>2.32941775012522e-09</v>
       </c>
       <c r="F162" t="n">
-        <v>1.897579550069259e-08</v>
+        <v>1.292046833603061e-08</v>
       </c>
       <c r="G162" t="n">
-        <v>5.249180554418212e-09</v>
+        <v>1.412898427904756e-08</v>
       </c>
       <c r="H162" t="n">
-        <v>3.083615660507123e-08</v>
+        <v>1.516819705206819e-08</v>
+      </c>
+      <c r="I162" t="n">
+        <v/>
       </c>
     </row>
     <row r="163">
@@ -6353,19 +6827,22 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>-1.422055672919e-09</v>
+        <v>1.022214971781588e-09</v>
       </c>
       <c r="E163" t="n">
-        <v>-2.539912862946367e-09</v>
+        <v>3.253087090757025e-08</v>
       </c>
       <c r="F163" t="n">
-        <v>3.058383922026089e-08</v>
+        <v>2.129553029420654e-08</v>
       </c>
       <c r="G163" t="n">
-        <v>1.197157160488542e-08</v>
+        <v>2.496481814447618e-08</v>
       </c>
       <c r="H163" t="n">
-        <v>5.143297834852907e-08</v>
+        <v>2.550120177439684e-08</v>
+      </c>
+      <c r="I163" t="n">
+        <v/>
       </c>
     </row>
     <row r="164">
@@ -6385,19 +6862,22 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>-1.56751442121355e-09</v>
+        <v>-1.7034221257792e-09</v>
       </c>
       <c r="E164" t="n">
-        <v>-3.546384182784702e-09</v>
+        <v>1.287900391649948e-09</v>
       </c>
       <c r="F164" t="n">
-        <v>2.442786965916346e-08</v>
+        <v>1.073280011035347e-08</v>
       </c>
       <c r="G164" t="n">
-        <v>3.827350566280319e-08</v>
+        <v>2.493311680919391e-08</v>
       </c>
       <c r="H164" t="n">
-        <v>3.653648608276784e-08</v>
+        <v>1.191127911396604e-08</v>
+      </c>
+      <c r="I164" t="n">
+        <v/>
       </c>
     </row>
     <row r="165">
@@ -6417,19 +6897,22 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>-2.024101466587256e-09</v>
+        <v>-7.585125873031171e-10</v>
       </c>
       <c r="E165" t="n">
-        <v>-3.419080153520211e-09</v>
+        <v>4.005171535193175e-09</v>
       </c>
       <c r="F165" t="n">
-        <v>2.295290540555052e-08</v>
+        <v>1.629679217717537e-08</v>
       </c>
       <c r="G165" t="n">
-        <v>7.793138449047564e-09</v>
+        <v>1.86218504805099e-08</v>
       </c>
       <c r="H165" t="n">
-        <v>9.795335202333163e-08</v>
+        <v>5.077507844581744e-08</v>
+      </c>
+      <c r="I165" t="n">
+        <v/>
       </c>
     </row>
     <row r="166">
@@ -6449,19 +6932,22 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>-1.705971200534413e-09</v>
+        <v>-7.734806929931303e-10</v>
       </c>
       <c r="E166" t="n">
-        <v>-3.341588172125075e-09</v>
+        <v>-8.229469663148191e-10</v>
       </c>
       <c r="F166" t="n">
-        <v>-1.551965487925354e-10</v>
+        <v>-5.208327727356517e-10</v>
       </c>
       <c r="G166" t="n">
-        <v>-1.210837196908474e-10</v>
+        <v>-3.493209619044678e-11</v>
       </c>
       <c r="H166" t="n">
-        <v>-5.294469751144817e-11</v>
+        <v>-1.409643173280763e-10</v>
+      </c>
+      <c r="I166" t="n">
+        <v/>
       </c>
     </row>
     <row r="167">
@@ -6481,19 +6967,22 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>-8.925031067656137e-10</v>
+        <v>1.81335598477625e-09</v>
       </c>
       <c r="E167" t="n">
-        <v>-3.341365836104152e-09</v>
+        <v>6.393164288836821e-09</v>
       </c>
       <c r="F167" t="n">
-        <v>3.214644792725262e-08</v>
+        <v>3.32680827244836e-08</v>
       </c>
       <c r="G167" t="n">
-        <v>2.516955159366989e-09</v>
+        <v>1.002803707212494e-08</v>
       </c>
       <c r="H167" t="n">
-        <v>3.788532135587202e-08</v>
+        <v>2.167364304052293e-08</v>
+      </c>
+      <c r="I167" t="n">
+        <v/>
       </c>
     </row>
     <row r="168">
@@ -6513,19 +7002,22 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>3.645248717704374e-09</v>
+        <v>-1.085806881599645e-09</v>
       </c>
       <c r="E168" t="n">
-        <v>-2.995887231854431e-09</v>
+        <v>2.172282507867616e-08</v>
       </c>
       <c r="F168" t="n">
-        <v>1.284433452129932e-07</v>
+        <v>3.237679541900981e-08</v>
       </c>
       <c r="G168" t="n">
-        <v>6.464632946450576e-09</v>
+        <v>8.476325324017535e-09</v>
       </c>
       <c r="H168" t="n">
-        <v>7.69791506517676e-08</v>
+        <v>1.657930531385096e-08</v>
+      </c>
+      <c r="I168" t="n">
+        <v/>
       </c>
     </row>
     <row r="169">
@@ -6545,19 +7037,22 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>-1.570264155363076e-09</v>
+        <v>-8.806026309810213e-10</v>
       </c>
       <c r="E169" t="n">
-        <v>-3.390581776212882e-09</v>
+        <v>7.51248898542122e-09</v>
       </c>
       <c r="F169" t="n">
-        <v>1.752094528878007e-07</v>
+        <v>9.379791804541147e-08</v>
       </c>
       <c r="G169" t="n">
-        <v>3.281388896216109e-09</v>
+        <v>8.960005714751333e-09</v>
       </c>
       <c r="H169" t="n">
-        <v>4.267624318347418e-08</v>
+        <v>1.796151767129085e-08</v>
+      </c>
+      <c r="I169" t="n">
+        <v/>
       </c>
     </row>
     <row r="170">
@@ -6577,19 +7072,22 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>-1.187475685660546e-09</v>
+        <v>-6.438758984504269e-10</v>
       </c>
       <c r="E170" t="n">
-        <v>-3.30361859800118e-09</v>
+        <v>7.587285570543237e-09</v>
       </c>
       <c r="F170" t="n">
-        <v>5.063951302004028e-08</v>
+        <v>3.947648366365977e-08</v>
       </c>
       <c r="G170" t="n">
-        <v>4.153536915604995e-09</v>
+        <v>1.061314399444003e-08</v>
       </c>
       <c r="H170" t="n">
-        <v>2.695850346243405e-07</v>
+        <v>7.156573085229242e-08</v>
+      </c>
+      <c r="I170" t="n">
+        <v/>
       </c>
     </row>
     <row r="171">
@@ -6609,19 +7107,22 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>2.611720202056652e-09</v>
+        <v>4.373026584376374e-09</v>
       </c>
       <c r="E171" t="n">
-        <v>1.229590357840159e-08</v>
+        <v>3.284757044495856e-09</v>
       </c>
       <c r="F171" t="n">
-        <v>1.918649850944799e-10</v>
+        <v>1.057425966193469e-09</v>
       </c>
       <c r="G171" t="n">
-        <v>-1.346023837869933e-10</v>
+        <v>1.978286374220296e-10</v>
       </c>
       <c r="H171" t="n">
-        <v>1.905719160793399e-10</v>
+        <v>1.222008236085705e-09</v>
+      </c>
+      <c r="I171" t="n">
+        <v/>
       </c>
     </row>
     <row r="172">
@@ -6641,19 +7142,22 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>-1.143043762765105e-09</v>
+        <v>4.533906778286426e-10</v>
       </c>
       <c r="E172" t="n">
-        <v>-3.388350392088864e-09</v>
+        <v>3.65885592371942e-09</v>
       </c>
       <c r="F172" t="n">
-        <v>2.926874196439711e-08</v>
+        <v>2.495271725801673e-08</v>
       </c>
       <c r="G172" t="n">
-        <v>6.021377757770517e-09</v>
+        <v>1.474382674239393e-08</v>
       </c>
       <c r="H172" t="n">
-        <v>2.05304681430868e-08</v>
+        <v>1.112127776194064e-08</v>
+      </c>
+      <c r="I172" t="n">
+        <v/>
       </c>
     </row>
     <row r="173">
@@ -6673,19 +7177,22 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>-1.469430926909945e-09</v>
+        <v>-8.003015616336624e-10</v>
       </c>
       <c r="E173" t="n">
-        <v>-2.756306433983834e-09</v>
+        <v>2.040981757519638e-08</v>
       </c>
       <c r="F173" t="n">
-        <v>4.62753719927049e-08</v>
+        <v>3.329816775810746e-08</v>
       </c>
       <c r="G173" t="n">
-        <v>1.065266717062449e-08</v>
+        <v>1.645434275178426e-08</v>
       </c>
       <c r="H173" t="n">
-        <v>2.504068012107249e-08</v>
+        <v>1.168965025615409e-08</v>
+      </c>
+      <c r="I173" t="n">
+        <v/>
       </c>
     </row>
     <row r="174">
@@ -6705,19 +7212,22 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>-2.022224155000355e-09</v>
+        <v>-5.416894134723947e-10</v>
       </c>
       <c r="E174" t="n">
-        <v>-3.303652941833328e-09</v>
+        <v>7.572330954892676e-09</v>
       </c>
       <c r="F174" t="n">
-        <v>9.40611315845711e-08</v>
+        <v>1.083362169424156e-07</v>
       </c>
       <c r="G174" t="n">
-        <v>7.51802158214709e-09</v>
+        <v>1.821023765391217e-08</v>
       </c>
       <c r="H174" t="n">
-        <v>2.223938814586807e-08</v>
+        <v>1.28317595841167e-08</v>
+      </c>
+      <c r="I174" t="n">
+        <v/>
       </c>
     </row>
     <row r="175">
@@ -6737,19 +7247,22 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>-1.61274542047586e-09</v>
+        <v>-1.373864635337235e-09</v>
       </c>
       <c r="E175" t="n">
-        <v>-3.453703384039661e-09</v>
+        <v>2.947223301710365e-09</v>
       </c>
       <c r="F175" t="n">
-        <v>3.772274515773798e-08</v>
+        <v>2.164079207878566e-08</v>
       </c>
       <c r="G175" t="n">
-        <v>4.45180390590703e-08</v>
+        <v>3.244793256587914e-08</v>
       </c>
       <c r="H175" t="n">
-        <v>2.267396397901591e-08</v>
+        <v>9.98234824379292e-09</v>
+      </c>
+      <c r="I175" t="n">
+        <v/>
       </c>
     </row>
     <row r="176">
@@ -6769,19 +7282,22 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>-1.772782227300844e-09</v>
+        <v>-6.619852544139881e-10</v>
       </c>
       <c r="E176" t="n">
-        <v>-2.833516669055814e-09</v>
+        <v>-9.644738943514241e-11</v>
       </c>
       <c r="F176" t="n">
-        <v>-6.23956840995244e-11</v>
+        <v>2.446063305402782e-10</v>
       </c>
       <c r="G176" t="n">
-        <v>-8.402003641653573e-11</v>
+        <v>1.776585553581917e-10</v>
       </c>
       <c r="H176" t="n">
-        <v>-1.699088247981572e-10</v>
+        <v>-3.569454460994488e-10</v>
+      </c>
+      <c r="I176" t="n">
+        <v/>
       </c>
     </row>
     <row r="177">
@@ -6801,19 +7317,22 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>8.065116380998893e-10</v>
+        <v>2.434868782624165e-08</v>
       </c>
       <c r="E177" t="n">
-        <v>-2.071704316700693e-09</v>
+        <v>1.732926031556638e-08</v>
       </c>
       <c r="F177" t="n">
-        <v>4.801134703391113e-08</v>
+        <v>6.887047801826525e-08</v>
       </c>
       <c r="G177" t="n">
-        <v>2.27062208621051e-08</v>
+        <v>2.115136388323455e-08</v>
       </c>
       <c r="H177" t="n">
-        <v>6.31853700574028e-08</v>
+        <v>4.128125324819508e-08</v>
+      </c>
+      <c r="I177" t="n">
+        <v/>
       </c>
     </row>
     <row r="178">
@@ -6833,19 +7352,22 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>2.015099469977391e-09</v>
+        <v>1.605152470607654e-09</v>
       </c>
       <c r="E178" t="n">
-        <v>0.1546174033169199</v>
+        <v>0.1762865432838912</v>
       </c>
       <c r="F178" t="n">
-        <v>1.419108610081119e-07</v>
+        <v>5.84552721028005e-08</v>
       </c>
       <c r="G178" t="n">
-        <v>3.079243299838828e-05</v>
+        <v>1.595730077387749e-08</v>
       </c>
       <c r="H178" t="n">
-        <v>1.059246430229621e-07</v>
+        <v>2.536974858225301e-08</v>
+      </c>
+      <c r="I178" t="n">
+        <v/>
       </c>
     </row>
     <row r="179">
@@ -6865,19 +7387,22 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>-8.687563531507961e-10</v>
+        <v>5.409016585507953e-10</v>
       </c>
       <c r="E179" t="n">
-        <v>-2.73828756014172e-09</v>
+        <v>1.570181975433406e-08</v>
       </c>
       <c r="F179" t="n">
-        <v>5.181772509394109e-07</v>
+        <v>0.288777211500485</v>
       </c>
       <c r="G179" t="n">
-        <v>3.500856366142929e-08</v>
+        <v>1.574291312640028e-08</v>
       </c>
       <c r="H179" t="n">
-        <v>6.72154495066541e-08</v>
+        <v>2.764549650147608e-08</v>
+      </c>
+      <c r="I179" t="n">
+        <v/>
       </c>
     </row>
     <row r="180">
@@ -6897,19 +7422,22 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>7.677239311138841e-09</v>
+        <v>1.05714860095149e-08</v>
       </c>
       <c r="E180" t="n">
-        <v>1.334793639704788e-08</v>
+        <v>3.967605190304901e-08</v>
       </c>
       <c r="F180" t="n">
-        <v>2.429035122037704e-07</v>
+        <v>1.300392892347071e-07</v>
       </c>
       <c r="G180" t="n">
-        <v>6.886454743637985e-05</v>
+        <v>0.1658458472407109</v>
       </c>
       <c r="H180" t="n">
-        <v>2.883586873746236e-07</v>
+        <v>7.922145298235415e-08</v>
+      </c>
+      <c r="I180" t="n">
+        <v/>
       </c>
     </row>
     <row r="181">
@@ -6929,19 +7457,22 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>-1.094562997134739e-09</v>
+        <v>1.573998291444293e-09</v>
       </c>
       <c r="E181" t="n">
-        <v>-2.074481781643897e-09</v>
+        <v>1.761615898893408e-08</v>
       </c>
       <c r="F181" t="n">
-        <v>5.993982473927149e-08</v>
+        <v>7.833345807079393e-08</v>
       </c>
       <c r="G181" t="n">
-        <v>3.898567901650923e-08</v>
+        <v>2.052208335235545e-08</v>
       </c>
       <c r="H181" t="n">
-        <v>7.821000490801537e-07</v>
+        <v>0.2313016763191874</v>
+      </c>
+      <c r="I181" t="n">
+        <v/>
       </c>
     </row>
     <row r="182">
@@ -8219,8 +8750,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="n">
-        <v>1.616780471168727</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -8239,7 +8772,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>60.17358303070068</v>
+        <v>0.02705212216824293</v>
       </c>
     </row>
   </sheetData>

--- a/6node_spain/output_all.xlsx
+++ b/6node_spain/output_all.xlsx
@@ -457,22 +457,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.0001412526301437265</v>
+        <v>2.037059400143211e-07</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9329649128919539</v>
+        <v>0.4627926178921389</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1378556983081443</v>
+        <v>0.135675740102069</v>
       </c>
       <c r="D2" t="n">
-        <v>1.050100798331301</v>
+        <v>0.2212602538490411</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07434178915609041</v>
+        <v>2.343011181345656e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8459403920442028</v>
+        <v>0.5883231662166573</v>
       </c>
     </row>
   </sheetData>
@@ -523,22 +523,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2.220071449848034e-06</v>
+        <v>-8.575487758459032e-09</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4097073999142399</v>
+        <v>-6.468446366239777e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>2.47876868612077e-06</v>
+        <v>3.790778159484525e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0009996009137786224</v>
+        <v>3.002207203777346e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.43544164196468e-06</v>
+        <v>2.170709579249682e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1127786116306059</v>
+        <v>0.2313926714121446</v>
       </c>
     </row>
   </sheetData>
@@ -597,19 +597,19 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002181636648008357</v>
+        <v>5.179411820573688e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>4.064371929212977e-06</v>
+        <v>4.762286582811358e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>3.233029264942841e-06</v>
+        <v>6.161241028001198e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.092554890546369e-05</v>
+        <v>2.428902565565311e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.582521294328548e-06</v>
+        <v>1.171688434473688e-07</v>
       </c>
     </row>
     <row r="3">
@@ -619,22 +619,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0002181636648008357</v>
+        <v>5.179411820573688e-08</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>5.669230804807989e-05</v>
+        <v>3.324611320296732e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>1.368828954250352</v>
+        <v>2.835380145013437e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.181651926593764e-06</v>
+        <v>6.290551596954223e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8681733980848008</v>
+        <v>0.7713083582593593</v>
       </c>
     </row>
     <row r="4">
@@ -644,22 +644,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.064371929212977e-06</v>
+        <v>4.762286582811358e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.669230804807989e-05</v>
+        <v>3.324611320296732e-06</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003342225635356782</v>
+        <v>2.420654074389561e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>5.348014375516973e-06</v>
+        <v>6.233613771235813e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2262366487586565</v>
+        <v>0.2261177097458624</v>
       </c>
     </row>
     <row r="5">
@@ -669,22 +669,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.233029264942841e-06</v>
+        <v>6.161241028001198e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.368828954250352</v>
+        <v>2.835380145013437e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003342225635356782</v>
+        <v>2.420654074389561e-06</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>4.902817725195176e-06</v>
+        <v>7.026513302330341e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3791951598320455</v>
+        <v>0.36875781269967</v>
       </c>
     </row>
     <row r="6">
@@ -694,22 +694,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.092554890546369e-05</v>
+        <v>2.428902565565311e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.181651926593764e-06</v>
+        <v>6.290551596954223e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.348014375516973e-06</v>
+        <v>6.233613771235813e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>4.902817725195176e-06</v>
+        <v>7.026513302330341e-08</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1238120553059773</v>
+        <v>1.843653084902649e-07</v>
       </c>
     </row>
     <row r="7">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.582521294328548e-06</v>
+        <v>1.171688434473688e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8681733980848008</v>
+        <v>0.7713083582593593</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2262366487586565</v>
+        <v>0.2261177097458624</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3791951598320455</v>
+        <v>0.36875781269967</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1238120553059773</v>
+        <v>1.843653084902649e-07</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -790,22 +790,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1.113819562403862e-05</v>
+        <v>9.096687851685471e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.125783088973265e-07</v>
+        <v>9.569230677420959e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>1.175067394498797e-07</v>
+        <v>2.381027388531277e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>2.782525888700427e-06</v>
+        <v>3.076360450281411e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>6.275939146149767e-08</v>
+        <v>1.179230962676735e-08</v>
       </c>
     </row>
     <row r="3">
@@ -815,22 +815,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.136655958433597e-05</v>
+        <v>1.153930774460598e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>7.756185693708062e-08</v>
+        <v>1.770371903237364e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1442050125639238</v>
+        <v>3.997554802108575e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.128833746477653e-07</v>
+        <v>2.461340913036838e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1746735028859643</v>
+        <v>0.1541403629497881</v>
       </c>
     </row>
     <row r="4">
@@ -840,22 +840,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.361757255846641e-07</v>
+        <v>1.035708490489386e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>9.7880210159218e-08</v>
+        <v>1.615566302139686e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0009460265365519582</v>
+        <v>7.83096788717369e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.319883749661415e-08</v>
+        <v>2.593088624778275e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2973362337248007</v>
+        <v>0.2971837786882226</v>
       </c>
     </row>
     <row r="5">
@@ -865,22 +865,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.202102644093372e-07</v>
+        <v>2.527265564361579e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1427162844365196</v>
+        <v>4.086355185370991e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009378946820528533</v>
+        <v>7.653878602194445e-08</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>6.460285817411204e-08</v>
+        <v>6.959554488261688e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>0.164636369534559</v>
+        <v>0.1600915189893897</v>
       </c>
     </row>
     <row r="6">
@@ -890,22 +890,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.759645402417021e-06</v>
+        <v>2.941019752976872e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.180478916840144e-07</v>
+        <v>2.317824318869715e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>6.442679434393028e-08</v>
+        <v>2.464844598859458e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>6.983276534811012e-08</v>
+        <v>7.45327001228091e-08</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2312286427436917</v>
+        <v>1.549215361159485e-06</v>
       </c>
     </row>
     <row r="7">
@@ -915,19 +915,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.006842169168578e-08</v>
+        <v>1.19228379804192e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1762866420917085</v>
+        <v>0.1566183369125971</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2887775527700376</v>
+        <v>0.2843986250247791</v>
       </c>
       <c r="E7" t="n">
-        <v>0.165845921661725</v>
+        <v>0.1612824241403525</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2313018508793159</v>
+        <v>1.443482383325099e-06</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>0.999988861804376</v>
+        <v>0.9999999909033122</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9999998874216911</v>
+        <v>0.9999999904307694</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999998824932606</v>
+        <v>0.9999999761897261</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999972174741113</v>
+        <v>0.9999999692363954</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9999999372406085</v>
+        <v>0.9999999882076904</v>
       </c>
     </row>
     <row r="3">
@@ -1011,22 +1011,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9999886334404157</v>
+        <v>0.9999999884606923</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9999999224381431</v>
+        <v>0.999999982296281</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8557949874360762</v>
+        <v>0.999999960024452</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999998871166254</v>
+        <v>0.9999999753865909</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8253264971140357</v>
+        <v>0.8458596370502119</v>
       </c>
     </row>
     <row r="4">
@@ -1036,22 +1036,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9999998638242744</v>
+        <v>0.9999999896429151</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9999999021197898</v>
+        <v>0.999999983844337</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>0.999053973463448</v>
+        <v>0.9999999216903211</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9999999368011625</v>
+        <v>0.9999999740691138</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7026637662751993</v>
+        <v>0.7028162213117775</v>
       </c>
     </row>
     <row r="5">
@@ -1061,22 +1061,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9999998797897356</v>
+        <v>0.9999999747273444</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8572837155634804</v>
+        <v>0.9999999591364481</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9990621053179471</v>
+        <v>0.999999923461214</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9999999353971418</v>
+        <v>0.9999999304044551</v>
       </c>
       <c r="G5" t="n">
-        <v>0.835363630465441</v>
+        <v>0.8399084810106103</v>
       </c>
     </row>
     <row r="6">
@@ -1086,22 +1086,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9999972403545976</v>
+        <v>0.9999999705898025</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9999998819521083</v>
+        <v>0.9999999768217568</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9999999355732057</v>
+        <v>0.999999975351554</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9999999301672347</v>
+        <v>0.9999999254672999</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7687713572563083</v>
+        <v>0.9999984507846389</v>
       </c>
     </row>
     <row r="7">
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9999999599315783</v>
+        <v>0.9999999880771621</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8237133579082915</v>
+        <v>0.8433816630874029</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7112224472299624</v>
+        <v>0.7156013749752209</v>
       </c>
       <c r="E7" t="n">
-        <v>0.834154078338275</v>
+        <v>0.8387175758596476</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7686981491206841</v>
+        <v>0.9999985565176167</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
     </row>
   </sheetData>
@@ -1195,19 +1195,19 @@
         <v/>
       </c>
       <c r="E2" t="n">
-        <v>1.113036390693752e-05</v>
+        <v>-2.95798206696531e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>1.386681060049398e-08</v>
+        <v>7.002581410011346e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>7.018923276282935e-09</v>
+        <v>4.712454959786824e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>7.00516149576723e-09</v>
+        <v>7.243059136097731e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>7.601391688857664e-09</v>
+        <v>6.908567919152009e-10</v>
       </c>
     </row>
     <row r="3">
@@ -1230,19 +1230,19 @@
         <v/>
       </c>
       <c r="E3" t="n">
-        <v>-4.289234445341601e-10</v>
+        <v>6.301859612007004e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>9.660721926120328e-08</v>
+        <v>2.821082316790431e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>6.054835936386965e-09</v>
+        <v>4.196505787950366e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>5.980766152072504e-09</v>
+        <v>6.639043223372117e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>6.363504824261628e-09</v>
+        <v>3.30914979521553e-10</v>
       </c>
     </row>
     <row r="4">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.001</v>
+        <v/>
       </c>
       <c r="E4" t="n">
-        <v>4.106955412505385e-09</v>
+        <v>2.018951445246814e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>8.494793562115414e-09</v>
+        <v>1.647974393754767e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>9.800880900195733e-08</v>
+        <v>5.884052528266753e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>7.549992605790588e-09</v>
+        <v>8.528973550004608e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>8.85257550644848e-09</v>
+        <v>1.658704852485419e-09</v>
       </c>
     </row>
     <row r="5">
@@ -1300,19 +1300,19 @@
         <v/>
       </c>
       <c r="E5" t="n">
-        <v>6.896455753577099e-09</v>
+        <v>2.271016433289736e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.466454988142029e-09</v>
+        <v>1.823998639091402e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>7.714976254635556e-09</v>
+        <v>7.049530199120687e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>2.761279458549696e-06</v>
+        <v>7.49111330955521e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>4.8237801840849e-09</v>
+        <v>1.586917339009094e-09</v>
       </c>
     </row>
     <row r="6">
@@ -1335,19 +1335,19 @@
         <v/>
       </c>
       <c r="E6" t="n">
-        <v>-3.849648865250157e-09</v>
+        <v>4.668301719560828e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.210000478414463e-10</v>
+        <v>5.227948804638417e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>-7.216361495681907e-10</v>
+        <v>1.911095436043528e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.61478523050937e-09</v>
+        <v>7.359185961284384e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>3.347633139089317e-08</v>
+        <v>7.821424691854067e-09</v>
       </c>
     </row>
     <row r="7">
@@ -1367,22 +1367,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.001</v>
+        <v/>
       </c>
       <c r="E7" t="n">
-        <v>-1.969904035319007e-09</v>
+        <v>-4.508110879403434e-10</v>
       </c>
       <c r="F7" t="n">
-        <v>1.036818421736439e-09</v>
+        <v>-8.16375023791879e-10</v>
       </c>
       <c r="G7" t="n">
-        <v>1.101344704155611e-09</v>
+        <v>2.706189368017924e-10</v>
       </c>
       <c r="H7" t="n">
-        <v>1.025961254794309e-09</v>
+        <v>5.358337262741364e-10</v>
       </c>
       <c r="I7" t="n">
-        <v>1.51538115536144e-09</v>
+        <v>-4.881700830511376e-10</v>
       </c>
     </row>
     <row r="8">
@@ -1405,19 +1405,19 @@
         <v/>
       </c>
       <c r="E8" t="n">
-        <v>-3.895269502901722e-09</v>
+        <v>-2.381824048341753e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.559421878074629e-08</v>
+        <v>-1.156290950302866e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>4.299687162939098e-09</v>
+        <v>2.018351989148722e-10</v>
       </c>
       <c r="H8" t="n">
-        <v>2.261703335089935e-09</v>
+        <v>1.973335645529278e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>3.602953063878478e-09</v>
+        <v>-2.355152665028385e-09</v>
       </c>
     </row>
     <row r="9">
@@ -1440,19 +1440,19 @@
         <v/>
       </c>
       <c r="E9" t="n">
-        <v>-4.091580548521304e-09</v>
+        <v>-2.113018905443869e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.793360210584129e-10</v>
+        <v>-2.299979386933867e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>4.050306011774721e-09</v>
+        <v>3.030734157549562e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>-8.36017791646727e-10</v>
+        <v>4.367578184250459e-10</v>
       </c>
       <c r="I9" t="n">
-        <v>1.57839860554923e-10</v>
+        <v>-2.056089332273169e-09</v>
       </c>
     </row>
     <row r="10">
@@ -1475,19 +1475,19 @@
         <v/>
       </c>
       <c r="E10" t="n">
-        <v>-4.327532270373517e-09</v>
+        <v>-2.283934108971187e-09</v>
       </c>
       <c r="F10" t="n">
-        <v>3.061409507323717e-10</v>
+        <v>-2.470759410907195e-09</v>
       </c>
       <c r="G10" t="n">
-        <v>1.928967132161557e-09</v>
+        <v>6.625471516138554e-11</v>
       </c>
       <c r="H10" t="n">
-        <v>4.64348644632712e-09</v>
+        <v>6.079712525576476e-09</v>
       </c>
       <c r="I10" t="n">
-        <v>5.754836582035277e-10</v>
+        <v>-2.26937352280539e-09</v>
       </c>
     </row>
     <row r="11">
@@ -1510,19 +1510,19 @@
         <v/>
       </c>
       <c r="E11" t="n">
-        <v>-4.492015779640615e-09</v>
+        <v>-9.904630479987553e-10</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.295773623890641e-09</v>
+        <v>-1.143108393618607e-09</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.206516954764175e-09</v>
+        <v>-8.389121480058526e-10</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.950263612920613e-09</v>
+        <v>-1.293137941677706e-09</v>
       </c>
       <c r="I11" t="n">
-        <v>1.110633525089023e-09</v>
+        <v>-3.519684836212419e-10</v>
       </c>
     </row>
     <row r="12">
@@ -1545,19 +1545,19 @@
         <v/>
       </c>
       <c r="E12" t="n">
-        <v>-1.084964960148373e-09</v>
+        <v>-6.764341952638449e-10</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.375368125795622e-10</v>
+        <v>-1.784897816896501e-10</v>
       </c>
       <c r="G12" t="n">
-        <v>6.866342006017646e-10</v>
+        <v>1.480814657628277e-10</v>
       </c>
       <c r="H12" t="n">
-        <v>5.005992819882563e-10</v>
+        <v>3.23648458772965e-10</v>
       </c>
       <c r="I12" t="n">
-        <v>7.460584096684323e-10</v>
+        <v>-4.296548353749345e-10</v>
       </c>
     </row>
     <row r="13">
@@ -1580,19 +1580,19 @@
         <v/>
       </c>
       <c r="E13" t="n">
-        <v>-2.845980972773412e-09</v>
+        <v>-8.61691955986672e-10</v>
       </c>
       <c r="F13" t="n">
-        <v>8.901214867797349e-10</v>
+        <v>-2.364544570114797e-09</v>
       </c>
       <c r="G13" t="n">
-        <v>3.98879770519558e-09</v>
+        <v>1.660615898883282e-10</v>
       </c>
       <c r="H13" t="n">
-        <v>1.869001187099739e-09</v>
+        <v>1.757264357036616e-09</v>
       </c>
       <c r="I13" t="n">
-        <v>3.026002775517072e-09</v>
+        <v>-2.304453125534906e-09</v>
       </c>
     </row>
     <row r="14">
@@ -1615,19 +1615,19 @@
         <v/>
       </c>
       <c r="E14" t="n">
-        <v>-4.276987553079628e-09</v>
+        <v>-2.261637503066348e-09</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.280224786710368e-09</v>
+        <v>-2.163446062607325e-09</v>
       </c>
       <c r="G14" t="n">
-        <v>4.204097862365146e-09</v>
+        <v>2.93389254193985e-09</v>
       </c>
       <c r="H14" t="n">
-        <v>-7.825342027222203e-10</v>
+        <v>4.425323088643542e-10</v>
       </c>
       <c r="I14" t="n">
-        <v>1.426578238415719e-10</v>
+        <v>-2.107996736283097e-09</v>
       </c>
     </row>
     <row r="15">
@@ -1650,19 +1650,19 @@
         <v/>
       </c>
       <c r="E15" t="n">
-        <v>-4.533147559210108e-09</v>
+        <v>-2.378986762475898e-09</v>
       </c>
       <c r="F15" t="n">
-        <v>-9.241853398356815e-10</v>
+        <v>-2.316856582002374e-09</v>
       </c>
       <c r="G15" t="n">
-        <v>2.271487281912871e-09</v>
+        <v>1.214175373984816e-10</v>
       </c>
       <c r="H15" t="n">
-        <v>5.34522515826243e-09</v>
+        <v>6.555503525283889e-09</v>
       </c>
       <c r="I15" t="n">
-        <v>6.109908503663567e-10</v>
+        <v>-2.277279026471706e-09</v>
       </c>
     </row>
     <row r="16">
@@ -1685,19 +1685,19 @@
         <v/>
       </c>
       <c r="E16" t="n">
-        <v>-4.296995018775821e-09</v>
+        <v>-1.612886998891974e-09</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.504739431267031e-09</v>
+        <v>-1.252260797354398e-09</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.079340224983505e-09</v>
+        <v>-9.9721390228555e-10</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.894285973391466e-09</v>
+        <v>-1.339599058610761e-09</v>
       </c>
       <c r="I16" t="n">
-        <v>2.128256877219839e-09</v>
+        <v>-9.527856626690968e-10</v>
       </c>
     </row>
     <row r="17">
@@ -1720,19 +1720,19 @@
         <v/>
       </c>
       <c r="E17" t="n">
-        <v>1.063360835669627e-09</v>
+        <v>-3.029675211547256e-10</v>
       </c>
       <c r="F17" t="n">
-        <v>1.430832032743528e-09</v>
+        <v>-4.198339438534387e-10</v>
       </c>
       <c r="G17" t="n">
-        <v>-6.437224348221077e-10</v>
+        <v>-4.371624156666205e-10</v>
       </c>
       <c r="H17" t="n">
-        <v>1.416026191480356e-09</v>
+        <v>8.173015223160058e-10</v>
       </c>
       <c r="I17" t="n">
-        <v>7.632457748622214e-10</v>
+        <v>-1.311117466551056e-10</v>
       </c>
     </row>
     <row r="18">
@@ -1755,19 +1755,19 @@
         <v/>
       </c>
       <c r="E18" t="n">
-        <v>-1.598417124586239e-09</v>
+        <v>-1.049036147042697e-10</v>
       </c>
       <c r="F18" t="n">
-        <v>6.040560586949836e-10</v>
+        <v>-2.2841546295958e-09</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.057073723153078e-09</v>
+        <v>-9.666736363859214e-10</v>
       </c>
       <c r="H18" t="n">
-        <v>-7.540372435542546e-10</v>
+        <v>5.112864741503896e-10</v>
       </c>
       <c r="I18" t="n">
-        <v>-5.073797497067084e-10</v>
+        <v>-2.081404300688306e-09</v>
       </c>
     </row>
     <row r="19">
@@ -1790,19 +1790,19 @@
         <v/>
       </c>
       <c r="E19" t="n">
-        <v>-3.761402756225831e-09</v>
+        <v>-2.285010429851386e-09</v>
       </c>
       <c r="F19" t="n">
-        <v>4.426350876776947e-09</v>
+        <v>-6.063328497857239e-10</v>
       </c>
       <c r="G19" t="n">
-        <v>-9.461311287989981e-10</v>
+        <v>-9.689177899833386e-10</v>
       </c>
       <c r="H19" t="n">
-        <v>-5.322516469655264e-10</v>
+        <v>6.550446733231406e-10</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.057896966346033e-10</v>
+        <v>-2.192057407318387e-09</v>
       </c>
     </row>
     <row r="20">
@@ -1822,22 +1822,22 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.001</v>
+        <v/>
       </c>
       <c r="E20" t="n">
-        <v>-4.218191827466365e-09</v>
+        <v>-2.205007507197117e-09</v>
       </c>
       <c r="F20" t="n">
-        <v>4.245264999038013e-10</v>
+        <v>-2.318205666243836e-09</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.739507894546942e-10</v>
+        <v>-5.99922504250237e-10</v>
       </c>
       <c r="H20" t="n">
-        <v>4.656335546430131e-09</v>
+        <v>6.990632653704296e-09</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.658392777793136e-10</v>
+        <v>-2.125433319607579e-09</v>
       </c>
     </row>
     <row r="21">
@@ -1860,19 +1860,19 @@
         <v/>
       </c>
       <c r="E21" t="n">
-        <v>-4.008043168218126e-09</v>
+        <v>-3.484528595989256e-11</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.378663850326657e-09</v>
+        <v>3.195504204087505e-11</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.96768925522705e-09</v>
+        <v>-4.207447911218773e-10</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.117755526242572e-09</v>
+        <v>-7.828514947737794e-11</v>
       </c>
       <c r="I21" t="n">
-        <v>6.543067074369435e-09</v>
+        <v>1.298768827294325e-09</v>
       </c>
     </row>
     <row r="22">
@@ -1895,19 +1895,19 @@
         <v/>
       </c>
       <c r="E22" t="n">
-        <v>6.611881829346997e-09</v>
+        <v>1.70013357526006e-10</v>
       </c>
       <c r="F22" t="n">
-        <v>8.437168254666333e-11</v>
+        <v>6.96826054411893e-11</v>
       </c>
       <c r="G22" t="n">
-        <v>9.336682542369051e-10</v>
+        <v>8.387999772006955e-10</v>
       </c>
       <c r="H22" t="n">
-        <v>-4.936508318269135e-10</v>
+        <v>-5.861702106014601e-10</v>
       </c>
       <c r="I22" t="n">
-        <v>1.907109634640205e-10</v>
+        <v>5.342825868552582e-10</v>
       </c>
     </row>
     <row r="23">
@@ -1930,19 +1930,19 @@
         <v/>
       </c>
       <c r="E23" t="n">
-        <v>-4.089044929160331e-09</v>
+        <v>-4.108552782989174e-10</v>
       </c>
       <c r="F23" t="n">
-        <v>7.811879686542918e-10</v>
+        <v>-2.377957308983115e-09</v>
       </c>
       <c r="G23" t="n">
-        <v>1.54184928976048e-09</v>
+        <v>8.285616984862698e-11</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.031014788834865e-09</v>
+        <v>-4.513970274558715e-10</v>
       </c>
       <c r="I23" t="n">
-        <v>1.825138799249094e-10</v>
+        <v>-2.135669387981683e-09</v>
       </c>
     </row>
     <row r="24">
@@ -1965,19 +1965,19 @@
         <v/>
       </c>
       <c r="E24" t="n">
-        <v>-4.429561358159157e-09</v>
+        <v>-2.391256447617038e-09</v>
       </c>
       <c r="F24" t="n">
-        <v>4.511564581504649e-09</v>
+        <v>-9.534387683779506e-10</v>
       </c>
       <c r="G24" t="n">
-        <v>2.023587597601991e-09</v>
+        <v>8.321074230459912e-11</v>
       </c>
       <c r="H24" t="n">
-        <v>-7.503881344026382e-10</v>
+        <v>-3.258648061247789e-10</v>
       </c>
       <c r="I24" t="n">
-        <v>4.714333996948073e-10</v>
+        <v>-2.267368362837605e-09</v>
       </c>
     </row>
     <row r="25">
@@ -2000,19 +2000,19 @@
         <v/>
       </c>
       <c r="E25" t="n">
-        <v>-4.295411622385984e-09</v>
+        <v>-2.034928710155704e-09</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.121765043024582e-10</v>
+        <v>-2.14179342903679e-09</v>
       </c>
       <c r="G25" t="n">
-        <v>6.881069763613266e-09</v>
+        <v>5.366982451127682e-09</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.085496821370898e-09</v>
+        <v>-3.316176726670224e-10</v>
       </c>
       <c r="I25" t="n">
-        <v>1.99143813910734e-10</v>
+        <v>-1.849563180821279e-09</v>
       </c>
     </row>
     <row r="26">
@@ -2032,22 +2032,22 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.001</v>
+        <v/>
       </c>
       <c r="E26" t="n">
-        <v>-4.532683942203711e-09</v>
+        <v>-2.174505040537127e-09</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.227772233030481e-09</v>
+        <v>-2.207641390678137e-09</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.911424418747484e-09</v>
+        <v>-1.075866407189954e-09</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.001081011893348e-09</v>
+        <v>-1.836871369555136e-09</v>
       </c>
       <c r="I26" t="n">
-        <v>1.389296843413113e-09</v>
+        <v>-1.717685255284451e-09</v>
       </c>
     </row>
     <row r="27">
@@ -2070,19 +2070,19 @@
         <v/>
       </c>
       <c r="E27" t="n">
-        <v>-4.620354255003145e-09</v>
+        <v>9.500155229000234e-10</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.71448522345802e-09</v>
+        <v>1.003357363413101e-09</v>
       </c>
       <c r="G27" t="n">
-        <v>-2.077924336239886e-09</v>
+        <v>-9.385981506079307e-10</v>
       </c>
       <c r="H27" t="n">
-        <v>-2.44893394244557e-09</v>
+        <v>-1.203675115093234e-09</v>
       </c>
       <c r="I27" t="n">
-        <v>-3.215396298160228e-09</v>
+        <v>2.084965403475057e-10</v>
       </c>
     </row>
     <row r="28">
@@ -2102,22 +2102,22 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.001</v>
+        <v/>
       </c>
       <c r="E28" t="n">
-        <v>-3.550121152703622e-09</v>
+        <v>3.056039133449308e-09</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.78010760580055e-09</v>
+        <v>-1.5601147979185e-09</v>
       </c>
       <c r="G28" t="n">
-        <v>-2.318708491847873e-09</v>
+        <v>-1.264168222729729e-09</v>
       </c>
       <c r="H28" t="n">
-        <v>-2.944241018801392e-09</v>
+        <v>-1.327711165634871e-09</v>
       </c>
       <c r="I28" t="n">
-        <v>-3.340237331505456e-09</v>
+        <v>-1.690084064574351e-09</v>
       </c>
     </row>
     <row r="29">
@@ -2140,19 +2140,19 @@
         <v/>
       </c>
       <c r="E29" t="n">
-        <v>-4.522919002426998e-09</v>
+        <v>-1.363732451068012e-09</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.58164012092429e-09</v>
+        <v>4.18230353421559e-09</v>
       </c>
       <c r="G29" t="n">
-        <v>-2.360302742968255e-09</v>
+        <v>-1.140394706495267e-09</v>
       </c>
       <c r="H29" t="n">
-        <v>-2.921824254598207e-09</v>
+        <v>-1.202209144810843e-09</v>
       </c>
       <c r="I29" t="n">
-        <v>-3.478134854422212e-09</v>
+        <v>-1.588505930703135e-09</v>
       </c>
     </row>
     <row r="30">
@@ -2175,19 +2175,19 @@
         <v/>
       </c>
       <c r="E30" t="n">
-        <v>-3.965669729812913e-09</v>
+        <v>-5.421006852973089e-10</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.31595463254479e-09</v>
+        <v>-6.393275626763368e-10</v>
       </c>
       <c r="G30" t="n">
-        <v>-5.694203935219213e-11</v>
+        <v>3.262816281362284e-09</v>
       </c>
       <c r="H30" t="n">
-        <v>-2.177626468983502e-09</v>
+        <v>-1.806658306610163e-10</v>
       </c>
       <c r="I30" t="n">
-        <v>-3.024912879724147e-09</v>
+        <v>-8.762935500877884e-10</v>
       </c>
     </row>
     <row r="31">
@@ -2210,19 +2210,19 @@
         <v/>
       </c>
       <c r="E31" t="n">
-        <v>-4.55240411862345e-09</v>
+        <v>-2.244620173663077e-09</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.235761604134518e-09</v>
+        <v>-2.329325271635812e-09</v>
       </c>
       <c r="G31" t="n">
-        <v>-2.0727293928239e-09</v>
+        <v>-1.341297014098937e-09</v>
       </c>
       <c r="H31" t="n">
-        <v>-2.085545670182372e-09</v>
+        <v>1.02286332987174e-10</v>
       </c>
       <c r="I31" t="n">
-        <v>-3.411316514366885e-09</v>
+        <v>-2.350835070258663e-09</v>
       </c>
     </row>
     <row r="32">
@@ -2242,22 +2242,22 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-3.69317143762145e-09</v>
+        <v>-2.239500455853553e-09</v>
       </c>
       <c r="E32" t="n">
-        <v>0.001</v>
+        <v/>
       </c>
       <c r="F32" t="n">
-        <v>-1.893655081590023e-10</v>
+        <v>-1.528103616089221e-09</v>
       </c>
       <c r="G32" t="n">
-        <v>-6.385396229970459e-11</v>
+        <v>-1.699070459325832e-10</v>
       </c>
       <c r="H32" t="n">
-        <v>3.754763433934879e-10</v>
+        <v>1.934015429181933e-10</v>
       </c>
       <c r="I32" t="n">
-        <v>-2.286325128103791e-09</v>
+        <v>-3.304939373491114e-10</v>
       </c>
     </row>
     <row r="33">
@@ -2277,22 +2277,22 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-4.493794384026831e-09</v>
+        <v>-2.961436110454527e-09</v>
       </c>
       <c r="E33" t="n">
         <v/>
       </c>
       <c r="F33" t="n">
-        <v>1.617223316083949e-09</v>
+        <v>-1.443633888734018e-09</v>
       </c>
       <c r="G33" t="n">
-        <v>8.839785627017017e-09</v>
+        <v>-1.451976133401065e-09</v>
       </c>
       <c r="H33" t="n">
-        <v>6.404920111775167e-10</v>
+        <v>-2.33670721740496e-10</v>
       </c>
       <c r="I33" t="n">
-        <v>-4.041504267714164e-09</v>
+        <v>3.904506802046468e-09</v>
       </c>
     </row>
     <row r="34">
@@ -2312,22 +2312,22 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-4.386946360132971e-09</v>
+        <v>-2.86097199275945e-09</v>
       </c>
       <c r="E34" t="n">
         <v/>
       </c>
       <c r="F34" t="n">
-        <v>3.782246736562618e-10</v>
+        <v>-2.747067255462848e-09</v>
       </c>
       <c r="G34" t="n">
-        <v>2.488587840183524e-08</v>
+        <v>3.638157169417964e-09</v>
       </c>
       <c r="H34" t="n">
-        <v>1.664634739930471e-09</v>
+        <v>2.992201550633193e-10</v>
       </c>
       <c r="I34" t="n">
-        <v>-3.505943046883095e-09</v>
+        <v>5.134649216606724e-09</v>
       </c>
     </row>
     <row r="35">
@@ -2347,22 +2347,22 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-4.454006044915851e-09</v>
+        <v>-2.798996500687055e-09</v>
       </c>
       <c r="E35" t="n">
         <v/>
       </c>
       <c r="F35" t="n">
-        <v>-4.406017677567334e-10</v>
+        <v>-2.688991596984676e-09</v>
       </c>
       <c r="G35" t="n">
-        <v>7.04653463982327e-09</v>
+        <v>-9.792563005355892e-10</v>
       </c>
       <c r="H35" t="n">
-        <v>5.982716397258804e-09</v>
+        <v>4.105579734041342e-09</v>
       </c>
       <c r="I35" t="n">
-        <v>-3.759946460547391e-09</v>
+        <v>4.492685819175144e-09</v>
       </c>
     </row>
     <row r="36">
@@ -2382,22 +2382,22 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-4.639785992278809e-09</v>
+        <v>-2.822609701764304e-09</v>
       </c>
       <c r="E36" t="n">
         <v/>
       </c>
       <c r="F36" t="n">
-        <v>-1.948029155466617e-09</v>
+        <v>-2.708169173060772e-09</v>
       </c>
       <c r="G36" t="n">
-        <v>4.37609749664806e-09</v>
+        <v>-1.468449768570775e-09</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.919057893124717e-09</v>
+        <v>-1.060642024046662e-09</v>
       </c>
       <c r="I36" t="n">
-        <v>-2.036205183938167e-09</v>
+        <v>9.873027343714837e-09</v>
       </c>
     </row>
     <row r="37">
@@ -2417,22 +2417,22 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1.135526257185091e-05</v>
+        <v>-6.031608818516433e-10</v>
       </c>
       <c r="E37" t="n">
         <v/>
       </c>
       <c r="F37" t="n">
-        <v>2.108405422030542e-09</v>
+        <v>-3.667710610551054e-10</v>
       </c>
       <c r="G37" t="n">
-        <v>1.761952368124537e-08</v>
+        <v>5.340003855832906e-09</v>
       </c>
       <c r="H37" t="n">
-        <v>6.330403339817373e-09</v>
+        <v>4.98051679549163e-09</v>
       </c>
       <c r="I37" t="n">
-        <v>6.30970369240664e-10</v>
+        <v>6.915846038527825e-09</v>
       </c>
     </row>
     <row r="38">
@@ -2452,22 +2452,22 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1.59036599206093e-08</v>
+        <v>2.24280740281144e-10</v>
       </c>
       <c r="E38" t="n">
         <v/>
       </c>
       <c r="F38" t="n">
-        <v>8.014275947859846e-08</v>
+        <v>1.067551902685116e-09</v>
       </c>
       <c r="G38" t="n">
-        <v>6.007959485435506e-08</v>
+        <v>7.994694711746674e-09</v>
       </c>
       <c r="H38" t="n">
-        <v>1.576725493155117e-08</v>
+        <v>7.530599540646138e-09</v>
       </c>
       <c r="I38" t="n">
-        <v>1.512291128900862e-08</v>
+        <v>8.23899400907616e-09</v>
       </c>
     </row>
     <row r="39">
@@ -2487,22 +2487,22 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-1.332877069332781e-09</v>
+        <v>1.499629657990844e-09</v>
       </c>
       <c r="E39" t="n">
-        <v>0.001</v>
+        <v/>
       </c>
       <c r="F39" t="n">
-        <v>2.908610502247928e-09</v>
+        <v>1.796384400780475e-09</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1442049055471118</v>
+        <v>8.582746343319386e-09</v>
       </c>
       <c r="H39" t="n">
-        <v>4.382780873458568e-09</v>
+        <v>5.461933876755102e-09</v>
       </c>
       <c r="I39" t="n">
-        <v>-6.906867383792801e-10</v>
+        <v>1.342998841405551e-08</v>
       </c>
     </row>
     <row r="40">
@@ -2522,22 +2522,22 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-7.862973688165211e-10</v>
+        <v>1.015119640434702e-09</v>
       </c>
       <c r="E40" t="n">
         <v/>
       </c>
       <c r="F40" t="n">
-        <v>3.304299259255586e-09</v>
+        <v>1.05851453112626e-09</v>
       </c>
       <c r="G40" t="n">
-        <v>2.177001407429877e-08</v>
+        <v>9.528751699910862e-09</v>
       </c>
       <c r="H40" t="n">
-        <v>8.707666082508518e-08</v>
+        <v>4.996244235442196e-09</v>
       </c>
       <c r="I40" t="n">
-        <v>1.873937549986661e-09</v>
+        <v>8.902119028647482e-09</v>
       </c>
     </row>
     <row r="41">
@@ -2557,22 +2557,22 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-3.702051110473355e-09</v>
+        <v>9.571230163373565e-09</v>
       </c>
       <c r="E41" t="n">
         <v/>
       </c>
       <c r="F41" t="n">
-        <v>-1.352594216621293e-09</v>
+        <v>1.414723622787489e-08</v>
       </c>
       <c r="G41" t="n">
-        <v>7.161645059499944e-09</v>
+        <v>8.703305850566841e-09</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.552323718282145e-09</v>
+        <v>1.660854210481278e-09</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1746734758827457</v>
+        <v>0.1541403254654685</v>
       </c>
     </row>
     <row r="42">
@@ -2592,22 +2592,22 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-2.957552998522707e-09</v>
+        <v>-9.860057473045518e-10</v>
       </c>
       <c r="E42" t="n">
         <v/>
       </c>
       <c r="F42" t="n">
-        <v>-6.199813800583645e-10</v>
+        <v>-2.880701837246614e-09</v>
       </c>
       <c r="G42" t="n">
-        <v>1.087686184039591e-08</v>
+        <v>-1.230410771659814e-09</v>
       </c>
       <c r="H42" t="n">
-        <v>1.317043436808972e-09</v>
+        <v>3.266112198775628e-11</v>
       </c>
       <c r="I42" t="n">
-        <v>-3.771456672120116e-09</v>
+        <v>3.610433531204571e-09</v>
       </c>
     </row>
     <row r="43">
@@ -2627,22 +2627,22 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1.384221694230547e-08</v>
+        <v>-1.006677250648056e-09</v>
       </c>
       <c r="E43" t="n">
         <v/>
       </c>
       <c r="F43" t="n">
-        <v>1.568002499243932e-09</v>
+        <v>-1.269778182498123e-09</v>
       </c>
       <c r="G43" t="n">
-        <v>1.475158855464631e-09</v>
+        <v>7.331325952622288e-10</v>
       </c>
       <c r="H43" t="n">
-        <v>2.983558601003991e-09</v>
+        <v>1.087508569525576e-09</v>
       </c>
       <c r="I43" t="n">
-        <v>1.204956378199939e-08</v>
+        <v>-2.802019077461274e-10</v>
       </c>
     </row>
     <row r="44">
@@ -2662,22 +2662,22 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-3.768685770910559e-09</v>
+        <v>-2.258109103549613e-09</v>
       </c>
       <c r="E44" t="n">
         <v/>
       </c>
       <c r="F44" t="n">
-        <v>3.820120809645587e-11</v>
+        <v>-2.658536930338239e-09</v>
       </c>
       <c r="G44" t="n">
-        <v>5.724184185108211e-08</v>
+        <v>4.543142384479497e-09</v>
       </c>
       <c r="H44" t="n">
-        <v>1.155134904783134e-09</v>
+        <v>2.409113284783915e-10</v>
       </c>
       <c r="I44" t="n">
-        <v>-3.717782890915769e-09</v>
+        <v>5.987568199493196e-09</v>
       </c>
     </row>
     <row r="45">
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>-4.293923484240085e-09</v>
+        <v>-2.295075342200209e-09</v>
       </c>
       <c r="E45" t="n">
         <v/>
       </c>
       <c r="F45" t="n">
-        <v>1.51334145712953e-10</v>
+        <v>-2.701408641549776e-09</v>
       </c>
       <c r="G45" t="n">
-        <v>1.404486219529233e-08</v>
+        <v>-7.833031224317237e-10</v>
       </c>
       <c r="H45" t="n">
-        <v>1.090499853159825e-08</v>
+        <v>4.940396466947654e-09</v>
       </c>
       <c r="I45" t="n">
-        <v>-3.465453772613996e-09</v>
+        <v>4.375173130350604e-09</v>
       </c>
     </row>
     <row r="46">
@@ -2732,22 +2732,22 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>-3.939927276398467e-09</v>
+        <v>-1.865122591299024e-09</v>
       </c>
       <c r="E46" t="n">
         <v/>
       </c>
       <c r="F46" t="n">
-        <v>-1.921032421224416e-09</v>
+        <v>-2.370973798987729e-09</v>
       </c>
       <c r="G46" t="n">
-        <v>6.907585114480853e-09</v>
+        <v>-1.107891712026352e-09</v>
       </c>
       <c r="H46" t="n">
-        <v>-2.062481712726999e-09</v>
+        <v>-9.647919844228101e-10</v>
       </c>
       <c r="I46" t="n">
-        <v>-2.918667982441778e-09</v>
+        <v>1.650235473382478e-08</v>
       </c>
     </row>
     <row r="47">
@@ -2767,22 +2767,22 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-1.40072210495777e-09</v>
+        <v>-6.148253030648578e-10</v>
       </c>
       <c r="E47" t="n">
         <v/>
       </c>
       <c r="F47" t="n">
-        <v>3.76311379864773e-10</v>
+        <v>-2.734123263916209e-09</v>
       </c>
       <c r="G47" t="n">
-        <v>5.609820381921614e-09</v>
+        <v>-1.916880404041939e-09</v>
       </c>
       <c r="H47" t="n">
-        <v>1.257159037549386e-09</v>
+        <v>2.145884499552491e-10</v>
       </c>
       <c r="I47" t="n">
-        <v>-3.987170560623659e-09</v>
+        <v>3.568818623232743e-09</v>
       </c>
     </row>
     <row r="48">
@@ -2802,22 +2802,22 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-4.131208897374992e-09</v>
+        <v>-2.826185898234394e-10</v>
       </c>
       <c r="E48" t="n">
         <v/>
       </c>
       <c r="F48" t="n">
-        <v>1.826695119415328e-10</v>
+        <v>-3.52770057219948e-10</v>
       </c>
       <c r="G48" t="n">
-        <v>-6.345812269477688e-10</v>
+        <v>-1.119093969541276e-09</v>
       </c>
       <c r="H48" t="n">
-        <v>-3.514853244713791e-10</v>
+        <v>2.657861002040361e-10</v>
       </c>
       <c r="I48" t="n">
-        <v>-3.611689283520155e-09</v>
+        <v>-7.699548123472895e-11</v>
       </c>
     </row>
     <row r="49">
@@ -2837,22 +2837,22 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-3.899895146543647e-09</v>
+        <v>-2.239904942019307e-09</v>
       </c>
       <c r="E49" t="n">
         <v/>
       </c>
       <c r="F49" t="n">
-        <v>2.897295486536898e-09</v>
+        <v>-2.609886427318342e-10</v>
       </c>
       <c r="G49" t="n">
-        <v>6.702064380566613e-09</v>
+        <v>-1.93402728901246e-09</v>
       </c>
       <c r="H49" t="n">
-        <v>2.168808953373418e-10</v>
+        <v>-4.354138415735854e-11</v>
       </c>
       <c r="I49" t="n">
-        <v>-4.268593110227891e-09</v>
+        <v>4.792900936917059e-09</v>
       </c>
     </row>
     <row r="50">
@@ -2872,22 +2872,22 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-4.035671795437813e-09</v>
+        <v>-2.088070462533226e-09</v>
       </c>
       <c r="E50" t="n">
-        <v>0.001</v>
+        <v/>
       </c>
       <c r="F50" t="n">
-        <v>7.562468866420974e-10</v>
+        <v>-2.47605020017486e-09</v>
       </c>
       <c r="G50" t="n">
-        <v>5.996145276190102e-09</v>
+        <v>-1.679351972545959e-09</v>
       </c>
       <c r="H50" t="n">
-        <v>6.30974910414328e-09</v>
+        <v>4.837823700676785e-09</v>
       </c>
       <c r="I50" t="n">
-        <v>-3.984262348720991e-09</v>
+        <v>4.675850341397271e-09</v>
       </c>
     </row>
     <row r="51">
@@ -2907,22 +2907,22 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>-3.821582128467596e-09</v>
+        <v>-5.462837026581623e-10</v>
       </c>
       <c r="E51" t="n">
         <v/>
       </c>
       <c r="F51" t="n">
-        <v>-9.968218870142542e-10</v>
+        <v>-1.171253653100743e-09</v>
       </c>
       <c r="G51" t="n">
-        <v>4.437548389296383e-09</v>
+        <v>-1.115919442343847e-09</v>
       </c>
       <c r="H51" t="n">
-        <v>-1.313679986945935e-09</v>
+        <v>3.405123628707977e-10</v>
       </c>
       <c r="I51" t="n">
-        <v>-2.088078747322859e-10</v>
+        <v>3.08913507211372e-08</v>
       </c>
     </row>
     <row r="52">
@@ -2942,22 +2942,22 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>-3.744703788468363e-09</v>
+        <v>-4.771224185494558e-10</v>
       </c>
       <c r="E52" t="n">
         <v/>
       </c>
       <c r="F52" t="n">
-        <v>-5.104031753329182e-10</v>
+        <v>-2.673885797998914e-09</v>
       </c>
       <c r="G52" t="n">
-        <v>7.122616624035064e-09</v>
+        <v>-9.566373960706314e-10</v>
       </c>
       <c r="H52" t="n">
-        <v>-1.943479332408944e-10</v>
+        <v>-9.589375597961325e-10</v>
       </c>
       <c r="I52" t="n">
-        <v>-3.654905442354816e-09</v>
+        <v>4.579383505712983e-09</v>
       </c>
     </row>
     <row r="53">
@@ -2977,22 +2977,22 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>-1.752506341831659e-09</v>
+        <v>-7.703854132042466e-10</v>
       </c>
       <c r="E53" t="n">
         <v/>
       </c>
       <c r="F53" t="n">
-        <v>2.576676727891132e-10</v>
+        <v>-7.467139502022141e-10</v>
       </c>
       <c r="G53" t="n">
-        <v>1.830605164531584e-10</v>
+        <v>5.758098062734292e-10</v>
       </c>
       <c r="H53" t="n">
-        <v>-5.580310770960329e-10</v>
+        <v>-8.245106320034719e-10</v>
       </c>
       <c r="I53" t="n">
-        <v>-1.43785112466897e-09</v>
+        <v>-5.21315268224744e-11</v>
       </c>
     </row>
     <row r="54">
@@ -3012,22 +3012,22 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-4.153894763417958e-09</v>
+        <v>-2.415189345181208e-09</v>
       </c>
       <c r="E54" t="n">
         <v/>
       </c>
       <c r="F54" t="n">
-        <v>3.263613784712122e-09</v>
+        <v>-7.518120639651511e-10</v>
       </c>
       <c r="G54" t="n">
-        <v>1.131909665277027e-08</v>
+        <v>-1.057970246725079e-09</v>
       </c>
       <c r="H54" t="n">
-        <v>4.765251790851367e-11</v>
+        <v>-1.007632083079279e-09</v>
       </c>
       <c r="I54" t="n">
-        <v>-3.754781619828955e-09</v>
+        <v>4.767351703766481e-09</v>
       </c>
     </row>
     <row r="55">
@@ -3047,22 +3047,22 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-4.010554143187793e-09</v>
+        <v>-2.099134796036356e-09</v>
       </c>
       <c r="E55" t="n">
         <v/>
       </c>
       <c r="F55" t="n">
-        <v>6.987440137567641e-10</v>
+        <v>-2.421493984996151e-09</v>
       </c>
       <c r="G55" t="n">
-        <v>2.94628718730051e-08</v>
+        <v>7.293968456217155e-09</v>
       </c>
       <c r="H55" t="n">
-        <v>1.270029045652411e-10</v>
+        <v>-7.421485016957691e-10</v>
       </c>
       <c r="I55" t="n">
-        <v>-3.351106073406787e-09</v>
+        <v>7.24547119756431e-09</v>
       </c>
     </row>
     <row r="56">
@@ -3082,22 +3082,22 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-4.34041273847125e-09</v>
+        <v>-2.385102653751244e-09</v>
       </c>
       <c r="E56" t="n">
-        <v>0.001</v>
+        <v/>
       </c>
       <c r="F56" t="n">
-        <v>-1.91920018393538e-09</v>
+        <v>-2.683624226754624e-09</v>
       </c>
       <c r="G56" t="n">
-        <v>4.430501545925537e-09</v>
+        <v>-1.454664230951315e-09</v>
       </c>
       <c r="H56" t="n">
-        <v>-2.379900257391961e-09</v>
+        <v>-1.826524800604561e-09</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.990079925220022e-09</v>
+        <v>1.026892247769578e-08</v>
       </c>
     </row>
     <row r="57">
@@ -3117,22 +3117,22 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>-3.495548862056048e-09</v>
+        <v>1.072295960160939e-09</v>
       </c>
       <c r="E57" t="n">
-        <v>0.001</v>
+        <v/>
       </c>
       <c r="F57" t="n">
-        <v>-1.936880688840705e-09</v>
+        <v>-2.460483570073337e-09</v>
       </c>
       <c r="G57" t="n">
-        <v>3.855619675843031e-09</v>
+        <v>-1.667507363099911e-09</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.965996282358502e-09</v>
+        <v>-9.649401214450561e-10</v>
       </c>
       <c r="I57" t="n">
-        <v>-4.847361782292492e-09</v>
+        <v>4.399893545549154e-09</v>
       </c>
     </row>
     <row r="58">
@@ -3152,22 +3152,22 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>-4.265328259842365e-09</v>
+        <v>3.931584658706883e-09</v>
       </c>
       <c r="E58" t="n">
         <v/>
       </c>
       <c r="F58" t="n">
-        <v>-1.818973580213967e-09</v>
+        <v>3.569848276508239e-09</v>
       </c>
       <c r="G58" t="n">
-        <v>-9.636691286938211e-10</v>
+        <v>-4.319547975067635e-10</v>
       </c>
       <c r="H58" t="n">
-        <v>-2.449518277514357e-09</v>
+        <v>-8.48506201113582e-10</v>
       </c>
       <c r="I58" t="n">
-        <v>-4.826518063344988e-09</v>
+        <v>4.212360738143965e-10</v>
       </c>
     </row>
     <row r="59">
@@ -3187,22 +3187,22 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>-4.473948214297139e-09</v>
+        <v>-1.018740377129701e-09</v>
       </c>
       <c r="E59" t="n">
         <v/>
       </c>
       <c r="F59" t="n">
-        <v>-1.59288816538954e-09</v>
+        <v>7.537916833165854e-09</v>
       </c>
       <c r="G59" t="n">
-        <v>3.605768342175373e-09</v>
+        <v>-1.396051669026319e-09</v>
       </c>
       <c r="H59" t="n">
-        <v>-2.374026594550828e-09</v>
+        <v>-9.090698491491166e-10</v>
       </c>
       <c r="I59" t="n">
-        <v>-4.881829824092064e-09</v>
+        <v>8.491574235328283e-09</v>
       </c>
     </row>
     <row r="60">
@@ -3222,22 +3222,22 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>-3.790016729425227e-09</v>
+        <v>-5.311676600348454e-11</v>
       </c>
       <c r="E60" t="n">
         <v/>
       </c>
       <c r="F60" t="n">
-        <v>-8.080790197564764e-10</v>
+        <v>-9.644720471567026e-10</v>
       </c>
       <c r="G60" t="n">
-        <v>1.715506768944471e-08</v>
+        <v>8.738228441824454e-09</v>
       </c>
       <c r="H60" t="n">
-        <v>-1.210929697134936e-09</v>
+        <v>3.5525237093002e-10</v>
       </c>
       <c r="I60" t="n">
-        <v>-4.795004428117606e-09</v>
+        <v>1.205424811371897e-08</v>
       </c>
     </row>
     <row r="61">
@@ -3257,22 +3257,22 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>-4.432173081548759e-09</v>
+        <v>-1.979911961878995e-09</v>
       </c>
       <c r="E61" t="n">
         <v/>
       </c>
       <c r="F61" t="n">
-        <v>-1.980856410782259e-09</v>
+        <v>-2.469594116370732e-09</v>
       </c>
       <c r="G61" t="n">
-        <v>3.660591026386771e-09</v>
+        <v>-1.686333915592883e-09</v>
       </c>
       <c r="H61" t="n">
-        <v>-1.226972717006471e-09</v>
+        <v>5.166715650842472e-10</v>
       </c>
       <c r="I61" t="n">
-        <v>-4.852999155062821e-09</v>
+        <v>4.363169038353214e-09</v>
       </c>
     </row>
     <row r="62">
@@ -3292,22 +3292,22 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>-1.745691894852981e-09</v>
+        <v>-3.006734571242058e-09</v>
       </c>
       <c r="E62" t="n">
-        <v>1.824899206582511e-09</v>
+        <v>-1.293484755111874e-09</v>
       </c>
       <c r="F62" t="n">
         <v/>
       </c>
       <c r="G62" t="n">
-        <v>6.324066054170985e-08</v>
+        <v>-1.036503621464002e-10</v>
       </c>
       <c r="H62" t="n">
-        <v>9.069258237553507e-10</v>
+        <v>-7.079363560173532e-11</v>
       </c>
       <c r="I62" t="n">
-        <v>8.688392942309089e-08</v>
+        <v>-4.280009160108462e-09</v>
       </c>
     </row>
     <row r="63">
@@ -3327,22 +3327,22 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>-1.872722264866878e-09</v>
+        <v>-2.37140812994239e-09</v>
       </c>
       <c r="E63" t="n">
-        <v>-3.637604318368076e-10</v>
+        <v>-1.66277164616956e-09</v>
       </c>
       <c r="F63" t="n">
-        <v>0.001</v>
+        <v/>
       </c>
       <c r="G63" t="n">
-        <v>-6.274759073109553e-11</v>
+        <v>2.474631616580054e-11</v>
       </c>
       <c r="H63" t="n">
-        <v>9.264175801956023e-11</v>
+        <v>9.912123443468411e-11</v>
       </c>
       <c r="I63" t="n">
-        <v>1.398697638894002e-10</v>
+        <v>-3.752435594243041e-09</v>
       </c>
     </row>
     <row r="64">
@@ -3362,22 +3362,22 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>-1.504875110826658e-09</v>
+        <v>-2.941099295140557e-09</v>
       </c>
       <c r="E64" t="n">
-        <v>3.131056020289352e-10</v>
+        <v>-2.714900692003625e-09</v>
       </c>
       <c r="F64" t="n">
         <v/>
       </c>
       <c r="G64" t="n">
-        <v>1.363452441905524e-07</v>
+        <v>1.08485388307175e-08</v>
       </c>
       <c r="H64" t="n">
-        <v>1.623256343772626e-09</v>
+        <v>3.690805166043215e-10</v>
       </c>
       <c r="I64" t="n">
-        <v>1.238323808583114e-07</v>
+        <v>-4.19978197168434e-09</v>
       </c>
     </row>
     <row r="65">
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>-1.952290531625786e-09</v>
+        <v>-2.896262859846645e-09</v>
       </c>
       <c r="E65" t="n">
-        <v>-5.16617473395985e-10</v>
+        <v>-2.67111025918589e-09</v>
       </c>
       <c r="F65" t="n">
         <v/>
       </c>
       <c r="G65" t="n">
-        <v>4.186322014514979e-08</v>
+        <v>7.428433247710508e-10</v>
       </c>
       <c r="H65" t="n">
-        <v>5.255160403959393e-09</v>
+        <v>3.732841428645261e-09</v>
       </c>
       <c r="I65" t="n">
-        <v>8.874011374142123e-08</v>
+        <v>-4.239345845835028e-09</v>
       </c>
     </row>
     <row r="66">
@@ -3432,22 +3432,22 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>-2.779069552186397e-09</v>
+        <v>-2.814177212836546e-09</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.979868921441566e-09</v>
+        <v>-2.583214150060644e-09</v>
       </c>
       <c r="F66" t="n">
         <v/>
       </c>
       <c r="G66" t="n">
-        <v>4.772071924828812e-08</v>
+        <v>-1.198374371476616e-09</v>
       </c>
       <c r="H66" t="n">
-        <v>-1.952766524837365e-09</v>
+        <v>-1.267604839157847e-09</v>
       </c>
       <c r="I66" t="n">
-        <v>2.181651226405789e-07</v>
+        <v>-3.953963536276531e-09</v>
       </c>
     </row>
     <row r="67">
@@ -3467,22 +3467,22 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1.229454251830606e-08</v>
+        <v>-1.420372232647205e-09</v>
       </c>
       <c r="E67" t="n">
-        <v>-5.317416382734693e-10</v>
+        <v>-2.894344535349682e-09</v>
       </c>
       <c r="F67" t="n">
         <v/>
       </c>
       <c r="G67" t="n">
-        <v>6.52222254290488e-08</v>
+        <v>9.599010844613505e-10</v>
       </c>
       <c r="H67" t="n">
-        <v>1.785295172031281e-09</v>
+        <v>2.541327203170191e-10</v>
       </c>
       <c r="I67" t="n">
-        <v>1.220319858619881e-07</v>
+        <v>-4.230868670738822e-09</v>
       </c>
     </row>
     <row r="68">
@@ -3502,22 +3502,22 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>4.292216402203161e-09</v>
+        <v>-1.319105783831055e-09</v>
       </c>
       <c r="E68" t="n">
-        <v>1.720631318323104e-09</v>
+        <v>-1.463471436668816e-09</v>
       </c>
       <c r="F68" t="n">
         <v/>
       </c>
       <c r="G68" t="n">
-        <v>2.613395211827474e-10</v>
+        <v>1.863481154736655e-09</v>
       </c>
       <c r="H68" t="n">
-        <v>2.881077197507161e-09</v>
+        <v>1.360244133280716e-09</v>
       </c>
       <c r="I68" t="n">
-        <v>3.423826563755429e-10</v>
+        <v>1.430022682482054e-08</v>
       </c>
     </row>
     <row r="69">
@@ -3537,22 +3537,22 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1.073273373609578e-09</v>
+        <v>-2.35114710801259e-09</v>
       </c>
       <c r="E69" t="n">
-        <v>-2.20273815444345e-10</v>
+        <v>-2.600949725192328e-09</v>
       </c>
       <c r="F69" t="n">
         <v/>
       </c>
       <c r="G69" t="n">
-        <v>1.371223770350843e-05</v>
+        <v>1.052589714081471e-08</v>
       </c>
       <c r="H69" t="n">
-        <v>8.762284757294595e-10</v>
+        <v>1.869402096105057e-10</v>
       </c>
       <c r="I69" t="n">
-        <v>1.492797583061999e-07</v>
+        <v>-4.276604183935692e-09</v>
       </c>
     </row>
     <row r="70">
@@ -3572,22 +3572,22 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1.134424327497759e-09</v>
+        <v>-2.467210221216759e-09</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.328940074781586e-10</v>
+        <v>-2.702884167795331e-09</v>
       </c>
       <c r="F70" t="n">
         <v/>
       </c>
       <c r="G70" t="n">
-        <v>7.468170822076345e-08</v>
+        <v>1.357101313513734e-09</v>
       </c>
       <c r="H70" t="n">
-        <v>7.81867088320707e-09</v>
+        <v>4.240059346040057e-09</v>
       </c>
       <c r="I70" t="n">
-        <v>1.2896005566614e-07</v>
+        <v>-4.22680382452137e-09</v>
       </c>
     </row>
     <row r="71">
@@ -3607,22 +3607,22 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>-1.894419761689235e-09</v>
+        <v>-1.398213218696677e-09</v>
       </c>
       <c r="E71" t="n">
-        <v>-2.28988041442329e-09</v>
+        <v>-1.919409150286469e-09</v>
       </c>
       <c r="F71" t="n">
         <v/>
       </c>
       <c r="G71" t="n">
-        <v>6.085280237815311e-08</v>
+        <v>-1.120325879850634e-09</v>
       </c>
       <c r="H71" t="n">
-        <v>-2.23491833009329e-09</v>
+        <v>-1.197482311664775e-09</v>
       </c>
       <c r="I71" t="n">
-        <v>2.317715719771417e-07</v>
+        <v>-4.173335497590254e-09</v>
       </c>
     </row>
     <row r="72">
@@ -3642,22 +3642,22 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>9.863845844246635e-08</v>
+        <v>-9.861281308981685e-11</v>
       </c>
       <c r="E72" t="n">
-        <v>1.777700901497717e-09</v>
+        <v>-1.750422398607089e-10</v>
       </c>
       <c r="F72" t="n">
         <v/>
       </c>
       <c r="G72" t="n">
-        <v>9.632056000502654e-08</v>
+        <v>1.089004211036671e-08</v>
       </c>
       <c r="H72" t="n">
-        <v>4.64046097564468e-09</v>
+        <v>4.33097909376469e-09</v>
       </c>
       <c r="I72" t="n">
-        <v>1.785411121299707e-07</v>
+        <v>-3.237598143329788e-09</v>
       </c>
     </row>
     <row r="73">
@@ -3677,22 +3677,22 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2.079842205079652e-08</v>
+        <v>1.770592157937252e-10</v>
       </c>
       <c r="E73" t="n">
-        <v>7.96538013082544e-08</v>
+        <v>1.129631818080343e-09</v>
       </c>
       <c r="F73" t="n">
         <v/>
       </c>
       <c r="G73" t="n">
-        <v>1.365196188793321e-05</v>
+        <v>1.668917398145862e-08</v>
       </c>
       <c r="H73" t="n">
-        <v>1.25729063544515e-08</v>
+        <v>7.382557334846007e-09</v>
       </c>
       <c r="I73" t="n">
-        <v>3.443763987641717e-07</v>
+        <v>1.476647409982282e-08</v>
       </c>
     </row>
     <row r="74">
@@ -3712,22 +3712,22 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>6.160918635437486e-09</v>
+        <v>1.135723064495917e-09</v>
       </c>
       <c r="E74" t="n">
-        <v>3.086527370266555e-09</v>
+        <v>1.98288011984379e-09</v>
       </c>
       <c r="F74" t="n">
-        <v>0.001</v>
+        <v/>
       </c>
       <c r="G74" t="n">
-        <v>0.0009319978586902488</v>
+        <v>2.875354071637594e-08</v>
       </c>
       <c r="H74" t="n">
-        <v>3.951642417071748e-09</v>
+        <v>4.646993253775482e-09</v>
       </c>
       <c r="I74" t="n">
-        <v>2.872893634895279e-07</v>
+        <v>-3.408331322967798e-09</v>
       </c>
     </row>
     <row r="75">
@@ -3747,22 +3747,22 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>6.137765027043009e-09</v>
+        <v>6.254969858357107e-10</v>
       </c>
       <c r="E75" t="n">
-        <v>3.579177414696797e-09</v>
+        <v>1.23795661365556e-09</v>
       </c>
       <c r="F75" t="n">
         <v/>
       </c>
       <c r="G75" t="n">
-        <v>1.217868087663223e-07</v>
+        <v>2.084255318838701e-08</v>
       </c>
       <c r="H75" t="n">
-        <v>4.284357176839737e-08</v>
+        <v>9.128205445910344e-09</v>
       </c>
       <c r="I75" t="n">
-        <v>2.338195088628347e-07</v>
+        <v>-1.404072887172448e-09</v>
       </c>
     </row>
     <row r="76">
@@ -3782,22 +3782,22 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>-1.112212068491488e-10</v>
+        <v>8.56893321471521e-09</v>
       </c>
       <c r="E76" t="n">
-        <v>-7.614872285590392e-10</v>
+        <v>1.201723089575903e-08</v>
       </c>
       <c r="F76" t="n">
         <v/>
       </c>
       <c r="G76" t="n">
-        <v>1.580279614318453e-07</v>
+        <v>1.328856202266619e-09</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.515560220615902e-09</v>
+        <v>3.842314084464483e-10</v>
       </c>
       <c r="I76" t="n">
-        <v>0.297335189195819</v>
+        <v>0.2971837722761086</v>
       </c>
     </row>
     <row r="77">
@@ -3817,22 +3817,22 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>7.099751561689034e-09</v>
+        <v>-1.096259061811609e-09</v>
       </c>
       <c r="E77" t="n">
-        <v>4.223585843626621e-10</v>
+        <v>-2.733159785492757e-09</v>
       </c>
       <c r="F77" t="n">
         <v/>
       </c>
       <c r="G77" t="n">
-        <v>4.398576064322761e-08</v>
+        <v>-1.124748948006895e-09</v>
       </c>
       <c r="H77" t="n">
-        <v>1.400119993204404e-09</v>
+        <v>2.96116034200799e-10</v>
       </c>
       <c r="I77" t="n">
-        <v>9.155510342025651e-08</v>
+        <v>-4.273991627093597e-09</v>
       </c>
     </row>
     <row r="78">
@@ -3852,22 +3852,22 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>-3.400492596824471e-10</v>
+        <v>-2.298170347396506e-09</v>
       </c>
       <c r="E78" t="n">
-        <v>2.59521649562194e-09</v>
+        <v>8.329710092245363e-11</v>
       </c>
       <c r="F78" t="n">
         <v/>
       </c>
       <c r="G78" t="n">
-        <v>6.305167294373498e-08</v>
+        <v>-1.573415039453521e-09</v>
       </c>
       <c r="H78" t="n">
-        <v>4.785021954105795e-11</v>
+        <v>-1.597467809944962e-10</v>
       </c>
       <c r="I78" t="n">
-        <v>7.628855926056622e-08</v>
+        <v>-4.352989377677586e-09</v>
       </c>
     </row>
     <row r="79">
@@ -3887,22 +3887,22 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>-2.682407685965077e-10</v>
+        <v>-7.526182824728784e-10</v>
       </c>
       <c r="E79" t="n">
-        <v>3.478580234394867e-10</v>
+        <v>-7.050311706876024e-10</v>
       </c>
       <c r="F79" t="n">
         <v/>
       </c>
       <c r="G79" t="n">
-        <v>-5.703918321071826e-11</v>
+        <v>-1.414157014693229e-09</v>
       </c>
       <c r="H79" t="n">
-        <v>-2.432198763451754e-10</v>
+        <v>1.914753216272533e-10</v>
       </c>
       <c r="I79" t="n">
-        <v>1.000962648625797e-10</v>
+        <v>-4.069700546292408e-09</v>
       </c>
     </row>
     <row r="80">
@@ -3922,22 +3922,22 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>-1.600047730960581e-11</v>
+        <v>-2.292093169391351e-09</v>
       </c>
       <c r="E80" t="n">
-        <v>7.290908529222786e-10</v>
+        <v>-2.471148816918683e-09</v>
       </c>
       <c r="F80" t="n">
-        <v>0.001</v>
+        <v/>
       </c>
       <c r="G80" t="n">
-        <v>4.58022051818766e-08</v>
+        <v>-1.011848411029799e-09</v>
       </c>
       <c r="H80" t="n">
-        <v>5.641743621192259e-09</v>
+        <v>4.226455795289664e-09</v>
       </c>
       <c r="I80" t="n">
-        <v>9.140268507935354e-08</v>
+        <v>-4.281336396444825e-09</v>
       </c>
     </row>
     <row r="81">
@@ -3957,22 +3957,22 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>-1.341642251187985e-09</v>
+        <v>-3.431944258419521e-10</v>
       </c>
       <c r="E81" t="n">
-        <v>-9.924834815465981e-10</v>
+        <v>-8.141757693707012e-10</v>
       </c>
       <c r="F81" t="n">
         <v/>
       </c>
       <c r="G81" t="n">
-        <v>5.278542258284994e-08</v>
+        <v>-1.464273823722963e-09</v>
       </c>
       <c r="H81" t="n">
-        <v>-1.33964473516346e-09</v>
+        <v>-1.18337608673177e-10</v>
       </c>
       <c r="I81" t="n">
-        <v>4.775855371909564e-07</v>
+        <v>-3.541135359214382e-09</v>
       </c>
     </row>
     <row r="82">
@@ -3992,22 +3992,22 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>4.113238331950654e-09</v>
+        <v>-9.196107077523718e-10</v>
       </c>
       <c r="E82" t="n">
-        <v>-4.786223674119086e-10</v>
+        <v>-2.660130717427557e-09</v>
       </c>
       <c r="F82" t="n">
         <v/>
       </c>
       <c r="G82" t="n">
-        <v>4.210790714969312e-08</v>
+        <v>1.087370363683265e-09</v>
       </c>
       <c r="H82" t="n">
-        <v>5.140523470360305e-11</v>
+        <v>-7.945778176670766e-10</v>
       </c>
       <c r="I82" t="n">
-        <v>9.660640433046509e-08</v>
+        <v>-4.189741041127193e-09</v>
       </c>
     </row>
     <row r="83">
@@ -4027,22 +4027,22 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>2.132975114188877e-10</v>
+        <v>-2.450414302121828e-09</v>
       </c>
       <c r="E83" t="n">
-        <v>2.894348477143323e-09</v>
+        <v>-3.82865613888827e-10</v>
       </c>
       <c r="F83" t="n">
         <v/>
       </c>
       <c r="G83" t="n">
-        <v>7.09857181154781e-08</v>
+        <v>4.331631188006212e-10</v>
       </c>
       <c r="H83" t="n">
-        <v>-3.306292779432547e-11</v>
+        <v>-8.971309222898745e-10</v>
       </c>
       <c r="I83" t="n">
-        <v>9.786628340932694e-08</v>
+        <v>-4.238366078402893e-09</v>
       </c>
     </row>
     <row r="84">
@@ -4062,22 +4062,22 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>2.699419000544611e-10</v>
+        <v>-1.22620802547463e-09</v>
       </c>
       <c r="E84" t="n">
-        <v>4.754389465353677e-10</v>
+        <v>-1.098140501979864e-09</v>
       </c>
       <c r="F84" t="n">
         <v/>
       </c>
       <c r="G84" t="n">
-        <v>-1.456598175712066e-11</v>
+        <v>9.489339988582728e-10</v>
       </c>
       <c r="H84" t="n">
-        <v>-2.323920162380037e-10</v>
+        <v>-6.38519587383946e-10</v>
       </c>
       <c r="I84" t="n">
-        <v>2.150823455617192e-10</v>
+        <v>-2.156693916679092e-09</v>
       </c>
     </row>
     <row r="85">
@@ -4097,22 +4097,22 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>5.136504213286967e-10</v>
+        <v>-2.245975125279964e-09</v>
       </c>
       <c r="E85" t="n">
-        <v>7.059110924852794e-10</v>
+        <v>-2.378005326063422e-09</v>
       </c>
       <c r="F85" t="n">
         <v/>
       </c>
       <c r="G85" t="n">
-        <v>1.633259976889927e-07</v>
+        <v>1.904106994649445e-08</v>
       </c>
       <c r="H85" t="n">
-        <v>2.96466885203505e-10</v>
+        <v>-6.092168246087571e-10</v>
       </c>
       <c r="I85" t="n">
-        <v>1.401174239588963e-07</v>
+        <v>-4.152074274019605e-09</v>
       </c>
     </row>
     <row r="86">
@@ -4132,22 +4132,22 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>-2.062173547855187e-09</v>
+        <v>-2.386627583784983e-09</v>
       </c>
       <c r="E86" t="n">
-        <v>-1.924392772894821e-09</v>
+        <v>-2.556575516006847e-09</v>
       </c>
       <c r="F86" t="n">
-        <v>0.001</v>
+        <v/>
       </c>
       <c r="G86" t="n">
-        <v>4.787018217003626e-08</v>
+        <v>-1.157988580866339e-09</v>
       </c>
       <c r="H86" t="n">
-        <v>-2.354100782048232e-09</v>
+        <v>-1.901727840877254e-09</v>
       </c>
       <c r="I86" t="n">
-        <v>2.363515247202729e-07</v>
+        <v>-3.910029857594637e-09</v>
       </c>
     </row>
     <row r="87">
@@ -4167,22 +4167,22 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>-3.762979549813964e-10</v>
+        <v>2.775755333986797e-10</v>
       </c>
       <c r="E87" t="n">
-        <v>-1.911937498151289e-09</v>
+        <v>-2.462804224295846e-09</v>
       </c>
       <c r="F87" t="n">
-        <v>0.001</v>
+        <v/>
       </c>
       <c r="G87" t="n">
-        <v>4.147064330801392e-08</v>
+        <v>-1.498460872475502e-09</v>
       </c>
       <c r="H87" t="n">
-        <v>-1.952063570869694e-09</v>
+        <v>-1.224005325667442e-09</v>
       </c>
       <c r="I87" t="n">
-        <v>2.902681068454876e-08</v>
+        <v>-4.493336642350608e-09</v>
       </c>
     </row>
     <row r="88">
@@ -4202,22 +4202,22 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>-2.025941547864877e-09</v>
+        <v>-1.377788559462646e-09</v>
       </c>
       <c r="E88" t="n">
-        <v>-1.086703142126318e-09</v>
+        <v>5.326574416549925e-09</v>
       </c>
       <c r="F88" t="n">
         <v/>
       </c>
       <c r="G88" t="n">
-        <v>6.401583952339826e-08</v>
+        <v>-1.859216885007297e-09</v>
       </c>
       <c r="H88" t="n">
-        <v>-2.368266071623073e-09</v>
+        <v>-1.410991898397838e-09</v>
       </c>
       <c r="I88" t="n">
-        <v>2.697058361076645e-08</v>
+        <v>-4.502494846438318e-09</v>
       </c>
     </row>
     <row r="89">
@@ -4237,22 +4237,22 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>-2.421194572994772e-09</v>
+        <v>5.305537102358343e-09</v>
       </c>
       <c r="E89" t="n">
-        <v>-2.180168993424828e-09</v>
+        <v>4.67785998111282e-09</v>
       </c>
       <c r="F89" t="n">
         <v/>
       </c>
       <c r="G89" t="n">
-        <v>-1.269876158269017e-10</v>
+        <v>-1.674201093841155e-09</v>
       </c>
       <c r="H89" t="n">
-        <v>-2.498107614841147e-09</v>
+        <v>-1.137506032272953e-09</v>
       </c>
       <c r="I89" t="n">
-        <v>-5.462084737011546e-10</v>
+        <v>-4.483721649569053e-09</v>
       </c>
     </row>
     <row r="90">
@@ -4272,22 +4272,22 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>-1.109148515322225e-09</v>
+        <v>-3.798368229595357e-10</v>
       </c>
       <c r="E90" t="n">
-        <v>-7.832297744792421e-10</v>
+        <v>-9.292428180709768e-10</v>
       </c>
       <c r="F90" t="n">
         <v/>
       </c>
       <c r="G90" t="n">
-        <v>2.217562957671923e-07</v>
+        <v>2.997872966286006e-09</v>
       </c>
       <c r="H90" t="n">
-        <v>-1.240744899304774e-09</v>
+        <v>-1.578343939380042e-10</v>
       </c>
       <c r="I90" t="n">
-        <v>3.641305460296557e-08</v>
+        <v>-4.482361566005594e-09</v>
       </c>
     </row>
     <row r="91">
@@ -4307,22 +4307,22 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>-2.255943729072871e-09</v>
+        <v>-2.198766479947512e-09</v>
       </c>
       <c r="E91" t="n">
-        <v>-1.986073410691257e-09</v>
+        <v>-2.468531045098816e-09</v>
       </c>
       <c r="F91" t="n">
         <v/>
       </c>
       <c r="G91" t="n">
-        <v>4.014129682833421e-08</v>
+        <v>-1.57810056864678e-09</v>
       </c>
       <c r="H91" t="n">
-        <v>-1.33780843606449e-09</v>
+        <v>-1.705835416470947e-10</v>
       </c>
       <c r="I91" t="n">
-        <v>2.82343554147192e-08</v>
+        <v>-4.495346213699018e-09</v>
       </c>
     </row>
     <row r="92">
@@ -4342,22 +4342,22 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>-5.183601438975077e-10</v>
+        <v>-1.372808119780875e-09</v>
       </c>
       <c r="E92" t="n">
-        <v>1.956937938194429e-08</v>
+        <v>3.824290250718538e-09</v>
       </c>
       <c r="F92" t="n">
-        <v>8.164810384737742e-08</v>
+        <v>8.712501203986712e-10</v>
       </c>
       <c r="G92" t="n">
         <v/>
       </c>
       <c r="H92" t="n">
-        <v>1.993229923602788e-09</v>
+        <v>1.546522837029223e-09</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.78971812537464e-09</v>
+        <v>1.372642300444711e-08</v>
       </c>
     </row>
     <row r="93">
@@ -4377,22 +4377,22 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>-7.211789492545289e-10</v>
+        <v>-1.451455852466549e-09</v>
       </c>
       <c r="E93" t="n">
-        <v>1.002500298038112e-08</v>
+        <v>-1.321444497256705e-09</v>
       </c>
       <c r="F93" t="n">
-        <v>1.256796158359861e-07</v>
+        <v>9.1126143528189e-09</v>
       </c>
       <c r="G93" t="n">
         <v/>
       </c>
       <c r="H93" t="n">
-        <v>1.64287210622647e-09</v>
+        <v>1.248402856633715e-09</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.96991666986629e-09</v>
+        <v>1.2824177575524e-08</v>
       </c>
     </row>
     <row r="94">
@@ -4412,22 +4412,22 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>-6.026713927037175e-10</v>
+        <v>-1.201642493647371e-09</v>
       </c>
       <c r="E94" t="n">
-        <v>2.495720016459382e-10</v>
+        <v>-5.005000830616606e-10</v>
       </c>
       <c r="F94" t="n">
-        <v>-1.03445467977432e-10</v>
+        <v>6.80563647245752e-10</v>
       </c>
       <c r="G94" t="n">
         <v/>
       </c>
       <c r="H94" t="n">
-        <v>1.512593975183118e-09</v>
+        <v>1.41518525324405e-09</v>
       </c>
       <c r="I94" t="n">
-        <v>2.208418522585411e-09</v>
+        <v>-1.406912839160073e-10</v>
       </c>
     </row>
     <row r="95">
@@ -4447,22 +4447,22 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>-6.16278432830002e-10</v>
+        <v>-1.146368645236566e-09</v>
       </c>
       <c r="E95" t="n">
-        <v>6.127439483402009e-09</v>
+        <v>-9.965111488335904e-10</v>
       </c>
       <c r="F95" t="n">
-        <v>4.338213471896067e-08</v>
+        <v>9.484091361406949e-10</v>
       </c>
       <c r="G95" t="n">
         <v/>
       </c>
       <c r="H95" t="n">
-        <v>6.889438132592771e-09</v>
+        <v>5.966685397636603e-09</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.54366648389213e-09</v>
+        <v>1.398104993610254e-08</v>
       </c>
     </row>
     <row r="96">
@@ -4482,22 +4482,22 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>-2.529038527030753e-09</v>
+        <v>-1.917462245481084e-09</v>
       </c>
       <c r="E96" t="n">
-        <v>2.386936900606571e-09</v>
+        <v>-1.819729772127485e-09</v>
       </c>
       <c r="F96" t="n">
-        <v>4.381473806586608e-08</v>
+        <v>-1.499745893266711e-09</v>
       </c>
       <c r="G96" t="n">
         <v/>
       </c>
       <c r="H96" t="n">
-        <v>-1.960766693680716e-09</v>
+        <v>-1.821170812878708e-09</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.463180564800296e-09</v>
+        <v>2.597644435250489e-08</v>
       </c>
     </row>
     <row r="97">
@@ -4517,22 +4517,22 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>5.320194612735689e-09</v>
+        <v>2.975355993156841e-09</v>
       </c>
       <c r="E97" t="n">
-        <v>4.115781021468726e-09</v>
+        <v>-1.989267607303447e-09</v>
       </c>
       <c r="F97" t="n">
-        <v>5.409934881009621e-08</v>
+        <v>-1.531403270130566e-10</v>
       </c>
       <c r="G97" t="n">
         <v/>
       </c>
       <c r="H97" t="n">
-        <v>1.432697660630277e-09</v>
+        <v>1.033519210289649e-09</v>
       </c>
       <c r="I97" t="n">
-        <v>-1.926265247495201e-09</v>
+        <v>1.171528663228201e-08</v>
       </c>
     </row>
     <row r="98">
@@ -4552,22 +4552,22 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>3.918678349545901e-09</v>
+        <v>1.056916636533889e-10</v>
       </c>
       <c r="E98" t="n">
-        <v>1.128414211950307e-08</v>
+        <v>-1.728958645184725e-09</v>
       </c>
       <c r="F98" t="n">
-        <v>1.377456619989336e-05</v>
+        <v>1.424530688168483e-08</v>
       </c>
       <c r="G98" t="n">
         <v/>
       </c>
       <c r="H98" t="n">
-        <v>4.019029590646689e-09</v>
+        <v>3.242313641255555e-09</v>
       </c>
       <c r="I98" t="n">
-        <v>-6.909325537360562e-10</v>
+        <v>1.316944428888345e-08</v>
       </c>
     </row>
     <row r="99">
@@ -4587,22 +4587,22 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1.873891926548022e-10</v>
+        <v>-1.549479149545577e-10</v>
       </c>
       <c r="E99" t="n">
-        <v>-5.129212838954303e-10</v>
+        <v>-1.443435677698002e-09</v>
       </c>
       <c r="F99" t="n">
-        <v>7.480076549161823e-11</v>
+        <v>-3.189712040411439e-10</v>
       </c>
       <c r="G99" t="n">
         <v/>
       </c>
       <c r="H99" t="n">
-        <v>-1.27667437335904e-10</v>
+        <v>-1.181081226212414e-10</v>
       </c>
       <c r="I99" t="n">
-        <v>-9.549582599189155e-10</v>
+        <v>-8.24631815588668e-11</v>
       </c>
     </row>
     <row r="100">
@@ -4622,22 +4622,22 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1.409807999132426e-09</v>
+        <v>2.905864788338664e-11</v>
       </c>
       <c r="E100" t="n">
-        <v>4.939626621498417e-09</v>
+        <v>-1.7695588241189e-09</v>
       </c>
       <c r="F100" t="n">
-        <v>6.312445915277064e-08</v>
+        <v>3.17896531336727e-10</v>
       </c>
       <c r="G100" t="n">
         <v/>
       </c>
       <c r="H100" t="n">
-        <v>5.354648602623331e-09</v>
+        <v>4.553432135537482e-09</v>
       </c>
       <c r="I100" t="n">
-        <v>-1.70323238868451e-09</v>
+        <v>1.343401157509621e-08</v>
       </c>
     </row>
     <row r="101">
@@ -4657,22 +4657,22 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>-2.375168908821785e-09</v>
+        <v>-1.023277564457805e-09</v>
       </c>
       <c r="E101" t="n">
-        <v>8.514140407399728e-10</v>
+        <v>-2.071182470074444e-09</v>
       </c>
       <c r="F101" t="n">
-        <v>4.647381532392683e-08</v>
+        <v>-1.810785315951356e-09</v>
       </c>
       <c r="G101" t="n">
         <v/>
       </c>
       <c r="H101" t="n">
-        <v>-2.470723037566912e-09</v>
+        <v>-2.260160680492505e-09</v>
       </c>
       <c r="I101" t="n">
-        <v>-2.537405309961709e-09</v>
+        <v>4.568521891160057e-08</v>
       </c>
     </row>
     <row r="102">
@@ -4692,22 +4692,22 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>4.47801917193882e-09</v>
+        <v>2.793159876726274e-09</v>
       </c>
       <c r="E102" t="n">
-        <v>6.364008273301359e-09</v>
+        <v>-1.396531954190227e-09</v>
       </c>
       <c r="F102" t="n">
-        <v>4.24661516543112e-08</v>
+        <v>-1.338766347282757e-09</v>
       </c>
       <c r="G102" t="n">
         <v/>
       </c>
       <c r="H102" t="n">
-        <v>1.074691742417854e-09</v>
+        <v>7.317387142509799e-10</v>
       </c>
       <c r="I102" t="n">
-        <v>-2.080753145869011e-09</v>
+        <v>1.216084693948156e-08</v>
       </c>
     </row>
     <row r="103">
@@ -4727,22 +4727,22 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>4.15076880524667e-09</v>
+        <v>1.462610325158458e-10</v>
       </c>
       <c r="E103" t="n">
-        <v>6.228031569108658e-08</v>
+        <v>5.981466358087928e-09</v>
       </c>
       <c r="F103" t="n">
-        <v>1.112863571062352e-07</v>
+        <v>-5.415627007410532e-10</v>
       </c>
       <c r="G103" t="n">
         <v/>
       </c>
       <c r="H103" t="n">
-        <v>3.8950411969137e-09</v>
+        <v>3.135337582889104e-09</v>
       </c>
       <c r="I103" t="n">
-        <v>-6.68185534970537e-10</v>
+        <v>1.436391099573472e-08</v>
       </c>
     </row>
     <row r="104">
@@ -4762,22 +4762,22 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>3.315204444717707e-10</v>
+        <v>-1.664825857931729e-10</v>
       </c>
       <c r="E104" t="n">
-        <v>1.347058467252457e-10</v>
+        <v>-5.287745793419761e-10</v>
       </c>
       <c r="F104" t="n">
-        <v>-6.137739052331144e-11</v>
+        <v>-1.333367182076194e-09</v>
       </c>
       <c r="G104" t="n">
         <v/>
       </c>
       <c r="H104" t="n">
-        <v>4.318318567769453e-11</v>
+        <v>3.815283517324391e-11</v>
       </c>
       <c r="I104" t="n">
-        <v>-6.502513410356457e-10</v>
+        <v>-8.106297883557205e-11</v>
       </c>
     </row>
     <row r="105">
@@ -4797,22 +4797,22 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1.849617233781028e-09</v>
+        <v>1.062398686361232e-10</v>
       </c>
       <c r="E105" t="n">
-        <v>8.507250704791194e-09</v>
+        <v>-9.947952465916094e-10</v>
       </c>
       <c r="F105" t="n">
-        <v>4.873575545860146e-08</v>
+        <v>-9.213089867977598e-10</v>
       </c>
       <c r="G105" t="n">
         <v/>
       </c>
       <c r="H105" t="n">
-        <v>6.610773298968857e-09</v>
+        <v>5.66061858933117e-09</v>
       </c>
       <c r="I105" t="n">
-        <v>-1.405951910711573e-09</v>
+        <v>1.372856518531237e-08</v>
       </c>
     </row>
     <row r="106">
@@ -4832,22 +4832,22 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>-2.232824886247034e-09</v>
+        <v>-1.160968274595283e-09</v>
       </c>
       <c r="E106" t="n">
-        <v>2.649098053763585e-09</v>
+        <v>-1.658495424843546e-09</v>
       </c>
       <c r="F106" t="n">
-        <v>4.856822215647089e-08</v>
+        <v>-2.305282331394661e-09</v>
       </c>
       <c r="G106" t="n">
         <v/>
       </c>
       <c r="H106" t="n">
-        <v>-2.413791425135983e-09</v>
+        <v>-2.211492744959172e-09</v>
       </c>
       <c r="I106" t="n">
-        <v>-2.383335661330935e-09</v>
+        <v>3.763473833251223e-08</v>
       </c>
     </row>
     <row r="107">
@@ -4867,22 +4867,22 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>9.718450175264301e-08</v>
+        <v>6.678404679073179e-09</v>
       </c>
       <c r="E107" t="n">
-        <v>1.89516609537534e-08</v>
+        <v>4.815448452225004e-09</v>
       </c>
       <c r="F107" t="n">
-        <v>1.088182734631975e-07</v>
+        <v>1.217599931671123e-08</v>
       </c>
       <c r="G107" t="n">
         <v/>
       </c>
       <c r="H107" t="n">
-        <v>8.935916504950029e-09</v>
+        <v>8.146515380283683e-09</v>
       </c>
       <c r="I107" t="n">
-        <v>5.116402806164358e-09</v>
+        <v>1.684016755551754e-08</v>
       </c>
     </row>
     <row r="108">
@@ -4902,22 +4902,22 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>5.163279439471101e-09</v>
+        <v>3.848522757723354e-09</v>
       </c>
       <c r="E108" t="n">
-        <v>0.1427161906423875</v>
+        <v>8.520501605622857e-09</v>
       </c>
       <c r="F108" t="n">
-        <v>1.354941568586203e-05</v>
+        <v>1.191472093867184e-08</v>
       </c>
       <c r="G108" t="n">
         <v/>
       </c>
       <c r="H108" t="n">
-        <v>4.126780757091951e-09</v>
+        <v>3.684774670730315e-09</v>
       </c>
       <c r="I108" t="n">
-        <v>4.075533950757324e-10</v>
+        <v>2.298367248832592e-08</v>
       </c>
     </row>
     <row r="109">
@@ -4937,22 +4937,22 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>5.441042482995439e-09</v>
+        <v>3.673226321218236e-09</v>
       </c>
       <c r="E109" t="n">
-        <v>4.173351283904709e-08</v>
+        <v>6.043666186936107e-09</v>
       </c>
       <c r="F109" t="n">
-        <v>0.0009239831649658084</v>
+        <v>2.862048600807251e-08</v>
       </c>
       <c r="G109" t="n">
         <v/>
       </c>
       <c r="H109" t="n">
-        <v>4.872422980796698e-09</v>
+        <v>4.377390266029749e-09</v>
       </c>
       <c r="I109" t="n">
-        <v>9.044286785229355e-10</v>
+        <v>2.054687191674862e-08</v>
       </c>
     </row>
     <row r="110">
@@ -4972,22 +4972,22 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>8.620445038867386e-09</v>
+        <v>5.801512473377212e-09</v>
       </c>
       <c r="E110" t="n">
-        <v>2.247530306209932e-08</v>
+        <v>8.668459604308573e-09</v>
       </c>
       <c r="F110" t="n">
-        <v>1.283414884840549e-07</v>
+        <v>1.984263210507551e-08</v>
       </c>
       <c r="G110" t="n">
         <v/>
       </c>
       <c r="H110" t="n">
-        <v>4.576054528083475e-08</v>
+        <v>5.723411015061107e-08</v>
       </c>
       <c r="I110" t="n">
-        <v>6.440327785723372e-09</v>
+        <v>2.037285783855224e-08</v>
       </c>
     </row>
     <row r="111">
@@ -5007,22 +5007,22 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>3.027167298854047e-10</v>
+        <v>5.247436664673758e-09</v>
       </c>
       <c r="E111" t="n">
-        <v>9.394761539141645e-09</v>
+        <v>1.249358181727175e-08</v>
       </c>
       <c r="F111" t="n">
-        <v>1.244089996598997e-07</v>
+        <v>3.989201298280016e-09</v>
       </c>
       <c r="G111" t="n">
         <v/>
       </c>
       <c r="H111" t="n">
-        <v>-1.076990490422684e-10</v>
+        <v>-1.592429327694601e-10</v>
       </c>
       <c r="I111" t="n">
-        <v>0.1646363579105326</v>
+        <v>0.1600914382460162</v>
       </c>
     </row>
     <row r="112">
@@ -5042,22 +5042,22 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>5.806605525399817e-09</v>
+        <v>4.506340721902843e-09</v>
       </c>
       <c r="E112" t="n">
-        <v>5.804342958023104e-09</v>
+        <v>-9.742273699261399e-10</v>
       </c>
       <c r="F112" t="n">
-        <v>4.136154714011575e-08</v>
+        <v>7.304549848854326e-10</v>
       </c>
       <c r="G112" t="n">
         <v/>
       </c>
       <c r="H112" t="n">
-        <v>5.415582190905876e-10</v>
+        <v>2.271981673558009e-10</v>
       </c>
       <c r="I112" t="n">
-        <v>-1.485973177328646e-09</v>
+        <v>1.435089289755784e-08</v>
       </c>
     </row>
     <row r="113">
@@ -5077,22 +5077,22 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1.862922280801448e-09</v>
+        <v>8.166149144785729e-11</v>
       </c>
       <c r="E113" t="n">
-        <v>2.355265757789159e-08</v>
+        <v>7.042484287988413e-09</v>
       </c>
       <c r="F113" t="n">
-        <v>8.926307237374403e-08</v>
+        <v>1.346767270836817e-09</v>
       </c>
       <c r="G113" t="n">
         <v/>
       </c>
       <c r="H113" t="n">
-        <v>5.331644266667461e-10</v>
+        <v>2.326266734311091e-10</v>
       </c>
       <c r="I113" t="n">
-        <v>-1.49153265263732e-09</v>
+        <v>1.649523517320378e-08</v>
       </c>
     </row>
     <row r="114">
@@ -5112,22 +5112,22 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>2.217612189331901e-09</v>
+        <v>2.674571473234962e-11</v>
       </c>
       <c r="E114" t="n">
-        <v>1.304451568644584e-08</v>
+        <v>-8.915345937137916e-10</v>
       </c>
       <c r="F114" t="n">
-        <v>1.578323331759992e-07</v>
+        <v>1.729790918813132e-08</v>
       </c>
       <c r="G114" t="n">
         <v/>
       </c>
       <c r="H114" t="n">
-        <v>9.404171734610423e-10</v>
+        <v>5.6995913748533e-10</v>
       </c>
       <c r="I114" t="n">
-        <v>-1.172809867857551e-09</v>
+        <v>1.481207430593327e-08</v>
       </c>
     </row>
     <row r="115">
@@ -5147,22 +5147,22 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1.374415488568261e-09</v>
+        <v>5.149981413210654e-10</v>
       </c>
       <c r="E115" t="n">
-        <v>3.780186751296611e-10</v>
+        <v>2.438124401759054e-10</v>
       </c>
       <c r="F115" t="n">
-        <v>-7.379482605494779e-11</v>
+        <v>1.073928158880187e-09</v>
       </c>
       <c r="G115" t="n">
         <v/>
       </c>
       <c r="H115" t="n">
-        <v>5.820909674641964e-11</v>
+        <v>1.40864507714285e-11</v>
       </c>
       <c r="I115" t="n">
-        <v>3.283124206443669e-09</v>
+        <v>4.185247373096297e-11</v>
       </c>
     </row>
     <row r="116">
@@ -5182,22 +5182,22 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>-2.030516485664822e-09</v>
+        <v>-1.279209445806915e-09</v>
       </c>
       <c r="E116" t="n">
-        <v>2.318960703035882e-09</v>
+        <v>-1.807613869602072e-09</v>
       </c>
       <c r="F116" t="n">
-        <v>4.267003711472212e-08</v>
+        <v>-1.555012451406149e-09</v>
       </c>
       <c r="G116" t="n">
         <v/>
       </c>
       <c r="H116" t="n">
-        <v>-2.404694035077416e-09</v>
+        <v>-2.219707199520318e-09</v>
       </c>
       <c r="I116" t="n">
-        <v>-1.537497731686834e-09</v>
+        <v>2.69572765510236e-08</v>
       </c>
     </row>
     <row r="117">
@@ -5217,22 +5217,22 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>-1.064863159356301e-09</v>
+        <v>1.485601843641997e-09</v>
       </c>
       <c r="E117" t="n">
-        <v>3.122537541249488e-09</v>
+        <v>-1.269316771422373e-09</v>
       </c>
       <c r="F117" t="n">
-        <v>4.767582593247449e-08</v>
+        <v>-1.30145626398258e-09</v>
       </c>
       <c r="G117" t="n">
         <v/>
       </c>
       <c r="H117" t="n">
-        <v>-1.907496683164269e-09</v>
+        <v>-1.783345940515209e-09</v>
       </c>
       <c r="I117" t="n">
-        <v>-4.181474554199748e-09</v>
+        <v>1.130020955983422e-08</v>
       </c>
     </row>
     <row r="118">
@@ -5252,22 +5252,22 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>-2.197709136346068e-09</v>
+        <v>-7.717563365468147e-10</v>
       </c>
       <c r="E118" t="n">
-        <v>7.832422199557155e-09</v>
+        <v>6.543079296968539e-09</v>
       </c>
       <c r="F118" t="n">
-        <v>1.067254047559174e-07</v>
+        <v>-1.310869063172224e-09</v>
       </c>
       <c r="G118" t="n">
         <v/>
       </c>
       <c r="H118" t="n">
-        <v>-2.340230925277868e-09</v>
+        <v>-2.148265580110823e-09</v>
       </c>
       <c r="I118" t="n">
-        <v>-4.270910837357531e-09</v>
+        <v>1.635225656460006e-08</v>
       </c>
     </row>
     <row r="119">
@@ -5287,22 +5287,22 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>-2.279053303283574e-09</v>
+        <v>-6.359979297654283e-10</v>
       </c>
       <c r="E119" t="n">
-        <v>3.848204944498801e-09</v>
+        <v>-6.988592976872198e-10</v>
       </c>
       <c r="F119" t="n">
-        <v>1.039014076323047e-07</v>
+        <v>1.036942035826524e-09</v>
       </c>
       <c r="G119" t="n">
         <v/>
       </c>
       <c r="H119" t="n">
-        <v>-2.264843852288855e-09</v>
+        <v>-2.083710924719075e-09</v>
       </c>
       <c r="I119" t="n">
-        <v>-4.259247180838187e-09</v>
+        <v>1.64544303870861e-08</v>
       </c>
     </row>
     <row r="120">
@@ -5322,22 +5322,22 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>-1.290653638370529e-09</v>
+        <v>7.285772779950409e-10</v>
       </c>
       <c r="E120" t="n">
-        <v>-2.508691769970244e-10</v>
+        <v>1.856330542627738e-09</v>
       </c>
       <c r="F120" t="n">
-        <v>1.638168360038084e-10</v>
+        <v>-3.126597679993399e-10</v>
       </c>
       <c r="G120" t="n">
         <v/>
       </c>
       <c r="H120" t="n">
-        <v>-1.486119716057817e-09</v>
+        <v>-1.34931926838781e-09</v>
       </c>
       <c r="I120" t="n">
-        <v>-3.867410840394706e-09</v>
+        <v>1.09258892104907e-10</v>
       </c>
     </row>
     <row r="121">
@@ -5357,22 +5357,22 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>-2.032552840534961e-09</v>
+        <v>-9.399057210237705e-10</v>
       </c>
       <c r="E121" t="n">
-        <v>3.048875728469714e-09</v>
+        <v>-1.294673489750582e-09</v>
       </c>
       <c r="F121" t="n">
-        <v>4.746935716404455e-08</v>
+        <v>-1.293581634454934e-09</v>
       </c>
       <c r="G121" t="n">
         <v/>
       </c>
       <c r="H121" t="n">
-        <v>-1.358983063714605e-09</v>
+        <v>-1.307132656887345e-09</v>
       </c>
       <c r="I121" t="n">
-        <v>-4.192166227074119e-09</v>
+        <v>1.114084686639524e-08</v>
       </c>
     </row>
     <row r="122">
@@ -5392,22 +5392,22 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>-1.455344022728378e-09</v>
+        <v>-6.432138147414263e-10</v>
       </c>
       <c r="E122" t="n">
-        <v>5.631820195857999e-09</v>
+        <v>3.916482686566843e-09</v>
       </c>
       <c r="F122" t="n">
-        <v>1.772016983651563e-09</v>
+        <v>2.434496902310195e-10</v>
       </c>
       <c r="G122" t="n">
-        <v>1.742731117832767e-09</v>
+        <v>1.311800070638349e-09</v>
       </c>
       <c r="H122" t="n">
         <v/>
       </c>
       <c r="I122" t="n">
-        <v>1.247842281375548e-08</v>
+        <v>4.464462342498877e-08</v>
       </c>
     </row>
     <row r="123">
@@ -5427,22 +5427,22 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>-1.647622088017149e-09</v>
+        <v>-7.76116152698768e-10</v>
       </c>
       <c r="E123" t="n">
-        <v>1.32893120507574e-09</v>
+        <v>-7.6592697107617e-12</v>
       </c>
       <c r="F123" t="n">
-        <v>4.184507621201882e-09</v>
+        <v>3.192120669584956e-09</v>
       </c>
       <c r="G123" t="n">
-        <v>1.358631711665265e-09</v>
+        <v>9.84061713292058e-10</v>
       </c>
       <c r="H123" t="n">
         <v/>
       </c>
       <c r="I123" t="n">
-        <v>1.155480714324914e-08</v>
+        <v>4.262607018742098e-08</v>
       </c>
     </row>
     <row r="124">
@@ -5462,22 +5462,22 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>-1.337034013363635e-09</v>
+        <v>-4.892218343740192e-10</v>
       </c>
       <c r="E124" t="n">
-        <v>1.315964884175658e-09</v>
+        <v>2.495558648970137e-10</v>
       </c>
       <c r="F124" t="n">
-        <v>1.436313069612246e-09</v>
+        <v>3.221626352753976e-10</v>
       </c>
       <c r="G124" t="n">
-        <v>8.49516350450629e-09</v>
+        <v>7.423512679779261e-09</v>
       </c>
       <c r="H124" t="n">
         <v/>
       </c>
       <c r="I124" t="n">
-        <v>1.764102513869354e-08</v>
+        <v>5.447003048119466e-08</v>
       </c>
     </row>
     <row r="125">
@@ -5497,22 +5497,22 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>-1.096817994175544e-09</v>
+        <v>-7.823004662586015e-10</v>
       </c>
       <c r="E125" t="n">
-        <v>6.57746945551153e-10</v>
+        <v>3.937858486325639e-10</v>
       </c>
       <c r="F125" t="n">
-        <v>7.429173236504551e-10</v>
+        <v>5.075663700057076e-10</v>
       </c>
       <c r="G125" t="n">
-        <v>8.865286879746762e-10</v>
+        <v>8.097043125004291e-10</v>
       </c>
       <c r="H125" t="n">
         <v/>
       </c>
       <c r="I125" t="n">
-        <v>5.188388487249271e-10</v>
+        <v>7.751849455028833e-11</v>
       </c>
     </row>
     <row r="126">
@@ -5532,22 +5532,22 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>-2.999959928576881e-09</v>
+        <v>-1.712301984138619e-09</v>
       </c>
       <c r="E126" t="n">
-        <v>-1.924778168774927e-09</v>
+        <v>-9.959508247419466e-10</v>
       </c>
       <c r="F126" t="n">
-        <v>-1.932531934846038e-09</v>
+        <v>-1.234197075731738e-09</v>
       </c>
       <c r="G126" t="n">
-        <v>-1.714791935452241e-09</v>
+        <v>-1.607791422135039e-09</v>
       </c>
       <c r="H126" t="n">
         <v/>
       </c>
       <c r="I126" t="n">
-        <v>3.715923456152328e-08</v>
+        <v>9.97194843265279e-08</v>
       </c>
     </row>
     <row r="127">
@@ -5567,22 +5567,22 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>5.076279783950605e-09</v>
+        <v>5.760434318311836e-09</v>
       </c>
       <c r="E127" t="n">
-        <v>-4.984840439777241e-10</v>
+        <v>-6.857138933541964e-10</v>
       </c>
       <c r="F127" t="n">
-        <v>9.910250971518049e-10</v>
+        <v>-5.082328028153581e-11</v>
       </c>
       <c r="G127" t="n">
-        <v>2.315658545179192e-09</v>
+        <v>1.811095191443161e-09</v>
       </c>
       <c r="H127" t="n">
         <v/>
       </c>
       <c r="I127" t="n">
-        <v>1.525449529088985e-08</v>
+        <v>4.333150893237832e-08</v>
       </c>
     </row>
     <row r="128">
@@ -5602,22 +5602,22 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>2.072226909952989e-09</v>
+        <v>1.821309979961016e-09</v>
       </c>
       <c r="E128" t="n">
-        <v>1.122110105961279e-09</v>
+        <v>-1.206819195105995e-10</v>
       </c>
       <c r="F128" t="n">
-        <v>1.124002376049579e-08</v>
+        <v>5.709545365606157e-09</v>
       </c>
       <c r="G128" t="n">
-        <v>4.293011529925872e-09</v>
+        <v>3.472391787829547e-09</v>
       </c>
       <c r="H128" t="n">
         <v/>
       </c>
       <c r="I128" t="n">
-        <v>2.037025082835692e-08</v>
+        <v>5.011056409242719e-08</v>
       </c>
     </row>
     <row r="129">
@@ -5637,22 +5637,22 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>-6.167121367642002e-10</v>
+        <v>5.502675908623226e-10</v>
       </c>
       <c r="E129" t="n">
-        <v>-1.022875792455938e-09</v>
+        <v>-6.644374785923073e-10</v>
       </c>
       <c r="F129" t="n">
-        <v>1.180909993519207e-10</v>
+        <v>-1.650607379111766e-10</v>
       </c>
       <c r="G129" t="n">
-        <v>4.056000639191653e-09</v>
+        <v>3.463139190730569e-09</v>
       </c>
       <c r="H129" t="n">
         <v/>
       </c>
       <c r="I129" t="n">
-        <v>1.345316730219646e-08</v>
+        <v>5.152027240663986e-08</v>
       </c>
     </row>
     <row r="130">
@@ -5672,22 +5672,22 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1.024957016863462e-09</v>
+        <v>5.478628622017613e-10</v>
       </c>
       <c r="E130" t="n">
-        <v>-6.779924291947858e-10</v>
+        <v>-4.178644942573858e-10</v>
       </c>
       <c r="F130" t="n">
-        <v>6.881120229139615e-10</v>
+        <v>3.241911549197963e-10</v>
       </c>
       <c r="G130" t="n">
-        <v>8.735297079746314e-10</v>
+        <v>8.018668305287168e-10</v>
       </c>
       <c r="H130" t="n">
         <v/>
       </c>
       <c r="I130" t="n">
-        <v>6.260991339354284e-10</v>
+        <v>7.381203585514672e-11</v>
       </c>
     </row>
     <row r="131">
@@ -5707,22 +5707,22 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>-2.8559572649411e-09</v>
+        <v>-1.149772546814717e-09</v>
       </c>
       <c r="E131" t="n">
-        <v>-2.711820730369872e-09</v>
+        <v>-1.343639271419796e-09</v>
       </c>
       <c r="F131" t="n">
-        <v>-2.381262341924954e-09</v>
+        <v>-1.330940560698663e-09</v>
       </c>
       <c r="G131" t="n">
-        <v>-2.179455218327687e-09</v>
+        <v>-2.003929497035251e-09</v>
       </c>
       <c r="H131" t="n">
         <v/>
       </c>
       <c r="I131" t="n">
-        <v>2.169755852449848e-08</v>
+        <v>1.110766791538907e-07</v>
       </c>
     </row>
     <row r="132">
@@ -5742,22 +5742,22 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>4.251069815647419e-09</v>
+        <v>5.372924701074706e-09</v>
       </c>
       <c r="E132" t="n">
-        <v>7.406743646222817e-10</v>
+        <v>-1.627587349160656e-10</v>
       </c>
       <c r="F132" t="n">
-        <v>-5.236368442034786e-10</v>
+        <v>-7.139159163500724e-10</v>
       </c>
       <c r="G132" t="n">
-        <v>1.960804817629001e-09</v>
+        <v>1.513276020224146e-09</v>
       </c>
       <c r="H132" t="n">
         <v/>
       </c>
       <c r="I132" t="n">
-        <v>1.431488818434651e-08</v>
+        <v>4.292106247451883e-08</v>
       </c>
     </row>
     <row r="133">
@@ -5777,22 +5777,22 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>2.490697964000077e-09</v>
+        <v>1.980039578893122e-09</v>
       </c>
       <c r="E133" t="n">
-        <v>1.399805692325011e-08</v>
+        <v>5.951712428185419e-09</v>
       </c>
       <c r="F133" t="n">
-        <v>1.451079620707007e-09</v>
+        <v>5.815925428800805e-11</v>
       </c>
       <c r="G133" t="n">
-        <v>4.46145336494794e-09</v>
+        <v>3.627582208988273e-09</v>
       </c>
       <c r="H133" t="n">
         <v/>
       </c>
       <c r="I133" t="n">
-        <v>2.085869131603478e-08</v>
+        <v>5.157324833491014e-08</v>
       </c>
     </row>
     <row r="134">
@@ -5812,22 +5812,22 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>-3.982868379571935e-10</v>
+        <v>6.702567023921975e-10</v>
       </c>
       <c r="E134" t="n">
-        <v>3.056832289198463e-10</v>
+        <v>-4.318176466329874e-11</v>
       </c>
       <c r="F134" t="n">
-        <v>-7.869509121785706e-10</v>
+        <v>-6.954393079431083e-10</v>
       </c>
       <c r="G134" t="n">
-        <v>4.776494095842812e-09</v>
+        <v>4.110713572770374e-09</v>
       </c>
       <c r="H134" t="n">
         <v/>
       </c>
       <c r="I134" t="n">
-        <v>1.450482917718643e-08</v>
+        <v>5.212995586392094e-08</v>
       </c>
     </row>
     <row r="135">
@@ -5847,22 +5847,22 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1.711000141714675e-09</v>
+        <v>7.714707711851117e-10</v>
       </c>
       <c r="E135" t="n">
-        <v>1.047427219791475e-09</v>
+        <v>3.85698572828749e-10</v>
       </c>
       <c r="F135" t="n">
-        <v>-3.200887172569846e-10</v>
+        <v>-2.454994953101367e-10</v>
       </c>
       <c r="G135" t="n">
-        <v>1.319185715658186e-09</v>
+        <v>1.217631897807604e-09</v>
       </c>
       <c r="H135" t="n">
         <v/>
       </c>
       <c r="I135" t="n">
-        <v>8.159266634592474e-10</v>
+        <v>8.610070426859833e-11</v>
       </c>
     </row>
     <row r="136">
@@ -5882,22 +5882,22 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>-2.752461024733442e-09</v>
+        <v>-1.153528770538517e-09</v>
       </c>
       <c r="E136" t="n">
-        <v>-2.221088758476061e-09</v>
+        <v>-1.04160440244498e-09</v>
       </c>
       <c r="F136" t="n">
-        <v>-2.598824597259993e-09</v>
+        <v>-1.687262847495002e-09</v>
       </c>
       <c r="G136" t="n">
-        <v>-2.096710838180109e-09</v>
+        <v>-1.932479938011194e-09</v>
       </c>
       <c r="H136" t="n">
         <v/>
       </c>
       <c r="I136" t="n">
-        <v>2.494837912972528e-08</v>
+        <v>1.029959676299075e-07</v>
       </c>
     </row>
     <row r="137">
@@ -5917,22 +5917,22 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>5.326127597837684e-09</v>
+        <v>6.792871008053848e-09</v>
       </c>
       <c r="E137" t="n">
-        <v>1.737707126797457e-09</v>
+        <v>3.049081233762697e-10</v>
       </c>
       <c r="F137" t="n">
-        <v>1.673500809258403e-09</v>
+        <v>3.54208371654206e-10</v>
       </c>
       <c r="G137" t="n">
-        <v>4.925838395010888e-11</v>
+        <v>-1.760031307519838e-10</v>
       </c>
       <c r="H137" t="n">
         <v/>
       </c>
       <c r="I137" t="n">
-        <v>1.239915931453239e-08</v>
+        <v>4.05308172461781e-08</v>
       </c>
     </row>
     <row r="138">
@@ -5952,22 +5952,22 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>-7.096233761559455e-10</v>
+        <v>5.567602611217546e-10</v>
       </c>
       <c r="E138" t="n">
-        <v>3.853778748298355e-09</v>
+        <v>4.334248368833377e-09</v>
       </c>
       <c r="F138" t="n">
-        <v>8.570646513941095e-10</v>
+        <v>1.763791935859783e-10</v>
       </c>
       <c r="G138" t="n">
-        <v>-9.728051603851206e-10</v>
+        <v>-1.025780924716933e-09</v>
       </c>
       <c r="H138" t="n">
         <v/>
       </c>
       <c r="I138" t="n">
-        <v>8.227415607832414e-09</v>
+        <v>4.019888123766506e-08</v>
       </c>
     </row>
     <row r="139">
@@ -5987,22 +5987,22 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>-6.497889829366556e-10</v>
+        <v>5.735733657842513e-10</v>
       </c>
       <c r="E139" t="n">
-        <v>1.163710235466328e-09</v>
+        <v>2.613584335314133e-10</v>
       </c>
       <c r="F139" t="n">
-        <v>3.546939516172125e-09</v>
+        <v>3.560862715324673e-09</v>
       </c>
       <c r="G139" t="n">
-        <v>-8.634217929087307e-10</v>
+        <v>-9.361694472348619e-10</v>
       </c>
       <c r="H139" t="n">
         <v/>
       </c>
       <c r="I139" t="n">
-        <v>8.636893377350368e-09</v>
+        <v>3.9621302389098e-08</v>
       </c>
     </row>
     <row r="140">
@@ -6022,22 +6022,22 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>9.345244389094555e-10</v>
+        <v>7.145995188242167e-10</v>
       </c>
       <c r="E140" t="n">
-        <v>1.112549616068346e-09</v>
+        <v>7.017700387415997e-10</v>
       </c>
       <c r="F140" t="n">
-        <v>1.054972330674204e-09</v>
+        <v>7.436477911192176e-10</v>
       </c>
       <c r="G140" t="n">
-        <v>-8.014688162181161e-10</v>
+        <v>-7.699491172105753e-10</v>
       </c>
       <c r="H140" t="n">
         <v/>
       </c>
       <c r="I140" t="n">
-        <v>2.488189025776145e-10</v>
+        <v>4.383372001374e-11</v>
       </c>
     </row>
     <row r="141">
@@ -6057,22 +6057,22 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>-2.021380160307685e-09</v>
+        <v>1.123953763538535e-10</v>
       </c>
       <c r="E141" t="n">
-        <v>-1.185153322001479e-09</v>
+        <v>5.314463095201416e-10</v>
       </c>
       <c r="F141" t="n">
-        <v>-1.238419481173668e-09</v>
+        <v>-1.81530707104155e-11</v>
       </c>
       <c r="G141" t="n">
-        <v>-1.896686794969576e-09</v>
+        <v>-1.788979252549416e-09</v>
       </c>
       <c r="H141" t="n">
         <v/>
       </c>
       <c r="I141" t="n">
-        <v>6.942279406286224e-08</v>
+        <v>2.255401579379831e-07</v>
       </c>
     </row>
     <row r="142">
@@ -6092,22 +6092,22 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>2.738284934719351e-06</v>
+        <v>6.735640262067493e-09</v>
       </c>
       <c r="E142" t="n">
-        <v>6.929366579648039e-09</v>
+        <v>5.145795191577333e-09</v>
       </c>
       <c r="F142" t="n">
-        <v>5.995968007522377e-09</v>
+        <v>4.734739990056663e-09</v>
       </c>
       <c r="G142" t="n">
-        <v>8.294613608102659e-09</v>
+        <v>7.507716404136862e-09</v>
       </c>
       <c r="H142" t="n">
         <v/>
       </c>
       <c r="I142" t="n">
-        <v>3.747399107779688e-08</v>
+        <v>9.584998698336834e-08</v>
       </c>
     </row>
     <row r="143">
@@ -6127,22 +6127,22 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>7.274248987642358e-09</v>
+        <v>6.917385306432077e-09</v>
       </c>
       <c r="E143" t="n">
-        <v>8.732399842451955e-08</v>
+        <v>5.044016755687302e-09</v>
       </c>
       <c r="F143" t="n">
-        <v>8.762016944948419e-09</v>
+        <v>5.347361640668183e-09</v>
       </c>
       <c r="G143" t="n">
-        <v>6.500797425346892e-09</v>
+        <v>5.809926307379959e-09</v>
       </c>
       <c r="H143" t="n">
         <v/>
       </c>
       <c r="I143" t="n">
-        <v>3.04172084640501e-08</v>
+        <v>1.005127988745428e-07</v>
       </c>
     </row>
     <row r="144">
@@ -6162,22 +6162,22 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>8.445403538517495e-09</v>
+        <v>7.227696196446564e-09</v>
       </c>
       <c r="E144" t="n">
-        <v>1.243377028525282e-08</v>
+        <v>5.820780017311241e-09</v>
       </c>
       <c r="F144" t="n">
-        <v>4.303237885912553e-08</v>
+        <v>8.834941124060868e-09</v>
       </c>
       <c r="G144" t="n">
-        <v>7.94977171881402e-09</v>
+        <v>7.147541461601413e-09</v>
       </c>
       <c r="H144" t="n">
         <v/>
       </c>
       <c r="I144" t="n">
-        <v>3.542172242734508e-08</v>
+        <v>9.780521617332916e-08</v>
       </c>
     </row>
     <row r="145">
@@ -6197,22 +6197,22 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>7.321292460020358e-09</v>
+        <v>8.133173848633184e-09</v>
       </c>
       <c r="E145" t="n">
-        <v>7.351491726310172e-09</v>
+        <v>6.461649071013892e-09</v>
       </c>
       <c r="F145" t="n">
-        <v>6.424964841892185e-09</v>
+        <v>5.674805104966121e-09</v>
       </c>
       <c r="G145" t="n">
-        <v>4.711773864345821e-08</v>
+        <v>5.874916462620603e-08</v>
       </c>
       <c r="H145" t="n">
         <v/>
       </c>
       <c r="I145" t="n">
-        <v>5.272734699892715e-08</v>
+        <v>1.622127216588375e-07</v>
       </c>
     </row>
     <row r="146">
@@ -6232,22 +6232,22 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>-1.668530421838129e-09</v>
+        <v>4.145631395138966e-10</v>
       </c>
       <c r="E146" t="n">
-        <v>-9.987907768552429e-10</v>
+        <v>7.935075842072311e-10</v>
       </c>
       <c r="F146" t="n">
-        <v>-1.163116261182929e-09</v>
+        <v>8.934874779234127e-11</v>
       </c>
       <c r="G146" t="n">
-        <v>-1.04531565801628e-09</v>
+        <v>-9.936692585973113e-10</v>
       </c>
       <c r="H146" t="n">
         <v/>
       </c>
       <c r="I146" t="n">
-        <v>0.2312284873984679</v>
+        <v>1.09283492517703e-06</v>
       </c>
     </row>
     <row r="147">
@@ -6267,22 +6267,22 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>-1.817840930079067e-09</v>
+        <v>5.058222594944497e-10</v>
       </c>
       <c r="E147" t="n">
-        <v>-1.899578965227379e-09</v>
+        <v>-1.046016381047561e-09</v>
       </c>
       <c r="F147" t="n">
-        <v>-1.933634006381282e-09</v>
+        <v>-1.293106875691571e-09</v>
       </c>
       <c r="G147" t="n">
-        <v>-1.852072268334337e-09</v>
+        <v>-1.734797130977185e-09</v>
       </c>
       <c r="H147" t="n">
         <v/>
       </c>
       <c r="I147" t="n">
-        <v>-9.020536137163251e-11</v>
+        <v>1.890435127825149e-08</v>
       </c>
     </row>
     <row r="148">
@@ -6302,22 +6302,22 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>-2.899185243794787e-09</v>
+        <v>-1.280869127189324e-09</v>
       </c>
       <c r="E148" t="n">
-        <v>-1.556881336993756e-09</v>
+        <v>8.459574703788626e-10</v>
       </c>
       <c r="F148" t="n">
-        <v>-2.186188662520972e-09</v>
+        <v>-1.338437837148019e-09</v>
       </c>
       <c r="G148" t="n">
-        <v>-2.373431543798665e-09</v>
+        <v>-2.178964158792842e-09</v>
       </c>
       <c r="H148" t="n">
         <v/>
       </c>
       <c r="I148" t="n">
-        <v>-5.801671220640834e-10</v>
+        <v>1.918328474906008e-08</v>
       </c>
     </row>
     <row r="149">
@@ -6337,22 +6337,22 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>-2.918199318797059e-09</v>
+        <v>-1.205300406394359e-09</v>
       </c>
       <c r="E149" t="n">
-        <v>-2.177768853658337e-09</v>
+        <v>-8.639311626514448e-10</v>
       </c>
       <c r="F149" t="n">
-        <v>-1.730058626277137e-09</v>
+        <v>1.194885715997366e-10</v>
       </c>
       <c r="G149" t="n">
-        <v>-2.316766011598648e-09</v>
+        <v>-2.131101753708933e-09</v>
       </c>
       <c r="H149" t="n">
         <v/>
       </c>
       <c r="I149" t="n">
-        <v>-5.40959305319524e-10</v>
+        <v>1.95431821652636e-08</v>
       </c>
     </row>
     <row r="150">
@@ -6372,22 +6372,22 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>-2.089399954554731e-09</v>
+        <v>-1.142767775369133e-10</v>
       </c>
       <c r="E150" t="n">
-        <v>-1.267671642305711e-09</v>
+        <v>1.301455813192956e-10</v>
       </c>
       <c r="F150" t="n">
-        <v>-1.298360172346126e-09</v>
+        <v>-3.195226934117675e-10</v>
       </c>
       <c r="G150" t="n">
-        <v>-1.129961934565409e-10</v>
+        <v>-2.226852077349188e-10</v>
       </c>
       <c r="H150" t="n">
         <v/>
       </c>
       <c r="I150" t="n">
-        <v>6.087126481066881e-10</v>
+        <v>2.560201212034267e-08</v>
       </c>
     </row>
     <row r="151">
@@ -6407,22 +6407,22 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>-2.573663353445867e-09</v>
+        <v>-1.394020734045165e-09</v>
       </c>
       <c r="E151" t="n">
-        <v>-2.139730958316385e-09</v>
+        <v>-1.122396112861699e-09</v>
       </c>
       <c r="F151" t="n">
-        <v>-2.165913148670359e-09</v>
+        <v>-1.349625972195988e-09</v>
       </c>
       <c r="G151" t="n">
-        <v>-2.277694427757469e-09</v>
+        <v>-2.059301117114401e-09</v>
       </c>
       <c r="H151" t="n">
         <v/>
       </c>
       <c r="I151" t="n">
-        <v>-2.272563459538408e-09</v>
+        <v>-3.944373278071634e-10</v>
       </c>
     </row>
     <row r="152">
@@ -6442,19 +6442,19 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>-2.032403299142022e-09</v>
+        <v>-2.725409677095825e-09</v>
       </c>
       <c r="E152" t="n">
-        <v>1.767612463424781e-08</v>
+        <v>3.931172871990564e-09</v>
       </c>
       <c r="F152" t="n">
-        <v>3.336673502202328e-08</v>
+        <v>4.810499659033917e-08</v>
       </c>
       <c r="G152" t="n">
-        <v>1.502704496615528e-08</v>
+        <v>3.098976918237641e-10</v>
       </c>
       <c r="H152" t="n">
-        <v>1.903086493160659e-08</v>
+        <v>4.584076905185927e-08</v>
       </c>
       <c r="I152" t="n">
         <v/>
@@ -6477,19 +6477,19 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>-2.129842580682795e-09</v>
+        <v>-2.798477961214551e-09</v>
       </c>
       <c r="E153" t="n">
-        <v>5.333806610294974e-09</v>
+        <v>-5.396572568030606e-10</v>
       </c>
       <c r="F153" t="n">
-        <v>7.410262478772521e-08</v>
+        <v>1.064181126782305e-07</v>
       </c>
       <c r="G153" t="n">
-        <v>1.425393254482902e-08</v>
+        <v>9.213788276468459e-11</v>
       </c>
       <c r="H153" t="n">
-        <v>1.809329086825625e-08</v>
+        <v>4.428500518825596e-08</v>
       </c>
       <c r="I153" t="n">
         <v/>
@@ -6512,19 +6512,19 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>-2.252424716349819e-09</v>
+        <v>-2.663042762024431e-09</v>
       </c>
       <c r="E154" t="n">
-        <v>2.899381400347561e-09</v>
+        <v>-7.866733803086277e-10</v>
       </c>
       <c r="F154" t="n">
-        <v>2.255234845307749e-08</v>
+        <v>5.190655274374108e-08</v>
       </c>
       <c r="G154" t="n">
-        <v>3.043637379810863e-08</v>
+        <v>2.821021528521352e-09</v>
       </c>
       <c r="H154" t="n">
-        <v>1.639337795721073e-08</v>
+        <v>4.537462739399831e-08</v>
       </c>
       <c r="I154" t="n">
         <v/>
@@ -6547,19 +6547,19 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>-2.232627656428985e-09</v>
+        <v>-2.553278186498949e-09</v>
       </c>
       <c r="E155" t="n">
-        <v>4.291747753510944e-09</v>
+        <v>-4.350856067166044e-11</v>
       </c>
       <c r="F155" t="n">
-        <v>3.014872226077786e-08</v>
+        <v>5.465369883419838e-08</v>
       </c>
       <c r="G155" t="n">
-        <v>1.518291815508653e-08</v>
+        <v>9.055825594493076e-10</v>
       </c>
       <c r="H155" t="n">
-        <v>5.179118816277243e-08</v>
+        <v>1.249920402890275e-07</v>
       </c>
       <c r="I155" t="n">
         <v/>
@@ -6582,19 +6582,19 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>-1.736432517391601e-09</v>
+        <v>-2.040265648918789e-09</v>
       </c>
       <c r="E156" t="n">
-        <v>5.434663371294545e-11</v>
+        <v>-4.957858382024996e-10</v>
       </c>
       <c r="F156" t="n">
-        <v>3.550788696197008e-10</v>
+        <v>-8.810310925619145e-11</v>
       </c>
       <c r="G156" t="n">
-        <v>2.080946813497527e-10</v>
+        <v>7.927488516367521e-11</v>
       </c>
       <c r="H156" t="n">
-        <v>3.541021140091031e-10</v>
+        <v>-2.729622452226373e-11</v>
       </c>
       <c r="I156" t="n">
         <v/>
@@ -6617,19 +6617,19 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1.158121509762415e-09</v>
+        <v>-1.480904822334046e-09</v>
       </c>
       <c r="E157" t="n">
-        <v>5.447087535615825e-10</v>
+        <v>-1.53839835506924e-09</v>
       </c>
       <c r="F157" t="n">
-        <v>2.051376305618043e-08</v>
+        <v>4.942899369310478e-08</v>
       </c>
       <c r="G157" t="n">
-        <v>1.505615216864946e-08</v>
+        <v>2.686007419871061e-10</v>
       </c>
       <c r="H157" t="n">
-        <v>1.64184529312397e-08</v>
+        <v>4.603885415291957e-08</v>
       </c>
       <c r="I157" t="n">
         <v/>
@@ -6652,19 +6652,19 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1.280971807305458e-09</v>
+        <v>-2.418215431464324e-09</v>
       </c>
       <c r="E158" t="n">
-        <v>3.209967312540542e-09</v>
+        <v>-9.966326510194791e-10</v>
       </c>
       <c r="F158" t="n">
-        <v>1.192369118656629e-07</v>
+        <v>1.28080971548768e-07</v>
       </c>
       <c r="G158" t="n">
-        <v>2.544674857692036e-08</v>
+        <v>1.439677677757391e-09</v>
       </c>
       <c r="H158" t="n">
-        <v>2.668272744384879e-08</v>
+        <v>5.261688536916477e-08</v>
       </c>
       <c r="I158" t="n">
         <v/>
@@ -6687,19 +6687,19 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>-1.665677374181226e-09</v>
+        <v>-2.165483453310369e-09</v>
       </c>
       <c r="E159" t="n">
-        <v>-3.100360284076275e-10</v>
+        <v>-1.846752692420917e-09</v>
       </c>
       <c r="F159" t="n">
-        <v>1.501147594186441e-08</v>
+        <v>6.192191495046305e-08</v>
       </c>
       <c r="G159" t="n">
-        <v>2.346717804859302e-08</v>
+        <v>1.201194616760053e-09</v>
       </c>
       <c r="H159" t="n">
-        <v>1.149374681663834e-08</v>
+        <v>4.453246282096602e-08</v>
       </c>
       <c r="I159" t="n">
         <v/>
@@ -6722,19 +6722,19 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>-8.634323357184824e-10</v>
+        <v>-2.200372580633368e-09</v>
       </c>
       <c r="E160" t="n">
-        <v>9.91416518130039e-10</v>
+        <v>-1.256420432259943e-09</v>
       </c>
       <c r="F160" t="n">
-        <v>2.421704419544731e-08</v>
+        <v>5.785074990385732e-08</v>
       </c>
       <c r="G160" t="n">
-        <v>1.70940022868162e-08</v>
+        <v>7.483553304653863e-10</v>
       </c>
       <c r="H160" t="n">
-        <v>4.379151616097291e-08</v>
+        <v>1.279846366214507e-07</v>
       </c>
       <c r="I160" t="n">
         <v/>
@@ -6757,19 +6757,19 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>-1.201127907546831e-09</v>
+        <v>2.639000090396419e-10</v>
       </c>
       <c r="E161" t="n">
-        <v>-1.744049870248517e-09</v>
+        <v>-1.587070836711551e-09</v>
       </c>
       <c r="F161" t="n">
-        <v>-1.866944629577314e-10</v>
+        <v>3.835165226011077e-11</v>
       </c>
       <c r="G161" t="n">
-        <v>-1.842491205785316e-10</v>
+        <v>-6.168321899660703e-10</v>
       </c>
       <c r="H161" t="n">
-        <v>-2.156724945170604e-10</v>
+        <v>4.900596348978904e-12</v>
       </c>
       <c r="I161" t="n">
         <v/>
@@ -6792,19 +6792,19 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>4.829392746757358e-10</v>
+        <v>-1.369348564995226e-09</v>
       </c>
       <c r="E162" t="n">
-        <v>2.32941775012522e-09</v>
+        <v>-8.553592962881245e-10</v>
       </c>
       <c r="F162" t="n">
-        <v>1.292046833603061e-08</v>
+        <v>4.616524524037534e-08</v>
       </c>
       <c r="G162" t="n">
-        <v>1.412898427904756e-08</v>
+        <v>9.471107959360529e-11</v>
       </c>
       <c r="H162" t="n">
-        <v>1.516819705206819e-08</v>
+        <v>4.520772113111941e-08</v>
       </c>
       <c r="I162" t="n">
         <v/>
@@ -6827,19 +6827,19 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1.022214971781588e-09</v>
+        <v>-2.29090357938658e-09</v>
       </c>
       <c r="E163" t="n">
-        <v>3.253087090757025e-08</v>
+        <v>6.440798138900145e-09</v>
       </c>
       <c r="F163" t="n">
-        <v>2.129553029420654e-08</v>
+        <v>4.805147357109437e-08</v>
       </c>
       <c r="G163" t="n">
-        <v>2.496481814447618e-08</v>
+        <v>1.473864084313441e-09</v>
       </c>
       <c r="H163" t="n">
-        <v>2.550120177439684e-08</v>
+        <v>5.291534410089298e-08</v>
       </c>
       <c r="I163" t="n">
         <v/>
@@ -6862,19 +6862,19 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>-1.7034221257792e-09</v>
+        <v>-2.168211008015792e-09</v>
       </c>
       <c r="E164" t="n">
-        <v>1.287900391649948e-09</v>
+        <v>-1.199686328822965e-09</v>
       </c>
       <c r="F164" t="n">
-        <v>1.073280011035347e-08</v>
+        <v>5.47239137172411e-08</v>
       </c>
       <c r="G164" t="n">
-        <v>2.493311680919391e-08</v>
+        <v>1.413482542426403e-09</v>
       </c>
       <c r="H164" t="n">
-        <v>1.191127911396604e-08</v>
+        <v>4.443222191575076e-08</v>
       </c>
       <c r="I164" t="n">
         <v/>
@@ -6897,19 +6897,19 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>-7.585125873031171e-10</v>
+        <v>-2.163042635071823e-09</v>
       </c>
       <c r="E165" t="n">
-        <v>4.005171535193175e-09</v>
+        <v>-1.546447398257844e-10</v>
       </c>
       <c r="F165" t="n">
-        <v>1.629679217717537e-08</v>
+        <v>5.229553001199944e-08</v>
       </c>
       <c r="G165" t="n">
-        <v>1.86218504805099e-08</v>
+        <v>1.067945111707436e-09</v>
       </c>
       <c r="H165" t="n">
-        <v>5.077507844581744e-08</v>
+        <v>1.336837455032581e-07</v>
       </c>
       <c r="I165" t="n">
         <v/>
@@ -6932,19 +6932,19 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>-7.734806929931303e-10</v>
+        <v>-3.781486070950294e-10</v>
       </c>
       <c r="E166" t="n">
-        <v>-8.229469663148191e-10</v>
+        <v>-8.952632464498909e-10</v>
       </c>
       <c r="F166" t="n">
-        <v>-5.208327727356517e-10</v>
+        <v>-2.752843352197467e-11</v>
       </c>
       <c r="G166" t="n">
-        <v>-3.493209619044678e-11</v>
+        <v>-5.628184658797468e-10</v>
       </c>
       <c r="H166" t="n">
-        <v>-1.409643173280763e-10</v>
+        <v>-1.360188580623321e-11</v>
       </c>
       <c r="I166" t="n">
         <v/>
@@ -6967,19 +6967,19 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1.81335598477625e-09</v>
+        <v>-1.13997639332961e-09</v>
       </c>
       <c r="E167" t="n">
-        <v>6.393164288836821e-09</v>
+        <v>1.5387423088344e-10</v>
       </c>
       <c r="F167" t="n">
-        <v>3.32680827244836e-08</v>
+        <v>5.148438307208908e-08</v>
       </c>
       <c r="G167" t="n">
-        <v>1.002803707212494e-08</v>
+        <v>-3.508523691223201e-10</v>
       </c>
       <c r="H167" t="n">
-        <v>2.167364304052293e-08</v>
+        <v>5.23769082616374e-08</v>
       </c>
       <c r="I167" t="n">
         <v/>
@@ -7002,19 +7002,19 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>-1.085806881599645e-09</v>
+        <v>-2.041886272126136e-09</v>
       </c>
       <c r="E168" t="n">
-        <v>2.172282507867616e-08</v>
+        <v>5.354386182621736e-09</v>
       </c>
       <c r="F168" t="n">
-        <v>3.237679541900981e-08</v>
+        <v>6.039454938304426e-08</v>
       </c>
       <c r="G168" t="n">
-        <v>8.476325324017535e-09</v>
+        <v>-9.012174434422569e-10</v>
       </c>
       <c r="H168" t="n">
-        <v>1.657930531385096e-08</v>
+        <v>5.15700532449171e-08</v>
       </c>
       <c r="I168" t="n">
         <v/>
@@ -7037,19 +7037,19 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>-8.806026309810213e-10</v>
+        <v>-2.201417079981653e-09</v>
       </c>
       <c r="E169" t="n">
-        <v>7.51248898542122e-09</v>
+        <v>-1.396058917572817e-11</v>
       </c>
       <c r="F169" t="n">
-        <v>9.379791804541147e-08</v>
+        <v>1.691918526435142e-07</v>
       </c>
       <c r="G169" t="n">
-        <v>8.960005714751333e-09</v>
+        <v>-8.301537369312879e-10</v>
       </c>
       <c r="H169" t="n">
-        <v>1.796151767129085e-08</v>
+        <v>5.114077818793836e-08</v>
       </c>
       <c r="I169" t="n">
         <v/>
@@ -7072,19 +7072,19 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>-6.438758984504269e-10</v>
+        <v>-1.965821709564114e-09</v>
       </c>
       <c r="E170" t="n">
-        <v>7.587285570543237e-09</v>
+        <v>7.861113507749869e-10</v>
       </c>
       <c r="F170" t="n">
-        <v>3.947648366365977e-08</v>
+        <v>6.187468447715729e-08</v>
       </c>
       <c r="G170" t="n">
-        <v>1.061314399444003e-08</v>
+        <v>-8.652935826941284e-11</v>
       </c>
       <c r="H170" t="n">
-        <v>7.156573085229242e-08</v>
+        <v>1.802670669480082e-07</v>
       </c>
       <c r="I170" t="n">
         <v/>
@@ -7107,19 +7107,19 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>4.373026584376374e-09</v>
+        <v>3.355560949980505e-09</v>
       </c>
       <c r="E171" t="n">
-        <v>3.284757044495856e-09</v>
+        <v>3.245355073669349e-09</v>
       </c>
       <c r="F171" t="n">
-        <v>1.057425966193469e-09</v>
+        <v>7.840893165600501e-11</v>
       </c>
       <c r="G171" t="n">
-        <v>1.978286374220296e-10</v>
+        <v>7.862899056941057e-10</v>
       </c>
       <c r="H171" t="n">
-        <v>1.222008236085705e-09</v>
+        <v>1.638450052990861e-10</v>
       </c>
       <c r="I171" t="n">
         <v/>
@@ -7142,19 +7142,19 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>4.533906778286426e-10</v>
+        <v>-1.143712949515118e-09</v>
       </c>
       <c r="E172" t="n">
-        <v>3.65885592371942e-09</v>
+        <v>-2.553714153392774e-10</v>
       </c>
       <c r="F172" t="n">
-        <v>2.495271725801673e-08</v>
+        <v>5.201481610274091e-08</v>
       </c>
       <c r="G172" t="n">
-        <v>1.474382674239393e-08</v>
+        <v>7.963929776939664e-10</v>
       </c>
       <c r="H172" t="n">
-        <v>1.112127776194064e-08</v>
+        <v>3.130643691826532e-08</v>
       </c>
       <c r="I172" t="n">
         <v/>
@@ -7177,19 +7177,19 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>-8.003015616336624e-10</v>
+        <v>-2.267781154906592e-09</v>
       </c>
       <c r="E173" t="n">
-        <v>2.040981757519638e-08</v>
+        <v>5.435762286403507e-09</v>
       </c>
       <c r="F173" t="n">
-        <v>3.329816775810746e-08</v>
+        <v>5.361608357533347e-08</v>
       </c>
       <c r="G173" t="n">
-        <v>1.645434275178426e-08</v>
+        <v>7.007884504785836e-10</v>
       </c>
       <c r="H173" t="n">
-        <v>1.168965025615409e-08</v>
+        <v>3.149336329547044e-08</v>
       </c>
       <c r="I173" t="n">
         <v/>
@@ -7212,19 +7212,19 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>-5.416894134723947e-10</v>
+        <v>-2.423276104048103e-09</v>
       </c>
       <c r="E174" t="n">
-        <v>7.572330954892676e-09</v>
+        <v>4.130648379610997e-11</v>
       </c>
       <c r="F174" t="n">
-        <v>1.083362169424156e-07</v>
+        <v>1.240340316468963e-07</v>
       </c>
       <c r="G174" t="n">
-        <v>1.821023765391217e-08</v>
+        <v>9.403430695486914e-10</v>
       </c>
       <c r="H174" t="n">
-        <v>1.28317595841167e-08</v>
+        <v>3.1350312687475e-08</v>
       </c>
       <c r="I174" t="n">
         <v/>
@@ -7247,19 +7247,19 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>-1.373864635337235e-09</v>
+        <v>-2.088160442953857e-09</v>
       </c>
       <c r="E175" t="n">
-        <v>2.947223301710365e-09</v>
+        <v>-5.297741839638034e-10</v>
       </c>
       <c r="F175" t="n">
-        <v>2.164079207878566e-08</v>
+        <v>6.084464336394714e-08</v>
       </c>
       <c r="G175" t="n">
-        <v>3.244793256587914e-08</v>
+        <v>3.504083514130914e-09</v>
       </c>
       <c r="H175" t="n">
-        <v>9.98234824379292e-09</v>
+        <v>3.147373482972519e-08</v>
       </c>
       <c r="I175" t="n">
         <v/>
@@ -7282,19 +7282,19 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>-6.619852544139881e-10</v>
+        <v>-1.614736898688981e-09</v>
       </c>
       <c r="E176" t="n">
-        <v>-9.644738943514241e-11</v>
+        <v>-6.184650378810795e-10</v>
       </c>
       <c r="F176" t="n">
-        <v>2.446063305402782e-10</v>
+        <v>-9.186436938107897e-11</v>
       </c>
       <c r="G176" t="n">
-        <v>1.776585553581917e-10</v>
+        <v>-3.274888670730833e-11</v>
       </c>
       <c r="H176" t="n">
-        <v>-3.569454460994488e-10</v>
+        <v>-2.236019786414635e-10</v>
       </c>
       <c r="I176" t="n">
         <v/>
@@ -7317,19 +7317,19 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>2.434868782624165e-08</v>
+        <v>4.862122166689372e-09</v>
       </c>
       <c r="E177" t="n">
-        <v>1.732926031556638e-08</v>
+        <v>4.560802672101587e-09</v>
       </c>
       <c r="F177" t="n">
-        <v>6.887047801826525e-08</v>
+        <v>6.190181962894089e-08</v>
       </c>
       <c r="G177" t="n">
-        <v>2.115136388323455e-08</v>
+        <v>3.399062117395234e-09</v>
       </c>
       <c r="H177" t="n">
-        <v>4.128125324819508e-08</v>
+        <v>8.55352252346686e-08</v>
       </c>
       <c r="I177" t="n">
         <v/>
@@ -7352,19 +7352,19 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1.605152470607654e-09</v>
+        <v>1.3249044048327e-09</v>
       </c>
       <c r="E178" t="n">
-        <v>0.1762865432838912</v>
+        <v>0.1566183088873287</v>
       </c>
       <c r="F178" t="n">
-        <v>5.84552721028005e-08</v>
+        <v>8.715387862865258e-08</v>
       </c>
       <c r="G178" t="n">
-        <v>1.595730077387749e-08</v>
+        <v>1.457663393757469e-09</v>
       </c>
       <c r="H178" t="n">
-        <v>2.536974858225301e-08</v>
+        <v>8.935820986771752e-08</v>
       </c>
       <c r="I178" t="n">
         <v/>
@@ -7387,19 +7387,19 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>5.409016585507953e-10</v>
+        <v>1.471732182339955e-09</v>
       </c>
       <c r="E179" t="n">
-        <v>1.570181975433406e-08</v>
+        <v>4.844788541395546e-09</v>
       </c>
       <c r="F179" t="n">
-        <v>0.288777211500485</v>
+        <v>0.2843982985961488</v>
       </c>
       <c r="G179" t="n">
-        <v>1.574291312640028e-08</v>
+        <v>1.845179458517242e-09</v>
       </c>
       <c r="H179" t="n">
-        <v>2.764549650147608e-08</v>
+        <v>9.68324493323684e-08</v>
       </c>
       <c r="I179" t="n">
         <v/>
@@ -7422,19 +7422,19 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1.05714860095149e-08</v>
+        <v>5.091357161372147e-09</v>
       </c>
       <c r="E180" t="n">
-        <v>3.967605190304901e-08</v>
+        <v>1.388865283435153e-08</v>
       </c>
       <c r="F180" t="n">
-        <v>1.300392892347071e-07</v>
+        <v>1.136268537320826e-07</v>
       </c>
       <c r="G180" t="n">
-        <v>0.1658458472407109</v>
+        <v>0.1612824141388331</v>
       </c>
       <c r="H180" t="n">
-        <v>7.922145298235415e-08</v>
+        <v>1.697056046873607e-07</v>
       </c>
       <c r="I180" t="n">
         <v/>
@@ -7457,19 +7457,19 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1.573998291444293e-09</v>
+        <v>-6.551524384945303e-10</v>
       </c>
       <c r="E181" t="n">
-        <v>1.761615898893408e-08</v>
+        <v>4.741920515960747e-09</v>
       </c>
       <c r="F181" t="n">
-        <v>7.833345807079393e-08</v>
+        <v>6.374304709231522e-08</v>
       </c>
       <c r="G181" t="n">
-        <v>2.052208335235545e-08</v>
+        <v>3.273505482327726e-09</v>
       </c>
       <c r="H181" t="n">
-        <v>0.2313016763191874</v>
+        <v>1.002046768577321e-06</v>
       </c>
       <c r="I181" t="n">
         <v/>
@@ -8772,7 +8772,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>0.02705212216824293</v>
+        <v>0.1149584</v>
       </c>
     </row>
   </sheetData>

--- a/6node_spain/output_all.xlsx
+++ b/6node_spain/output_all.xlsx
@@ -459,19 +459,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9578470287923996</v>
+        <v>0.2467214034409604</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3221590341322774</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1.246580118475737</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1.495862458951819e-07</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6566439605498499</v>
+        <v>0.4934428023807521</v>
       </c>
     </row>
   </sheetData>
@@ -558,16 +558,16 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.730986718142402e-09</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1.456339744773028</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3.383646089117478e-09</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8681712543787548</v>
+        <v>0.8224046618651433</v>
       </c>
     </row>
     <row r="4">
@@ -580,19 +580,19 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>4.730986718142402e-09</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6212937859852071</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>4.606944385398174e-09</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2262353465376618</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>1.456339744773028</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6212937859852071</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -630,10 +630,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>3.383646089117478e-09</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>4.606944385398174e-09</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -655,10 +655,10 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8681712543787548</v>
+        <v>0.8224046618651433</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2262353465376618</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -757,13 +757,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1534299501887093</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1746730418292456</v>
+        <v>0.1654650941974328</v>
       </c>
     </row>
     <row r="4">
@@ -782,13 +782,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1733978752903481</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2973389475499364</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -801,10 +801,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.151844318605133</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1719042554221162</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -813,7 +813,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.340884573432845e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -838,7 +838,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2.262885172577001e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -851,16 +851,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1762869203706064</v>
+        <v>0.1669938951199662</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2887757409130483</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-9.765202091394087e-08</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.244895449532436e-07</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -953,13 +953,13 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8465700498112907</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8253269581707544</v>
+        <v>0.8345349058025672</v>
       </c>
     </row>
     <row r="4">
@@ -978,13 +978,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8266021247096519</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7026610524500636</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -997,10 +997,10 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.848155681394867</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8280957445778838</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -1009,7 +1009,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1.000000334088457</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1034,7 +1034,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9999997737114827</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1047,16 +1047,16 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8237130796293936</v>
+        <v>0.8330061048800338</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7112242590869517</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.000000097652021</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1.000000224489545</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1128,19 +1128,19 @@
         <v/>
       </c>
       <c r="E2" t="n">
-        <v>7.560598347843168e-08</v>
+        <v>9.511605729066415e-11</v>
       </c>
       <c r="F2" t="n">
-        <v>7.763840499173934e-11</v>
+        <v>7.600570597868428e-12</v>
       </c>
       <c r="G2" t="n">
-        <v>4.379501547472486e-11</v>
+        <v>7.819013270903964e-11</v>
       </c>
       <c r="H2" t="n">
-        <v>5.66264659606161e-11</v>
+        <v>1.545090071243787e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>4.571628630120552e-11</v>
+        <v>1.276984759702831e-10</v>
       </c>
     </row>
     <row r="3">
@@ -1163,19 +1163,19 @@
         <v/>
       </c>
       <c r="E3" t="n">
-        <v>-1.125663630957453e-11</v>
+        <v>2.58776238079935e-11</v>
       </c>
       <c r="F3" t="n">
-        <v>8.908687990641655e-10</v>
+        <v>-2.469142535212143e-11</v>
       </c>
       <c r="G3" t="n">
-        <v>3.904998390353364e-11</v>
+        <v>9.863810589696852e-11</v>
       </c>
       <c r="H3" t="n">
-        <v>5.169568230200894e-11</v>
+        <v>1.442727105387217e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.05282352161317e-11</v>
+        <v>6.604222351635129e-11</v>
       </c>
     </row>
     <row r="4">
@@ -1198,19 +1198,19 @@
         <v/>
       </c>
       <c r="E4" t="n">
-        <v>1.252831523919708e-11</v>
+        <v>4.005196597571373e-11</v>
       </c>
       <c r="F4" t="n">
-        <v>5.835544513288241e-11</v>
+        <v>3.806657682500966e-11</v>
       </c>
       <c r="G4" t="n">
-        <v>5.683790122258441e-10</v>
+        <v>-6.992928067992941e-11</v>
       </c>
       <c r="H4" t="n">
-        <v>6.243808922603441e-11</v>
+        <v>1.591957250398907e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>7.005943254151098e-11</v>
+        <v>7.28654697534176e-11</v>
       </c>
     </row>
     <row r="5">
@@ -1233,19 +1233,19 @@
         <v/>
       </c>
       <c r="E5" t="n">
-        <v>5.453615218882986e-11</v>
+        <v>3.203079430918896e-11</v>
       </c>
       <c r="F5" t="n">
-        <v>1.609596564589608e-11</v>
+        <v>2.071822685123497e-11</v>
       </c>
       <c r="G5" t="n">
-        <v>3.856395641354052e-11</v>
+        <v>1.02476676920911e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>3.938334607885137e-09</v>
+        <v>-6.391364630794719e-11</v>
       </c>
       <c r="I5" t="n">
-        <v>1.672732316918242e-11</v>
+        <v>6.531987530673796e-11</v>
       </c>
     </row>
     <row r="6">
@@ -1268,19 +1268,19 @@
         <v/>
       </c>
       <c r="E6" t="n">
-        <v>-2.722582994798881e-11</v>
+        <v>4.873699210519324e-11</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.095539426944633e-12</v>
+        <v>2.625148893842049e-11</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.692937123672406e-12</v>
+        <v>2.618829041864886e-11</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.719709969594142e-12</v>
+        <v>1.390524041577588e-11</v>
       </c>
       <c r="I6" t="n">
-        <v>1.701972517751136e-10</v>
+        <v>1.681539673639826e-11</v>
       </c>
     </row>
     <row r="7">
@@ -1303,19 +1303,19 @@
         <v/>
       </c>
       <c r="E7" t="n">
-        <v>-1.806407747825697e-11</v>
+        <v>-2.32697622356106e-11</v>
       </c>
       <c r="F7" t="n">
-        <v>5.556390003340075e-12</v>
+        <v>-5.680035226698028e-13</v>
       </c>
       <c r="G7" t="n">
-        <v>6.918121706533873e-12</v>
+        <v>1.028344859783746e-11</v>
       </c>
       <c r="H7" t="n">
-        <v>5.621079683148141e-12</v>
+        <v>8.66794057304781e-12</v>
       </c>
       <c r="I7" t="n">
-        <v>8.445094947473e-12</v>
+        <v>-1.518330302221432e-11</v>
       </c>
     </row>
     <row r="8">
@@ -1338,19 +1338,19 @@
         <v/>
       </c>
       <c r="E8" t="n">
-        <v>-2.612591858440627e-11</v>
+        <v>-5.92767690388017e-11</v>
       </c>
       <c r="F8" t="n">
-        <v>8.793656585053683e-11</v>
+        <v>-5.191632323331026e-11</v>
       </c>
       <c r="G8" t="n">
-        <v>2.929046549478114e-11</v>
+        <v>-7.884204357908406e-12</v>
       </c>
       <c r="H8" t="n">
-        <v>2.934897963370585e-11</v>
+        <v>1.886543973626821e-11</v>
       </c>
       <c r="I8" t="n">
-        <v>2.458498441301957e-11</v>
+        <v>-5.731520343069717e-11</v>
       </c>
     </row>
     <row r="9">
@@ -1373,19 +1373,19 @@
         <v/>
       </c>
       <c r="E9" t="n">
-        <v>-2.750529548203042e-11</v>
+        <v>-5.800041179400182e-11</v>
       </c>
       <c r="F9" t="n">
-        <v>5.568187868695163e-13</v>
+        <v>-5.499951896293651e-11</v>
       </c>
       <c r="G9" t="n">
-        <v>2.703465295912525e-11</v>
+        <v>3.036695777777328e-11</v>
       </c>
       <c r="H9" t="n">
-        <v>4.521676051613718e-12</v>
+        <v>-4.227461410679017e-12</v>
       </c>
       <c r="I9" t="n">
-        <v>4.595119275444765e-12</v>
+        <v>-5.681519653430552e-11</v>
       </c>
     </row>
     <row r="10">
@@ -1408,19 +1408,19 @@
         <v/>
       </c>
       <c r="E10" t="n">
-        <v>-2.711162483754401e-11</v>
+        <v>-4.223502693365971e-11</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.028108497480392e-12</v>
+        <v>-3.443239556050597e-11</v>
       </c>
       <c r="G10" t="n">
-        <v>1.032386414980827e-11</v>
+        <v>2.50990166388332e-11</v>
       </c>
       <c r="H10" t="n">
-        <v>4.830149731713874e-11</v>
+        <v>1.615232016275086e-10</v>
       </c>
       <c r="I10" t="n">
-        <v>-5.733549542647438e-13</v>
+        <v>-3.97429064822929e-11</v>
       </c>
     </row>
     <row r="11">
@@ -1443,19 +1443,19 @@
         <v/>
       </c>
       <c r="E11" t="n">
-        <v>-2.838813124506728e-11</v>
+        <v>-5.344788696551354e-12</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.337289037713349e-11</v>
+        <v>2.8517882462712e-11</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.135807596080735e-11</v>
+        <v>9.981001306994011e-12</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.210299114837256e-11</v>
+        <v>-1.777539384437544e-11</v>
       </c>
       <c r="I11" t="n">
-        <v>8.018218283510887e-12</v>
+        <v>1.563850510403426e-10</v>
       </c>
     </row>
     <row r="12">
@@ -1478,19 +1478,19 @@
         <v/>
       </c>
       <c r="E12" t="n">
-        <v>-1.533209447263984e-11</v>
+        <v>7.196097125150368e-12</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.742981415080658e-12</v>
+        <v>-2.16320685439295e-11</v>
       </c>
       <c r="G12" t="n">
-        <v>5.184683290936591e-12</v>
+        <v>6.708969387388821e-12</v>
       </c>
       <c r="H12" t="n">
-        <v>3.612194770648316e-12</v>
+        <v>7.976010386728246e-12</v>
       </c>
       <c r="I12" t="n">
-        <v>6.62564670583729e-12</v>
+        <v>8.546396313819076e-12</v>
       </c>
     </row>
     <row r="13">
@@ -1513,19 +1513,19 @@
         <v/>
       </c>
       <c r="E13" t="n">
-        <v>-2.350810250500099e-11</v>
+        <v>-4.851014901952964e-11</v>
       </c>
       <c r="F13" t="n">
-        <v>6.41889424569212e-12</v>
+        <v>-5.91619615853652e-11</v>
       </c>
       <c r="G13" t="n">
-        <v>2.702135037524327e-11</v>
+        <v>-9.749767443423733e-12</v>
       </c>
       <c r="H13" t="n">
-        <v>2.56200756901318e-11</v>
+        <v>2.448477850090274e-11</v>
       </c>
       <c r="I13" t="n">
-        <v>2.157916129820085e-11</v>
+        <v>-4.942472082839528e-11</v>
       </c>
     </row>
     <row r="14">
@@ -1548,19 +1548,19 @@
         <v/>
       </c>
       <c r="E14" t="n">
-        <v>-2.727311830135865e-11</v>
+        <v>-4.16521945603215e-11</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.58863747237262e-12</v>
+        <v>-4.972588594536136e-11</v>
       </c>
       <c r="G14" t="n">
-        <v>2.965272314869601e-11</v>
+        <v>8.102328955910846e-11</v>
       </c>
       <c r="H14" t="n">
-        <v>5.199592651723365e-12</v>
+        <v>9.992238043861501e-12</v>
       </c>
       <c r="I14" t="n">
-        <v>5.393460276859551e-12</v>
+        <v>-4.260497692450227e-11</v>
       </c>
     </row>
     <row r="15">
@@ -1583,19 +1583,19 @@
         <v/>
       </c>
       <c r="E15" t="n">
-        <v>-2.672125225341784e-11</v>
+        <v>-4.430959149799106e-11</v>
       </c>
       <c r="F15" t="n">
-        <v>-7.410103636002545e-12</v>
+        <v>-5.261262566695272e-11</v>
       </c>
       <c r="G15" t="n">
-        <v>1.290262860147743e-11</v>
+        <v>3.97239568912818e-12</v>
       </c>
       <c r="H15" t="n">
-        <v>5.669414625923367e-11</v>
+        <v>1.358959560789334e-10</v>
       </c>
       <c r="I15" t="n">
-        <v>9.012077155568319e-13</v>
+        <v>-4.439865023417673e-11</v>
       </c>
     </row>
     <row r="16">
@@ -1618,19 +1618,19 @@
         <v/>
       </c>
       <c r="E16" t="n">
-        <v>-2.814819812534563e-11</v>
+        <v>-3.147030461332534e-11</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.488701324718788e-11</v>
+        <v>-4.509978184105134e-11</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.082853225829634e-11</v>
+        <v>-1.545102096885572e-11</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.17788537235426e-11</v>
+        <v>-2.352792821506025e-11</v>
       </c>
       <c r="I16" t="n">
-        <v>1.167187293310954e-11</v>
+        <v>3.125964547261432e-12</v>
       </c>
     </row>
     <row r="17">
@@ -1653,19 +1653,19 @@
         <v/>
       </c>
       <c r="E17" t="n">
-        <v>7.072107421193338e-12</v>
+        <v>2.061153035969945e-11</v>
       </c>
       <c r="F17" t="n">
-        <v>1.225558145299e-11</v>
+        <v>1.465179807154687e-11</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.568696098135457e-12</v>
+        <v>-1.848820149989819e-11</v>
       </c>
       <c r="H17" t="n">
-        <v>7.598013467819495e-12</v>
+        <v>1.974722497185587e-11</v>
       </c>
       <c r="I17" t="n">
-        <v>7.573787377575515e-12</v>
+        <v>3.199879897502376e-11</v>
       </c>
     </row>
     <row r="18">
@@ -1688,19 +1688,19 @@
         <v/>
       </c>
       <c r="E18" t="n">
-        <v>-2.685540666125778e-11</v>
+        <v>-4.742530497886044e-11</v>
       </c>
       <c r="F18" t="n">
-        <v>6.690585476279631e-12</v>
+        <v>-5.483135578572071e-11</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.376804088000444e-12</v>
+        <v>-3.369187416906565e-11</v>
       </c>
       <c r="H18" t="n">
-        <v>5.229930241148639e-12</v>
+        <v>4.581674721959608e-12</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.446796209548336e-13</v>
+        <v>-4.786428784147798e-11</v>
       </c>
     </row>
     <row r="19">
@@ -1723,19 +1723,19 @@
         <v/>
       </c>
       <c r="E19" t="n">
-        <v>-2.707412187839308e-11</v>
+        <v>-3.964281380310902e-11</v>
       </c>
       <c r="F19" t="n">
-        <v>3.059546070108153e-11</v>
+        <v>-2.832563757821653e-11</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.39244885909337e-12</v>
+        <v>-2.172300211835237e-11</v>
       </c>
       <c r="H19" t="n">
-        <v>7.463144894272393e-12</v>
+        <v>2.054405380725467e-11</v>
       </c>
       <c r="I19" t="n">
-        <v>1.531473639074049e-12</v>
+        <v>-3.753680586893757e-11</v>
       </c>
     </row>
     <row r="20">
@@ -1758,19 +1758,19 @@
         <v/>
       </c>
       <c r="E20" t="n">
-        <v>-2.686049338338515e-11</v>
+        <v>-5.255259885112998e-11</v>
       </c>
       <c r="F20" t="n">
-        <v>-7.2325916252384e-13</v>
+        <v>-5.477779488141467e-11</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.641886439868801e-12</v>
+        <v>-3.061016169348001e-11</v>
       </c>
       <c r="H20" t="n">
-        <v>5.157269065015666e-11</v>
+        <v>9.931090900155062e-11</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.274706903313237e-12</v>
+        <v>-5.150865909271416e-11</v>
       </c>
     </row>
     <row r="21">
@@ -1793,19 +1793,19 @@
         <v/>
       </c>
       <c r="E21" t="n">
-        <v>-2.788362043930163e-11</v>
+        <v>-5.159558833701856e-11</v>
       </c>
       <c r="F21" t="n">
-        <v>-6.094385885284642e-12</v>
+        <v>-5.469303122301615e-11</v>
       </c>
       <c r="G21" t="n">
-        <v>-9.778721810631388e-12</v>
+        <v>-3.766328968962184e-11</v>
       </c>
       <c r="H21" t="n">
-        <v>-5.487088942060496e-12</v>
+        <v>-1.570699035770137e-11</v>
       </c>
       <c r="I21" t="n">
-        <v>5.545024680011369e-11</v>
+        <v>-3.696803700437596e-11</v>
       </c>
     </row>
     <row r="22">
@@ -1828,19 +1828,19 @@
         <v/>
       </c>
       <c r="E22" t="n">
-        <v>5.36321689970237e-11</v>
+        <v>3.887877625334494e-12</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.003728291891378e-12</v>
+        <v>3.935843385776388e-12</v>
       </c>
       <c r="G22" t="n">
-        <v>4.237772083946464e-12</v>
+        <v>1.540812438910408e-11</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.819432237132045e-12</v>
+        <v>-1.285365995229715e-11</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.274744303979702e-12</v>
+        <v>1.144613803615447e-11</v>
       </c>
     </row>
     <row r="23">
@@ -1863,19 +1863,19 @@
         <v/>
       </c>
       <c r="E23" t="n">
-        <v>-2.64829189823418e-11</v>
+        <v>-1.514130303743068e-11</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.039122574964068e-12</v>
+        <v>-3.34219557777433e-11</v>
       </c>
       <c r="G23" t="n">
-        <v>8.196419794848225e-12</v>
+        <v>2.620017046514544e-11</v>
       </c>
       <c r="H23" t="n">
-        <v>3.474575336531526e-13</v>
+        <v>-1.21989579957311e-12</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.753634644997551e-12</v>
+        <v>-1.885057753028616e-11</v>
       </c>
     </row>
     <row r="24">
@@ -1898,19 +1898,19 @@
         <v/>
       </c>
       <c r="E24" t="n">
-        <v>-2.654584862562808e-11</v>
+        <v>-4.634687540243128e-11</v>
       </c>
       <c r="F24" t="n">
-        <v>1.215676119860906e-11</v>
+        <v>-3.765697446029998e-11</v>
       </c>
       <c r="G24" t="n">
-        <v>1.109302171278096e-11</v>
+        <v>9.94015179997381e-12</v>
       </c>
       <c r="H24" t="n">
-        <v>2.472776316906957e-12</v>
+        <v>-6.654596018924447e-12</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.199092277423435e-12</v>
+        <v>-4.443820166367059e-11</v>
       </c>
     </row>
     <row r="25">
@@ -1933,19 +1933,19 @@
         <v/>
       </c>
       <c r="E25" t="n">
-        <v>-2.681325581353422e-11</v>
+        <v>-5.39658392512739e-11</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.191609830988449e-12</v>
+        <v>-5.4797322382429e-11</v>
       </c>
       <c r="G25" t="n">
-        <v>3.577981596321562e-11</v>
+        <v>4.738820111626061e-11</v>
       </c>
       <c r="H25" t="n">
-        <v>2.421207398544041e-13</v>
+        <v>-1.64491506679032e-11</v>
       </c>
       <c r="I25" t="n">
-        <v>-9.183984666382147e-13</v>
+        <v>-5.327822109020496e-11</v>
       </c>
     </row>
     <row r="26">
@@ -1968,19 +1968,19 @@
         <v/>
       </c>
       <c r="E26" t="n">
-        <v>-2.824916042729991e-11</v>
+        <v>-4.385129673416665e-11</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.444195788783914e-11</v>
+        <v>-4.666876190075326e-11</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.046514017459648e-11</v>
+        <v>-1.746051640454578e-11</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.326002592220614e-11</v>
+        <v>-3.444073443550141e-11</v>
       </c>
       <c r="I26" t="n">
-        <v>1.795248764280356e-12</v>
+        <v>-2.201124306346564e-11</v>
       </c>
     </row>
     <row r="27">
@@ -2003,19 +2003,19 @@
         <v/>
       </c>
       <c r="E27" t="n">
-        <v>-2.730694804834971e-11</v>
+        <v>-8.425858851193861e-12</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.039006538270843e-11</v>
+        <v>3.612396282069289e-12</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.114954658128958e-11</v>
+        <v>-1.391229285874406e-11</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.107246719657393e-11</v>
+        <v>-2.353762975424182e-11</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.836574464500148e-11</v>
+        <v>-3.68080620040613e-11</v>
       </c>
     </row>
     <row r="28">
@@ -2038,19 +2038,19 @@
         <v/>
       </c>
       <c r="E28" t="n">
-        <v>-2.807571248098957e-11</v>
+        <v>6.964749051258958e-11</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.205998637243769e-11</v>
+        <v>2.642049519731178e-11</v>
       </c>
       <c r="G28" t="n">
-        <v>-1.242695320697129e-11</v>
+        <v>6.897558402038399e-12</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.21336878882504e-11</v>
+        <v>-1.530183786579582e-11</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.932707136860734e-11</v>
+        <v>-2.423044820083978e-11</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2073,19 @@
         <v/>
       </c>
       <c r="E29" t="n">
-        <v>-2.831179934582584e-11</v>
+        <v>-3.935730812987884e-11</v>
       </c>
       <c r="F29" t="n">
-        <v>-8.711607341188338e-12</v>
+        <v>-1.770064223216705e-11</v>
       </c>
       <c r="G29" t="n">
-        <v>-1.210816909404305e-11</v>
+        <v>-1.2467184996347e-11</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.163342749902256e-11</v>
+        <v>-2.220655326958839e-11</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.927425206090718e-11</v>
+        <v>-5.150799968130978e-11</v>
       </c>
     </row>
     <row r="30">
@@ -2108,19 +2108,19 @@
         <v/>
       </c>
       <c r="E30" t="n">
-        <v>-2.797736948315097e-11</v>
+        <v>-5.703829597978343e-11</v>
       </c>
       <c r="F30" t="n">
-        <v>-7.408034034305774e-12</v>
+        <v>-5.65198709355129e-11</v>
       </c>
       <c r="G30" t="n">
-        <v>1.240161819598614e-12</v>
+        <v>4.538180304483887e-12</v>
       </c>
       <c r="H30" t="n">
-        <v>-6.024788358979144e-12</v>
+        <v>-2.003447886278338e-11</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.699349233458154e-11</v>
+        <v>-6.20460660374992e-11</v>
       </c>
     </row>
     <row r="31">
@@ -2143,19 +2143,19 @@
         <v/>
       </c>
       <c r="E31" t="n">
-        <v>-2.830179656567739e-11</v>
+        <v>-4.835101382864894e-11</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.427535502311126e-11</v>
+        <v>-4.750458187748539e-11</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.130667334477452e-11</v>
+        <v>-1.94617961887613e-11</v>
       </c>
       <c r="H31" t="n">
-        <v>-5.220075415897435e-12</v>
+        <v>3.534693310469444e-12</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.967580344977379e-11</v>
+        <v>-5.680176480940763e-11</v>
       </c>
     </row>
     <row r="32">
@@ -2175,22 +2175,22 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-2.401020741910641e-11</v>
+        <v>-5.109043634741899e-11</v>
       </c>
       <c r="E32" t="n">
         <v/>
       </c>
       <c r="F32" t="n">
-        <v>-3.443778029168457e-12</v>
+        <v>-4.873815621937968e-11</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.926518215633133e-13</v>
+        <v>-1.802599747362123e-11</v>
       </c>
       <c r="H32" t="n">
-        <v>1.949581722930902e-12</v>
+        <v>1.78777148915375e-12</v>
       </c>
       <c r="I32" t="n">
-        <v>2.266305196590907e-12</v>
+        <v>3.03714377418666e-12</v>
       </c>
     </row>
     <row r="33">
@@ -2210,22 +2210,22 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-2.709953861100764e-11</v>
+        <v>-5.282390788171459e-11</v>
       </c>
       <c r="E33" t="n">
         <v/>
       </c>
       <c r="F33" t="n">
-        <v>6.472834477026345e-12</v>
+        <v>-4.444979844368133e-11</v>
       </c>
       <c r="G33" t="n">
-        <v>9.938241766945086e-11</v>
+        <v>-1.802820694699855e-11</v>
       </c>
       <c r="H33" t="n">
-        <v>6.010623162290198e-12</v>
+        <v>6.696117556624353e-12</v>
       </c>
       <c r="I33" t="n">
-        <v>7.29403910793835e-11</v>
+        <v>-3.78398296785355e-11</v>
       </c>
     </row>
     <row r="34">
@@ -2245,22 +2245,22 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-2.67568072118995e-11</v>
+        <v>-5.055460120339712e-11</v>
       </c>
       <c r="E34" t="n">
         <v/>
       </c>
       <c r="F34" t="n">
-        <v>2.402840625088557e-12</v>
+        <v>-4.768556776192433e-11</v>
       </c>
       <c r="G34" t="n">
-        <v>1.355087069837751e-10</v>
+        <v>7.371337315134422e-11</v>
       </c>
       <c r="H34" t="n">
-        <v>1.251029429795595e-11</v>
+        <v>1.241675631263436e-11</v>
       </c>
       <c r="I34" t="n">
-        <v>1.127705352937689e-10</v>
+        <v>-2.827833695549503e-11</v>
       </c>
     </row>
     <row r="35">
@@ -2280,22 +2280,22 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-2.67813137648753e-11</v>
+        <v>-5.401928598334396e-11</v>
       </c>
       <c r="E35" t="n">
         <v/>
       </c>
       <c r="F35" t="n">
-        <v>-7.274832218205738e-12</v>
+        <v>-5.100555729160691e-11</v>
       </c>
       <c r="G35" t="n">
-        <v>3.975824385789124e-11</v>
+        <v>-2.556618155732874e-11</v>
       </c>
       <c r="H35" t="n">
-        <v>3.302440161831049e-11</v>
+        <v>4.273718460734315e-11</v>
       </c>
       <c r="I35" t="n">
-        <v>5.790870774467081e-11</v>
+        <v>-3.309632787855475e-11</v>
       </c>
     </row>
     <row r="36">
@@ -2315,22 +2315,22 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-2.807510004987041e-11</v>
+        <v>-5.667291178364606e-11</v>
       </c>
       <c r="E36" t="n">
         <v/>
       </c>
       <c r="F36" t="n">
-        <v>-1.003583805575432e-11</v>
+        <v>-5.125275922434009e-11</v>
       </c>
       <c r="G36" t="n">
-        <v>7.761534980079215e-11</v>
+        <v>-3.671828656763683e-11</v>
       </c>
       <c r="H36" t="n">
-        <v>-9.091415372066906e-12</v>
+        <v>-1.882793769462869e-11</v>
       </c>
       <c r="I36" t="n">
-        <v>1.751037230578124e-10</v>
+        <v>-5.680665605469904e-12</v>
       </c>
     </row>
     <row r="37">
@@ -2350,22 +2350,22 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>7.732587779685448e-08</v>
+        <v>7.840144754691244e-11</v>
       </c>
       <c r="E37" t="n">
         <v/>
       </c>
       <c r="F37" t="n">
-        <v>6.69561053609474e-12</v>
+        <v>-4.146403071682648e-11</v>
       </c>
       <c r="G37" t="n">
-        <v>9.013103939521761e-11</v>
+        <v>7.077291202213873e-11</v>
       </c>
       <c r="H37" t="n">
-        <v>3.444033189096869e-11</v>
+        <v>5.461033258153606e-11</v>
       </c>
       <c r="I37" t="n">
-        <v>1.668462955657775e-10</v>
+        <v>6.511160550061171e-11</v>
       </c>
     </row>
     <row r="38">
@@ -2385,22 +2385,22 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>9.734515522908978e-11</v>
+        <v>-4.087028677942068e-11</v>
       </c>
       <c r="E38" t="n">
         <v/>
       </c>
       <c r="F38" t="n">
-        <v>4.342936378154846e-10</v>
+        <v>-4.732657641400655e-11</v>
       </c>
       <c r="G38" t="n">
-        <v>1.532169446582926e-09</v>
+        <v>3.285644756879843e-11</v>
       </c>
       <c r="H38" t="n">
-        <v>1.012142008458021e-10</v>
+        <v>3.947437978460863e-11</v>
       </c>
       <c r="I38" t="n">
-        <v>7.193890354446384e-10</v>
+        <v>9.277766555343631e-11</v>
       </c>
     </row>
     <row r="39">
@@ -2420,22 +2420,22 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-2.180608087910738e-11</v>
+        <v>-3.517339274412425e-11</v>
       </c>
       <c r="E39" t="n">
         <v/>
       </c>
       <c r="F39" t="n">
-        <v>3.195378235653675e-11</v>
+        <v>-4.816187779206558e-11</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1517005394332606</v>
+        <v>9.609910010533133e-10</v>
       </c>
       <c r="H39" t="n">
-        <v>3.228175166461501e-11</v>
+        <v>2.389980304713374e-11</v>
       </c>
       <c r="I39" t="n">
-        <v>5.847069246906706e-10</v>
+        <v>1.804288768308001e-11</v>
       </c>
     </row>
     <row r="40">
@@ -2455,22 +2455,22 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-1.330707226676382e-11</v>
+        <v>2.048646767071368e-11</v>
       </c>
       <c r="E40" t="n">
         <v/>
       </c>
       <c r="F40" t="n">
-        <v>9.77512392457158e-12</v>
+        <v>-1.479208920162639e-11</v>
       </c>
       <c r="G40" t="n">
-        <v>9.706626227606624e-11</v>
+        <v>1.623920074189638e-10</v>
       </c>
       <c r="H40" t="n">
-        <v>3.12455341292026e-10</v>
+        <v>4.230918170072873e-10</v>
       </c>
       <c r="I40" t="n">
-        <v>1.816809853303054e-10</v>
+        <v>1.372051192426289e-10</v>
       </c>
     </row>
     <row r="41">
@@ -2490,22 +2490,22 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-2.730425304157247e-11</v>
+        <v>2.444534767727938e-10</v>
       </c>
       <c r="E41" t="n">
         <v/>
       </c>
       <c r="F41" t="n">
-        <v>-3.239700857426426e-12</v>
+        <v>2.251153837845759e-10</v>
       </c>
       <c r="G41" t="n">
-        <v>2.375145447796294e-10</v>
+        <v>1.72267993269304e-10</v>
       </c>
       <c r="H41" t="n">
-        <v>-6.156349347309165e-12</v>
+        <v>4.825927387585614e-11</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1748585935451141</v>
+        <v>0.165465126703093</v>
       </c>
     </row>
     <row r="42">
@@ -2525,22 +2525,22 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-2.44673399150653e-11</v>
+        <v>-2.385430264972232e-11</v>
       </c>
       <c r="E42" t="n">
         <v/>
       </c>
       <c r="F42" t="n">
-        <v>-3.565322055274376e-12</v>
+        <v>-5.395998829116281e-11</v>
       </c>
       <c r="G42" t="n">
-        <v>8.485361654692902e-11</v>
+        <v>-2.284538329736149e-11</v>
       </c>
       <c r="H42" t="n">
-        <v>1.017039235285238e-11</v>
+        <v>3.845542368377339e-12</v>
       </c>
       <c r="I42" t="n">
-        <v>1.009804187069583e-10</v>
+        <v>-3.530843598607474e-11</v>
       </c>
     </row>
     <row r="43">
@@ -2560,22 +2560,22 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>9.344584670767539e-11</v>
+        <v>-5.06610491910047e-11</v>
       </c>
       <c r="E43" t="n">
         <v/>
       </c>
       <c r="F43" t="n">
-        <v>1.237772098336446e-11</v>
+        <v>-5.728165447394162e-11</v>
       </c>
       <c r="G43" t="n">
-        <v>7.397852805117577e-12</v>
+        <v>-2.616908181025379e-11</v>
       </c>
       <c r="H43" t="n">
-        <v>1.795789650324669e-11</v>
+        <v>-2.19211021320744e-12</v>
       </c>
       <c r="I43" t="n">
-        <v>1.057194405313731e-11</v>
+        <v>3.097563503719076e-11</v>
       </c>
     </row>
     <row r="44">
@@ -2595,22 +2595,22 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-2.630402320902505e-11</v>
+        <v>-3.982427607311774e-11</v>
       </c>
       <c r="E44" t="n">
         <v/>
       </c>
       <c r="F44" t="n">
-        <v>8.641571061321447e-12</v>
+        <v>-4.795962911693949e-11</v>
       </c>
       <c r="G44" t="n">
-        <v>1.730088783598354e-09</v>
+        <v>7.503226792805972e-11</v>
       </c>
       <c r="H44" t="n">
-        <v>1.266416430084548e-11</v>
+        <v>9.751014530092659e-12</v>
       </c>
       <c r="I44" t="n">
-        <v>2.294685726256479e-10</v>
+        <v>-3.415039867580941e-11</v>
       </c>
     </row>
     <row r="45">
@@ -2630,22 +2630,22 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>-2.554296832565227e-11</v>
+        <v>-4.679955785400583e-11</v>
       </c>
       <c r="E45" t="n">
         <v/>
       </c>
       <c r="F45" t="n">
-        <v>-5.211278930452196e-13</v>
+        <v>-5.273583250913805e-11</v>
       </c>
       <c r="G45" t="n">
-        <v>9.175855284301172e-11</v>
+        <v>-2.462257253055324e-11</v>
       </c>
       <c r="H45" t="n">
-        <v>7.240455209062851e-11</v>
+        <v>4.912340076962926e-11</v>
       </c>
       <c r="I45" t="n">
-        <v>1.1867597549235e-10</v>
+        <v>-2.912377868568692e-11</v>
       </c>
     </row>
     <row r="46">
@@ -2665,22 +2665,22 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>-2.770167376232188e-11</v>
+        <v>-4.426903550195624e-11</v>
       </c>
       <c r="E46" t="n">
         <v/>
       </c>
       <c r="F46" t="n">
-        <v>-7.835616741826032e-12</v>
+        <v>-4.558900988364762e-11</v>
       </c>
       <c r="G46" t="n">
-        <v>2.521373171922449e-10</v>
+        <v>-3.211915101656658e-11</v>
       </c>
       <c r="H46" t="n">
-        <v>-9.381381521184299e-12</v>
+        <v>-1.604062305989931e-11</v>
       </c>
       <c r="I46" t="n">
-        <v>5.256245946137176e-10</v>
+        <v>-1.557056038728996e-11</v>
       </c>
     </row>
     <row r="47">
@@ -2700,22 +2700,22 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-2.483542693879989e-11</v>
+        <v>-2.21773794146068e-11</v>
       </c>
       <c r="E47" t="n">
         <v/>
       </c>
       <c r="F47" t="n">
-        <v>2.437302092225305e-12</v>
+        <v>-4.985374741137029e-11</v>
       </c>
       <c r="G47" t="n">
-        <v>7.062290011504295e-11</v>
+        <v>-4.078625484598153e-11</v>
       </c>
       <c r="H47" t="n">
-        <v>1.019732134416953e-11</v>
+        <v>1.009539347252154e-11</v>
       </c>
       <c r="I47" t="n">
-        <v>7.784448837774914e-11</v>
+        <v>-3.58756153552887e-11</v>
       </c>
     </row>
     <row r="48">
@@ -2735,22 +2735,22 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-2.38653704204231e-11</v>
+        <v>-5.109394164340153e-11</v>
       </c>
       <c r="E48" t="n">
         <v/>
       </c>
       <c r="F48" t="n">
-        <v>6.038615925917987e-12</v>
+        <v>-5.405773637560262e-11</v>
       </c>
       <c r="G48" t="n">
-        <v>3.553545945234078e-12</v>
+        <v>-4.54762900996834e-11</v>
       </c>
       <c r="H48" t="n">
-        <v>-9.339456001922963e-14</v>
+        <v>-1.105407813910407e-11</v>
       </c>
       <c r="I48" t="n">
-        <v>3.078624703840778e-12</v>
+        <v>-2.584932818090574e-11</v>
       </c>
     </row>
     <row r="49">
@@ -2770,22 +2770,22 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-2.676841357664869e-11</v>
+        <v>-4.166434588280098e-11</v>
       </c>
       <c r="E49" t="n">
         <v/>
       </c>
       <c r="F49" t="n">
-        <v>3.465211699157172e-11</v>
+        <v>-3.597625007706093e-11</v>
       </c>
       <c r="G49" t="n">
-        <v>2.496873605637311e-10</v>
+        <v>-3.755527341489568e-11</v>
       </c>
       <c r="H49" t="n">
-        <v>6.086360765922315e-12</v>
+        <v>1.239470617154357e-11</v>
       </c>
       <c r="I49" t="n">
-        <v>9.122199719838894e-11</v>
+        <v>-4.209279340719989e-11</v>
       </c>
     </row>
     <row r="50">
@@ -2805,22 +2805,22 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-2.614191042005108e-11</v>
+        <v>-5.499455096810766e-11</v>
       </c>
       <c r="E50" t="n">
         <v/>
       </c>
       <c r="F50" t="n">
-        <v>2.965457242131905e-12</v>
+        <v>-5.69902639455461e-11</v>
       </c>
       <c r="G50" t="n">
-        <v>7.013638818279919e-11</v>
+        <v>-4.827954563623042e-11</v>
       </c>
       <c r="H50" t="n">
-        <v>4.39690646421097e-11</v>
+        <v>2.12648817735814e-11</v>
       </c>
       <c r="I50" t="n">
-        <v>7.712307795428352e-11</v>
+        <v>-4.013286376115436e-11</v>
       </c>
     </row>
     <row r="51">
@@ -2840,22 +2840,22 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>-2.749795444924037e-11</v>
+        <v>-5.754881513874569e-11</v>
       </c>
       <c r="E51" t="n">
         <v/>
       </c>
       <c r="F51" t="n">
-        <v>2.253955816424551e-12</v>
+        <v>-5.760680131747136e-11</v>
       </c>
       <c r="G51" t="n">
-        <v>1.951187736234693e-10</v>
+        <v>-5.214950985120448e-11</v>
       </c>
       <c r="H51" t="n">
-        <v>-4.017576942422815e-12</v>
+        <v>-2.097907571596346e-11</v>
       </c>
       <c r="I51" t="n">
-        <v>8.277679519335495e-10</v>
+        <v>4.072685534097524e-12</v>
       </c>
     </row>
     <row r="52">
@@ -2875,22 +2875,22 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>-2.461226789663407e-11</v>
+        <v>-1.832063766762179e-11</v>
       </c>
       <c r="E52" t="n">
         <v/>
       </c>
       <c r="F52" t="n">
-        <v>-7.229345239080418e-12</v>
+        <v>-5.010439993933176e-11</v>
       </c>
       <c r="G52" t="n">
-        <v>4.051354049694688e-11</v>
+        <v>-1.009190460894219e-11</v>
       </c>
       <c r="H52" t="n">
-        <v>-9.94568748921001e-13</v>
+        <v>-8.152642053897151e-12</v>
       </c>
       <c r="I52" t="n">
-        <v>6.147177138384442e-11</v>
+        <v>-2.823903187125595e-11</v>
       </c>
     </row>
     <row r="53">
@@ -2910,22 +2910,22 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>-1.798834313904665e-11</v>
+        <v>-1.650423516611827e-11</v>
       </c>
       <c r="E53" t="n">
         <v/>
       </c>
       <c r="F53" t="n">
-        <v>-2.477897861453572e-12</v>
+        <v>-2.562100816950096e-11</v>
       </c>
       <c r="G53" t="n">
-        <v>1.511608369163514e-13</v>
+        <v>3.200449252617342e-11</v>
       </c>
       <c r="H53" t="n">
-        <v>-3.515669065057384e-12</v>
+        <v>4.438556712778404e-12</v>
       </c>
       <c r="I53" t="n">
-        <v>3.035414744487813e-12</v>
+        <v>5.252058191551391e-11</v>
       </c>
     </row>
     <row r="54">
@@ -2945,22 +2945,22 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-2.594839182775956e-11</v>
+        <v>-4.335652016681127e-11</v>
       </c>
       <c r="E54" t="n">
         <v/>
       </c>
       <c r="F54" t="n">
-        <v>1.134318145937838e-11</v>
+        <v>-4.178172235139466e-11</v>
       </c>
       <c r="G54" t="n">
-        <v>1.050201768466664e-10</v>
+        <v>-2.549103644552924e-12</v>
       </c>
       <c r="H54" t="n">
-        <v>1.586050215445144e-12</v>
+        <v>-4.335619717034244e-12</v>
       </c>
       <c r="I54" t="n">
-        <v>8.712613487513369e-11</v>
+        <v>-2.76247479134636e-11</v>
       </c>
     </row>
     <row r="55">
@@ -2980,22 +2980,22 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-2.591947291810844e-11</v>
+        <v>-5.085014972591898e-11</v>
       </c>
       <c r="E55" t="n">
         <v/>
       </c>
       <c r="F55" t="n">
-        <v>3.09570148853991e-12</v>
+        <v>-5.508402485649774e-11</v>
       </c>
       <c r="G55" t="n">
-        <v>1.389566359764346e-10</v>
+        <v>4.901686472322766e-11</v>
       </c>
       <c r="H55" t="n">
-        <v>2.432174914543129e-12</v>
+        <v>-1.551478273699537e-11</v>
       </c>
       <c r="I55" t="n">
-        <v>1.212631534715319e-10</v>
+        <v>-2.923891091648149e-11</v>
       </c>
     </row>
     <row r="56">
@@ -3015,22 +3015,22 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-2.789320618293248e-11</v>
+        <v>-4.963987415899833e-11</v>
       </c>
       <c r="E56" t="n">
         <v/>
       </c>
       <c r="F56" t="n">
-        <v>-1.028604040007303e-11</v>
+        <v>-4.910430621814666e-11</v>
       </c>
       <c r="G56" t="n">
-        <v>7.630757754105955e-11</v>
+        <v>-3.076925211702286e-11</v>
       </c>
       <c r="H56" t="n">
-        <v>-1.221872243822337e-11</v>
+        <v>-2.747138750022325e-11</v>
       </c>
       <c r="I56" t="n">
-        <v>1.753933186521111e-10</v>
+        <v>-3.912984100477405e-13</v>
       </c>
     </row>
     <row r="57">
@@ -3050,22 +3050,22 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>-2.74822881617988e-11</v>
+        <v>-1.19266051866991e-11</v>
       </c>
       <c r="E57" t="n">
         <v/>
       </c>
       <c r="F57" t="n">
-        <v>-9.880103066575501e-12</v>
+        <v>-4.751899005696145e-11</v>
       </c>
       <c r="G57" t="n">
-        <v>6.595096993610514e-11</v>
+        <v>-2.167466866504167e-11</v>
       </c>
       <c r="H57" t="n">
-        <v>-9.409991409687852e-12</v>
+        <v>-1.558873409859319e-11</v>
       </c>
       <c r="I57" t="n">
-        <v>1.384668833764921e-11</v>
+        <v>-6.754653862582502e-11</v>
       </c>
     </row>
     <row r="58">
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>-2.758274489785926e-11</v>
+        <v>1.693496616275872e-10</v>
       </c>
       <c r="E58" t="n">
         <v/>
       </c>
       <c r="F58" t="n">
-        <v>-8.853843719817404e-12</v>
+        <v>1.856985497287147e-10</v>
       </c>
       <c r="G58" t="n">
-        <v>3.107955875434073e-12</v>
+        <v>5.766679524372377e-11</v>
       </c>
       <c r="H58" t="n">
-        <v>-1.278713320532776e-11</v>
+        <v>7.019798351386099e-12</v>
       </c>
       <c r="I58" t="n">
-        <v>-7.31356265458752e-12</v>
+        <v>-6.421375696370808e-11</v>
       </c>
     </row>
     <row r="59">
@@ -3120,22 +3120,22 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>-2.809896971807849e-11</v>
+        <v>-2.6691142539807e-11</v>
       </c>
       <c r="E59" t="n">
         <v/>
       </c>
       <c r="F59" t="n">
-        <v>-2.911965732726846e-12</v>
+        <v>-1.517030455127552e-11</v>
       </c>
       <c r="G59" t="n">
-        <v>1.79976721322468e-10</v>
+        <v>-5.447784287778652e-12</v>
       </c>
       <c r="H59" t="n">
-        <v>-1.10816112629227e-11</v>
+        <v>-9.742359399964309e-12</v>
       </c>
       <c r="I59" t="n">
-        <v>1.464394689372185e-11</v>
+        <v>-6.839783324970595e-11</v>
       </c>
     </row>
     <row r="60">
@@ -3155,22 +3155,22 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>-2.756886798345712e-11</v>
+        <v>-5.106458396296897e-11</v>
       </c>
       <c r="E60" t="n">
         <v/>
       </c>
       <c r="F60" t="n">
-        <v>2.253552536370376e-12</v>
+        <v>-5.531211925623155e-11</v>
       </c>
       <c r="G60" t="n">
-        <v>5.274282712648888e-10</v>
+        <v>1.628006223811657e-11</v>
       </c>
       <c r="H60" t="n">
-        <v>-3.746609927363629e-12</v>
+        <v>-1.883096359059573e-11</v>
       </c>
       <c r="I60" t="n">
-        <v>2.882695408706762e-11</v>
+        <v>-6.625315630300646e-11</v>
       </c>
     </row>
     <row r="61">
@@ -3190,22 +3190,22 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>-2.796796466111669e-11</v>
+        <v>-4.334448974946322e-11</v>
       </c>
       <c r="E61" t="n">
         <v/>
       </c>
       <c r="F61" t="n">
-        <v>-1.031456865037643e-11</v>
+        <v>-4.613462872401687e-11</v>
       </c>
       <c r="G61" t="n">
-        <v>6.22296445382969e-11</v>
+        <v>-2.631261081464679e-11</v>
       </c>
       <c r="H61" t="n">
-        <v>-4.288743122761227e-12</v>
+        <v>2.082508641399233e-12</v>
       </c>
       <c r="I61" t="n">
-        <v>1.290104660585077e-11</v>
+        <v>-6.782555612299375e-11</v>
       </c>
     </row>
     <row r="62">
@@ -3225,22 +3225,22 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>-1.039689638540588e-11</v>
+        <v>-5.462175188528885e-11</v>
       </c>
       <c r="E62" t="n">
-        <v>7.871872627281717e-12</v>
+        <v>-5.113871220258026e-11</v>
       </c>
       <c r="F62" t="n">
         <v/>
       </c>
       <c r="G62" t="n">
-        <v>3.739095466650108e-10</v>
+        <v>1.052171226748776e-11</v>
       </c>
       <c r="H62" t="n">
-        <v>5.642274226472231e-12</v>
+        <v>7.910333149605348e-12</v>
       </c>
       <c r="I62" t="n">
-        <v>7.314009155926009e-10</v>
+        <v>5.974047497905563e-10</v>
       </c>
     </row>
     <row r="63">
@@ -3260,22 +3260,22 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>-1.089981038287918e-11</v>
+        <v>-2.793250264535734e-11</v>
       </c>
       <c r="E63" t="n">
-        <v>-4.421971197737145e-12</v>
+        <v>-1.909159165242768e-11</v>
       </c>
       <c r="F63" t="n">
         <v/>
       </c>
       <c r="G63" t="n">
-        <v>1.214059452892158e-12</v>
+        <v>6.843537352954831e-12</v>
       </c>
       <c r="H63" t="n">
-        <v>3.01332641390981e-13</v>
+        <v>8.203558764151946e-12</v>
       </c>
       <c r="I63" t="n">
-        <v>2.423802667642585e-12</v>
+        <v>3.275048883321129e-12</v>
       </c>
     </row>
     <row r="64">
@@ -3295,22 +3295,22 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>-8.408627356890389e-12</v>
+        <v>-5.168909630097966e-11</v>
       </c>
       <c r="E64" t="n">
-        <v>1.835400010154327e-12</v>
+        <v>-4.877217128659812e-11</v>
       </c>
       <c r="F64" t="n">
         <v/>
       </c>
       <c r="G64" t="n">
-        <v>4.327985473264815e-10</v>
+        <v>1.667687598621052e-10</v>
       </c>
       <c r="H64" t="n">
-        <v>1.008554647491092e-11</v>
+        <v>1.167776610871668e-11</v>
       </c>
       <c r="I64" t="n">
-        <v>9.812834052115944e-10</v>
+        <v>5.378608503048576e-10</v>
       </c>
     </row>
     <row r="65">
@@ -3330,22 +3330,22 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>-1.314780070525957e-11</v>
+        <v>-5.318722098294216e-11</v>
       </c>
       <c r="E65" t="n">
-        <v>-7.616431817431525e-12</v>
+        <v>-5.071127108300489e-11</v>
       </c>
       <c r="F65" t="n">
         <v/>
       </c>
       <c r="G65" t="n">
-        <v>1.631610853546117e-10</v>
+        <v>1.890485304129783e-11</v>
       </c>
       <c r="H65" t="n">
-        <v>2.644864901560219e-11</v>
+        <v>5.863000877143757e-11</v>
       </c>
       <c r="I65" t="n">
-        <v>5.696678015730627e-10</v>
+        <v>5.207704716607288e-10</v>
       </c>
     </row>
     <row r="66">
@@ -3365,22 +3365,22 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>-1.597024212405966e-11</v>
+        <v>-5.341925620344185e-11</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.028302095560087e-11</v>
+        <v>-4.908208805988965e-11</v>
       </c>
       <c r="F66" t="n">
         <v/>
       </c>
       <c r="G66" t="n">
-        <v>3.205588296318872e-10</v>
+        <v>-1.832382576724743e-11</v>
       </c>
       <c r="H66" t="n">
-        <v>-1.043753661271776e-11</v>
+        <v>-2.074809136386585e-11</v>
       </c>
       <c r="I66" t="n">
-        <v>1.360029444676338e-09</v>
+        <v>3.224961415979213e-09</v>
       </c>
     </row>
     <row r="67">
@@ -3400,22 +3400,22 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>6.049067863226205e-11</v>
+        <v>-3.449376952968559e-11</v>
       </c>
       <c r="E67" t="n">
-        <v>-3.734124852138627e-12</v>
+        <v>-5.262065728994036e-11</v>
       </c>
       <c r="F67" t="n">
         <v/>
       </c>
       <c r="G67" t="n">
-        <v>2.837140141966603e-10</v>
+        <v>2.509820258079062e-11</v>
       </c>
       <c r="H67" t="n">
-        <v>1.018392178473474e-11</v>
+        <v>5.239186627996527e-12</v>
       </c>
       <c r="I67" t="n">
-        <v>8.865190975295032e-10</v>
+        <v>4.375200558381708e-10</v>
       </c>
     </row>
     <row r="68">
@@ -3435,22 +3435,22 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2.864727262815348e-11</v>
+        <v>-4.06096873874823e-11</v>
       </c>
       <c r="E68" t="n">
-        <v>1.196572979606733e-11</v>
+        <v>-4.468738412199919e-11</v>
       </c>
       <c r="F68" t="n">
         <v/>
       </c>
       <c r="G68" t="n">
-        <v>3.729134196628278e-12</v>
+        <v>1.350255232067364e-11</v>
       </c>
       <c r="H68" t="n">
-        <v>1.722061495486362e-11</v>
+        <v>2.625143811905795e-12</v>
       </c>
       <c r="I68" t="n">
-        <v>3.435949746480063e-12</v>
+        <v>7.38792513078936e-13</v>
       </c>
     </row>
     <row r="69">
@@ -3470,22 +3470,22 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1.021142914816995e-11</v>
+        <v>-5.559250032996816e-11</v>
       </c>
       <c r="E69" t="n">
-        <v>6.640980966209219e-12</v>
+        <v>-5.708829106263944e-11</v>
       </c>
       <c r="F69" t="n">
         <v/>
       </c>
       <c r="G69" t="n">
-        <v>8.526589559714401e-09</v>
+        <v>8.435188853402902e-11</v>
       </c>
       <c r="H69" t="n">
-        <v>7.428306230659903e-12</v>
+        <v>-1.046674143094892e-11</v>
       </c>
       <c r="I69" t="n">
-        <v>1.808433952439585e-09</v>
+        <v>3.545951612047474e-10</v>
       </c>
     </row>
     <row r="70">
@@ -3505,22 +3505,22 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>7.93871889445058e-13</v>
+        <v>-3.541736672585853e-11</v>
       </c>
       <c r="E70" t="n">
-        <v>-2.407466409522521e-12</v>
+        <v>-3.86264804569137e-11</v>
       </c>
       <c r="F70" t="n">
         <v/>
       </c>
       <c r="G70" t="n">
-        <v>2.994696000981267e-10</v>
+        <v>4.286387222627926e-11</v>
       </c>
       <c r="H70" t="n">
-        <v>4.271208899286485e-11</v>
+        <v>9.399521062628057e-11</v>
       </c>
       <c r="I70" t="n">
-        <v>9.237311851323901e-10</v>
+        <v>5.308626785042571e-10</v>
       </c>
     </row>
     <row r="71">
@@ -3540,22 +3540,22 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>-1.081101522124829e-11</v>
+        <v>1.769103655453694e-11</v>
       </c>
       <c r="E71" t="n">
-        <v>-9.352692211779881e-12</v>
+        <v>2.788440598506605e-11</v>
       </c>
       <c r="F71" t="n">
         <v/>
       </c>
       <c r="G71" t="n">
-        <v>1.004070644521119e-09</v>
+        <v>-7.422797038060974e-12</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.160280749245363e-11</v>
+        <v>-9.080663146405895e-12</v>
       </c>
       <c r="I71" t="n">
-        <v>2.856314079766882e-09</v>
+        <v>1.107409720830978e-08</v>
       </c>
     </row>
     <row r="72">
@@ -3575,22 +3575,22 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>9.493484250012957e-10</v>
+        <v>-2.318203688028629e-11</v>
       </c>
       <c r="E72" t="n">
-        <v>6.196832034694701e-12</v>
+        <v>-1.594548373637881e-11</v>
       </c>
       <c r="F72" t="n">
         <v/>
       </c>
       <c r="G72" t="n">
-        <v>3.081165357587436e-10</v>
+        <v>1.594059790207423e-10</v>
       </c>
       <c r="H72" t="n">
-        <v>2.415693509405993e-11</v>
+        <v>7.662842618955299e-11</v>
       </c>
       <c r="I72" t="n">
-        <v>1.144840743721984e-09</v>
+        <v>3.169384782005986e-09</v>
       </c>
     </row>
     <row r="73">
@@ -3610,22 +3610,22 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1.160437042749706e-10</v>
+        <v>-3.069617332359391e-11</v>
       </c>
       <c r="E73" t="n">
-        <v>4.469612381431805e-10</v>
+        <v>-3.48689440775815e-11</v>
       </c>
       <c r="F73" t="n">
         <v/>
       </c>
       <c r="G73" t="n">
-        <v>6.925182561269631e-09</v>
+        <v>1.470833272731156e-10</v>
       </c>
       <c r="H73" t="n">
-        <v>7.080588990001019e-11</v>
+        <v>8.23701440078367e-11</v>
       </c>
       <c r="I73" t="n">
-        <v>3.814557539207288e-09</v>
+        <v>1.020551180832014e-08</v>
       </c>
     </row>
     <row r="74">
@@ -3645,22 +3645,22 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>4.476464351832724e-11</v>
+        <v>3.822003699529595e-11</v>
       </c>
       <c r="E74" t="n">
-        <v>3.341538847535233e-11</v>
+        <v>1.541986600424012e-11</v>
       </c>
       <c r="F74" t="n">
         <v/>
       </c>
       <c r="G74" t="n">
-        <v>0.1653365729504659</v>
+        <v>-5.139780072376636e-11</v>
       </c>
       <c r="H74" t="n">
-        <v>2.52523917733353e-11</v>
+        <v>8.027105274932522e-11</v>
       </c>
       <c r="I74" t="n">
-        <v>3.778015405067797e-09</v>
+        <v>3.487933258554552e-09</v>
       </c>
     </row>
     <row r="75">
@@ -3680,22 +3680,22 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1.977749451924134e-11</v>
+        <v>9.341689171340463e-12</v>
       </c>
       <c r="E75" t="n">
-        <v>1.165042316726057e-11</v>
+        <v>-7.14543439344548e-12</v>
       </c>
       <c r="F75" t="n">
         <v/>
       </c>
       <c r="G75" t="n">
-        <v>3.231776325884398e-10</v>
+        <v>2.073657384792493e-10</v>
       </c>
       <c r="H75" t="n">
-        <v>2.05234145813953e-10</v>
+        <v>-3.355959615142595e-12</v>
       </c>
       <c r="I75" t="n">
-        <v>1.326925854805186e-09</v>
+        <v>5.190092939562687e-09</v>
       </c>
     </row>
     <row r="76">
@@ -3715,22 +3715,22 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>-4.310006005659572e-12</v>
+        <v>9.496333621103761e-11</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.682198514363535e-12</v>
+        <v>8.754599821144254e-11</v>
       </c>
       <c r="F76" t="n">
         <v/>
       </c>
       <c r="G76" t="n">
-        <v>1.785091709167051e-09</v>
+        <v>2.081509805481919e-11</v>
       </c>
       <c r="H76" t="n">
-        <v>-7.961231773733047e-12</v>
+        <v>9.722728543769586e-12</v>
       </c>
       <c r="I76" t="n">
-        <v>0.2973394921970289</v>
+        <v>6.038348849487467e-11</v>
       </c>
     </row>
     <row r="77">
@@ -3750,22 +3750,22 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>4.565910599148537e-11</v>
+        <v>-2.954622381258861e-11</v>
       </c>
       <c r="E77" t="n">
-        <v>2.491165983705327e-12</v>
+        <v>-4.927282617406387e-11</v>
       </c>
       <c r="F77" t="n">
         <v/>
       </c>
       <c r="G77" t="n">
-        <v>2.697807118684117e-10</v>
+        <v>-1.443399531591686e-11</v>
       </c>
       <c r="H77" t="n">
-        <v>8.87362154043347e-12</v>
+        <v>1.449517866417656e-11</v>
       </c>
       <c r="I77" t="n">
-        <v>7.253481985610562e-10</v>
+        <v>5.606000742879348e-10</v>
       </c>
     </row>
     <row r="78">
@@ -3785,22 +3785,22 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>4.660969570327735e-13</v>
+        <v>-5.55979230098056e-11</v>
       </c>
       <c r="E78" t="n">
-        <v>3.210484283741648e-11</v>
+        <v>-5.528178112652478e-11</v>
       </c>
       <c r="F78" t="n">
         <v/>
       </c>
       <c r="G78" t="n">
-        <v>1.23749298556273e-09</v>
+        <v>-2.73642387445101e-11</v>
       </c>
       <c r="H78" t="n">
-        <v>2.344735061728055e-12</v>
+        <v>-5.408410669745751e-12</v>
       </c>
       <c r="I78" t="n">
-        <v>8.428721030940605e-10</v>
+        <v>4.924505373261752e-10</v>
       </c>
     </row>
     <row r="79">
@@ -3820,22 +3820,22 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1.704848129676922e-12</v>
+        <v>1.531674994519536e-11</v>
       </c>
       <c r="E79" t="n">
-        <v>7.295285291431699e-12</v>
+        <v>1.235131785373994e-11</v>
       </c>
       <c r="F79" t="n">
         <v/>
       </c>
       <c r="G79" t="n">
-        <v>2.983149773060126e-12</v>
+        <v>-2.164783882163088e-11</v>
       </c>
       <c r="H79" t="n">
-        <v>-8.864504465270295e-14</v>
+        <v>1.366434456220133e-11</v>
       </c>
       <c r="I79" t="n">
-        <v>2.653471970385204e-12</v>
+        <v>4.154657086144367e-12</v>
       </c>
     </row>
     <row r="80">
@@ -3855,22 +3855,22 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>-2.425058424473443e-12</v>
+        <v>-5.544668674072658e-11</v>
       </c>
       <c r="E80" t="n">
-        <v>2.680429427264933e-12</v>
+        <v>-5.630422718728508e-11</v>
       </c>
       <c r="F80" t="n">
         <v/>
       </c>
       <c r="G80" t="n">
-        <v>2.672088483820751e-10</v>
+        <v>-2.121092434313205e-11</v>
       </c>
       <c r="H80" t="n">
-        <v>3.377638686578802e-11</v>
+        <v>3.850103513774757e-11</v>
       </c>
       <c r="I80" t="n">
-        <v>7.149883725914504e-10</v>
+        <v>4.617110346254979e-10</v>
       </c>
     </row>
     <row r="81">
@@ -3890,22 +3890,22 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>-5.570966082370343e-12</v>
+        <v>-5.595147240873817e-11</v>
       </c>
       <c r="E81" t="n">
-        <v>2.05673311434475e-12</v>
+        <v>-5.569820614747182e-11</v>
       </c>
       <c r="F81" t="n">
         <v/>
       </c>
       <c r="G81" t="n">
-        <v>1.025809657953312e-09</v>
+        <v>-3.374061204567454e-11</v>
       </c>
       <c r="H81" t="n">
-        <v>-5.923055095939328e-12</v>
+        <v>-1.964598954902831e-11</v>
       </c>
       <c r="I81" t="n">
-        <v>5.741660638639426e-09</v>
+        <v>3.483443450180224e-09</v>
       </c>
     </row>
     <row r="82">
@@ -3925,22 +3925,22 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1.100241094894678e-11</v>
+        <v>-3.304980730021997e-11</v>
       </c>
       <c r="E82" t="n">
-        <v>-7.252402324934699e-12</v>
+        <v>-5.084925550779915e-11</v>
       </c>
       <c r="F82" t="n">
         <v/>
       </c>
       <c r="G82" t="n">
-        <v>1.652609695440453e-10</v>
+        <v>3.263601479557342e-11</v>
       </c>
       <c r="H82" t="n">
-        <v>-5.719875769421767e-13</v>
+        <v>-9.782411274580005e-12</v>
       </c>
       <c r="I82" t="n">
-        <v>5.995206227767354e-10</v>
+        <v>5.749494396086643e-10</v>
       </c>
     </row>
     <row r="83">
@@ -3960,22 +3960,22 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>-3.642022233282358e-12</v>
+        <v>-3.483110508418477e-11</v>
       </c>
       <c r="E83" t="n">
-        <v>1.026304594379717e-11</v>
+        <v>-3.270596346706301e-11</v>
       </c>
       <c r="F83" t="n">
         <v/>
       </c>
       <c r="G83" t="n">
-        <v>3.81880714433565e-10</v>
+        <v>4.180946337269116e-11</v>
       </c>
       <c r="H83" t="n">
-        <v>-1.092173264421788e-13</v>
+        <v>3.309207317730256e-12</v>
       </c>
       <c r="I83" t="n">
-        <v>7.85623637242403e-10</v>
+        <v>9.173950130870091e-10</v>
       </c>
     </row>
     <row r="84">
@@ -3995,22 +3995,22 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>-2.731385736572677e-12</v>
+        <v>-1.060074977784742e-11</v>
       </c>
       <c r="E84" t="n">
-        <v>-1.853755724531375e-12</v>
+        <v>-1.408205238832183e-11</v>
       </c>
       <c r="F84" t="n">
         <v/>
       </c>
       <c r="G84" t="n">
-        <v>1.334636347677208e-12</v>
+        <v>2.418478980731138e-11</v>
       </c>
       <c r="H84" t="n">
-        <v>-1.862905699213153e-12</v>
+        <v>-6.105794609186956e-12</v>
       </c>
       <c r="I84" t="n">
-        <v>2.643304164348712e-12</v>
+        <v>5.16123272558087e-12</v>
       </c>
     </row>
     <row r="85">
@@ -4030,22 +4030,22 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>-6.119749546576479e-13</v>
+        <v>-5.543210160851926e-11</v>
       </c>
       <c r="E85" t="n">
-        <v>2.843594579370588e-12</v>
+        <v>-5.621608463746675e-11</v>
       </c>
       <c r="F85" t="n">
         <v/>
       </c>
       <c r="G85" t="n">
-        <v>4.406323868276404e-10</v>
+        <v>1.444625509226485e-10</v>
       </c>
       <c r="H85" t="n">
-        <v>2.040403267177624e-12</v>
+        <v>-1.73040328422352e-11</v>
       </c>
       <c r="I85" t="n">
-        <v>1.049663557759072e-09</v>
+        <v>4.850004982477932e-10</v>
       </c>
     </row>
     <row r="86">
@@ -4065,22 +4065,22 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>-1.35433143413654e-11</v>
+        <v>-4.850924541185535e-11</v>
       </c>
       <c r="E86" t="n">
-        <v>-1.041729237607469e-11</v>
+        <v>-4.726642489131185e-11</v>
       </c>
       <c r="F86" t="n">
         <v/>
       </c>
       <c r="G86" t="n">
-        <v>3.159863765624522e-10</v>
+        <v>-1.525989503575997e-11</v>
       </c>
       <c r="H86" t="n">
-        <v>-1.293367020544453e-11</v>
+        <v>-3.093516294980684e-11</v>
       </c>
       <c r="I86" t="n">
-        <v>1.378425541111357e-09</v>
+        <v>4.860727216474844e-09</v>
       </c>
     </row>
     <row r="87">
@@ -4100,22 +4100,22 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>-4.512141088280739e-12</v>
+        <v>-3.192899371820218e-11</v>
       </c>
       <c r="E87" t="n">
-        <v>-9.963563043111068e-12</v>
+        <v>-5.01345788835582e-11</v>
       </c>
       <c r="F87" t="n">
         <v/>
       </c>
       <c r="G87" t="n">
-        <v>2.647698370637047e-10</v>
+        <v>-1.799116432537737e-11</v>
       </c>
       <c r="H87" t="n">
-        <v>-1.060222509700693e-11</v>
+        <v>-2.090680477721303e-11</v>
       </c>
       <c r="I87" t="n">
-        <v>2.885767071320243e-10</v>
+        <v>1.418181848774339e-10</v>
       </c>
     </row>
     <row r="88">
@@ -4135,22 +4135,22 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>-1.313864553742535e-11</v>
+        <v>2.732280983054255e-11</v>
       </c>
       <c r="E88" t="n">
-        <v>-2.428617712446279e-12</v>
+        <v>5.388660119512945e-11</v>
       </c>
       <c r="F88" t="n">
         <v/>
       </c>
       <c r="G88" t="n">
-        <v>1.199107144795817e-09</v>
+        <v>-1.365654554470058e-11</v>
       </c>
       <c r="H88" t="n">
-        <v>-1.27415573913024e-11</v>
+        <v>-5.869137317998713e-12</v>
       </c>
       <c r="I88" t="n">
-        <v>3.039800694784695e-10</v>
+        <v>1.850517878468097e-10</v>
       </c>
     </row>
     <row r="89">
@@ -4170,22 +4170,22 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>-1.323064705023844e-11</v>
+        <v>6.38262232044145e-11</v>
       </c>
       <c r="E89" t="n">
-        <v>-9.27008209666788e-12</v>
+        <v>6.550978060574619e-11</v>
       </c>
       <c r="F89" t="n">
         <v/>
       </c>
       <c r="G89" t="n">
-        <v>2.683786241029573e-12</v>
+        <v>-2.288298607345403e-11</v>
       </c>
       <c r="H89" t="n">
-        <v>-1.35042031144444e-11</v>
+        <v>-1.838732389261924e-11</v>
       </c>
       <c r="I89" t="n">
-        <v>5.730035316233752e-13</v>
+        <v>-1.332952511208723e-11</v>
       </c>
     </row>
     <row r="90">
@@ -4205,22 +4205,22 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>-6.121443783376705e-12</v>
+        <v>-5.673191327697436e-11</v>
       </c>
       <c r="E90" t="n">
-        <v>1.893092622993221e-12</v>
+        <v>-5.754700767753461e-11</v>
       </c>
       <c r="F90" t="n">
         <v/>
       </c>
       <c r="G90" t="n">
-        <v>2.732878532443775e-09</v>
+        <v>2.068927965247206e-11</v>
       </c>
       <c r="H90" t="n">
-        <v>-5.823604418678685e-12</v>
+        <v>-2.257188643845526e-11</v>
       </c>
       <c r="I90" t="n">
-        <v>4.101264643780554e-10</v>
+        <v>1.369699851942391e-10</v>
       </c>
     </row>
     <row r="91">
@@ -4240,22 +4240,22 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>-1.432082225320302e-11</v>
+        <v>-4.771372730090029e-11</v>
       </c>
       <c r="E91" t="n">
-        <v>-1.051821637547628e-11</v>
+        <v>-4.833111014189622e-11</v>
       </c>
       <c r="F91" t="n">
         <v/>
       </c>
       <c r="G91" t="n">
-        <v>2.52077917292417e-10</v>
+        <v>-2.009061554089769e-11</v>
       </c>
       <c r="H91" t="n">
-        <v>-6.886255069150952e-12</v>
+        <v>-2.952026038191059e-12</v>
       </c>
       <c r="I91" t="n">
-        <v>2.805634489521218e-10</v>
+        <v>1.397962757901984e-10</v>
       </c>
     </row>
     <row r="92">
@@ -4275,22 +4275,22 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>-1.852224380283631e-12</v>
+        <v>-1.881814291804605e-11</v>
       </c>
       <c r="E92" t="n">
-        <v>1.288222733344332e-10</v>
+        <v>3.181099528158852e-11</v>
       </c>
       <c r="F92" t="n">
-        <v>3.961750685005583e-10</v>
+        <v>2.193320737905035e-11</v>
       </c>
       <c r="G92" t="n">
         <v/>
       </c>
       <c r="H92" t="n">
-        <v>1.264307847844471e-11</v>
+        <v>3.336601713102318e-11</v>
       </c>
       <c r="I92" t="n">
-        <v>4.907004775906134e-10</v>
+        <v>3.120426119369662e-11</v>
       </c>
     </row>
     <row r="93">
@@ -4310,22 +4310,22 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>-2.986462554014386e-12</v>
+        <v>-1.958286953374157e-11</v>
       </c>
       <c r="E93" t="n">
-        <v>1.050585762309298e-10</v>
+        <v>-2.25308232597038e-11</v>
       </c>
       <c r="F93" t="n">
-        <v>4.150403219392211e-10</v>
+        <v>1.137753302120475e-10</v>
       </c>
       <c r="G93" t="n">
         <v/>
       </c>
       <c r="H93" t="n">
-        <v>1.059188808934491e-11</v>
+        <v>2.757586113131176e-11</v>
       </c>
       <c r="I93" t="n">
-        <v>4.997050694557218e-10</v>
+        <v>2.274200745044068e-11</v>
       </c>
     </row>
     <row r="94">
@@ -4345,22 +4345,22 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>-2.880728787741902e-12</v>
+        <v>-2.048069454665419e-12</v>
       </c>
       <c r="E94" t="n">
-        <v>-1.649860826268701e-13</v>
+        <v>2.861141125044638e-11</v>
       </c>
       <c r="F94" t="n">
-        <v>1.211741835447249e-12</v>
+        <v>2.598869753626719e-11</v>
       </c>
       <c r="G94" t="n">
         <v/>
       </c>
       <c r="H94" t="n">
-        <v>1.005210307423157e-11</v>
+        <v>2.520848039947655e-11</v>
       </c>
       <c r="I94" t="n">
-        <v>4.722662490029284e-13</v>
+        <v>2.49442215123344e-11</v>
       </c>
     </row>
     <row r="95">
@@ -4380,22 +4380,22 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>-3.761429793599369e-12</v>
+        <v>-1.517186699199822e-11</v>
       </c>
       <c r="E95" t="n">
-        <v>3.834845712503878e-11</v>
+        <v>-1.115243049453674e-11</v>
       </c>
       <c r="F95" t="n">
-        <v>1.617621645406012e-10</v>
+        <v>3.077365648576753e-11</v>
       </c>
       <c r="G95" t="n">
         <v/>
       </c>
       <c r="H95" t="n">
-        <v>4.079995585243866e-11</v>
+        <v>1.12945395115016e-10</v>
       </c>
       <c r="I95" t="n">
-        <v>2.522493833080195e-10</v>
+        <v>3.611074864345543e-11</v>
       </c>
     </row>
     <row r="96">
@@ -4415,22 +4415,22 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>-1.361499676793582e-11</v>
+        <v>-3.027377935616151e-11</v>
       </c>
       <c r="E96" t="n">
-        <v>6.573445559158951e-11</v>
+        <v>-2.157957247491214e-11</v>
       </c>
       <c r="F96" t="n">
-        <v>3.021895600023472e-10</v>
+        <v>-1.734293825849159e-11</v>
       </c>
       <c r="G96" t="n">
         <v/>
       </c>
       <c r="H96" t="n">
-        <v>-1.043293908648691e-11</v>
+        <v>-3.194780924731572e-11</v>
       </c>
       <c r="I96" t="n">
-        <v>7.098717320055237e-10</v>
+        <v>1.986178483825869e-10</v>
       </c>
     </row>
     <row r="97">
@@ -4450,22 +4450,22 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>3.314784317648275e-11</v>
+        <v>4.025707404005536e-11</v>
       </c>
       <c r="E97" t="n">
-        <v>6.235546190180222e-11</v>
+        <v>-4.217025414928931e-11</v>
       </c>
       <c r="F97" t="n">
-        <v>2.659653377210077e-10</v>
+        <v>1.172469029253206e-11</v>
       </c>
       <c r="G97" t="n">
         <v/>
       </c>
       <c r="H97" t="n">
-        <v>9.390964276853155e-12</v>
+        <v>2.410326196253172e-11</v>
       </c>
       <c r="I97" t="n">
-        <v>4.277659757952853e-10</v>
+        <v>1.603464414139981e-11</v>
       </c>
     </row>
     <row r="98">
@@ -4485,22 +4485,22 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>2.698517410124216e-11</v>
+        <v>-1.563341439577671e-11</v>
       </c>
       <c r="E98" t="n">
-        <v>3.918745513622442e-10</v>
+        <v>-4.724236935427103e-11</v>
       </c>
       <c r="F98" t="n">
-        <v>8.99267707805299e-09</v>
+        <v>9.731679579496627e-11</v>
       </c>
       <c r="G98" t="n">
         <v/>
       </c>
       <c r="H98" t="n">
-        <v>2.450702012925379e-11</v>
+        <v>6.677244165631893e-11</v>
       </c>
       <c r="I98" t="n">
-        <v>3.807178433464945e-09</v>
+        <v>2.605490819575684e-11</v>
       </c>
     </row>
     <row r="99">
@@ -4520,22 +4520,22 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>2.400440388815939e-12</v>
+        <v>-6.560574015489415e-12</v>
       </c>
       <c r="E99" t="n">
-        <v>3.646482208473431e-12</v>
+        <v>-3.563333489314577e-11</v>
       </c>
       <c r="F99" t="n">
-        <v>3.203858166338743e-12</v>
+        <v>-2.831102916094371e-12</v>
       </c>
       <c r="G99" t="n">
         <v/>
       </c>
       <c r="H99" t="n">
-        <v>3.487555360034312e-13</v>
+        <v>-1.741947587369938e-12</v>
       </c>
       <c r="I99" t="n">
-        <v>1.783123666788287e-12</v>
+        <v>-3.746467927979492e-12</v>
       </c>
     </row>
     <row r="100">
@@ -4555,22 +4555,22 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>7.597800042570684e-12</v>
+        <v>2.12603472783903e-11</v>
       </c>
       <c r="E100" t="n">
-        <v>6.723035030278306e-11</v>
+        <v>-2.781288958699774e-11</v>
       </c>
       <c r="F100" t="n">
-        <v>2.814147260290519e-10</v>
+        <v>3.985550620540912e-11</v>
       </c>
       <c r="G100" t="n">
         <v/>
       </c>
       <c r="H100" t="n">
-        <v>3.199636978029563e-11</v>
+        <v>8.792661356340692e-11</v>
       </c>
       <c r="I100" t="n">
-        <v>4.520501875766298e-10</v>
+        <v>3.527708635426218e-11</v>
       </c>
     </row>
     <row r="101">
@@ -4590,22 +4590,22 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>-1.236694681657443e-11</v>
+        <v>6.520991189964243e-12</v>
       </c>
       <c r="E101" t="n">
-        <v>1.105130706541685e-10</v>
+        <v>-2.1145800064689e-11</v>
       </c>
       <c r="F101" t="n">
-        <v>7.582667326186402e-10</v>
+        <v>-1.278941936837381e-11</v>
       </c>
       <c r="G101" t="n">
         <v/>
       </c>
       <c r="H101" t="n">
-        <v>-1.344800119229045e-11</v>
+        <v>-4.041174216905964e-11</v>
       </c>
       <c r="I101" t="n">
-        <v>8.155345179344452e-09</v>
+        <v>1.454514566430028e-10</v>
       </c>
     </row>
     <row r="102">
@@ -4625,22 +4625,22 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>3.013151137324573e-11</v>
+        <v>4.837614063877744e-11</v>
       </c>
       <c r="E102" t="n">
-        <v>7.320507832251943e-11</v>
+        <v>-1.908266670019756e-11</v>
       </c>
       <c r="F102" t="n">
-        <v>2.619709381729164e-10</v>
+        <v>-1.69623345310272e-11</v>
       </c>
       <c r="G102" t="n">
         <v/>
       </c>
       <c r="H102" t="n">
-        <v>7.298329088900063e-12</v>
+        <v>1.820090693101538e-11</v>
       </c>
       <c r="I102" t="n">
-        <v>4.230022962846799e-10</v>
+        <v>1.856781388076153e-11</v>
       </c>
     </row>
     <row r="103">
@@ -4660,22 +4660,22 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>2.843867085287926e-11</v>
+        <v>-7.668822864758332e-12</v>
       </c>
       <c r="E103" t="n">
-        <v>1.760388957652975e-09</v>
+        <v>1.845243515891687e-11</v>
       </c>
       <c r="F103" t="n">
-        <v>2.303677955870526e-09</v>
+        <v>-1.214829640285829e-11</v>
       </c>
       <c r="G103" t="n">
         <v/>
       </c>
       <c r="H103" t="n">
-        <v>2.379277943086128e-11</v>
+        <v>6.475739984214816e-11</v>
       </c>
       <c r="I103" t="n">
-        <v>2.318405556787043e-09</v>
+        <v>4.303241421226112e-11</v>
       </c>
     </row>
     <row r="104">
@@ -4695,22 +4695,22 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>3.841774753760416e-12</v>
+        <v>2.559744570192717e-11</v>
       </c>
       <c r="E104" t="n">
-        <v>4.971672525389736e-12</v>
+        <v>4.438760474713425e-11</v>
       </c>
       <c r="F104" t="n">
-        <v>3.012765812483432e-12</v>
+        <v>-1.592025010741757e-11</v>
       </c>
       <c r="G104" t="n">
         <v/>
       </c>
       <c r="H104" t="n">
-        <v>1.365305685625633e-12</v>
+        <v>1.089577676993926e-12</v>
       </c>
       <c r="I104" t="n">
-        <v>1.713408531532262e-12</v>
+        <v>1.071053128064137e-11</v>
       </c>
     </row>
     <row r="105">
@@ -4730,22 +4730,22 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1.075733389068498e-11</v>
+        <v>7.715515051412687e-12</v>
       </c>
       <c r="E105" t="n">
-        <v>8.00967480583074e-11</v>
+        <v>-3.563792372204337e-12</v>
       </c>
       <c r="F105" t="n">
-        <v>2.748886745955121e-10</v>
+        <v>-7.789128861175951e-12</v>
       </c>
       <c r="G105" t="n">
         <v/>
       </c>
       <c r="H105" t="n">
-        <v>3.926794672348954e-11</v>
+        <v>1.084295469633233e-10</v>
       </c>
       <c r="I105" t="n">
-        <v>4.500900347273686e-10</v>
+        <v>3.89836866078802e-11</v>
       </c>
     </row>
     <row r="106">
@@ -4765,22 +4765,22 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>-1.170455674362505e-11</v>
+        <v>-1.394825653108085e-11</v>
       </c>
       <c r="E106" t="n">
-        <v>1.56302298917759e-10</v>
+        <v>-7.621201017919233e-12</v>
       </c>
       <c r="F106" t="n">
-        <v>8.571084501193943e-10</v>
+        <v>-3.460426590912463e-11</v>
       </c>
       <c r="G106" t="n">
         <v/>
       </c>
       <c r="H106" t="n">
-        <v>-1.310905588869292e-11</v>
+        <v>-3.946403462191095e-11</v>
       </c>
       <c r="I106" t="n">
-        <v>0.0004356461341270531</v>
+        <v>1.242510070051676e-10</v>
       </c>
     </row>
     <row r="107">
@@ -4800,22 +4800,22 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>5.657315532588498e-10</v>
+        <v>-2.631517483850029e-11</v>
       </c>
       <c r="E107" t="n">
-        <v>9.796370011475744e-11</v>
+        <v>1.288112389759367e-10</v>
       </c>
       <c r="F107" t="n">
-        <v>3.138582824094447e-10</v>
+        <v>1.811578432063732e-10</v>
       </c>
       <c r="G107" t="n">
         <v/>
       </c>
       <c r="H107" t="n">
-        <v>5.29804403046235e-11</v>
+        <v>1.471855728337537e-10</v>
       </c>
       <c r="I107" t="n">
-        <v>6.01190420060099e-10</v>
+        <v>2.983780651601949e-10</v>
       </c>
     </row>
     <row r="108">
@@ -4835,22 +4835,22 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>3.313276165622682e-11</v>
+        <v>4.051517359314754e-11</v>
       </c>
       <c r="E108" t="n">
-        <v>0.1502304975748493</v>
+        <v>1.009043085219943e-09</v>
       </c>
       <c r="F108" t="n">
-        <v>5.435696030914787e-09</v>
+        <v>8.969681996268351e-11</v>
       </c>
       <c r="G108" t="n">
         <v/>
       </c>
       <c r="H108" t="n">
-        <v>2.49723665862459e-11</v>
+        <v>6.81963847848913e-11</v>
       </c>
       <c r="I108" t="n">
-        <v>9.096571573723583e-09</v>
+        <v>1.419149946915289e-10</v>
       </c>
     </row>
     <row r="109">
@@ -4870,22 +4870,22 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>3.70910186277706e-11</v>
+        <v>1.122683483720751e-10</v>
       </c>
       <c r="E109" t="n">
-        <v>1.255622632044216e-09</v>
+        <v>1.57931737032046e-10</v>
       </c>
       <c r="F109" t="n">
-        <v>0.1636353323252659</v>
+        <v>-5.13381215834523e-11</v>
       </c>
       <c r="G109" t="n">
         <v/>
       </c>
       <c r="H109" t="n">
-        <v>2.930102143986313e-11</v>
+        <v>8.046090805688557e-11</v>
       </c>
       <c r="I109" t="n">
-        <v>0.0004356440753528661</v>
+        <v>1.99752939197699e-10</v>
       </c>
     </row>
     <row r="110">
@@ -4905,22 +4905,22 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>4.322408485529103e-11</v>
+        <v>5.958021157436902e-11</v>
       </c>
       <c r="E110" t="n">
-        <v>9.80442499801536e-11</v>
+        <v>8.422130830705205e-11</v>
       </c>
       <c r="F110" t="n">
-        <v>3.113672416789591e-10</v>
+        <v>1.527503698800835e-10</v>
       </c>
       <c r="G110" t="n">
         <v/>
       </c>
       <c r="H110" t="n">
-        <v>2.502310628126743e-10</v>
+        <v>7.19435715213408e-10</v>
       </c>
       <c r="I110" t="n">
-        <v>5.929119393518056e-10</v>
+        <v>2.586044417662403e-10</v>
       </c>
     </row>
     <row r="111">
@@ -4940,22 +4940,22 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>4.119997696469893e-12</v>
+        <v>1.629610819564825e-11</v>
       </c>
       <c r="E111" t="n">
-        <v>3.005807825766199e-10</v>
+        <v>4.987223403225309e-11</v>
       </c>
       <c r="F111" t="n">
-        <v>1.573135541015103e-09</v>
+        <v>2.942165011540489e-11</v>
       </c>
       <c r="G111" t="n">
         <v/>
       </c>
       <c r="H111" t="n">
-        <v>4.000650489899704e-13</v>
+        <v>-1.565754965982796e-12</v>
       </c>
       <c r="I111" t="n">
-        <v>0.0008728292120616338</v>
+        <v>7.217088127701322e-11</v>
       </c>
     </row>
     <row r="112">
@@ -4975,22 +4975,22 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>2.969454388743586e-11</v>
+        <v>4.991631250489599e-11</v>
       </c>
       <c r="E112" t="n">
-        <v>3.854351963906839e-11</v>
+        <v>-2.551040468429436e-11</v>
       </c>
       <c r="F112" t="n">
-        <v>1.62911600560082e-10</v>
+        <v>1.898959789124906e-11</v>
       </c>
       <c r="G112" t="n">
         <v/>
       </c>
       <c r="H112" t="n">
-        <v>4.208698858053471e-12</v>
+        <v>8.72309042892107e-12</v>
       </c>
       <c r="I112" t="n">
-        <v>2.561054003096062e-10</v>
+        <v>3.051719805164604e-11</v>
       </c>
     </row>
     <row r="113">
@@ -5010,22 +5010,22 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>9.747086622882895e-12</v>
+        <v>2.302694672664803e-11</v>
       </c>
       <c r="E113" t="n">
-        <v>1.323448070554874e-10</v>
+        <v>9.636922199379666e-11</v>
       </c>
       <c r="F113" t="n">
-        <v>4.026555106254156e-10</v>
+        <v>4.312764659927173e-11</v>
       </c>
       <c r="G113" t="n">
         <v/>
       </c>
       <c r="H113" t="n">
-        <v>4.148757694184307e-12</v>
+        <v>8.575274392931154e-12</v>
       </c>
       <c r="I113" t="n">
-        <v>5.059084848122542e-10</v>
+        <v>5.201705443649749e-11</v>
       </c>
     </row>
     <row r="114">
@@ -5045,22 +5045,22 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1.192226668815149e-11</v>
+        <v>-2.688758983711221e-13</v>
       </c>
       <c r="E114" t="n">
-        <v>1.110218174431714e-10</v>
+        <v>-2.466660912970912e-11</v>
       </c>
       <c r="F114" t="n">
-        <v>4.250325368829987e-10</v>
+        <v>1.448526628151321e-10</v>
       </c>
       <c r="G114" t="n">
         <v/>
       </c>
       <c r="H114" t="n">
-        <v>6.535462565340104e-12</v>
+        <v>1.520071350811024e-11</v>
       </c>
       <c r="I114" t="n">
-        <v>5.269946141002513e-10</v>
+        <v>3.787371160664836e-11</v>
       </c>
     </row>
     <row r="115">
@@ -5080,22 +5080,22 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>6.556313613629373e-12</v>
+        <v>1.147423567508647e-12</v>
       </c>
       <c r="E115" t="n">
-        <v>9.607793915640481e-14</v>
+        <v>-1.009702213535837e-11</v>
       </c>
       <c r="F115" t="n">
-        <v>1.316198429316276e-12</v>
+        <v>1.050883664570471e-11</v>
       </c>
       <c r="G115" t="n">
         <v/>
       </c>
       <c r="H115" t="n">
-        <v>1.585459767747432e-12</v>
+        <v>1.614065317533363e-12</v>
       </c>
       <c r="I115" t="n">
-        <v>5.614599997854568e-13</v>
+        <v>1.686829620017237e-11</v>
       </c>
     </row>
     <row r="116">
@@ -5115,22 +5115,22 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>-1.11575258009076e-11</v>
+        <v>-2.033273012250759e-11</v>
       </c>
       <c r="E116" t="n">
-        <v>6.413836273948584e-11</v>
+        <v>-2.574251811119555e-11</v>
       </c>
       <c r="F116" t="n">
-        <v>2.967553673291825e-10</v>
+        <v>-1.912039142584744e-11</v>
       </c>
       <c r="G116" t="n">
         <v/>
       </c>
       <c r="H116" t="n">
-        <v>-1.306541740068582e-11</v>
+        <v>-3.952477292929637e-11</v>
       </c>
       <c r="I116" t="n">
-        <v>6.946904861064468e-10</v>
+        <v>1.820430143252641e-10</v>
       </c>
     </row>
     <row r="117">
@@ -5150,22 +5150,22 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>-4.718338081032707e-12</v>
+        <v>4.215658502106088e-12</v>
       </c>
       <c r="E117" t="n">
-        <v>6.573101622069174e-11</v>
+        <v>-3.688833314023185e-11</v>
       </c>
       <c r="F117" t="n">
-        <v>2.716726979550507e-10</v>
+        <v>-1.978184350470406e-11</v>
       </c>
       <c r="G117" t="n">
         <v/>
       </c>
       <c r="H117" t="n">
-        <v>-1.022434612045843e-11</v>
+        <v>-3.106488762670913e-11</v>
       </c>
       <c r="I117" t="n">
-        <v>2.449348361590223e-10</v>
+        <v>-4.987863405143686e-11</v>
       </c>
     </row>
     <row r="118">
@@ -5185,22 +5185,22 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>-1.170198385928527e-11</v>
+        <v>8.789269559920265e-12</v>
       </c>
       <c r="E118" t="n">
-        <v>3.531205511379167e-10</v>
+        <v>1.001991494973503e-10</v>
       </c>
       <c r="F118" t="n">
-        <v>1.763323166677056e-09</v>
+        <v>-9.332907529169409e-12</v>
       </c>
       <c r="G118" t="n">
         <v/>
       </c>
       <c r="H118" t="n">
-        <v>-1.276187365962038e-11</v>
+        <v>-3.824644872516505e-11</v>
       </c>
       <c r="I118" t="n">
-        <v>4.325368069345439e-10</v>
+        <v>-4.909709712887882e-11</v>
       </c>
     </row>
     <row r="119">
@@ -5220,22 +5220,22 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>-1.154726273608199e-11</v>
+        <v>-1.671116654767803e-11</v>
       </c>
       <c r="E119" t="n">
-        <v>2.113871783956855e-10</v>
+        <v>-3.091955547207932e-11</v>
       </c>
       <c r="F119" t="n">
-        <v>1.489993322430741e-09</v>
+        <v>9.657675959136643e-12</v>
       </c>
       <c r="G119" t="n">
         <v/>
       </c>
       <c r="H119" t="n">
-        <v>-1.232008718361786e-11</v>
+        <v>-3.699652756105482e-11</v>
       </c>
       <c r="I119" t="n">
-        <v>4.181073047801347e-10</v>
+        <v>-5.087811346271206e-11</v>
       </c>
     </row>
     <row r="120">
@@ -5255,22 +5255,22 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>-6.509051714327231e-12</v>
+        <v>-1.813629800423202e-11</v>
       </c>
       <c r="E120" t="n">
-        <v>4.605445373147586e-12</v>
+        <v>-2.726859059866909e-11</v>
       </c>
       <c r="F120" t="n">
-        <v>3.228057039045367e-12</v>
+        <v>-1.774623858712121e-11</v>
       </c>
       <c r="G120" t="n">
         <v/>
       </c>
       <c r="H120" t="n">
-        <v>-7.779329732324598e-12</v>
+        <v>-2.422162090671133e-11</v>
       </c>
       <c r="I120" t="n">
-        <v>2.777892222771264e-13</v>
+        <v>-4.877644627582113e-11</v>
       </c>
     </row>
     <row r="121">
@@ -5290,22 +5290,22 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>-1.10551039839296e-11</v>
+        <v>-1.989513013312746e-11</v>
       </c>
       <c r="E121" t="n">
-        <v>6.242477935057838e-11</v>
+        <v>-3.133952791983093e-11</v>
       </c>
       <c r="F121" t="n">
-        <v>2.592384069830124e-10</v>
+        <v>-1.723205118494358e-11</v>
       </c>
       <c r="G121" t="n">
         <v/>
       </c>
       <c r="H121" t="n">
-        <v>-7.189005188725964e-12</v>
+        <v>-2.238462911392261e-11</v>
       </c>
       <c r="I121" t="n">
-        <v>2.369589003649994e-10</v>
+        <v>-4.965668875180225e-11</v>
       </c>
     </row>
     <row r="122">
@@ -5325,22 +5325,22 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>-1.869780948774591e-12</v>
+        <v>-1.421100942454967e-11</v>
       </c>
       <c r="E122" t="n">
-        <v>3.225491922858641e-11</v>
+        <v>3.734276113342294e-11</v>
       </c>
       <c r="F122" t="n">
-        <v>1.012349360477326e-11</v>
+        <v>5.04350508909099e-12</v>
       </c>
       <c r="G122" t="n">
-        <v>1.143340178830576e-11</v>
+        <v>2.928082961064286e-11</v>
       </c>
       <c r="H122" t="n">
         <v/>
       </c>
       <c r="I122" t="n">
-        <v>2.48427709193629e-09</v>
+        <v>2.840842975364916e-10</v>
       </c>
     </row>
     <row r="123">
@@ -5360,22 +5360,22 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>-3.155531465098936e-12</v>
+        <v>-1.340294817424956e-11</v>
       </c>
       <c r="E123" t="n">
-        <v>9.799155071282807e-12</v>
+        <v>6.112370086994416e-12</v>
       </c>
       <c r="F123" t="n">
-        <v>2.153685853755272e-11</v>
+        <v>5.498303233179014e-11</v>
       </c>
       <c r="G123" t="n">
-        <v>9.172991362741445e-12</v>
+        <v>2.294364632809383e-11</v>
       </c>
       <c r="H123" t="n">
         <v/>
       </c>
       <c r="I123" t="n">
-        <v>2.498657228700181e-09</v>
+        <v>2.676991070427755e-10</v>
       </c>
     </row>
     <row r="124">
@@ -5395,22 +5395,22 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>-7.682981364383555e-13</v>
+        <v>-6.509737255122353e-12</v>
       </c>
       <c r="E124" t="n">
-        <v>1.007207281980324e-11</v>
+        <v>1.325835642877809e-11</v>
       </c>
       <c r="F124" t="n">
-        <v>8.830002749299252e-12</v>
+        <v>1.828446307856268e-11</v>
       </c>
       <c r="G124" t="n">
-        <v>5.041058648246778e-11</v>
+        <v>1.392487115871123e-10</v>
       </c>
       <c r="H124" t="n">
         <v/>
       </c>
       <c r="I124" t="n">
-        <v>2.587595333953786e-09</v>
+        <v>3.9089367273524e-10</v>
       </c>
     </row>
     <row r="125">
@@ -5430,22 +5430,22 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>-4.927518164774273e-12</v>
+        <v>-1.512461254109508e-11</v>
       </c>
       <c r="E125" t="n">
-        <v>2.757836164679788e-12</v>
+        <v>8.102075374231535e-12</v>
       </c>
       <c r="F125" t="n">
-        <v>3.359842617096028e-12</v>
+        <v>8.037338364097724e-12</v>
       </c>
       <c r="G125" t="n">
-        <v>6.691741005912081e-12</v>
+        <v>1.507339783011337e-11</v>
       </c>
       <c r="H125" t="n">
         <v/>
       </c>
       <c r="I125" t="n">
-        <v>7.630071275826918e-13</v>
+        <v>6.676758175537582e-12</v>
       </c>
     </row>
     <row r="126">
@@ -5465,22 +5465,22 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>-1.306722016207867e-11</v>
+        <v>-3.29891092203015e-11</v>
       </c>
       <c r="E126" t="n">
-        <v>-9.36385488399078e-12</v>
+        <v>-1.40141675428574e-11</v>
       </c>
       <c r="F126" t="n">
-        <v>-1.045983454944253e-11</v>
+        <v>-1.852116329199579e-11</v>
       </c>
       <c r="G126" t="n">
-        <v>-8.880135813106292e-12</v>
+        <v>-2.784615025972617e-11</v>
       </c>
       <c r="H126" t="n">
         <v/>
       </c>
       <c r="I126" t="n">
-        <v>2.81809365235369e-09</v>
+        <v>5.543608021259822e-09</v>
       </c>
     </row>
     <row r="127">
@@ -5500,22 +5500,22 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>5.060843867852795e-11</v>
+        <v>1.352355620911471e-10</v>
       </c>
       <c r="E127" t="n">
-        <v>-9.154334122627234e-13</v>
+        <v>-1.263704379848964e-11</v>
       </c>
       <c r="F127" t="n">
-        <v>5.726773217253471e-12</v>
+        <v>1.283412452961273e-11</v>
       </c>
       <c r="G127" t="n">
-        <v>1.475060139040742e-11</v>
+        <v>3.867449897326755e-11</v>
       </c>
       <c r="H127" t="n">
         <v/>
       </c>
       <c r="I127" t="n">
-        <v>2.116794036181124e-09</v>
+        <v>3.34299760749753e-10</v>
       </c>
     </row>
     <row r="128">
@@ -5535,22 +5535,22 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>2.683519270324667e-11</v>
+        <v>2.203538323399357e-11</v>
       </c>
       <c r="E128" t="n">
-        <v>1.159588771254414e-11</v>
+        <v>-1.79718695157e-11</v>
       </c>
       <c r="F128" t="n">
-        <v>6.389986107112188e-11</v>
+        <v>5.307390030070084e-11</v>
       </c>
       <c r="G128" t="n">
-        <v>2.641394306802722e-11</v>
+        <v>7.131723604949129e-11</v>
       </c>
       <c r="H128" t="n">
         <v/>
       </c>
       <c r="I128" t="n">
-        <v>2.971240006246539e-08</v>
+        <v>3.423602640622403e-10</v>
       </c>
     </row>
     <row r="129">
@@ -5570,22 +5570,22 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>5.92420588438562e-12</v>
+        <v>5.518692178415103e-12</v>
       </c>
       <c r="E129" t="n">
-        <v>-2.523560248491687e-12</v>
+        <v>-2.209123111248218e-11</v>
       </c>
       <c r="F129" t="n">
-        <v>2.590222127553733e-12</v>
+        <v>-2.217099427504403e-12</v>
       </c>
       <c r="G129" t="n">
-        <v>2.464174559511257e-11</v>
+        <v>6.664440969007537e-11</v>
       </c>
       <c r="H129" t="n">
         <v/>
       </c>
       <c r="I129" t="n">
-        <v>1.696410622638517e-08</v>
+        <v>2.92285812116658e-10</v>
       </c>
     </row>
     <row r="130">
@@ -5605,22 +5605,22 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>5.677067012971517e-12</v>
+        <v>2.525219917142191e-11</v>
       </c>
       <c r="E130" t="n">
-        <v>-2.7299146540635e-12</v>
+        <v>4.459403273525993e-13</v>
       </c>
       <c r="F130" t="n">
-        <v>4.227332424200629e-12</v>
+        <v>2.886085724826667e-11</v>
       </c>
       <c r="G130" t="n">
-        <v>6.591798077196274e-12</v>
+        <v>1.484004046437236e-11</v>
       </c>
       <c r="H130" t="n">
         <v/>
       </c>
       <c r="I130" t="n">
-        <v>1.086349921965517e-12</v>
+        <v>9.103457820511525e-12</v>
       </c>
     </row>
     <row r="131">
@@ -5640,22 +5640,22 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>-1.157730605451179e-11</v>
+        <v>-1.261283046184392e-11</v>
       </c>
       <c r="E131" t="n">
-        <v>-1.362309574950763e-11</v>
+        <v>-1.019538516685605e-11</v>
       </c>
       <c r="F131" t="n">
-        <v>-1.260959942756859e-11</v>
+        <v>-2.005827370687884e-12</v>
       </c>
       <c r="G131" t="n">
-        <v>-1.164409739088239e-11</v>
+        <v>-3.555566847898666e-11</v>
       </c>
       <c r="H131" t="n">
         <v/>
       </c>
       <c r="I131" t="n">
-        <v>1.924291073002012e-08</v>
+        <v>5.04811178111681e-09</v>
       </c>
     </row>
     <row r="132">
@@ -5675,22 +5675,22 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>4.672378459830957e-11</v>
+        <v>1.175374496882377e-10</v>
       </c>
       <c r="E132" t="n">
-        <v>6.289283860419325e-12</v>
+        <v>7.165743917626384e-12</v>
       </c>
       <c r="F132" t="n">
-        <v>-2.068066221309772e-12</v>
+        <v>-1.355457157861463e-11</v>
       </c>
       <c r="G132" t="n">
-        <v>1.266554376091069e-11</v>
+        <v>3.281743862821347e-11</v>
       </c>
       <c r="H132" t="n">
         <v/>
       </c>
       <c r="I132" t="n">
-        <v>2.140145123041731e-09</v>
+        <v>3.311709936615954e-10</v>
       </c>
     </row>
     <row r="133">
@@ -5710,22 +5710,22 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>3.015032214687774e-11</v>
+        <v>2.028286041007692e-11</v>
       </c>
       <c r="E133" t="n">
-        <v>9.091217493164315e-11</v>
+        <v>3.2920208047759e-11</v>
       </c>
       <c r="F133" t="n">
-        <v>1.112080703618825e-11</v>
+        <v>-1.572121907952859e-11</v>
       </c>
       <c r="G133" t="n">
-        <v>2.74006821526606e-11</v>
+        <v>7.408649334738182e-11</v>
       </c>
       <c r="H133" t="n">
         <v/>
       </c>
       <c r="I133" t="n">
-        <v>1.766923414493053e-08</v>
+        <v>3.762580812278516e-10</v>
       </c>
     </row>
     <row r="134">
@@ -5745,22 +5745,22 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>8.08452477785249e-12</v>
+        <v>2.034779998552208e-11</v>
       </c>
       <c r="E134" t="n">
-        <v>6.22357546216407e-12</v>
+        <v>1.280511286171801e-11</v>
       </c>
       <c r="F134" t="n">
-        <v>-2.444514301152945e-12</v>
+        <v>-1.049266121420483e-11</v>
       </c>
       <c r="G134" t="n">
-        <v>2.881720296253459e-11</v>
+        <v>7.845866847742842e-11</v>
       </c>
       <c r="H134" t="n">
         <v/>
       </c>
       <c r="I134" t="n">
-        <v>1.465517805214213e-08</v>
+        <v>3.588569024500118e-10</v>
       </c>
     </row>
     <row r="135">
@@ -5780,22 +5780,22 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>8.755704254801498e-12</v>
+        <v>1.591174142712422e-11</v>
       </c>
       <c r="E135" t="n">
-        <v>6.748698694390039e-12</v>
+        <v>1.364728532208344e-11</v>
       </c>
       <c r="F135" t="n">
-        <v>-7.107719845917344e-13</v>
+        <v>-1.134994822140387e-11</v>
       </c>
       <c r="G135" t="n">
-        <v>9.262135746186315e-12</v>
+        <v>2.213732284408555e-11</v>
       </c>
       <c r="H135" t="n">
         <v/>
       </c>
       <c r="I135" t="n">
-        <v>1.089733398170698e-12</v>
+        <v>9.415982436548118e-12</v>
       </c>
     </row>
     <row r="136">
@@ -5815,22 +5815,22 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>-1.087393805538601e-11</v>
+        <v>-2.088244882551194e-11</v>
       </c>
       <c r="E136" t="n">
-        <v>-1.071863999768783e-11</v>
+        <v>-9.509157231121172e-12</v>
       </c>
       <c r="F136" t="n">
-        <v>-1.397478805852051e-11</v>
+        <v>-2.982254721608606e-11</v>
       </c>
       <c r="G136" t="n">
-        <v>-1.115309699642519e-11</v>
+        <v>-3.418850968568723e-11</v>
       </c>
       <c r="H136" t="n">
         <v/>
       </c>
       <c r="I136" t="n">
-        <v>5.467903126744367e-08</v>
+        <v>2.966913411485924e-09</v>
       </c>
     </row>
     <row r="137">
@@ -5850,22 +5850,22 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>5.63661237549569e-11</v>
+        <v>1.27883136053586e-10</v>
       </c>
       <c r="E137" t="n">
-        <v>1.265953436142074e-11</v>
+        <v>1.218432689186564e-11</v>
       </c>
       <c r="F137" t="n">
-        <v>1.01772054760457e-11</v>
+        <v>1.279960070302192e-11</v>
       </c>
       <c r="G137" t="n">
-        <v>1.491997793315566e-12</v>
+        <v>7.043480448026364e-13</v>
       </c>
       <c r="H137" t="n">
         <v/>
       </c>
       <c r="I137" t="n">
-        <v>2.160047600694229e-09</v>
+        <v>2.849439510873597e-10</v>
       </c>
     </row>
     <row r="138">
@@ -5885,22 +5885,22 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>5.050434509701925e-12</v>
+        <v>-4.450326489581734e-12</v>
       </c>
       <c r="E138" t="n">
-        <v>2.909478664462964e-11</v>
+        <v>1.433438946529942e-11</v>
       </c>
       <c r="F138" t="n">
-        <v>7.013115477114822e-12</v>
+        <v>-9.657066745440941e-12</v>
       </c>
       <c r="G138" t="n">
-        <v>-4.536494565589813e-12</v>
+        <v>-1.600125870762985e-11</v>
       </c>
       <c r="H138" t="n">
         <v/>
       </c>
       <c r="I138" t="n">
-        <v>1.031374228394586e-08</v>
+        <v>1.966378057701089e-10</v>
       </c>
     </row>
     <row r="139">
@@ -5920,22 +5920,22 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>5.845156404921857e-12</v>
+        <v>1.153479609094692e-11</v>
       </c>
       <c r="E139" t="n">
-        <v>1.217977530910884e-11</v>
+        <v>1.229369141560049e-11</v>
       </c>
       <c r="F139" t="n">
-        <v>2.241049014267029e-11</v>
+        <v>5.856024434115502e-11</v>
       </c>
       <c r="G139" t="n">
-        <v>-3.888864379251092e-12</v>
+        <v>-1.419890498913878e-11</v>
       </c>
       <c r="H139" t="n">
         <v/>
       </c>
       <c r="I139" t="n">
-        <v>1.225363510457695e-08</v>
+        <v>2.208512503673811e-10</v>
       </c>
     </row>
     <row r="140">
@@ -5955,22 +5955,22 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>5.50195869350916e-12</v>
+        <v>-2.262643246535848e-13</v>
       </c>
       <c r="E140" t="n">
-        <v>7.284929611063982e-12</v>
+        <v>-3.313412582032049e-12</v>
       </c>
       <c r="F140" t="n">
-        <v>6.785174783155434e-12</v>
+        <v>-3.628393386463173e-12</v>
       </c>
       <c r="G140" t="n">
-        <v>-3.340427916264245e-12</v>
+        <v>-1.26332251832357e-11</v>
       </c>
       <c r="H140" t="n">
         <v/>
       </c>
       <c r="I140" t="n">
-        <v>1.05581422165221e-12</v>
+        <v>2.743023536678235e-12</v>
       </c>
     </row>
     <row r="141">
@@ -5990,22 +5990,22 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>-5.044409744194433e-12</v>
+        <v>-1.776630105423953e-11</v>
       </c>
       <c r="E141" t="n">
-        <v>-3.524245272267491e-12</v>
+        <v>-1.614122108638578e-11</v>
       </c>
       <c r="F141" t="n">
-        <v>-5.504415602022949e-12</v>
+        <v>-1.935276503002892e-11</v>
       </c>
       <c r="G141" t="n">
-        <v>-9.957287437663564e-12</v>
+        <v>-3.114981317213507e-11</v>
       </c>
       <c r="H141" t="n">
         <v/>
       </c>
       <c r="I141" t="n">
-        <v>7.469261033687977e-08</v>
+        <v>1.484487803361589e-08</v>
       </c>
     </row>
     <row r="142">
@@ -6025,22 +6025,22 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>3.713202107573388e-09</v>
+        <v>-6.342752864079842e-11</v>
       </c>
       <c r="E142" t="n">
-        <v>3.670312972691601e-11</v>
+        <v>6.230321678024661e-11</v>
       </c>
       <c r="F142" t="n">
-        <v>3.014599703067763e-11</v>
+        <v>7.513640072192333e-11</v>
       </c>
       <c r="G142" t="n">
-        <v>4.970903871081036e-11</v>
+        <v>1.366410228696927e-10</v>
       </c>
       <c r="H142" t="n">
         <v/>
       </c>
       <c r="I142" t="n">
-        <v>2.379838178768477e-09</v>
+        <v>5.515418601539209e-09</v>
       </c>
     </row>
     <row r="143">
@@ -6060,22 +6060,22 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>5.616644657912276e-11</v>
+        <v>1.909954618484426e-10</v>
       </c>
       <c r="E143" t="n">
-        <v>3.236787868664098e-10</v>
+        <v>4.623591429929488e-10</v>
       </c>
       <c r="F143" t="n">
-        <v>4.736830623941477e-11</v>
+        <v>1.18284995244398e-10</v>
       </c>
       <c r="G143" t="n">
-        <v>3.930989414926364e-11</v>
+        <v>1.073288304176106e-10</v>
       </c>
       <c r="H143" t="n">
         <v/>
       </c>
       <c r="I143" t="n">
-        <v>3.363565376883933e-08</v>
+        <v>5.145909598358408e-09</v>
       </c>
     </row>
     <row r="144">
@@ -6095,22 +6095,22 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>6.518821127535168e-11</v>
+        <v>1.55733635618867e-10</v>
       </c>
       <c r="E144" t="n">
-        <v>7.583436817368806e-11</v>
+        <v>7.067925497407832e-11</v>
       </c>
       <c r="F144" t="n">
-        <v>1.955865411428328e-10</v>
+        <v>-5.295330972898874e-12</v>
       </c>
       <c r="G144" t="n">
-        <v>4.78121159255924e-11</v>
+        <v>1.310825491773446e-10</v>
       </c>
       <c r="H144" t="n">
         <v/>
       </c>
       <c r="I144" t="n">
-        <v>4.1125567754691e-08</v>
+        <v>3.191348844818083e-09</v>
       </c>
     </row>
     <row r="145">
@@ -6130,22 +6130,22 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>6.009996096195697e-11</v>
+        <v>1.146294998634321e-10</v>
       </c>
       <c r="E145" t="n">
-        <v>4.832341044591027e-11</v>
+        <v>3.6854239693443e-11</v>
       </c>
       <c r="F145" t="n">
-        <v>3.818886296424535e-11</v>
+        <v>5.263106598111013e-11</v>
       </c>
       <c r="G145" t="n">
-        <v>2.58351456067247e-10</v>
+        <v>7.365842470887464e-10</v>
       </c>
       <c r="H145" t="n">
         <v/>
       </c>
       <c r="I145" t="n">
-        <v>6.051289567681254e-08</v>
+        <v>1.447167398996584e-08</v>
       </c>
     </row>
     <row r="146">
@@ -6165,22 +6165,22 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>-3.557051488784981e-12</v>
+        <v>1.017933977531867e-11</v>
       </c>
       <c r="E146" t="n">
-        <v>-3.557384927751069e-12</v>
+        <v>1.248705418105166e-11</v>
       </c>
       <c r="F146" t="n">
-        <v>-6.030565645760382e-12</v>
+        <v>4.926286042749723e-12</v>
       </c>
       <c r="G146" t="n">
-        <v>-5.036002400232045e-12</v>
+        <v>-1.708213528410146e-11</v>
       </c>
       <c r="H146" t="n">
         <v/>
       </c>
       <c r="I146" t="n">
-        <v>0.003112450983744927</v>
+        <v>1.284447150028766e-09</v>
       </c>
     </row>
     <row r="147">
@@ -6200,22 +6200,22 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>-3.507002590842806e-12</v>
+        <v>8.644402421972942e-12</v>
       </c>
       <c r="E147" t="n">
-        <v>-9.21638613597527e-12</v>
+        <v>-1.821484830943995e-11</v>
       </c>
       <c r="F147" t="n">
-        <v>-1.059154654312879e-11</v>
+        <v>-1.938837880482984e-11</v>
       </c>
       <c r="G147" t="n">
-        <v>-9.788596829123487e-12</v>
+        <v>-3.013687341974267e-11</v>
       </c>
       <c r="H147" t="n">
         <v/>
       </c>
       <c r="I147" t="n">
-        <v>1.592561375385901e-09</v>
+        <v>2.712854971201221e-11</v>
       </c>
     </row>
     <row r="148">
@@ -6235,22 +6235,22 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>-1.202982406392952e-11</v>
+        <v>-1.718798013293492e-11</v>
       </c>
       <c r="E148" t="n">
-        <v>-6.719342865919235e-12</v>
+        <v>3.527674273137069e-11</v>
       </c>
       <c r="F148" t="n">
-        <v>-1.17911329446016e-11</v>
+        <v>-7.404259229578872e-12</v>
       </c>
       <c r="G148" t="n">
-        <v>-1.285349278478005e-11</v>
+        <v>-3.87743779697887e-11</v>
       </c>
       <c r="H148" t="n">
         <v/>
       </c>
       <c r="I148" t="n">
-        <v>3.934390115321824e-09</v>
+        <v>2.327129297308309e-11</v>
       </c>
     </row>
     <row r="149">
@@ -6270,22 +6270,22 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>-1.187263119648267e-11</v>
+        <v>-2.270346408461845e-11</v>
       </c>
       <c r="E149" t="n">
-        <v>-9.954093315687994e-12</v>
+        <v>-1.408425404277199e-11</v>
       </c>
       <c r="F149" t="n">
-        <v>-8.919608577508824e-12</v>
+        <v>3.420591414351651e-12</v>
       </c>
       <c r="G149" t="n">
-        <v>-1.251771835124115e-11</v>
+        <v>-3.783311295436673e-11</v>
       </c>
       <c r="H149" t="n">
         <v/>
       </c>
       <c r="I149" t="n">
-        <v>3.554418170522802e-09</v>
+        <v>2.035590497102991e-11</v>
       </c>
     </row>
     <row r="150">
@@ -6305,22 +6305,22 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>-5.621129867262053e-12</v>
+        <v>-1.701121449347642e-11</v>
       </c>
       <c r="E150" t="n">
-        <v>-4.400717824872843e-12</v>
+        <v>-2.146870376695808e-11</v>
       </c>
       <c r="F150" t="n">
-        <v>-6.283003262881136e-12</v>
+        <v>-1.948414853286769e-11</v>
       </c>
       <c r="G150" t="n">
-        <v>2.270986555565135e-13</v>
+        <v>-1.781667080434825e-12</v>
       </c>
       <c r="H150" t="n">
         <v/>
       </c>
       <c r="I150" t="n">
-        <v>4.701315851025429e-09</v>
+        <v>3.634368711009689e-11</v>
       </c>
     </row>
     <row r="151">
@@ -6340,22 +6340,22 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>-1.194163355105562e-11</v>
+        <v>-2.581309349885745e-11</v>
       </c>
       <c r="E151" t="n">
-        <v>-1.105393443127209e-11</v>
+        <v>-1.888181345741659e-11</v>
       </c>
       <c r="F151" t="n">
-        <v>-1.189221192174478e-11</v>
+        <v>-2.191982171273474e-11</v>
       </c>
       <c r="G151" t="n">
-        <v>-1.229538923954088e-11</v>
+        <v>-3.729624545630688e-11</v>
       </c>
       <c r="H151" t="n">
         <v/>
       </c>
       <c r="I151" t="n">
-        <v>8.31646843709918e-13</v>
+        <v>-2.793954018215902e-11</v>
       </c>
     </row>
     <row r="152">
@@ -6375,19 +6375,19 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>-1.07124490412269e-11</v>
+        <v>-6.155943101099589e-11</v>
       </c>
       <c r="E152" t="n">
-        <v>2.227527235223694e-10</v>
+        <v>-1.111224806247147e-12</v>
       </c>
       <c r="F152" t="n">
-        <v>8.216370403193888e-10</v>
+        <v>4.27334348195703e-10</v>
       </c>
       <c r="G152" t="n">
-        <v>5.332171933949804e-10</v>
+        <v>-8.145753873155739e-12</v>
       </c>
       <c r="H152" t="n">
-        <v>2.497036716361267e-09</v>
+        <v>3.156602582656001e-10</v>
       </c>
       <c r="I152" t="n">
         <v/>
@@ -6410,19 +6410,19 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>-1.136026216758408e-11</v>
+        <v>-5.820617095792516e-11</v>
       </c>
       <c r="E153" t="n">
-        <v>1.442576736379778e-10</v>
+        <v>-3.377828219566026e-11</v>
       </c>
       <c r="F153" t="n">
-        <v>1.260692792500754e-09</v>
+        <v>3.63370217944181e-09</v>
       </c>
       <c r="G153" t="n">
-        <v>5.432258503493607e-10</v>
+        <v>-7.846471142948533e-12</v>
       </c>
       <c r="H153" t="n">
-        <v>2.50567429533202e-09</v>
+        <v>3.159237232746998e-10</v>
       </c>
       <c r="I153" t="n">
         <v/>
@@ -6445,19 +6445,19 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>-1.157600283481391e-11</v>
+        <v>-5.509575773499468e-11</v>
       </c>
       <c r="E154" t="n">
-        <v>1.16576087480394e-10</v>
+        <v>-3.298941504976181e-11</v>
       </c>
       <c r="F154" t="n">
-        <v>6.295339922574201e-10</v>
+        <v>6.122228639041992e-10</v>
       </c>
       <c r="G154" t="n">
-        <v>7.499234994048653e-10</v>
+        <v>1.548873246947416e-10</v>
       </c>
       <c r="H154" t="n">
-        <v>2.40898214603202e-09</v>
+        <v>2.738163660589478e-10</v>
       </c>
       <c r="I154" t="n">
         <v/>
@@ -6480,19 +6480,19 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>-1.358145802542775e-11</v>
+        <v>-5.760042443657512e-11</v>
       </c>
       <c r="E155" t="n">
-        <v>7.584888674658811e-11</v>
+        <v>-2.815750389462789e-11</v>
       </c>
       <c r="F155" t="n">
-        <v>5.184068824469475e-10</v>
+        <v>5.919231840911879e-10</v>
       </c>
       <c r="G155" t="n">
-        <v>2.609529661598146e-10</v>
+        <v>1.590298928476343e-12</v>
       </c>
       <c r="H155" t="n">
-        <v>2.696333153018373e-09</v>
+        <v>5.867085670450465e-09</v>
       </c>
       <c r="I155" t="n">
         <v/>
@@ -6515,19 +6515,19 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>-1.061500282197678e-11</v>
+        <v>-5.542036155846857e-11</v>
       </c>
       <c r="E156" t="n">
-        <v>2.317342250506201e-12</v>
+        <v>3.897507439311149e-12</v>
       </c>
       <c r="F156" t="n">
-        <v>2.649631364796529e-12</v>
+        <v>5.924309535712746e-13</v>
       </c>
       <c r="G156" t="n">
-        <v>2.765049763503648e-13</v>
+        <v>1.199559848930739e-11</v>
       </c>
       <c r="H156" t="n">
-        <v>8.03628253442875e-13</v>
+        <v>3.16374869723109e-12</v>
       </c>
       <c r="I156" t="n">
         <v/>
@@ -6550,19 +6550,19 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>9.757112716422426e-12</v>
+        <v>3.575819427713261e-11</v>
       </c>
       <c r="E157" t="n">
-        <v>7.636798915818953e-11</v>
+        <v>-4.87241068134843e-11</v>
       </c>
       <c r="F157" t="n">
-        <v>5.389736401932326e-10</v>
+        <v>6.715023238616829e-10</v>
       </c>
       <c r="G157" t="n">
-        <v>4.288487282254204e-10</v>
+        <v>-3.971323359222885e-12</v>
       </c>
       <c r="H157" t="n">
-        <v>2.109496985119801e-09</v>
+        <v>2.732136492977648e-10</v>
       </c>
       <c r="I157" t="n">
         <v/>
@@ -6585,19 +6585,19 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1.214918002296299e-11</v>
+        <v>-5.141035530471864e-11</v>
       </c>
       <c r="E158" t="n">
-        <v>2.179241844995045e-10</v>
+        <v>-4.5650077293219e-11</v>
       </c>
       <c r="F158" t="n">
-        <v>4.174110781553711e-09</v>
+        <v>1.079510175633173e-08</v>
       </c>
       <c r="G158" t="n">
-        <v>4.563732703495622e-09</v>
+        <v>8.818735227235644e-12</v>
       </c>
       <c r="H158" t="n">
-        <v>2.902431538968916e-08</v>
+        <v>3.536602907682843e-10</v>
       </c>
       <c r="I158" t="n">
         <v/>
@@ -6620,19 +6620,19 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>-6.646542736506443e-12</v>
+        <v>-4.673556628056705e-11</v>
       </c>
       <c r="E159" t="n">
-        <v>1.111041172223013e-10</v>
+        <v>-5.438125731817723e-11</v>
       </c>
       <c r="F159" t="n">
-        <v>6.228956465066186e-10</v>
+        <v>5.603140752168425e-10</v>
       </c>
       <c r="G159" t="n">
-        <v>0.0004030600373798356</v>
+        <v>5.036297764440174e-11</v>
       </c>
       <c r="H159" t="n">
-        <v>1.121105652066381e-08</v>
+        <v>1.86992041177466e-10</v>
       </c>
       <c r="I159" t="n">
         <v/>
@@ -6655,19 +6655,19 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>-6.071089327856984e-12</v>
+        <v>-1.922973868574689e-11</v>
       </c>
       <c r="E160" t="n">
-        <v>8.296457771293033e-11</v>
+        <v>-4.353565810288031e-11</v>
       </c>
       <c r="F160" t="n">
-        <v>5.943696771430726e-10</v>
+        <v>1.026961900267051e-09</v>
       </c>
       <c r="G160" t="n">
-        <v>4.583933030880176e-10</v>
+        <v>7.798836783873825e-12</v>
       </c>
       <c r="H160" t="n">
-        <v>3.672226774445595e-08</v>
+        <v>4.890227176012285e-09</v>
       </c>
       <c r="I160" t="n">
         <v/>
@@ -6690,19 +6690,19 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>-6.377130872678058e-12</v>
+        <v>1.79759952591898e-10</v>
       </c>
       <c r="E161" t="n">
-        <v>1.514155034154269e-12</v>
+        <v>-3.336534668586975e-11</v>
       </c>
       <c r="F161" t="n">
-        <v>2.487316073122404e-12</v>
+        <v>6.953082158571695e-12</v>
       </c>
       <c r="G161" t="n">
-        <v>1.418263654057627e-12</v>
+        <v>2.907962874770362e-12</v>
       </c>
       <c r="H161" t="n">
-        <v>1.098357547021315e-12</v>
+        <v>4.064088140976073e-13</v>
       </c>
       <c r="I161" t="n">
         <v/>
@@ -6725,19 +6725,19 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>8.180440175842374e-12</v>
+        <v>-4.643918465742987e-13</v>
       </c>
       <c r="E162" t="n">
-        <v>9.733558356552223e-11</v>
+        <v>-3.701244663114536e-11</v>
       </c>
       <c r="F162" t="n">
-        <v>4.169653131576782e-10</v>
+        <v>2.502397884195432e-10</v>
       </c>
       <c r="G162" t="n">
-        <v>4.256980312744771e-10</v>
+        <v>-9.264050446176258e-12</v>
       </c>
       <c r="H162" t="n">
-        <v>2.136169069870587e-09</v>
+        <v>2.542195146350062e-10</v>
       </c>
       <c r="I162" t="n">
         <v/>
@@ -6760,19 +6760,19 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1.208690468375211e-11</v>
+        <v>-5.750508909456899e-11</v>
       </c>
       <c r="E163" t="n">
-        <v>1.060222652897597e-09</v>
+        <v>1.006293088542691e-11</v>
       </c>
       <c r="F163" t="n">
-        <v>8.356740649238364e-10</v>
+        <v>2.134350889863489e-10</v>
       </c>
       <c r="G163" t="n">
-        <v>2.654345925733196e-09</v>
+        <v>3.550433987327249e-12</v>
       </c>
       <c r="H163" t="n">
-        <v>1.794517037538265e-08</v>
+        <v>3.363515576763317e-10</v>
       </c>
       <c r="I163" t="n">
         <v/>
@@ -6795,19 +6795,19 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>-5.81666271018445e-12</v>
+        <v>-3.830761904625006e-11</v>
       </c>
       <c r="E164" t="n">
-        <v>1.558253117748028e-10</v>
+        <v>-4.030822553872753e-11</v>
       </c>
       <c r="F164" t="n">
-        <v>4.839412421627967e-10</v>
+        <v>2.700614543201537e-10</v>
       </c>
       <c r="G164" t="n">
-        <v>1.60864173390484e-08</v>
+        <v>7.412203325240346e-11</v>
       </c>
       <c r="H164" t="n">
-        <v>1.024258529358062e-08</v>
+        <v>2.085612648586294e-10</v>
       </c>
       <c r="I164" t="n">
         <v/>
@@ -6830,19 +6830,19 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>-4.493448228881518e-12</v>
+        <v>-4.484670409048449e-11</v>
       </c>
       <c r="E165" t="n">
-        <v>1.13313695449434e-10</v>
+        <v>-2.764344134415482e-11</v>
       </c>
       <c r="F165" t="n">
-        <v>4.756849811649688e-10</v>
+        <v>2.784550097796864e-10</v>
       </c>
       <c r="G165" t="n">
-        <v>4.564141795970224e-10</v>
+        <v>4.445647784797177e-12</v>
       </c>
       <c r="H165" t="n">
-        <v>4.156822195632999e-08</v>
+        <v>3.34343583335076e-09</v>
       </c>
       <c r="I165" t="n">
         <v/>
@@ -6865,19 +6865,19 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>-4.4308645637994e-12</v>
+        <v>-2.997880051148936e-11</v>
       </c>
       <c r="E166" t="n">
-        <v>3.908729435560049e-12</v>
+        <v>-1.434391793141784e-11</v>
       </c>
       <c r="F166" t="n">
-        <v>2.087505667562902e-12</v>
+        <v>-7.5937924552787e-12</v>
       </c>
       <c r="G166" t="n">
-        <v>1.560223837523153e-12</v>
+        <v>-5.182667524443699e-12</v>
       </c>
       <c r="H166" t="n">
-        <v>1.132163421742221e-12</v>
+        <v>-1.451894216793733e-12</v>
       </c>
       <c r="I166" t="n">
         <v/>
@@ -6900,19 +6900,19 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>2.249044568110756e-11</v>
+        <v>-7.9285721184597e-12</v>
       </c>
       <c r="E167" t="n">
-        <v>1.351567965796641e-10</v>
+        <v>-2.907271077779642e-11</v>
       </c>
       <c r="F167" t="n">
-        <v>7.395959312351894e-10</v>
+        <v>5.337437057766787e-10</v>
       </c>
       <c r="G167" t="n">
-        <v>3.622075662100379e-10</v>
+        <v>-3.452652970479054e-11</v>
       </c>
       <c r="H167" t="n">
-        <v>2.3051738214897e-09</v>
+        <v>3.69223600892281e-10</v>
       </c>
       <c r="I167" t="n">
         <v/>
@@ -6935,19 +6935,19 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>-1.767800596691497e-12</v>
+        <v>-5.942940639947976e-11</v>
       </c>
       <c r="E168" t="n">
-        <v>8.535410874946459e-10</v>
+        <v>-1.9717025671376e-11</v>
       </c>
       <c r="F168" t="n">
-        <v>1.258433463306751e-09</v>
+        <v>3.458161601244995e-10</v>
       </c>
       <c r="G168" t="n">
-        <v>9.715744790910963e-10</v>
+        <v>-4.274887189512766e-11</v>
       </c>
       <c r="H168" t="n">
-        <v>1.499959509587995e-08</v>
+        <v>2.764199528949581e-10</v>
       </c>
       <c r="I168" t="n">
         <v/>
@@ -6970,19 +6970,19 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>-4.520910674475977e-13</v>
+        <v>-4.620040383530486e-11</v>
       </c>
       <c r="E169" t="n">
-        <v>3.66576537386845e-10</v>
+        <v>-3.381871151803121e-11</v>
       </c>
       <c r="F169" t="n">
-        <v>3.671880441586918e-09</v>
+        <v>3.735925318942211e-09</v>
       </c>
       <c r="G169" t="n">
-        <v>1.084236345539324e-09</v>
+        <v>-3.880871570975538e-11</v>
       </c>
       <c r="H169" t="n">
-        <v>1.914118874595035e-08</v>
+        <v>3.407780348743058e-10</v>
       </c>
       <c r="I169" t="n">
         <v/>
@@ -7005,19 +7005,19 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>-3.560911408174312e-12</v>
+        <v>-5.53370351958724e-11</v>
       </c>
       <c r="E170" t="n">
-        <v>1.405835679750814e-10</v>
+        <v>-3.107688270181333e-11</v>
       </c>
       <c r="F170" t="n">
-        <v>7.930852726904557e-10</v>
+        <v>4.775362998343275e-10</v>
       </c>
       <c r="G170" t="n">
-        <v>3.637297214772755e-10</v>
+        <v>-3.564658290464622e-11</v>
       </c>
       <c r="H170" t="n">
-        <v>6.017011166590605e-08</v>
+        <v>1.519951083283286e-08</v>
       </c>
       <c r="I170" t="n">
         <v/>
@@ -7040,19 +7040,19 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>2.719433371239376e-11</v>
+        <v>-5.240465632958522e-11</v>
       </c>
       <c r="E171" t="n">
-        <v>8.705036960687969e-12</v>
+        <v>4.18606924973435e-11</v>
       </c>
       <c r="F171" t="n">
-        <v>3.751822861992556e-12</v>
+        <v>-3.613326725659924e-13</v>
       </c>
       <c r="G171" t="n">
-        <v>1.189956435756107e-12</v>
+        <v>-2.125185592388315e-11</v>
       </c>
       <c r="H171" t="n">
-        <v>1.170481003380031e-12</v>
+        <v>9.298007026031851e-12</v>
       </c>
       <c r="I171" t="n">
         <v/>
@@ -7075,19 +7075,19 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>6.038259930207211e-13</v>
+        <v>-2.030317868877999e-12</v>
       </c>
       <c r="E172" t="n">
-        <v>7.377283558417381e-11</v>
+        <v>-3.082256022312016e-11</v>
       </c>
       <c r="F172" t="n">
-        <v>4.872065528666575e-10</v>
+        <v>5.405706016011901e-10</v>
       </c>
       <c r="G172" t="n">
-        <v>2.603765889882956e-10</v>
+        <v>2.472416872453055e-12</v>
       </c>
       <c r="H172" t="n">
-        <v>1.021491559907725e-09</v>
+        <v>1.292285105811979e-10</v>
       </c>
       <c r="I172" t="n">
         <v/>
@@ -7110,19 +7110,19 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>-5.524329458185603e-12</v>
+        <v>-4.332420258045577e-11</v>
       </c>
       <c r="E173" t="n">
-        <v>2.313081062902613e-10</v>
+        <v>2.456721018839924e-11</v>
       </c>
       <c r="F173" t="n">
-        <v>8.289745845729366e-10</v>
+        <v>5.366007597993089e-10</v>
       </c>
       <c r="G173" t="n">
-        <v>5.40433940544942e-10</v>
+        <v>4.262397598880083e-12</v>
       </c>
       <c r="H173" t="n">
-        <v>1.741641214136281e-09</v>
+        <v>1.436043928582697e-10</v>
       </c>
       <c r="I173" t="n">
         <v/>
@@ -7145,19 +7145,19 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>-4.308369290633886e-12</v>
+        <v>-4.703531779496404e-11</v>
       </c>
       <c r="E174" t="n">
-        <v>1.612999216272723e-10</v>
+        <v>-2.6484132951465e-11</v>
       </c>
       <c r="F174" t="n">
-        <v>1.49988514687004e-09</v>
+        <v>5.61556096497889e-09</v>
       </c>
       <c r="G174" t="n">
-        <v>5.610450184869848e-10</v>
+        <v>7.013565125724706e-12</v>
       </c>
       <c r="H174" t="n">
-        <v>1.755597057772517e-09</v>
+        <v>1.450663881554663e-10</v>
       </c>
       <c r="I174" t="n">
         <v/>
@@ -7180,19 +7180,19 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>-7.502713075865017e-12</v>
+        <v>-5.152004270267164e-11</v>
       </c>
       <c r="E175" t="n">
-        <v>1.169532170723625e-10</v>
+        <v>-3.690544692209633e-11</v>
       </c>
       <c r="F175" t="n">
-        <v>6.194821891176842e-10</v>
+        <v>4.956621512247512e-10</v>
       </c>
       <c r="G175" t="n">
-        <v>7.546094531230134e-10</v>
+        <v>1.3698863301897e-10</v>
       </c>
       <c r="H175" t="n">
-        <v>1.692029560994794e-09</v>
+        <v>1.089090349955617e-10</v>
       </c>
       <c r="I175" t="n">
         <v/>
@@ -7215,19 +7215,19 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>-7.165294640330081e-12</v>
+        <v>-4.195615955147341e-11</v>
       </c>
       <c r="E176" t="n">
-        <v>2.135645379069635e-12</v>
+        <v>3.122733118983807e-13</v>
       </c>
       <c r="F176" t="n">
-        <v>2.562633211799688e-12</v>
+        <v>4.096282904390895e-13</v>
       </c>
       <c r="G176" t="n">
-        <v>2.769423142731233e-13</v>
+        <v>1.153091961042571e-11</v>
       </c>
       <c r="H176" t="n">
-        <v>6.264517723868327e-13</v>
+        <v>-1.141635547270732e-11</v>
       </c>
       <c r="I176" t="n">
         <v/>
@@ -7250,19 +7250,19 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1.133375572594254e-10</v>
+        <v>9.395103151233181e-12</v>
       </c>
       <c r="E177" t="n">
-        <v>1.791195087496946e-10</v>
+        <v>5.349290595003422e-11</v>
       </c>
       <c r="F177" t="n">
-        <v>1.050178901436553e-09</v>
+        <v>3.269718586926545e-09</v>
       </c>
       <c r="G177" t="n">
-        <v>6.104650995874979e-10</v>
+        <v>1.977704837341446e-10</v>
       </c>
       <c r="H177" t="n">
-        <v>2.536498502609338e-09</v>
+        <v>5.749764491340429e-09</v>
       </c>
       <c r="I177" t="n">
         <v/>
@@ -7285,19 +7285,19 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>8.927145155100035e-12</v>
+        <v>3.199606156829522e-10</v>
       </c>
       <c r="E178" t="n">
-        <v>0.1762870535515593</v>
+        <v>0.166993927400421</v>
       </c>
       <c r="F178" t="n">
-        <v>2.18811790834705e-09</v>
+        <v>1.153764678073077e-08</v>
       </c>
       <c r="G178" t="n">
-        <v>0.0004030607902013275</v>
+        <v>1.089989833534346e-10</v>
       </c>
       <c r="H178" t="n">
-        <v>4.188479159571581e-08</v>
+        <v>4.632463404375154e-09</v>
       </c>
       <c r="I178" t="n">
         <v/>
@@ -7320,19 +7320,19 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>9.497911859585187e-12</v>
+        <v>3.174964330126851e-11</v>
       </c>
       <c r="E179" t="n">
-        <v>5.405476559718902e-10</v>
+        <v>3.048610339413871e-11</v>
       </c>
       <c r="F179" t="n">
-        <v>0.2900570132164118</v>
+        <v>5.578851581969273e-11</v>
       </c>
       <c r="G179" t="n">
-        <v>1.287219578161949e-08</v>
+        <v>9.849428355307822e-11</v>
       </c>
       <c r="H179" t="n">
-        <v>1.946650336984153e-08</v>
+        <v>2.985687839230491e-09</v>
       </c>
       <c r="I179" t="n">
         <v/>
@@ -7355,19 +7355,19 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>7.544589767841507e-11</v>
+        <v>-2.963878741865846e-11</v>
       </c>
       <c r="E180" t="n">
-        <v>1.00410429284717e-09</v>
+        <v>9.275970666695488e-11</v>
       </c>
       <c r="F180" t="n">
-        <v>4.110893861636057e-09</v>
+        <v>3.154399607339883e-09</v>
       </c>
       <c r="G180" t="n">
-        <v>0.000879247629123279</v>
+        <v>8.887384549149853e-11</v>
       </c>
       <c r="H180" t="n">
-        <v>7.106258628895839e-08</v>
+        <v>1.541695172142998e-08</v>
       </c>
       <c r="I180" t="n">
         <v/>
@@ -7390,19 +7390,19 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>4.466526575114304e-12</v>
+        <v>-8.852138091967863e-12</v>
       </c>
       <c r="E181" t="n">
-        <v>1.727589980695936e-10</v>
+        <v>6.108082945294124e-11</v>
       </c>
       <c r="F181" t="n">
-        <v>1.056564293193623e-09</v>
+        <v>4.813927711922383e-09</v>
       </c>
       <c r="G181" t="n">
-        <v>5.772517731357392e-10</v>
+        <v>1.840797316341362e-10</v>
       </c>
       <c r="H181" t="n">
-        <v>0.003113438184777561</v>
+        <v>1.302513734453169e-09</v>
       </c>
       <c r="I181" t="n">
         <v/>
@@ -8684,7 +8684,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>0.1217516</v>
+        <v>0.11929</v>
       </c>
     </row>
   </sheetData>
@@ -8738,10 +8738,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4369176121787284</v>
+        <v>0.2467213991860113</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1863948966897414</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>

--- a/6node_spain/output_all.xlsx
+++ b/6node_spain/output_all.xlsx
@@ -459,19 +459,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2467214034409604</v>
+        <v>0.9572118407648046</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.3220873957491368</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1.245309948323212</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>6.294582074789266e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4934428023807521</v>
+        <v>0.6566439572261955</v>
       </c>
     </row>
   </sheetData>
@@ -558,16 +558,16 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2.74771350488413e-11</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1.454363032110768</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1.416896192563044e-11</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8224046618651433</v>
+        <v>0.8681712529391943</v>
       </c>
     </row>
     <row r="4">
@@ -580,19 +580,19 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2.74771350488413e-11</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.6211535484264601</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1.588918924010747e-11</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.2262353424377983</v>
       </c>
     </row>
     <row r="5">
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1.454363032110768</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.6211535484264601</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -630,10 +630,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1.416896192563044e-11</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1.588918924010747e-11</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -655,10 +655,10 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8224046618651433</v>
+        <v>0.8681712529391943</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.2262353424377983</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -757,13 +757,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.1532216079795203</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1654650941974328</v>
+        <v>0.1746731811308531</v>
       </c>
     </row>
     <row r="4">
@@ -782,13 +782,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.1733576579319678</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.2973395199056027</v>
       </c>
     </row>
     <row r="5">
@@ -801,10 +801,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.1516397779043354</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.1718649646636453</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -813,7 +813,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1.850097852695853e-11</v>
       </c>
     </row>
     <row r="6">
@@ -838,7 +838,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-2.116662400908353e-11</v>
       </c>
     </row>
     <row r="7">
@@ -851,16 +851,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1669938951199662</v>
+        <v>0.1762870588476576</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.288776244866266</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1.289723883246552e-11</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>7.346123709339736e-11</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -953,13 +953,13 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.8467783920204797</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8345349058025672</v>
+        <v>0.8253268188691469</v>
       </c>
     </row>
     <row r="4">
@@ -978,13 +978,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0.8266423420680322</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.7026604800943973</v>
       </c>
     </row>
     <row r="5">
@@ -997,10 +997,10 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0.8483602220956646</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0.8281350353363547</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -1009,7 +1009,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0.999999999981499</v>
       </c>
     </row>
     <row r="6">
@@ -1034,7 +1034,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>1.000000000021167</v>
       </c>
     </row>
     <row r="7">
@@ -1047,16 +1047,16 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8330061048800338</v>
+        <v>0.8237129411523424</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0.711223755133734</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0.9999999999871028</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0.9999999999265388</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1073,7 +1073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I217"/>
+  <dimension ref="A1:I181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1128,19 +1128,19 @@
         <v/>
       </c>
       <c r="E2" t="n">
-        <v>9.511605729066415e-11</v>
+        <v>5.458669009792795e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>7.600570597868428e-12</v>
+        <v>5.495509331106087e-11</v>
       </c>
       <c r="G2" t="n">
-        <v>7.819013270903964e-11</v>
+        <v>3.169458621617864e-11</v>
       </c>
       <c r="H2" t="n">
-        <v>1.545090071243787e-10</v>
+        <v>4.163509348923588e-11</v>
       </c>
       <c r="I2" t="n">
-        <v>1.276984759702831e-10</v>
+        <v>3.403769464154021e-11</v>
       </c>
     </row>
     <row r="3">
@@ -1163,19 +1163,19 @@
         <v/>
       </c>
       <c r="E3" t="n">
-        <v>2.58776238079935e-11</v>
+        <v>-5.664563833087858e-12</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.469142535212143e-11</v>
+        <v>7.038447857988301e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>9.863810589696852e-11</v>
+        <v>2.835688270432345e-11</v>
       </c>
       <c r="H3" t="n">
-        <v>1.442727105387217e-10</v>
+        <v>3.814321689810269e-11</v>
       </c>
       <c r="I3" t="n">
-        <v>6.604222351635129e-11</v>
+        <v>3.074645032021281e-11</v>
       </c>
     </row>
     <row r="4">
@@ -1198,19 +1198,19 @@
         <v/>
       </c>
       <c r="E4" t="n">
-        <v>4.005196597571373e-11</v>
+        <v>1.257528136712982e-11</v>
       </c>
       <c r="F4" t="n">
-        <v>3.806657682500966e-11</v>
+        <v>3.813757876956261e-11</v>
       </c>
       <c r="G4" t="n">
-        <v>-6.992928067992941e-11</v>
+        <v>4.279511322579283e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>1.591957250398907e-10</v>
+        <v>4.504639992536817e-11</v>
       </c>
       <c r="I4" t="n">
-        <v>7.28654697534176e-11</v>
+        <v>4.875455466868499e-11</v>
       </c>
     </row>
     <row r="5">
@@ -1233,19 +1233,19 @@
         <v/>
       </c>
       <c r="E5" t="n">
-        <v>3.203079430918896e-11</v>
+        <v>3.76186674357357e-11</v>
       </c>
       <c r="F5" t="n">
-        <v>2.071822685123497e-11</v>
+        <v>7.379650599831761e-12</v>
       </c>
       <c r="G5" t="n">
-        <v>1.02476676920911e-10</v>
+        <v>2.494206642450477e-11</v>
       </c>
       <c r="H5" t="n">
-        <v>-6.391364630794719e-11</v>
+        <v>2.166573792341249e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>6.531987530673796e-11</v>
+        <v>8.800796531291943e-12</v>
       </c>
     </row>
     <row r="6">
@@ -1268,19 +1268,19 @@
         <v/>
       </c>
       <c r="E6" t="n">
-        <v>4.873699210519324e-11</v>
+        <v>-1.97469468039694e-11</v>
       </c>
       <c r="F6" t="n">
-        <v>2.625148893842049e-11</v>
+        <v>-3.239103669510194e-12</v>
       </c>
       <c r="G6" t="n">
-        <v>2.618829041864886e-11</v>
+        <v>-2.562132090288395e-12</v>
       </c>
       <c r="H6" t="n">
-        <v>1.390524041577588e-11</v>
+        <v>-2.433320119822662e-12</v>
       </c>
       <c r="I6" t="n">
-        <v>1.681539673639826e-11</v>
+        <v>1.813774292066346e-10</v>
       </c>
     </row>
     <row r="7">
@@ -1303,19 +1303,19 @@
         <v/>
       </c>
       <c r="E7" t="n">
-        <v>-2.32697622356106e-11</v>
+        <v>-1.237460106586204e-11</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.680035226698028e-13</v>
+        <v>4.979683581779496e-12</v>
       </c>
       <c r="G7" t="n">
-        <v>1.028344859783746e-11</v>
+        <v>5.072392112992006e-12</v>
       </c>
       <c r="H7" t="n">
-        <v>8.66794057304781e-12</v>
+        <v>3.897662216402091e-12</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.518330302221432e-11</v>
+        <v>6.89306858068079e-12</v>
       </c>
     </row>
     <row r="8">
@@ -1338,19 +1338,19 @@
         <v/>
       </c>
       <c r="E8" t="n">
-        <v>-5.92767690388017e-11</v>
+        <v>-1.875855466580556e-11</v>
       </c>
       <c r="F8" t="n">
-        <v>-5.191632323331026e-11</v>
+        <v>6.002083298912924e-11</v>
       </c>
       <c r="G8" t="n">
-        <v>-7.884204357908406e-12</v>
+        <v>2.088184457562157e-11</v>
       </c>
       <c r="H8" t="n">
-        <v>1.886543973626821e-11</v>
+        <v>2.128006499931926e-11</v>
       </c>
       <c r="I8" t="n">
-        <v>-5.731520343069717e-11</v>
+        <v>1.67424676852212e-11</v>
       </c>
     </row>
     <row r="9">
@@ -1373,19 +1373,19 @@
         <v/>
       </c>
       <c r="E9" t="n">
-        <v>-5.800041179400182e-11</v>
+        <v>-2.011007363739208e-11</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.499951896293651e-11</v>
+        <v>-1.218392215247025e-12</v>
       </c>
       <c r="G9" t="n">
-        <v>3.036695777777328e-11</v>
+        <v>1.906049224485343e-11</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.227461410679017e-12</v>
+        <v>2.753105116376404e-12</v>
       </c>
       <c r="I9" t="n">
-        <v>-5.681519653430552e-11</v>
+        <v>1.643144504851301e-12</v>
       </c>
     </row>
     <row r="10">
@@ -1408,19 +1408,19 @@
         <v/>
       </c>
       <c r="E10" t="n">
-        <v>-4.223502693365971e-11</v>
+        <v>-1.991658833758559e-11</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.443239556050597e-11</v>
+        <v>-4.938132936923566e-12</v>
       </c>
       <c r="G10" t="n">
-        <v>2.50990166388332e-11</v>
+        <v>5.415369891048147e-12</v>
       </c>
       <c r="H10" t="n">
-        <v>1.615232016275086e-10</v>
+        <v>3.465649421337698e-11</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.97429064822929e-11</v>
+        <v>-3.262284662500962e-12</v>
       </c>
     </row>
     <row r="11">
@@ -1443,19 +1443,19 @@
         <v/>
       </c>
       <c r="E11" t="n">
-        <v>-5.344788696551354e-12</v>
+        <v>-2.093876131630506e-11</v>
       </c>
       <c r="F11" t="n">
-        <v>2.8517882462712e-11</v>
+        <v>-1.062138027456614e-11</v>
       </c>
       <c r="G11" t="n">
-        <v>9.981001306994011e-12</v>
+        <v>-8.892949736551117e-12</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.777539384437544e-11</v>
+        <v>-9.328199820029157e-12</v>
       </c>
       <c r="I11" t="n">
-        <v>1.563850510403426e-10</v>
+        <v>5.174740127655349e-12</v>
       </c>
     </row>
     <row r="12">
@@ -1478,19 +1478,19 @@
         <v/>
       </c>
       <c r="E12" t="n">
-        <v>7.196097125150368e-12</v>
+        <v>-1.087648552313578e-11</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.16320685439295e-11</v>
+        <v>-2.577526010598021e-12</v>
       </c>
       <c r="G12" t="n">
-        <v>6.708969387388821e-12</v>
+        <v>3.734290665998911e-12</v>
       </c>
       <c r="H12" t="n">
-        <v>7.976010386728246e-12</v>
+        <v>2.389029405858259e-12</v>
       </c>
       <c r="I12" t="n">
-        <v>8.546396313819076e-12</v>
+        <v>5.220183572791662e-12</v>
       </c>
     </row>
     <row r="13">
@@ -1513,19 +1513,19 @@
         <v/>
       </c>
       <c r="E13" t="n">
-        <v>-4.851014901952964e-11</v>
+        <v>-1.554313932647495e-11</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.91619615853652e-11</v>
+        <v>3.774389378775924e-12</v>
       </c>
       <c r="G13" t="n">
-        <v>-9.749767443423733e-12</v>
+        <v>1.91593495238469e-11</v>
       </c>
       <c r="H13" t="n">
-        <v>2.448477850090274e-11</v>
+        <v>1.845222972494235e-11</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.942472082839528e-11</v>
+        <v>1.428226112463149e-11</v>
       </c>
     </row>
     <row r="14">
@@ -1548,19 +1548,19 @@
         <v/>
       </c>
       <c r="E14" t="n">
-        <v>-4.16521945603215e-11</v>
+        <v>-1.97525996836988e-11</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.972588594536136e-11</v>
+        <v>-5.326104442354552e-12</v>
       </c>
       <c r="G14" t="n">
-        <v>8.102328955910846e-11</v>
+        <v>2.093362794981034e-11</v>
       </c>
       <c r="H14" t="n">
-        <v>9.992238043861501e-12</v>
+        <v>3.231316222458044e-12</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.260497692450227e-11</v>
+        <v>2.156973134766827e-12</v>
       </c>
     </row>
     <row r="15">
@@ -1583,19 +1583,19 @@
         <v/>
       </c>
       <c r="E15" t="n">
-        <v>-4.430959149799106e-11</v>
+        <v>-1.950063970810557e-11</v>
       </c>
       <c r="F15" t="n">
-        <v>-5.261262566695272e-11</v>
+        <v>-7.453326850208513e-12</v>
       </c>
       <c r="G15" t="n">
-        <v>3.97239568912818e-12</v>
+        <v>7.199644077253196e-12</v>
       </c>
       <c r="H15" t="n">
-        <v>1.358959560789334e-10</v>
+        <v>4.096597078095721e-11</v>
       </c>
       <c r="I15" t="n">
-        <v>-4.439865023417673e-11</v>
+        <v>-2.317823639750988e-12</v>
       </c>
     </row>
     <row r="16">
@@ -1618,19 +1618,19 @@
         <v/>
       </c>
       <c r="E16" t="n">
-        <v>-3.147030461332534e-11</v>
+        <v>-2.064110999540803e-11</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.509978184105134e-11</v>
+        <v>-1.146259969436776e-11</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.545102096885572e-11</v>
+        <v>-8.414572973424955e-12</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.352792821506025e-11</v>
+        <v>-9.046967874661217e-12</v>
       </c>
       <c r="I16" t="n">
-        <v>3.125964547261432e-12</v>
+        <v>9.045211774332619e-12</v>
       </c>
     </row>
     <row r="17">
@@ -1653,19 +1653,19 @@
         <v/>
       </c>
       <c r="E17" t="n">
-        <v>2.061153035969945e-11</v>
+        <v>6.66602871585139e-12</v>
       </c>
       <c r="F17" t="n">
-        <v>1.465179807154687e-11</v>
+        <v>8.93653131517284e-12</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.848820149989819e-11</v>
+        <v>-2.253740649743893e-12</v>
       </c>
       <c r="H17" t="n">
-        <v>1.974722497185587e-11</v>
+        <v>5.216257383794539e-12</v>
       </c>
       <c r="I17" t="n">
-        <v>3.199879897502376e-11</v>
+        <v>5.117849667352556e-12</v>
       </c>
     </row>
     <row r="18">
@@ -1688,19 +1688,19 @@
         <v/>
       </c>
       <c r="E18" t="n">
-        <v>-4.742530497886044e-11</v>
+        <v>-1.90632835044536e-11</v>
       </c>
       <c r="F18" t="n">
-        <v>-5.483135578572071e-11</v>
+        <v>2.68636858173043e-12</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.369187416906565e-11</v>
+        <v>-3.907872454472458e-12</v>
       </c>
       <c r="H18" t="n">
-        <v>4.581674721959608e-12</v>
+        <v>3.27362620947652e-12</v>
       </c>
       <c r="I18" t="n">
-        <v>-4.786428784147798e-11</v>
+        <v>-1.67042466962033e-12</v>
       </c>
     </row>
     <row r="19">
@@ -1723,19 +1723,19 @@
         <v/>
       </c>
       <c r="E19" t="n">
-        <v>-3.964281380310902e-11</v>
+        <v>-1.955186696042984e-11</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.832563757821653e-11</v>
+        <v>1.777880394003778e-11</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.172300211835237e-11</v>
+        <v>-3.19830436215341e-12</v>
       </c>
       <c r="H19" t="n">
-        <v>2.054405380725467e-11</v>
+        <v>4.904912947348859e-12</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.753680586893757e-11</v>
+        <v>-5.094232993435027e-13</v>
       </c>
     </row>
     <row r="20">
@@ -1758,19 +1758,19 @@
         <v/>
       </c>
       <c r="E20" t="n">
-        <v>-5.255259885112998e-11</v>
+        <v>-1.967068787097253e-11</v>
       </c>
       <c r="F20" t="n">
-        <v>-5.477779488141467e-11</v>
+        <v>-3.870148683739519e-12</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.061016169348001e-11</v>
+        <v>-2.643379905521186e-12</v>
       </c>
       <c r="H20" t="n">
-        <v>9.931090900155062e-11</v>
+        <v>3.630234177890778e-11</v>
       </c>
       <c r="I20" t="n">
-        <v>-5.150865909271416e-11</v>
+        <v>-4.476364069772428e-12</v>
       </c>
     </row>
     <row r="21">
@@ -1793,19 +1793,19 @@
         <v/>
       </c>
       <c r="E21" t="n">
-        <v>-5.159558833701856e-11</v>
+        <v>-2.034704043217426e-11</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.469303122301615e-11</v>
+        <v>-5.805081624028984e-12</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.766328968962184e-11</v>
+        <v>-7.80277342336253e-12</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.570699035770137e-11</v>
+        <v>-4.54453074867379e-12</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.696803700437596e-11</v>
+        <v>3.703996080325909e-11</v>
       </c>
     </row>
     <row r="22">
@@ -1828,19 +1828,19 @@
         <v/>
       </c>
       <c r="E22" t="n">
-        <v>3.887877625334494e-12</v>
+        <v>3.635012404503641e-11</v>
       </c>
       <c r="F22" t="n">
-        <v>3.935843385776388e-12</v>
+        <v>-3.496117300325294e-12</v>
       </c>
       <c r="G22" t="n">
-        <v>1.540812438910408e-11</v>
+        <v>2.15457720016647e-12</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.285365995229715e-11</v>
+        <v>-2.851174869823847e-12</v>
       </c>
       <c r="I22" t="n">
-        <v>1.144613803615447e-11</v>
+        <v>-2.89618456695903e-12</v>
       </c>
     </row>
     <row r="23">
@@ -1863,19 +1863,19 @@
         <v/>
       </c>
       <c r="E23" t="n">
-        <v>-1.514130303743068e-11</v>
+        <v>-1.901522772033153e-11</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.34219557777433e-11</v>
+        <v>-3.657839987356861e-12</v>
       </c>
       <c r="G23" t="n">
-        <v>2.620017046514544e-11</v>
+        <v>4.186857519919358e-12</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.21989579957311e-12</v>
+        <v>-8.157853814525164e-13</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.885057753028616e-11</v>
+        <v>-4.597537281177279e-12</v>
       </c>
     </row>
     <row r="24">
@@ -1898,19 +1898,19 @@
         <v/>
       </c>
       <c r="E24" t="n">
-        <v>-4.634687540243128e-11</v>
+        <v>-1.929312032480439e-11</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.765697446029998e-11</v>
+        <v>3.489866073936948e-12</v>
       </c>
       <c r="G24" t="n">
-        <v>9.94015179997381e-12</v>
+        <v>6.011358048543665e-12</v>
       </c>
       <c r="H24" t="n">
-        <v>-6.654596018924447e-12</v>
+        <v>6.232488123511552e-13</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.443820166367059e-11</v>
+        <v>-3.731298943973402e-12</v>
       </c>
     </row>
     <row r="25">
@@ -1933,19 +1933,19 @@
         <v/>
       </c>
       <c r="E25" t="n">
-        <v>-5.39658392512739e-11</v>
+        <v>-1.960126025614961e-11</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.4797322382429e-11</v>
+        <v>-5.180759310721063e-12</v>
       </c>
       <c r="G25" t="n">
-        <v>4.738820111626061e-11</v>
+        <v>2.196537318317595e-11</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.64491506679032e-11</v>
+        <v>-9.915536328865195e-13</v>
       </c>
       <c r="I25" t="n">
-        <v>-5.327822109020496e-11</v>
+        <v>-3.728749321255794e-12</v>
       </c>
     </row>
     <row r="26">
@@ -1968,19 +1968,19 @@
         <v/>
       </c>
       <c r="E26" t="n">
-        <v>-4.385129673416665e-11</v>
+        <v>-2.081401664418638e-11</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.666876190075326e-11</v>
+        <v>-1.194804872561434e-11</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.746051640454578e-11</v>
+        <v>-8.571945693599407e-12</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.444073443550141e-11</v>
+        <v>-1.038697063605085e-11</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.201124306346564e-11</v>
+        <v>-1.713715235584109e-12</v>
       </c>
     </row>
     <row r="27">
@@ -2003,19 +2003,19 @@
         <v/>
       </c>
       <c r="E27" t="n">
-        <v>-8.425858851193861e-12</v>
+        <v>-1.97661788499361e-11</v>
       </c>
       <c r="F27" t="n">
-        <v>3.612396282069289e-12</v>
+        <v>-7.519139753485585e-12</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.391229285874406e-11</v>
+        <v>-8.435149205549128e-12</v>
       </c>
       <c r="H27" t="n">
-        <v>-2.353762975424182e-11</v>
+        <v>-8.414582136632417e-12</v>
       </c>
       <c r="I27" t="n">
-        <v>-3.68080620040613e-11</v>
+        <v>-1.401815382177383e-11</v>
       </c>
     </row>
     <row r="28">
@@ -2038,19 +2038,19 @@
         <v/>
       </c>
       <c r="E28" t="n">
-        <v>6.964749051258958e-11</v>
+        <v>-2.056646115256088e-11</v>
       </c>
       <c r="F28" t="n">
-        <v>2.642049519731178e-11</v>
+        <v>-9.535400139804619e-12</v>
       </c>
       <c r="G28" t="n">
-        <v>6.897558402038399e-12</v>
+        <v>-9.595771717370733e-12</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.530183786579582e-11</v>
+        <v>-9.286037317108956e-12</v>
       </c>
       <c r="I28" t="n">
-        <v>-2.423044820083978e-11</v>
+        <v>-1.486085757993615e-11</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2073,19 @@
         <v/>
       </c>
       <c r="E29" t="n">
-        <v>-3.935730812987884e-11</v>
+        <v>-2.085880877231465e-11</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.770064223216705e-11</v>
+        <v>-7.501341707607854e-12</v>
       </c>
       <c r="G29" t="n">
-        <v>-1.2467184996347e-11</v>
+        <v>-9.439441723360325e-12</v>
       </c>
       <c r="H29" t="n">
-        <v>-2.220655326958839e-11</v>
+        <v>-8.959865396764957e-12</v>
       </c>
       <c r="I29" t="n">
-        <v>-5.150799968130978e-11</v>
+        <v>-1.486138979538406e-11</v>
       </c>
     </row>
     <row r="30">
@@ -2108,19 +2108,19 @@
         <v/>
       </c>
       <c r="E30" t="n">
-        <v>-5.703829597978343e-11</v>
+        <v>-2.051577170001593e-11</v>
       </c>
       <c r="F30" t="n">
-        <v>-5.65198709355129e-11</v>
+        <v>-6.685849272392029e-12</v>
       </c>
       <c r="G30" t="n">
-        <v>4.538180304483887e-12</v>
+        <v>3.328078855093979e-13</v>
       </c>
       <c r="H30" t="n">
-        <v>-2.003447886278338e-11</v>
+        <v>-4.886660061156343e-12</v>
       </c>
       <c r="I30" t="n">
-        <v>-6.20460660374992e-11</v>
+        <v>-1.332432455538449e-11</v>
       </c>
     </row>
     <row r="31">
@@ -2143,19 +2143,19 @@
         <v/>
       </c>
       <c r="E31" t="n">
-        <v>-4.835101382864894e-11</v>
+        <v>-2.090425241917208e-11</v>
       </c>
       <c r="F31" t="n">
-        <v>-4.750458187748539e-11</v>
+        <v>-1.188899218299237e-11</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.94617961887613e-11</v>
+        <v>-9.167480229039877e-12</v>
       </c>
       <c r="H31" t="n">
-        <v>3.534693310469444e-12</v>
+        <v>-4.254779541885717e-12</v>
       </c>
       <c r="I31" t="n">
-        <v>-5.680176480940763e-11</v>
+        <v>-1.536049790731079e-11</v>
       </c>
     </row>
     <row r="32">
@@ -2175,22 +2175,22 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-5.109043634741899e-11</v>
+        <v>-1.799358330140869e-11</v>
       </c>
       <c r="E32" t="n">
         <v/>
       </c>
       <c r="F32" t="n">
-        <v>-4.873815621937968e-11</v>
+        <v>-5.096588627107797e-12</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.802599747362123e-11</v>
+        <v>-2.33164062395365e-12</v>
       </c>
       <c r="H32" t="n">
-        <v>1.78777148915375e-12</v>
+        <v>8.940554561517882e-14</v>
       </c>
       <c r="I32" t="n">
-        <v>3.03714377418666e-12</v>
+        <v>1.259329507793711e-13</v>
       </c>
     </row>
     <row r="33">
@@ -2210,22 +2210,22 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-5.282390788171459e-11</v>
+        <v>-2.009361323640589e-11</v>
       </c>
       <c r="E33" t="n">
         <v/>
       </c>
       <c r="F33" t="n">
-        <v>-4.444979844368133e-11</v>
+        <v>-3.533395765510211e-13</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.802820694699855e-11</v>
+        <v>4.941045968668433e-11</v>
       </c>
       <c r="H33" t="n">
-        <v>6.696117556624353e-12</v>
+        <v>2.40556785159887e-12</v>
       </c>
       <c r="I33" t="n">
-        <v>-3.78398296785355e-11</v>
+        <v>1.969031231000211e-11</v>
       </c>
     </row>
     <row r="34">
@@ -2245,22 +2245,22 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-5.055460120339712e-11</v>
+        <v>-1.983539833582138e-11</v>
       </c>
       <c r="E34" t="n">
         <v/>
       </c>
       <c r="F34" t="n">
-        <v>-4.768556776192433e-11</v>
+        <v>-2.6400638298881e-12</v>
       </c>
       <c r="G34" t="n">
-        <v>7.371337315134422e-11</v>
+        <v>6.844809718687699e-11</v>
       </c>
       <c r="H34" t="n">
-        <v>1.241675631263436e-11</v>
+        <v>6.495759518416505e-12</v>
       </c>
       <c r="I34" t="n">
-        <v>-2.827833695549503e-11</v>
+        <v>3.805772777289481e-11</v>
       </c>
     </row>
     <row r="35">
@@ -2280,22 +2280,22 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-5.401928598334396e-11</v>
+        <v>-1.986137107535863e-11</v>
       </c>
       <c r="E35" t="n">
         <v/>
       </c>
       <c r="F35" t="n">
-        <v>-5.100555729160691e-11</v>
+        <v>-8.737228503707478e-12</v>
       </c>
       <c r="G35" t="n">
-        <v>-2.556618155732874e-11</v>
+        <v>1.700844188174574e-11</v>
       </c>
       <c r="H35" t="n">
-        <v>4.273718460734315e-11</v>
+        <v>1.981714203894107e-11</v>
       </c>
       <c r="I35" t="n">
-        <v>-3.309632787855475e-11</v>
+        <v>1.789666106381746e-11</v>
       </c>
     </row>
     <row r="36">
@@ -2315,22 +2315,22 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-5.667291178364606e-11</v>
+        <v>-2.083146019924447e-11</v>
       </c>
       <c r="E36" t="n">
         <v/>
       </c>
       <c r="F36" t="n">
-        <v>-5.125275922434009e-11</v>
+        <v>-9.625201513879022e-12</v>
       </c>
       <c r="G36" t="n">
-        <v>-3.671828656763683e-11</v>
+        <v>3.774591912935002e-11</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.882793769462869e-11</v>
+        <v>-7.664990927088142e-12</v>
       </c>
       <c r="I36" t="n">
-        <v>-5.680665605469904e-12</v>
+        <v>7.036664243312659e-11</v>
       </c>
     </row>
     <row r="37">
@@ -2350,22 +2350,22 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>7.840144754691244e-11</v>
+        <v>5.575134878544022e-08</v>
       </c>
       <c r="E37" t="n">
         <v/>
       </c>
       <c r="F37" t="n">
-        <v>-4.146403071682648e-11</v>
+        <v>1.045504168548879e-13</v>
       </c>
       <c r="G37" t="n">
-        <v>7.077291202213873e-11</v>
+        <v>4.530695744443999e-11</v>
       </c>
       <c r="H37" t="n">
-        <v>5.461033258153606e-11</v>
+        <v>2.117569801819841e-11</v>
       </c>
       <c r="I37" t="n">
-        <v>6.511160550061171e-11</v>
+        <v>7.480801291794841e-11</v>
       </c>
     </row>
     <row r="38">
@@ -2385,22 +2385,22 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-4.087028677942068e-11</v>
+        <v>7.421549354407823e-11</v>
       </c>
       <c r="E38" t="n">
         <v/>
       </c>
       <c r="F38" t="n">
-        <v>-4.732657641400655e-11</v>
+        <v>4.240976183217319e-10</v>
       </c>
       <c r="G38" t="n">
-        <v>3.285644756879843e-11</v>
+        <v>8.961072217928141e-10</v>
       </c>
       <c r="H38" t="n">
-        <v>3.947437978460863e-11</v>
+        <v>7.667677810616076e-11</v>
       </c>
       <c r="I38" t="n">
-        <v>9.277766555343631e-11</v>
+        <v>2.602372035343039e-10</v>
       </c>
     </row>
     <row r="39">
@@ -2420,22 +2420,22 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-3.517339274412425e-11</v>
+        <v>-1.45905248653193e-11</v>
       </c>
       <c r="E39" t="n">
         <v/>
       </c>
       <c r="F39" t="n">
-        <v>-4.816187779206558e-11</v>
+        <v>1.992952493966975e-11</v>
       </c>
       <c r="G39" t="n">
-        <v>9.609910010533133e-10</v>
+        <v>0.1511920838274534</v>
       </c>
       <c r="H39" t="n">
-        <v>2.389980304713374e-11</v>
+        <v>2.316216014542745e-11</v>
       </c>
       <c r="I39" t="n">
-        <v>1.804288768308001e-11</v>
+        <v>1.946155976977453e-10</v>
       </c>
     </row>
     <row r="40">
@@ -2455,22 +2455,22 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2.048646767071368e-11</v>
+        <v>-9.666005637475715e-12</v>
       </c>
       <c r="E40" t="n">
         <v/>
       </c>
       <c r="F40" t="n">
-        <v>-1.479208920162639e-11</v>
+        <v>2.522650216764293e-12</v>
       </c>
       <c r="G40" t="n">
-        <v>1.623920074189638e-10</v>
+        <v>5.075322632994215e-11</v>
       </c>
       <c r="H40" t="n">
-        <v>4.230918170072873e-10</v>
+        <v>2.420763868352722e-10</v>
       </c>
       <c r="I40" t="n">
-        <v>1.372051192426289e-10</v>
+        <v>8.391849089558241e-11</v>
       </c>
     </row>
     <row r="41">
@@ -2490,22 +2490,22 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2.444534767727938e-10</v>
+        <v>-1.985535424171089e-11</v>
       </c>
       <c r="E41" t="n">
         <v/>
       </c>
       <c r="F41" t="n">
-        <v>2.251153837845759e-10</v>
+        <v>-3.756631683915198e-12</v>
       </c>
       <c r="G41" t="n">
-        <v>1.72267993269304e-10</v>
+        <v>1.333313704672364e-10</v>
       </c>
       <c r="H41" t="n">
-        <v>4.825927387585614e-11</v>
+        <v>-4.836670414878655e-12</v>
       </c>
       <c r="I41" t="n">
-        <v>0.165465126703093</v>
+        <v>0.1748625092892639</v>
       </c>
     </row>
     <row r="42">
@@ -2525,22 +2525,22 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-2.385430264972232e-11</v>
+        <v>-1.653142568097186e-11</v>
       </c>
       <c r="E42" t="n">
         <v/>
       </c>
       <c r="F42" t="n">
-        <v>-5.395998829116281e-11</v>
+        <v>-5.767801455811101e-12</v>
       </c>
       <c r="G42" t="n">
-        <v>-2.284538329736149e-11</v>
+        <v>4.192241360425644e-11</v>
       </c>
       <c r="H42" t="n">
-        <v>3.845542368377339e-12</v>
+        <v>5.388146271108125e-12</v>
       </c>
       <c r="I42" t="n">
-        <v>-3.530843598607474e-11</v>
+        <v>3.415415933299357e-11</v>
       </c>
     </row>
     <row r="43">
@@ -2560,22 +2560,22 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-5.06610491910047e-11</v>
+        <v>6.888121872248338e-11</v>
       </c>
       <c r="E43" t="n">
         <v/>
       </c>
       <c r="F43" t="n">
-        <v>-5.728165447394162e-11</v>
+        <v>1.256588968710767e-11</v>
       </c>
       <c r="G43" t="n">
-        <v>-2.616908181025379e-11</v>
+        <v>5.719450672542947e-12</v>
       </c>
       <c r="H43" t="n">
-        <v>-2.19211021320744e-12</v>
+        <v>1.380402726208834e-11</v>
       </c>
       <c r="I43" t="n">
-        <v>3.097563503719076e-11</v>
+        <v>1.350185274786154e-11</v>
       </c>
     </row>
     <row r="44">
@@ -2595,22 +2595,22 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-3.982427607311774e-11</v>
+        <v>-1.867540756937877e-11</v>
       </c>
       <c r="E44" t="n">
         <v/>
       </c>
       <c r="F44" t="n">
-        <v>-4.795962911693949e-11</v>
+        <v>3.870948705619461e-12</v>
       </c>
       <c r="G44" t="n">
-        <v>7.503226792805972e-11</v>
+        <v>9.977721284439171e-10</v>
       </c>
       <c r="H44" t="n">
-        <v>9.751014530092659e-12</v>
+        <v>8.606310800151748e-12</v>
       </c>
       <c r="I44" t="n">
-        <v>-3.415039867580941e-11</v>
+        <v>7.005960162970715e-11</v>
       </c>
     </row>
     <row r="45">
@@ -2630,22 +2630,22 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>-4.679955785400583e-11</v>
+        <v>-1.821866224591861e-11</v>
       </c>
       <c r="E45" t="n">
         <v/>
       </c>
       <c r="F45" t="n">
-        <v>-5.273583250913805e-11</v>
+        <v>-3.629508073158747e-12</v>
       </c>
       <c r="G45" t="n">
-        <v>-2.462257253055324e-11</v>
+        <v>4.72202908776816e-11</v>
       </c>
       <c r="H45" t="n">
-        <v>4.912340076962926e-11</v>
+        <v>5.301759799886398e-11</v>
       </c>
       <c r="I45" t="n">
-        <v>-2.912377868568692e-11</v>
+        <v>4.346688832748383e-11</v>
       </c>
     </row>
     <row r="46">
@@ -2665,22 +2665,22 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>-4.426903550195624e-11</v>
+        <v>-2.040285926682139e-11</v>
       </c>
       <c r="E46" t="n">
         <v/>
       </c>
       <c r="F46" t="n">
-        <v>-4.558900988364762e-11</v>
+        <v>-6.950427162500832e-12</v>
       </c>
       <c r="G46" t="n">
-        <v>-3.211915101656658e-11</v>
+        <v>1.421024558749814e-10</v>
       </c>
       <c r="H46" t="n">
-        <v>-1.604062305989931e-11</v>
+        <v>-7.185431264093062e-12</v>
       </c>
       <c r="I46" t="n">
-        <v>-1.557056038728996e-11</v>
+        <v>1.611811770102112e-10</v>
       </c>
     </row>
     <row r="47">
@@ -2700,22 +2700,22 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-2.21773794146068e-11</v>
+        <v>-1.732940148527849e-11</v>
       </c>
       <c r="E47" t="n">
         <v/>
       </c>
       <c r="F47" t="n">
-        <v>-4.985374741137029e-11</v>
+        <v>-2.631811866142333e-12</v>
       </c>
       <c r="G47" t="n">
-        <v>-4.078625484598153e-11</v>
+        <v>3.387235571712831e-11</v>
       </c>
       <c r="H47" t="n">
-        <v>1.009539347252154e-11</v>
+        <v>5.104648959822795e-12</v>
       </c>
       <c r="I47" t="n">
-        <v>-3.58756153552887e-11</v>
+        <v>2.285654703143029e-11</v>
       </c>
     </row>
     <row r="48">
@@ -2735,22 +2735,22 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-5.109394164340153e-11</v>
+        <v>-1.715179980910297e-11</v>
       </c>
       <c r="E48" t="n">
         <v/>
       </c>
       <c r="F48" t="n">
-        <v>-5.405773637560262e-11</v>
+        <v>3.63900969895414e-12</v>
       </c>
       <c r="G48" t="n">
-        <v>-4.54762900996834e-11</v>
+        <v>8.787453917824833e-13</v>
       </c>
       <c r="H48" t="n">
-        <v>-1.105407813910407e-11</v>
+        <v>-3.976615461867086e-13</v>
       </c>
       <c r="I48" t="n">
-        <v>-2.584932818090574e-11</v>
+        <v>-3.265074757378019e-13</v>
       </c>
     </row>
     <row r="49">
@@ -2770,22 +2770,22 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-4.166434588280098e-11</v>
+        <v>-1.940639315774444e-11</v>
       </c>
       <c r="E49" t="n">
         <v/>
       </c>
       <c r="F49" t="n">
-        <v>-3.597625007706093e-11</v>
+        <v>2.030826737014188e-11</v>
       </c>
       <c r="G49" t="n">
-        <v>-3.755527341489568e-11</v>
+        <v>1.372420326836486e-10</v>
       </c>
       <c r="H49" t="n">
-        <v>1.239470617154357e-11</v>
+        <v>3.632989051282229e-12</v>
       </c>
       <c r="I49" t="n">
-        <v>-4.209279340719989e-11</v>
+        <v>2.187410681357104e-11</v>
       </c>
     </row>
     <row r="50">
@@ -2805,22 +2805,22 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-5.499455096810766e-11</v>
+        <v>-1.903575150069756e-11</v>
       </c>
       <c r="E50" t="n">
         <v/>
       </c>
       <c r="F50" t="n">
-        <v>-5.69902639455461e-11</v>
+        <v>-2.046097060817134e-12</v>
       </c>
       <c r="G50" t="n">
-        <v>-4.827954563623042e-11</v>
+        <v>3.433388335192275e-11</v>
       </c>
       <c r="H50" t="n">
-        <v>2.12648817735814e-11</v>
+        <v>3.017139158457534e-11</v>
       </c>
       <c r="I50" t="n">
-        <v>-4.013286376115436e-11</v>
+        <v>2.275754150033124e-11</v>
       </c>
     </row>
     <row r="51">
@@ -2840,22 +2840,22 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>-5.754881513874569e-11</v>
+        <v>-2.004418878055731e-11</v>
       </c>
       <c r="E51" t="n">
         <v/>
       </c>
       <c r="F51" t="n">
-        <v>-5.760680131747136e-11</v>
+        <v>-5.933800231422675e-13</v>
       </c>
       <c r="G51" t="n">
-        <v>-5.214950985120448e-11</v>
+        <v>1.070211266896005e-10</v>
       </c>
       <c r="H51" t="n">
-        <v>-2.097907571596346e-11</v>
+        <v>-3.522171225305779e-12</v>
       </c>
       <c r="I51" t="n">
-        <v>4.072685534097524e-12</v>
+        <v>2.771593392952255e-10</v>
       </c>
     </row>
     <row r="52">
@@ -2875,22 +2875,22 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>-1.832063766762179e-11</v>
+        <v>-1.741244688398596e-11</v>
       </c>
       <c r="E52" t="n">
         <v/>
       </c>
       <c r="F52" t="n">
-        <v>-5.010439993933176e-11</v>
+        <v>-8.755471517736687e-12</v>
       </c>
       <c r="G52" t="n">
-        <v>-1.009190460894219e-11</v>
+        <v>1.726045346733226e-11</v>
       </c>
       <c r="H52" t="n">
-        <v>-8.152642053897151e-12</v>
+        <v>-2.807929268624375e-12</v>
       </c>
       <c r="I52" t="n">
-        <v>-2.823903187125595e-11</v>
+        <v>1.978972992110858e-11</v>
       </c>
     </row>
     <row r="53">
@@ -2910,22 +2910,22 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>-1.650423516611827e-11</v>
+        <v>-1.360632167002799e-11</v>
       </c>
       <c r="E53" t="n">
         <v/>
       </c>
       <c r="F53" t="n">
-        <v>-2.562100816950096e-11</v>
+        <v>-3.778290611348033e-12</v>
       </c>
       <c r="G53" t="n">
-        <v>3.200449252617342e-11</v>
+        <v>-1.538368811459094e-12</v>
       </c>
       <c r="H53" t="n">
-        <v>4.438556712778404e-12</v>
+        <v>-3.570553044150819e-12</v>
       </c>
       <c r="I53" t="n">
-        <v>5.252058191551391e-11</v>
+        <v>1.485698995186186e-12</v>
       </c>
     </row>
     <row r="54">
@@ -2945,22 +2945,22 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-4.335652016681127e-11</v>
+        <v>-1.898486372567413e-11</v>
       </c>
       <c r="E54" t="n">
         <v/>
       </c>
       <c r="F54" t="n">
-        <v>-4.178172235139466e-11</v>
+        <v>2.561258474489215e-12</v>
       </c>
       <c r="G54" t="n">
-        <v>-2.549103644552924e-12</v>
+        <v>5.336461293239866e-11</v>
       </c>
       <c r="H54" t="n">
-        <v>-4.335619717034244e-12</v>
+        <v>-4.583987403151216e-13</v>
       </c>
       <c r="I54" t="n">
-        <v>-2.76247479134636e-11</v>
+        <v>2.655094079594038e-11</v>
       </c>
     </row>
     <row r="55">
@@ -2980,22 +2980,22 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-5.085014972591898e-11</v>
+        <v>-1.891526373815077e-11</v>
       </c>
       <c r="E55" t="n">
         <v/>
       </c>
       <c r="F55" t="n">
-        <v>-5.508402485649774e-11</v>
+        <v>-1.935313300762028e-12</v>
       </c>
       <c r="G55" t="n">
-        <v>4.901686472322766e-11</v>
+        <v>7.251162133631937e-11</v>
       </c>
       <c r="H55" t="n">
-        <v>-1.551478273699537e-11</v>
+        <v>5.706470657034893e-14</v>
       </c>
       <c r="I55" t="n">
-        <v>-2.923891091648149e-11</v>
+        <v>4.253575815275362e-11</v>
       </c>
     </row>
     <row r="56">
@@ -3015,22 +3015,22 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-4.963987415899833e-11</v>
+        <v>-2.052889620993699e-11</v>
       </c>
       <c r="E56" t="n">
         <v/>
       </c>
       <c r="F56" t="n">
-        <v>-4.910430621814666e-11</v>
+        <v>-9.632191497316397e-12</v>
       </c>
       <c r="G56" t="n">
-        <v>-3.076925211702286e-11</v>
+        <v>3.777950518014849e-11</v>
       </c>
       <c r="H56" t="n">
-        <v>-2.747138750022325e-11</v>
+        <v>-9.775982045031538e-12</v>
       </c>
       <c r="I56" t="n">
-        <v>-3.912984100477405e-13</v>
+        <v>7.18730571916394e-11</v>
       </c>
     </row>
     <row r="57">
@@ -3050,22 +3050,22 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>-1.19266051866991e-11</v>
+        <v>-2.024970753269523e-11</v>
       </c>
       <c r="E57" t="n">
         <v/>
       </c>
       <c r="F57" t="n">
-        <v>-4.751899005696145e-11</v>
+        <v>-9.391743124150867e-12</v>
       </c>
       <c r="G57" t="n">
-        <v>-2.167466866504167e-11</v>
+        <v>3.191909702804344e-11</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.558873409859319e-11</v>
+        <v>-7.717679952881946e-12</v>
       </c>
       <c r="I57" t="n">
-        <v>-6.754653862582502e-11</v>
+        <v>-5.471172675213415e-12</v>
       </c>
     </row>
     <row r="58">
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1.693496616275872e-10</v>
+        <v>-2.012981697768131e-11</v>
       </c>
       <c r="E58" t="n">
         <v/>
       </c>
       <c r="F58" t="n">
-        <v>1.856985497287147e-10</v>
+        <v>-7.072327922755138e-12</v>
       </c>
       <c r="G58" t="n">
-        <v>5.766679524372377e-11</v>
+        <v>5.948048840338254e-13</v>
       </c>
       <c r="H58" t="n">
-        <v>7.019798351386099e-12</v>
+        <v>-9.674362875395187e-12</v>
       </c>
       <c r="I58" t="n">
-        <v>-6.421375696370808e-11</v>
+        <v>-1.049497146438432e-11</v>
       </c>
     </row>
     <row r="59">
@@ -3120,22 +3120,22 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>-2.6691142539807e-11</v>
+        <v>-2.067775946473263e-11</v>
       </c>
       <c r="E59" t="n">
         <v/>
       </c>
       <c r="F59" t="n">
-        <v>-1.517030455127552e-11</v>
+        <v>-3.940510483897191e-12</v>
       </c>
       <c r="G59" t="n">
-        <v>-5.447784287778652e-12</v>
+        <v>9.861241237844133e-11</v>
       </c>
       <c r="H59" t="n">
-        <v>-9.742359399964309e-12</v>
+        <v>-8.626285200726418e-12</v>
       </c>
       <c r="I59" t="n">
-        <v>-6.839783324970595e-11</v>
+        <v>-5.988884407292063e-12</v>
       </c>
     </row>
     <row r="60">
@@ -3155,22 +3155,22 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>-5.106458396296897e-11</v>
+        <v>-2.011004010909518e-11</v>
       </c>
       <c r="E60" t="n">
         <v/>
       </c>
       <c r="F60" t="n">
-        <v>-5.531211925623155e-11</v>
+        <v>-5.491083957723916e-13</v>
       </c>
       <c r="G60" t="n">
-        <v>1.628006223811657e-11</v>
+        <v>2.967920813869968e-10</v>
       </c>
       <c r="H60" t="n">
-        <v>-1.883096359059573e-11</v>
+        <v>-3.332098346085417e-12</v>
       </c>
       <c r="I60" t="n">
-        <v>-6.625315630300646e-11</v>
+        <v>-9.476580861496635e-13</v>
       </c>
     </row>
     <row r="61">
@@ -3190,22 +3190,22 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>-4.334448974946322e-11</v>
+        <v>-2.05756235497734e-11</v>
       </c>
       <c r="E61" t="n">
         <v/>
       </c>
       <c r="F61" t="n">
-        <v>-4.613462872401687e-11</v>
+        <v>-9.637162242676949e-12</v>
       </c>
       <c r="G61" t="n">
-        <v>-2.631261081464679e-11</v>
+        <v>3.006198166301387e-11</v>
       </c>
       <c r="H61" t="n">
-        <v>2.082508641399233e-12</v>
+        <v>-3.668286073844835e-12</v>
       </c>
       <c r="I61" t="n">
-        <v>-6.782555612299375e-11</v>
+        <v>-5.804396732133344e-12</v>
       </c>
     </row>
     <row r="62">
@@ -3225,22 +3225,22 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>-5.462175188528885e-11</v>
+        <v>-9.832919697511444e-12</v>
       </c>
       <c r="E62" t="n">
-        <v>-5.113871220258026e-11</v>
+        <v>3.331841537264232e-13</v>
       </c>
       <c r="F62" t="n">
         <v/>
       </c>
       <c r="G62" t="n">
-        <v>1.052171226748776e-11</v>
+        <v>2.014209744319861e-10</v>
       </c>
       <c r="H62" t="n">
-        <v>7.910333149605348e-12</v>
+        <v>2.953103098256373e-12</v>
       </c>
       <c r="I62" t="n">
-        <v>5.974047497905563e-10</v>
+        <v>4.673234387952061e-10</v>
       </c>
     </row>
     <row r="63">
@@ -3260,22 +3260,22 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>-2.793250264535734e-11</v>
+        <v>-9.923485585281325e-12</v>
       </c>
       <c r="E63" t="n">
-        <v>-1.909159165242768e-11</v>
+        <v>-5.67872913049431e-12</v>
       </c>
       <c r="F63" t="n">
         <v/>
       </c>
       <c r="G63" t="n">
-        <v>6.843537352954831e-12</v>
+        <v>-6.314183167237903e-13</v>
       </c>
       <c r="H63" t="n">
-        <v>8.203558764151946e-12</v>
+        <v>-7.012764635959664e-13</v>
       </c>
       <c r="I63" t="n">
-        <v>3.275048883321129e-12</v>
+        <v>5.950391966970896e-13</v>
       </c>
     </row>
     <row r="64">
@@ -3295,22 +3295,22 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>-5.168909630097966e-11</v>
+        <v>-8.731616445548724e-12</v>
       </c>
       <c r="E64" t="n">
-        <v>-4.877217128659812e-11</v>
+        <v>-2.968910829921884e-12</v>
       </c>
       <c r="F64" t="n">
         <v/>
       </c>
       <c r="G64" t="n">
-        <v>1.667687598621052e-10</v>
+        <v>2.331869001574307e-10</v>
       </c>
       <c r="H64" t="n">
-        <v>1.167776610871668e-11</v>
+        <v>5.865776147374326e-12</v>
       </c>
       <c r="I64" t="n">
-        <v>5.378608503048576e-10</v>
+        <v>6.064027571245704e-10</v>
       </c>
     </row>
     <row r="65">
@@ -3330,22 +3330,22 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>-5.318722098294216e-11</v>
+        <v>-1.185334956606791e-11</v>
       </c>
       <c r="E65" t="n">
-        <v>-5.071127108300489e-11</v>
+        <v>-8.935684292644143e-12</v>
       </c>
       <c r="F65" t="n">
         <v/>
       </c>
       <c r="G65" t="n">
-        <v>1.890485304129783e-11</v>
+        <v>8.712349185405685e-11</v>
       </c>
       <c r="H65" t="n">
-        <v>5.863000877143757e-11</v>
+        <v>1.709443244392435e-11</v>
       </c>
       <c r="I65" t="n">
-        <v>5.207704716607288e-10</v>
+        <v>3.43376534286808e-10</v>
       </c>
     </row>
     <row r="66">
@@ -3365,22 +3365,22 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>-5.341925620344185e-11</v>
+        <v>-1.315378490740854e-11</v>
       </c>
       <c r="E66" t="n">
-        <v>-4.908208805988965e-11</v>
+        <v>-9.803325608881655e-12</v>
       </c>
       <c r="F66" t="n">
         <v/>
       </c>
       <c r="G66" t="n">
-        <v>-1.832382576724743e-11</v>
+        <v>1.735714221757273e-10</v>
       </c>
       <c r="H66" t="n">
-        <v>-2.074809136386585e-11</v>
+        <v>-8.174646982334858e-12</v>
       </c>
       <c r="I66" t="n">
-        <v>3.224961415979213e-09</v>
+        <v>8.055328183460255e-10</v>
       </c>
     </row>
     <row r="67">
@@ -3400,22 +3400,22 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>-3.449376952968559e-11</v>
+        <v>4.171153112926063e-11</v>
       </c>
       <c r="E67" t="n">
-        <v>-5.262065728994036e-11</v>
+        <v>-5.911709162483406e-12</v>
       </c>
       <c r="F67" t="n">
         <v/>
       </c>
       <c r="G67" t="n">
-        <v>2.509820258079062e-11</v>
+        <v>1.53338034820275e-10</v>
       </c>
       <c r="H67" t="n">
-        <v>5.239186627996527e-12</v>
+        <v>6.27594995347649e-12</v>
       </c>
       <c r="I67" t="n">
-        <v>4.375200558381708e-10</v>
+        <v>5.443515214060961e-10</v>
       </c>
     </row>
     <row r="68">
@@ -3435,22 +3435,22 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>-4.06096873874823e-11</v>
+        <v>2.432486155416121e-11</v>
       </c>
       <c r="E68" t="n">
-        <v>-4.468738412199919e-11</v>
+        <v>1.236798117424034e-11</v>
       </c>
       <c r="F68" t="n">
         <v/>
       </c>
       <c r="G68" t="n">
-        <v>1.350255232067364e-11</v>
+        <v>1.918535679179958e-12</v>
       </c>
       <c r="H68" t="n">
-        <v>2.625143811905795e-12</v>
+        <v>1.318176596802744e-11</v>
       </c>
       <c r="I68" t="n">
-        <v>7.38792513078936e-13</v>
+        <v>1.586072173485416e-12</v>
       </c>
     </row>
     <row r="69">
@@ -3470,22 +3470,22 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>-5.559250032996816e-11</v>
+        <v>5.796301823910705e-12</v>
       </c>
       <c r="E69" t="n">
-        <v>-5.708829106263944e-11</v>
+        <v>2.454106425706798e-12</v>
       </c>
       <c r="F69" t="n">
         <v/>
       </c>
       <c r="G69" t="n">
-        <v>8.435188853402902e-11</v>
+        <v>5.030241114738261e-09</v>
       </c>
       <c r="H69" t="n">
-        <v>-1.046674143094892e-11</v>
+        <v>5.675088980447437e-12</v>
       </c>
       <c r="I69" t="n">
-        <v>3.545951612047474e-10</v>
+        <v>1.279323666381533e-09</v>
       </c>
     </row>
     <row r="70">
@@ -3505,22 +3505,22 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>-3.541736672585853e-11</v>
+        <v>-2.319217649621378e-12</v>
       </c>
       <c r="E70" t="n">
-        <v>-3.86264804569137e-11</v>
+        <v>-4.8471903214192e-12</v>
       </c>
       <c r="F70" t="n">
         <v/>
       </c>
       <c r="G70" t="n">
-        <v>4.286387222627926e-11</v>
+        <v>1.654752210551478e-10</v>
       </c>
       <c r="H70" t="n">
-        <v>9.399521062628057e-11</v>
+        <v>3.239402626900391e-11</v>
       </c>
       <c r="I70" t="n">
-        <v>5.308626785042571e-10</v>
+        <v>5.722221428994648e-10</v>
       </c>
     </row>
     <row r="71">
@@ -3540,22 +3540,22 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1.769103655453694e-11</v>
+        <v>-8.5163255093027e-12</v>
       </c>
       <c r="E71" t="n">
-        <v>2.788440598506605e-11</v>
+        <v>-8.214079797489812e-12</v>
       </c>
       <c r="F71" t="n">
         <v/>
       </c>
       <c r="G71" t="n">
-        <v>-7.422797038060974e-12</v>
+        <v>5.920169027911063e-10</v>
       </c>
       <c r="H71" t="n">
-        <v>-9.080663146405895e-12</v>
+        <v>-8.550076250330172e-12</v>
       </c>
       <c r="I71" t="n">
-        <v>1.107409720830978e-08</v>
+        <v>1.996131773273122e-09</v>
       </c>
     </row>
     <row r="72">
@@ -3575,22 +3575,22 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>-2.318203688028629e-11</v>
+        <v>7.377200361230742e-10</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.594548373637881e-11</v>
+        <v>-2.047921913262664e-13</v>
       </c>
       <c r="F72" t="n">
         <v/>
       </c>
       <c r="G72" t="n">
-        <v>1.594059790207423e-10</v>
+        <v>1.656060969715372e-10</v>
       </c>
       <c r="H72" t="n">
-        <v>7.662842618955299e-11</v>
+        <v>1.568947135030311e-11</v>
       </c>
       <c r="I72" t="n">
-        <v>3.169384782005986e-09</v>
+        <v>6.735910468890297e-10</v>
       </c>
     </row>
     <row r="73">
@@ -3610,22 +3610,22 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>-3.069617332359391e-11</v>
+        <v>8.751112804823273e-11</v>
       </c>
       <c r="E73" t="n">
-        <v>-3.48689440775815e-11</v>
+        <v>4.390769746705679e-10</v>
       </c>
       <c r="F73" t="n">
         <v/>
       </c>
       <c r="G73" t="n">
-        <v>1.470833272731156e-10</v>
+        <v>4.093883459785454e-09</v>
       </c>
       <c r="H73" t="n">
-        <v>8.23701440078367e-11</v>
+        <v>5.462010211436343e-11</v>
       </c>
       <c r="I73" t="n">
-        <v>1.020551180832014e-08</v>
+        <v>2.614933685261347e-09</v>
       </c>
     </row>
     <row r="74">
@@ -3645,22 +3645,22 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>3.822003699529595e-11</v>
+        <v>2.952588098251313e-11</v>
       </c>
       <c r="E74" t="n">
-        <v>1.541986600424012e-11</v>
+        <v>2.090126274790815e-11</v>
       </c>
       <c r="F74" t="n">
         <v/>
       </c>
       <c r="G74" t="n">
-        <v>-5.139780072376636e-11</v>
+        <v>0.1642889280724779</v>
       </c>
       <c r="H74" t="n">
-        <v>8.027105274932522e-11</v>
+        <v>1.909516033495786e-11</v>
       </c>
       <c r="I74" t="n">
-        <v>3.487933258554552e-09</v>
+        <v>2.579438046625887e-09</v>
       </c>
     </row>
     <row r="75">
@@ -3680,22 +3680,22 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>9.341689171340463e-12</v>
+        <v>9.110563381731232e-12</v>
       </c>
       <c r="E75" t="n">
-        <v>-7.14543439344548e-12</v>
+        <v>3.773686245888334e-12</v>
       </c>
       <c r="F75" t="n">
         <v/>
       </c>
       <c r="G75" t="n">
-        <v>2.073657384792493e-10</v>
+        <v>1.811510644239889e-10</v>
       </c>
       <c r="H75" t="n">
-        <v>-3.355959615142595e-12</v>
+        <v>1.619645544440863e-10</v>
       </c>
       <c r="I75" t="n">
-        <v>5.190092939562687e-09</v>
+        <v>7.785716724756581e-10</v>
       </c>
     </row>
     <row r="76">
@@ -3715,22 +3715,22 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>9.496333621103761e-11</v>
+        <v>-3.023782702733629e-12</v>
       </c>
       <c r="E76" t="n">
-        <v>8.754599821144254e-11</v>
+        <v>-2.514062607665928e-12</v>
       </c>
       <c r="F76" t="n">
         <v/>
       </c>
       <c r="G76" t="n">
-        <v>2.081509805481919e-11</v>
+        <v>1.083093215289345e-09</v>
       </c>
       <c r="H76" t="n">
-        <v>9.722728543769586e-12</v>
+        <v>-5.642789649249366e-12</v>
       </c>
       <c r="I76" t="n">
-        <v>6.038348849487467e-11</v>
+        <v>0.2973395027496102</v>
       </c>
     </row>
     <row r="77">
@@ -3750,22 +3750,22 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>-2.954622381258861e-11</v>
+        <v>2.793385137883039e-11</v>
       </c>
       <c r="E77" t="n">
-        <v>-4.927282617406387e-11</v>
+        <v>-2.653134102656471e-12</v>
       </c>
       <c r="F77" t="n">
         <v/>
       </c>
       <c r="G77" t="n">
-        <v>-1.443399531591686e-11</v>
+        <v>1.442493465070701e-10</v>
       </c>
       <c r="H77" t="n">
-        <v>1.449517866417656e-11</v>
+        <v>5.10386009502002e-12</v>
       </c>
       <c r="I77" t="n">
-        <v>5.606000742879348e-10</v>
+        <v>4.544384505422908e-10</v>
       </c>
     </row>
     <row r="78">
@@ -3785,22 +3785,22 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>-5.55979230098056e-11</v>
+        <v>-1.221103963707667e-12</v>
       </c>
       <c r="E78" t="n">
-        <v>-5.528178112652478e-11</v>
+        <v>1.860835460886081e-11</v>
       </c>
       <c r="F78" t="n">
         <v/>
       </c>
       <c r="G78" t="n">
-        <v>-2.73642387445101e-11</v>
+        <v>7.195714365453871e-10</v>
       </c>
       <c r="H78" t="n">
-        <v>-5.408410669745751e-12</v>
+        <v>1.684856511414653e-12</v>
       </c>
       <c r="I78" t="n">
-        <v>4.924505373261752e-10</v>
+        <v>5.930429311126752e-10</v>
       </c>
     </row>
     <row r="79">
@@ -3820,22 +3820,22 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1.531674994519536e-11</v>
+        <v>3.7383096096251e-13</v>
       </c>
       <c r="E79" t="n">
-        <v>1.235131785373994e-11</v>
+        <v>4.554023496772576e-12</v>
       </c>
       <c r="F79" t="n">
         <v/>
       </c>
       <c r="G79" t="n">
-        <v>-2.164783882163088e-11</v>
+        <v>9.380092563574003e-13</v>
       </c>
       <c r="H79" t="n">
-        <v>1.366434456220133e-11</v>
+        <v>-1.345217379143131e-13</v>
       </c>
       <c r="I79" t="n">
-        <v>4.154657086144367e-12</v>
+        <v>8.201529473703902e-13</v>
       </c>
     </row>
     <row r="80">
@@ -3855,22 +3855,22 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>-5.544668674072658e-11</v>
+        <v>-4.60132681505562e-12</v>
       </c>
       <c r="E80" t="n">
-        <v>-5.630422718728508e-11</v>
+        <v>-2.247792555745306e-12</v>
       </c>
       <c r="F80" t="n">
         <v/>
       </c>
       <c r="G80" t="n">
-        <v>-2.121092434313205e-11</v>
+        <v>1.456966167391813e-10</v>
       </c>
       <c r="H80" t="n">
-        <v>3.850103513774757e-11</v>
+        <v>2.461506600474495e-11</v>
       </c>
       <c r="I80" t="n">
-        <v>4.617110346254979e-10</v>
+        <v>4.519730593615772e-10</v>
       </c>
     </row>
     <row r="81">
@@ -3890,22 +3890,22 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>-5.595147240873817e-11</v>
+        <v>-5.193045643816112e-12</v>
       </c>
       <c r="E81" t="n">
-        <v>-5.569820614747182e-11</v>
+        <v>-8.243464498468357e-13</v>
       </c>
       <c r="F81" t="n">
         <v/>
       </c>
       <c r="G81" t="n">
-        <v>-3.374061204567454e-11</v>
+        <v>5.97690397843443e-10</v>
       </c>
       <c r="H81" t="n">
-        <v>-1.964598954902831e-11</v>
+        <v>-4.410332203596523e-12</v>
       </c>
       <c r="I81" t="n">
-        <v>3.483443450180224e-09</v>
+        <v>3.903601882722328e-09</v>
       </c>
     </row>
     <row r="82">
@@ -3925,22 +3925,22 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>-3.304980730021997e-11</v>
+        <v>3.26046806430306e-12</v>
       </c>
       <c r="E82" t="n">
-        <v>-5.084925550779915e-11</v>
+        <v>-8.800270514941141e-12</v>
       </c>
       <c r="F82" t="n">
         <v/>
       </c>
       <c r="G82" t="n">
-        <v>3.263601479557342e-11</v>
+        <v>8.742821693874261e-11</v>
       </c>
       <c r="H82" t="n">
-        <v>-9.782411274580005e-12</v>
+        <v>-1.926608282042029e-12</v>
       </c>
       <c r="I82" t="n">
-        <v>5.749494396086643e-10</v>
+        <v>3.571773680173611e-10</v>
       </c>
     </row>
     <row r="83">
@@ -3960,22 +3960,22 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>-3.483110508418477e-11</v>
+        <v>-5.280030977914827e-12</v>
       </c>
       <c r="E83" t="n">
-        <v>-3.270596346706301e-11</v>
+        <v>2.033957799052043e-12</v>
       </c>
       <c r="F83" t="n">
         <v/>
       </c>
       <c r="G83" t="n">
-        <v>4.180946337269116e-11</v>
+        <v>2.104152723176256e-10</v>
       </c>
       <c r="H83" t="n">
-        <v>3.309207317730256e-12</v>
+        <v>-9.082833798447927e-13</v>
       </c>
       <c r="I83" t="n">
-        <v>9.173950130870091e-10</v>
+        <v>5.031091957741871e-10</v>
       </c>
     </row>
     <row r="84">
@@ -3995,22 +3995,22 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>-1.060074977784742e-11</v>
+        <v>-4.355625512158293e-12</v>
       </c>
       <c r="E84" t="n">
-        <v>-1.408205238832183e-11</v>
+        <v>-3.414057825823867e-12</v>
       </c>
       <c r="F84" t="n">
         <v/>
       </c>
       <c r="G84" t="n">
-        <v>2.418478980731138e-11</v>
+        <v>-3.150137017578083e-13</v>
       </c>
       <c r="H84" t="n">
-        <v>-6.105794609186956e-12</v>
+        <v>-2.197093527468859e-12</v>
       </c>
       <c r="I84" t="n">
-        <v>5.16123272558087e-12</v>
+        <v>8.455684488021472e-13</v>
       </c>
     </row>
     <row r="85">
@@ -4030,22 +4030,22 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>-5.543210160851926e-11</v>
+        <v>-3.724539002223453e-12</v>
       </c>
       <c r="E85" t="n">
-        <v>-5.621608463746675e-11</v>
+        <v>-2.119516301227907e-12</v>
       </c>
       <c r="F85" t="n">
         <v/>
       </c>
       <c r="G85" t="n">
-        <v>1.444625509226485e-10</v>
+        <v>2.460123592872045e-10</v>
       </c>
       <c r="H85" t="n">
-        <v>-1.73040328422352e-11</v>
+        <v>4.791550552121084e-13</v>
       </c>
       <c r="I85" t="n">
-        <v>4.850004982477932e-10</v>
+        <v>6.490099282678452e-10</v>
       </c>
     </row>
     <row r="86">
@@ -4065,22 +4065,22 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>-4.850924541185535e-11</v>
+        <v>-1.13268069370985e-11</v>
       </c>
       <c r="E86" t="n">
-        <v>-4.726642489131185e-11</v>
+        <v>-9.759440907890533e-12</v>
       </c>
       <c r="F86" t="n">
         <v/>
       </c>
       <c r="G86" t="n">
-        <v>-1.525989503575997e-11</v>
+        <v>1.742000916364692e-10</v>
       </c>
       <c r="H86" t="n">
-        <v>-3.093516294980684e-11</v>
+        <v>-9.926142895878708e-12</v>
       </c>
       <c r="I86" t="n">
-        <v>4.860727216474844e-09</v>
+        <v>8.243225931984795e-10</v>
       </c>
     </row>
     <row r="87">
@@ -4100,22 +4100,22 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>-3.192899371820218e-11</v>
+        <v>-3.563808407271924e-12</v>
       </c>
       <c r="E87" t="n">
-        <v>-5.01345788835582e-11</v>
+        <v>-9.474563849502317e-12</v>
       </c>
       <c r="F87" t="n">
         <v/>
       </c>
       <c r="G87" t="n">
-        <v>-1.799116432537737e-11</v>
+        <v>1.440496750647754e-10</v>
       </c>
       <c r="H87" t="n">
-        <v>-2.090680477721303e-11</v>
+        <v>-8.105284872749388e-12</v>
       </c>
       <c r="I87" t="n">
-        <v>1.418181848774339e-10</v>
+        <v>1.936722008946905e-10</v>
       </c>
     </row>
     <row r="88">
@@ -4135,22 +4135,22 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>2.732280983054255e-11</v>
+        <v>-1.017992206064587e-11</v>
       </c>
       <c r="E88" t="n">
-        <v>5.388660119512945e-11</v>
+        <v>-3.475338458624481e-12</v>
       </c>
       <c r="F88" t="n">
         <v/>
       </c>
       <c r="G88" t="n">
-        <v>-1.365654554470058e-11</v>
+        <v>7.17698666003431e-10</v>
       </c>
       <c r="H88" t="n">
-        <v>-5.869137317998713e-12</v>
+        <v>-9.373023423677681e-12</v>
       </c>
       <c r="I88" t="n">
-        <v>1.850517878468097e-10</v>
+        <v>2.152059251902602e-10</v>
       </c>
     </row>
     <row r="89">
@@ -4170,22 +4170,22 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>6.38262232044145e-11</v>
+        <v>-1.019996511306999e-11</v>
       </c>
       <c r="E89" t="n">
-        <v>6.550978060574619e-11</v>
+        <v>-7.583267037849307e-12</v>
       </c>
       <c r="F89" t="n">
         <v/>
       </c>
       <c r="G89" t="n">
-        <v>-2.288298607345403e-11</v>
+        <v>6.900781992811015e-13</v>
       </c>
       <c r="H89" t="n">
-        <v>-1.838732389261924e-11</v>
+        <v>-1.002183991137386e-11</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.332952511208723e-11</v>
+        <v>-9.685953052326753e-13</v>
       </c>
     </row>
     <row r="90">
@@ -4205,22 +4205,22 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>-5.673191327697436e-11</v>
+        <v>-5.573821441547803e-12</v>
       </c>
       <c r="E90" t="n">
-        <v>-5.754700767753461e-11</v>
+        <v>-8.298370453454962e-13</v>
       </c>
       <c r="F90" t="n">
         <v/>
       </c>
       <c r="G90" t="n">
-        <v>2.068927965247206e-11</v>
+        <v>1.619839078062647e-09</v>
       </c>
       <c r="H90" t="n">
-        <v>-2.257188643845526e-11</v>
+        <v>-4.256251848419649e-12</v>
       </c>
       <c r="I90" t="n">
-        <v>1.369699851942391e-10</v>
+        <v>2.897020782864481e-10</v>
       </c>
     </row>
     <row r="91">
@@ -4240,22 +4240,22 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>-4.771372730090029e-11</v>
+        <v>-1.175051793986378e-11</v>
       </c>
       <c r="E91" t="n">
-        <v>-4.833111014189622e-11</v>
+        <v>-9.787316132823562e-12</v>
       </c>
       <c r="F91" t="n">
         <v/>
       </c>
       <c r="G91" t="n">
-        <v>-2.009061554089769e-11</v>
+        <v>1.382945324061069e-10</v>
       </c>
       <c r="H91" t="n">
-        <v>-2.952026038191059e-12</v>
+        <v>-5.00623293577948e-12</v>
       </c>
       <c r="I91" t="n">
-        <v>1.397962757901984e-10</v>
+        <v>1.883212446830619e-10</v>
       </c>
     </row>
     <row r="92">
@@ -4275,22 +4275,22 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>-1.881814291804605e-11</v>
+        <v>-3.073199599465757e-12</v>
       </c>
       <c r="E92" t="n">
-        <v>3.181099528158852e-11</v>
+        <v>6.623576102585932e-11</v>
       </c>
       <c r="F92" t="n">
-        <v>2.193320737905035e-11</v>
+        <v>2.138210364218099e-10</v>
       </c>
       <c r="G92" t="n">
         <v/>
       </c>
       <c r="H92" t="n">
-        <v>3.336601713102318e-11</v>
+        <v>8.654484373168335e-12</v>
       </c>
       <c r="I92" t="n">
-        <v>3.120426119369662e-11</v>
+        <v>2.623430707781532e-10</v>
       </c>
     </row>
     <row r="93">
@@ -4310,22 +4310,22 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>-1.958286953374157e-11</v>
+        <v>-3.797380014952477e-12</v>
       </c>
       <c r="E93" t="n">
-        <v>-2.25308232597038e-11</v>
+        <v>5.536211852747019e-11</v>
       </c>
       <c r="F93" t="n">
-        <v>1.137753302120475e-10</v>
+        <v>2.242588086229916e-10</v>
       </c>
       <c r="G93" t="n">
         <v/>
       </c>
       <c r="H93" t="n">
-        <v>2.757586113131176e-11</v>
+        <v>7.158217798231398e-12</v>
       </c>
       <c r="I93" t="n">
-        <v>2.274200745044068e-11</v>
+        <v>2.680937818221881e-10</v>
       </c>
     </row>
     <row r="94">
@@ -4345,22 +4345,22 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>-2.048069454665419e-12</v>
+        <v>-3.445335482130919e-12</v>
       </c>
       <c r="E94" t="n">
-        <v>2.861141125044638e-11</v>
+        <v>-2.156805906745407e-12</v>
       </c>
       <c r="F94" t="n">
-        <v>2.598869753626719e-11</v>
+        <v>-6.363249921000177e-13</v>
       </c>
       <c r="G94" t="n">
         <v/>
       </c>
       <c r="H94" t="n">
-        <v>2.520848039947655e-11</v>
+        <v>6.587882847450644e-12</v>
       </c>
       <c r="I94" t="n">
-        <v>2.49442215123344e-11</v>
+        <v>-3.608664882131516e-13</v>
       </c>
     </row>
     <row r="95">
@@ -4380,22 +4380,22 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>-1.517186699199822e-11</v>
+        <v>-4.722253520799799e-12</v>
       </c>
       <c r="E95" t="n">
-        <v>-1.115243049453674e-11</v>
+        <v>1.694467953044648e-11</v>
       </c>
       <c r="F95" t="n">
-        <v>3.077365648576753e-11</v>
+        <v>8.651050771195837e-11</v>
       </c>
       <c r="G95" t="n">
         <v/>
       </c>
       <c r="H95" t="n">
-        <v>1.12945395115016e-10</v>
+        <v>2.938640219294784e-11</v>
       </c>
       <c r="I95" t="n">
-        <v>3.611074864345543e-11</v>
+        <v>1.35482053310248e-10</v>
       </c>
     </row>
     <row r="96">
@@ -4415,22 +4415,22 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>-3.027377935616151e-11</v>
+        <v>-1.091153111600976e-11</v>
       </c>
       <c r="E96" t="n">
-        <v>-2.157957247491214e-11</v>
+        <v>3.547853775410561e-11</v>
       </c>
       <c r="F96" t="n">
-        <v>-1.734293825849159e-11</v>
+        <v>1.653448558840059e-10</v>
       </c>
       <c r="G96" t="n">
         <v/>
       </c>
       <c r="H96" t="n">
-        <v>-3.194780924731572e-11</v>
+        <v>-8.233362164741135e-12</v>
       </c>
       <c r="I96" t="n">
-        <v>1.986178483825869e-10</v>
+        <v>3.833494163770937e-10</v>
       </c>
     </row>
     <row r="97">
@@ -4450,22 +4450,22 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>4.025707404005536e-11</v>
+        <v>2.308560527717044e-11</v>
       </c>
       <c r="E97" t="n">
-        <v>-4.217025414928931e-11</v>
+        <v>3.227343431901134e-11</v>
       </c>
       <c r="F97" t="n">
-        <v>1.172469029253206e-11</v>
+        <v>1.440249298640483e-10</v>
       </c>
       <c r="G97" t="n">
         <v/>
       </c>
       <c r="H97" t="n">
-        <v>2.410326196253172e-11</v>
+        <v>6.263753168104973e-12</v>
       </c>
       <c r="I97" t="n">
-        <v>1.603464414139981e-11</v>
+        <v>2.301208654002881e-10</v>
       </c>
     </row>
     <row r="98">
@@ -4485,22 +4485,22 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>-1.563341439577671e-11</v>
+        <v>1.959836271376108e-11</v>
       </c>
       <c r="E98" t="n">
-        <v>-4.724236935427103e-11</v>
+        <v>2.698275901636271e-10</v>
       </c>
       <c r="F98" t="n">
-        <v>9.731679579496627e-11</v>
+        <v>5.56186657866659e-09</v>
       </c>
       <c r="G98" t="n">
         <v/>
       </c>
       <c r="H98" t="n">
-        <v>6.677244165631893e-11</v>
+        <v>1.730859389404578e-11</v>
       </c>
       <c r="I98" t="n">
-        <v>2.605490819575684e-11</v>
+        <v>2.055011400512402e-09</v>
       </c>
     </row>
     <row r="99">
@@ -4520,22 +4520,22 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>-6.560574015489415e-12</v>
+        <v>1.915370855570789e-12</v>
       </c>
       <c r="E99" t="n">
-        <v>-3.563333489314577e-11</v>
+        <v>1.607525775563123e-12</v>
       </c>
       <c r="F99" t="n">
-        <v>-2.831102916094371e-12</v>
+        <v>1.250697710725332e-12</v>
       </c>
       <c r="G99" t="n">
         <v/>
       </c>
       <c r="H99" t="n">
-        <v>-1.741947587369938e-12</v>
+        <v>-4.205588067026997e-13</v>
       </c>
       <c r="I99" t="n">
-        <v>-3.746467927979492e-12</v>
+        <v>9.49928077129064e-13</v>
       </c>
     </row>
     <row r="100">
@@ -4555,22 +4555,22 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>2.12603472783903e-11</v>
+        <v>3.849778806541902e-12</v>
       </c>
       <c r="E100" t="n">
-        <v>-2.781288958699774e-11</v>
+        <v>3.563408103262252e-11</v>
       </c>
       <c r="F100" t="n">
-        <v>3.985550620540912e-11</v>
+        <v>1.551792139218063e-10</v>
       </c>
       <c r="G100" t="n">
         <v/>
       </c>
       <c r="H100" t="n">
-        <v>8.792661356340692e-11</v>
+        <v>2.289353140192013e-11</v>
       </c>
       <c r="I100" t="n">
-        <v>3.527708635426218e-11</v>
+        <v>2.46139501214949e-10</v>
       </c>
     </row>
     <row r="101">
@@ -4590,22 +4590,22 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>6.520991189964243e-12</v>
+        <v>-9.501999315393915e-12</v>
       </c>
       <c r="E101" t="n">
-        <v>-2.1145800064689e-11</v>
+        <v>7.3673966652653e-11</v>
       </c>
       <c r="F101" t="n">
-        <v>-1.278941936837381e-11</v>
+        <v>4.565187622313816e-10</v>
       </c>
       <c r="G101" t="n">
         <v/>
       </c>
       <c r="H101" t="n">
-        <v>-4.041174216905964e-11</v>
+        <v>-1.042340145796654e-11</v>
       </c>
       <c r="I101" t="n">
-        <v>1.454514566430028e-10</v>
+        <v>4.590615968672479e-09</v>
       </c>
     </row>
     <row r="102">
@@ -4625,22 +4625,22 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>4.837614063877744e-11</v>
+        <v>2.092558991344725e-11</v>
       </c>
       <c r="E102" t="n">
-        <v>-1.908266670019756e-11</v>
+        <v>3.775450660034247e-11</v>
       </c>
       <c r="F102" t="n">
-        <v>-1.69623345310272e-11</v>
+        <v>1.415506851931195e-10</v>
       </c>
       <c r="G102" t="n">
         <v/>
       </c>
       <c r="H102" t="n">
-        <v>1.820090693101538e-11</v>
+        <v>4.73574672721983e-12</v>
       </c>
       <c r="I102" t="n">
-        <v>1.856781388076153e-11</v>
+        <v>2.261332354847626e-10</v>
       </c>
     </row>
     <row r="103">
@@ -4660,22 +4660,22 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>-7.668822864758332e-12</v>
+        <v>2.059703866143622e-11</v>
       </c>
       <c r="E103" t="n">
-        <v>1.845243515891687e-11</v>
+        <v>1.200294151168351e-09</v>
       </c>
       <c r="F103" t="n">
-        <v>-1.214829640285829e-11</v>
+        <v>1.402183783951876e-09</v>
       </c>
       <c r="G103" t="n">
         <v/>
       </c>
       <c r="H103" t="n">
-        <v>6.475739984214816e-11</v>
+        <v>1.678111029705459e-11</v>
       </c>
       <c r="I103" t="n">
-        <v>4.303241421226112e-11</v>
+        <v>1.257517798985538e-09</v>
       </c>
     </row>
     <row r="104">
@@ -4695,22 +4695,22 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>2.559744570192717e-11</v>
+        <v>3.013295199224526e-12</v>
       </c>
       <c r="E104" t="n">
-        <v>4.438760474713425e-11</v>
+        <v>2.876178914388342e-12</v>
       </c>
       <c r="F104" t="n">
-        <v>-1.592025010741757e-11</v>
+        <v>1.037516691904334e-12</v>
       </c>
       <c r="G104" t="n">
         <v/>
       </c>
       <c r="H104" t="n">
-        <v>1.089577676993926e-12</v>
+        <v>3.128550190514759e-13</v>
       </c>
       <c r="I104" t="n">
-        <v>1.071053128064137e-11</v>
+        <v>8.703591567271764e-13</v>
       </c>
     </row>
     <row r="105">
@@ -4730,22 +4730,22 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>7.715515051412687e-12</v>
+        <v>6.046289245559822e-12</v>
       </c>
       <c r="E105" t="n">
-        <v>-3.563792372204337e-12</v>
+        <v>4.25307463020261e-11</v>
       </c>
       <c r="F105" t="n">
-        <v>-7.789128861175951e-12</v>
+        <v>1.519759292264591e-10</v>
       </c>
       <c r="G105" t="n">
         <v/>
       </c>
       <c r="H105" t="n">
-        <v>1.084295469633233e-10</v>
+        <v>2.822833920802895e-11</v>
       </c>
       <c r="I105" t="n">
-        <v>3.89836866078802e-11</v>
+        <v>2.454568249758778e-10</v>
       </c>
     </row>
     <row r="106">
@@ -4765,22 +4765,22 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>-1.394825653108085e-11</v>
+        <v>-8.920179566191439e-12</v>
       </c>
       <c r="E106" t="n">
-        <v>-7.621201017919233e-12</v>
+        <v>1.082863112700618e-10</v>
       </c>
       <c r="F106" t="n">
-        <v>-3.460426590912463e-11</v>
+        <v>5.273009363733855e-10</v>
       </c>
       <c r="G106" t="n">
         <v/>
       </c>
       <c r="H106" t="n">
-        <v>-3.946403462191095e-11</v>
+        <v>-1.01776703204241e-11</v>
       </c>
       <c r="I106" t="n">
-        <v>1.242510070051676e-10</v>
+        <v>0.0004448385647781896</v>
       </c>
     </row>
     <row r="107">
@@ -4800,22 +4800,22 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>-2.631517483850029e-11</v>
+        <v>4.259198893547682e-10</v>
       </c>
       <c r="E107" t="n">
-        <v>1.288112389759367e-10</v>
+        <v>5.022211891265542e-11</v>
       </c>
       <c r="F107" t="n">
-        <v>1.811578432063732e-10</v>
+        <v>1.692784560586809e-10</v>
       </c>
       <c r="G107" t="n">
         <v/>
       </c>
       <c r="H107" t="n">
-        <v>1.471855728337537e-10</v>
+        <v>3.816535017016115e-11</v>
       </c>
       <c r="I107" t="n">
-        <v>2.983780651601949e-10</v>
+        <v>3.277000145922685e-10</v>
       </c>
     </row>
     <row r="108">
@@ -4835,22 +4835,22 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>4.051517359314754e-11</v>
+        <v>2.515676568686206e-11</v>
       </c>
       <c r="E108" t="n">
-        <v>1.009043085219943e-09</v>
+        <v>0.1497293201907243</v>
       </c>
       <c r="F108" t="n">
-        <v>8.969681996268351e-11</v>
+        <v>3.383130836045312e-09</v>
       </c>
       <c r="G108" t="n">
         <v/>
       </c>
       <c r="H108" t="n">
-        <v>6.81963847848913e-11</v>
+        <v>1.76941732248074e-11</v>
       </c>
       <c r="I108" t="n">
-        <v>1.419149946915289e-10</v>
+        <v>5.098625064963582e-09</v>
       </c>
     </row>
     <row r="109">
@@ -4870,22 +4870,22 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1.122683483720751e-10</v>
+        <v>2.82504222033625e-11</v>
       </c>
       <c r="E109" t="n">
-        <v>1.57931737032046e-10</v>
+        <v>8.665931944841839e-10</v>
       </c>
       <c r="F109" t="n">
-        <v>-5.13381215834523e-11</v>
+        <v>0.1625908450583093</v>
       </c>
       <c r="G109" t="n">
         <v/>
       </c>
       <c r="H109" t="n">
-        <v>8.046090805688557e-11</v>
+        <v>2.086663401229553e-11</v>
       </c>
       <c r="I109" t="n">
-        <v>1.99752939197699e-10</v>
+        <v>0.0004448374628852944</v>
       </c>
     </row>
     <row r="110">
@@ -4905,22 +4905,22 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>5.958021157436902e-11</v>
+        <v>2.792911735825091e-11</v>
       </c>
       <c r="E110" t="n">
-        <v>8.422130830705205e-11</v>
+        <v>5.248516029006329e-11</v>
       </c>
       <c r="F110" t="n">
-        <v>1.527503698800835e-10</v>
+        <v>1.742826619744803e-10</v>
       </c>
       <c r="G110" t="n">
         <v/>
       </c>
       <c r="H110" t="n">
-        <v>7.19435715213408e-10</v>
+        <v>1.878615375974894e-10</v>
       </c>
       <c r="I110" t="n">
-        <v>2.586044417662403e-10</v>
+        <v>3.471205138066861e-10</v>
       </c>
     </row>
     <row r="111">
@@ -4940,22 +4940,22 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1.629610819564825e-11</v>
+        <v>3.007481853151502e-12</v>
       </c>
       <c r="E111" t="n">
-        <v>4.987223403225309e-11</v>
+        <v>2.064473748262027e-10</v>
       </c>
       <c r="F111" t="n">
-        <v>2.942165011540489e-11</v>
+        <v>9.635988389273441e-10</v>
       </c>
       <c r="G111" t="n">
         <v/>
       </c>
       <c r="H111" t="n">
-        <v>-1.565754965982796e-12</v>
+        <v>-3.686017312812156e-13</v>
       </c>
       <c r="I111" t="n">
-        <v>7.217088127701322e-11</v>
+        <v>0.0008912225100016449</v>
       </c>
     </row>
     <row r="112">
@@ -4975,22 +4975,22 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>4.991631250489599e-11</v>
+        <v>1.78251692684311e-11</v>
       </c>
       <c r="E112" t="n">
-        <v>-2.551040468429436e-11</v>
+        <v>1.69245916579288e-11</v>
       </c>
       <c r="F112" t="n">
-        <v>1.898959789124906e-11</v>
+        <v>8.626522534932763e-11</v>
       </c>
       <c r="G112" t="n">
         <v/>
       </c>
       <c r="H112" t="n">
-        <v>8.72309042892107e-12</v>
+        <v>2.39562183133773e-12</v>
       </c>
       <c r="I112" t="n">
-        <v>3.051719805164604e-11</v>
+        <v>1.365478573727958e-10</v>
       </c>
     </row>
     <row r="113">
@@ -5010,22 +5010,22 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>2.302694672664803e-11</v>
+        <v>5.205383957864947e-12</v>
       </c>
       <c r="E113" t="n">
-        <v>9.636922199379666e-11</v>
+        <v>7.040788427288382e-11</v>
       </c>
       <c r="F113" t="n">
-        <v>4.312764659927173e-11</v>
+        <v>2.23360709216099e-10</v>
       </c>
       <c r="G113" t="n">
         <v/>
       </c>
       <c r="H113" t="n">
-        <v>8.575274392931154e-12</v>
+        <v>2.357783862704848e-12</v>
       </c>
       <c r="I113" t="n">
-        <v>5.201705443649749e-11</v>
+        <v>2.752803802909962e-10</v>
       </c>
     </row>
     <row r="114">
@@ -5045,22 +5045,22 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>-2.688758983711221e-13</v>
+        <v>6.527660550020569e-12</v>
       </c>
       <c r="E114" t="n">
-        <v>-2.466660912970912e-11</v>
+        <v>5.939519435761922e-11</v>
       </c>
       <c r="F114" t="n">
-        <v>1.448526628151321e-10</v>
+        <v>2.359089786935768e-10</v>
       </c>
       <c r="G114" t="n">
         <v/>
       </c>
       <c r="H114" t="n">
-        <v>1.520071350811024e-11</v>
+        <v>4.088425800681357e-12</v>
       </c>
       <c r="I114" t="n">
-        <v>3.787371160664836e-11</v>
+        <v>2.870039137393362e-10</v>
       </c>
     </row>
     <row r="115">
@@ -5080,22 +5080,22 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1.147423567508647e-12</v>
+        <v>3.662144611137253e-12</v>
       </c>
       <c r="E115" t="n">
-        <v>-1.009702213535837e-11</v>
+        <v>-1.484471905360367e-12</v>
       </c>
       <c r="F115" t="n">
-        <v>1.050883664570471e-11</v>
+        <v>-3.785290737547251e-13</v>
       </c>
       <c r="G115" t="n">
         <v/>
       </c>
       <c r="H115" t="n">
-        <v>1.614065317533363e-12</v>
+        <v>4.342813167949879e-13</v>
       </c>
       <c r="I115" t="n">
-        <v>1.686829620017237e-11</v>
+        <v>-1.348125815494013e-13</v>
       </c>
     </row>
     <row r="116">
@@ -5115,22 +5115,22 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>-2.033273012250759e-11</v>
+        <v>-8.993294360005683e-12</v>
       </c>
       <c r="E116" t="n">
-        <v>-2.574251811119555e-11</v>
+        <v>3.524279124259891e-11</v>
       </c>
       <c r="F116" t="n">
-        <v>-1.912039142584744e-11</v>
+        <v>1.653611998179278e-10</v>
       </c>
       <c r="G116" t="n">
         <v/>
       </c>
       <c r="H116" t="n">
-        <v>-3.952477292929637e-11</v>
+        <v>-1.016521660877445e-11</v>
       </c>
       <c r="I116" t="n">
-        <v>1.820430143252641e-10</v>
+        <v>4.000867567829339e-10</v>
       </c>
     </row>
     <row r="117">
@@ -5150,22 +5150,22 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>4.215658502106088e-12</v>
+        <v>-3.761944983296092e-12</v>
       </c>
       <c r="E117" t="n">
-        <v>-3.688833314023185e-11</v>
+        <v>3.468963944115207e-11</v>
       </c>
       <c r="F117" t="n">
-        <v>-1.978184350470406e-11</v>
+        <v>1.481795871832674e-10</v>
       </c>
       <c r="G117" t="n">
         <v/>
       </c>
       <c r="H117" t="n">
-        <v>-3.106488762670913e-11</v>
+        <v>-8.006846849766944e-12</v>
       </c>
       <c r="I117" t="n">
-        <v>-4.987863405143686e-11</v>
+        <v>1.284054829494364e-10</v>
       </c>
     </row>
     <row r="118">
@@ -5185,22 +5185,22 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>8.789269559920265e-12</v>
+        <v>-8.938870368976264e-12</v>
       </c>
       <c r="E118" t="n">
-        <v>1.001991494973503e-10</v>
+        <v>2.486561944575467e-10</v>
       </c>
       <c r="F118" t="n">
-        <v>-9.332907529169409e-12</v>
+        <v>1.09634381675966e-09</v>
       </c>
       <c r="G118" t="n">
         <v/>
       </c>
       <c r="H118" t="n">
-        <v>-3.824644872516505e-11</v>
+        <v>-9.865633558333512e-12</v>
       </c>
       <c r="I118" t="n">
-        <v>-4.909709712887882e-11</v>
+        <v>2.290713488590353e-10</v>
       </c>
     </row>
     <row r="119">
@@ -5220,22 +5220,22 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>-1.671116654767803e-11</v>
+        <v>-8.917031998841752e-12</v>
       </c>
       <c r="E119" t="n">
-        <v>-3.091955547207932e-11</v>
+        <v>1.405637967226644e-10</v>
       </c>
       <c r="F119" t="n">
-        <v>9.657675959136643e-12</v>
+        <v>8.897832586895876e-10</v>
       </c>
       <c r="G119" t="n">
         <v/>
       </c>
       <c r="H119" t="n">
-        <v>-3.699652756105482e-11</v>
+        <v>-9.541490574324224e-12</v>
       </c>
       <c r="I119" t="n">
-        <v>-5.087811346271206e-11</v>
+        <v>2.217622156463132e-10</v>
       </c>
     </row>
     <row r="120">
@@ -5255,22 +5255,22 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>-1.813629800423202e-11</v>
+        <v>-4.894059448952638e-12</v>
       </c>
       <c r="E120" t="n">
-        <v>-2.726859059866909e-11</v>
+        <v>2.328028652463332e-12</v>
       </c>
       <c r="F120" t="n">
-        <v>-1.774623858712121e-11</v>
+        <v>1.248659433176264e-12</v>
       </c>
       <c r="G120" t="n">
         <v/>
       </c>
       <c r="H120" t="n">
-        <v>-2.422162090671133e-11</v>
+        <v>-6.253569908348541e-12</v>
       </c>
       <c r="I120" t="n">
-        <v>-4.877644627582113e-11</v>
+        <v>-9.456281379697788e-13</v>
       </c>
     </row>
     <row r="121">
@@ -5290,22 +5290,22 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>-1.989513013312746e-11</v>
+        <v>-8.875867862090384e-12</v>
       </c>
       <c r="E121" t="n">
-        <v>-3.133952791983093e-11</v>
+        <v>3.289132247126601e-11</v>
       </c>
       <c r="F121" t="n">
-        <v>-1.723205118494358e-11</v>
+        <v>1.425692711683103e-10</v>
       </c>
       <c r="G121" t="n">
         <v/>
       </c>
       <c r="H121" t="n">
-        <v>-2.238462911392261e-11</v>
+        <v>-5.754752958716538e-12</v>
       </c>
       <c r="I121" t="n">
-        <v>-4.965668875180225e-11</v>
+        <v>1.245852022966947e-10</v>
       </c>
     </row>
     <row r="122">
@@ -5325,22 +5325,22 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>-1.421100942454967e-11</v>
+        <v>-2.528784955067676e-12</v>
       </c>
       <c r="E122" t="n">
-        <v>3.734276113342294e-11</v>
+        <v>1.892619844304246e-11</v>
       </c>
       <c r="F122" t="n">
-        <v>5.04350508909099e-12</v>
+        <v>6.024743157847692e-12</v>
       </c>
       <c r="G122" t="n">
-        <v>2.928082961064286e-11</v>
+        <v>7.618028190240517e-12</v>
       </c>
       <c r="H122" t="n">
         <v/>
       </c>
       <c r="I122" t="n">
-        <v>2.840842975364916e-10</v>
+        <v>1.36780331610701e-09</v>
       </c>
     </row>
     <row r="123">
@@ -5360,22 +5360,22 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>-1.340294817424956e-11</v>
+        <v>-3.393102735723507e-12</v>
       </c>
       <c r="E123" t="n">
-        <v>6.112370086994416e-12</v>
+        <v>4.894945645566456e-12</v>
       </c>
       <c r="F123" t="n">
-        <v>5.498303233179014e-11</v>
+        <v>1.366515040334089e-11</v>
       </c>
       <c r="G123" t="n">
-        <v>2.294364632809383e-11</v>
+        <v>5.976509993930992e-12</v>
       </c>
       <c r="H123" t="n">
         <v/>
       </c>
       <c r="I123" t="n">
-        <v>2.676991070427755e-10</v>
+        <v>1.384170765856745e-09</v>
       </c>
     </row>
     <row r="124">
@@ -5395,22 +5395,22 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>-6.509737255122353e-12</v>
+        <v>-1.840331528204863e-12</v>
       </c>
       <c r="E124" t="n">
-        <v>1.325835642877809e-11</v>
+        <v>4.863388911188516e-12</v>
       </c>
       <c r="F124" t="n">
-        <v>1.828446307856268e-11</v>
+        <v>4.954427473227728e-12</v>
       </c>
       <c r="G124" t="n">
-        <v>1.392487115871123e-10</v>
+        <v>3.623656402099831e-11</v>
       </c>
       <c r="H124" t="n">
         <v/>
       </c>
       <c r="I124" t="n">
-        <v>3.9089367273524e-10</v>
+        <v>1.412910831283051e-09</v>
       </c>
     </row>
     <row r="125">
@@ -5430,22 +5430,22 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>-1.512461254109508e-11</v>
+        <v>-4.453420692614903e-12</v>
       </c>
       <c r="E125" t="n">
-        <v>8.102075374231535e-12</v>
+        <v>9.354849898709832e-13</v>
       </c>
       <c r="F125" t="n">
-        <v>8.037338364097724e-12</v>
+        <v>1.556720826272429e-12</v>
       </c>
       <c r="G125" t="n">
-        <v>1.507339783011337e-11</v>
+        <v>3.970077060522078e-12</v>
       </c>
       <c r="H125" t="n">
         <v/>
       </c>
       <c r="I125" t="n">
-        <v>6.676758175537582e-12</v>
+        <v>-9.248125369324267e-14</v>
       </c>
     </row>
     <row r="126">
@@ -5465,22 +5465,22 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>-3.29891092203015e-11</v>
+        <v>-1.030771350293257e-11</v>
       </c>
       <c r="E126" t="n">
-        <v>-1.40141675428574e-11</v>
+        <v>-7.92702315266003e-12</v>
       </c>
       <c r="F126" t="n">
-        <v>-1.852116329199579e-11</v>
+        <v>-8.25749036729295e-12</v>
       </c>
       <c r="G126" t="n">
-        <v>-2.784615025972617e-11</v>
+        <v>-7.164351826039251e-12</v>
       </c>
       <c r="H126" t="n">
         <v/>
       </c>
       <c r="I126" t="n">
-        <v>5.543608021259822e-09</v>
+        <v>1.559888632066088e-09</v>
       </c>
     </row>
     <row r="127">
@@ -5500,22 +5500,22 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1.352355620911471e-10</v>
+        <v>3.645181096977985e-11</v>
       </c>
       <c r="E127" t="n">
-        <v>-1.263704379848964e-11</v>
+        <v>-2.14832914245847e-12</v>
       </c>
       <c r="F127" t="n">
-        <v>1.283412452961273e-11</v>
+        <v>3.027973600933198e-12</v>
       </c>
       <c r="G127" t="n">
-        <v>3.867449897326755e-11</v>
+        <v>1.005541466655088e-11</v>
       </c>
       <c r="H127" t="n">
         <v/>
       </c>
       <c r="I127" t="n">
-        <v>3.34299760749753e-10</v>
+        <v>1.167632931371541e-09</v>
       </c>
     </row>
     <row r="128">
@@ -5535,22 +5535,22 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>2.203538323399357e-11</v>
+        <v>1.956719559746263e-11</v>
       </c>
       <c r="E128" t="n">
-        <v>-1.79718695157e-11</v>
+        <v>7.925104453300937e-12</v>
       </c>
       <c r="F128" t="n">
-        <v>5.307390030070084e-11</v>
+        <v>4.871039560960151e-11</v>
       </c>
       <c r="G128" t="n">
-        <v>7.131723604949129e-11</v>
+        <v>1.851742541133651e-11</v>
       </c>
       <c r="H128" t="n">
         <v/>
       </c>
       <c r="I128" t="n">
-        <v>3.423602640622403e-10</v>
+        <v>1.731013389548988e-08</v>
       </c>
     </row>
     <row r="129">
@@ -5570,22 +5570,22 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>5.518692178415103e-12</v>
+        <v>3.858740331346219e-12</v>
       </c>
       <c r="E129" t="n">
-        <v>-2.209123111248218e-11</v>
+        <v>-2.569105304871934e-12</v>
       </c>
       <c r="F129" t="n">
-        <v>-2.217099427504403e-12</v>
+        <v>1.813938209163697e-12</v>
       </c>
       <c r="G129" t="n">
-        <v>6.664440969007537e-11</v>
+        <v>1.737967479279485e-11</v>
       </c>
       <c r="H129" t="n">
         <v/>
       </c>
       <c r="I129" t="n">
-        <v>2.92285812116658e-10</v>
+        <v>9.357044548265742e-09</v>
       </c>
     </row>
     <row r="130">
@@ -5605,22 +5605,22 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>2.525219917142191e-11</v>
+        <v>3.923475391288571e-12</v>
       </c>
       <c r="E130" t="n">
-        <v>4.459403273525993e-13</v>
+        <v>-2.240576261469496e-12</v>
       </c>
       <c r="F130" t="n">
-        <v>2.886085724826667e-11</v>
+        <v>3.118603922551808e-12</v>
       </c>
       <c r="G130" t="n">
-        <v>1.484004046437236e-11</v>
+        <v>3.909604231522977e-12</v>
       </c>
       <c r="H130" t="n">
         <v/>
       </c>
       <c r="I130" t="n">
-        <v>9.103457820511525e-12</v>
+        <v>2.187226155480906e-13</v>
       </c>
     </row>
     <row r="131">
@@ -5640,22 +5640,22 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>-1.261283046184392e-11</v>
+        <v>-8.896182150978985e-12</v>
       </c>
       <c r="E131" t="n">
-        <v>-1.019538516685605e-11</v>
+        <v>-1.052694829956718e-11</v>
       </c>
       <c r="F131" t="n">
-        <v>-2.005827370687884e-12</v>
+        <v>-9.426819413310507e-12</v>
       </c>
       <c r="G131" t="n">
-        <v>-3.555566847898666e-11</v>
+        <v>-9.160769618857657e-12</v>
       </c>
       <c r="H131" t="n">
         <v/>
       </c>
       <c r="I131" t="n">
-        <v>5.04811178111681e-09</v>
+        <v>1.109088558702066e-08</v>
       </c>
     </row>
     <row r="132">
@@ -5675,22 +5675,22 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1.175374496882377e-10</v>
+        <v>3.355088899363736e-11</v>
       </c>
       <c r="E132" t="n">
-        <v>7.165743917626384e-12</v>
+        <v>2.582430608473189e-12</v>
       </c>
       <c r="F132" t="n">
-        <v>-1.355457157861463e-11</v>
+        <v>-2.322815847136363e-12</v>
       </c>
       <c r="G132" t="n">
-        <v>3.281743862821347e-11</v>
+        <v>8.539449045526711e-12</v>
       </c>
       <c r="H132" t="n">
         <v/>
       </c>
       <c r="I132" t="n">
-        <v>3.311709936615954e-10</v>
+        <v>1.171787695931715e-09</v>
       </c>
     </row>
     <row r="133">
@@ -5710,22 +5710,22 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>2.028286041007692e-11</v>
+        <v>2.190584897176501e-11</v>
       </c>
       <c r="E133" t="n">
-        <v>3.2920208047759e-11</v>
+        <v>6.543723341657578e-11</v>
       </c>
       <c r="F133" t="n">
-        <v>-1.572121907952859e-11</v>
+        <v>8.422824904796784e-12</v>
       </c>
       <c r="G133" t="n">
-        <v>7.408649334738182e-11</v>
+        <v>1.923605994468224e-11</v>
       </c>
       <c r="H133" t="n">
         <v/>
       </c>
       <c r="I133" t="n">
-        <v>3.762580812278516e-10</v>
+        <v>9.978611622640385e-09</v>
       </c>
     </row>
     <row r="134">
@@ -5745,22 +5745,22 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>2.034779998552208e-11</v>
+        <v>5.408463822990886e-12</v>
       </c>
       <c r="E134" t="n">
-        <v>1.280511286171801e-11</v>
+        <v>3.6441157071353e-12</v>
       </c>
       <c r="F134" t="n">
-        <v>-1.049266121420483e-11</v>
+        <v>-1.921411811118078e-12</v>
       </c>
       <c r="G134" t="n">
-        <v>7.845866847742842e-11</v>
+        <v>2.044029048985035e-11</v>
       </c>
       <c r="H134" t="n">
         <v/>
       </c>
       <c r="I134" t="n">
-        <v>3.588569024500118e-10</v>
+        <v>8.129491440607814e-09</v>
       </c>
     </row>
     <row r="135">
@@ -5780,22 +5780,22 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1.591174142712422e-11</v>
+        <v>6.253274101189226e-12</v>
       </c>
       <c r="E135" t="n">
-        <v>1.364728532208344e-11</v>
+        <v>5.004268068568035e-12</v>
       </c>
       <c r="F135" t="n">
-        <v>-1.134994822140387e-11</v>
+        <v>-5.132992240908117e-13</v>
       </c>
       <c r="G135" t="n">
-        <v>2.213732284408555e-11</v>
+        <v>5.816941935736494e-12</v>
       </c>
       <c r="H135" t="n">
         <v/>
       </c>
       <c r="I135" t="n">
-        <v>9.415982436548118e-12</v>
+        <v>2.231052030115603e-13</v>
       </c>
     </row>
     <row r="136">
@@ -5815,22 +5815,22 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>-2.088244882551194e-11</v>
+        <v>-8.328774254243975e-12</v>
       </c>
       <c r="E136" t="n">
-        <v>-9.509157231121172e-12</v>
+        <v>-8.345742978560127e-12</v>
       </c>
       <c r="F136" t="n">
-        <v>-2.982254721608606e-11</v>
+        <v>-1.039983635218799e-11</v>
       </c>
       <c r="G136" t="n">
-        <v>-3.418850968568723e-11</v>
+        <v>-8.805307137728585e-12</v>
       </c>
       <c r="H136" t="n">
         <v/>
       </c>
       <c r="I136" t="n">
-        <v>2.966913411485924e-09</v>
+        <v>3.239573562705025e-08</v>
       </c>
     </row>
     <row r="137">
@@ -5850,22 +5850,22 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1.27883136053586e-10</v>
+        <v>3.973519823742701e-11</v>
       </c>
       <c r="E137" t="n">
-        <v>1.218432689186564e-11</v>
+        <v>6.53300949304785e-12</v>
       </c>
       <c r="F137" t="n">
-        <v>1.279960070302192e-11</v>
+        <v>5.893895672552951e-12</v>
       </c>
       <c r="G137" t="n">
-        <v>7.043480448026364e-13</v>
+        <v>3.237595610295255e-13</v>
       </c>
       <c r="H137" t="n">
         <v/>
       </c>
       <c r="I137" t="n">
-        <v>2.849439510873597e-10</v>
+        <v>1.176862463408462e-09</v>
       </c>
     </row>
     <row r="138">
@@ -5885,22 +5885,22 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>-4.450326489581734e-12</v>
+        <v>3.199455735726471e-12</v>
       </c>
       <c r="E138" t="n">
-        <v>1.433438946529942e-11</v>
+        <v>1.980553568047862e-11</v>
       </c>
       <c r="F138" t="n">
-        <v>-9.657066745440941e-12</v>
+        <v>5.165579344891835e-12</v>
       </c>
       <c r="G138" t="n">
-        <v>-1.600125870762985e-11</v>
+        <v>-4.031231445135443e-12</v>
       </c>
       <c r="H138" t="n">
         <v/>
       </c>
       <c r="I138" t="n">
-        <v>1.966378057701089e-10</v>
+        <v>5.8022979198302e-09</v>
       </c>
     </row>
     <row r="139">
@@ -5920,22 +5920,22 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1.153479609094692e-11</v>
+        <v>3.792576135273928e-12</v>
       </c>
       <c r="E139" t="n">
-        <v>1.229369141560049e-11</v>
+        <v>7.936169451154773e-12</v>
       </c>
       <c r="F139" t="n">
-        <v>5.856024434115502e-11</v>
+        <v>1.658766225302346e-11</v>
       </c>
       <c r="G139" t="n">
-        <v>-1.419890498913878e-11</v>
+        <v>-3.563923239070261e-12</v>
       </c>
       <c r="H139" t="n">
         <v/>
       </c>
       <c r="I139" t="n">
-        <v>2.208512503673811e-10</v>
+        <v>6.876702666116299e-09</v>
       </c>
     </row>
     <row r="140">
@@ -5955,22 +5955,22 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>-2.262643246535848e-13</v>
+        <v>3.639882508593877e-12</v>
       </c>
       <c r="E140" t="n">
-        <v>-3.313412582032049e-12</v>
+        <v>5.07041277655576e-12</v>
       </c>
       <c r="F140" t="n">
-        <v>-3.628393386463173e-12</v>
+        <v>4.836976865251772e-12</v>
       </c>
       <c r="G140" t="n">
-        <v>-1.26332251832357e-11</v>
+        <v>-3.243010137799566e-12</v>
       </c>
       <c r="H140" t="n">
         <v/>
       </c>
       <c r="I140" t="n">
-        <v>2.743023536678235e-12</v>
+        <v>1.628432269818131e-13</v>
       </c>
     </row>
     <row r="141">
@@ -5990,22 +5990,22 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>-1.776630105423953e-11</v>
+        <v>-4.169166713716965e-12</v>
       </c>
       <c r="E141" t="n">
-        <v>-1.614122108638578e-11</v>
+        <v>-3.316572602128218e-12</v>
       </c>
       <c r="F141" t="n">
-        <v>-1.935276503002892e-11</v>
+        <v>-4.206949658813952e-12</v>
       </c>
       <c r="G141" t="n">
-        <v>-3.114981317213507e-11</v>
+        <v>-7.97507347383748e-12</v>
       </c>
       <c r="H141" t="n">
         <v/>
       </c>
       <c r="I141" t="n">
-        <v>1.484487803361589e-08</v>
+        <v>4.142034838412522e-08</v>
       </c>
     </row>
     <row r="142">
@@ -6025,22 +6025,22 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>-6.342752864079842e-11</v>
+        <v>2.049205773638716e-09</v>
       </c>
       <c r="E142" t="n">
-        <v>6.230321678024661e-11</v>
+        <v>2.239764744833389e-11</v>
       </c>
       <c r="F142" t="n">
-        <v>7.513640072192333e-11</v>
+        <v>1.948986482448e-11</v>
       </c>
       <c r="G142" t="n">
-        <v>1.366410228696927e-10</v>
+        <v>3.54764203691092e-11</v>
       </c>
       <c r="H142" t="n">
         <v/>
       </c>
       <c r="I142" t="n">
-        <v>5.515418601539209e-09</v>
+        <v>1.325166026520962e-09</v>
       </c>
     </row>
     <row r="143">
@@ -6060,22 +6060,22 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1.909954618484426e-10</v>
+        <v>4.150221078758429e-11</v>
       </c>
       <c r="E143" t="n">
-        <v>4.623591429929488e-10</v>
+        <v>2.52427976503725e-10</v>
       </c>
       <c r="F143" t="n">
-        <v>1.18284995244398e-10</v>
+        <v>3.629392166585222e-11</v>
       </c>
       <c r="G143" t="n">
-        <v>1.073288304176106e-10</v>
+        <v>2.787386033520057e-11</v>
       </c>
       <c r="H143" t="n">
         <v/>
       </c>
       <c r="I143" t="n">
-        <v>5.145909598358408e-09</v>
+        <v>1.953150906944228e-08</v>
       </c>
     </row>
     <row r="144">
@@ -6095,22 +6095,22 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1.55733635618867e-10</v>
+        <v>4.792417856180814e-11</v>
       </c>
       <c r="E144" t="n">
-        <v>7.067925497407832e-11</v>
+        <v>5.541899466023984e-11</v>
       </c>
       <c r="F144" t="n">
-        <v>-5.295330972898874e-12</v>
+        <v>1.492617698899137e-10</v>
       </c>
       <c r="G144" t="n">
-        <v>1.310825491773446e-10</v>
+        <v>3.404825957730214e-11</v>
       </c>
       <c r="H144" t="n">
         <v/>
       </c>
       <c r="I144" t="n">
-        <v>3.191348844818083e-09</v>
+        <v>2.407663431685211e-08</v>
       </c>
     </row>
     <row r="145">
@@ -6130,22 +6130,22 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1.146294998634321e-10</v>
+        <v>4.331294569466019e-11</v>
       </c>
       <c r="E145" t="n">
-        <v>3.6854239693443e-11</v>
+        <v>3.400114966011559e-11</v>
       </c>
       <c r="F145" t="n">
-        <v>5.263106598111013e-11</v>
+        <v>2.809066891396706e-11</v>
       </c>
       <c r="G145" t="n">
-        <v>7.365842470887464e-10</v>
+        <v>1.931971796043048e-10</v>
       </c>
       <c r="H145" t="n">
         <v/>
       </c>
       <c r="I145" t="n">
-        <v>1.447167398996584e-08</v>
+        <v>3.372933259148856e-08</v>
       </c>
     </row>
     <row r="146">
@@ -6165,22 +6165,22 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1.017933977531867e-11</v>
+        <v>-2.968767514647813e-12</v>
       </c>
       <c r="E146" t="n">
-        <v>1.248705418105166e-11</v>
+        <v>-3.152889817300491e-12</v>
       </c>
       <c r="F146" t="n">
-        <v>4.926286042749723e-12</v>
+        <v>-4.487967125759331e-12</v>
       </c>
       <c r="G146" t="n">
-        <v>-1.708213528410146e-11</v>
+        <v>-4.377999120448109e-12</v>
       </c>
       <c r="H146" t="n">
         <v/>
       </c>
       <c r="I146" t="n">
-        <v>1.284447150028766e-09</v>
+        <v>0.003112539382762653</v>
       </c>
     </row>
     <row r="147">
@@ -6200,22 +6200,22 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>8.644402421972942e-12</v>
+        <v>-2.816844986613905e-12</v>
       </c>
       <c r="E147" t="n">
-        <v>-1.821484830943995e-11</v>
+        <v>-7.671763570166647e-12</v>
       </c>
       <c r="F147" t="n">
-        <v>-1.938837880482984e-11</v>
+        <v>-8.145366757009606e-12</v>
       </c>
       <c r="G147" t="n">
-        <v>-3.013687341974267e-11</v>
+        <v>-7.758216202563968e-12</v>
       </c>
       <c r="H147" t="n">
         <v/>
       </c>
       <c r="I147" t="n">
-        <v>2.712854971201221e-11</v>
+        <v>8.832319468266446e-10</v>
       </c>
     </row>
     <row r="148">
@@ -6235,22 +6235,22 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>-1.718798013293492e-11</v>
+        <v>-9.173690401525728e-12</v>
       </c>
       <c r="E148" t="n">
-        <v>3.527674273137069e-11</v>
+        <v>-5.399165928681093e-12</v>
       </c>
       <c r="F148" t="n">
-        <v>-7.404259229578872e-12</v>
+        <v>-8.662977144309137e-12</v>
       </c>
       <c r="G148" t="n">
-        <v>-3.87743779697887e-11</v>
+        <v>-9.995367541640408e-12</v>
       </c>
       <c r="H148" t="n">
         <v/>
       </c>
       <c r="I148" t="n">
-        <v>2.327129297308309e-11</v>
+        <v>2.24569375674359e-09</v>
       </c>
     </row>
     <row r="149">
@@ -6270,22 +6270,22 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>-2.270346408461845e-11</v>
+        <v>-9.101145923740273e-12</v>
       </c>
       <c r="E149" t="n">
-        <v>-1.408425404277199e-11</v>
+        <v>-7.852909388371585e-12</v>
       </c>
       <c r="F149" t="n">
-        <v>3.420591414351651e-12</v>
+        <v>-6.553294153360506e-12</v>
       </c>
       <c r="G149" t="n">
-        <v>-3.783311295436673e-11</v>
+        <v>-9.750837465432806e-12</v>
       </c>
       <c r="H149" t="n">
         <v/>
       </c>
       <c r="I149" t="n">
-        <v>2.035590497102991e-11</v>
+        <v>2.028207847117987e-09</v>
       </c>
     </row>
     <row r="150">
@@ -6305,22 +6305,22 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>-1.701121449347642e-11</v>
+        <v>-4.541872415856052e-12</v>
       </c>
       <c r="E150" t="n">
-        <v>-2.146870376695808e-11</v>
+        <v>-3.910994174752488e-12</v>
       </c>
       <c r="F150" t="n">
-        <v>-1.948414853286769e-11</v>
+        <v>-4.66045830876433e-12</v>
       </c>
       <c r="G150" t="n">
-        <v>-1.781667080434825e-12</v>
+        <v>-3.990935988947174e-13</v>
       </c>
       <c r="H150" t="n">
         <v/>
       </c>
       <c r="I150" t="n">
-        <v>3.634368711009689e-11</v>
+        <v>2.647594865062287e-09</v>
       </c>
     </row>
     <row r="151">
@@ -6340,22 +6340,22 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>-2.581309349885745e-11</v>
+        <v>-9.113010472954675e-12</v>
       </c>
       <c r="E151" t="n">
-        <v>-1.888181345741659e-11</v>
+        <v>-8.483965097774004e-12</v>
       </c>
       <c r="F151" t="n">
-        <v>-2.191982171273474e-11</v>
+        <v>-8.836689371946403e-12</v>
       </c>
       <c r="G151" t="n">
-        <v>-3.729624545630688e-11</v>
+        <v>-9.627884641443628e-12</v>
       </c>
       <c r="H151" t="n">
         <v/>
       </c>
       <c r="I151" t="n">
-        <v>-2.793954018215902e-11</v>
+        <v>-1.415429489720933e-13</v>
       </c>
     </row>
     <row r="152">
@@ -6375,19 +6375,19 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>-6.155943101099589e-11</v>
+        <v>-1.00300659052361e-11</v>
       </c>
       <c r="E152" t="n">
-        <v>-1.111224806247147e-12</v>
+        <v>1.117032902140805e-10</v>
       </c>
       <c r="F152" t="n">
-        <v>4.27334348195703e-10</v>
+        <v>4.560849967414262e-10</v>
       </c>
       <c r="G152" t="n">
-        <v>-8.145753873155739e-12</v>
+        <v>2.838375287022956e-10</v>
       </c>
       <c r="H152" t="n">
-        <v>3.156602582656001e-10</v>
+        <v>1.37079257362726e-09</v>
       </c>
       <c r="I152" t="n">
         <v/>
@@ -6410,19 +6410,19 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>-5.820617095792516e-11</v>
+        <v>-1.040045133299141e-11</v>
       </c>
       <c r="E153" t="n">
-        <v>-3.377828219566026e-11</v>
+        <v>6.873657090757619e-11</v>
       </c>
       <c r="F153" t="n">
-        <v>3.63370217944181e-09</v>
+        <v>6.976669784500898e-10</v>
       </c>
       <c r="G153" t="n">
-        <v>-7.846471142948533e-12</v>
+        <v>2.9024220805707e-10</v>
       </c>
       <c r="H153" t="n">
-        <v>3.159237232746998e-10</v>
+        <v>1.384468863840869e-09</v>
       </c>
       <c r="I153" t="n">
         <v/>
@@ -6445,19 +6445,19 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>-5.509575773499468e-11</v>
+        <v>-1.062010323770802e-11</v>
       </c>
       <c r="E154" t="n">
-        <v>-3.298941504976181e-11</v>
+        <v>5.358533539557554e-11</v>
       </c>
       <c r="F154" t="n">
-        <v>6.122228639041992e-10</v>
+        <v>3.486236302383773e-10</v>
       </c>
       <c r="G154" t="n">
-        <v>1.548873246947416e-10</v>
+        <v>4.109650069842021e-10</v>
       </c>
       <c r="H154" t="n">
-        <v>2.738163660589478e-10</v>
+        <v>1.317490363322678e-09</v>
       </c>
       <c r="I154" t="n">
         <v/>
@@ -6480,19 +6480,19 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>-5.760042443657512e-11</v>
+        <v>-1.210615530877825e-11</v>
       </c>
       <c r="E155" t="n">
-        <v>-2.815750389462789e-11</v>
+        <v>3.493732842215095e-11</v>
       </c>
       <c r="F155" t="n">
-        <v>5.919231840911879e-10</v>
+        <v>2.872057764196802e-10</v>
       </c>
       <c r="G155" t="n">
-        <v>1.590298928476343e-12</v>
+        <v>1.403521620025723e-10</v>
       </c>
       <c r="H155" t="n">
-        <v>5.867085670450465e-09</v>
+        <v>1.524705851935393e-09</v>
       </c>
       <c r="I155" t="n">
         <v/>
@@ -6515,19 +6515,19 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>-5.542036155846857e-11</v>
+        <v>-9.438279626267074e-12</v>
       </c>
       <c r="E156" t="n">
-        <v>3.897507439311149e-12</v>
+        <v>-4.390517606761561e-13</v>
       </c>
       <c r="F156" t="n">
-        <v>5.924309535712746e-13</v>
+        <v>8.055858099093036e-13</v>
       </c>
       <c r="G156" t="n">
-        <v>1.199559848930739e-11</v>
+        <v>-5.980049793854515e-13</v>
       </c>
       <c r="H156" t="n">
-        <v>3.16374869723109e-12</v>
+        <v>-9.934824446236613e-14</v>
       </c>
       <c r="I156" t="n">
         <v/>
@@ -6550,19 +6550,19 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>3.575819427713261e-11</v>
+        <v>4.524232838943399e-12</v>
       </c>
       <c r="E157" t="n">
-        <v>-4.87241068134843e-11</v>
+        <v>3.332027305605963e-11</v>
       </c>
       <c r="F157" t="n">
-        <v>6.715023238616829e-10</v>
+        <v>2.988748777522946e-10</v>
       </c>
       <c r="G157" t="n">
-        <v>-3.971323359222885e-12</v>
+        <v>2.299661427643342e-10</v>
       </c>
       <c r="H157" t="n">
-        <v>2.732136492977648e-10</v>
+        <v>1.16912839519194e-09</v>
       </c>
       <c r="I157" t="n">
         <v/>
@@ -6585,19 +6585,19 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>-5.141035530471864e-11</v>
+        <v>7.1490993442053e-12</v>
       </c>
       <c r="E158" t="n">
-        <v>-4.5650077293219e-11</v>
+        <v>1.014264985179696e-10</v>
       </c>
       <c r="F158" t="n">
-        <v>1.079510175633173e-08</v>
+        <v>2.363151916429742e-09</v>
       </c>
       <c r="G158" t="n">
-        <v>8.818735227235644e-12</v>
+        <v>2.410146045391304e-09</v>
       </c>
       <c r="H158" t="n">
-        <v>3.536602907682843e-10</v>
+        <v>1.701825650140779e-08</v>
       </c>
       <c r="I158" t="n">
         <v/>
@@ -6620,19 +6620,19 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>-4.673556628056705e-11</v>
+        <v>-6.567423593793444e-12</v>
       </c>
       <c r="E159" t="n">
-        <v>-5.438125731817723e-11</v>
+        <v>4.809771633512386e-11</v>
       </c>
       <c r="F159" t="n">
-        <v>5.603140752168425e-10</v>
+        <v>3.483615595556946e-10</v>
       </c>
       <c r="G159" t="n">
-        <v>5.036297764440174e-11</v>
+        <v>0.0004115687273144448</v>
       </c>
       <c r="H159" t="n">
-        <v>1.86992041177466e-10</v>
+        <v>6.318997209808188e-09</v>
       </c>
       <c r="I159" t="n">
         <v/>
@@ -6655,19 +6655,19 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>-1.922973868574689e-11</v>
+        <v>-6.93704445324318e-12</v>
       </c>
       <c r="E160" t="n">
-        <v>-4.353565810288031e-11</v>
+        <v>3.700347936844583e-11</v>
       </c>
       <c r="F160" t="n">
-        <v>1.026961900267051e-09</v>
+        <v>3.310111595387523e-10</v>
       </c>
       <c r="G160" t="n">
-        <v>7.798836783873825e-12</v>
+        <v>2.495999427715805e-10</v>
       </c>
       <c r="H160" t="n">
-        <v>4.890227176012285e-09</v>
+        <v>2.144594916753769e-08</v>
       </c>
       <c r="I160" t="n">
         <v/>
@@ -6690,19 +6690,19 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1.79759952591898e-10</v>
+        <v>-4.908478957013548e-12</v>
       </c>
       <c r="E161" t="n">
-        <v>-3.336534668586975e-11</v>
+        <v>-1.570795769364943e-12</v>
       </c>
       <c r="F161" t="n">
-        <v>6.953082158571695e-12</v>
+        <v>5.779376544495585e-13</v>
       </c>
       <c r="G161" t="n">
-        <v>2.907962874770362e-12</v>
+        <v>5.489829897459066e-13</v>
       </c>
       <c r="H161" t="n">
-        <v>4.064088140976073e-13</v>
+        <v>2.060978238813977e-13</v>
       </c>
       <c r="I161" t="n">
         <v/>
@@ -6725,19 +6725,19 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>-4.643918465742987e-13</v>
+        <v>3.263712291451135e-12</v>
       </c>
       <c r="E162" t="n">
-        <v>-3.701244663114536e-11</v>
+        <v>4.452797136091411e-11</v>
       </c>
       <c r="F162" t="n">
-        <v>2.502397884195432e-10</v>
+        <v>2.299315217760117e-10</v>
       </c>
       <c r="G162" t="n">
-        <v>-9.264050446176258e-12</v>
+        <v>2.267465711652122e-10</v>
       </c>
       <c r="H162" t="n">
-        <v>2.542195146350062e-10</v>
+        <v>1.174527424475149e-09</v>
       </c>
       <c r="I162" t="n">
         <v/>
@@ -6760,19 +6760,19 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>-5.750508909456899e-11</v>
+        <v>6.514095203845252e-12</v>
       </c>
       <c r="E163" t="n">
-        <v>1.006293088542691e-11</v>
+        <v>5.223550490523076e-10</v>
       </c>
       <c r="F163" t="n">
-        <v>2.134350889863489e-10</v>
+        <v>4.702467743390053e-10</v>
       </c>
       <c r="G163" t="n">
-        <v>3.550433987327249e-12</v>
+        <v>1.417406992184482e-09</v>
       </c>
       <c r="H163" t="n">
-        <v>3.363515576763317e-10</v>
+        <v>1.016198088628386e-08</v>
       </c>
       <c r="I163" t="n">
         <v/>
@@ -6795,19 +6795,19 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>-3.830761904625006e-11</v>
+        <v>-6.066299441428134e-12</v>
       </c>
       <c r="E164" t="n">
-        <v>-4.030822553872753e-11</v>
+        <v>7.049039157550515e-11</v>
       </c>
       <c r="F164" t="n">
-        <v>2.700614543201537e-10</v>
+        <v>2.69627948677013e-10</v>
       </c>
       <c r="G164" t="n">
-        <v>7.412203325240346e-11</v>
+        <v>9.17235616694537e-09</v>
       </c>
       <c r="H164" t="n">
-        <v>2.085612648586294e-10</v>
+        <v>5.774144450140393e-09</v>
       </c>
       <c r="I164" t="n">
         <v/>
@@ -6830,19 +6830,19 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>-4.484670409048449e-11</v>
+        <v>-5.973342704676237e-12</v>
       </c>
       <c r="E165" t="n">
-        <v>-2.764344134415482e-11</v>
+        <v>5.396249463478388e-11</v>
       </c>
       <c r="F165" t="n">
-        <v>2.784550097796864e-10</v>
+        <v>2.640654743591141e-10</v>
       </c>
       <c r="G165" t="n">
-        <v>4.445647784797177e-12</v>
+        <v>2.488660028262101e-10</v>
       </c>
       <c r="H165" t="n">
-        <v>3.34343583335076e-09</v>
+        <v>2.404649679625104e-08</v>
       </c>
       <c r="I165" t="n">
         <v/>
@@ -6865,19 +6865,19 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>-2.997880051148936e-11</v>
+        <v>-3.048465628008995e-12</v>
       </c>
       <c r="E166" t="n">
-        <v>-1.434391793141784e-11</v>
+        <v>7.378745895427847e-13</v>
       </c>
       <c r="F166" t="n">
-        <v>-7.5937924552787e-12</v>
+        <v>1.558045862852729e-13</v>
       </c>
       <c r="G166" t="n">
-        <v>-5.182667524443699e-12</v>
+        <v>7.294977314592999e-13</v>
       </c>
       <c r="H166" t="n">
-        <v>-1.451894216793733e-12</v>
+        <v>2.450321075853297e-13</v>
       </c>
       <c r="I166" t="n">
         <v/>
@@ -6900,19 +6900,19 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>-7.9285721184597e-12</v>
+        <v>1.163122747898615e-11</v>
       </c>
       <c r="E167" t="n">
-        <v>-2.907271077779642e-11</v>
+        <v>6.492774216247606e-11</v>
       </c>
       <c r="F167" t="n">
-        <v>5.337437057766787e-10</v>
+        <v>4.081795445089952e-10</v>
       </c>
       <c r="G167" t="n">
-        <v>-3.452652970479054e-11</v>
+        <v>1.900126010881941e-10</v>
       </c>
       <c r="H167" t="n">
-        <v>3.69223600892281e-10</v>
+        <v>1.256136158076457e-09</v>
       </c>
       <c r="I167" t="n">
         <v/>
@@ -6935,19 +6935,19 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>-5.942940639947976e-11</v>
+        <v>-3.367352524312482e-12</v>
       </c>
       <c r="E168" t="n">
-        <v>-1.9717025671376e-11</v>
+        <v>4.101388079603998e-10</v>
       </c>
       <c r="F168" t="n">
-        <v>3.458161601244995e-10</v>
+        <v>7.081154187306932e-10</v>
       </c>
       <c r="G168" t="n">
-        <v>-4.274887189512766e-11</v>
+        <v>5.091877231871872e-10</v>
       </c>
       <c r="H168" t="n">
-        <v>2.764199528949581e-10</v>
+        <v>8.339733992654923e-09</v>
       </c>
       <c r="I168" t="n">
         <v/>
@@ -6970,19 +6970,19 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>-4.620040383530486e-11</v>
+        <v>-2.43459476339621e-12</v>
       </c>
       <c r="E169" t="n">
-        <v>-3.381871151803121e-11</v>
+        <v>1.729756166316535e-10</v>
       </c>
       <c r="F169" t="n">
-        <v>3.735925318942211e-09</v>
+        <v>2.049226212017406e-09</v>
       </c>
       <c r="G169" t="n">
-        <v>-3.880871570975538e-11</v>
+        <v>5.656057736054665e-10</v>
       </c>
       <c r="H169" t="n">
-        <v>3.407780348743058e-10</v>
+        <v>1.057189616550792e-08</v>
       </c>
       <c r="I169" t="n">
         <v/>
@@ -7005,19 +7005,19 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>-5.53370351958724e-11</v>
+        <v>-5.597886465180445e-12</v>
       </c>
       <c r="E170" t="n">
-        <v>-3.107688270181333e-11</v>
+        <v>6.892979375021586e-11</v>
       </c>
       <c r="F170" t="n">
-        <v>4.775362998343275e-10</v>
+        <v>4.409224272814742e-10</v>
       </c>
       <c r="G170" t="n">
-        <v>-3.564658290464622e-11</v>
+        <v>1.934285359065478e-10</v>
       </c>
       <c r="H170" t="n">
-        <v>1.519951083283286e-08</v>
+        <v>3.356656159697019e-08</v>
       </c>
       <c r="I170" t="n">
         <v/>
@@ -7040,19 +7040,19 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>-5.240465632958522e-11</v>
+        <v>2.421452967586036e-11</v>
       </c>
       <c r="E171" t="n">
-        <v>4.18606924973435e-11</v>
+        <v>7.024318927989168e-12</v>
       </c>
       <c r="F171" t="n">
-        <v>-3.613326725659924e-13</v>
+        <v>2.025662195309692e-12</v>
       </c>
       <c r="G171" t="n">
-        <v>-2.125185592388315e-11</v>
+        <v>1.838697620884762e-13</v>
       </c>
       <c r="H171" t="n">
-        <v>9.298007026031851e-12</v>
+        <v>2.928635888276671e-13</v>
       </c>
       <c r="I171" t="n">
         <v/>
@@ -7075,19 +7075,19 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>-2.030317868877999e-12</v>
+        <v>-3.197592443204566e-12</v>
       </c>
       <c r="E172" t="n">
-        <v>-3.082256022312016e-11</v>
+        <v>3.343786783183564e-11</v>
       </c>
       <c r="F172" t="n">
-        <v>5.405706016011901e-10</v>
+        <v>2.686724515507331e-10</v>
       </c>
       <c r="G172" t="n">
-        <v>2.472416872453055e-12</v>
+        <v>1.383562510693814e-10</v>
       </c>
       <c r="H172" t="n">
-        <v>1.292285105811979e-10</v>
+        <v>5.669201050659044e-10</v>
       </c>
       <c r="I172" t="n">
         <v/>
@@ -7110,19 +7110,19 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>-4.332420258045577e-11</v>
+        <v>-6.650355324864173e-12</v>
       </c>
       <c r="E173" t="n">
-        <v>2.456721018839924e-11</v>
+        <v>1.185622827005647e-10</v>
       </c>
       <c r="F173" t="n">
-        <v>5.366007597993089e-10</v>
+        <v>4.640006882583779e-10</v>
       </c>
       <c r="G173" t="n">
-        <v>4.262397598880083e-12</v>
+        <v>2.924492711992995e-10</v>
       </c>
       <c r="H173" t="n">
-        <v>1.436043928582697e-10</v>
+        <v>9.794349679997001e-10</v>
       </c>
       <c r="I173" t="n">
         <v/>
@@ -7145,19 +7145,19 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>-4.703531779496404e-11</v>
+        <v>-5.942438947023284e-12</v>
       </c>
       <c r="E174" t="n">
-        <v>-2.6484132951465e-11</v>
+        <v>7.886251212087795e-11</v>
       </c>
       <c r="F174" t="n">
-        <v>5.61556096497889e-09</v>
+        <v>8.365932304533964e-10</v>
       </c>
       <c r="G174" t="n">
-        <v>7.013565125724706e-12</v>
+        <v>3.038957998324524e-10</v>
       </c>
       <c r="H174" t="n">
-        <v>1.450663881554663e-10</v>
+        <v>9.879542117243122e-10</v>
       </c>
       <c r="I174" t="n">
         <v/>
@@ -7180,19 +7180,19 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>-5.152004270267164e-11</v>
+        <v>-7.993132811462284e-12</v>
       </c>
       <c r="E175" t="n">
-        <v>-3.690544692209633e-11</v>
+        <v>5.422740381522912e-11</v>
       </c>
       <c r="F175" t="n">
-        <v>4.956621512247512e-10</v>
+        <v>3.44744454785427e-10</v>
       </c>
       <c r="G175" t="n">
-        <v>1.3698863301897e-10</v>
+        <v>4.396063548348384e-10</v>
       </c>
       <c r="H175" t="n">
-        <v>1.089090349955617e-10</v>
+        <v>9.464637954433079e-10</v>
       </c>
       <c r="I175" t="n">
         <v/>
@@ -7215,19 +7215,19 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>-4.195615955147341e-11</v>
+        <v>-6.7874248817903e-12</v>
       </c>
       <c r="E176" t="n">
-        <v>3.122733118983807e-13</v>
+        <v>-4.12769583918616e-13</v>
       </c>
       <c r="F176" t="n">
-        <v>4.096282904390895e-13</v>
+        <v>7.535837774435289e-13</v>
       </c>
       <c r="G176" t="n">
-        <v>1.153091961042571e-11</v>
+        <v>-4.839843336421052e-13</v>
       </c>
       <c r="H176" t="n">
-        <v>-1.141635547270732e-11</v>
+        <v>-2.721323332488369e-13</v>
       </c>
       <c r="I176" t="n">
         <v/>
@@ -7250,19 +7250,19 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>9.395103151233181e-12</v>
+        <v>1.260514158286267e-10</v>
       </c>
       <c r="E177" t="n">
-        <v>5.349290595003422e-11</v>
+        <v>9.230961876704838e-11</v>
       </c>
       <c r="F177" t="n">
-        <v>3.269718586926545e-09</v>
+        <v>5.847285720714462e-10</v>
       </c>
       <c r="G177" t="n">
-        <v>1.977704837341446e-10</v>
+        <v>3.397173346797232e-10</v>
       </c>
       <c r="H177" t="n">
-        <v>5.749764491340429e-09</v>
+        <v>1.430646221672396e-09</v>
       </c>
       <c r="I177" t="n">
         <v/>
@@ -7285,19 +7285,19 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>3.199606156829522e-10</v>
+        <v>6.830110327708683e-12</v>
       </c>
       <c r="E178" t="n">
-        <v>0.166993927400421</v>
+        <v>0.1762870559642668</v>
       </c>
       <c r="F178" t="n">
-        <v>1.153764678073077e-08</v>
+        <v>1.24352957286176e-09</v>
       </c>
       <c r="G178" t="n">
-        <v>1.089989833534346e-10</v>
+        <v>0.0004115691146942133</v>
       </c>
       <c r="H178" t="n">
-        <v>4.632463404375154e-09</v>
+        <v>2.510059495120384e-08</v>
       </c>
       <c r="I178" t="n">
         <v/>
@@ -7320,19 +7320,19 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>3.174964330126851e-11</v>
+        <v>6.318085420546777e-12</v>
       </c>
       <c r="E179" t="n">
-        <v>3.048610339413871e-11</v>
+        <v>2.700725830360457e-10</v>
       </c>
       <c r="F179" t="n">
-        <v>5.578851581969273e-11</v>
+        <v>0.2900840392419096</v>
       </c>
       <c r="G179" t="n">
-        <v>9.849428355307822e-11</v>
+        <v>7.496215403966598e-09</v>
       </c>
       <c r="H179" t="n">
-        <v>2.985687839230491e-09</v>
+        <v>1.119481884677697e-08</v>
       </c>
       <c r="I179" t="n">
         <v/>
@@ -7355,19 +7355,19 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>-2.963878741865846e-11</v>
+        <v>5.56928824864111e-11</v>
       </c>
       <c r="E180" t="n">
-        <v>9.275970666695488e-11</v>
+        <v>4.97595432311277e-10</v>
       </c>
       <c r="F180" t="n">
-        <v>3.154399607339883e-09</v>
+        <v>2.297111671477251e-09</v>
       </c>
       <c r="G180" t="n">
-        <v>8.887384549149853e-11</v>
+        <v>0.0008977762343158594</v>
       </c>
       <c r="H180" t="n">
-        <v>1.541695172142998e-08</v>
+        <v>3.937752495808388e-08</v>
       </c>
       <c r="I180" t="n">
         <v/>
@@ -7390,1282 +7390,22 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>-8.852138091967863e-12</v>
+        <v>7.867891442648171e-14</v>
       </c>
       <c r="E181" t="n">
-        <v>6.108082945294124e-11</v>
+        <v>8.984420070959352e-11</v>
       </c>
       <c r="F181" t="n">
-        <v>4.813927711922383e-09</v>
+        <v>5.915595712263479e-10</v>
       </c>
       <c r="G181" t="n">
-        <v>1.840797316341362e-10</v>
+        <v>3.415770490955721e-10</v>
       </c>
       <c r="H181" t="n">
-        <v>1.302513734453169e-09</v>
+        <v>0.003113526271699747</v>
       </c>
       <c r="I181" t="n">
         <v/>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>i1</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>i1</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E182" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F182" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G182" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H182" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I182" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>i1</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>i2</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E183" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F183" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G183" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H183" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I183" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>i1</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>i3</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E184" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F184" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G184" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H184" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I184" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>i1</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>i4</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E185" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F185" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G185" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H185" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I185" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>i1</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>i5</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E186" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F186" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G186" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H186" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I186" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>i1</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E187" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F187" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G187" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H187" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I187" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>i2</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>i1</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E188" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F188" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G188" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H188" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I188" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>i2</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>i2</t>
-        </is>
-      </c>
-      <c r="D189" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E189" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F189" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G189" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H189" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I189" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>i2</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>i3</t>
-        </is>
-      </c>
-      <c r="D190" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E190" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F190" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G190" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H190" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I190" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>i2</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>i4</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E191" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F191" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G191" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H191" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I191" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>i2</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>i5</t>
-        </is>
-      </c>
-      <c r="D192" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E192" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F192" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G192" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H192" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I192" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>i2</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="D193" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E193" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F193" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G193" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H193" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I193" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>i3</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>i1</t>
-        </is>
-      </c>
-      <c r="D194" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E194" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F194" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G194" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H194" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I194" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>i3</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>i2</t>
-        </is>
-      </c>
-      <c r="D195" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E195" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F195" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G195" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H195" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I195" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>i3</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>i3</t>
-        </is>
-      </c>
-      <c r="D196" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E196" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F196" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G196" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H196" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I196" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>i3</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>i4</t>
-        </is>
-      </c>
-      <c r="D197" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E197" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F197" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G197" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H197" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I197" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>i3</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>i5</t>
-        </is>
-      </c>
-      <c r="D198" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E198" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F198" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G198" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H198" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I198" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>i3</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="D199" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E199" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F199" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G199" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H199" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I199" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>i4</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>i1</t>
-        </is>
-      </c>
-      <c r="D200" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E200" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F200" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G200" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H200" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I200" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>i4</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>i2</t>
-        </is>
-      </c>
-      <c r="D201" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E201" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F201" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G201" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H201" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I201" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>i4</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>i3</t>
-        </is>
-      </c>
-      <c r="D202" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E202" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F202" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G202" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H202" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I202" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>i4</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>i4</t>
-        </is>
-      </c>
-      <c r="D203" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E203" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F203" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G203" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H203" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I203" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>i4</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>i5</t>
-        </is>
-      </c>
-      <c r="D204" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E204" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F204" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G204" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H204" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I204" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>i4</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="D205" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E205" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F205" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G205" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H205" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I205" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>i5</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>i1</t>
-        </is>
-      </c>
-      <c r="D206" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E206" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F206" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G206" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H206" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I206" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>i5</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>i2</t>
-        </is>
-      </c>
-      <c r="D207" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E207" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F207" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G207" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H207" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I207" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>i5</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>i3</t>
-        </is>
-      </c>
-      <c r="D208" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E208" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F208" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G208" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H208" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I208" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>i5</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>i4</t>
-        </is>
-      </c>
-      <c r="D209" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E209" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F209" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G209" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H209" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I209" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>i5</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>i5</t>
-        </is>
-      </c>
-      <c r="D210" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E210" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F210" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G210" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H210" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I210" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>i5</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="D211" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E211" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F211" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G211" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H211" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I211" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>i1</t>
-        </is>
-      </c>
-      <c r="D212" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E212" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F212" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G212" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H212" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I212" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>i2</t>
-        </is>
-      </c>
-      <c r="D213" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E213" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F213" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G213" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H213" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I213" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>i3</t>
-        </is>
-      </c>
-      <c r="D214" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E214" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F214" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G214" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H214" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I214" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>i4</t>
-        </is>
-      </c>
-      <c r="D215" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E215" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F215" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G215" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H215" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I215" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>i5</t>
-        </is>
-      </c>
-      <c r="D216" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E216" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F216" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G216" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H216" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I216" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="D217" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E217" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F217" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G217" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H217" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I217" t="n">
-        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -8684,7 +7424,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>0.11929</v>
+        <v>0.0275642</v>
       </c>
     </row>
   </sheetData>
@@ -8738,10 +7478,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2467213991860113</v>
+        <v>0.4363089759121188</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.1863460931282018</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>

--- a/6node_spain/output_all.xlsx
+++ b/6node_spain/output_all.xlsx
@@ -459,19 +459,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9572118407648046</v>
+        <v>0.2247648678086808</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3220873957491368</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1.245309948323212</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>6.294582074789266e-10</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6566439572261955</v>
+        <v>0.4495297368291778</v>
       </c>
     </row>
   </sheetData>
@@ -558,16 +558,16 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2.74771350488413e-11</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1.454363032110768</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.416896192563044e-11</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8681712529391943</v>
+        <v>0.7492162247732381</v>
       </c>
     </row>
     <row r="4">
@@ -580,19 +580,19 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>2.74771350488413e-11</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6211535484264601</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1.588918924010747e-11</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2262353424377983</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>1.454363032110768</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6211535484264601</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -630,10 +630,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>1.416896192563044e-11</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1.588918924010747e-11</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -655,10 +655,10 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8681712529391943</v>
+        <v>0.7492162247732381</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2262353424377983</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -757,13 +757,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1532216079795203</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1746731811308531</v>
+        <v>0.1507398233537224</v>
       </c>
     </row>
     <row r="4">
@@ -782,13 +782,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1733576579319678</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2973395199056027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -801,10 +801,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1516397779043354</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1718649646636453</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -813,7 +813,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1.850097852695853e-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -838,7 +838,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.116662400908353e-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -851,16 +851,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1762870588476576</v>
+        <v>0.1521325710087522</v>
       </c>
       <c r="D7" t="n">
-        <v>0.288776244866266</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1.289723883246552e-11</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>7.346123709339736e-11</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -953,13 +953,13 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8467783920204797</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8253268188691469</v>
+        <v>0.8492601766462776</v>
       </c>
     </row>
     <row r="4">
@@ -978,13 +978,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8266423420680322</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7026604800943973</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -997,10 +997,10 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8483602220956646</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8281350353363547</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -1009,7 +1009,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.999999999981499</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1034,7 +1034,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1.000000000021167</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1047,16 +1047,16 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8237129411523424</v>
+        <v>0.8478674289912478</v>
       </c>
       <c r="D7" t="n">
-        <v>0.711223755133734</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9999999999871028</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9999999999265388</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1128,19 +1128,19 @@
         <v/>
       </c>
       <c r="E2" t="n">
-        <v>5.458669009792795e-08</v>
+        <v>1.480044337645017e-11</v>
       </c>
       <c r="F2" t="n">
-        <v>5.495509331106087e-11</v>
+        <v>1.882583757692968e-12</v>
       </c>
       <c r="G2" t="n">
-        <v>3.169458621617864e-11</v>
+        <v>1.400526107459821e-11</v>
       </c>
       <c r="H2" t="n">
-        <v>4.163509348923588e-11</v>
+        <v>2.757933747757716e-11</v>
       </c>
       <c r="I2" t="n">
-        <v>3.403769464154021e-11</v>
+        <v>1.957034997895108e-11</v>
       </c>
     </row>
     <row r="3">
@@ -1163,19 +1163,19 @@
         <v/>
       </c>
       <c r="E3" t="n">
-        <v>-5.664563833087858e-12</v>
+        <v>4.285430911263871e-12</v>
       </c>
       <c r="F3" t="n">
-        <v>7.038447857988301e-10</v>
+        <v>-3.940294805374026e-12</v>
       </c>
       <c r="G3" t="n">
-        <v>2.835688270432345e-11</v>
+        <v>1.751978890581288e-11</v>
       </c>
       <c r="H3" t="n">
-        <v>3.814321689810269e-11</v>
+        <v>2.531506167909295e-11</v>
       </c>
       <c r="I3" t="n">
-        <v>3.074645032021281e-11</v>
+        <v>1.119602695961126e-11</v>
       </c>
     </row>
     <row r="4">
@@ -1198,19 +1198,19 @@
         <v/>
       </c>
       <c r="E4" t="n">
-        <v>1.257528136712982e-11</v>
+        <v>5.934416599282776e-12</v>
       </c>
       <c r="F4" t="n">
-        <v>3.813757876956261e-11</v>
+        <v>6.564276097864454e-12</v>
       </c>
       <c r="G4" t="n">
-        <v>4.279511322579283e-10</v>
+        <v>-1.322524736983353e-11</v>
       </c>
       <c r="H4" t="n">
-        <v>4.504639992536817e-11</v>
+        <v>2.752021605291402e-11</v>
       </c>
       <c r="I4" t="n">
-        <v>4.875455466868499e-11</v>
+        <v>1.142451502653555e-11</v>
       </c>
     </row>
     <row r="5">
@@ -1233,19 +1233,19 @@
         <v/>
       </c>
       <c r="E5" t="n">
-        <v>3.76186674357357e-11</v>
+        <v>5.464167333579032e-12</v>
       </c>
       <c r="F5" t="n">
-        <v>7.379650599831761e-12</v>
+        <v>4.309576577509042e-12</v>
       </c>
       <c r="G5" t="n">
-        <v>2.494206642450477e-11</v>
+        <v>1.853755366252409e-11</v>
       </c>
       <c r="H5" t="n">
-        <v>2.166573792341249e-09</v>
+        <v>-1.264665777439352e-11</v>
       </c>
       <c r="I5" t="n">
-        <v>8.800796531291943e-12</v>
+        <v>1.115817386391917e-11</v>
       </c>
     </row>
     <row r="6">
@@ -1268,19 +1268,19 @@
         <v/>
       </c>
       <c r="E6" t="n">
-        <v>-1.97469468039694e-11</v>
+        <v>8.248740565663363e-12</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.239103669510194e-12</v>
+        <v>5.690839786624128e-12</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.562132090288395e-12</v>
+        <v>4.814128686613123e-12</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.433320119822662e-12</v>
+        <v>2.468971370679038e-12</v>
       </c>
       <c r="I6" t="n">
-        <v>1.813774292066346e-10</v>
+        <v>2.024338096019279e-12</v>
       </c>
     </row>
     <row r="7">
@@ -1303,19 +1303,19 @@
         <v/>
       </c>
       <c r="E7" t="n">
-        <v>-1.237460106586204e-11</v>
+        <v>-4.081759188525122e-12</v>
       </c>
       <c r="F7" t="n">
-        <v>4.979683581779496e-12</v>
+        <v>-3.297129083464744e-13</v>
       </c>
       <c r="G7" t="n">
-        <v>5.072392112992006e-12</v>
+        <v>1.77843467520911e-12</v>
       </c>
       <c r="H7" t="n">
-        <v>3.897662216402091e-12</v>
+        <v>1.46474733611659e-12</v>
       </c>
       <c r="I7" t="n">
-        <v>6.89306858068079e-12</v>
+        <v>-2.575749045587882e-12</v>
       </c>
     </row>
     <row r="8">
@@ -1338,19 +1338,19 @@
         <v/>
       </c>
       <c r="E8" t="n">
-        <v>-1.875855466580556e-11</v>
+        <v>-1.018466915260351e-11</v>
       </c>
       <c r="F8" t="n">
-        <v>6.002083298912924e-11</v>
+        <v>-8.59820617336918e-12</v>
       </c>
       <c r="G8" t="n">
-        <v>2.088184457562157e-11</v>
+        <v>-6.13609727358168e-13</v>
       </c>
       <c r="H8" t="n">
-        <v>2.128006499931926e-11</v>
+        <v>3.979734168809137e-12</v>
       </c>
       <c r="I8" t="n">
-        <v>1.67424676852212e-11</v>
+        <v>-9.786491440949261e-12</v>
       </c>
     </row>
     <row r="9">
@@ -1373,19 +1373,19 @@
         <v/>
       </c>
       <c r="E9" t="n">
-        <v>-2.011007363739208e-11</v>
+        <v>-1.04886000988543e-11</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.218392215247025e-12</v>
+        <v>-1.007419155672141e-11</v>
       </c>
       <c r="G9" t="n">
-        <v>1.906049224485343e-11</v>
+        <v>4.109848975930856e-12</v>
       </c>
       <c r="H9" t="n">
-        <v>2.753105116376404e-12</v>
+        <v>-1.139542169859491e-12</v>
       </c>
       <c r="I9" t="n">
-        <v>1.643144504851301e-12</v>
+        <v>-1.026189403422301e-11</v>
       </c>
     </row>
     <row r="10">
@@ -1408,19 +1408,19 @@
         <v/>
       </c>
       <c r="E10" t="n">
-        <v>-1.991658833758559e-11</v>
+        <v>-7.262095286688394e-12</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.938132936923566e-12</v>
+        <v>-5.948534356496038e-12</v>
       </c>
       <c r="G10" t="n">
-        <v>5.415369891048147e-12</v>
+        <v>4.69382491667004e-12</v>
       </c>
       <c r="H10" t="n">
-        <v>3.465649421337698e-11</v>
+        <v>2.84349609184671e-11</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.262284662500962e-12</v>
+        <v>-6.769186341098366e-12</v>
       </c>
     </row>
     <row r="11">
@@ -1443,19 +1443,19 @@
         <v/>
       </c>
       <c r="E11" t="n">
-        <v>-2.093876131630506e-11</v>
+        <v>-8.781242135200942e-13</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.062138027456614e-11</v>
+        <v>4.690726669037883e-12</v>
       </c>
       <c r="G11" t="n">
-        <v>-8.892949736551117e-12</v>
+        <v>1.62519976913137e-12</v>
       </c>
       <c r="H11" t="n">
-        <v>-9.328199820029157e-12</v>
+        <v>-3.212387299987847e-12</v>
       </c>
       <c r="I11" t="n">
-        <v>5.174740127655349e-12</v>
+        <v>2.391681409174153e-11</v>
       </c>
     </row>
     <row r="12">
@@ -1478,19 +1478,19 @@
         <v/>
       </c>
       <c r="E12" t="n">
-        <v>-1.087648552313578e-11</v>
+        <v>1.135520093578737e-12</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.577526010598021e-12</v>
+        <v>-4.073747051970698e-12</v>
       </c>
       <c r="G12" t="n">
-        <v>3.734290665998911e-12</v>
+        <v>1.222484456775506e-12</v>
       </c>
       <c r="H12" t="n">
-        <v>2.389029405858259e-12</v>
+        <v>1.434703667790598e-12</v>
       </c>
       <c r="I12" t="n">
-        <v>5.220183572791662e-12</v>
+        <v>1.43050864266003e-12</v>
       </c>
     </row>
     <row r="13">
@@ -1513,19 +1513,19 @@
         <v/>
       </c>
       <c r="E13" t="n">
-        <v>-1.554313932647495e-11</v>
+        <v>-8.575382633216793e-12</v>
       </c>
       <c r="F13" t="n">
-        <v>3.774389378775924e-12</v>
+        <v>-1.048172210643201e-11</v>
       </c>
       <c r="G13" t="n">
-        <v>1.91593495238469e-11</v>
+        <v>-1.616835127448535e-12</v>
       </c>
       <c r="H13" t="n">
-        <v>1.845222972494235e-11</v>
+        <v>4.549625537383269e-12</v>
       </c>
       <c r="I13" t="n">
-        <v>1.428226112463149e-11</v>
+        <v>-8.738455358498939e-12</v>
       </c>
     </row>
     <row r="14">
@@ -1548,19 +1548,19 @@
         <v/>
       </c>
       <c r="E14" t="n">
-        <v>-1.97525996836988e-11</v>
+        <v>-7.343278573240007e-12</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.326104442354552e-12</v>
+        <v>-8.874919845299587e-12</v>
       </c>
       <c r="G14" t="n">
-        <v>2.093362794981034e-11</v>
+        <v>1.4725298270698e-11</v>
       </c>
       <c r="H14" t="n">
-        <v>3.231316222458044e-12</v>
+        <v>1.788516824178246e-12</v>
       </c>
       <c r="I14" t="n">
-        <v>2.156973134766827e-12</v>
+        <v>-7.467212177334567e-12</v>
       </c>
     </row>
     <row r="15">
@@ -1583,19 +1583,19 @@
         <v/>
       </c>
       <c r="E15" t="n">
-        <v>-1.950063970810557e-11</v>
+        <v>-7.730401510260072e-12</v>
       </c>
       <c r="F15" t="n">
-        <v>-7.453326850208513e-12</v>
+        <v>-9.318833876269673e-12</v>
       </c>
       <c r="G15" t="n">
-        <v>7.199644077253196e-12</v>
+        <v>8.911471846243703e-13</v>
       </c>
       <c r="H15" t="n">
-        <v>4.096597078095721e-11</v>
+        <v>2.431117448349816e-11</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.317823639750988e-12</v>
+        <v>-7.74082659335309e-12</v>
       </c>
     </row>
     <row r="16">
@@ -1618,19 +1618,19 @@
         <v/>
       </c>
       <c r="E16" t="n">
-        <v>-2.064110999540803e-11</v>
+        <v>-5.20990903664746e-12</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.146259969436776e-11</v>
+        <v>-7.842892660664941e-12</v>
       </c>
       <c r="G16" t="n">
-        <v>-8.414572973424955e-12</v>
+        <v>-2.534737212008831e-12</v>
       </c>
       <c r="H16" t="n">
-        <v>-9.046967874661217e-12</v>
+        <v>-4.090408756408231e-12</v>
       </c>
       <c r="I16" t="n">
-        <v>9.045211774332619e-12</v>
+        <v>8.14937928458056e-13</v>
       </c>
     </row>
     <row r="17">
@@ -1653,19 +1653,19 @@
         <v/>
       </c>
       <c r="E17" t="n">
-        <v>6.66602871585139e-12</v>
+        <v>3.096789187146547e-12</v>
       </c>
       <c r="F17" t="n">
-        <v>8.93653131517284e-12</v>
+        <v>2.23158802841522e-12</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.253740649743893e-12</v>
+        <v>-3.402065828207578e-12</v>
       </c>
       <c r="H17" t="n">
-        <v>5.216257383794539e-12</v>
+        <v>3.452342120011355e-12</v>
       </c>
       <c r="I17" t="n">
-        <v>5.117849667352556e-12</v>
+        <v>4.927195262150634e-12</v>
       </c>
     </row>
     <row r="18">
@@ -1688,19 +1688,19 @@
         <v/>
       </c>
       <c r="E18" t="n">
-        <v>-1.90632835044536e-11</v>
+        <v>-9.143683744957088e-12</v>
       </c>
       <c r="F18" t="n">
-        <v>2.68636858173043e-12</v>
+        <v>-1.019808148321294e-11</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.907872454472458e-12</v>
+        <v>-6.472825050731262e-12</v>
       </c>
       <c r="H18" t="n">
-        <v>3.27362620947652e-12</v>
+        <v>1.78122396622682e-13</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.67042466962033e-12</v>
+        <v>-9.178125154088039e-12</v>
       </c>
     </row>
     <row r="19">
@@ -1723,19 +1723,19 @@
         <v/>
       </c>
       <c r="E19" t="n">
-        <v>-1.955186696042984e-11</v>
+        <v>-6.956117341428425e-12</v>
       </c>
       <c r="F19" t="n">
-        <v>1.777880394003778e-11</v>
+        <v>-4.657224898382269e-12</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.19830436215341e-12</v>
+        <v>-3.93045962479569e-12</v>
       </c>
       <c r="H19" t="n">
-        <v>4.904912947348859e-12</v>
+        <v>3.648817390956299e-12</v>
       </c>
       <c r="I19" t="n">
-        <v>-5.094232993435027e-13</v>
+        <v>-6.574436047935008e-12</v>
       </c>
     </row>
     <row r="20">
@@ -1758,19 +1758,19 @@
         <v/>
       </c>
       <c r="E20" t="n">
-        <v>-1.967068787097253e-11</v>
+        <v>-9.313098246389676e-12</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.870148683739519e-12</v>
+        <v>-9.714860016080569e-12</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.643379905521186e-12</v>
+        <v>-5.488553903191298e-12</v>
       </c>
       <c r="H20" t="n">
-        <v>3.630234177890778e-11</v>
+        <v>1.732567109607292e-11</v>
       </c>
       <c r="I20" t="n">
-        <v>-4.476364069772428e-12</v>
+        <v>-9.132903198742838e-12</v>
       </c>
     </row>
     <row r="21">
@@ -1793,19 +1793,19 @@
         <v/>
       </c>
       <c r="E21" t="n">
-        <v>-2.034704043217426e-11</v>
+        <v>-8.990956208086479e-12</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.805081624028984e-12</v>
+        <v>-9.534832738499326e-12</v>
       </c>
       <c r="G21" t="n">
-        <v>-7.80277342336253e-12</v>
+        <v>-6.607187428004606e-12</v>
       </c>
       <c r="H21" t="n">
-        <v>-4.54453074867379e-12</v>
+        <v>-2.666407741542247e-12</v>
       </c>
       <c r="I21" t="n">
-        <v>3.703996080325909e-11</v>
+        <v>-6.484719966092916e-12</v>
       </c>
     </row>
     <row r="22">
@@ -1828,19 +1828,19 @@
         <v/>
       </c>
       <c r="E22" t="n">
-        <v>3.635012404503641e-11</v>
+        <v>7.468005152939783e-13</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.496117300325294e-12</v>
+        <v>9.065074288774658e-13</v>
       </c>
       <c r="G22" t="n">
-        <v>2.15457720016647e-12</v>
+        <v>2.809812507814784e-12</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.851174869823847e-12</v>
+        <v>-2.207931736095556e-12</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.89618456695903e-12</v>
+        <v>2.162391815599093e-12</v>
       </c>
     </row>
     <row r="23">
@@ -1863,19 +1863,19 @@
         <v/>
       </c>
       <c r="E23" t="n">
-        <v>-1.901522772033153e-11</v>
+        <v>-2.625561055605301e-12</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.657839987356861e-12</v>
+        <v>-5.740192309045231e-12</v>
       </c>
       <c r="G23" t="n">
-        <v>4.186857519919358e-12</v>
+        <v>4.76236771928022e-12</v>
       </c>
       <c r="H23" t="n">
-        <v>-8.157853814525164e-13</v>
+        <v>-2.993844483445183e-14</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.597537281177279e-12</v>
+        <v>-3.266246555879968e-12</v>
       </c>
     </row>
     <row r="24">
@@ -1898,19 +1898,19 @@
         <v/>
       </c>
       <c r="E24" t="n">
-        <v>-1.929312032480439e-11</v>
+        <v>-8.028774823523644e-12</v>
       </c>
       <c r="F24" t="n">
-        <v>3.489866073936948e-12</v>
+        <v>-6.187342979198611e-12</v>
       </c>
       <c r="G24" t="n">
-        <v>6.011358048543665e-12</v>
+        <v>2.01996984805698e-12</v>
       </c>
       <c r="H24" t="n">
-        <v>6.232488123511552e-13</v>
+        <v>-9.954331097238055e-13</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.731298943973402e-12</v>
+        <v>-7.657006010478657e-12</v>
       </c>
     </row>
     <row r="25">
@@ -1933,19 +1933,19 @@
         <v/>
       </c>
       <c r="E25" t="n">
-        <v>-1.960126025614961e-11</v>
+        <v>-9.514293981368435e-12</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.180759310721063e-12</v>
+        <v>-9.665471988953811e-12</v>
       </c>
       <c r="G25" t="n">
-        <v>2.196537318317595e-11</v>
+        <v>8.778653238769607e-12</v>
       </c>
       <c r="H25" t="n">
-        <v>-9.915536328865195e-13</v>
+        <v>-2.815362679910304e-12</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.728749321255794e-12</v>
+        <v>-9.365147465501821e-12</v>
       </c>
     </row>
     <row r="26">
@@ -1968,19 +1968,19 @@
         <v/>
       </c>
       <c r="E26" t="n">
-        <v>-2.081401664418638e-11</v>
+        <v>-7.739864312263999e-12</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.194804872561434e-11</v>
+        <v>-8.205224262763684e-12</v>
       </c>
       <c r="G26" t="n">
-        <v>-8.571945693599407e-12</v>
+        <v>-3.073270295449894e-12</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.038697063605085e-11</v>
+        <v>-6.063110787486421e-12</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.713715235584109e-12</v>
+        <v>-4.160315236241705e-12</v>
       </c>
     </row>
     <row r="27">
@@ -2003,19 +2003,19 @@
         <v/>
       </c>
       <c r="E27" t="n">
-        <v>-1.97661788499361e-11</v>
+        <v>-8.973380868670217e-13</v>
       </c>
       <c r="F27" t="n">
-        <v>-7.519139753485585e-12</v>
+        <v>1.265388229244651e-12</v>
       </c>
       <c r="G27" t="n">
-        <v>-8.435149205549128e-12</v>
+        <v>-2.408658437731791e-12</v>
       </c>
       <c r="H27" t="n">
-        <v>-8.414582136632417e-12</v>
+        <v>-4.143782527430161e-12</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.401815382177383e-11</v>
+        <v>-5.944266542180305e-12</v>
       </c>
     </row>
     <row r="28">
@@ -2038,19 +2038,19 @@
         <v/>
       </c>
       <c r="E28" t="n">
-        <v>-2.056646115256088e-11</v>
+        <v>1.138212238235325e-11</v>
       </c>
       <c r="F28" t="n">
-        <v>-9.535400139804619e-12</v>
+        <v>4.277493814983187e-12</v>
       </c>
       <c r="G28" t="n">
-        <v>-9.595771717370733e-12</v>
+        <v>9.157299936222989e-13</v>
       </c>
       <c r="H28" t="n">
-        <v>-9.286037317108956e-12</v>
+        <v>-2.749634013219662e-12</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.486085757993615e-11</v>
+        <v>-3.864029680760062e-12</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2073,19 @@
         <v/>
       </c>
       <c r="E29" t="n">
-        <v>-2.085880877231465e-11</v>
+        <v>-6.839321253564789e-12</v>
       </c>
       <c r="F29" t="n">
-        <v>-7.501341707607854e-12</v>
+        <v>-2.702088996577053e-12</v>
       </c>
       <c r="G29" t="n">
-        <v>-9.439441723360325e-12</v>
+        <v>-2.308331829153093e-12</v>
       </c>
       <c r="H29" t="n">
-        <v>-8.959865396764957e-12</v>
+        <v>-3.954568372404846e-12</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.486138979538406e-11</v>
+        <v>-8.879141018090029e-12</v>
       </c>
     </row>
     <row r="30">
@@ -2108,19 +2108,19 @@
         <v/>
       </c>
       <c r="E30" t="n">
-        <v>-2.051577170001593e-11</v>
+        <v>-9.895310299309784e-12</v>
       </c>
       <c r="F30" t="n">
-        <v>-6.685849272392029e-12</v>
+        <v>-9.823103814466558e-12</v>
       </c>
       <c r="G30" t="n">
-        <v>3.328078855093979e-13</v>
+        <v>1.3618326354723e-12</v>
       </c>
       <c r="H30" t="n">
-        <v>-4.886660061156343e-12</v>
+        <v>-3.415282764685844e-12</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.332432455538449e-11</v>
+        <v>-1.077325045425067e-11</v>
       </c>
     </row>
     <row r="31">
@@ -2143,19 +2143,19 @@
         <v/>
       </c>
       <c r="E31" t="n">
-        <v>-2.090425241917208e-11</v>
+        <v>-8.320265947573286e-12</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.188899218299237e-11</v>
+        <v>-8.219072439165488e-12</v>
       </c>
       <c r="G31" t="n">
-        <v>-9.167480229039877e-12</v>
+        <v>-3.33643884174925e-12</v>
       </c>
       <c r="H31" t="n">
-        <v>-4.254779541885717e-12</v>
+        <v>6.999244638843131e-13</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.536049790731079e-11</v>
+        <v>-9.801581183270302e-12</v>
       </c>
     </row>
     <row r="32">
@@ -2175,22 +2175,22 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-1.799358330140869e-11</v>
+        <v>-8.773688849237916e-12</v>
       </c>
       <c r="E32" t="n">
         <v/>
       </c>
       <c r="F32" t="n">
-        <v>-5.096588627107797e-12</v>
+        <v>-8.47854922560406e-12</v>
       </c>
       <c r="G32" t="n">
-        <v>-2.33164062395365e-12</v>
+        <v>-2.992244395354313e-12</v>
       </c>
       <c r="H32" t="n">
-        <v>8.940554561517882e-14</v>
+        <v>5.25463101600051e-13</v>
       </c>
       <c r="I32" t="n">
-        <v>1.259329507793711e-13</v>
+        <v>8.135137709027688e-13</v>
       </c>
     </row>
     <row r="33">
@@ -2210,22 +2210,22 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-2.009361323640589e-11</v>
+        <v>-9.214588646259493e-12</v>
       </c>
       <c r="E33" t="n">
         <v/>
       </c>
       <c r="F33" t="n">
-        <v>-3.533395765510211e-13</v>
+        <v>-7.662793330341453e-12</v>
       </c>
       <c r="G33" t="n">
-        <v>4.941045968668433e-11</v>
+        <v>-3.336370691887008e-12</v>
       </c>
       <c r="H33" t="n">
-        <v>2.40556785159887e-12</v>
+        <v>1.161290077464622e-12</v>
       </c>
       <c r="I33" t="n">
-        <v>1.969031231000211e-11</v>
+        <v>-4.950756258523404e-12</v>
       </c>
     </row>
     <row r="34">
@@ -2245,22 +2245,22 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-1.983539833582138e-11</v>
+        <v>-8.831269184411388e-12</v>
       </c>
       <c r="E34" t="n">
         <v/>
       </c>
       <c r="F34" t="n">
-        <v>-2.6400638298881e-12</v>
+        <v>-8.469790252605914e-12</v>
       </c>
       <c r="G34" t="n">
-        <v>6.844809718687699e-11</v>
+        <v>1.521934774982162e-11</v>
       </c>
       <c r="H34" t="n">
-        <v>6.495759518416505e-12</v>
+        <v>2.170808897850027e-12</v>
       </c>
       <c r="I34" t="n">
-        <v>3.805772777289481e-11</v>
+        <v>-3.030621365024244e-12</v>
       </c>
     </row>
     <row r="35">
@@ -2280,22 +2280,22 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-1.986137107535863e-11</v>
+        <v>-9.398568090012188e-12</v>
       </c>
       <c r="E35" t="n">
         <v/>
       </c>
       <c r="F35" t="n">
-        <v>-8.737228503707478e-12</v>
+        <v>-8.978013101376043e-12</v>
       </c>
       <c r="G35" t="n">
-        <v>1.700844188174574e-11</v>
+        <v>-4.634567991002373e-12</v>
       </c>
       <c r="H35" t="n">
-        <v>1.981714203894107e-11</v>
+        <v>7.654015544782998e-12</v>
       </c>
       <c r="I35" t="n">
-        <v>1.789666106381746e-11</v>
+        <v>-4.104968958415913e-12</v>
       </c>
     </row>
     <row r="36">
@@ -2315,22 +2315,22 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-2.083146019924447e-11</v>
+        <v>-9.853890267818632e-12</v>
       </c>
       <c r="E36" t="n">
         <v/>
       </c>
       <c r="F36" t="n">
-        <v>-9.625201513879022e-12</v>
+        <v>-9.029509522959255e-12</v>
       </c>
       <c r="G36" t="n">
-        <v>3.774591912935002e-11</v>
+        <v>-6.578356476666941e-12</v>
       </c>
       <c r="H36" t="n">
-        <v>-7.664990927088142e-12</v>
+        <v>-3.242188143578547e-12</v>
       </c>
       <c r="I36" t="n">
-        <v>7.036664243312659e-11</v>
+        <v>1.900279282356372e-12</v>
       </c>
     </row>
     <row r="37">
@@ -2350,22 +2350,22 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>5.575134878544022e-08</v>
+        <v>1.348624368448632e-11</v>
       </c>
       <c r="E37" t="n">
         <v/>
       </c>
       <c r="F37" t="n">
-        <v>1.045504168548879e-13</v>
+        <v>-7.158368682174508e-12</v>
       </c>
       <c r="G37" t="n">
-        <v>4.530695744443999e-11</v>
+        <v>1.461161300502125e-11</v>
       </c>
       <c r="H37" t="n">
-        <v>2.117569801819841e-11</v>
+        <v>9.509244754871782e-12</v>
       </c>
       <c r="I37" t="n">
-        <v>7.480801291794841e-11</v>
+        <v>1.358611432319459e-11</v>
       </c>
     </row>
     <row r="38">
@@ -2385,22 +2385,22 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>7.421549354407823e-11</v>
+        <v>-6.487145928014846e-12</v>
       </c>
       <c r="E38" t="n">
         <v/>
       </c>
       <c r="F38" t="n">
-        <v>4.240976183217319e-10</v>
+        <v>-7.364201659926054e-12</v>
       </c>
       <c r="G38" t="n">
-        <v>8.961072217928141e-10</v>
+        <v>9.909862267120363e-12</v>
       </c>
       <c r="H38" t="n">
-        <v>7.667677810616076e-11</v>
+        <v>8.361748020554197e-12</v>
       </c>
       <c r="I38" t="n">
-        <v>2.602372035343039e-10</v>
+        <v>1.783721174359784e-11</v>
       </c>
     </row>
     <row r="39">
@@ -2420,22 +2420,22 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-1.45905248653193e-11</v>
+        <v>-7.042583747593363e-12</v>
       </c>
       <c r="E39" t="n">
         <v/>
       </c>
       <c r="F39" t="n">
-        <v>1.992952493966975e-11</v>
+        <v>-8.950106673274015e-12</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1511920838274534</v>
+        <v>1.825480354021187e-10</v>
       </c>
       <c r="H39" t="n">
-        <v>2.316216014542745e-11</v>
+        <v>3.011358989942017e-12</v>
       </c>
       <c r="I39" t="n">
-        <v>1.946155976977453e-10</v>
+        <v>4.181955984399974e-12</v>
       </c>
     </row>
     <row r="40">
@@ -2455,22 +2455,22 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-9.666005637475715e-12</v>
+        <v>4.216904675216612e-12</v>
       </c>
       <c r="E40" t="n">
         <v/>
       </c>
       <c r="F40" t="n">
-        <v>2.522650216764293e-12</v>
+        <v>-1.881806238784987e-12</v>
       </c>
       <c r="G40" t="n">
-        <v>5.075322632994215e-11</v>
+        <v>3.352752862574831e-11</v>
       </c>
       <c r="H40" t="n">
-        <v>2.420763868352722e-10</v>
+        <v>7.27754746569467e-11</v>
       </c>
       <c r="I40" t="n">
-        <v>8.391849089558241e-11</v>
+        <v>2.752493457194828e-11</v>
       </c>
     </row>
     <row r="41">
@@ -2490,22 +2490,22 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-1.985535424171089e-11</v>
+        <v>4.266331811148036e-11</v>
       </c>
       <c r="E41" t="n">
         <v/>
       </c>
       <c r="F41" t="n">
-        <v>-3.756631683915198e-12</v>
+        <v>4.056000488237e-11</v>
       </c>
       <c r="G41" t="n">
-        <v>1.333313704672364e-10</v>
+        <v>3.08875515903206e-11</v>
       </c>
       <c r="H41" t="n">
-        <v>-4.836670414878655e-12</v>
+        <v>8.121670880784533e-12</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1748625092892639</v>
+        <v>0.1507398305837125</v>
       </c>
     </row>
     <row r="42">
@@ -2525,22 +2525,22 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-1.653142568097186e-11</v>
+        <v>-4.027618637006211e-12</v>
       </c>
       <c r="E42" t="n">
         <v/>
       </c>
       <c r="F42" t="n">
-        <v>-5.767801455811101e-12</v>
+        <v>-9.591186002113208e-12</v>
       </c>
       <c r="G42" t="n">
-        <v>4.192241360425644e-11</v>
+        <v>-3.992160168022464e-12</v>
       </c>
       <c r="H42" t="n">
-        <v>5.388146271108125e-12</v>
+        <v>8.813041305641428e-13</v>
       </c>
       <c r="I42" t="n">
-        <v>3.415415933299357e-11</v>
+        <v>-4.382500257810072e-12</v>
       </c>
     </row>
     <row r="43">
@@ -2560,22 +2560,22 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>6.888121872248338e-11</v>
+        <v>-8.794450561140084e-12</v>
       </c>
       <c r="E43" t="n">
         <v/>
       </c>
       <c r="F43" t="n">
-        <v>1.256588968710767e-11</v>
+        <v>-1.01083372870876e-11</v>
       </c>
       <c r="G43" t="n">
-        <v>5.719450672542947e-12</v>
+        <v>-4.354307415273967e-12</v>
       </c>
       <c r="H43" t="n">
-        <v>1.380402726208834e-11</v>
+        <v>-7.086275876909424e-14</v>
       </c>
       <c r="I43" t="n">
-        <v>1.350185274786154e-11</v>
+        <v>4.042924454283079e-12</v>
       </c>
     </row>
     <row r="44">
@@ -2595,22 +2595,22 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-1.867540756937877e-11</v>
+        <v>-6.981965979509854e-12</v>
       </c>
       <c r="E44" t="n">
         <v/>
       </c>
       <c r="F44" t="n">
-        <v>3.870948705619461e-12</v>
+        <v>-8.586086642094387e-12</v>
       </c>
       <c r="G44" t="n">
-        <v>9.977721284439171e-10</v>
+        <v>1.619959896003524e-11</v>
       </c>
       <c r="H44" t="n">
-        <v>8.606310800151748e-12</v>
+        <v>1.860346464922034e-12</v>
       </c>
       <c r="I44" t="n">
-        <v>7.005960162970715e-11</v>
+        <v>-3.97965023107259e-12</v>
       </c>
     </row>
     <row r="45">
@@ -2630,22 +2630,22 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>-1.821866224591861e-11</v>
+        <v>-8.150199332800683e-12</v>
       </c>
       <c r="E45" t="n">
         <v/>
       </c>
       <c r="F45" t="n">
-        <v>-3.629508073158747e-12</v>
+        <v>-9.353260892370366e-12</v>
       </c>
       <c r="G45" t="n">
-        <v>4.72202908776816e-11</v>
+        <v>-4.368612861482046e-12</v>
       </c>
       <c r="H45" t="n">
-        <v>5.301759799886398e-11</v>
+        <v>9.093868723887889e-12</v>
       </c>
       <c r="I45" t="n">
-        <v>4.346688832748383e-11</v>
+        <v>-3.230300270077418e-12</v>
       </c>
     </row>
     <row r="46">
@@ -2665,22 +2665,22 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>-2.040285926682139e-11</v>
+        <v>-7.487723172956772e-12</v>
       </c>
       <c r="E46" t="n">
         <v/>
       </c>
       <c r="F46" t="n">
-        <v>-6.950427162500832e-12</v>
+        <v>-7.998801890393465e-12</v>
       </c>
       <c r="G46" t="n">
-        <v>1.421024558749814e-10</v>
+        <v>-5.650656860476095e-12</v>
       </c>
       <c r="H46" t="n">
-        <v>-7.185431264093062e-12</v>
+        <v>-2.594486463642038e-12</v>
       </c>
       <c r="I46" t="n">
-        <v>1.611811770102112e-10</v>
+        <v>7.472855679831887e-13</v>
       </c>
     </row>
     <row r="47">
@@ -2700,22 +2700,22 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-1.732940148527849e-11</v>
+        <v>-3.937640027149871e-12</v>
       </c>
       <c r="E47" t="n">
         <v/>
       </c>
       <c r="F47" t="n">
-        <v>-2.631811866142333e-12</v>
+        <v>-8.840253242457342e-12</v>
       </c>
       <c r="G47" t="n">
-        <v>3.387235571712831e-11</v>
+        <v>-7.513727750897413e-12</v>
       </c>
       <c r="H47" t="n">
-        <v>5.104648959822795e-12</v>
+        <v>1.797352747785981e-12</v>
       </c>
       <c r="I47" t="n">
-        <v>2.285654703143029e-11</v>
+        <v>-4.557946047153962e-12</v>
       </c>
     </row>
     <row r="48">
@@ -2735,22 +2735,22 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-1.715179980910297e-11</v>
+        <v>-9.553212824485616e-12</v>
       </c>
       <c r="E48" t="n">
         <v/>
       </c>
       <c r="F48" t="n">
-        <v>3.63900969895414e-12</v>
+        <v>-1.008525634840271e-11</v>
       </c>
       <c r="G48" t="n">
-        <v>8.787453917824833e-13</v>
+        <v>-8.614512882322293e-12</v>
       </c>
       <c r="H48" t="n">
-        <v>-3.976615461867086e-13</v>
+        <v>-2.678334157128324e-12</v>
       </c>
       <c r="I48" t="n">
-        <v>-3.265074757378019e-13</v>
+        <v>-4.297613322677601e-12</v>
       </c>
     </row>
     <row r="49">
@@ -2770,22 +2770,22 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-1.940639315774444e-11</v>
+        <v>-7.367501783533301e-12</v>
       </c>
       <c r="E49" t="n">
         <v/>
       </c>
       <c r="F49" t="n">
-        <v>2.030826737014188e-11</v>
+        <v>-6.144574463089558e-12</v>
       </c>
       <c r="G49" t="n">
-        <v>1.372420326836486e-10</v>
+        <v>-7.033770977454184e-12</v>
       </c>
       <c r="H49" t="n">
-        <v>3.632989051282229e-12</v>
+        <v>2.090830448441715e-12</v>
       </c>
       <c r="I49" t="n">
-        <v>2.187410681357104e-11</v>
+        <v>-5.687076338555642e-12</v>
       </c>
     </row>
     <row r="50">
@@ -2805,22 +2805,22 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-1.903575150069756e-11</v>
+        <v>-9.743747874764248e-12</v>
       </c>
       <c r="E50" t="n">
         <v/>
       </c>
       <c r="F50" t="n">
-        <v>-2.046097060817134e-12</v>
+        <v>-1.012214691737176e-11</v>
       </c>
       <c r="G50" t="n">
-        <v>3.433388335192275e-11</v>
+        <v>-8.80889085574071e-12</v>
       </c>
       <c r="H50" t="n">
-        <v>3.017139158457534e-11</v>
+        <v>3.621577432809258e-12</v>
       </c>
       <c r="I50" t="n">
-        <v>2.275754150033124e-11</v>
+        <v>-5.688261950966782e-12</v>
       </c>
     </row>
     <row r="51">
@@ -2840,22 +2840,22 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>-2.004418878055731e-11</v>
+        <v>-1.004983391557203e-11</v>
       </c>
       <c r="E51" t="n">
         <v/>
       </c>
       <c r="F51" t="n">
-        <v>-5.933800231422675e-13</v>
+        <v>-1.011089185025438e-11</v>
       </c>
       <c r="G51" t="n">
-        <v>1.070211266896005e-10</v>
+        <v>-9.365269458220394e-12</v>
       </c>
       <c r="H51" t="n">
-        <v>-3.522171225305779e-12</v>
+        <v>-3.532267454777617e-12</v>
       </c>
       <c r="I51" t="n">
-        <v>2.771593392952255e-10</v>
+        <v>3.206498424475474e-12</v>
       </c>
     </row>
     <row r="52">
@@ -2875,22 +2875,22 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>-1.741244688398596e-11</v>
+        <v>-3.027517995132379e-12</v>
       </c>
       <c r="E52" t="n">
         <v/>
       </c>
       <c r="F52" t="n">
-        <v>-8.755471517736687e-12</v>
+        <v>-8.790401199066002e-12</v>
       </c>
       <c r="G52" t="n">
-        <v>1.726045346733226e-11</v>
+        <v>-1.564126386790425e-12</v>
       </c>
       <c r="H52" t="n">
-        <v>-2.807929268624375e-12</v>
+        <v>-1.259346396390317e-12</v>
       </c>
       <c r="I52" t="n">
-        <v>1.978972992110858e-11</v>
+        <v>-2.911748493096952e-12</v>
       </c>
     </row>
     <row r="53">
@@ -2910,22 +2910,22 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>-1.360632167002799e-11</v>
+        <v>-2.34592240922979e-12</v>
       </c>
       <c r="E53" t="n">
         <v/>
       </c>
       <c r="F53" t="n">
-        <v>-3.778290611348033e-12</v>
+        <v>-4.100819250114763e-12</v>
       </c>
       <c r="G53" t="n">
-        <v>-1.538368811459094e-12</v>
+        <v>6.745547793997939e-12</v>
       </c>
       <c r="H53" t="n">
-        <v>-3.570553044150819e-12</v>
+        <v>1.104451046198211e-12</v>
       </c>
       <c r="I53" t="n">
-        <v>1.485698995186186e-12</v>
+        <v>9.042273390874016e-12</v>
       </c>
     </row>
     <row r="54">
@@ -2945,22 +2945,22 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-1.898486372567413e-11</v>
+        <v>-7.528225717918576e-12</v>
       </c>
       <c r="E54" t="n">
         <v/>
       </c>
       <c r="F54" t="n">
-        <v>2.561258474489215e-12</v>
+        <v>-6.998408118947596e-12</v>
       </c>
       <c r="G54" t="n">
-        <v>5.336461293239866e-11</v>
+        <v>-1.97642981842868e-13</v>
       </c>
       <c r="H54" t="n">
-        <v>-4.583987403151216e-13</v>
+        <v>-5.807475453134418e-13</v>
       </c>
       <c r="I54" t="n">
-        <v>2.655094079594038e-11</v>
+        <v>-2.735804847330973e-12</v>
       </c>
     </row>
     <row r="55">
@@ -2980,22 +2980,22 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-1.891526373815077e-11</v>
+        <v>-8.963249914223538e-12</v>
       </c>
       <c r="E55" t="n">
         <v/>
       </c>
       <c r="F55" t="n">
-        <v>-1.935313300762028e-12</v>
+        <v>-9.719194083772392e-12</v>
       </c>
       <c r="G55" t="n">
-        <v>7.251162133631937e-11</v>
+        <v>1.146576739991167e-11</v>
       </c>
       <c r="H55" t="n">
-        <v>5.706470657034893e-14</v>
+        <v>-2.629590979882315e-12</v>
       </c>
       <c r="I55" t="n">
-        <v>4.253575815275362e-11</v>
+        <v>-3.338344579032408e-12</v>
       </c>
     </row>
     <row r="56">
@@ -3015,22 +3015,22 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-2.052889620993699e-11</v>
+        <v>-8.704316783744903e-12</v>
       </c>
       <c r="E56" t="n">
         <v/>
       </c>
       <c r="F56" t="n">
-        <v>-9.632191497316397e-12</v>
+        <v>-8.696988621360351e-12</v>
       </c>
       <c r="G56" t="n">
-        <v>3.777950518014849e-11</v>
+        <v>-5.508441858122587e-12</v>
       </c>
       <c r="H56" t="n">
-        <v>-9.775982045031538e-12</v>
+        <v>-4.795228301859591e-12</v>
       </c>
       <c r="I56" t="n">
-        <v>7.18730571916394e-11</v>
+        <v>3.27230009112533e-12</v>
       </c>
     </row>
     <row r="57">
@@ -3050,22 +3050,22 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>-2.024970753269523e-11</v>
+        <v>-1.728725257074258e-12</v>
       </c>
       <c r="E57" t="n">
         <v/>
       </c>
       <c r="F57" t="n">
-        <v>-9.391743124150867e-12</v>
+        <v>-8.238446306808734e-12</v>
       </c>
       <c r="G57" t="n">
-        <v>3.191909702804344e-11</v>
+        <v>-3.86379050459698e-12</v>
       </c>
       <c r="H57" t="n">
-        <v>-7.717679952881946e-12</v>
+        <v>-2.659165758903037e-12</v>
       </c>
       <c r="I57" t="n">
-        <v>-5.471172675213415e-12</v>
+        <v>-1.110647305646199e-11</v>
       </c>
     </row>
     <row r="58">
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>-2.012981697768131e-11</v>
+        <v>2.946726463332756e-11</v>
       </c>
       <c r="E58" t="n">
         <v/>
       </c>
       <c r="F58" t="n">
-        <v>-7.072327922755138e-12</v>
+        <v>3.277298201817243e-11</v>
       </c>
       <c r="G58" t="n">
-        <v>5.948048840338254e-13</v>
+        <v>9.215501453274466e-12</v>
       </c>
       <c r="H58" t="n">
-        <v>-9.674362875395187e-12</v>
+        <v>1.119314505269241e-12</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.049497146438432e-11</v>
+        <v>-1.041160013339622e-11</v>
       </c>
     </row>
     <row r="59">
@@ -3120,22 +3120,22 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>-2.067775946473263e-11</v>
+        <v>-4.844495607688692e-12</v>
       </c>
       <c r="E59" t="n">
         <v/>
       </c>
       <c r="F59" t="n">
-        <v>-3.940510483897191e-12</v>
+        <v>-2.262193420379885e-12</v>
       </c>
       <c r="G59" t="n">
-        <v>9.861241237844133e-11</v>
+        <v>-1.508215960935025e-12</v>
       </c>
       <c r="H59" t="n">
-        <v>-8.626285200726418e-12</v>
+        <v>-1.862950904138786e-12</v>
       </c>
       <c r="I59" t="n">
-        <v>-5.988884407292063e-12</v>
+        <v>-1.126581503656471e-11</v>
       </c>
     </row>
     <row r="60">
@@ -3155,22 +3155,22 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>-2.011004010909518e-11</v>
+        <v>-8.832867600098365e-12</v>
       </c>
       <c r="E60" t="n">
         <v/>
       </c>
       <c r="F60" t="n">
-        <v>-5.491083957723916e-13</v>
+        <v>-9.577945169658518e-12</v>
       </c>
       <c r="G60" t="n">
-        <v>2.967920813869968e-10</v>
+        <v>4.715684899215489e-12</v>
       </c>
       <c r="H60" t="n">
-        <v>-3.332098346085417e-12</v>
+        <v>-3.113764355325342e-12</v>
       </c>
       <c r="I60" t="n">
-        <v>-9.476580861496635e-13</v>
+        <v>-1.085773904341874e-11</v>
       </c>
     </row>
     <row r="61">
@@ -3190,22 +3190,22 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>-2.05756235497734e-11</v>
+        <v>-7.493622197782639e-12</v>
       </c>
       <c r="E61" t="n">
         <v/>
       </c>
       <c r="F61" t="n">
-        <v>-9.637162242676949e-12</v>
+        <v>-7.970584122868228e-12</v>
       </c>
       <c r="G61" t="n">
-        <v>3.006198166301387e-11</v>
+        <v>-4.774352950304565e-12</v>
       </c>
       <c r="H61" t="n">
-        <v>-3.668286073844835e-12</v>
+        <v>4.740670304765253e-13</v>
       </c>
       <c r="I61" t="n">
-        <v>-5.804396732133344e-12</v>
+        <v>-1.11727278308762e-11</v>
       </c>
     </row>
     <row r="62">
@@ -3225,22 +3225,22 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>-9.832919697511444e-12</v>
+        <v>-9.408785469169345e-12</v>
       </c>
       <c r="E62" t="n">
-        <v>3.331841537264232e-13</v>
+        <v>-9.070737101815118e-12</v>
       </c>
       <c r="F62" t="n">
         <v/>
       </c>
       <c r="G62" t="n">
-        <v>2.014209744319861e-10</v>
+        <v>1.972891183642051e-12</v>
       </c>
       <c r="H62" t="n">
-        <v>2.953103098256373e-12</v>
+        <v>1.640224816930182e-12</v>
       </c>
       <c r="I62" t="n">
-        <v>4.673234387952061e-10</v>
+        <v>1.065642574437119e-10</v>
       </c>
     </row>
     <row r="63">
@@ -3260,22 +3260,22 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>-9.923485585281325e-12</v>
+        <v>-4.368392432582422e-12</v>
       </c>
       <c r="E63" t="n">
-        <v>-5.67872913049431e-12</v>
+        <v>-3.479896820631635e-12</v>
       </c>
       <c r="F63" t="n">
         <v/>
       </c>
       <c r="G63" t="n">
-        <v>-6.314183167237903e-13</v>
+        <v>1.055520370559705e-12</v>
       </c>
       <c r="H63" t="n">
-        <v>-7.012764635959664e-13</v>
+        <v>1.255730555275998e-12</v>
       </c>
       <c r="I63" t="n">
-        <v>5.950391966970896e-13</v>
+        <v>5.506979270108505e-13</v>
       </c>
     </row>
     <row r="64">
@@ -3295,22 +3295,22 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>-8.731616445548724e-12</v>
+        <v>-8.916612187532657e-12</v>
       </c>
       <c r="E64" t="n">
-        <v>-2.968910829921884e-12</v>
+        <v>-8.64159596011545e-12</v>
       </c>
       <c r="F64" t="n">
         <v/>
       </c>
       <c r="G64" t="n">
-        <v>2.331869001574307e-10</v>
+        <v>2.889745913267483e-11</v>
       </c>
       <c r="H64" t="n">
-        <v>5.865776147374326e-12</v>
+        <v>2.102447063728519e-12</v>
       </c>
       <c r="I64" t="n">
-        <v>6.064027571245704e-10</v>
+        <v>9.678329695929546e-11</v>
       </c>
     </row>
     <row r="65">
@@ -3330,22 +3330,22 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>-1.185334956606791e-11</v>
+        <v>-9.125828170571485e-12</v>
       </c>
       <c r="E65" t="n">
-        <v>-8.935684292644143e-12</v>
+        <v>-8.903489510084835e-12</v>
       </c>
       <c r="F65" t="n">
         <v/>
       </c>
       <c r="G65" t="n">
-        <v>8.712349185405685e-11</v>
+        <v>3.542672800870787e-12</v>
       </c>
       <c r="H65" t="n">
-        <v>1.709443244392435e-11</v>
+        <v>1.021169140980958e-11</v>
       </c>
       <c r="I65" t="n">
-        <v>3.43376534286808e-10</v>
+        <v>9.349658331654846e-11</v>
       </c>
     </row>
     <row r="66">
@@ -3365,22 +3365,22 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>-1.315378490740854e-11</v>
+        <v>-9.181914666714512e-12</v>
       </c>
       <c r="E66" t="n">
-        <v>-9.803325608881655e-12</v>
+        <v>-8.651203410252004e-12</v>
       </c>
       <c r="F66" t="n">
         <v/>
       </c>
       <c r="G66" t="n">
-        <v>1.735714221757273e-10</v>
+        <v>-3.141066045051867e-12</v>
       </c>
       <c r="H66" t="n">
-        <v>-8.174646982334858e-12</v>
+        <v>-3.547764032642585e-12</v>
       </c>
       <c r="I66" t="n">
-        <v>8.055328183460255e-10</v>
+        <v>5.910524148899551e-10</v>
       </c>
     </row>
     <row r="67">
@@ -3400,22 +3400,22 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>4.171153112926063e-11</v>
+        <v>-6.325688436464735e-12</v>
       </c>
       <c r="E67" t="n">
-        <v>-5.911709162483406e-12</v>
+        <v>-9.22896809559395e-12</v>
       </c>
       <c r="F67" t="n">
         <v/>
       </c>
       <c r="G67" t="n">
-        <v>1.53338034820275e-10</v>
+        <v>4.56823095742037e-12</v>
       </c>
       <c r="H67" t="n">
-        <v>6.27594995347649e-12</v>
+        <v>9.85486937948476e-13</v>
       </c>
       <c r="I67" t="n">
-        <v>5.443515214060961e-10</v>
+        <v>7.90698222174657e-11</v>
       </c>
     </row>
     <row r="68">
@@ -3435,22 +3435,22 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2.432486155416121e-11</v>
+        <v>-6.48684131869521e-12</v>
       </c>
       <c r="E68" t="n">
-        <v>1.236798117424034e-11</v>
+        <v>-7.130287893411611e-12</v>
       </c>
       <c r="F68" t="n">
         <v/>
       </c>
       <c r="G68" t="n">
-        <v>1.918535679179958e-12</v>
+        <v>2.845953514902505e-12</v>
       </c>
       <c r="H68" t="n">
-        <v>1.318176596802744e-11</v>
+        <v>8.722449547392165e-13</v>
       </c>
       <c r="I68" t="n">
-        <v>1.586072173485416e-12</v>
+        <v>2.155981432442095e-13</v>
       </c>
     </row>
     <row r="69">
@@ -3470,22 +3470,22 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>5.796301823910705e-12</v>
+        <v>-1.016479816700016e-11</v>
       </c>
       <c r="E69" t="n">
-        <v>2.454106425706798e-12</v>
+        <v>-1.036023980655818e-11</v>
       </c>
       <c r="F69" t="n">
         <v/>
       </c>
       <c r="G69" t="n">
-        <v>5.030241114738261e-09</v>
+        <v>1.311955953692874e-11</v>
       </c>
       <c r="H69" t="n">
-        <v>5.675088980447437e-12</v>
+        <v>-2.285297861058264e-12</v>
       </c>
       <c r="I69" t="n">
-        <v>1.279323666381533e-09</v>
+        <v>6.172041904039852e-11</v>
       </c>
     </row>
     <row r="70">
@@ -3505,22 +3505,22 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>-2.319217649621378e-12</v>
+        <v>-6.10149007759322e-12</v>
       </c>
       <c r="E70" t="n">
-        <v>-4.8471903214192e-12</v>
+        <v>-6.529437840481954e-12</v>
       </c>
       <c r="F70" t="n">
         <v/>
       </c>
       <c r="G70" t="n">
-        <v>1.654752210551478e-10</v>
+        <v>7.930761131950438e-12</v>
       </c>
       <c r="H70" t="n">
-        <v>3.239402626900391e-11</v>
+        <v>1.621564081804435e-11</v>
       </c>
       <c r="I70" t="n">
-        <v>5.722221428994648e-10</v>
+        <v>9.629565108989083e-11</v>
       </c>
     </row>
     <row r="71">
@@ -3540,22 +3540,22 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>-8.5163255093027e-12</v>
+        <v>2.614487505478487e-12</v>
       </c>
       <c r="E71" t="n">
-        <v>-8.214079797489812e-12</v>
+        <v>4.768432823188081e-12</v>
       </c>
       <c r="F71" t="n">
         <v/>
       </c>
       <c r="G71" t="n">
-        <v>5.920169027911063e-10</v>
+        <v>-1.277552003735417e-12</v>
       </c>
       <c r="H71" t="n">
-        <v>-8.550076250330172e-12</v>
+        <v>-1.608507613109465e-12</v>
       </c>
       <c r="I71" t="n">
-        <v>1.996131773273122e-09</v>
+        <v>1.908302033620437e-09</v>
       </c>
     </row>
     <row r="72">
@@ -3575,22 +3575,22 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>7.377200361230742e-10</v>
+        <v>-4.385009436503646e-12</v>
       </c>
       <c r="E72" t="n">
-        <v>-2.047921913262664e-13</v>
+        <v>-3.214519985024296e-12</v>
       </c>
       <c r="F72" t="n">
         <v/>
       </c>
       <c r="G72" t="n">
-        <v>1.656060969715372e-10</v>
+        <v>2.736439777843704e-11</v>
       </c>
       <c r="H72" t="n">
-        <v>1.568947135030311e-11</v>
+        <v>1.291407767518251e-11</v>
       </c>
       <c r="I72" t="n">
-        <v>6.735910468890297e-10</v>
+        <v>5.795527850541729e-10</v>
       </c>
     </row>
     <row r="73">
@@ -3610,22 +3610,22 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>8.751112804823273e-11</v>
+        <v>-5.605831291563514e-12</v>
       </c>
       <c r="E73" t="n">
-        <v>4.390769746705679e-10</v>
+        <v>-6.536922020489851e-12</v>
       </c>
       <c r="F73" t="n">
         <v/>
       </c>
       <c r="G73" t="n">
-        <v>4.093883459785454e-09</v>
+        <v>2.528150568609302e-11</v>
       </c>
       <c r="H73" t="n">
-        <v>5.462010211436343e-11</v>
+        <v>1.408350182103699e-11</v>
       </c>
       <c r="I73" t="n">
-        <v>2.614933685261347e-09</v>
+        <v>1.761443134877485e-09</v>
       </c>
     </row>
     <row r="74">
@@ -3645,22 +3645,22 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>2.952588098251313e-11</v>
+        <v>5.280039003590173e-12</v>
       </c>
       <c r="E74" t="n">
-        <v>2.090126274790815e-11</v>
+        <v>1.658900514445116e-12</v>
       </c>
       <c r="F74" t="n">
         <v/>
       </c>
       <c r="G74" t="n">
-        <v>0.1642889280724779</v>
+        <v>-1.073196316589763e-11</v>
       </c>
       <c r="H74" t="n">
-        <v>1.909516033495786e-11</v>
+        <v>1.326996166140504e-11</v>
       </c>
       <c r="I74" t="n">
-        <v>2.579438046625887e-09</v>
+        <v>6.482353142961035e-10</v>
       </c>
     </row>
     <row r="75">
@@ -3680,22 +3680,22 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>9.110563381731232e-12</v>
+        <v>1.228485392439802e-12</v>
       </c>
       <c r="E75" t="n">
-        <v>3.773686245888334e-12</v>
+        <v>-1.608667945347284e-12</v>
       </c>
       <c r="F75" t="n">
         <v/>
       </c>
       <c r="G75" t="n">
-        <v>1.811510644239889e-10</v>
+        <v>3.601317736127342e-11</v>
       </c>
       <c r="H75" t="n">
-        <v>1.619645544440863e-10</v>
+        <v>-1.674917111768755e-12</v>
       </c>
       <c r="I75" t="n">
-        <v>7.785716724756581e-10</v>
+        <v>9.463350493162063e-10</v>
       </c>
     </row>
     <row r="76">
@@ -3715,22 +3715,22 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>-3.023782702733629e-12</v>
+        <v>1.68436867369695e-11</v>
       </c>
       <c r="E76" t="n">
-        <v>-2.514062607665928e-12</v>
+        <v>1.46748707795425e-11</v>
       </c>
       <c r="F76" t="n">
         <v/>
       </c>
       <c r="G76" t="n">
-        <v>1.083093215289345e-09</v>
+        <v>3.781194552766498e-12</v>
       </c>
       <c r="H76" t="n">
-        <v>-5.642789649249366e-12</v>
+        <v>1.737497165772157e-12</v>
       </c>
       <c r="I76" t="n">
-        <v>0.2973395027496102</v>
+        <v>7.554457810942575e-13</v>
       </c>
     </row>
     <row r="77">
@@ -3750,22 +3750,22 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>2.793385137883039e-11</v>
+        <v>-5.517858309603315e-12</v>
       </c>
       <c r="E77" t="n">
-        <v>-2.653134102656471e-12</v>
+        <v>-8.730000046845511e-12</v>
       </c>
       <c r="F77" t="n">
         <v/>
       </c>
       <c r="G77" t="n">
-        <v>1.442493465070701e-10</v>
+        <v>-2.489976236208991e-12</v>
       </c>
       <c r="H77" t="n">
-        <v>5.10386009502002e-12</v>
+        <v>2.693859628219133e-12</v>
       </c>
       <c r="I77" t="n">
-        <v>4.544384505422908e-10</v>
+        <v>9.959926822181975e-11</v>
       </c>
     </row>
     <row r="78">
@@ -3785,22 +3785,22 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>-1.221103963707667e-12</v>
+        <v>-1.03209917983152e-11</v>
       </c>
       <c r="E78" t="n">
-        <v>1.860835460886081e-11</v>
+        <v>-1.036044950438105e-11</v>
       </c>
       <c r="F78" t="n">
         <v/>
       </c>
       <c r="G78" t="n">
-        <v>7.195714365453871e-10</v>
+        <v>-5.131382921360361e-12</v>
       </c>
       <c r="H78" t="n">
-        <v>1.684856511414653e-12</v>
+        <v>-1.615666887519306e-12</v>
       </c>
       <c r="I78" t="n">
-        <v>5.930429311126752e-10</v>
+        <v>8.042808668786063e-11</v>
       </c>
     </row>
     <row r="79">
@@ -3820,22 +3820,22 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>3.7383096096251e-13</v>
+        <v>2.066633412003892e-12</v>
       </c>
       <c r="E79" t="n">
-        <v>4.554023496772576e-12</v>
+        <v>1.636172935393892e-12</v>
       </c>
       <c r="F79" t="n">
         <v/>
       </c>
       <c r="G79" t="n">
-        <v>9.380092563574003e-13</v>
+        <v>-3.898005280833131e-12</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.345217379143131e-13</v>
+        <v>2.170413556824124e-12</v>
       </c>
       <c r="I79" t="n">
-        <v>8.201529473703902e-13</v>
+        <v>6.850838914368913e-13</v>
       </c>
     </row>
     <row r="80">
@@ -3855,22 +3855,22 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>-4.60132681505562e-12</v>
+        <v>-9.83000712111249e-12</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.247792555745306e-12</v>
+        <v>-9.990446395273703e-12</v>
       </c>
       <c r="F80" t="n">
         <v/>
       </c>
       <c r="G80" t="n">
-        <v>1.456966167391813e-10</v>
+        <v>-3.700339465502053e-12</v>
       </c>
       <c r="H80" t="n">
-        <v>2.461506600474495e-11</v>
+        <v>6.509567428245468e-12</v>
       </c>
       <c r="I80" t="n">
-        <v>4.519730593615772e-10</v>
+        <v>8.165810354593408e-11</v>
       </c>
     </row>
     <row r="81">
@@ -3890,22 +3890,22 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>-5.193045643816112e-12</v>
+        <v>-9.797188180638797e-12</v>
       </c>
       <c r="E81" t="n">
-        <v>-8.243464498468357e-13</v>
+        <v>-9.77255795938182e-12</v>
       </c>
       <c r="F81" t="n">
         <v/>
       </c>
       <c r="G81" t="n">
-        <v>5.97690397843443e-10</v>
+        <v>-5.857749691038355e-12</v>
       </c>
       <c r="H81" t="n">
-        <v>-4.410332203596523e-12</v>
+        <v>-3.258973164415831e-12</v>
       </c>
       <c r="I81" t="n">
-        <v>3.903601882722328e-09</v>
+        <v>6.578123069997215e-10</v>
       </c>
     </row>
     <row r="82">
@@ -3925,22 +3925,22 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>3.26046806430306e-12</v>
+        <v>-5.938316014179939e-12</v>
       </c>
       <c r="E82" t="n">
-        <v>-8.800270514941141e-12</v>
+        <v>-8.922505345230617e-12</v>
       </c>
       <c r="F82" t="n">
         <v/>
       </c>
       <c r="G82" t="n">
-        <v>8.742821693874261e-11</v>
+        <v>5.963866780390914e-12</v>
       </c>
       <c r="H82" t="n">
-        <v>-1.926608282042029e-12</v>
+        <v>-1.410854786301849e-12</v>
       </c>
       <c r="I82" t="n">
-        <v>3.571773680173611e-10</v>
+        <v>1.045248011845105e-10</v>
       </c>
     </row>
     <row r="83">
@@ -3960,22 +3960,22 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>-5.280030977914827e-12</v>
+        <v>-6.006140174840043e-12</v>
       </c>
       <c r="E83" t="n">
-        <v>2.033957799052043e-12</v>
+        <v>-5.82535525857515e-12</v>
       </c>
       <c r="F83" t="n">
         <v/>
       </c>
       <c r="G83" t="n">
-        <v>2.104152723176256e-10</v>
+        <v>7.526274484087412e-12</v>
       </c>
       <c r="H83" t="n">
-        <v>-9.082833798447927e-13</v>
+        <v>1.041310899323861e-12</v>
       </c>
       <c r="I83" t="n">
-        <v>5.031091957741871e-10</v>
+        <v>1.643445699400753e-10</v>
       </c>
     </row>
     <row r="84">
@@ -3995,22 +3995,22 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>-4.355625512158293e-12</v>
+        <v>-1.71577170508039e-12</v>
       </c>
       <c r="E84" t="n">
-        <v>-3.414057825823867e-12</v>
+        <v>-2.258261174253236e-12</v>
       </c>
       <c r="F84" t="n">
         <v/>
       </c>
       <c r="G84" t="n">
-        <v>-3.150137017578083e-13</v>
+        <v>4.155919191532962e-12</v>
       </c>
       <c r="H84" t="n">
-        <v>-2.197093527468859e-12</v>
+        <v>-9.376710319524367e-13</v>
       </c>
       <c r="I84" t="n">
-        <v>8.455684488021472e-13</v>
+        <v>9.119561311335255e-13</v>
       </c>
     </row>
     <row r="85">
@@ -4030,22 +4030,22 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>-3.724539002223453e-12</v>
+        <v>-9.777230434400238e-12</v>
       </c>
       <c r="E85" t="n">
-        <v>-2.119516301227907e-12</v>
+        <v>-9.916597406888169e-12</v>
       </c>
       <c r="F85" t="n">
         <v/>
       </c>
       <c r="G85" t="n">
-        <v>2.460123592872045e-10</v>
+        <v>2.534746016008125e-11</v>
       </c>
       <c r="H85" t="n">
-        <v>4.791550552121084e-13</v>
+        <v>-2.840948811704343e-12</v>
       </c>
       <c r="I85" t="n">
-        <v>6.490099282678452e-10</v>
+        <v>8.832801965071906e-11</v>
       </c>
     </row>
     <row r="86">
@@ -4065,22 +4065,22 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>-1.13268069370985e-11</v>
+        <v>-8.578822073806106e-12</v>
       </c>
       <c r="E86" t="n">
-        <v>-9.759440907890533e-12</v>
+        <v>-8.397016696794851e-12</v>
       </c>
       <c r="F86" t="n">
         <v/>
       </c>
       <c r="G86" t="n">
-        <v>1.742000916364692e-10</v>
+        <v>-2.644010735541679e-12</v>
       </c>
       <c r="H86" t="n">
-        <v>-9.926142895878708e-12</v>
+        <v>-5.327766442525556e-12</v>
       </c>
       <c r="I86" t="n">
-        <v>8.243225931984795e-10</v>
+        <v>8.849673650526488e-10</v>
       </c>
     </row>
     <row r="87">
@@ -4100,22 +4100,22 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>-3.563808407271924e-12</v>
+        <v>-5.473332859792194e-12</v>
       </c>
       <c r="E87" t="n">
-        <v>-9.474563849502317e-12</v>
+        <v>-8.650929329837253e-12</v>
       </c>
       <c r="F87" t="n">
         <v/>
       </c>
       <c r="G87" t="n">
-        <v>1.440496750647754e-10</v>
+        <v>-3.079041837387995e-12</v>
       </c>
       <c r="H87" t="n">
-        <v>-8.105284872749388e-12</v>
+        <v>-3.520239642118267e-12</v>
       </c>
       <c r="I87" t="n">
-        <v>1.936722008946905e-10</v>
+        <v>2.570057385848624e-11</v>
       </c>
     </row>
     <row r="88">
@@ -4135,22 +4135,22 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>-1.017992206064587e-11</v>
+        <v>4.877418239255797e-12</v>
       </c>
       <c r="E88" t="n">
-        <v>-3.475338458624481e-12</v>
+        <v>8.28664059316076e-12</v>
       </c>
       <c r="F88" t="n">
         <v/>
       </c>
       <c r="G88" t="n">
-        <v>7.17698666003431e-10</v>
+        <v>-2.462335294825126e-12</v>
       </c>
       <c r="H88" t="n">
-        <v>-9.373023423677681e-12</v>
+        <v>-9.698034134001419e-13</v>
       </c>
       <c r="I88" t="n">
-        <v>2.152059251902602e-10</v>
+        <v>3.282347516240752e-11</v>
       </c>
     </row>
     <row r="89">
@@ -4170,22 +4170,22 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>-1.019996511306999e-11</v>
+        <v>1.050441457953119e-11</v>
       </c>
       <c r="E89" t="n">
-        <v>-7.583267037849307e-12</v>
+        <v>1.123225677501817e-11</v>
       </c>
       <c r="F89" t="n">
         <v/>
       </c>
       <c r="G89" t="n">
-        <v>6.900781992811015e-13</v>
+        <v>-4.159404025510073e-12</v>
       </c>
       <c r="H89" t="n">
-        <v>-1.002183991137386e-11</v>
+        <v>-3.36080647729436e-12</v>
       </c>
       <c r="I89" t="n">
-        <v>-9.685953052326753e-13</v>
+        <v>-2.363297556463798e-12</v>
       </c>
     </row>
     <row r="90">
@@ -4205,22 +4205,22 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>-5.573821441547803e-12</v>
+        <v>-9.82081021280168e-12</v>
       </c>
       <c r="E90" t="n">
-        <v>-8.298370453454962e-13</v>
+        <v>-9.957748311884848e-12</v>
       </c>
       <c r="F90" t="n">
         <v/>
       </c>
       <c r="G90" t="n">
-        <v>1.619839078062647e-09</v>
+        <v>3.998359183322618e-12</v>
       </c>
       <c r="H90" t="n">
-        <v>-4.256251848419649e-12</v>
+        <v>-3.746961490704635e-12</v>
       </c>
       <c r="I90" t="n">
-        <v>2.897020782864481e-10</v>
+        <v>2.511579940012633e-11</v>
       </c>
     </row>
     <row r="91">
@@ -4240,22 +4240,22 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>-1.175051793986378e-11</v>
+        <v>-8.187440425192965e-12</v>
       </c>
       <c r="E91" t="n">
-        <v>-9.787316132823562e-12</v>
+        <v>-8.287694190135871e-12</v>
       </c>
       <c r="F91" t="n">
         <v/>
       </c>
       <c r="G91" t="n">
-        <v>1.382945324061069e-10</v>
+        <v>-3.436761948274495e-12</v>
       </c>
       <c r="H91" t="n">
-        <v>-5.00623293577948e-12</v>
+        <v>-4.077030629950829e-13</v>
       </c>
       <c r="I91" t="n">
-        <v>1.883212446830619e-10</v>
+        <v>2.529132469072868e-11</v>
       </c>
     </row>
     <row r="92">
@@ -4275,22 +4275,22 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>-3.073199599465757e-12</v>
+        <v>-2.8975892742096e-12</v>
       </c>
       <c r="E92" t="n">
-        <v>6.623576102585932e-11</v>
+        <v>8.441450126251004e-12</v>
       </c>
       <c r="F92" t="n">
-        <v>2.138210364218099e-10</v>
+        <v>4.307707615418214e-12</v>
       </c>
       <c r="G92" t="n">
         <v/>
       </c>
       <c r="H92" t="n">
-        <v>8.654484373168335e-12</v>
+        <v>5.943563489157844e-12</v>
       </c>
       <c r="I92" t="n">
-        <v>2.623430707781532e-10</v>
+        <v>5.735279650001962e-12</v>
       </c>
     </row>
     <row r="93">
@@ -4310,22 +4310,22 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>-3.797380014952477e-12</v>
+        <v>-3.178550469041701e-12</v>
       </c>
       <c r="E93" t="n">
-        <v>5.536211852747019e-11</v>
+        <v>-4.186551400306686e-12</v>
       </c>
       <c r="F93" t="n">
-        <v>2.242588086229916e-10</v>
+        <v>1.984264924573402e-11</v>
       </c>
       <c r="G93" t="n">
         <v/>
       </c>
       <c r="H93" t="n">
-        <v>7.158217798231398e-12</v>
+        <v>4.916244586009863e-12</v>
       </c>
       <c r="I93" t="n">
-        <v>2.680937818221881e-10</v>
+        <v>4.104463510856189e-12</v>
       </c>
     </row>
     <row r="94">
@@ -4345,22 +4345,22 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>-3.445335482130919e-12</v>
+        <v>1.484972387090625e-14</v>
       </c>
       <c r="E94" t="n">
-        <v>-2.156805906745407e-12</v>
+        <v>5.370664509684756e-12</v>
       </c>
       <c r="F94" t="n">
-        <v>-6.363249921000177e-13</v>
+        <v>4.713649046071252e-12</v>
       </c>
       <c r="G94" t="n">
         <v/>
       </c>
       <c r="H94" t="n">
-        <v>6.587882847450644e-12</v>
+        <v>4.381625753612211e-12</v>
       </c>
       <c r="I94" t="n">
-        <v>-3.608664882131516e-13</v>
+        <v>4.447205614963386e-12</v>
       </c>
     </row>
     <row r="95">
@@ -4380,22 +4380,22 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>-4.722253520799799e-12</v>
+        <v>-2.294572000058611e-12</v>
       </c>
       <c r="E95" t="n">
-        <v>1.694467953044648e-11</v>
+        <v>-1.817940630268232e-12</v>
       </c>
       <c r="F95" t="n">
-        <v>8.651050771195837e-11</v>
+        <v>5.600323439250676e-12</v>
       </c>
       <c r="G95" t="n">
         <v/>
       </c>
       <c r="H95" t="n">
-        <v>2.938640219294784e-11</v>
+        <v>2.012803163566734e-11</v>
       </c>
       <c r="I95" t="n">
-        <v>1.35482053310248e-10</v>
+        <v>6.516232877134711e-12</v>
       </c>
     </row>
     <row r="96">
@@ -4415,22 +4415,22 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>-1.091153111600976e-11</v>
+        <v>-5.136116842081906e-12</v>
       </c>
       <c r="E96" t="n">
-        <v>3.547853775410561e-11</v>
+        <v>-4.10753824662486e-12</v>
       </c>
       <c r="F96" t="n">
-        <v>1.653448558840059e-10</v>
+        <v>-3.070219353531572e-12</v>
       </c>
       <c r="G96" t="n">
         <v/>
       </c>
       <c r="H96" t="n">
-        <v>-8.233362164741135e-12</v>
+        <v>-5.654736940469281e-12</v>
       </c>
       <c r="I96" t="n">
-        <v>3.833494163770937e-10</v>
+        <v>3.205705593874495e-11</v>
       </c>
     </row>
     <row r="97">
@@ -4450,22 +4450,22 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>2.308560527717044e-11</v>
+        <v>6.450134200985306e-12</v>
       </c>
       <c r="E97" t="n">
-        <v>3.227343431901134e-11</v>
+        <v>-7.95117417750144e-12</v>
       </c>
       <c r="F97" t="n">
-        <v>1.440249298640483e-10</v>
+        <v>1.778479077414061e-12</v>
       </c>
       <c r="G97" t="n">
         <v/>
       </c>
       <c r="H97" t="n">
-        <v>6.263753168104973e-12</v>
+        <v>4.302608377149528e-12</v>
       </c>
       <c r="I97" t="n">
-        <v>2.301208654002881e-10</v>
+        <v>2.823574547084874e-12</v>
       </c>
     </row>
     <row r="98">
@@ -4485,22 +4485,22 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1.959836271376108e-11</v>
+        <v>-2.23674866579948e-12</v>
       </c>
       <c r="E98" t="n">
-        <v>2.698275901636271e-10</v>
+        <v>-8.497145711193901e-12</v>
       </c>
       <c r="F98" t="n">
-        <v>5.56186657866659e-09</v>
+        <v>1.813643065411518e-11</v>
       </c>
       <c r="G98" t="n">
         <v/>
       </c>
       <c r="H98" t="n">
-        <v>1.730859389404578e-11</v>
+        <v>1.187930153182219e-11</v>
       </c>
       <c r="I98" t="n">
-        <v>2.055011400512402e-09</v>
+        <v>5.124212022422026e-12</v>
       </c>
     </row>
     <row r="99">
@@ -4520,22 +4520,22 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1.915370855570789e-12</v>
+        <v>-1.980483219469508e-12</v>
       </c>
       <c r="E99" t="n">
-        <v>1.607525775563123e-12</v>
+        <v>-7.158530600725824e-12</v>
       </c>
       <c r="F99" t="n">
-        <v>1.250697710725332e-12</v>
+        <v>-1.051062773317768e-12</v>
       </c>
       <c r="G99" t="n">
         <v/>
       </c>
       <c r="H99" t="n">
-        <v>-4.205588067026997e-13</v>
+        <v>-3.612630559112978e-13</v>
       </c>
       <c r="I99" t="n">
-        <v>9.49928077129064e-13</v>
+        <v>-9.426722580051249e-13</v>
       </c>
     </row>
     <row r="100">
@@ -4555,22 +4555,22 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>3.849778806541902e-12</v>
+        <v>3.751814953570147e-12</v>
       </c>
       <c r="E100" t="n">
-        <v>3.563408103262252e-11</v>
+        <v>-5.52723715211617e-12</v>
       </c>
       <c r="F100" t="n">
-        <v>1.551792139218063e-10</v>
+        <v>6.755918668091753e-12</v>
       </c>
       <c r="G100" t="n">
         <v/>
       </c>
       <c r="H100" t="n">
-        <v>2.289353140192013e-11</v>
+        <v>1.568052861882171e-11</v>
       </c>
       <c r="I100" t="n">
-        <v>2.46139501214949e-10</v>
+        <v>6.277698497204487e-12</v>
       </c>
     </row>
     <row r="101">
@@ -4590,22 +4590,22 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>-9.501999315393915e-12</v>
+        <v>7.831574987174018e-13</v>
       </c>
       <c r="E101" t="n">
-        <v>7.3673966652653e-11</v>
+        <v>-5.059304687939396e-12</v>
       </c>
       <c r="F101" t="n">
-        <v>4.565187622313816e-10</v>
+        <v>-2.537905464662319e-12</v>
       </c>
       <c r="G101" t="n">
         <v/>
       </c>
       <c r="H101" t="n">
-        <v>-1.042340145796654e-11</v>
+        <v>-7.15659943393612e-12</v>
       </c>
       <c r="I101" t="n">
-        <v>4.590615968672479e-09</v>
+        <v>2.280199789927768e-11</v>
       </c>
     </row>
     <row r="102">
@@ -4625,22 +4625,22 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>2.092558991344725e-11</v>
+        <v>8.391321874867424e-12</v>
       </c>
       <c r="E102" t="n">
-        <v>3.775450660034247e-11</v>
+        <v>-3.531977872057132e-12</v>
       </c>
       <c r="F102" t="n">
-        <v>1.415506851931195e-10</v>
+        <v>-2.935770761021088e-12</v>
       </c>
       <c r="G102" t="n">
         <v/>
       </c>
       <c r="H102" t="n">
-        <v>4.73574672721983e-12</v>
+        <v>3.253932621926405e-12</v>
       </c>
       <c r="I102" t="n">
-        <v>2.261332354847626e-10</v>
+        <v>3.386515843733349e-12</v>
       </c>
     </row>
     <row r="103">
@@ -4660,22 +4660,22 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>2.059703866143622e-11</v>
+        <v>-1.075827730400414e-12</v>
       </c>
       <c r="E103" t="n">
-        <v>1.200294151168351e-09</v>
+        <v>5.81880726766571e-12</v>
       </c>
       <c r="F103" t="n">
-        <v>1.402183783951876e-09</v>
+        <v>-1.869470570453797e-12</v>
       </c>
       <c r="G103" t="n">
         <v/>
       </c>
       <c r="H103" t="n">
-        <v>1.678111029705459e-11</v>
+        <v>1.151863508009721e-11</v>
       </c>
       <c r="I103" t="n">
-        <v>1.257517798985538e-09</v>
+        <v>7.915555446071419e-12</v>
       </c>
     </row>
     <row r="104">
@@ -4695,22 +4695,22 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>3.013295199224526e-12</v>
+        <v>4.574940073373813e-12</v>
       </c>
       <c r="E104" t="n">
-        <v>2.876178914388342e-12</v>
+        <v>8.232096440635198e-12</v>
       </c>
       <c r="F104" t="n">
-        <v>1.037516691904334e-12</v>
+        <v>-2.711926103864828e-12</v>
       </c>
       <c r="G104" t="n">
         <v/>
       </c>
       <c r="H104" t="n">
-        <v>3.128550190514759e-13</v>
+        <v>1.37506741970004e-13</v>
       </c>
       <c r="I104" t="n">
-        <v>8.703591567271764e-13</v>
+        <v>1.944793275409265e-12</v>
       </c>
     </row>
     <row r="105">
@@ -4730,22 +4730,22 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>6.046289245559822e-12</v>
+        <v>1.599828143104954e-12</v>
       </c>
       <c r="E105" t="n">
-        <v>4.25307463020261e-11</v>
+        <v>-3.493422849519617e-13</v>
       </c>
       <c r="F105" t="n">
-        <v>1.519759292264591e-10</v>
+        <v>-1.230033194968024e-12</v>
       </c>
       <c r="G105" t="n">
         <v/>
       </c>
       <c r="H105" t="n">
-        <v>2.822833920802895e-11</v>
+        <v>1.932995833061318e-11</v>
       </c>
       <c r="I105" t="n">
-        <v>2.454568249758778e-10</v>
+        <v>7.063014332688233e-12</v>
       </c>
     </row>
     <row r="106">
@@ -4765,22 +4765,22 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>-8.920179566191439e-12</v>
+        <v>-2.273601606190606e-12</v>
       </c>
       <c r="E106" t="n">
-        <v>1.082863112700618e-10</v>
+        <v>-1.664880330833171e-12</v>
       </c>
       <c r="F106" t="n">
-        <v>5.273009363733855e-10</v>
+        <v>-6.076492506945438e-12</v>
       </c>
       <c r="G106" t="n">
         <v/>
       </c>
       <c r="H106" t="n">
-        <v>-1.01776703204241e-11</v>
+        <v>-6.98842481924036e-12</v>
       </c>
       <c r="I106" t="n">
-        <v>0.0004448385647781896</v>
+        <v>2.062985491243903e-11</v>
       </c>
     </row>
     <row r="107">
@@ -4800,22 +4800,22 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>4.259198893547682e-10</v>
+        <v>-5.605929530338149e-12</v>
       </c>
       <c r="E107" t="n">
-        <v>5.022211891265542e-11</v>
+        <v>2.672849438299642e-11</v>
       </c>
       <c r="F107" t="n">
-        <v>1.692784560586809e-10</v>
+        <v>3.26211151047537e-11</v>
       </c>
       <c r="G107" t="n">
         <v/>
       </c>
       <c r="H107" t="n">
-        <v>3.816535017016115e-11</v>
+        <v>2.605445332361732e-11</v>
       </c>
       <c r="I107" t="n">
-        <v>3.277000145922685e-10</v>
+        <v>4.983830628295425e-11</v>
       </c>
     </row>
     <row r="108">
@@ -4835,22 +4835,22 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>2.515676568686206e-11</v>
+        <v>4.741789428499246e-12</v>
       </c>
       <c r="E108" t="n">
-        <v>0.1497293201907243</v>
+        <v>1.949254737094283e-10</v>
       </c>
       <c r="F108" t="n">
-        <v>3.383130836045312e-09</v>
+        <v>1.410565102778751e-11</v>
       </c>
       <c r="G108" t="n">
         <v/>
       </c>
       <c r="H108" t="n">
-        <v>1.76941732248074e-11</v>
+        <v>1.208191977595119e-11</v>
       </c>
       <c r="I108" t="n">
-        <v>5.098625064963582e-09</v>
+        <v>2.154751090038051e-11</v>
       </c>
     </row>
     <row r="109">
@@ -4870,22 +4870,22 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>2.82504222033625e-11</v>
+        <v>1.94793800396099e-11</v>
       </c>
       <c r="E109" t="n">
-        <v>8.665931944841839e-10</v>
+        <v>3.17550658083199e-11</v>
       </c>
       <c r="F109" t="n">
-        <v>0.1625908450583093</v>
+        <v>-1.069636194623953e-11</v>
       </c>
       <c r="G109" t="n">
         <v/>
       </c>
       <c r="H109" t="n">
-        <v>2.086663401229553e-11</v>
+        <v>1.425356437857309e-11</v>
       </c>
       <c r="I109" t="n">
-        <v>0.0004448374628852944</v>
+        <v>3.372231549696416e-11</v>
       </c>
     </row>
     <row r="110">
@@ -4905,22 +4905,22 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>2.792911735825091e-11</v>
+        <v>1.034009668806523e-11</v>
       </c>
       <c r="E110" t="n">
-        <v>5.248516029006329e-11</v>
+        <v>1.907843938762915e-11</v>
       </c>
       <c r="F110" t="n">
-        <v>1.742826619744803e-10</v>
+        <v>2.766009032022266e-11</v>
       </c>
       <c r="G110" t="n">
         <v/>
       </c>
       <c r="H110" t="n">
-        <v>1.878615375974894e-10</v>
+        <v>1.253590213437897e-10</v>
       </c>
       <c r="I110" t="n">
-        <v>3.471205138066861e-10</v>
+        <v>4.314906599196239e-11</v>
       </c>
     </row>
     <row r="111">
@@ -4940,22 +4940,22 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>3.007481853151502e-12</v>
+        <v>3.261773616943753e-12</v>
       </c>
       <c r="E111" t="n">
-        <v>2.064473748262027e-10</v>
+        <v>1.119994630235885e-11</v>
       </c>
       <c r="F111" t="n">
-        <v>9.635988389273441e-10</v>
+        <v>5.594222325617197e-12</v>
       </c>
       <c r="G111" t="n">
         <v/>
       </c>
       <c r="H111" t="n">
-        <v>-3.686017312812156e-13</v>
+        <v>-2.77484624424374e-13</v>
       </c>
       <c r="I111" t="n">
-        <v>0.0008912225100016449</v>
+        <v>1.311131548058271e-12</v>
       </c>
     </row>
     <row r="112">
@@ -4975,22 +4975,22 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1.78251692684311e-11</v>
+        <v>8.699093096970614e-12</v>
       </c>
       <c r="E112" t="n">
-        <v>1.69245916579288e-11</v>
+        <v>-4.78324209645126e-12</v>
       </c>
       <c r="F112" t="n">
-        <v>8.626522534932763e-11</v>
+        <v>3.401735023430218e-12</v>
       </c>
       <c r="G112" t="n">
         <v/>
       </c>
       <c r="H112" t="n">
-        <v>2.39562183133773e-12</v>
+        <v>1.595256256559384e-12</v>
       </c>
       <c r="I112" t="n">
-        <v>1.365478573727958e-10</v>
+        <v>5.559016101358637e-12</v>
       </c>
     </row>
     <row r="113">
@@ -5010,22 +5010,22 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>5.205383957864947e-12</v>
+        <v>4.488001847062588e-12</v>
       </c>
       <c r="E113" t="n">
-        <v>7.040788427288382e-11</v>
+        <v>2.195110914471667e-11</v>
       </c>
       <c r="F113" t="n">
-        <v>2.23360709216099e-10</v>
+        <v>8.157832628185449e-12</v>
       </c>
       <c r="G113" t="n">
         <v/>
       </c>
       <c r="H113" t="n">
-        <v>2.357783862704848e-12</v>
+        <v>1.568470724325089e-12</v>
       </c>
       <c r="I113" t="n">
-        <v>2.752803802909962e-10</v>
+        <v>9.508870131515152e-12</v>
       </c>
     </row>
     <row r="114">
@@ -5045,22 +5045,22 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>6.527660550020569e-12</v>
+        <v>1.635545271355527e-13</v>
       </c>
       <c r="E114" t="n">
-        <v>5.939519435761922e-11</v>
+        <v>-4.590689979042299e-12</v>
       </c>
       <c r="F114" t="n">
-        <v>2.359089786935768e-10</v>
+        <v>2.568585847462796e-11</v>
       </c>
       <c r="G114" t="n">
         <v/>
       </c>
       <c r="H114" t="n">
-        <v>4.088425800681357e-12</v>
+        <v>2.748299391321809e-12</v>
       </c>
       <c r="I114" t="n">
-        <v>2.870039137393362e-10</v>
+        <v>6.935474370991931e-12</v>
       </c>
     </row>
     <row r="115">
@@ -5080,22 +5080,22 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>3.662144611137253e-12</v>
+        <v>2.922586022684336e-13</v>
       </c>
       <c r="E115" t="n">
-        <v>-1.484471905360367e-12</v>
+        <v>-1.800559232454521e-12</v>
       </c>
       <c r="F115" t="n">
-        <v>-3.785290737547251e-13</v>
+        <v>1.99492524894651e-12</v>
       </c>
       <c r="G115" t="n">
         <v/>
       </c>
       <c r="H115" t="n">
-        <v>4.342813167949879e-13</v>
+        <v>2.253039971660863e-13</v>
       </c>
       <c r="I115" t="n">
-        <v>-1.348125815494013e-13</v>
+        <v>3.092032831862641e-12</v>
       </c>
     </row>
     <row r="116">
@@ -5115,22 +5115,22 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>-8.993294360005683e-12</v>
+        <v>-3.609660004157514e-12</v>
       </c>
       <c r="E116" t="n">
-        <v>3.524279124259891e-11</v>
+        <v>-5.060229985792348e-12</v>
       </c>
       <c r="F116" t="n">
-        <v>1.653611998179278e-10</v>
+        <v>-3.441569323863736e-12</v>
       </c>
       <c r="G116" t="n">
         <v/>
       </c>
       <c r="H116" t="n">
-        <v>-1.016521660877445e-11</v>
+        <v>-6.992978356782632e-12</v>
       </c>
       <c r="I116" t="n">
-        <v>4.000867567829339e-10</v>
+        <v>2.920410725735117e-11</v>
       </c>
     </row>
     <row r="117">
@@ -5150,22 +5150,22 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>-3.761944983296092e-12</v>
+        <v>7.90525498737566e-13</v>
       </c>
       <c r="E117" t="n">
-        <v>3.468963944115207e-11</v>
+        <v>-6.762015878471353e-12</v>
       </c>
       <c r="F117" t="n">
-        <v>1.481795871832674e-10</v>
+        <v>-3.471448451609092e-12</v>
       </c>
       <c r="G117" t="n">
         <v/>
       </c>
       <c r="H117" t="n">
-        <v>-8.006846849766944e-12</v>
+        <v>-5.491522055274559e-12</v>
       </c>
       <c r="I117" t="n">
-        <v>1.284054829494364e-10</v>
+        <v>-8.747175183074576e-12</v>
       </c>
     </row>
     <row r="118">
@@ -5185,22 +5185,22 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>-8.938870368976264e-12</v>
+        <v>1.511500496992348e-12</v>
       </c>
       <c r="E118" t="n">
-        <v>2.486561944575467e-10</v>
+        <v>1.835718591869407e-11</v>
       </c>
       <c r="F118" t="n">
-        <v>1.09634381675966e-09</v>
+        <v>-1.619860539225051e-12</v>
       </c>
       <c r="G118" t="n">
         <v/>
       </c>
       <c r="H118" t="n">
-        <v>-9.865633558333512e-12</v>
+        <v>-6.768013031585139e-12</v>
       </c>
       <c r="I118" t="n">
-        <v>2.290713488590353e-10</v>
+        <v>-8.622405419832433e-12</v>
       </c>
     </row>
     <row r="119">
@@ -5220,22 +5220,22 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>-8.917031998841752e-12</v>
+        <v>-3.010974677243386e-12</v>
       </c>
       <c r="E119" t="n">
-        <v>1.405637967226644e-10</v>
+        <v>-5.975975497513708e-12</v>
       </c>
       <c r="F119" t="n">
-        <v>8.897832586895876e-10</v>
+        <v>1.492465613387838e-12</v>
       </c>
       <c r="G119" t="n">
         <v/>
       </c>
       <c r="H119" t="n">
-        <v>-9.541490574324224e-12</v>
+        <v>-6.545801932361253e-12</v>
       </c>
       <c r="I119" t="n">
-        <v>2.217622156463132e-10</v>
+        <v>-8.946731591112897e-12</v>
       </c>
     </row>
     <row r="120">
@@ -5255,22 +5255,22 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>-4.894059448952638e-12</v>
+        <v>-2.901578940043462e-12</v>
       </c>
       <c r="E120" t="n">
-        <v>2.328028652463332e-12</v>
+        <v>-4.643670022387839e-12</v>
       </c>
       <c r="F120" t="n">
-        <v>1.248659433176264e-12</v>
+        <v>-2.945603764742366e-12</v>
       </c>
       <c r="G120" t="n">
         <v/>
       </c>
       <c r="H120" t="n">
-        <v>-6.253569908348541e-12</v>
+        <v>-4.320512467319673e-12</v>
       </c>
       <c r="I120" t="n">
-        <v>-9.456281379697788e-13</v>
+        <v>-8.541361722270736e-12</v>
       </c>
     </row>
     <row r="121">
@@ -5290,22 +5290,22 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>-8.875867862090384e-12</v>
+        <v>-3.363919715330465e-12</v>
       </c>
       <c r="E121" t="n">
-        <v>3.289132247126601e-11</v>
+        <v>-5.667531469578671e-12</v>
       </c>
       <c r="F121" t="n">
-        <v>1.425692711683103e-10</v>
+        <v>-2.987517181240767e-12</v>
       </c>
       <c r="G121" t="n">
         <v/>
       </c>
       <c r="H121" t="n">
-        <v>-5.754752958716538e-12</v>
+        <v>-3.9443746883122e-12</v>
       </c>
       <c r="I121" t="n">
-        <v>1.245852022966947e-10</v>
+        <v>-8.706511006199756e-12</v>
       </c>
     </row>
     <row r="122">
@@ -5325,22 +5325,22 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>-2.528784955067676e-12</v>
+        <v>-2.358603501980058e-12</v>
       </c>
       <c r="E122" t="n">
-        <v>1.892619844304246e-11</v>
+        <v>6.872960163459441e-12</v>
       </c>
       <c r="F122" t="n">
-        <v>6.024743157847692e-12</v>
+        <v>1.060013159500647e-12</v>
       </c>
       <c r="G122" t="n">
-        <v>7.618028190240517e-12</v>
+        <v>5.217889103752818e-12</v>
       </c>
       <c r="H122" t="n">
         <v/>
       </c>
       <c r="I122" t="n">
-        <v>1.36780331610701e-09</v>
+        <v>4.852617179201361e-11</v>
       </c>
     </row>
     <row r="123">
@@ -5360,22 +5360,22 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>-3.393102735723507e-12</v>
+        <v>-2.272142899350268e-12</v>
       </c>
       <c r="E123" t="n">
-        <v>4.894945645566456e-12</v>
+        <v>1.197196820505731e-12</v>
       </c>
       <c r="F123" t="n">
-        <v>1.366515040334089e-11</v>
+        <v>9.96895686655225e-12</v>
       </c>
       <c r="G123" t="n">
-        <v>5.976509993930992e-12</v>
+        <v>4.093399184546356e-12</v>
       </c>
       <c r="H123" t="n">
         <v/>
       </c>
       <c r="I123" t="n">
-        <v>1.384170765856745e-09</v>
+        <v>4.581535967279078e-11</v>
       </c>
     </row>
     <row r="124">
@@ -5395,22 +5395,22 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>-1.840331528204863e-12</v>
+        <v>-1.060703057647263e-12</v>
       </c>
       <c r="E124" t="n">
-        <v>4.863388911188516e-12</v>
+        <v>2.261940563358063e-12</v>
       </c>
       <c r="F124" t="n">
-        <v>4.954427473227728e-12</v>
+        <v>3.15537063955898e-12</v>
       </c>
       <c r="G124" t="n">
-        <v>3.623656402099831e-11</v>
+        <v>2.483382832745832e-11</v>
       </c>
       <c r="H124" t="n">
         <v/>
       </c>
       <c r="I124" t="n">
-        <v>1.412910831283051e-09</v>
+        <v>6.746460297893938e-11</v>
       </c>
     </row>
     <row r="125">
@@ -5430,22 +5430,22 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>-4.453420692614903e-12</v>
+        <v>-2.61371818814644e-12</v>
       </c>
       <c r="E125" t="n">
-        <v>9.354849898709832e-13</v>
+        <v>1.399867807725118e-12</v>
       </c>
       <c r="F125" t="n">
-        <v>1.556720826272429e-12</v>
+        <v>1.480306945484574e-12</v>
       </c>
       <c r="G125" t="n">
-        <v>3.970077060522078e-12</v>
+        <v>2.576018953183616e-12</v>
       </c>
       <c r="H125" t="n">
         <v/>
       </c>
       <c r="I125" t="n">
-        <v>-9.248125369324267e-14</v>
+        <v>1.211134109326463e-12</v>
       </c>
     </row>
     <row r="126">
@@ -5465,22 +5465,22 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>-1.030771350293257e-11</v>
+        <v>-5.771821656219717e-12</v>
       </c>
       <c r="E126" t="n">
-        <v>-7.92702315266003e-12</v>
+        <v>-2.353634975861356e-12</v>
       </c>
       <c r="F126" t="n">
-        <v>-8.25749036729295e-12</v>
+        <v>-3.244783151337668e-12</v>
       </c>
       <c r="G126" t="n">
-        <v>-7.164351826039251e-12</v>
+        <v>-4.924889910956302e-12</v>
       </c>
       <c r="H126" t="n">
         <v/>
       </c>
       <c r="I126" t="n">
-        <v>1.559888632066088e-09</v>
+        <v>8.863155153120884e-10</v>
       </c>
     </row>
     <row r="127">
@@ -5500,22 +5500,22 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>3.645181096977985e-11</v>
+        <v>2.376443796904808e-11</v>
       </c>
       <c r="E127" t="n">
-        <v>-2.14832914245847e-12</v>
+        <v>-2.171769177173246e-12</v>
       </c>
       <c r="F127" t="n">
-        <v>3.027973600933198e-12</v>
+        <v>2.156826049410595e-12</v>
       </c>
       <c r="G127" t="n">
-        <v>1.005541466655088e-11</v>
+        <v>6.896467805061504e-12</v>
       </c>
       <c r="H127" t="n">
         <v/>
       </c>
       <c r="I127" t="n">
-        <v>1.167632931371541e-09</v>
+        <v>5.778267540916261e-11</v>
       </c>
     </row>
     <row r="128">
@@ -5535,22 +5535,22 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1.956719559746263e-11</v>
+        <v>4.55586372018878e-12</v>
       </c>
       <c r="E128" t="n">
-        <v>7.925104453300937e-12</v>
+        <v>-2.661203381545765e-12</v>
       </c>
       <c r="F128" t="n">
-        <v>4.871039560960151e-11</v>
+        <v>1.109019606352043e-11</v>
       </c>
       <c r="G128" t="n">
-        <v>1.851742541133651e-11</v>
+        <v>1.269007969716323e-11</v>
       </c>
       <c r="H128" t="n">
         <v/>
       </c>
       <c r="I128" t="n">
-        <v>1.731013389548988e-08</v>
+        <v>6.121228602257582e-11</v>
       </c>
     </row>
     <row r="129">
@@ -5570,22 +5570,22 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>3.858740331346219e-12</v>
+        <v>4.56647479347287e-13</v>
       </c>
       <c r="E129" t="n">
-        <v>-2.569105304871934e-12</v>
+        <v>-4.290280342433001e-12</v>
       </c>
       <c r="F129" t="n">
-        <v>1.813938209163697e-12</v>
+        <v>-1.046708565907089e-12</v>
       </c>
       <c r="G129" t="n">
-        <v>1.737967479279485e-11</v>
+        <v>1.190550928507552e-11</v>
       </c>
       <c r="H129" t="n">
         <v/>
       </c>
       <c r="I129" t="n">
-        <v>9.357044548265742e-09</v>
+        <v>4.940919768857468e-11</v>
       </c>
     </row>
     <row r="130">
@@ -5605,22 +5605,22 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>3.923475391288571e-12</v>
+        <v>4.418924072093224e-12</v>
       </c>
       <c r="E130" t="n">
-        <v>-2.240576261469496e-12</v>
+        <v>7.557676176355488e-14</v>
       </c>
       <c r="F130" t="n">
-        <v>3.118603922551808e-12</v>
+        <v>5.040959877768434e-12</v>
       </c>
       <c r="G130" t="n">
-        <v>3.909604231522977e-12</v>
+        <v>2.53803995863538e-12</v>
       </c>
       <c r="H130" t="n">
         <v/>
       </c>
       <c r="I130" t="n">
-        <v>2.187226155480906e-13</v>
+        <v>1.66753189561959e-12</v>
       </c>
     </row>
     <row r="131">
@@ -5640,22 +5640,22 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>-8.896182150978985e-12</v>
+        <v>-2.323212060877468e-12</v>
       </c>
       <c r="E131" t="n">
-        <v>-1.052694829956718e-11</v>
+        <v>-1.817640522323683e-12</v>
       </c>
       <c r="F131" t="n">
-        <v>-9.426819413310507e-12</v>
+        <v>-5.787030535614716e-13</v>
       </c>
       <c r="G131" t="n">
-        <v>-9.160769618857657e-12</v>
+        <v>-6.292520881453622e-12</v>
       </c>
       <c r="H131" t="n">
         <v/>
       </c>
       <c r="I131" t="n">
-        <v>1.109088558702066e-08</v>
+        <v>7.168050179978529e-10</v>
       </c>
     </row>
     <row r="132">
@@ -5675,22 +5675,22 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>3.355088899363736e-11</v>
+        <v>2.120632301262599e-11</v>
       </c>
       <c r="E132" t="n">
-        <v>2.582430608473189e-12</v>
+        <v>1.450260645088464e-12</v>
       </c>
       <c r="F132" t="n">
-        <v>-2.322815847136363e-12</v>
+        <v>-2.394955652124648e-12</v>
       </c>
       <c r="G132" t="n">
-        <v>8.539449045526711e-12</v>
+        <v>5.855402678863169e-12</v>
       </c>
       <c r="H132" t="n">
         <v/>
       </c>
       <c r="I132" t="n">
-        <v>1.171787695931715e-09</v>
+        <v>5.702442223205635e-11</v>
       </c>
     </row>
     <row r="133">
@@ -5710,22 +5710,22 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>2.190584897176501e-11</v>
+        <v>3.803523585349038e-12</v>
       </c>
       <c r="E133" t="n">
-        <v>6.543723341657578e-11</v>
+        <v>6.142967170831481e-12</v>
       </c>
       <c r="F133" t="n">
-        <v>8.422824904796784e-12</v>
+        <v>-2.685149459019903e-12</v>
       </c>
       <c r="G133" t="n">
-        <v>1.923605994468224e-11</v>
+        <v>1.317878372032696e-11</v>
       </c>
       <c r="H133" t="n">
         <v/>
       </c>
       <c r="I133" t="n">
-        <v>9.978611622640385e-09</v>
+        <v>6.492206267161497e-11</v>
       </c>
     </row>
     <row r="134">
@@ -5745,22 +5745,22 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>5.408463822990886e-12</v>
+        <v>3.624270190477199e-12</v>
       </c>
       <c r="E134" t="n">
-        <v>3.6441157071353e-12</v>
+        <v>2.265687739330711e-12</v>
       </c>
       <c r="F134" t="n">
-        <v>-1.921411811118078e-12</v>
+        <v>-1.914735816336227e-12</v>
       </c>
       <c r="G134" t="n">
-        <v>2.044029048985035e-11</v>
+        <v>1.401056821127315e-11</v>
       </c>
       <c r="H134" t="n">
         <v/>
       </c>
       <c r="I134" t="n">
-        <v>8.129491440607814e-09</v>
+        <v>6.184563815738715e-11</v>
       </c>
     </row>
     <row r="135">
@@ -5780,22 +5780,22 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>6.253274101189226e-12</v>
+        <v>2.877153231696002e-12</v>
       </c>
       <c r="E135" t="n">
-        <v>5.004268068568035e-12</v>
+        <v>2.432831034627314e-12</v>
       </c>
       <c r="F135" t="n">
-        <v>-5.132992240908117e-13</v>
+        <v>-1.985822494256549e-12</v>
       </c>
       <c r="G135" t="n">
-        <v>5.816941935736494e-12</v>
+        <v>3.818604947872747e-12</v>
       </c>
       <c r="H135" t="n">
         <v/>
       </c>
       <c r="I135" t="n">
-        <v>2.231052030115603e-13</v>
+        <v>1.721918999702367e-12</v>
       </c>
     </row>
     <row r="136">
@@ -5815,22 +5815,22 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>-8.328774254243975e-12</v>
+        <v>-3.612586620671482e-12</v>
       </c>
       <c r="E136" t="n">
-        <v>-8.345742978560127e-12</v>
+        <v>-1.418019123590738e-12</v>
       </c>
       <c r="F136" t="n">
-        <v>-1.039983635218799e-11</v>
+        <v>-5.235703056922186e-12</v>
       </c>
       <c r="G136" t="n">
-        <v>-8.805307137728585e-12</v>
+        <v>-6.049795295948776e-12</v>
       </c>
       <c r="H136" t="n">
         <v/>
       </c>
       <c r="I136" t="n">
-        <v>3.239573562705025e-08</v>
+        <v>4.90267626235113e-10</v>
       </c>
     </row>
     <row r="137">
@@ -5850,22 +5850,22 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>3.973519823742701e-11</v>
+        <v>2.266668964220528e-11</v>
       </c>
       <c r="E137" t="n">
-        <v>6.53300949304785e-12</v>
+        <v>2.337737601961875e-12</v>
       </c>
       <c r="F137" t="n">
-        <v>5.893895672552951e-12</v>
+        <v>2.260448275070366e-12</v>
       </c>
       <c r="G137" t="n">
-        <v>3.237595610295255e-13</v>
+        <v>1.668437346320241e-13</v>
       </c>
       <c r="H137" t="n">
         <v/>
       </c>
       <c r="I137" t="n">
-        <v>1.176862463408462e-09</v>
+        <v>4.852033680800874e-11</v>
       </c>
     </row>
     <row r="138">
@@ -5885,22 +5885,22 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>3.199455735726471e-12</v>
+        <v>-1.331112675994266e-12</v>
       </c>
       <c r="E138" t="n">
-        <v>1.980553568047862e-11</v>
+        <v>1.310753696867581e-12</v>
       </c>
       <c r="F138" t="n">
-        <v>5.165579344891835e-12</v>
+        <v>-2.352245630967319e-12</v>
       </c>
       <c r="G138" t="n">
-        <v>-4.031231445135443e-12</v>
+        <v>-2.808059581139486e-12</v>
       </c>
       <c r="H138" t="n">
         <v/>
       </c>
       <c r="I138" t="n">
-        <v>5.8022979198302e-09</v>
+        <v>3.214769799181555e-11</v>
       </c>
     </row>
     <row r="139">
@@ -5920,22 +5920,22 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>3.792576135273928e-12</v>
+        <v>2.012947075191207e-12</v>
       </c>
       <c r="E139" t="n">
-        <v>7.936169451154773e-12</v>
+        <v>2.353354906333215e-12</v>
       </c>
       <c r="F139" t="n">
-        <v>1.658766225302346e-11</v>
+        <v>1.050190017056709e-11</v>
       </c>
       <c r="G139" t="n">
-        <v>-3.563923239070261e-12</v>
+        <v>-2.486847391286201e-12</v>
       </c>
       <c r="H139" t="n">
         <v/>
       </c>
       <c r="I139" t="n">
-        <v>6.876702666116299e-09</v>
+        <v>3.736323823261665e-11</v>
       </c>
     </row>
     <row r="140">
@@ -5955,22 +5955,22 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>3.639882508593877e-12</v>
+        <v>-1.102953296257216e-13</v>
       </c>
       <c r="E140" t="n">
-        <v>5.07041277655576e-12</v>
+        <v>-6.503282305649515e-13</v>
       </c>
       <c r="F140" t="n">
-        <v>4.836976865251772e-12</v>
+        <v>-6.871689658323512e-13</v>
       </c>
       <c r="G140" t="n">
-        <v>-3.243010137799566e-12</v>
+        <v>-2.298718027884688e-12</v>
       </c>
       <c r="H140" t="n">
         <v/>
       </c>
       <c r="I140" t="n">
-        <v>1.628432269818131e-13</v>
+        <v>4.659907967039413e-13</v>
       </c>
     </row>
     <row r="141">
@@ -5990,22 +5990,22 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>-4.169166713716965e-12</v>
+        <v>-3.039685475874501e-12</v>
       </c>
       <c r="E141" t="n">
-        <v>-3.316572602128218e-12</v>
+        <v>-2.575429842753622e-12</v>
       </c>
       <c r="F141" t="n">
-        <v>-4.206949658813952e-12</v>
+        <v>-3.293160495047179e-12</v>
       </c>
       <c r="G141" t="n">
-        <v>-7.97507347383748e-12</v>
+        <v>-5.502820063772707e-12</v>
       </c>
       <c r="H141" t="n">
         <v/>
       </c>
       <c r="I141" t="n">
-        <v>4.142034838412522e-08</v>
+        <v>2.509112274045695e-09</v>
       </c>
     </row>
     <row r="142">
@@ -6025,22 +6025,22 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>2.049205773638716e-09</v>
+        <v>-1.251721624514172e-11</v>
       </c>
       <c r="E142" t="n">
-        <v>2.239764744833389e-11</v>
+        <v>1.079671491618875e-11</v>
       </c>
       <c r="F142" t="n">
-        <v>1.948986482448e-11</v>
+        <v>1.378698990721114e-11</v>
       </c>
       <c r="G142" t="n">
-        <v>3.54764203691092e-11</v>
+        <v>2.420375806654363e-11</v>
       </c>
       <c r="H142" t="n">
         <v/>
       </c>
       <c r="I142" t="n">
-        <v>1.325166026520962e-09</v>
+        <v>8.817484314936767e-10</v>
       </c>
     </row>
     <row r="143">
@@ -6060,22 +6060,22 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>4.150221078758429e-11</v>
+        <v>3.387188297532347e-11</v>
       </c>
       <c r="E143" t="n">
-        <v>2.52427976503725e-10</v>
+        <v>7.589552206146277e-11</v>
       </c>
       <c r="F143" t="n">
-        <v>3.629392166585222e-11</v>
+        <v>2.206607046295301e-11</v>
       </c>
       <c r="G143" t="n">
-        <v>2.787386033520057e-11</v>
+        <v>1.901083785430004e-11</v>
       </c>
       <c r="H143" t="n">
         <v/>
       </c>
       <c r="I143" t="n">
-        <v>1.953150906944228e-08</v>
+        <v>7.378095522165788e-10</v>
       </c>
     </row>
     <row r="144">
@@ -6095,22 +6095,22 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>4.792417856180814e-11</v>
+        <v>2.76791385785352e-11</v>
       </c>
       <c r="E144" t="n">
-        <v>5.541899466023984e-11</v>
+        <v>1.243355078507272e-11</v>
       </c>
       <c r="F144" t="n">
-        <v>1.492617698899137e-10</v>
+        <v>-1.659372350015281e-12</v>
       </c>
       <c r="G144" t="n">
-        <v>3.404825957730214e-11</v>
+        <v>2.321147886179739e-11</v>
       </c>
       <c r="H144" t="n">
         <v/>
       </c>
       <c r="I144" t="n">
-        <v>2.407663431685211e-08</v>
+        <v>5.283625618748881e-10</v>
       </c>
     </row>
     <row r="145">
@@ -6130,22 +6130,22 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>4.331294569466019e-11</v>
+        <v>2.006803774727999e-11</v>
       </c>
       <c r="E145" t="n">
-        <v>3.400114966011559e-11</v>
+        <v>6.107449395218597e-12</v>
       </c>
       <c r="F145" t="n">
-        <v>2.809066891396706e-11</v>
+        <v>9.539229800468045e-12</v>
       </c>
       <c r="G145" t="n">
-        <v>1.931971796043048e-10</v>
+        <v>1.281406499910723e-10</v>
       </c>
       <c r="H145" t="n">
         <v/>
       </c>
       <c r="I145" t="n">
-        <v>3.372933259148856e-08</v>
+        <v>2.442947946426671e-09</v>
       </c>
     </row>
     <row r="146">
@@ -6165,22 +6165,22 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>-2.968767514647813e-12</v>
+        <v>1.71608529039629e-12</v>
       </c>
       <c r="E146" t="n">
-        <v>-3.152889817300491e-12</v>
+        <v>2.012866442959657e-12</v>
       </c>
       <c r="F146" t="n">
-        <v>-4.487967125759331e-12</v>
+        <v>9.057545590726672e-13</v>
       </c>
       <c r="G146" t="n">
-        <v>-4.377999120448109e-12</v>
+        <v>-3.022374180910387e-12</v>
       </c>
       <c r="H146" t="n">
         <v/>
       </c>
       <c r="I146" t="n">
-        <v>0.003112539382762653</v>
+        <v>1.653168840555694e-10</v>
       </c>
     </row>
     <row r="147">
@@ -6200,22 +6200,22 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>-2.816844986613905e-12</v>
+        <v>1.620718466311995e-12</v>
       </c>
       <c r="E147" t="n">
-        <v>-7.671763570166647e-12</v>
+        <v>-3.034613606686233e-12</v>
       </c>
       <c r="F147" t="n">
-        <v>-8.145366757009606e-12</v>
+        <v>-3.389444119473951e-12</v>
       </c>
       <c r="G147" t="n">
-        <v>-7.758216202563968e-12</v>
+        <v>-5.326226627116136e-12</v>
       </c>
       <c r="H147" t="n">
         <v/>
       </c>
       <c r="I147" t="n">
-        <v>8.832319468266446e-10</v>
+        <v>4.256917922214365e-12</v>
       </c>
     </row>
     <row r="148">
@@ -6235,22 +6235,22 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>-9.173690401525728e-12</v>
+        <v>-3.113029203173112e-12</v>
       </c>
       <c r="E148" t="n">
-        <v>-5.399165928681093e-12</v>
+        <v>6.158613825479785e-12</v>
       </c>
       <c r="F148" t="n">
-        <v>-8.662977144309137e-12</v>
+        <v>-1.426118161271599e-12</v>
       </c>
       <c r="G148" t="n">
-        <v>-9.995367541640408e-12</v>
+        <v>-6.861875232759147e-12</v>
       </c>
       <c r="H148" t="n">
         <v/>
       </c>
       <c r="I148" t="n">
-        <v>2.24569375674359e-09</v>
+        <v>3.471224341701837e-12</v>
       </c>
     </row>
     <row r="149">
@@ -6270,22 +6270,22 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>-9.101145923740273e-12</v>
+        <v>-4.077123074601908e-12</v>
       </c>
       <c r="E149" t="n">
-        <v>-7.852909388371585e-12</v>
+        <v>-2.449171664354281e-12</v>
       </c>
       <c r="F149" t="n">
-        <v>-6.553294153360506e-12</v>
+        <v>5.205454471237822e-13</v>
       </c>
       <c r="G149" t="n">
-        <v>-9.750837465432806e-12</v>
+        <v>-6.694546089833112e-12</v>
       </c>
       <c r="H149" t="n">
         <v/>
       </c>
       <c r="I149" t="n">
-        <v>2.028207847117987e-09</v>
+        <v>3.028222493056173e-12</v>
       </c>
     </row>
     <row r="150">
@@ -6305,22 +6305,22 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>-4.541872415856052e-12</v>
+        <v>-2.889709123584472e-12</v>
       </c>
       <c r="E150" t="n">
-        <v>-3.910994174752488e-12</v>
+        <v>-3.568709223991599e-12</v>
       </c>
       <c r="F150" t="n">
-        <v>-4.66045830876433e-12</v>
+        <v>-3.303382704081646e-12</v>
       </c>
       <c r="G150" t="n">
-        <v>-3.990935988947174e-13</v>
+        <v>-2.75098188717306e-13</v>
       </c>
       <c r="H150" t="n">
         <v/>
       </c>
       <c r="I150" t="n">
-        <v>2.647594865062287e-09</v>
+        <v>5.942152623373222e-12</v>
       </c>
     </row>
     <row r="151">
@@ -6340,22 +6340,22 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>-9.113010472954675e-12</v>
+        <v>-4.572077588229241e-12</v>
       </c>
       <c r="E151" t="n">
-        <v>-8.483965097774004e-12</v>
+        <v>-3.257977352039611e-12</v>
       </c>
       <c r="F151" t="n">
-        <v>-8.836689371946403e-12</v>
+        <v>-3.848195660021928e-12</v>
       </c>
       <c r="G151" t="n">
-        <v>-9.627884641443628e-12</v>
+        <v>-6.634654194615242e-12</v>
       </c>
       <c r="H151" t="n">
         <v/>
       </c>
       <c r="I151" t="n">
-        <v>-1.415429489720933e-13</v>
+        <v>-5.066586420712213e-12</v>
       </c>
     </row>
     <row r="152">
@@ -6375,19 +6375,19 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>-1.00300659052361e-11</v>
+        <v>-1.075143643054941e-11</v>
       </c>
       <c r="E152" t="n">
-        <v>1.117032902140805e-10</v>
+        <v>3.178399576375402e-12</v>
       </c>
       <c r="F152" t="n">
-        <v>4.560849967414262e-10</v>
+        <v>7.622497484543942e-11</v>
       </c>
       <c r="G152" t="n">
-        <v>2.838375287022956e-10</v>
+        <v>-1.57712340553494e-12</v>
       </c>
       <c r="H152" t="n">
-        <v>1.37079257362726e-09</v>
+        <v>5.477628765147441e-11</v>
       </c>
       <c r="I152" t="n">
         <v/>
@@ -6410,19 +6410,19 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>-1.040045133299141e-11</v>
+        <v>-1.014744524654103e-11</v>
       </c>
       <c r="E153" t="n">
-        <v>6.873657090757619e-11</v>
+        <v>-4.081947995157384e-12</v>
       </c>
       <c r="F153" t="n">
-        <v>6.976669784500898e-10</v>
+        <v>5.746060865137311e-10</v>
       </c>
       <c r="G153" t="n">
-        <v>2.9024220805707e-10</v>
+        <v>-1.568498396969594e-12</v>
       </c>
       <c r="H153" t="n">
-        <v>1.384468863840869e-09</v>
+        <v>5.450680501179113e-11</v>
       </c>
       <c r="I153" t="n">
         <v/>
@@ -6445,19 +6445,19 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>-1.062010323770802e-11</v>
+        <v>-9.636637530804827e-12</v>
       </c>
       <c r="E154" t="n">
-        <v>5.358533539557554e-11</v>
+        <v>-3.915934471359766e-12</v>
       </c>
       <c r="F154" t="n">
-        <v>3.486236302383773e-10</v>
+        <v>9.89695803284044e-11</v>
       </c>
       <c r="G154" t="n">
-        <v>4.109650069842021e-10</v>
+        <v>2.602292402817117e-11</v>
       </c>
       <c r="H154" t="n">
-        <v>1.317490363322678e-09</v>
+        <v>4.640953344068854e-11</v>
       </c>
       <c r="I154" t="n">
         <v/>
@@ -6480,19 +6480,19 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>-1.210615530877825e-11</v>
+        <v>-1.0037379601529e-11</v>
       </c>
       <c r="E155" t="n">
-        <v>3.493732842215095e-11</v>
+        <v>-2.844576368309007e-12</v>
       </c>
       <c r="F155" t="n">
-        <v>2.872057764196802e-10</v>
+        <v>1.009913481336738e-10</v>
       </c>
       <c r="G155" t="n">
-        <v>1.403521620025723e-10</v>
+        <v>1.096010852975887e-13</v>
       </c>
       <c r="H155" t="n">
-        <v>1.524705851935393e-09</v>
+        <v>9.475585173896831e-10</v>
       </c>
       <c r="I155" t="n">
         <v/>
@@ -6515,19 +6515,19 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>-9.438279626267074e-12</v>
+        <v>-9.56875546314938e-12</v>
       </c>
       <c r="E156" t="n">
-        <v>-4.390517606761561e-13</v>
+        <v>7.746065642076743e-13</v>
       </c>
       <c r="F156" t="n">
-        <v>8.055858099093036e-13</v>
+        <v>1.546571824845779e-13</v>
       </c>
       <c r="G156" t="n">
-        <v>-5.980049793854515e-13</v>
+        <v>2.223503777863664e-12</v>
       </c>
       <c r="H156" t="n">
-        <v>-9.934824446236613e-14</v>
+        <v>5.796585917835369e-13</v>
       </c>
       <c r="I156" t="n">
         <v/>
@@ -6550,19 +6550,19 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>4.524232838943399e-12</v>
+        <v>5.343404137419416e-12</v>
       </c>
       <c r="E157" t="n">
-        <v>3.332027305605963e-11</v>
+        <v>-7.324753587234575e-12</v>
       </c>
       <c r="F157" t="n">
-        <v>2.988748777522946e-10</v>
+        <v>1.033562964637057e-10</v>
       </c>
       <c r="G157" t="n">
-        <v>2.299661427643342e-10</v>
+        <v>-9.733890492036089e-13</v>
       </c>
       <c r="H157" t="n">
-        <v>1.16912839519194e-09</v>
+        <v>4.635896897550089e-11</v>
       </c>
       <c r="I157" t="n">
         <v/>
@@ -6585,19 +6585,19 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>7.1490993442053e-12</v>
+        <v>-8.684982317626626e-12</v>
       </c>
       <c r="E158" t="n">
-        <v>1.014264985179696e-10</v>
+        <v>-6.755107768213961e-12</v>
       </c>
       <c r="F158" t="n">
-        <v>2.363151916429742e-09</v>
+        <v>1.637114055234828e-09</v>
       </c>
       <c r="G158" t="n">
-        <v>2.410146045391304e-09</v>
+        <v>1.689035308585005e-12</v>
       </c>
       <c r="H158" t="n">
-        <v>1.701825650140779e-08</v>
+        <v>6.266979008973848e-11</v>
       </c>
       <c r="I158" t="n">
         <v/>
@@ -6620,19 +6620,19 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>-6.567423593793444e-12</v>
+        <v>-8.801037958948247e-12</v>
       </c>
       <c r="E159" t="n">
-        <v>4.809771633512386e-11</v>
+        <v>-8.626984274240117e-12</v>
       </c>
       <c r="F159" t="n">
-        <v>3.483615595556946e-10</v>
+        <v>8.047577149175697e-11</v>
       </c>
       <c r="G159" t="n">
-        <v>0.0004115687273144448</v>
+        <v>7.508142021615668e-12</v>
       </c>
       <c r="H159" t="n">
-        <v>6.318997209808188e-09</v>
+        <v>3.076908072344351e-11</v>
       </c>
       <c r="I159" t="n">
         <v/>
@@ -6655,19 +6655,19 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>-6.93704445324318e-12</v>
+        <v>-3.307722569048477e-12</v>
       </c>
       <c r="E160" t="n">
-        <v>3.700347936844583e-11</v>
+        <v>-6.036776282805075e-12</v>
       </c>
       <c r="F160" t="n">
-        <v>3.310111595387523e-10</v>
+        <v>1.54795520028756e-10</v>
       </c>
       <c r="G160" t="n">
-        <v>2.495999427715805e-10</v>
+        <v>1.10993561818755e-12</v>
       </c>
       <c r="H160" t="n">
-        <v>2.144594916753769e-08</v>
+        <v>7.127763859784756e-10</v>
       </c>
       <c r="I160" t="n">
         <v/>
@@ -6690,19 +6690,19 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>-4.908478957013548e-12</v>
+        <v>3.055334997589769e-11</v>
       </c>
       <c r="E161" t="n">
-        <v>-1.570795769364943e-12</v>
+        <v>-4.635241247989782e-12</v>
       </c>
       <c r="F161" t="n">
-        <v>5.779376544495585e-13</v>
+        <v>1.064814487583638e-12</v>
       </c>
       <c r="G161" t="n">
-        <v>5.489829897459066e-13</v>
+        <v>3.24958244928646e-13</v>
       </c>
       <c r="H161" t="n">
-        <v>2.060978238813977e-13</v>
+        <v>-4.723531228903219e-16</v>
       </c>
       <c r="I161" t="n">
         <v/>
@@ -6725,19 +6725,19 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>3.263712291451135e-12</v>
+        <v>-7.40763650301099e-14</v>
       </c>
       <c r="E162" t="n">
-        <v>4.452797136091411e-11</v>
+        <v>-4.609960969102878e-12</v>
       </c>
       <c r="F162" t="n">
-        <v>2.299315217760117e-10</v>
+        <v>4.149999840063643e-11</v>
       </c>
       <c r="G162" t="n">
-        <v>2.267465711652122e-10</v>
+        <v>-1.849651259170689e-12</v>
       </c>
       <c r="H162" t="n">
-        <v>1.174527424475149e-09</v>
+        <v>4.330143187733544e-11</v>
       </c>
       <c r="I162" t="n">
         <v/>
@@ -6760,19 +6760,19 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>6.514095203845252e-12</v>
+        <v>-1.009785754832292e-11</v>
       </c>
       <c r="E163" t="n">
-        <v>5.223550490523076e-10</v>
+        <v>4.873225829200167e-12</v>
       </c>
       <c r="F163" t="n">
-        <v>4.702467743390053e-10</v>
+        <v>3.74692837851908e-11</v>
       </c>
       <c r="G163" t="n">
-        <v>1.417406992184482e-09</v>
+        <v>5.108831008096975e-13</v>
       </c>
       <c r="H163" t="n">
-        <v>1.016198088628386e-08</v>
+        <v>5.84233685511591e-11</v>
       </c>
       <c r="I163" t="n">
         <v/>
@@ -6795,19 +6795,19 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>-6.066299441428134e-12</v>
+        <v>-6.775076743502955e-12</v>
       </c>
       <c r="E164" t="n">
-        <v>7.049039157550515e-11</v>
+        <v>-5.181775914314594e-12</v>
       </c>
       <c r="F164" t="n">
-        <v>2.69627948677013e-10</v>
+        <v>4.356462186374671e-11</v>
       </c>
       <c r="G164" t="n">
-        <v>9.17235616694537e-09</v>
+        <v>1.224028316585925e-11</v>
       </c>
       <c r="H164" t="n">
-        <v>5.774144450140393e-09</v>
+        <v>3.504783556996767e-11</v>
       </c>
       <c r="I164" t="n">
         <v/>
@@ -6830,19 +6830,19 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>-5.973342704676237e-12</v>
+        <v>-7.831906348539193e-12</v>
       </c>
       <c r="E165" t="n">
-        <v>5.396249463478388e-11</v>
+        <v>-2.583442134577976e-12</v>
       </c>
       <c r="F165" t="n">
-        <v>2.640654743591141e-10</v>
+        <v>4.686909068071391e-11</v>
       </c>
       <c r="G165" t="n">
-        <v>2.488660028262101e-10</v>
+        <v>5.954236773802932e-13</v>
       </c>
       <c r="H165" t="n">
-        <v>2.404649679625104e-08</v>
+        <v>5.35658001458677e-10</v>
       </c>
       <c r="I165" t="n">
         <v/>
@@ -6865,19 +6865,19 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>-3.048465628008995e-12</v>
+        <v>-4.693863455639021e-12</v>
       </c>
       <c r="E166" t="n">
-        <v>7.378745895427847e-13</v>
+        <v>-1.167807586406914e-12</v>
       </c>
       <c r="F166" t="n">
-        <v>1.558045862852729e-13</v>
+        <v>-1.391176896779631e-12</v>
       </c>
       <c r="G166" t="n">
-        <v>7.294977314592999e-13</v>
+        <v>-9.103570682922665e-13</v>
       </c>
       <c r="H166" t="n">
-        <v>2.450321075853297e-13</v>
+        <v>-2.824488825296496e-13</v>
       </c>
       <c r="I166" t="n">
         <v/>
@@ -6900,19 +6900,19 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1.163122747898615e-11</v>
+        <v>-1.405174989939484e-12</v>
       </c>
       <c r="E167" t="n">
-        <v>6.492774216247606e-11</v>
+        <v>-3.062057803711662e-12</v>
       </c>
       <c r="F167" t="n">
-        <v>4.081795445089952e-10</v>
+        <v>9.11387338341205e-11</v>
       </c>
       <c r="G167" t="n">
-        <v>1.900126010881941e-10</v>
+        <v>-6.230006658574363e-12</v>
       </c>
       <c r="H167" t="n">
-        <v>1.256136158076457e-09</v>
+        <v>6.387369600344458e-11</v>
       </c>
       <c r="I167" t="n">
         <v/>
@@ -6935,19 +6935,19 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>-3.367352524312482e-12</v>
+        <v>-1.079721176878139e-11</v>
       </c>
       <c r="E168" t="n">
-        <v>4.101388079603998e-10</v>
+        <v>-1.679332527508257e-12</v>
       </c>
       <c r="F168" t="n">
-        <v>7.081154187306932e-10</v>
+        <v>5.783209344418807e-11</v>
       </c>
       <c r="G168" t="n">
-        <v>5.091877231871872e-10</v>
+        <v>-7.770225564365827e-12</v>
       </c>
       <c r="H168" t="n">
-        <v>8.339733992654923e-09</v>
+        <v>4.625662797033736e-11</v>
       </c>
       <c r="I168" t="n">
         <v/>
@@ -6970,19 +6970,19 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>-2.43459476339621e-12</v>
+        <v>-8.056319279620026e-12</v>
       </c>
       <c r="E169" t="n">
-        <v>1.729756166316535e-10</v>
+        <v>-3.867244914432287e-12</v>
       </c>
       <c r="F169" t="n">
-        <v>2.049226212017406e-09</v>
+        <v>6.150110857383696e-10</v>
       </c>
       <c r="G169" t="n">
-        <v>5.656057736054665e-10</v>
+        <v>-6.982554986843492e-12</v>
       </c>
       <c r="H169" t="n">
-        <v>1.057189616550792e-08</v>
+        <v>5.902371668218025e-11</v>
       </c>
       <c r="I169" t="n">
         <v/>
@@ -7005,19 +7005,19 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>-5.597886465180445e-12</v>
+        <v>-9.775846746543702e-12</v>
       </c>
       <c r="E170" t="n">
-        <v>6.892979375021586e-11</v>
+        <v>-3.675999469727091e-12</v>
       </c>
       <c r="F170" t="n">
-        <v>4.409224272814742e-10</v>
+        <v>8.27997685864078e-11</v>
       </c>
       <c r="G170" t="n">
-        <v>1.934285359065478e-10</v>
+        <v>-6.418277715243904e-12</v>
       </c>
       <c r="H170" t="n">
-        <v>3.356656159697019e-08</v>
+        <v>2.59788125660062e-09</v>
       </c>
       <c r="I170" t="n">
         <v/>
@@ -7040,19 +7040,19 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>2.421452967586036e-11</v>
+        <v>-9.038858789422727e-12</v>
       </c>
       <c r="E171" t="n">
-        <v>7.024318927989168e-12</v>
+        <v>5.032662089928868e-12</v>
       </c>
       <c r="F171" t="n">
-        <v>2.025662195309692e-12</v>
+        <v>8.979603468513935e-14</v>
       </c>
       <c r="G171" t="n">
-        <v>1.838697620884762e-13</v>
+        <v>-3.694552274289041e-12</v>
       </c>
       <c r="H171" t="n">
-        <v>2.928635888276671e-13</v>
+        <v>1.771343251686019e-12</v>
       </c>
       <c r="I171" t="n">
         <v/>
@@ -7075,19 +7075,19 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>-3.197592443204566e-12</v>
+        <v>-1.186384962340377e-13</v>
       </c>
       <c r="E172" t="n">
-        <v>3.343786783183564e-11</v>
+        <v>-3.533387507178138e-12</v>
       </c>
       <c r="F172" t="n">
-        <v>2.686724515507331e-10</v>
+        <v>9.04199218232293e-11</v>
       </c>
       <c r="G172" t="n">
-        <v>1.383562510693814e-10</v>
+        <v>2.36537958191069e-13</v>
       </c>
       <c r="H172" t="n">
-        <v>5.669201050659044e-10</v>
+        <v>2.213201267895248e-11</v>
       </c>
       <c r="I172" t="n">
         <v/>
@@ -7110,19 +7110,19 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>-6.650355324864173e-12</v>
+        <v>-7.43775792073763e-12</v>
       </c>
       <c r="E173" t="n">
-        <v>1.185622827005647e-10</v>
+        <v>9.635007757439382e-12</v>
       </c>
       <c r="F173" t="n">
-        <v>4.640006882583779e-10</v>
+        <v>9.497945715380256e-11</v>
       </c>
       <c r="G173" t="n">
-        <v>2.924492711992995e-10</v>
+        <v>5.741105532634333e-13</v>
       </c>
       <c r="H173" t="n">
-        <v>9.794349679997001e-10</v>
+        <v>2.471924814056828e-11</v>
       </c>
       <c r="I173" t="n">
         <v/>
@@ -7145,19 +7145,19 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>-5.942438947023284e-12</v>
+        <v>-8.122297981427073e-12</v>
       </c>
       <c r="E174" t="n">
-        <v>7.886251212087795e-11</v>
+        <v>-2.675272163148212e-12</v>
       </c>
       <c r="F174" t="n">
-        <v>8.365932304533964e-10</v>
+        <v>9.126591570984202e-10</v>
       </c>
       <c r="G174" t="n">
-        <v>3.038957998324524e-10</v>
+        <v>1.096231340094624e-12</v>
       </c>
       <c r="H174" t="n">
-        <v>9.879542117243122e-10</v>
+        <v>2.505241231307428e-11</v>
       </c>
       <c r="I174" t="n">
         <v/>
@@ -7180,19 +7180,19 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>-7.993132811462284e-12</v>
+        <v>-9.079679511445215e-12</v>
       </c>
       <c r="E175" t="n">
-        <v>5.422740381522912e-11</v>
+        <v>-4.947313652093487e-12</v>
       </c>
       <c r="F175" t="n">
-        <v>3.44744454785427e-10</v>
+        <v>8.116458450321168e-11</v>
       </c>
       <c r="G175" t="n">
-        <v>4.396063548348384e-10</v>
+        <v>2.330070587494129e-11</v>
       </c>
       <c r="H175" t="n">
-        <v>9.464637954433079e-10</v>
+        <v>1.847708569542248e-11</v>
       </c>
       <c r="I175" t="n">
         <v/>
@@ -7215,19 +7215,19 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>-6.7874248817903e-12</v>
+        <v>-7.251869993791434e-12</v>
       </c>
       <c r="E176" t="n">
-        <v>-4.12769583918616e-13</v>
+        <v>1.614631621248299e-13</v>
       </c>
       <c r="F176" t="n">
-        <v>7.535837774435289e-13</v>
+        <v>8.191224004957263e-14</v>
       </c>
       <c r="G176" t="n">
-        <v>-4.839843336421052e-13</v>
+        <v>2.056456363142489e-12</v>
       </c>
       <c r="H176" t="n">
-        <v>-2.721323332488369e-13</v>
+        <v>-2.068105489637721e-12</v>
       </c>
       <c r="I176" t="n">
         <v/>
@@ -7250,19 +7250,19 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1.260514158286267e-10</v>
+        <v>1.357298054516675e-12</v>
       </c>
       <c r="E177" t="n">
-        <v>9.230961876704838e-11</v>
+        <v>1.16407071729417e-11</v>
       </c>
       <c r="F177" t="n">
-        <v>5.847285720714462e-10</v>
+        <v>5.245316964820667e-10</v>
       </c>
       <c r="G177" t="n">
-        <v>3.397173346797232e-10</v>
+        <v>3.402691609755258e-11</v>
       </c>
       <c r="H177" t="n">
-        <v>1.430646221672396e-09</v>
+        <v>9.281646925500737e-10</v>
       </c>
       <c r="I177" t="n">
         <v/>
@@ -7285,19 +7285,19 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>6.830110327708683e-12</v>
+        <v>5.418727493558772e-11</v>
       </c>
       <c r="E178" t="n">
-        <v>0.1762870559642668</v>
+        <v>0.1521325782296414</v>
       </c>
       <c r="F178" t="n">
-        <v>1.24352957286176e-09</v>
+        <v>1.710300648478072e-09</v>
       </c>
       <c r="G178" t="n">
-        <v>0.0004115691146942133</v>
+        <v>1.792103746024535e-11</v>
       </c>
       <c r="H178" t="n">
-        <v>2.510059495120384e-08</v>
+        <v>6.683982211006038e-10</v>
       </c>
       <c r="I178" t="n">
         <v/>
@@ -7320,19 +7320,19 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>6.318085420546777e-12</v>
+        <v>5.538264364373573e-12</v>
       </c>
       <c r="E179" t="n">
-        <v>2.700725830360457e-10</v>
+        <v>8.709812066404416e-12</v>
       </c>
       <c r="F179" t="n">
-        <v>0.2900840392419096</v>
+        <v>4.142200485956749e-13</v>
       </c>
       <c r="G179" t="n">
-        <v>7.496215403966598e-09</v>
+        <v>1.635236835152759e-11</v>
       </c>
       <c r="H179" t="n">
-        <v>1.119481884677697e-08</v>
+        <v>4.708954644778897e-10</v>
       </c>
       <c r="I179" t="n">
         <v/>
@@ -7355,19 +7355,19 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>5.56928824864111e-11</v>
+        <v>-4.780979829317597e-12</v>
       </c>
       <c r="E180" t="n">
-        <v>4.97595432311277e-10</v>
+        <v>1.542003568809198e-11</v>
       </c>
       <c r="F180" t="n">
-        <v>2.297111671477251e-09</v>
+        <v>5.426969194506089e-10</v>
       </c>
       <c r="G180" t="n">
-        <v>0.0008977762343158594</v>
+        <v>2.888735859350121e-12</v>
       </c>
       <c r="H180" t="n">
-        <v>3.937752495808388e-08</v>
+        <v>2.638103105078589e-09</v>
       </c>
       <c r="I180" t="n">
         <v/>
@@ -7390,19 +7390,19 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>7.867891442648171e-14</v>
+        <v>-1.057388637987392e-12</v>
       </c>
       <c r="E181" t="n">
-        <v>8.984420070959352e-11</v>
+        <v>1.378129185263285e-11</v>
       </c>
       <c r="F181" t="n">
-        <v>5.915595712263479e-10</v>
+        <v>7.93849305389142e-10</v>
       </c>
       <c r="G181" t="n">
-        <v>3.415770490955721e-10</v>
+        <v>3.186735942394794e-11</v>
       </c>
       <c r="H181" t="n">
-        <v>0.003113526271699747</v>
+        <v>1.679884135495855e-10</v>
       </c>
       <c r="I181" t="n">
         <v/>
@@ -7424,7 +7424,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>0.0275642</v>
+        <v>0.0212351</v>
       </c>
     </row>
   </sheetData>
@@ -7478,10 +7478,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4363089759121188</v>
+        <v>0.2247648674539142</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1863460931282018</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>

--- a/6node_spain/output_all.xlsx
+++ b/6node_spain/output_all.xlsx
@@ -459,19 +459,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2247648678086808</v>
+        <v>0.957506279652943</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.3219984429901943</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1.245684889957986</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>6.115042574241787e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4495297368291778</v>
+        <v>0.656643958524995</v>
       </c>
     </row>
   </sheetData>
@@ -558,16 +558,16 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1.964597279311804e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1.455308137692222</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1.200580695646784e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7492162247732381</v>
+        <v>0.8681712535801821</v>
       </c>
     </row>
     <row r="4">
@@ -580,19 +580,19 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1.964597279311804e-09</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.6208333455715651</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1.549967327866147e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.2262353439614763</v>
       </c>
     </row>
     <row r="5">
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1.455308137692222</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.6208333455715651</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -630,10 +630,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1.200580695646784e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1.549967327866147e-09</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -655,10 +655,10 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7492162247732381</v>
+        <v>0.8681712535801821</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.2262353439614763</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -757,13 +757,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.1533211854451907</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1507398233537224</v>
+        <v>0.1746731819131451</v>
       </c>
     </row>
     <row r="4">
@@ -782,13 +782,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.1732682923149792</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.2973395180660651</v>
       </c>
     </row>
     <row r="5">
@@ -801,10 +801,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.151738315241142</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.1717763677294855</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -813,7 +813,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2.067326088095456e-09</v>
       </c>
     </row>
     <row r="6">
@@ -838,7 +838,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>9.714338222721608e-10</v>
       </c>
     </row>
     <row r="7">
@@ -851,16 +851,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1521325710087522</v>
+        <v>0.1762870596787873</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.2887762466225903</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-6.828283494186849e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.091150281240516e-09</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -953,13 +953,13 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.8466788145548093</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8492601766462776</v>
+        <v>0.8253268180868549</v>
       </c>
     </row>
     <row r="4">
@@ -978,13 +978,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0.8267317076850208</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.7026604819339349</v>
       </c>
     </row>
     <row r="5">
@@ -997,10 +997,10 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0.848261684758858</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0.8282236322705145</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -1009,7 +1009,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0.9999999979326739</v>
       </c>
     </row>
     <row r="6">
@@ -1034,7 +1034,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0.9999999990285662</v>
       </c>
     </row>
     <row r="7">
@@ -1047,16 +1047,16 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8478674289912478</v>
+        <v>0.8237129403212127</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0.7112237533774097</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>1.000000006828283</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0.9999999989088497</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1128,19 +1128,19 @@
         <v/>
       </c>
       <c r="E2" t="n">
-        <v>1.480044337645017e-11</v>
+        <v>6.999058060787945e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.882583757692968e-12</v>
+        <v>6.928830899745241e-11</v>
       </c>
       <c r="G2" t="n">
-        <v>1.400526107459821e-11</v>
+        <v>3.974360684676744e-11</v>
       </c>
       <c r="H2" t="n">
-        <v>2.757933747757716e-11</v>
+        <v>5.158072893753792e-11</v>
       </c>
       <c r="I2" t="n">
-        <v>1.957034997895108e-11</v>
+        <v>4.326298760763133e-11</v>
       </c>
     </row>
     <row r="3">
@@ -1163,19 +1163,19 @@
         <v/>
       </c>
       <c r="E3" t="n">
-        <v>4.285430911263871e-12</v>
+        <v>-8.517692356288191e-12</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.940294805374026e-12</v>
+        <v>9.167244382282194e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>1.751978890581288e-11</v>
+        <v>3.534099445956839e-11</v>
       </c>
       <c r="H3" t="n">
-        <v>2.531506167909295e-11</v>
+        <v>4.702407910399666e-11</v>
       </c>
       <c r="I3" t="n">
-        <v>1.119602695961126e-11</v>
+        <v>3.84925830094839e-11</v>
       </c>
     </row>
     <row r="4">
@@ -1198,19 +1198,19 @@
         <v/>
       </c>
       <c r="E4" t="n">
-        <v>5.934416599282776e-12</v>
+        <v>1.297692133802654e-11</v>
       </c>
       <c r="F4" t="n">
-        <v>6.564276097864454e-12</v>
+        <v>5.11799366249469e-11</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.322524736983353e-11</v>
+        <v>5.592277644259414e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>2.752021605291402e-11</v>
+        <v>5.667653686536655e-11</v>
       </c>
       <c r="I4" t="n">
-        <v>1.142451502653555e-11</v>
+        <v>6.638373458011241e-11</v>
       </c>
     </row>
     <row r="5">
@@ -1233,19 +1233,19 @@
         <v/>
       </c>
       <c r="E5" t="n">
-        <v>5.464167333579032e-12</v>
+        <v>4.248445427333001e-11</v>
       </c>
       <c r="F5" t="n">
-        <v>4.309576577509042e-12</v>
+        <v>7.409721128955967e-12</v>
       </c>
       <c r="G5" t="n">
-        <v>1.853755366252409e-11</v>
+        <v>2.969710572324172e-11</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.264665777439352e-11</v>
+        <v>2.981827410239557e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.115817386391917e-11</v>
+        <v>9.239380299570248e-12</v>
       </c>
     </row>
     <row r="6">
@@ -1268,19 +1268,19 @@
         <v/>
       </c>
       <c r="E6" t="n">
-        <v>8.248740565663363e-12</v>
+        <v>-2.532132872371463e-11</v>
       </c>
       <c r="F6" t="n">
-        <v>5.690839786624128e-12</v>
+        <v>-4.345964607504906e-12</v>
       </c>
       <c r="G6" t="n">
-        <v>4.814128686613123e-12</v>
+        <v>-3.26956801572254e-12</v>
       </c>
       <c r="H6" t="n">
-        <v>2.468971370679038e-12</v>
+        <v>-3.23459156768826e-12</v>
       </c>
       <c r="I6" t="n">
-        <v>2.024338096019279e-12</v>
+        <v>2.102852451455637e-10</v>
       </c>
     </row>
     <row r="7">
@@ -1303,19 +1303,19 @@
         <v/>
       </c>
       <c r="E7" t="n">
-        <v>-4.081759188525122e-12</v>
+        <v>-1.601317232917517e-11</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.297129083464744e-13</v>
+        <v>5.959150226130867e-12</v>
       </c>
       <c r="G7" t="n">
-        <v>1.77843467520911e-12</v>
+        <v>6.341933088659929e-12</v>
       </c>
       <c r="H7" t="n">
-        <v>1.46474733611659e-12</v>
+        <v>4.80197797886277e-12</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.575749045587882e-12</v>
+        <v>8.387211465641228e-12</v>
       </c>
     </row>
     <row r="8">
@@ -1338,19 +1338,19 @@
         <v/>
       </c>
       <c r="E8" t="n">
-        <v>-1.018466915260351e-11</v>
+        <v>-2.398790323814109e-11</v>
       </c>
       <c r="F8" t="n">
-        <v>-8.59820617336918e-12</v>
+        <v>7.508594057698467e-11</v>
       </c>
       <c r="G8" t="n">
-        <v>-6.13609727358168e-13</v>
+        <v>2.605581044207033e-11</v>
       </c>
       <c r="H8" t="n">
-        <v>3.979734168809137e-12</v>
+        <v>2.625550513533907e-11</v>
       </c>
       <c r="I8" t="n">
-        <v>-9.786491440949261e-12</v>
+        <v>2.159591187208599e-11</v>
       </c>
     </row>
     <row r="9">
@@ -1373,19 +1373,19 @@
         <v/>
       </c>
       <c r="E9" t="n">
-        <v>-1.04886000988543e-11</v>
+        <v>-2.560450291038688e-11</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.007419155672141e-11</v>
+        <v>-1.250301784195878e-12</v>
       </c>
       <c r="G9" t="n">
-        <v>4.109848975930856e-12</v>
+        <v>2.383255484211595e-11</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.139542169859491e-12</v>
+        <v>3.405983904694474e-12</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.026189403422301e-11</v>
+        <v>3.094479851257352e-12</v>
       </c>
     </row>
     <row r="10">
@@ -1408,19 +1408,19 @@
         <v/>
       </c>
       <c r="E10" t="n">
-        <v>-7.262095286688394e-12</v>
+        <v>-2.524171739222478e-11</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.948534356496038e-12</v>
+        <v>-6.53354795162985e-12</v>
       </c>
       <c r="G10" t="n">
-        <v>4.69382491667004e-12</v>
+        <v>6.593327105312834e-12</v>
       </c>
       <c r="H10" t="n">
-        <v>2.84349609184671e-11</v>
+        <v>4.289475409806861e-11</v>
       </c>
       <c r="I10" t="n">
-        <v>-6.769186341098366e-12</v>
+        <v>-4.063167934603811e-12</v>
       </c>
     </row>
     <row r="11">
@@ -1443,19 +1443,19 @@
         <v/>
       </c>
       <c r="E11" t="n">
-        <v>-8.781242135200942e-13</v>
+        <v>-2.652385306480064e-11</v>
       </c>
       <c r="F11" t="n">
-        <v>4.690726669037883e-12</v>
+        <v>-1.347801608289485e-11</v>
       </c>
       <c r="G11" t="n">
-        <v>1.62519976913137e-12</v>
+        <v>-1.11837940841483e-11</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.212387299987847e-12</v>
+        <v>-1.180863341091301e-11</v>
       </c>
       <c r="I11" t="n">
-        <v>2.391681409174153e-11</v>
+        <v>6.896623672783823e-12</v>
       </c>
     </row>
     <row r="12">
@@ -1478,19 +1478,19 @@
         <v/>
       </c>
       <c r="E12" t="n">
-        <v>1.135520093578737e-12</v>
+        <v>-1.349631069680271e-11</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.073747051970698e-12</v>
+        <v>-3.442645605788137e-12</v>
       </c>
       <c r="G12" t="n">
-        <v>1.222484456775506e-12</v>
+        <v>4.699640858502962e-12</v>
       </c>
       <c r="H12" t="n">
-        <v>1.434703667790598e-12</v>
+        <v>2.930320314507146e-12</v>
       </c>
       <c r="I12" t="n">
-        <v>1.43050864266003e-12</v>
+        <v>6.533477415660082e-12</v>
       </c>
     </row>
     <row r="13">
@@ -1513,19 +1513,19 @@
         <v/>
       </c>
       <c r="E13" t="n">
-        <v>-8.575382633216793e-12</v>
+        <v>-2.137967613877841e-11</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.048172210643201e-11</v>
+        <v>4.159345762119093e-12</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.616835127448535e-12</v>
+        <v>2.390040238049258e-11</v>
       </c>
       <c r="H13" t="n">
-        <v>4.549625537383269e-12</v>
+        <v>2.278974652571581e-11</v>
       </c>
       <c r="I13" t="n">
-        <v>-8.738455358498939e-12</v>
+        <v>1.846117574925373e-11</v>
       </c>
     </row>
     <row r="14">
@@ -1548,19 +1548,19 @@
         <v/>
       </c>
       <c r="E14" t="n">
-        <v>-7.343278573240007e-12</v>
+        <v>-2.541296836343197e-11</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.874919845299587e-12</v>
+        <v>-6.593910520207246e-12</v>
       </c>
       <c r="G14" t="n">
-        <v>1.4725298270698e-11</v>
+        <v>2.619235415358592e-11</v>
       </c>
       <c r="H14" t="n">
-        <v>1.788516824178246e-12</v>
+        <v>4.019534116066079e-12</v>
       </c>
       <c r="I14" t="n">
-        <v>-7.467212177334567e-12</v>
+        <v>3.757288928822035e-12</v>
       </c>
     </row>
     <row r="15">
@@ -1583,19 +1583,19 @@
         <v/>
       </c>
       <c r="E15" t="n">
-        <v>-7.730401510260072e-12</v>
+        <v>-2.476580260311988e-11</v>
       </c>
       <c r="F15" t="n">
-        <v>-9.318833876269673e-12</v>
+        <v>-9.717717315927922e-12</v>
       </c>
       <c r="G15" t="n">
-        <v>8.911471846243703e-13</v>
+        <v>8.710478816495473e-12</v>
       </c>
       <c r="H15" t="n">
-        <v>2.431117448349816e-11</v>
+        <v>5.0503132749824e-11</v>
       </c>
       <c r="I15" t="n">
-        <v>-7.74082659335309e-12</v>
+        <v>-2.965408547631892e-12</v>
       </c>
     </row>
     <row r="16">
@@ -1618,19 +1618,19 @@
         <v/>
       </c>
       <c r="E16" t="n">
-        <v>-5.20990903664746e-12</v>
+        <v>-2.615357392930178e-11</v>
       </c>
       <c r="F16" t="n">
-        <v>-7.842892660664941e-12</v>
+        <v>-1.467427619293542e-11</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.534737212008831e-12</v>
+        <v>-1.063701612676422e-11</v>
       </c>
       <c r="H16" t="n">
-        <v>-4.090408756408231e-12</v>
+        <v>-1.148093199285091e-11</v>
       </c>
       <c r="I16" t="n">
-        <v>8.14937928458056e-13</v>
+        <v>1.115122227137664e-11</v>
       </c>
     </row>
     <row r="17">
@@ -1653,19 +1653,19 @@
         <v/>
       </c>
       <c r="E17" t="n">
-        <v>3.096789187146547e-12</v>
+        <v>1.333555246691729e-11</v>
       </c>
       <c r="F17" t="n">
-        <v>2.23158802841522e-12</v>
+        <v>1.257801681570798e-11</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.402065828207578e-12</v>
+        <v>-2.678407406024111e-12</v>
       </c>
       <c r="H17" t="n">
-        <v>3.452342120011355e-12</v>
+        <v>6.640279428968185e-12</v>
       </c>
       <c r="I17" t="n">
-        <v>4.927195262150634e-12</v>
+        <v>7.270373152011178e-12</v>
       </c>
     </row>
     <row r="18">
@@ -1688,19 +1688,19 @@
         <v/>
       </c>
       <c r="E18" t="n">
-        <v>-9.143683744957088e-12</v>
+        <v>-2.531036904557456e-11</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.019808148321294e-11</v>
+        <v>3.845404188217079e-12</v>
       </c>
       <c r="G18" t="n">
-        <v>-6.472825050731262e-12</v>
+        <v>-4.790806084144591e-12</v>
       </c>
       <c r="H18" t="n">
-        <v>1.78122396622682e-13</v>
+        <v>4.059346884763075e-12</v>
       </c>
       <c r="I18" t="n">
-        <v>-9.178125154088039e-12</v>
+        <v>-1.322564548797459e-12</v>
       </c>
     </row>
     <row r="19">
@@ -1723,19 +1723,19 @@
         <v/>
       </c>
       <c r="E19" t="n">
-        <v>-6.956117341428425e-12</v>
+        <v>-2.521931440510474e-11</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.657224898382269e-12</v>
+        <v>2.396590404045999e-11</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.93045962479569e-12</v>
+        <v>-3.890028350183149e-12</v>
       </c>
       <c r="H19" t="n">
-        <v>3.648817390956299e-12</v>
+        <v>6.10422660192328e-12</v>
       </c>
       <c r="I19" t="n">
-        <v>-6.574436047935008e-12</v>
+        <v>2.147404492661879e-13</v>
       </c>
     </row>
     <row r="20">
@@ -1758,19 +1758,19 @@
         <v/>
       </c>
       <c r="E20" t="n">
-        <v>-9.313098246389676e-12</v>
+        <v>-2.494080905260137e-11</v>
       </c>
       <c r="F20" t="n">
-        <v>-9.714860016080569e-12</v>
+        <v>-4.984879779464657e-12</v>
       </c>
       <c r="G20" t="n">
-        <v>-5.488553903191298e-12</v>
+        <v>-3.317333210056965e-12</v>
       </c>
       <c r="H20" t="n">
-        <v>1.732567109607292e-11</v>
+        <v>4.565089213730729e-11</v>
       </c>
       <c r="I20" t="n">
-        <v>-9.132903198742838e-12</v>
+        <v>-5.417857837240488e-12</v>
       </c>
     </row>
     <row r="21">
@@ -1793,19 +1793,19 @@
         <v/>
       </c>
       <c r="E21" t="n">
-        <v>-8.990956208086479e-12</v>
+        <v>-2.608047082408938e-11</v>
       </c>
       <c r="F21" t="n">
-        <v>-9.534832738499326e-12</v>
+        <v>-7.153155569694226e-12</v>
       </c>
       <c r="G21" t="n">
-        <v>-6.607187428004606e-12</v>
+        <v>-9.734806231061665e-12</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.666407741542247e-12</v>
+        <v>-5.777077470049302e-12</v>
       </c>
       <c r="I21" t="n">
-        <v>-6.484719966092916e-12</v>
+        <v>5.137158542891614e-11</v>
       </c>
     </row>
     <row r="22">
@@ -1828,19 +1828,19 @@
         <v/>
       </c>
       <c r="E22" t="n">
-        <v>7.468005152939783e-13</v>
+        <v>4.163790774031392e-11</v>
       </c>
       <c r="F22" t="n">
-        <v>9.065074288774658e-13</v>
+        <v>-5.179228738662628e-12</v>
       </c>
       <c r="G22" t="n">
-        <v>2.809812507814784e-12</v>
+        <v>2.375227234854036e-12</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.207931736095556e-12</v>
+        <v>-3.625808840505989e-12</v>
       </c>
       <c r="I22" t="n">
-        <v>2.162391815599093e-12</v>
+        <v>-4.569803176119799e-12</v>
       </c>
     </row>
     <row r="23">
@@ -1863,19 +1863,19 @@
         <v/>
       </c>
       <c r="E23" t="n">
-        <v>-2.625561055605301e-12</v>
+        <v>-2.45959100900128e-11</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.740192309045231e-12</v>
+        <v>-5.244038420594909e-12</v>
       </c>
       <c r="G23" t="n">
-        <v>4.76236771928022e-12</v>
+        <v>4.866236079404874e-12</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.993844483445183e-14</v>
+        <v>-1.114925771781769e-12</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.266246555879968e-12</v>
+        <v>-5.96246133064231e-12</v>
       </c>
     </row>
     <row r="24">
@@ -1898,19 +1898,19 @@
         <v/>
       </c>
       <c r="E24" t="n">
-        <v>-8.028774823523644e-12</v>
+        <v>-2.46352614361717e-11</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.187342979198611e-12</v>
+        <v>3.524129394245783e-12</v>
       </c>
       <c r="G24" t="n">
-        <v>2.01996984805698e-12</v>
+        <v>7.200697324693422e-12</v>
       </c>
       <c r="H24" t="n">
-        <v>-9.954331097238055e-13</v>
+        <v>7.147330841935875e-13</v>
       </c>
       <c r="I24" t="n">
-        <v>-7.657006010478657e-12</v>
+        <v>-4.851387357838654e-12</v>
       </c>
     </row>
     <row r="25">
@@ -1933,19 +1933,19 @@
         <v/>
       </c>
       <c r="E25" t="n">
-        <v>-9.514293981368435e-12</v>
+        <v>-2.491501054227165e-11</v>
       </c>
       <c r="F25" t="n">
-        <v>-9.665471988953811e-12</v>
+        <v>-6.79068821080299e-12</v>
       </c>
       <c r="G25" t="n">
-        <v>8.778653238769607e-12</v>
+        <v>2.654636761578175e-11</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.815362679910304e-12</v>
+        <v>-1.234899555323412e-12</v>
       </c>
       <c r="I25" t="n">
-        <v>-9.365147465501821e-12</v>
+        <v>-4.644452938013519e-12</v>
       </c>
     </row>
     <row r="26">
@@ -1968,19 +1968,19 @@
         <v/>
       </c>
       <c r="E26" t="n">
-        <v>-7.739864312263999e-12</v>
+        <v>-2.643234658306321e-11</v>
       </c>
       <c r="F26" t="n">
-        <v>-8.205224262763684e-12</v>
+        <v>-1.522472050670646e-11</v>
       </c>
       <c r="G26" t="n">
-        <v>-3.073270295449894e-12</v>
+        <v>-1.085641720278655e-11</v>
       </c>
       <c r="H26" t="n">
-        <v>-6.063110787486421e-12</v>
+        <v>-1.309067500878875e-11</v>
       </c>
       <c r="I26" t="n">
-        <v>-4.160315236241705e-12</v>
+        <v>-2.378686948627146e-12</v>
       </c>
     </row>
     <row r="27">
@@ -2003,19 +2003,19 @@
         <v/>
       </c>
       <c r="E27" t="n">
-        <v>-8.973380868670217e-13</v>
+        <v>-2.546243969591453e-11</v>
       </c>
       <c r="F27" t="n">
-        <v>1.265388229244651e-12</v>
+        <v>-9.808985288979614e-12</v>
       </c>
       <c r="G27" t="n">
-        <v>-2.408658437731791e-12</v>
+        <v>-1.06501407245235e-11</v>
       </c>
       <c r="H27" t="n">
-        <v>-4.143782527430161e-12</v>
+        <v>-1.066500308154121e-11</v>
       </c>
       <c r="I27" t="n">
-        <v>-5.944266542180305e-12</v>
+        <v>-1.750305279283975e-11</v>
       </c>
     </row>
     <row r="28">
@@ -2038,19 +2038,19 @@
         <v/>
       </c>
       <c r="E28" t="n">
-        <v>1.138212238235325e-11</v>
+        <v>-2.607294266530008e-11</v>
       </c>
       <c r="F28" t="n">
-        <v>4.277493814983187e-12</v>
+        <v>-1.226579554278199e-11</v>
       </c>
       <c r="G28" t="n">
-        <v>9.157299936222989e-13</v>
+        <v>-1.207960782850364e-11</v>
       </c>
       <c r="H28" t="n">
-        <v>-2.749634013219662e-12</v>
+        <v>-1.176530887048781e-11</v>
       </c>
       <c r="I28" t="n">
-        <v>-3.864029680760062e-12</v>
+        <v>-1.852807855073953e-11</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2073,19 @@
         <v/>
       </c>
       <c r="E29" t="n">
-        <v>-6.839321253564789e-12</v>
+        <v>-2.644517413999881e-11</v>
       </c>
       <c r="F29" t="n">
-        <v>-2.702088996577053e-12</v>
+        <v>-9.53376148070472e-12</v>
       </c>
       <c r="G29" t="n">
-        <v>-2.308331829153093e-12</v>
+        <v>-1.184161379368201e-11</v>
       </c>
       <c r="H29" t="n">
-        <v>-3.954568372404846e-12</v>
+        <v>-1.13367422113991e-11</v>
       </c>
       <c r="I29" t="n">
-        <v>-8.879141018090029e-12</v>
+        <v>-1.851409215618304e-11</v>
       </c>
     </row>
     <row r="30">
@@ -2108,19 +2108,19 @@
         <v/>
       </c>
       <c r="E30" t="n">
-        <v>-9.895310299309784e-12</v>
+        <v>-2.610393496288255e-11</v>
       </c>
       <c r="F30" t="n">
-        <v>-9.823103814466558e-12</v>
+        <v>-8.293746414462299e-12</v>
       </c>
       <c r="G30" t="n">
-        <v>1.3618326354723e-12</v>
+        <v>3.839055529988133e-13</v>
       </c>
       <c r="H30" t="n">
-        <v>-3.415282764685844e-12</v>
+        <v>-6.189487749700572e-12</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.077325045425067e-11</v>
+        <v>-1.647477377804845e-11</v>
       </c>
     </row>
     <row r="31">
@@ -2143,19 +2143,19 @@
         <v/>
       </c>
       <c r="E31" t="n">
-        <v>-8.320265947573286e-12</v>
+        <v>-2.647674613711317e-11</v>
       </c>
       <c r="F31" t="n">
-        <v>-8.219072439165488e-12</v>
+        <v>-1.507957936805244e-11</v>
       </c>
       <c r="G31" t="n">
-        <v>-3.33643884174925e-12</v>
+        <v>-1.155146738318009e-11</v>
       </c>
       <c r="H31" t="n">
-        <v>6.999244638843131e-13</v>
+        <v>-5.502174027914697e-12</v>
       </c>
       <c r="I31" t="n">
-        <v>-9.801581183270302e-12</v>
+        <v>-1.918695896312168e-11</v>
       </c>
     </row>
     <row r="32">
@@ -2175,22 +2175,22 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-8.773688849237916e-12</v>
+        <v>-2.246746265447055e-11</v>
       </c>
       <c r="E32" t="n">
         <v/>
       </c>
       <c r="F32" t="n">
-        <v>-8.47854922560406e-12</v>
+        <v>-6.207004017356655e-12</v>
       </c>
       <c r="G32" t="n">
-        <v>-2.992244395354313e-12</v>
+        <v>-2.261012074269936e-12</v>
       </c>
       <c r="H32" t="n">
-        <v>5.25463101600051e-13</v>
+        <v>1.771961344102814e-13</v>
       </c>
       <c r="I32" t="n">
-        <v>8.135137709027688e-13</v>
+        <v>9.214262095099883e-13</v>
       </c>
     </row>
     <row r="33">
@@ -2210,22 +2210,22 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-9.214588646259493e-12</v>
+        <v>-2.52541070637471e-11</v>
       </c>
       <c r="E33" t="n">
         <v/>
       </c>
       <c r="F33" t="n">
-        <v>-7.662793330341453e-12</v>
+        <v>-2.780873296573271e-13</v>
       </c>
       <c r="G33" t="n">
-        <v>-3.336370691887008e-12</v>
+        <v>6.244916854562583e-11</v>
       </c>
       <c r="H33" t="n">
-        <v>1.161290077464622e-12</v>
+        <v>3.204204497080095e-12</v>
       </c>
       <c r="I33" t="n">
-        <v>-4.950756258523404e-12</v>
+        <v>2.723321997475401e-11</v>
       </c>
     </row>
     <row r="34">
@@ -2245,22 +2245,22 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-8.831269184411388e-12</v>
+        <v>-2.492311828449002e-11</v>
       </c>
       <c r="E34" t="n">
         <v/>
       </c>
       <c r="F34" t="n">
-        <v>-8.469790252605914e-12</v>
+        <v>-2.944199973576939e-12</v>
       </c>
       <c r="G34" t="n">
-        <v>1.521934774982162e-11</v>
+        <v>8.490779196552646e-11</v>
       </c>
       <c r="H34" t="n">
-        <v>2.170808897850027e-12</v>
+        <v>8.600081624639062e-12</v>
       </c>
       <c r="I34" t="n">
-        <v>-3.030621365024244e-12</v>
+        <v>5.099367694226665e-11</v>
       </c>
     </row>
     <row r="35">
@@ -2280,22 +2280,22 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-9.398568090012188e-12</v>
+        <v>-2.496573138833164e-11</v>
       </c>
       <c r="E35" t="n">
         <v/>
       </c>
       <c r="F35" t="n">
-        <v>-8.978013101376043e-12</v>
+        <v>-1.115459589445084e-11</v>
       </c>
       <c r="G35" t="n">
-        <v>-4.634567991002373e-12</v>
+        <v>2.052739067104875e-11</v>
       </c>
       <c r="H35" t="n">
-        <v>7.654015544782998e-12</v>
+        <v>2.473316946899831e-11</v>
       </c>
       <c r="I35" t="n">
-        <v>-4.104968958415913e-12</v>
+        <v>2.378582200396776e-11</v>
       </c>
     </row>
     <row r="36">
@@ -2315,22 +2315,22 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-9.853890267818632e-12</v>
+        <v>-2.621921380589665e-11</v>
       </c>
       <c r="E36" t="n">
         <v/>
       </c>
       <c r="F36" t="n">
-        <v>-9.029509522959255e-12</v>
+        <v>-1.183180771159139e-11</v>
       </c>
       <c r="G36" t="n">
-        <v>-6.578356476666941e-12</v>
+        <v>4.834359262927933e-11</v>
       </c>
       <c r="H36" t="n">
-        <v>-3.242188143578547e-12</v>
+        <v>-9.527970371581851e-12</v>
       </c>
       <c r="I36" t="n">
-        <v>1.900279282356372e-12</v>
+        <v>9.115337430624441e-11</v>
       </c>
     </row>
     <row r="37">
@@ -2350,22 +2350,22 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1.348624368448632e-11</v>
+        <v>7.149333214431222e-08</v>
       </c>
       <c r="E37" t="n">
         <v/>
       </c>
       <c r="F37" t="n">
-        <v>-7.158368682174508e-12</v>
+        <v>1.760550464640016e-13</v>
       </c>
       <c r="G37" t="n">
-        <v>1.461161300502125e-11</v>
+        <v>5.617993208727526e-11</v>
       </c>
       <c r="H37" t="n">
-        <v>9.509244754871782e-12</v>
+        <v>2.666538278224646e-11</v>
       </c>
       <c r="I37" t="n">
-        <v>1.358611432319459e-11</v>
+        <v>9.60319571309135e-11</v>
       </c>
     </row>
     <row r="38">
@@ -2385,22 +2385,22 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-6.487145928014846e-12</v>
+        <v>9.171847876463956e-11</v>
       </c>
       <c r="E38" t="n">
         <v/>
       </c>
       <c r="F38" t="n">
-        <v>-7.364201659926054e-12</v>
+        <v>4.779856838989358e-10</v>
       </c>
       <c r="G38" t="n">
-        <v>9.909862267120363e-12</v>
+        <v>1.189354355816358e-09</v>
       </c>
       <c r="H38" t="n">
-        <v>8.361748020554197e-12</v>
+        <v>9.502232252289786e-11</v>
       </c>
       <c r="I38" t="n">
-        <v>1.783721174359784e-11</v>
+        <v>3.477754672947561e-10</v>
       </c>
     </row>
     <row r="39">
@@ -2420,22 +2420,22 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-7.042583747593363e-12</v>
+        <v>-1.976238226115868e-11</v>
       </c>
       <c r="E39" t="n">
         <v/>
       </c>
       <c r="F39" t="n">
-        <v>-8.950106673274015e-12</v>
+        <v>2.789273119478635e-11</v>
       </c>
       <c r="G39" t="n">
-        <v>1.825480354021187e-10</v>
+        <v>0.1512976964335687</v>
       </c>
       <c r="H39" t="n">
-        <v>3.011358989942017e-12</v>
+        <v>2.976570223705225e-11</v>
       </c>
       <c r="I39" t="n">
-        <v>4.181955984399974e-12</v>
+        <v>2.677082496817983e-10</v>
       </c>
     </row>
     <row r="40">
@@ -2455,22 +2455,22 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>4.216904675216612e-12</v>
+        <v>-1.216530656933102e-11</v>
       </c>
       <c r="E40" t="n">
         <v/>
       </c>
       <c r="F40" t="n">
-        <v>-1.881806238784987e-12</v>
+        <v>2.589668727451095e-12</v>
       </c>
       <c r="G40" t="n">
-        <v>3.352752862574831e-11</v>
+        <v>6.133868722836477e-11</v>
       </c>
       <c r="H40" t="n">
-        <v>7.27754746569467e-11</v>
+        <v>2.901680246233684e-10</v>
       </c>
       <c r="I40" t="n">
-        <v>2.752493457194828e-11</v>
+        <v>1.064434180176383e-10</v>
       </c>
     </row>
     <row r="41">
@@ -2490,22 +2490,22 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>4.266331811148036e-11</v>
+        <v>-2.535932560259697e-11</v>
       </c>
       <c r="E41" t="n">
         <v/>
       </c>
       <c r="F41" t="n">
-        <v>4.056000488237e-11</v>
+        <v>-4.160862238367848e-12</v>
       </c>
       <c r="G41" t="n">
-        <v>3.08875515903206e-11</v>
+        <v>1.777922993048335e-10</v>
       </c>
       <c r="H41" t="n">
-        <v>8.121670880784533e-12</v>
+        <v>-6.100497526861535e-12</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1507398305837125</v>
+        <v>0.1748626584843367</v>
       </c>
     </row>
     <row r="42">
@@ -2525,22 +2525,22 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-4.027618637006211e-12</v>
+        <v>-2.212126158039726e-11</v>
       </c>
       <c r="E42" t="n">
         <v/>
       </c>
       <c r="F42" t="n">
-        <v>-9.591186002113208e-12</v>
+        <v>-7.015983493198517e-12</v>
       </c>
       <c r="G42" t="n">
-        <v>-3.992160168022464e-12</v>
+        <v>5.25792932813211e-11</v>
       </c>
       <c r="H42" t="n">
-        <v>8.813041305641428e-13</v>
+        <v>6.904439248577098e-12</v>
       </c>
       <c r="I42" t="n">
-        <v>-4.382500257810072e-12</v>
+        <v>4.591527411035112e-11</v>
       </c>
     </row>
     <row r="43">
@@ -2560,22 +2560,22 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-8.794450561140084e-12</v>
+        <v>8.70678681950048e-11</v>
       </c>
       <c r="E43" t="n">
         <v/>
       </c>
       <c r="F43" t="n">
-        <v>-1.01083372870876e-11</v>
+        <v>1.41366110366308e-11</v>
       </c>
       <c r="G43" t="n">
-        <v>-4.354307415273967e-12</v>
+        <v>7.279188165321847e-12</v>
       </c>
       <c r="H43" t="n">
-        <v>-7.086275876909424e-14</v>
+        <v>1.702258837665909e-11</v>
       </c>
       <c r="I43" t="n">
-        <v>4.042924454283079e-12</v>
+        <v>1.563391316109112e-11</v>
       </c>
     </row>
     <row r="44">
@@ -2595,22 +2595,22 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-6.981965979509854e-12</v>
+        <v>-2.452524993813465e-11</v>
       </c>
       <c r="E44" t="n">
         <v/>
       </c>
       <c r="F44" t="n">
-        <v>-8.586086642094387e-12</v>
+        <v>6.291270527295881e-12</v>
       </c>
       <c r="G44" t="n">
-        <v>1.619959896003524e-11</v>
+        <v>1.328390603144198e-09</v>
       </c>
       <c r="H44" t="n">
-        <v>1.860346464922034e-12</v>
+        <v>1.121577725038919e-11</v>
       </c>
       <c r="I44" t="n">
-        <v>-3.97965023107259e-12</v>
+        <v>9.69500067989253e-11</v>
       </c>
     </row>
     <row r="45">
@@ -2630,22 +2630,22 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>-8.150199332800683e-12</v>
+        <v>-2.358341492397804e-11</v>
       </c>
       <c r="E45" t="n">
         <v/>
       </c>
       <c r="F45" t="n">
-        <v>-9.353260892370366e-12</v>
+        <v>-4.670598792276939e-12</v>
       </c>
       <c r="G45" t="n">
-        <v>-4.368612861482046e-12</v>
+        <v>5.772923156528802e-11</v>
       </c>
       <c r="H45" t="n">
-        <v>9.093868723887889e-12</v>
+        <v>6.575100982421754e-11</v>
       </c>
       <c r="I45" t="n">
-        <v>-3.230300270077418e-12</v>
+        <v>5.752833544446118e-11</v>
       </c>
     </row>
     <row r="46">
@@ -2665,22 +2665,22 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>-7.487723172956772e-12</v>
+        <v>-2.544742137154831e-11</v>
       </c>
       <c r="E46" t="n">
         <v/>
       </c>
       <c r="F46" t="n">
-        <v>-7.998801890393465e-12</v>
+        <v>-8.242670997715776e-12</v>
       </c>
       <c r="G46" t="n">
-        <v>-5.650656860476095e-12</v>
+        <v>1.907358236569441e-10</v>
       </c>
       <c r="H46" t="n">
-        <v>-2.594486463642038e-12</v>
+        <v>-9.063223507464176e-12</v>
       </c>
       <c r="I46" t="n">
-        <v>7.472855679831887e-13</v>
+        <v>2.202753335498146e-10</v>
       </c>
     </row>
     <row r="47">
@@ -2700,22 +2700,22 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-3.937640027149871e-12</v>
+        <v>-2.298385262737955e-11</v>
       </c>
       <c r="E47" t="n">
         <v/>
       </c>
       <c r="F47" t="n">
-        <v>-8.840253242457342e-12</v>
+        <v>-2.894513402582874e-12</v>
       </c>
       <c r="G47" t="n">
-        <v>-7.513727750897413e-12</v>
+        <v>4.343283452489355e-11</v>
       </c>
       <c r="H47" t="n">
-        <v>1.797352747785981e-12</v>
+        <v>6.780693368571739e-12</v>
       </c>
       <c r="I47" t="n">
-        <v>-4.557946047153962e-12</v>
+        <v>3.150001300299471e-11</v>
       </c>
     </row>
     <row r="48">
@@ -2735,22 +2735,22 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-9.553212824485616e-12</v>
+        <v>-2.174519845100084e-11</v>
       </c>
       <c r="E48" t="n">
         <v/>
       </c>
       <c r="F48" t="n">
-        <v>-1.008525634840271e-11</v>
+        <v>5.882576838671305e-12</v>
       </c>
       <c r="G48" t="n">
-        <v>-8.614512882322293e-12</v>
+        <v>2.47463626252501e-12</v>
       </c>
       <c r="H48" t="n">
-        <v>-2.678334157128324e-12</v>
+        <v>-3.929117678794021e-13</v>
       </c>
       <c r="I48" t="n">
-        <v>-4.297613322677601e-12</v>
+        <v>9.065769894363263e-13</v>
       </c>
     </row>
     <row r="49">
@@ -2770,22 +2770,22 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-7.367501783533301e-12</v>
+        <v>-2.483802070178098e-11</v>
       </c>
       <c r="E49" t="n">
         <v/>
       </c>
       <c r="F49" t="n">
-        <v>-6.144574463089558e-12</v>
+        <v>2.841431808774996e-11</v>
       </c>
       <c r="G49" t="n">
-        <v>-7.033770977454184e-12</v>
+        <v>1.861514665300926e-10</v>
       </c>
       <c r="H49" t="n">
-        <v>2.090830448441715e-12</v>
+        <v>4.893298672682964e-12</v>
       </c>
       <c r="I49" t="n">
-        <v>-5.687076338555642e-12</v>
+        <v>3.147478509978264e-11</v>
       </c>
     </row>
     <row r="50">
@@ -2805,22 +2805,22 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-9.743747874764248e-12</v>
+        <v>-2.417164179275057e-11</v>
       </c>
       <c r="E50" t="n">
         <v/>
       </c>
       <c r="F50" t="n">
-        <v>-1.012214691737176e-11</v>
+        <v>-2.435618421820755e-12</v>
       </c>
       <c r="G50" t="n">
-        <v>-8.80889085574071e-12</v>
+        <v>4.342900622811758e-11</v>
       </c>
       <c r="H50" t="n">
-        <v>3.621577432809258e-12</v>
+        <v>3.881679466407714e-11</v>
       </c>
       <c r="I50" t="n">
-        <v>-5.688261950966782e-12</v>
+        <v>3.123665509882629e-11</v>
       </c>
     </row>
     <row r="51">
@@ -2840,22 +2840,22 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>-1.004983391557203e-11</v>
+        <v>-2.563877688320901e-11</v>
       </c>
       <c r="E51" t="n">
         <v/>
       </c>
       <c r="F51" t="n">
-        <v>-1.011089185025438e-11</v>
+        <v>4.226598478008816e-13</v>
       </c>
       <c r="G51" t="n">
-        <v>-9.365269458220394e-12</v>
+        <v>1.451905002420831e-10</v>
       </c>
       <c r="H51" t="n">
-        <v>-3.532267454777617e-12</v>
+        <v>-4.261893872740633e-12</v>
       </c>
       <c r="I51" t="n">
-        <v>3.206498424475474e-12</v>
+        <v>3.776701326160373e-10</v>
       </c>
     </row>
     <row r="52">
@@ -2875,22 +2875,22 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>-3.027517995132379e-12</v>
+        <v>-2.262897176197638e-11</v>
       </c>
       <c r="E52" t="n">
         <v/>
       </c>
       <c r="F52" t="n">
-        <v>-8.790401199066002e-12</v>
+        <v>-1.113341576998017e-11</v>
       </c>
       <c r="G52" t="n">
-        <v>-1.564126386790425e-12</v>
+        <v>2.091350199863275e-11</v>
       </c>
       <c r="H52" t="n">
-        <v>-1.259346396390317e-12</v>
+        <v>-3.491220280753358e-12</v>
       </c>
       <c r="I52" t="n">
-        <v>-2.911748493096952e-12</v>
+        <v>2.616751774908712e-11</v>
       </c>
     </row>
     <row r="53">
@@ -2910,22 +2910,22 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>-2.34592240922979e-12</v>
+        <v>-1.71665638966024e-11</v>
       </c>
       <c r="E53" t="n">
         <v/>
       </c>
       <c r="F53" t="n">
-        <v>-4.100819250114763e-12</v>
+        <v>-5.221235825431453e-12</v>
       </c>
       <c r="G53" t="n">
-        <v>6.745547793997939e-12</v>
+        <v>-1.756038270450987e-12</v>
       </c>
       <c r="H53" t="n">
-        <v>1.104451046198211e-12</v>
+        <v>-4.543697468897777e-12</v>
       </c>
       <c r="I53" t="n">
-        <v>9.042273390874016e-12</v>
+        <v>2.219204742066074e-12</v>
       </c>
     </row>
     <row r="54">
@@ -2945,22 +2945,22 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-7.528225717918576e-12</v>
+        <v>-2.401043869703441e-11</v>
       </c>
       <c r="E54" t="n">
         <v/>
       </c>
       <c r="F54" t="n">
-        <v>-6.998408118947596e-12</v>
+        <v>3.003456179814342e-12</v>
       </c>
       <c r="G54" t="n">
-        <v>-1.97642981842868e-13</v>
+        <v>6.642744599908534e-11</v>
       </c>
       <c r="H54" t="n">
-        <v>-5.807475453134418e-13</v>
+        <v>-5.098315268338756e-13</v>
       </c>
       <c r="I54" t="n">
-        <v>-2.735804847330973e-12</v>
+        <v>3.587296472238284e-11</v>
       </c>
     </row>
     <row r="55">
@@ -2980,22 +2980,22 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-8.963249914223538e-12</v>
+        <v>-2.396148667700268e-11</v>
       </c>
       <c r="E55" t="n">
         <v/>
       </c>
       <c r="F55" t="n">
-        <v>-9.719194083772392e-12</v>
+        <v>-2.327956271286725e-12</v>
       </c>
       <c r="G55" t="n">
-        <v>1.146576739991167e-11</v>
+        <v>8.766396554607094e-11</v>
       </c>
       <c r="H55" t="n">
-        <v>-2.629590979882315e-12</v>
+        <v>2.520498551433558e-13</v>
       </c>
       <c r="I55" t="n">
-        <v>-3.338344579032408e-12</v>
+        <v>5.637196398148653e-11</v>
       </c>
     </row>
     <row r="56">
@@ -3015,22 +3015,22 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-8.704316783744903e-12</v>
+        <v>-2.60366545142928e-11</v>
       </c>
       <c r="E56" t="n">
         <v/>
       </c>
       <c r="F56" t="n">
-        <v>-8.696988621360351e-12</v>
+        <v>-1.195193109402557e-11</v>
       </c>
       <c r="G56" t="n">
-        <v>-5.508441858122587e-12</v>
+        <v>4.785002689598492e-11</v>
       </c>
       <c r="H56" t="n">
-        <v>-4.795228301859591e-12</v>
+        <v>-1.22364621269749e-11</v>
       </c>
       <c r="I56" t="n">
-        <v>3.27230009112533e-12</v>
+        <v>9.237104422022118e-11</v>
       </c>
     </row>
     <row r="57">
@@ -3050,22 +3050,22 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>-1.728725257074258e-12</v>
+        <v>-2.514800715574353e-11</v>
       </c>
       <c r="E57" t="n">
         <v/>
       </c>
       <c r="F57" t="n">
-        <v>-8.238446306808734e-12</v>
+        <v>-1.155594003589443e-11</v>
       </c>
       <c r="G57" t="n">
-        <v>-3.86379050459698e-12</v>
+        <v>4.086136984478308e-11</v>
       </c>
       <c r="H57" t="n">
-        <v>-2.659165758903037e-12</v>
+        <v>-9.672613765538966e-12</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.110647305646199e-11</v>
+        <v>-5.527242560222088e-12</v>
       </c>
     </row>
     <row r="58">
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2.946726463332756e-11</v>
+        <v>-2.568717630713048e-11</v>
       </c>
       <c r="E58" t="n">
         <v/>
       </c>
       <c r="F58" t="n">
-        <v>3.277298201817243e-11</v>
+        <v>-8.49699297865307e-12</v>
       </c>
       <c r="G58" t="n">
-        <v>9.215501453274466e-12</v>
+        <v>2.007393770974105e-12</v>
       </c>
       <c r="H58" t="n">
-        <v>1.119314505269241e-12</v>
+        <v>-1.218178893932623e-11</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.041160013339622e-11</v>
+        <v>-1.221671130008417e-11</v>
       </c>
     </row>
     <row r="59">
@@ -3120,22 +3120,22 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>-4.844495607688692e-12</v>
+        <v>-2.622539192077402e-11</v>
       </c>
       <c r="E59" t="n">
         <v/>
       </c>
       <c r="F59" t="n">
-        <v>-2.262193420379885e-12</v>
+        <v>-4.238711155925126e-12</v>
       </c>
       <c r="G59" t="n">
-        <v>-1.508215960935025e-12</v>
+        <v>1.323317029222635e-10</v>
       </c>
       <c r="H59" t="n">
-        <v>-1.862950904138786e-12</v>
+        <v>-1.077940297405817e-11</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.126581503656471e-11</v>
+        <v>-6.053574026719726e-12</v>
       </c>
     </row>
     <row r="60">
@@ -3155,22 +3155,22 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>-8.832867600098365e-12</v>
+        <v>-2.56913562468572e-11</v>
       </c>
       <c r="E60" t="n">
         <v/>
       </c>
       <c r="F60" t="n">
-        <v>-9.577945169658518e-12</v>
+        <v>4.775774724781195e-13</v>
       </c>
       <c r="G60" t="n">
-        <v>4.715684899215489e-12</v>
+        <v>3.966371897143478e-10</v>
       </c>
       <c r="H60" t="n">
-        <v>-3.113764355325342e-12</v>
+        <v>-3.997629901407194e-12</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.085773904341874e-11</v>
+        <v>7.642654030247045e-13</v>
       </c>
     </row>
     <row r="61">
@@ -3190,22 +3190,22 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>-7.493622197782639e-12</v>
+        <v>-2.610994410193399e-11</v>
       </c>
       <c r="E61" t="n">
         <v/>
       </c>
       <c r="F61" t="n">
-        <v>-7.970584122868228e-12</v>
+        <v>-1.195725154005103e-11</v>
       </c>
       <c r="G61" t="n">
-        <v>-4.774352950304565e-12</v>
+        <v>3.807458647638946e-11</v>
       </c>
       <c r="H61" t="n">
-        <v>4.740670304765253e-13</v>
+        <v>-4.581190670061632e-12</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.11727278308762e-11</v>
+        <v>-5.991535153775088e-12</v>
       </c>
     </row>
     <row r="62">
@@ -3225,22 +3225,22 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>-9.408785469169345e-12</v>
+        <v>-1.219565813894915e-11</v>
       </c>
       <c r="E62" t="n">
-        <v>-9.070737101815118e-12</v>
+        <v>6.322545319238239e-13</v>
       </c>
       <c r="F62" t="n">
         <v/>
       </c>
       <c r="G62" t="n">
-        <v>1.972891183642051e-12</v>
+        <v>2.530893639207546e-10</v>
       </c>
       <c r="H62" t="n">
-        <v>1.640224816930182e-12</v>
+        <v>3.874705064993068e-12</v>
       </c>
       <c r="I62" t="n">
-        <v>1.065642574437119e-10</v>
+        <v>6.178898660418252e-10</v>
       </c>
     </row>
     <row r="63">
@@ -3260,22 +3260,22 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>-4.368392432582422e-12</v>
+        <v>-1.224320329239846e-11</v>
       </c>
       <c r="E63" t="n">
-        <v>-3.479896820631635e-12</v>
+        <v>-6.968433097729496e-12</v>
       </c>
       <c r="F63" t="n">
         <v/>
       </c>
       <c r="G63" t="n">
-        <v>1.055520370559705e-12</v>
+        <v>-1.609841727375064e-13</v>
       </c>
       <c r="H63" t="n">
-        <v>1.255730555275998e-12</v>
+        <v>-8.438009404712036e-13</v>
       </c>
       <c r="I63" t="n">
-        <v>5.506979270108505e-13</v>
+        <v>1.35490364648446e-12</v>
       </c>
     </row>
     <row r="64">
@@ -3295,22 +3295,22 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>-8.916612187532657e-12</v>
+        <v>-1.070936912701949e-11</v>
       </c>
       <c r="E64" t="n">
-        <v>-8.64159596011545e-12</v>
+        <v>-3.349905906593549e-12</v>
       </c>
       <c r="F64" t="n">
         <v/>
       </c>
       <c r="G64" t="n">
-        <v>2.889745913267483e-11</v>
+        <v>2.891852122936442e-10</v>
       </c>
       <c r="H64" t="n">
-        <v>2.102447063728519e-12</v>
+        <v>7.706271816357955e-12</v>
       </c>
       <c r="I64" t="n">
-        <v>9.678329695929546e-11</v>
+        <v>7.953654233464686e-10</v>
       </c>
     </row>
     <row r="65">
@@ -3330,22 +3330,22 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>-9.125828170571485e-12</v>
+        <v>-1.496373587753474e-11</v>
       </c>
       <c r="E65" t="n">
-        <v>-8.903489510084835e-12</v>
+        <v>-1.137759259493626e-11</v>
       </c>
       <c r="F65" t="n">
         <v/>
       </c>
       <c r="G65" t="n">
-        <v>3.542672800870787e-12</v>
+        <v>1.061777031396214e-10</v>
       </c>
       <c r="H65" t="n">
-        <v>1.021169140980958e-11</v>
+        <v>2.131538577219962e-11</v>
       </c>
       <c r="I65" t="n">
-        <v>9.349658331654846e-11</v>
+        <v>4.384445770654197e-10</v>
       </c>
     </row>
     <row r="66">
@@ -3365,22 +3365,22 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>-9.181914666714512e-12</v>
+        <v>-1.643620808196607e-11</v>
       </c>
       <c r="E66" t="n">
-        <v>-8.651203410252004e-12</v>
+        <v>-1.20409872712892e-11</v>
       </c>
       <c r="F66" t="n">
         <v/>
       </c>
       <c r="G66" t="n">
-        <v>-3.141066045051867e-12</v>
+        <v>2.194144998546787e-10</v>
       </c>
       <c r="H66" t="n">
-        <v>-3.547764032642585e-12</v>
+        <v>-1.020711327149125e-11</v>
       </c>
       <c r="I66" t="n">
-        <v>5.910524148899551e-10</v>
+        <v>1.03029654212677e-09</v>
       </c>
     </row>
     <row r="67">
@@ -3400,22 +3400,22 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>-6.325688436464735e-12</v>
+        <v>5.133860950255988e-11</v>
       </c>
       <c r="E67" t="n">
-        <v>-9.22896809559395e-12</v>
+        <v>-7.213340324440656e-12</v>
       </c>
       <c r="F67" t="n">
         <v/>
       </c>
       <c r="G67" t="n">
-        <v>4.56823095742037e-12</v>
+        <v>1.91038335538023e-10</v>
       </c>
       <c r="H67" t="n">
-        <v>9.85486937948476e-13</v>
+        <v>7.929557730697553e-12</v>
       </c>
       <c r="I67" t="n">
-        <v>7.90698222174657e-11</v>
+        <v>7.055799883968218e-10</v>
       </c>
     </row>
     <row r="68">
@@ -3435,22 +3435,22 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>-6.48684131869521e-12</v>
+        <v>2.986100651531016e-11</v>
       </c>
       <c r="E68" t="n">
-        <v>-7.130287893411611e-12</v>
+        <v>1.378095446403172e-11</v>
       </c>
       <c r="F68" t="n">
         <v/>
       </c>
       <c r="G68" t="n">
-        <v>2.845953514902505e-12</v>
+        <v>2.99865255714681e-12</v>
       </c>
       <c r="H68" t="n">
-        <v>8.722449547392165e-13</v>
+        <v>1.634230359218023e-11</v>
       </c>
       <c r="I68" t="n">
-        <v>2.155981432442095e-13</v>
+        <v>2.484298601760688e-12</v>
       </c>
     </row>
     <row r="69">
@@ -3470,22 +3470,22 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>-1.016479816700016e-11</v>
+        <v>7.838282035482705e-12</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.036023980655818e-11</v>
+        <v>4.446656230586588e-12</v>
       </c>
       <c r="F69" t="n">
         <v/>
       </c>
       <c r="G69" t="n">
-        <v>1.311955953692874e-11</v>
+        <v>6.688005301227381e-09</v>
       </c>
       <c r="H69" t="n">
-        <v>-2.285297861058264e-12</v>
+        <v>7.337701225060303e-12</v>
       </c>
       <c r="I69" t="n">
-        <v>6.172041904039852e-11</v>
+        <v>1.790069956089822e-09</v>
       </c>
     </row>
     <row r="70">
@@ -3505,22 +3505,22 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>-6.10149007759322e-12</v>
+        <v>-3.475374532174636e-12</v>
       </c>
       <c r="E70" t="n">
-        <v>-6.529437840481954e-12</v>
+        <v>-6.075646758845659e-12</v>
       </c>
       <c r="F70" t="n">
         <v/>
       </c>
       <c r="G70" t="n">
-        <v>7.930761131950438e-12</v>
+        <v>2.027038772783739e-10</v>
       </c>
       <c r="H70" t="n">
-        <v>1.621564081804435e-11</v>
+        <v>4.048202855866445e-11</v>
       </c>
       <c r="I70" t="n">
-        <v>9.629565108989083e-11</v>
+        <v>7.385481096475596e-10</v>
       </c>
     </row>
     <row r="71">
@@ -3540,22 +3540,22 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2.614487505478487e-12</v>
+        <v>-1.093097913327097e-11</v>
       </c>
       <c r="E71" t="n">
-        <v>4.768432823188081e-12</v>
+        <v>-9.809635036282624e-12</v>
       </c>
       <c r="F71" t="n">
         <v/>
       </c>
       <c r="G71" t="n">
-        <v>-1.277552003735417e-12</v>
+        <v>7.816055084061548e-10</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.608507613109465e-12</v>
+        <v>-1.07554406746388e-11</v>
       </c>
       <c r="I71" t="n">
-        <v>1.908302033620437e-09</v>
+        <v>2.742407033177936e-09</v>
       </c>
     </row>
     <row r="72">
@@ -3575,22 +3575,22 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>-4.385009436503646e-12</v>
+        <v>9.580887343357152e-10</v>
       </c>
       <c r="E72" t="n">
-        <v>-3.214519985024296e-12</v>
+        <v>-1.515875987237702e-13</v>
       </c>
       <c r="F72" t="n">
         <v/>
       </c>
       <c r="G72" t="n">
-        <v>2.736439777843704e-11</v>
+        <v>2.057580630445692e-10</v>
       </c>
       <c r="H72" t="n">
-        <v>1.291407767518251e-11</v>
+        <v>1.980920742639763e-11</v>
       </c>
       <c r="I72" t="n">
-        <v>5.795527850541729e-10</v>
+        <v>8.60754165722309e-10</v>
       </c>
     </row>
     <row r="73">
@@ -3610,22 +3610,22 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>-5.605831291563514e-12</v>
+        <v>1.081219854790591e-10</v>
       </c>
       <c r="E73" t="n">
-        <v>-6.536922020489851e-12</v>
+        <v>4.934726991550212e-10</v>
       </c>
       <c r="F73" t="n">
         <v/>
       </c>
       <c r="G73" t="n">
-        <v>2.528150568609302e-11</v>
+        <v>5.431310875515554e-09</v>
       </c>
       <c r="H73" t="n">
-        <v>1.408350182103699e-11</v>
+        <v>6.807480465339172e-11</v>
       </c>
       <c r="I73" t="n">
-        <v>1.761443134877485e-09</v>
+        <v>3.579281517466278e-09</v>
       </c>
     </row>
     <row r="74">
@@ -3645,22 +3645,22 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>5.280039003590173e-12</v>
+        <v>3.995291530660954e-11</v>
       </c>
       <c r="E74" t="n">
-        <v>1.658900514445116e-12</v>
+        <v>2.923770396170841e-11</v>
       </c>
       <c r="F74" t="n">
         <v/>
       </c>
       <c r="G74" t="n">
-        <v>-1.073196316589763e-11</v>
+        <v>0.1639645356674524</v>
       </c>
       <c r="H74" t="n">
-        <v>1.326996166140504e-11</v>
+        <v>2.443171993681034e-11</v>
       </c>
       <c r="I74" t="n">
-        <v>6.482353142961035e-10</v>
+        <v>3.60455121322542e-09</v>
       </c>
     </row>
     <row r="75">
@@ -3680,22 +3680,22 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1.228485392439802e-12</v>
+        <v>9.931531605610744e-12</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.608667945347284e-12</v>
+        <v>3.92911681919733e-12</v>
       </c>
       <c r="F75" t="n">
         <v/>
       </c>
       <c r="G75" t="n">
-        <v>3.601317736127342e-11</v>
+        <v>2.182156087584199e-10</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.674917111768755e-12</v>
+        <v>1.958708989706166e-10</v>
       </c>
       <c r="I75" t="n">
-        <v>9.463350493162063e-10</v>
+        <v>9.767364083888732e-10</v>
       </c>
     </row>
     <row r="76">
@@ -3715,22 +3715,22 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1.68436867369695e-11</v>
+        <v>-4.528938369850443e-12</v>
       </c>
       <c r="E76" t="n">
-        <v>1.46748707795425e-11</v>
+        <v>-2.518607543127918e-12</v>
       </c>
       <c r="F76" t="n">
         <v/>
       </c>
       <c r="G76" t="n">
-        <v>3.781194552766498e-12</v>
+        <v>1.439025665086619e-09</v>
       </c>
       <c r="H76" t="n">
-        <v>1.737497165772157e-12</v>
+        <v>-7.191055059384405e-12</v>
       </c>
       <c r="I76" t="n">
-        <v>7.554457810942575e-13</v>
+        <v>0.2973394973009117</v>
       </c>
     </row>
     <row r="77">
@@ -3750,22 +3750,22 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>-5.517858309603315e-12</v>
+        <v>3.761584943463705e-11</v>
       </c>
       <c r="E77" t="n">
-        <v>-8.730000046845511e-12</v>
+        <v>-2.914762077448994e-12</v>
       </c>
       <c r="F77" t="n">
         <v/>
       </c>
       <c r="G77" t="n">
-        <v>-2.489976236208991e-12</v>
+        <v>1.824051248289736e-10</v>
       </c>
       <c r="H77" t="n">
-        <v>2.693859628219133e-12</v>
+        <v>6.700302787816376e-12</v>
       </c>
       <c r="I77" t="n">
-        <v>9.959926822181975e-11</v>
+        <v>5.9795296081754e-10</v>
       </c>
     </row>
     <row r="78">
@@ -3785,22 +3785,22 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>-1.03209917983152e-11</v>
+        <v>-1.175832110374955e-12</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.036044950438105e-11</v>
+        <v>2.616676079150623e-11</v>
       </c>
       <c r="F78" t="n">
         <v/>
       </c>
       <c r="G78" t="n">
-        <v>-5.131382921360361e-12</v>
+        <v>9.6802172764193e-10</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.615666887519306e-12</v>
+        <v>2.317816246126733e-12</v>
       </c>
       <c r="I78" t="n">
-        <v>8.042808668786063e-11</v>
+        <v>8.225063552440428e-10</v>
       </c>
     </row>
     <row r="79">
@@ -3820,22 +3820,22 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>2.066633412003892e-12</v>
+        <v>1.141443842104217e-12</v>
       </c>
       <c r="E79" t="n">
-        <v>1.636172935393892e-12</v>
+        <v>7.142772842583785e-12</v>
       </c>
       <c r="F79" t="n">
         <v/>
       </c>
       <c r="G79" t="n">
-        <v>-3.898005280833131e-12</v>
+        <v>2.090495433094005e-12</v>
       </c>
       <c r="H79" t="n">
-        <v>2.170413556824124e-12</v>
+        <v>-7.668549635568653e-14</v>
       </c>
       <c r="I79" t="n">
-        <v>6.850838914368913e-13</v>
+        <v>1.731532588718119e-12</v>
       </c>
     </row>
     <row r="80">
@@ -3855,22 +3855,22 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>-9.83000712111249e-12</v>
+        <v>-5.953665352240586e-12</v>
       </c>
       <c r="E80" t="n">
-        <v>-9.990446395273703e-12</v>
+        <v>-2.651484514340792e-12</v>
       </c>
       <c r="F80" t="n">
         <v/>
       </c>
       <c r="G80" t="n">
-        <v>-3.700339465502053e-12</v>
+        <v>1.819289120123292e-10</v>
       </c>
       <c r="H80" t="n">
-        <v>6.509567428245468e-12</v>
+        <v>3.147547850860415e-11</v>
       </c>
       <c r="I80" t="n">
-        <v>8.165810354593408e-11</v>
+        <v>5.922934137284969e-10</v>
       </c>
     </row>
     <row r="81">
@@ -3890,22 +3890,22 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>-9.797188180638797e-12</v>
+        <v>-6.35679862582598e-12</v>
       </c>
       <c r="E81" t="n">
-        <v>-9.77255795938182e-12</v>
+        <v>1.717995307313529e-13</v>
       </c>
       <c r="F81" t="n">
         <v/>
       </c>
       <c r="G81" t="n">
-        <v>-5.857749691038355e-12</v>
+        <v>8.025335952940798e-10</v>
       </c>
       <c r="H81" t="n">
-        <v>-3.258973164415831e-12</v>
+        <v>-5.446962883205999e-12</v>
       </c>
       <c r="I81" t="n">
-        <v>6.578123069997215e-10</v>
+        <v>5.422931431787704e-09</v>
       </c>
     </row>
     <row r="82">
@@ -3925,22 +3925,22 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>-5.938316014179939e-12</v>
+        <v>2.849304214472199e-12</v>
       </c>
       <c r="E82" t="n">
-        <v>-8.922505345230617e-12</v>
+        <v>-1.118985580572481e-11</v>
       </c>
       <c r="F82" t="n">
         <v/>
       </c>
       <c r="G82" t="n">
-        <v>5.963866780390914e-12</v>
+        <v>1.071033872400481e-10</v>
       </c>
       <c r="H82" t="n">
-        <v>-1.410854786301849e-12</v>
+        <v>-2.40425227281056e-12</v>
       </c>
       <c r="I82" t="n">
-        <v>1.045248011845105e-10</v>
+        <v>4.554851923050948e-10</v>
       </c>
     </row>
     <row r="83">
@@ -3960,22 +3960,22 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>-6.006140174840043e-12</v>
+        <v>-7.096260235564871e-12</v>
       </c>
       <c r="E83" t="n">
-        <v>-5.82535525857515e-12</v>
+        <v>2.323598195176411e-12</v>
       </c>
       <c r="F83" t="n">
         <v/>
       </c>
       <c r="G83" t="n">
-        <v>7.526274484087412e-12</v>
+        <v>2.598584313305191e-10</v>
       </c>
       <c r="H83" t="n">
-        <v>1.041310899323861e-12</v>
+        <v>-1.144713173962718e-12</v>
       </c>
       <c r="I83" t="n">
-        <v>1.643445699400753e-10</v>
+        <v>6.591448992304301e-10</v>
       </c>
     </row>
     <row r="84">
@@ -3995,22 +3995,22 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>-1.71577170508039e-12</v>
+        <v>-5.796522732503674e-12</v>
       </c>
       <c r="E84" t="n">
-        <v>-2.258261174253236e-12</v>
+        <v>-4.784709917676225e-12</v>
       </c>
       <c r="F84" t="n">
         <v/>
       </c>
       <c r="G84" t="n">
-        <v>4.155919191532962e-12</v>
+        <v>4.786696020280699e-14</v>
       </c>
       <c r="H84" t="n">
-        <v>-9.376710319524367e-13</v>
+        <v>-2.784976110030855e-12</v>
       </c>
       <c r="I84" t="n">
-        <v>9.119561311335255e-13</v>
+        <v>1.578862625958269e-12</v>
       </c>
     </row>
     <row r="85">
@@ -4030,22 +4030,22 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>-9.777230434400238e-12</v>
+        <v>-4.936793824096268e-12</v>
       </c>
       <c r="E85" t="n">
-        <v>-9.916597406888169e-12</v>
+        <v>-2.557479716251279e-12</v>
       </c>
       <c r="F85" t="n">
         <v/>
       </c>
       <c r="G85" t="n">
-        <v>2.534746016008125e-11</v>
+        <v>2.964078637128363e-10</v>
       </c>
       <c r="H85" t="n">
-        <v>-2.840948811704343e-12</v>
+        <v>7.342968474602742e-13</v>
       </c>
       <c r="I85" t="n">
-        <v>8.832801965071906e-11</v>
+        <v>8.431828911545241e-10</v>
       </c>
     </row>
     <row r="86">
@@ -4065,22 +4065,22 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>-8.578822073806106e-12</v>
+        <v>-1.444215303802371e-11</v>
       </c>
       <c r="E86" t="n">
-        <v>-8.397016696794851e-12</v>
+        <v>-1.209102943194886e-11</v>
       </c>
       <c r="F86" t="n">
         <v/>
       </c>
       <c r="G86" t="n">
-        <v>-2.644010735541679e-12</v>
+        <v>2.178475297743594e-10</v>
       </c>
       <c r="H86" t="n">
-        <v>-5.327766442525556e-12</v>
+        <v>-1.245109895629637e-11</v>
       </c>
       <c r="I86" t="n">
-        <v>8.849673650526488e-10</v>
+        <v>1.042375188175938e-09</v>
       </c>
     </row>
     <row r="87">
@@ -4100,22 +4100,22 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>-5.473332859792194e-12</v>
+        <v>-5.063067829997437e-12</v>
       </c>
       <c r="E87" t="n">
-        <v>-8.650929329837253e-12</v>
+        <v>-1.164415290130758e-11</v>
       </c>
       <c r="F87" t="n">
         <v/>
       </c>
       <c r="G87" t="n">
-        <v>-3.079041837387995e-12</v>
+        <v>1.814008843846664e-10</v>
       </c>
       <c r="H87" t="n">
-        <v>-3.520239642118267e-12</v>
+        <v>-1.018936723070362e-11</v>
       </c>
       <c r="I87" t="n">
-        <v>2.570057385848624e-11</v>
+        <v>2.635790049854487e-10</v>
       </c>
     </row>
     <row r="88">
@@ -4135,22 +4135,22 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>4.877418239255797e-12</v>
+        <v>-1.3022690607186e-11</v>
       </c>
       <c r="E88" t="n">
-        <v>8.28664059316076e-12</v>
+        <v>-3.585406637832523e-12</v>
       </c>
       <c r="F88" t="n">
         <v/>
       </c>
       <c r="G88" t="n">
-        <v>-2.462335294825126e-12</v>
+        <v>9.54071276598512e-10</v>
       </c>
       <c r="H88" t="n">
-        <v>-9.698034134001419e-13</v>
+        <v>-1.178646235923305e-11</v>
       </c>
       <c r="I88" t="n">
-        <v>3.282347516240752e-11</v>
+        <v>3.002667479316e-10</v>
       </c>
     </row>
     <row r="89">
@@ -4170,22 +4170,22 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1.050441457953119e-11</v>
+        <v>-1.289428976810786e-11</v>
       </c>
       <c r="E89" t="n">
-        <v>1.123225677501817e-11</v>
+        <v>-9.083020814124178e-12</v>
       </c>
       <c r="F89" t="n">
         <v/>
       </c>
       <c r="G89" t="n">
-        <v>-4.159404025510073e-12</v>
+        <v>1.747072779967747e-12</v>
       </c>
       <c r="H89" t="n">
-        <v>-3.36080647729436e-12</v>
+        <v>-1.259445781208267e-11</v>
       </c>
       <c r="I89" t="n">
-        <v>-2.363297556463798e-12</v>
+        <v>-1.829216022214976e-13</v>
       </c>
     </row>
     <row r="90">
@@ -4205,22 +4205,22 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>-9.82081021280168e-12</v>
+        <v>-6.874037202661255e-12</v>
       </c>
       <c r="E90" t="n">
-        <v>-9.957748311884848e-12</v>
+        <v>1.381120035388394e-13</v>
       </c>
       <c r="F90" t="n">
         <v/>
       </c>
       <c r="G90" t="n">
-        <v>3.998359183322618e-12</v>
+        <v>2.150968586822984e-09</v>
       </c>
       <c r="H90" t="n">
-        <v>-3.746961490704635e-12</v>
+        <v>-5.240040661712158e-12</v>
       </c>
       <c r="I90" t="n">
-        <v>2.511579940012633e-11</v>
+        <v>4.042462103497583e-10</v>
       </c>
     </row>
     <row r="91">
@@ -4240,22 +4240,22 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>-8.187440425192965e-12</v>
+        <v>-1.495356861681892e-11</v>
       </c>
       <c r="E91" t="n">
-        <v>-8.287694190135871e-12</v>
+        <v>-1.212071406436196e-11</v>
       </c>
       <c r="F91" t="n">
         <v/>
       </c>
       <c r="G91" t="n">
-        <v>-3.436761948274495e-12</v>
+        <v>1.722389778294714e-10</v>
       </c>
       <c r="H91" t="n">
-        <v>-4.077030629950829e-13</v>
+        <v>-6.303328191273513e-12</v>
       </c>
       <c r="I91" t="n">
-        <v>2.529132469072868e-11</v>
+        <v>2.557445246617921e-10</v>
       </c>
     </row>
     <row r="92">
@@ -4275,22 +4275,22 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>-2.8975892742096e-12</v>
+        <v>-3.552230388838961e-12</v>
       </c>
       <c r="E92" t="n">
-        <v>8.441450126251004e-12</v>
+        <v>8.135731350593653e-11</v>
       </c>
       <c r="F92" t="n">
-        <v>4.307707615418214e-12</v>
+        <v>2.661588604088594e-10</v>
       </c>
       <c r="G92" t="n">
         <v/>
       </c>
       <c r="H92" t="n">
-        <v>5.943563489157844e-12</v>
+        <v>1.075908936640099e-11</v>
       </c>
       <c r="I92" t="n">
-        <v>5.735279650001962e-12</v>
+        <v>3.288940569855002e-10</v>
       </c>
     </row>
     <row r="93">
@@ -4310,22 +4310,22 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>-3.178550469041701e-12</v>
+        <v>-4.503345697068115e-12</v>
       </c>
       <c r="E93" t="n">
-        <v>-4.186551400306686e-12</v>
+        <v>6.743720385718219e-11</v>
       </c>
       <c r="F93" t="n">
-        <v>1.984264924573402e-11</v>
+        <v>2.777983892632817e-10</v>
       </c>
       <c r="G93" t="n">
         <v/>
       </c>
       <c r="H93" t="n">
-        <v>4.916244586009863e-12</v>
+        <v>8.887294964239147e-12</v>
       </c>
       <c r="I93" t="n">
-        <v>4.104463510856189e-12</v>
+        <v>3.35042248125945e-10</v>
       </c>
     </row>
     <row r="94">
@@ -4345,22 +4345,22 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1.484972387090625e-14</v>
+        <v>-4.040738801693473e-12</v>
       </c>
       <c r="E94" t="n">
-        <v>5.370664509684756e-12</v>
+        <v>-2.172889850118085e-12</v>
       </c>
       <c r="F94" t="n">
-        <v>4.713649046071252e-12</v>
+        <v>-1.612609077529268e-13</v>
       </c>
       <c r="G94" t="n">
         <v/>
       </c>
       <c r="H94" t="n">
-        <v>4.381625753612211e-12</v>
+        <v>8.339817896929213e-12</v>
       </c>
       <c r="I94" t="n">
-        <v>4.447205614963386e-12</v>
+        <v>-5.817940342594795e-13</v>
       </c>
     </row>
     <row r="95">
@@ -4380,22 +4380,22 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>-2.294572000058611e-12</v>
+        <v>-5.893528941169833e-12</v>
       </c>
       <c r="E95" t="n">
-        <v>-1.817940630268232e-12</v>
+        <v>1.993761194585689e-11</v>
       </c>
       <c r="F95" t="n">
-        <v>5.600323439250676e-12</v>
+        <v>1.050838559243662e-10</v>
       </c>
       <c r="G95" t="n">
         <v/>
       </c>
       <c r="H95" t="n">
-        <v>2.012803163566734e-11</v>
+        <v>3.664563287944327e-11</v>
       </c>
       <c r="I95" t="n">
-        <v>6.516232877134711e-12</v>
+        <v>1.665989315989426e-10</v>
       </c>
     </row>
     <row r="96">
@@ -4415,22 +4415,22 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>-5.136116842081906e-12</v>
+        <v>-1.357681278470416e-11</v>
       </c>
       <c r="E96" t="n">
-        <v>-4.10753824662486e-12</v>
+        <v>4.257486885067202e-11</v>
       </c>
       <c r="F96" t="n">
-        <v>-3.070219353531572e-12</v>
+        <v>2.067864668593178e-10</v>
       </c>
       <c r="G96" t="n">
         <v/>
       </c>
       <c r="H96" t="n">
-        <v>-5.654736940469281e-12</v>
+        <v>-1.035903544912024e-11</v>
       </c>
       <c r="I96" t="n">
-        <v>3.205705593874495e-11</v>
+        <v>4.761852927350372e-10</v>
       </c>
     </row>
     <row r="97">
@@ -4450,22 +4450,22 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>6.450134200985306e-12</v>
+        <v>2.886651012641468e-11</v>
       </c>
       <c r="E97" t="n">
-        <v>-7.95117417750144e-12</v>
+        <v>3.925442461938296e-11</v>
       </c>
       <c r="F97" t="n">
-        <v>1.778479077414061e-12</v>
+        <v>1.79284887862958e-10</v>
       </c>
       <c r="G97" t="n">
         <v/>
       </c>
       <c r="H97" t="n">
-        <v>4.302608377149528e-12</v>
+        <v>7.776495502580512e-12</v>
       </c>
       <c r="I97" t="n">
-        <v>2.823574547084874e-12</v>
+        <v>2.875754793905238e-10</v>
       </c>
     </row>
     <row r="98">
@@ -4485,22 +4485,22 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>-2.23674866579948e-12</v>
+        <v>2.435743077516372e-11</v>
       </c>
       <c r="E98" t="n">
-        <v>-8.497145711193901e-12</v>
+        <v>3.22057699246474e-10</v>
       </c>
       <c r="F98" t="n">
-        <v>1.813643065411518e-11</v>
+        <v>7.056687462383032e-09</v>
       </c>
       <c r="G98" t="n">
         <v/>
       </c>
       <c r="H98" t="n">
-        <v>1.187930153182219e-11</v>
+        <v>2.158655342424423e-11</v>
       </c>
       <c r="I98" t="n">
-        <v>5.124212022422026e-12</v>
+        <v>2.605243874497001e-09</v>
       </c>
     </row>
     <row r="99">
@@ -4520,22 +4520,22 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>-1.980483219469508e-12</v>
+        <v>2.335036476907864e-12</v>
       </c>
       <c r="E99" t="n">
-        <v>-7.158530600725824e-12</v>
+        <v>2.874248481864461e-12</v>
       </c>
       <c r="F99" t="n">
-        <v>-1.051062773317768e-12</v>
+        <v>2.35442510609516e-12</v>
       </c>
       <c r="G99" t="n">
         <v/>
       </c>
       <c r="H99" t="n">
-        <v>-3.612630559112978e-13</v>
+        <v>-5.009535757666304e-13</v>
       </c>
       <c r="I99" t="n">
-        <v>-9.426722580051249e-13</v>
+        <v>1.077168108252132e-12</v>
       </c>
     </row>
     <row r="100">
@@ -4555,22 +4555,22 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>3.751814953570147e-12</v>
+        <v>4.555215545486911e-12</v>
       </c>
       <c r="E100" t="n">
-        <v>-5.52723715211617e-12</v>
+        <v>4.285760175588692e-11</v>
       </c>
       <c r="F100" t="n">
-        <v>6.755918668091753e-12</v>
+        <v>1.905463357161532e-10</v>
       </c>
       <c r="G100" t="n">
         <v/>
       </c>
       <c r="H100" t="n">
-        <v>1.568052861882171e-11</v>
+        <v>2.854903675028034e-11</v>
       </c>
       <c r="I100" t="n">
-        <v>6.277698497204487e-12</v>
+        <v>3.047824670903244e-10</v>
       </c>
     </row>
     <row r="101">
@@ -4590,22 +4590,22 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>7.831574987174018e-13</v>
+        <v>-1.197387778037514e-11</v>
       </c>
       <c r="E101" t="n">
-        <v>-5.059304687939396e-12</v>
+        <v>8.763979995152286e-11</v>
       </c>
       <c r="F101" t="n">
-        <v>-2.537905464662319e-12</v>
+        <v>5.822849826319701e-10</v>
       </c>
       <c r="G101" t="n">
         <v/>
       </c>
       <c r="H101" t="n">
-        <v>-7.15659943393612e-12</v>
+        <v>-1.309938064758448e-11</v>
       </c>
       <c r="I101" t="n">
-        <v>2.280199789927768e-11</v>
+        <v>5.982505866754861e-09</v>
       </c>
     </row>
     <row r="102">
@@ -4625,22 +4625,22 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>8.391321874867424e-12</v>
+        <v>2.627036693632919e-11</v>
       </c>
       <c r="E102" t="n">
-        <v>-3.531977872057132e-12</v>
+        <v>4.613732452187496e-11</v>
       </c>
       <c r="F102" t="n">
-        <v>-2.935770761021088e-12</v>
+        <v>1.764979418174182e-10</v>
       </c>
       <c r="G102" t="n">
         <v/>
       </c>
       <c r="H102" t="n">
-        <v>3.253932621926405e-12</v>
+        <v>5.865492162939296e-12</v>
       </c>
       <c r="I102" t="n">
-        <v>3.386515843733349e-12</v>
+        <v>2.830887339021809e-10</v>
       </c>
     </row>
     <row r="103">
@@ -4660,22 +4660,22 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>-1.075827730400414e-12</v>
+        <v>2.564266597744518e-11</v>
       </c>
       <c r="E103" t="n">
-        <v>5.81880726766571e-12</v>
+        <v>1.435597217570037e-09</v>
       </c>
       <c r="F103" t="n">
-        <v>-1.869470570453797e-12</v>
+        <v>1.78446625651259e-09</v>
       </c>
       <c r="G103" t="n">
         <v/>
       </c>
       <c r="H103" t="n">
-        <v>1.151863508009721e-11</v>
+        <v>2.092915755600953e-11</v>
       </c>
       <c r="I103" t="n">
-        <v>7.915555446071419e-12</v>
+        <v>1.609295541499225e-09</v>
       </c>
     </row>
     <row r="104">
@@ -4695,22 +4695,22 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>4.574940073373813e-12</v>
+        <v>3.721858917368893e-12</v>
       </c>
       <c r="E104" t="n">
-        <v>8.232096440635198e-12</v>
+        <v>4.373133644753169e-12</v>
       </c>
       <c r="F104" t="n">
-        <v>-2.711926103864828e-12</v>
+        <v>2.132341052535778e-12</v>
       </c>
       <c r="G104" t="n">
         <v/>
       </c>
       <c r="H104" t="n">
-        <v>1.37506741970004e-13</v>
+        <v>4.23978468464057e-13</v>
       </c>
       <c r="I104" t="n">
-        <v>1.944793275409265e-12</v>
+        <v>9.896760836422023e-13</v>
       </c>
     </row>
     <row r="105">
@@ -4730,22 +4730,22 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1.599828143104954e-12</v>
+        <v>7.179374917125719e-12</v>
       </c>
       <c r="E105" t="n">
-        <v>-3.493422849519617e-13</v>
+        <v>5.111025607188371e-11</v>
       </c>
       <c r="F105" t="n">
-        <v>-1.230033194968024e-12</v>
+        <v>1.865210762973501e-10</v>
       </c>
       <c r="G105" t="n">
         <v/>
       </c>
       <c r="H105" t="n">
-        <v>1.932995833061318e-11</v>
+        <v>3.521584551902487e-11</v>
       </c>
       <c r="I105" t="n">
-        <v>7.063014332688233e-12</v>
+        <v>3.035561752191666e-10</v>
       </c>
     </row>
     <row r="106">
@@ -4765,22 +4765,22 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>-2.273601606190606e-12</v>
+        <v>-1.129850297062298e-11</v>
       </c>
       <c r="E106" t="n">
-        <v>-1.664880330833171e-12</v>
+        <v>1.276991578652136e-10</v>
       </c>
       <c r="F106" t="n">
-        <v>-6.076492506945438e-12</v>
+        <v>6.6871097076556e-10</v>
       </c>
       <c r="G106" t="n">
         <v/>
       </c>
       <c r="H106" t="n">
-        <v>-6.98842481924036e-12</v>
+        <v>-1.279161384068078e-11</v>
       </c>
       <c r="I106" t="n">
-        <v>2.062985491243903e-11</v>
+        <v>0.0004451911037809074</v>
       </c>
     </row>
     <row r="107">
@@ -4800,22 +4800,22 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>-5.605929530338149e-12</v>
+        <v>5.564121471995542e-10</v>
       </c>
       <c r="E107" t="n">
-        <v>2.672849438299642e-11</v>
+        <v>6.15662416198213e-11</v>
       </c>
       <c r="F107" t="n">
-        <v>3.26211151047537e-11</v>
+        <v>2.09579617744234e-10</v>
       </c>
       <c r="G107" t="n">
         <v/>
       </c>
       <c r="H107" t="n">
-        <v>2.605445332361732e-11</v>
+        <v>4.771105715621461e-11</v>
       </c>
       <c r="I107" t="n">
-        <v>4.983830628295425e-11</v>
+        <v>4.047735756153231e-10</v>
       </c>
     </row>
     <row r="108">
@@ -4835,22 +4835,22 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>4.741789428499246e-12</v>
+        <v>3.117802871170882e-11</v>
       </c>
       <c r="E108" t="n">
-        <v>1.949254737094283e-10</v>
+        <v>0.149833919761137</v>
       </c>
       <c r="F108" t="n">
-        <v>1.410565102778751e-11</v>
+        <v>4.301216973596557e-09</v>
       </c>
       <c r="G108" t="n">
         <v/>
       </c>
       <c r="H108" t="n">
-        <v>1.208191977595119e-11</v>
+        <v>2.207942010892821e-11</v>
       </c>
       <c r="I108" t="n">
-        <v>2.154751090038051e-11</v>
+        <v>6.610055760910977e-09</v>
       </c>
     </row>
     <row r="109">
@@ -4870,22 +4870,22 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1.94793800396099e-11</v>
+        <v>3.499169046767135e-11</v>
       </c>
       <c r="E109" t="n">
-        <v>3.17550658083199e-11</v>
+        <v>1.035337403855622e-09</v>
       </c>
       <c r="F109" t="n">
-        <v>-1.069636194623953e-11</v>
+        <v>0.162269023483914</v>
       </c>
       <c r="G109" t="n">
         <v/>
       </c>
       <c r="H109" t="n">
-        <v>1.425356437857309e-11</v>
+        <v>2.604656249260268e-11</v>
       </c>
       <c r="I109" t="n">
-        <v>3.372231549696416e-11</v>
+        <v>0.0004451897221592537</v>
       </c>
     </row>
     <row r="110">
@@ -4905,22 +4905,22 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1.034009668806523e-11</v>
+        <v>3.372577765776814e-11</v>
       </c>
       <c r="E110" t="n">
-        <v>1.907843938762915e-11</v>
+        <v>6.23524300924527e-11</v>
       </c>
       <c r="F110" t="n">
-        <v>2.766009032022266e-11</v>
+        <v>2.10317547785359e-10</v>
       </c>
       <c r="G110" t="n">
         <v/>
       </c>
       <c r="H110" t="n">
-        <v>1.253590213437897e-10</v>
+        <v>2.33072225995709e-10</v>
       </c>
       <c r="I110" t="n">
-        <v>4.314906599196239e-11</v>
+        <v>4.092530436932912e-10</v>
       </c>
     </row>
     <row r="111">
@@ -4940,22 +4940,22 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>3.261773616943753e-12</v>
+        <v>3.547211103974028e-12</v>
       </c>
       <c r="E111" t="n">
-        <v>1.119994630235885e-11</v>
+        <v>2.466512393057768e-10</v>
       </c>
       <c r="F111" t="n">
-        <v>5.594222325617197e-12</v>
+        <v>1.226110141488965e-09</v>
       </c>
       <c r="G111" t="n">
         <v/>
       </c>
       <c r="H111" t="n">
-        <v>-2.77484624424374e-13</v>
+        <v>-5.153609846446081e-13</v>
       </c>
       <c r="I111" t="n">
-        <v>1.311131548058271e-12</v>
+        <v>0.0008919364604153442</v>
       </c>
     </row>
     <row r="112">
@@ -4975,22 +4975,22 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>8.699093096970614e-12</v>
+        <v>2.14616833603672e-11</v>
       </c>
       <c r="E112" t="n">
-        <v>-4.78324209645126e-12</v>
+        <v>2.000225634255816e-11</v>
       </c>
       <c r="F112" t="n">
-        <v>3.401735023430218e-12</v>
+        <v>1.05413251484814e-10</v>
       </c>
       <c r="G112" t="n">
         <v/>
       </c>
       <c r="H112" t="n">
-        <v>1.595256256559384e-12</v>
+        <v>2.998671987074423e-12</v>
       </c>
       <c r="I112" t="n">
-        <v>5.559016101358637e-12</v>
+        <v>1.685233243384231e-10</v>
       </c>
     </row>
     <row r="113">
@@ -5010,22 +5010,22 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>4.488001847062588e-12</v>
+        <v>6.150417589758834e-12</v>
       </c>
       <c r="E113" t="n">
-        <v>2.195110914471667e-11</v>
+        <v>8.428507187633362e-11</v>
       </c>
       <c r="F113" t="n">
-        <v>8.157832628185449e-12</v>
+        <v>2.722467513048244e-10</v>
       </c>
       <c r="G113" t="n">
         <v/>
       </c>
       <c r="H113" t="n">
-        <v>1.568470724325089e-12</v>
+        <v>2.949234305601834e-12</v>
       </c>
       <c r="I113" t="n">
-        <v>9.508870131515152e-12</v>
+        <v>3.407324170741467e-10</v>
       </c>
     </row>
     <row r="114">
@@ -5045,22 +5045,22 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1.635545271355527e-13</v>
+        <v>7.871700387291651e-12</v>
       </c>
       <c r="E114" t="n">
-        <v>-4.590689979042299e-12</v>
+        <v>7.144883807411539e-11</v>
       </c>
       <c r="F114" t="n">
-        <v>2.568585847462796e-11</v>
+        <v>2.861752508308487e-10</v>
       </c>
       <c r="G114" t="n">
         <v/>
       </c>
       <c r="H114" t="n">
-        <v>2.748299391321809e-12</v>
+        <v>5.12216660174276e-12</v>
       </c>
       <c r="I114" t="n">
-        <v>6.935474370991931e-12</v>
+        <v>3.5507555245049e-10</v>
       </c>
     </row>
     <row r="115">
@@ -5080,22 +5080,22 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>2.922586022684336e-13</v>
+        <v>4.251444080957658e-12</v>
       </c>
       <c r="E115" t="n">
-        <v>-1.800559232454521e-12</v>
+        <v>-1.724333968995517e-12</v>
       </c>
       <c r="F115" t="n">
-        <v>1.99492524894651e-12</v>
+        <v>1.870739525170177e-14</v>
       </c>
       <c r="G115" t="n">
         <v/>
       </c>
       <c r="H115" t="n">
-        <v>2.253039971660863e-13</v>
+        <v>5.903081454496403e-13</v>
       </c>
       <c r="I115" t="n">
-        <v>3.092032831862641e-12</v>
+        <v>-4.245206817296637e-13</v>
       </c>
     </row>
     <row r="116">
@@ -5115,22 +5115,22 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>-3.609660004157514e-12</v>
+        <v>-1.138666296559459e-11</v>
       </c>
       <c r="E116" t="n">
-        <v>-5.060229985792348e-12</v>
+        <v>4.179839154268481e-11</v>
       </c>
       <c r="F116" t="n">
-        <v>-3.441569323863736e-12</v>
+        <v>2.045616720324494e-10</v>
       </c>
       <c r="G116" t="n">
         <v/>
       </c>
       <c r="H116" t="n">
-        <v>-6.992978356782632e-12</v>
+        <v>-1.276250735524076e-11</v>
       </c>
       <c r="I116" t="n">
-        <v>2.920410725735117e-11</v>
+        <v>4.768826676792705e-10</v>
       </c>
     </row>
     <row r="117">
@@ -5150,22 +5150,22 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>7.90525498737566e-13</v>
+        <v>-4.872363831529827e-12</v>
       </c>
       <c r="E117" t="n">
-        <v>-6.762015878471353e-12</v>
+        <v>4.217386120591799e-11</v>
       </c>
       <c r="F117" t="n">
-        <v>-3.471448451609092e-12</v>
+        <v>1.8489061263816e-10</v>
       </c>
       <c r="G117" t="n">
         <v/>
       </c>
       <c r="H117" t="n">
-        <v>-5.491522055274559e-12</v>
+        <v>-1.007891715091562e-11</v>
       </c>
       <c r="I117" t="n">
-        <v>-8.747175183074576e-12</v>
+        <v>1.621776221650415e-10</v>
       </c>
     </row>
     <row r="118">
@@ -5185,22 +5185,22 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1.511500496992348e-12</v>
+        <v>-1.127856674674916e-11</v>
       </c>
       <c r="E118" t="n">
-        <v>1.835718591869407e-11</v>
+        <v>2.921460733123849e-10</v>
       </c>
       <c r="F118" t="n">
-        <v>-1.619860539225051e-12</v>
+        <v>1.387069251877235e-09</v>
       </c>
       <c r="G118" t="n">
         <v/>
       </c>
       <c r="H118" t="n">
-        <v>-6.768013031585139e-12</v>
+        <v>-1.240514988318695e-11</v>
       </c>
       <c r="I118" t="n">
-        <v>-8.622405419832433e-12</v>
+        <v>2.922070793712358e-10</v>
       </c>
     </row>
     <row r="119">
@@ -5220,22 +5220,22 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>-3.010974677243386e-12</v>
+        <v>-1.120171215536457e-11</v>
       </c>
       <c r="E119" t="n">
-        <v>-5.975975497513708e-12</v>
+        <v>1.686359446398887e-10</v>
       </c>
       <c r="F119" t="n">
-        <v>1.492465613387838e-12</v>
+        <v>1.138174978323798e-09</v>
       </c>
       <c r="G119" t="n">
         <v/>
       </c>
       <c r="H119" t="n">
-        <v>-6.545801932361253e-12</v>
+        <v>-1.199971761707187e-11</v>
       </c>
       <c r="I119" t="n">
-        <v>-8.946731591112897e-12</v>
+        <v>2.831901744688392e-10</v>
       </c>
     </row>
     <row r="120">
@@ -5255,22 +5255,22 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>-2.901578940043462e-12</v>
+        <v>-6.173547540340327e-12</v>
       </c>
       <c r="E120" t="n">
-        <v>-4.643670022387839e-12</v>
+        <v>3.855254357327903e-12</v>
       </c>
       <c r="F120" t="n">
-        <v>-2.945603764742366e-12</v>
+        <v>2.3725736137916e-12</v>
       </c>
       <c r="G120" t="n">
         <v/>
       </c>
       <c r="H120" t="n">
-        <v>-4.320512467319673e-12</v>
+        <v>-7.846880297898694e-12</v>
       </c>
       <c r="I120" t="n">
-        <v>-8.541361722270736e-12</v>
+        <v>-8.77684794304217e-13</v>
       </c>
     </row>
     <row r="121">
@@ -5290,22 +5290,22 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>-3.363919715330465e-12</v>
+        <v>-1.121825672641007e-11</v>
       </c>
       <c r="E121" t="n">
-        <v>-5.667531469578671e-12</v>
+        <v>3.955232400022455e-11</v>
       </c>
       <c r="F121" t="n">
-        <v>-2.987517181240767e-12</v>
+        <v>1.759468173252028e-10</v>
       </c>
       <c r="G121" t="n">
         <v/>
       </c>
       <c r="H121" t="n">
-        <v>-3.9443746883122e-12</v>
+        <v>-7.271716359120801e-12</v>
       </c>
       <c r="I121" t="n">
-        <v>-8.706511006199756e-12</v>
+        <v>1.565988232588937e-10</v>
       </c>
     </row>
     <row r="122">
@@ -5325,22 +5325,22 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>-2.358603501980058e-12</v>
+        <v>-3.066275715264086e-12</v>
       </c>
       <c r="E122" t="n">
-        <v>6.872960163459441e-12</v>
+        <v>2.409549432418922e-11</v>
       </c>
       <c r="F122" t="n">
-        <v>1.060013159500647e-12</v>
+        <v>7.658616408986337e-12</v>
       </c>
       <c r="G122" t="n">
-        <v>5.217889103752818e-12</v>
+        <v>9.494342511730961e-12</v>
       </c>
       <c r="H122" t="n">
         <v/>
       </c>
       <c r="I122" t="n">
-        <v>4.852617179201361e-11</v>
+        <v>1.718855212038178e-09</v>
       </c>
     </row>
     <row r="123">
@@ -5360,22 +5360,22 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>-2.272142899350268e-12</v>
+        <v>-4.18141463696776e-12</v>
       </c>
       <c r="E123" t="n">
-        <v>1.197196820505731e-12</v>
+        <v>6.27694090287122e-12</v>
       </c>
       <c r="F123" t="n">
-        <v>9.96895686655225e-12</v>
+        <v>1.722544271171746e-11</v>
       </c>
       <c r="G123" t="n">
-        <v>4.093399184546356e-12</v>
+        <v>7.439489516726069e-12</v>
       </c>
       <c r="H123" t="n">
         <v/>
       </c>
       <c r="I123" t="n">
-        <v>4.581535967279078e-11</v>
+        <v>1.731261779069476e-09</v>
       </c>
     </row>
     <row r="124">
@@ -5395,22 +5395,22 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>-1.060703057647263e-12</v>
+        <v>-2.129648510055299e-12</v>
       </c>
       <c r="E124" t="n">
-        <v>2.261940563358063e-12</v>
+        <v>6.446624430154685e-12</v>
       </c>
       <c r="F124" t="n">
-        <v>3.15537063955898e-12</v>
+        <v>6.461809978672621e-12</v>
       </c>
       <c r="G124" t="n">
-        <v>2.483382832745832e-11</v>
+        <v>4.524069336401322e-11</v>
       </c>
       <c r="H124" t="n">
         <v/>
       </c>
       <c r="I124" t="n">
-        <v>6.746460297893938e-11</v>
+        <v>1.784615315406774e-09</v>
       </c>
     </row>
     <row r="125">
@@ -5430,22 +5430,22 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>-2.61371818814644e-12</v>
+        <v>-5.550638784428713e-12</v>
       </c>
       <c r="E125" t="n">
-        <v>1.399867807725118e-12</v>
+        <v>1.0274102830567e-12</v>
       </c>
       <c r="F125" t="n">
-        <v>1.480306945484574e-12</v>
+        <v>1.848111491052284e-12</v>
       </c>
       <c r="G125" t="n">
-        <v>2.576018953183616e-12</v>
+        <v>5.065116142920972e-12</v>
       </c>
       <c r="H125" t="n">
         <v/>
       </c>
       <c r="I125" t="n">
-        <v>1.211134109326463e-12</v>
+        <v>-2.061592268122756e-13</v>
       </c>
     </row>
     <row r="126">
@@ -5465,22 +5465,22 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>-5.771821656219717e-12</v>
+        <v>-1.293102408902545e-11</v>
       </c>
       <c r="E126" t="n">
-        <v>-2.353634975861356e-12</v>
+        <v>-9.881322302030672e-12</v>
       </c>
       <c r="F126" t="n">
-        <v>-3.244783151337668e-12</v>
+        <v>-1.034971147217732e-11</v>
       </c>
       <c r="G126" t="n">
-        <v>-4.924889910956302e-12</v>
+        <v>-9.01246378639089e-12</v>
       </c>
       <c r="H126" t="n">
         <v/>
       </c>
       <c r="I126" t="n">
-        <v>8.863155153120884e-10</v>
+        <v>1.93039667860613e-09</v>
       </c>
     </row>
     <row r="127">
@@ -5500,22 +5500,22 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>2.376443796904808e-11</v>
+        <v>4.503164843310795e-11</v>
       </c>
       <c r="E127" t="n">
-        <v>-2.171769177173246e-12</v>
+        <v>-2.605702327983738e-12</v>
       </c>
       <c r="F127" t="n">
-        <v>2.156826049410595e-12</v>
+        <v>3.848341598724108e-12</v>
       </c>
       <c r="G127" t="n">
-        <v>6.896467805061504e-12</v>
+        <v>1.253401755341473e-11</v>
       </c>
       <c r="H127" t="n">
         <v/>
       </c>
       <c r="I127" t="n">
-        <v>5.778267540916261e-11</v>
+        <v>1.459655004123806e-09</v>
       </c>
     </row>
     <row r="128">
@@ -5535,22 +5535,22 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>4.55586372018878e-12</v>
+        <v>2.406146486124137e-11</v>
       </c>
       <c r="E128" t="n">
-        <v>-2.661203381545765e-12</v>
+        <v>9.986579532824141e-12</v>
       </c>
       <c r="F128" t="n">
-        <v>1.109019606352043e-11</v>
+        <v>6.055335503005614e-11</v>
       </c>
       <c r="G128" t="n">
-        <v>1.269007969716323e-11</v>
+        <v>2.313052975440405e-11</v>
       </c>
       <c r="H128" t="n">
         <v/>
       </c>
       <c r="I128" t="n">
-        <v>6.121228602257582e-11</v>
+        <v>2.229578980244085e-08</v>
       </c>
     </row>
     <row r="129">
@@ -5570,22 +5570,22 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>4.56647479347287e-13</v>
+        <v>4.753529688169733e-12</v>
       </c>
       <c r="E129" t="n">
-        <v>-4.290280342433001e-12</v>
+        <v>-3.052001135384146e-12</v>
       </c>
       <c r="F129" t="n">
-        <v>-1.046708565907089e-12</v>
+        <v>2.404930911728342e-12</v>
       </c>
       <c r="G129" t="n">
-        <v>1.190550928507552e-11</v>
+        <v>2.167013736146798e-11</v>
       </c>
       <c r="H129" t="n">
         <v/>
       </c>
       <c r="I129" t="n">
-        <v>4.940919768857468e-11</v>
+        <v>1.250061510394376e-08</v>
       </c>
     </row>
     <row r="130">
@@ -5605,22 +5605,22 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>4.418924072093224e-12</v>
+        <v>4.825035650988832e-12</v>
       </c>
       <c r="E130" t="n">
-        <v>7.557676176355488e-14</v>
+        <v>-2.868145639808219e-12</v>
       </c>
       <c r="F130" t="n">
-        <v>5.040959877768434e-12</v>
+        <v>3.852130912748183e-12</v>
       </c>
       <c r="G130" t="n">
-        <v>2.53803995863538e-12</v>
+        <v>4.984192640565891e-12</v>
       </c>
       <c r="H130" t="n">
         <v/>
       </c>
       <c r="I130" t="n">
-        <v>1.66753189561959e-12</v>
+        <v>1.831307637648858e-13</v>
       </c>
     </row>
     <row r="131">
@@ -5640,22 +5640,22 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>-2.323212060877468e-12</v>
+        <v>-1.130200413490589e-11</v>
       </c>
       <c r="E131" t="n">
-        <v>-1.817640522323683e-12</v>
+        <v>-1.319913616239456e-11</v>
       </c>
       <c r="F131" t="n">
-        <v>-5.787030535614716e-13</v>
+        <v>-1.187395665100967e-11</v>
       </c>
       <c r="G131" t="n">
-        <v>-6.292520881453622e-12</v>
+        <v>-1.151280687618251e-11</v>
       </c>
       <c r="H131" t="n">
         <v/>
       </c>
       <c r="I131" t="n">
-        <v>7.168050179978529e-10</v>
+        <v>1.424085037767381e-08</v>
       </c>
     </row>
     <row r="132">
@@ -5675,22 +5675,22 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>2.120632301262599e-11</v>
+        <v>4.156170725407198e-11</v>
       </c>
       <c r="E132" t="n">
-        <v>1.450260645088464e-12</v>
+        <v>3.406659711093276e-12</v>
       </c>
       <c r="F132" t="n">
-        <v>-2.394955652124648e-12</v>
+        <v>-2.872424799255144e-12</v>
       </c>
       <c r="G132" t="n">
-        <v>5.855402678863169e-12</v>
+        <v>1.063706544394696e-11</v>
       </c>
       <c r="H132" t="n">
         <v/>
       </c>
       <c r="I132" t="n">
-        <v>5.702442223205635e-11</v>
+        <v>1.469140392636812e-09</v>
       </c>
     </row>
     <row r="133">
@@ -5710,22 +5710,22 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>3.803523585349038e-12</v>
+        <v>2.702572179603226e-11</v>
       </c>
       <c r="E133" t="n">
-        <v>6.142967170831481e-12</v>
+        <v>8.220236716107761e-11</v>
       </c>
       <c r="F133" t="n">
-        <v>-2.685149459019903e-12</v>
+        <v>1.052939650288213e-11</v>
       </c>
       <c r="G133" t="n">
-        <v>1.317878372032696e-11</v>
+        <v>2.402924048845797e-11</v>
       </c>
       <c r="H133" t="n">
         <v/>
       </c>
       <c r="I133" t="n">
-        <v>6.492206267161497e-11</v>
+        <v>1.308672937908933e-08</v>
       </c>
     </row>
     <row r="134">
@@ -5745,22 +5745,22 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>3.624270190477199e-12</v>
+        <v>6.71721321452629e-12</v>
       </c>
       <c r="E134" t="n">
-        <v>2.265687739330711e-12</v>
+        <v>4.886368860639791e-12</v>
       </c>
       <c r="F134" t="n">
-        <v>-1.914735816336227e-12</v>
+        <v>-2.317218333187558e-12</v>
       </c>
       <c r="G134" t="n">
-        <v>1.401056821127315e-11</v>
+        <v>2.549300736909365e-11</v>
       </c>
       <c r="H134" t="n">
         <v/>
       </c>
       <c r="I134" t="n">
-        <v>6.184563815738715e-11</v>
+        <v>1.083998963815183e-08</v>
       </c>
     </row>
     <row r="135">
@@ -5780,22 +5780,22 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>2.877153231696002e-12</v>
+        <v>7.710537653951936e-12</v>
       </c>
       <c r="E135" t="n">
-        <v>2.432831034627314e-12</v>
+        <v>6.094235849529521e-12</v>
       </c>
       <c r="F135" t="n">
-        <v>-1.985822494256549e-12</v>
+        <v>-7.310703030145196e-13</v>
       </c>
       <c r="G135" t="n">
-        <v>3.818604947872747e-12</v>
+        <v>7.39480433640633e-12</v>
       </c>
       <c r="H135" t="n">
         <v/>
       </c>
       <c r="I135" t="n">
-        <v>1.721918999702367e-12</v>
+        <v>1.862307210096395e-13</v>
       </c>
     </row>
     <row r="136">
@@ -5815,22 +5815,22 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>-3.612586620671482e-12</v>
+        <v>-1.062388666780788e-11</v>
       </c>
       <c r="E136" t="n">
-        <v>-1.418019123590738e-12</v>
+        <v>-1.049900152168631e-11</v>
       </c>
       <c r="F136" t="n">
-        <v>-5.235703056922186e-12</v>
+        <v>-1.311168216820845e-11</v>
       </c>
       <c r="G136" t="n">
-        <v>-6.049795295948776e-12</v>
+        <v>-1.106789460315811e-11</v>
       </c>
       <c r="H136" t="n">
         <v/>
       </c>
       <c r="I136" t="n">
-        <v>4.90267626235113e-10</v>
+        <v>4.108409987869431e-08</v>
       </c>
     </row>
     <row r="137">
@@ -5850,22 +5850,22 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>2.266668964220528e-11</v>
+        <v>5.01336401548151e-11</v>
       </c>
       <c r="E137" t="n">
-        <v>2.337737601961875e-12</v>
+        <v>8.626561606820803e-12</v>
       </c>
       <c r="F137" t="n">
-        <v>2.260448275070366e-12</v>
+        <v>7.685757032671018e-12</v>
       </c>
       <c r="G137" t="n">
-        <v>1.668437346320241e-13</v>
+        <v>4.132690808046113e-13</v>
       </c>
       <c r="H137" t="n">
         <v/>
       </c>
       <c r="I137" t="n">
-        <v>4.852033680800874e-11</v>
+        <v>1.48372863877426e-09</v>
       </c>
     </row>
     <row r="138">
@@ -5885,22 +5885,22 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>-1.331112675994266e-12</v>
+        <v>3.945243672455007e-12</v>
       </c>
       <c r="E138" t="n">
-        <v>1.310753696867581e-12</v>
+        <v>2.562952108674146e-11</v>
       </c>
       <c r="F138" t="n">
-        <v>-2.352245630967319e-12</v>
+        <v>6.648196305427749e-12</v>
       </c>
       <c r="G138" t="n">
-        <v>-2.808059581139486e-12</v>
+        <v>-5.054544221132892e-12</v>
       </c>
       <c r="H138" t="n">
         <v/>
       </c>
       <c r="I138" t="n">
-        <v>3.214769799181555e-11</v>
+        <v>7.658867326969074e-09</v>
       </c>
     </row>
     <row r="139">
@@ -5920,22 +5920,22 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>2.012947075191207e-12</v>
+        <v>4.682441407875644e-12</v>
       </c>
       <c r="E139" t="n">
-        <v>2.353354906333215e-12</v>
+        <v>1.034509703456364e-11</v>
       </c>
       <c r="F139" t="n">
-        <v>1.050190017056709e-11</v>
+        <v>2.115888034367542e-11</v>
       </c>
       <c r="G139" t="n">
-        <v>-2.486847391286201e-12</v>
+        <v>-4.467636695753713e-12</v>
       </c>
       <c r="H139" t="n">
         <v/>
       </c>
       <c r="I139" t="n">
-        <v>3.736323823261665e-11</v>
+        <v>9.072509757175057e-09</v>
       </c>
     </row>
     <row r="140">
@@ -5955,22 +5955,22 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>-1.102953296257216e-13</v>
+        <v>4.614618299839683e-12</v>
       </c>
       <c r="E140" t="n">
-        <v>-6.503282305649515e-13</v>
+        <v>6.501437059701392e-12</v>
       </c>
       <c r="F140" t="n">
-        <v>-6.871689658323512e-13</v>
+        <v>6.212322491225391e-12</v>
       </c>
       <c r="G140" t="n">
-        <v>-2.298718027884688e-12</v>
+        <v>-4.027346480315157e-12</v>
       </c>
       <c r="H140" t="n">
         <v/>
       </c>
       <c r="I140" t="n">
-        <v>4.659907967039413e-13</v>
+        <v>1.447228459762697e-13</v>
       </c>
     </row>
     <row r="141">
@@ -5990,22 +5990,22 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>-3.039685475874501e-12</v>
+        <v>-5.343059159344265e-12</v>
       </c>
       <c r="E141" t="n">
-        <v>-2.575429842753622e-12</v>
+        <v>-4.014219082200785e-12</v>
       </c>
       <c r="F141" t="n">
-        <v>-3.293160495047179e-12</v>
+        <v>-5.237515668817526e-12</v>
       </c>
       <c r="G141" t="n">
-        <v>-5.502820063772707e-12</v>
+        <v>-1.000671566624388e-11</v>
       </c>
       <c r="H141" t="n">
         <v/>
       </c>
       <c r="I141" t="n">
-        <v>2.509112274045695e-09</v>
+        <v>5.471080872321377e-08</v>
       </c>
     </row>
     <row r="142">
@@ -6025,22 +6025,22 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>-1.251721624514172e-11</v>
+        <v>2.81016985664752e-09</v>
       </c>
       <c r="E142" t="n">
-        <v>1.079671491618875e-11</v>
+        <v>2.813988301339171e-11</v>
       </c>
       <c r="F142" t="n">
-        <v>1.378698990721114e-11</v>
+        <v>2.443859160960328e-11</v>
       </c>
       <c r="G142" t="n">
-        <v>2.420375806654363e-11</v>
+        <v>4.439782332002134e-11</v>
       </c>
       <c r="H142" t="n">
         <v/>
       </c>
       <c r="I142" t="n">
-        <v>8.817484314936767e-10</v>
+        <v>1.629985236223137e-09</v>
       </c>
     </row>
     <row r="143">
@@ -6060,22 +6060,22 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>3.387188297532347e-11</v>
+        <v>5.110050700268534e-11</v>
       </c>
       <c r="E143" t="n">
-        <v>7.589552206146277e-11</v>
+        <v>2.990019524712245e-10</v>
       </c>
       <c r="F143" t="n">
-        <v>2.206607046295301e-11</v>
+        <v>4.488308354515942e-11</v>
       </c>
       <c r="G143" t="n">
-        <v>1.901083785430004e-11</v>
+        <v>3.489222585337271e-11</v>
       </c>
       <c r="H143" t="n">
         <v/>
       </c>
       <c r="I143" t="n">
-        <v>7.378095522165788e-10</v>
+        <v>2.50994531561259e-08</v>
       </c>
     </row>
     <row r="144">
@@ -6095,22 +6095,22 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>2.76791385785352e-11</v>
+        <v>5.935044116553048e-11</v>
       </c>
       <c r="E144" t="n">
-        <v>1.243355078507272e-11</v>
+        <v>6.929804463974435e-11</v>
       </c>
       <c r="F144" t="n">
-        <v>-1.659372350015281e-12</v>
+        <v>1.848588339411875e-10</v>
       </c>
       <c r="G144" t="n">
-        <v>2.321147886179739e-11</v>
+        <v>4.263270042659604e-11</v>
       </c>
       <c r="H144" t="n">
         <v/>
       </c>
       <c r="I144" t="n">
-        <v>5.283625618748881e-10</v>
+        <v>3.073502175378298e-08</v>
       </c>
     </row>
     <row r="145">
@@ -6130,22 +6130,22 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>2.006803774727999e-11</v>
+        <v>5.446058369699782e-11</v>
       </c>
       <c r="E145" t="n">
-        <v>6.107449395218597e-12</v>
+        <v>4.354568009391313e-11</v>
       </c>
       <c r="F145" t="n">
-        <v>9.539229800468045e-12</v>
+        <v>3.570676354735384e-11</v>
       </c>
       <c r="G145" t="n">
-        <v>1.281406499910723e-10</v>
+        <v>2.399100581624925e-10</v>
       </c>
       <c r="H145" t="n">
         <v/>
       </c>
       <c r="I145" t="n">
-        <v>2.442947946426671e-09</v>
+        <v>4.431234530524735e-08</v>
       </c>
     </row>
     <row r="146">
@@ -6165,22 +6165,22 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1.71608529039629e-12</v>
+        <v>-3.956831947249685e-12</v>
       </c>
       <c r="E146" t="n">
-        <v>2.012866442959657e-12</v>
+        <v>-3.976930001138208e-12</v>
       </c>
       <c r="F146" t="n">
-        <v>9.057545590726672e-13</v>
+        <v>-5.718908075410605e-12</v>
       </c>
       <c r="G146" t="n">
-        <v>-3.022374180910387e-12</v>
+        <v>-5.524787950270351e-12</v>
       </c>
       <c r="H146" t="n">
         <v/>
       </c>
       <c r="I146" t="n">
-        <v>1.653168840555694e-10</v>
+        <v>0.003112504153832382</v>
       </c>
     </row>
     <row r="147">
@@ -6200,22 +6200,22 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1.620718466311995e-12</v>
+        <v>-3.780956607253563e-12</v>
       </c>
       <c r="E147" t="n">
-        <v>-3.034613606686233e-12</v>
+        <v>-9.602254365123851e-12</v>
       </c>
       <c r="F147" t="n">
-        <v>-3.389444119473951e-12</v>
+        <v>-1.025599632369564e-11</v>
       </c>
       <c r="G147" t="n">
-        <v>-5.326226627116136e-12</v>
+        <v>-9.754997649186309e-12</v>
       </c>
       <c r="H147" t="n">
         <v/>
       </c>
       <c r="I147" t="n">
-        <v>4.256917922214365e-12</v>
+        <v>1.122413554135777e-09</v>
       </c>
     </row>
     <row r="148">
@@ -6235,22 +6235,22 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>-3.113029203173112e-12</v>
+        <v>-1.163552225716356e-11</v>
       </c>
       <c r="E148" t="n">
-        <v>6.158613825479785e-12</v>
+        <v>-6.780520266075096e-12</v>
       </c>
       <c r="F148" t="n">
-        <v>-1.426118161271599e-12</v>
+        <v>-1.093449095994745e-11</v>
       </c>
       <c r="G148" t="n">
-        <v>-6.861875232759147e-12</v>
+        <v>-1.255519419875925e-11</v>
       </c>
       <c r="H148" t="n">
         <v/>
       </c>
       <c r="I148" t="n">
-        <v>3.471224341701837e-12</v>
+        <v>2.933188344723628e-09</v>
       </c>
     </row>
     <row r="149">
@@ -6270,22 +6270,22 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>-4.077123074601908e-12</v>
+        <v>-1.15216395472043e-11</v>
       </c>
       <c r="E149" t="n">
-        <v>-2.449171664354281e-12</v>
+        <v>-9.816032049499304e-12</v>
       </c>
       <c r="F149" t="n">
-        <v>5.205454471237822e-13</v>
+        <v>-8.262729752549272e-12</v>
       </c>
       <c r="G149" t="n">
-        <v>-6.694546089833112e-12</v>
+        <v>-1.22488599672255e-11</v>
       </c>
       <c r="H149" t="n">
         <v/>
       </c>
       <c r="I149" t="n">
-        <v>3.028222493056173e-12</v>
+        <v>2.645562426825101e-09</v>
       </c>
     </row>
     <row r="150">
@@ -6305,22 +6305,22 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>-2.889709123584472e-12</v>
+        <v>-5.768793713126477e-12</v>
       </c>
       <c r="E150" t="n">
-        <v>-3.568709223991599e-12</v>
+        <v>-4.738274543834749e-12</v>
       </c>
       <c r="F150" t="n">
-        <v>-3.303382704081646e-12</v>
+        <v>-5.788645600216624e-12</v>
       </c>
       <c r="G150" t="n">
-        <v>-2.75098188717306e-13</v>
+        <v>-5.535968639567732e-13</v>
       </c>
       <c r="H150" t="n">
         <v/>
       </c>
       <c r="I150" t="n">
-        <v>5.942152623373222e-12</v>
+        <v>3.488493806228511e-09</v>
       </c>
     </row>
     <row r="151">
@@ -6340,22 +6340,22 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>-4.572077588229241e-12</v>
+        <v>-1.151476814259462e-11</v>
       </c>
       <c r="E151" t="n">
-        <v>-3.257977352039611e-12</v>
+        <v>-1.066248316289654e-11</v>
       </c>
       <c r="F151" t="n">
-        <v>-3.848195660021928e-12</v>
+        <v>-1.112764615093708e-11</v>
       </c>
       <c r="G151" t="n">
-        <v>-6.634654194615242e-12</v>
+        <v>-1.207153979982942e-11</v>
       </c>
       <c r="H151" t="n">
         <v/>
       </c>
       <c r="I151" t="n">
-        <v>-5.066586420712213e-12</v>
+        <v>-1.230949818186465e-13</v>
       </c>
     </row>
     <row r="152">
@@ -6375,19 +6375,19 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>-1.075143643054941e-11</v>
+        <v>-1.2237612897659e-11</v>
       </c>
       <c r="E152" t="n">
-        <v>3.178399576375402e-12</v>
+        <v>1.337784378803917e-10</v>
       </c>
       <c r="F152" t="n">
-        <v>7.622497484543942e-11</v>
+        <v>5.8682564125821e-10</v>
       </c>
       <c r="G152" t="n">
-        <v>-1.57712340553494e-12</v>
+        <v>3.558395546005893e-10</v>
       </c>
       <c r="H152" t="n">
-        <v>5.477628765147441e-11</v>
+        <v>1.719698442026227e-09</v>
       </c>
       <c r="I152" t="n">
         <v/>
@@ -6410,19 +6410,19 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>-1.014744524654103e-11</v>
+        <v>-1.272522591549326e-11</v>
       </c>
       <c r="E153" t="n">
-        <v>-4.081947995157384e-12</v>
+        <v>7.929648307615335e-11</v>
       </c>
       <c r="F153" t="n">
-        <v>5.746060865137311e-10</v>
+        <v>8.865395223877147e-10</v>
       </c>
       <c r="G153" t="n">
-        <v>-1.568498396969594e-12</v>
+        <v>3.626688641970408e-10</v>
       </c>
       <c r="H153" t="n">
-        <v>5.450680501179113e-11</v>
+        <v>1.728425190046849e-09</v>
       </c>
       <c r="I153" t="n">
         <v/>
@@ -6445,19 +6445,19 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>-9.636637530804827e-12</v>
+        <v>-1.297134417751676e-11</v>
       </c>
       <c r="E154" t="n">
-        <v>-3.915934471359766e-12</v>
+        <v>6.118492231966037e-11</v>
       </c>
       <c r="F154" t="n">
-        <v>9.89695803284044e-11</v>
+        <v>4.513413181839385e-10</v>
       </c>
       <c r="G154" t="n">
-        <v>2.602292402817117e-11</v>
+        <v>5.072798445891825e-10</v>
       </c>
       <c r="H154" t="n">
-        <v>4.640953344068854e-11</v>
+        <v>1.662966376097547e-09</v>
       </c>
       <c r="I154" t="n">
         <v/>
@@ -6480,19 +6480,19 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>-1.0037379601529e-11</v>
+        <v>-1.51159378062044e-11</v>
       </c>
       <c r="E155" t="n">
-        <v>-2.844576368309007e-12</v>
+        <v>4.051025648877248e-11</v>
       </c>
       <c r="F155" t="n">
-        <v>1.009913481336738e-10</v>
+        <v>3.62750265241678e-10</v>
       </c>
       <c r="G155" t="n">
-        <v>1.096010852975887e-13</v>
+        <v>1.721379848240762e-10</v>
       </c>
       <c r="H155" t="n">
-        <v>9.475585173896831e-10</v>
+        <v>1.862283598484881e-09</v>
       </c>
       <c r="I155" t="n">
         <v/>
@@ -6515,19 +6515,19 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>-9.56875546314938e-12</v>
+        <v>-1.166131776326114e-11</v>
       </c>
       <c r="E156" t="n">
-        <v>7.746065642076743e-13</v>
+        <v>4.266111298074768e-13</v>
       </c>
       <c r="F156" t="n">
-        <v>1.546571824845779e-13</v>
+        <v>1.516786757025482e-12</v>
       </c>
       <c r="G156" t="n">
-        <v>2.223503777863664e-12</v>
+        <v>-8.223478248307264e-13</v>
       </c>
       <c r="H156" t="n">
-        <v>5.796585917835369e-13</v>
+        <v>-1.800767709158529e-13</v>
       </c>
       <c r="I156" t="n">
         <v/>
@@ -6550,19 +6550,19 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>5.343404137419416e-12</v>
+        <v>6.648658766295252e-12</v>
       </c>
       <c r="E157" t="n">
-        <v>-7.324753587234575e-12</v>
+        <v>3.727321025886097e-11</v>
       </c>
       <c r="F157" t="n">
-        <v>1.033562964637057e-10</v>
+        <v>3.847468740575876e-10</v>
       </c>
       <c r="G157" t="n">
-        <v>-9.733890492036089e-13</v>
+        <v>2.870082543107993e-10</v>
       </c>
       <c r="H157" t="n">
-        <v>4.635896897550089e-11</v>
+        <v>1.46037000076649e-09</v>
       </c>
       <c r="I157" t="n">
         <v/>
@@ -6585,19 +6585,19 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>-8.684982317626626e-12</v>
+        <v>9.656915689809807e-12</v>
       </c>
       <c r="E158" t="n">
-        <v>-6.755107768213961e-12</v>
+        <v>1.119035973146516e-10</v>
       </c>
       <c r="F158" t="n">
-        <v>1.637114055234828e-09</v>
+        <v>3.106402308312675e-09</v>
       </c>
       <c r="G158" t="n">
-        <v>1.689035308585005e-12</v>
+        <v>3.037046279445059e-09</v>
       </c>
       <c r="H158" t="n">
-        <v>6.266979008973848e-11</v>
+        <v>2.178012127989202e-08</v>
       </c>
       <c r="I158" t="n">
         <v/>
@@ -6620,19 +6620,19 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>-8.801037958948247e-12</v>
+        <v>-7.555558792698357e-12</v>
       </c>
       <c r="E159" t="n">
-        <v>-8.626984274240117e-12</v>
+        <v>5.193310792649807e-11</v>
       </c>
       <c r="F159" t="n">
-        <v>8.047577149175697e-11</v>
+        <v>4.595043368848418e-10</v>
       </c>
       <c r="G159" t="n">
-        <v>7.508142021615668e-12</v>
+        <v>0.0004118935670358778</v>
       </c>
       <c r="H159" t="n">
-        <v>3.076908072344351e-11</v>
+        <v>8.306562951711131e-09</v>
       </c>
       <c r="I159" t="n">
         <v/>
@@ -6655,19 +6655,19 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>-3.307722569048477e-12</v>
+        <v>-8.551656348820668e-12</v>
       </c>
       <c r="E160" t="n">
-        <v>-6.036776282805075e-12</v>
+        <v>4.138698428712754e-11</v>
       </c>
       <c r="F160" t="n">
-        <v>1.54795520028756e-10</v>
+        <v>4.242456860708534e-10</v>
       </c>
       <c r="G160" t="n">
-        <v>1.10993561818755e-12</v>
+        <v>3.077993482943522e-10</v>
       </c>
       <c r="H160" t="n">
-        <v>7.127763859784756e-10</v>
+        <v>2.737793959970017e-08</v>
       </c>
       <c r="I160" t="n">
         <v/>
@@ -6690,19 +6690,19 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>3.055334997589769e-11</v>
+        <v>-6.127836578078926e-12</v>
       </c>
       <c r="E161" t="n">
-        <v>-4.635241247989782e-12</v>
+        <v>-1.181028119524297e-12</v>
       </c>
       <c r="F161" t="n">
-        <v>1.064814487583638e-12</v>
+        <v>1.36437468921528e-12</v>
       </c>
       <c r="G161" t="n">
-        <v>3.24958244928646e-13</v>
+        <v>6.398827010485014e-13</v>
       </c>
       <c r="H161" t="n">
-        <v>-4.723531228903219e-16</v>
+        <v>2.028003250719098e-13</v>
       </c>
       <c r="I161" t="n">
         <v/>
@@ -6725,19 +6725,19 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>-7.40763650301099e-14</v>
+        <v>5.209855067866361e-12</v>
       </c>
       <c r="E162" t="n">
-        <v>-4.609960969102878e-12</v>
+        <v>5.099502231846182e-11</v>
       </c>
       <c r="F162" t="n">
-        <v>4.149999840063643e-11</v>
+        <v>2.981361565861589e-10</v>
       </c>
       <c r="G162" t="n">
-        <v>-1.849651259170689e-12</v>
+        <v>2.834787949356694e-10</v>
       </c>
       <c r="H162" t="n">
-        <v>4.330143187733544e-11</v>
+        <v>1.472004065906149e-09</v>
       </c>
       <c r="I162" t="n">
         <v/>
@@ -6760,19 +6760,19 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>-1.009785754832292e-11</v>
+        <v>9.117898072562866e-12</v>
       </c>
       <c r="E163" t="n">
-        <v>4.873225829200167e-12</v>
+        <v>5.944095496115925e-10</v>
       </c>
       <c r="F163" t="n">
-        <v>3.74692837851908e-11</v>
+        <v>6.19770757784971e-10</v>
       </c>
       <c r="G163" t="n">
-        <v>5.108831008096975e-13</v>
+        <v>1.8082795935796e-09</v>
       </c>
       <c r="H163" t="n">
-        <v>5.84233685511591e-11</v>
+        <v>1.329457150938505e-08</v>
       </c>
       <c r="I163" t="n">
         <v/>
@@ -6795,19 +6795,19 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>-6.775076743502955e-12</v>
+        <v>-6.879808600192403e-12</v>
       </c>
       <c r="E164" t="n">
-        <v>-5.181775914314594e-12</v>
+        <v>7.760691501750924e-11</v>
       </c>
       <c r="F164" t="n">
-        <v>4.356462186374671e-11</v>
+        <v>3.561641148156563e-10</v>
       </c>
       <c r="G164" t="n">
-        <v>1.224028316585925e-11</v>
+        <v>1.203592046785701e-08</v>
       </c>
       <c r="H164" t="n">
-        <v>3.504783556996767e-11</v>
+        <v>7.601397106285743e-09</v>
       </c>
       <c r="I164" t="n">
         <v/>
@@ -6830,19 +6830,19 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>-7.831906348539193e-12</v>
+        <v>-7.374192322438946e-12</v>
       </c>
       <c r="E165" t="n">
-        <v>-2.583442134577976e-12</v>
+        <v>6.200338091116584e-11</v>
       </c>
       <c r="F165" t="n">
-        <v>4.686909068071391e-11</v>
+        <v>3.406229961022686e-10</v>
       </c>
       <c r="G165" t="n">
-        <v>5.954236773802932e-13</v>
+        <v>3.065293452246736e-10</v>
       </c>
       <c r="H165" t="n">
-        <v>5.35658001458677e-10</v>
+        <v>3.082116171080027e-08</v>
       </c>
       <c r="I165" t="n">
         <v/>
@@ -6865,19 +6865,19 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>-4.693863455639021e-12</v>
+        <v>-3.97640816786215e-12</v>
       </c>
       <c r="E166" t="n">
-        <v>-1.167807586406914e-12</v>
+        <v>1.907196738475813e-12</v>
       </c>
       <c r="F166" t="n">
-        <v>-1.391176896779631e-12</v>
+        <v>9.014049415721811e-13</v>
       </c>
       <c r="G166" t="n">
-        <v>-9.103570682922665e-13</v>
+        <v>8.208602499152618e-13</v>
       </c>
       <c r="H166" t="n">
-        <v>-2.824488825296496e-13</v>
+        <v>2.461237182975996e-13</v>
       </c>
       <c r="I166" t="n">
         <v/>
@@ -6900,19 +6900,19 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>-1.405174989939484e-12</v>
+        <v>1.768471221629021e-11</v>
       </c>
       <c r="E167" t="n">
-        <v>-3.062057803711662e-12</v>
+        <v>7.696409085656662e-11</v>
       </c>
       <c r="F167" t="n">
-        <v>9.11387338341205e-11</v>
+        <v>5.244644348621654e-10</v>
       </c>
       <c r="G167" t="n">
-        <v>-6.230006658574363e-12</v>
+        <v>2.39335942627094e-10</v>
       </c>
       <c r="H167" t="n">
-        <v>6.387369600344458e-11</v>
+        <v>1.581421669355258e-09</v>
       </c>
       <c r="I167" t="n">
         <v/>
@@ -6935,19 +6935,19 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>-1.079721176878139e-11</v>
+        <v>-3.094502973894881e-12</v>
       </c>
       <c r="E168" t="n">
-        <v>-1.679332527508257e-12</v>
+        <v>4.708200944392907e-10</v>
       </c>
       <c r="F168" t="n">
-        <v>5.783209344418807e-11</v>
+        <v>9.372761397105952e-10</v>
       </c>
       <c r="G168" t="n">
-        <v>-7.770225564365827e-12</v>
+        <v>6.517599696594577e-10</v>
       </c>
       <c r="H168" t="n">
-        <v>4.625662797033736e-11</v>
+        <v>1.111368568120659e-08</v>
       </c>
       <c r="I168" t="n">
         <v/>
@@ -6970,19 +6970,19 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>-8.056319279620026e-12</v>
+        <v>-1.863297208204935e-12</v>
       </c>
       <c r="E169" t="n">
-        <v>-3.867244914432287e-12</v>
+        <v>1.947909542750338e-10</v>
       </c>
       <c r="F169" t="n">
-        <v>6.150110857383696e-10</v>
+        <v>2.736182420759484e-09</v>
       </c>
       <c r="G169" t="n">
-        <v>-6.982554986843492e-12</v>
+        <v>7.231041446095402e-10</v>
       </c>
       <c r="H169" t="n">
-        <v>5.902371668218025e-11</v>
+        <v>1.41188043443519e-08</v>
       </c>
       <c r="I169" t="n">
         <v/>
@@ -7005,19 +7005,19 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>-9.775846746543702e-12</v>
+        <v>-6.645454936279534e-12</v>
       </c>
       <c r="E170" t="n">
-        <v>-3.675999469727091e-12</v>
+        <v>8.14123786396552e-11</v>
       </c>
       <c r="F170" t="n">
-        <v>8.27997685864078e-11</v>
+        <v>5.62581711825185e-10</v>
       </c>
       <c r="G170" t="n">
-        <v>-6.418277715243904e-12</v>
+        <v>2.416919092903004e-10</v>
       </c>
       <c r="H170" t="n">
-        <v>2.59788125660062e-09</v>
+        <v>4.407536735837195e-08</v>
       </c>
       <c r="I170" t="n">
         <v/>
@@ -7040,19 +7040,19 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>-9.038858789422727e-12</v>
+        <v>3.047113324137081e-11</v>
       </c>
       <c r="E171" t="n">
-        <v>5.032662089928868e-12</v>
+        <v>9.951782219618625e-12</v>
       </c>
       <c r="F171" t="n">
-        <v>8.979603468513935e-14</v>
+        <v>2.914129666389257e-12</v>
       </c>
       <c r="G171" t="n">
-        <v>-3.694552274289041e-12</v>
+        <v>3.141266480086845e-13</v>
       </c>
       <c r="H171" t="n">
-        <v>1.771343251686019e-12</v>
+        <v>2.90115890781308e-13</v>
       </c>
       <c r="I171" t="n">
         <v/>
@@ -7075,19 +7075,19 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>-1.186384962340377e-13</v>
+        <v>-3.884056609508052e-12</v>
       </c>
       <c r="E172" t="n">
-        <v>-3.533387507178138e-12</v>
+        <v>3.878998446583182e-11</v>
       </c>
       <c r="F172" t="n">
-        <v>9.04199218232293e-11</v>
+        <v>3.412052817371099e-10</v>
       </c>
       <c r="G172" t="n">
-        <v>2.36537958191069e-13</v>
+        <v>1.709823853943311e-10</v>
       </c>
       <c r="H172" t="n">
-        <v>2.213201267895248e-11</v>
+        <v>7.06744387757004e-10</v>
       </c>
       <c r="I172" t="n">
         <v/>
@@ -7110,19 +7110,19 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>-7.43775792073763e-12</v>
+        <v>-8.19178229676602e-12</v>
       </c>
       <c r="E173" t="n">
-        <v>9.635007757439382e-12</v>
+        <v>1.406847479140909e-10</v>
       </c>
       <c r="F173" t="n">
-        <v>9.497945715380256e-11</v>
+        <v>5.938906702969686e-10</v>
       </c>
       <c r="G173" t="n">
-        <v>5.741105532634333e-13</v>
+        <v>3.625436156087968e-10</v>
       </c>
       <c r="H173" t="n">
-        <v>2.471924814056828e-11</v>
+        <v>1.226276354997859e-09</v>
       </c>
       <c r="I173" t="n">
         <v/>
@@ -7145,19 +7145,19 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>-8.122297981427073e-12</v>
+        <v>-7.290321913821747e-12</v>
       </c>
       <c r="E174" t="n">
-        <v>-2.675272163148212e-12</v>
+        <v>9.127960365549923e-11</v>
       </c>
       <c r="F174" t="n">
-        <v>9.126591570984202e-10</v>
+        <v>1.050424089191138e-09</v>
       </c>
       <c r="G174" t="n">
-        <v>1.096231340094624e-12</v>
+        <v>3.767220157928805e-10</v>
       </c>
       <c r="H174" t="n">
-        <v>2.505241231307428e-11</v>
+        <v>1.236014487965081e-09</v>
       </c>
       <c r="I174" t="n">
         <v/>
@@ -7180,19 +7180,19 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>-9.079679511445215e-12</v>
+        <v>-9.783522282212563e-12</v>
       </c>
       <c r="E175" t="n">
-        <v>-4.947313652093487e-12</v>
+        <v>6.151035947588454e-11</v>
       </c>
       <c r="F175" t="n">
-        <v>8.116458450321168e-11</v>
+        <v>4.450595229319256e-10</v>
       </c>
       <c r="G175" t="n">
-        <v>2.330070587494129e-11</v>
+        <v>5.191798970563995e-10</v>
       </c>
       <c r="H175" t="n">
-        <v>1.847708569542248e-11</v>
+        <v>1.191399521603229e-09</v>
       </c>
       <c r="I175" t="n">
         <v/>
@@ -7215,19 +7215,19 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>-7.251869993791434e-12</v>
+        <v>-8.708901254072734e-12</v>
       </c>
       <c r="E176" t="n">
-        <v>1.614631621248299e-13</v>
+        <v>2.406022958388071e-13</v>
       </c>
       <c r="F176" t="n">
-        <v>8.191224004957263e-14</v>
+        <v>1.436630222903866e-12</v>
       </c>
       <c r="G176" t="n">
-        <v>2.056456363142489e-12</v>
+        <v>-7.658502396159581e-13</v>
       </c>
       <c r="H176" t="n">
-        <v>-2.068105489637721e-12</v>
+        <v>-3.752546872173415e-13</v>
       </c>
       <c r="I176" t="n">
         <v/>
@@ -7250,19 +7250,19 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1.357298054516675e-12</v>
+        <v>1.369285336127888e-10</v>
       </c>
       <c r="E177" t="n">
-        <v>1.16407071729417e-11</v>
+        <v>1.111744029946482e-10</v>
       </c>
       <c r="F177" t="n">
-        <v>5.245316964820667e-10</v>
+        <v>7.404207865856665e-10</v>
       </c>
       <c r="G177" t="n">
-        <v>3.402691609755258e-11</v>
+        <v>4.162985231179139e-10</v>
       </c>
       <c r="H177" t="n">
-        <v>9.281646925500737e-10</v>
+        <v>1.752653406099677e-09</v>
       </c>
       <c r="I177" t="n">
         <v/>
@@ -7285,19 +7285,19 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>5.418727493558772e-11</v>
+        <v>8.478878643307771e-12</v>
       </c>
       <c r="E178" t="n">
-        <v>0.1521325782296414</v>
+        <v>0.1762870552421647</v>
       </c>
       <c r="F178" t="n">
-        <v>1.710300648478072e-09</v>
+        <v>1.638500370964857e-09</v>
       </c>
       <c r="G178" t="n">
-        <v>1.792103746024535e-11</v>
+        <v>0.0004118940211068839</v>
       </c>
       <c r="H178" t="n">
-        <v>6.683982211006038e-10</v>
+        <v>3.157096464477926e-08</v>
       </c>
       <c r="I178" t="n">
         <v/>
@@ -7320,19 +7320,19 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>5.538264364373573e-12</v>
+        <v>8.319273397686423e-12</v>
       </c>
       <c r="E179" t="n">
-        <v>8.709812066404416e-12</v>
+        <v>3.096514262781678e-10</v>
       </c>
       <c r="F179" t="n">
-        <v>4.142200485956749e-13</v>
+        <v>0.290085074514604</v>
       </c>
       <c r="G179" t="n">
-        <v>1.635236835152759e-11</v>
+        <v>9.935487757802836e-09</v>
       </c>
       <c r="H179" t="n">
-        <v>4.708954644778897e-10</v>
+        <v>1.432601521383932e-08</v>
       </c>
       <c r="I179" t="n">
         <v/>
@@ -7355,19 +7355,19 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>-4.780979829317597e-12</v>
+        <v>7.374282419212926e-11</v>
       </c>
       <c r="E180" t="n">
-        <v>1.542003568809198e-11</v>
+        <v>5.817039956913655e-10</v>
       </c>
       <c r="F180" t="n">
-        <v>5.426969194506089e-10</v>
+        <v>3.051349544007296e-09</v>
       </c>
       <c r="G180" t="n">
-        <v>2.888735859350121e-12</v>
+        <v>0.0008984954303954078</v>
       </c>
       <c r="H180" t="n">
-        <v>2.638103105078589e-09</v>
+        <v>5.212724321347923e-08</v>
       </c>
       <c r="I180" t="n">
         <v/>
@@ -7390,19 +7390,19 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>-1.057388637987392e-12</v>
+        <v>-1.558556274026872e-13</v>
       </c>
       <c r="E181" t="n">
-        <v>1.378129185263285e-11</v>
+        <v>1.071922974809948e-10</v>
       </c>
       <c r="F181" t="n">
-        <v>7.93849305389142e-10</v>
+        <v>7.418155351404575e-10</v>
       </c>
       <c r="G181" t="n">
-        <v>3.186735942394794e-11</v>
+        <v>4.00503475979635e-10</v>
       </c>
       <c r="H181" t="n">
-        <v>1.679884135495855e-10</v>
+        <v>0.003113491206743979</v>
       </c>
       <c r="I181" t="n">
         <v/>
@@ -7424,7 +7424,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>0.0212351</v>
+        <v>0.02973639219999313</v>
       </c>
     </row>
   </sheetData>
@@ -7478,10 +7478,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2247648674539142</v>
+        <v>0.4365964458709515</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.1862517895818428</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>

--- a/6node_spain/output_all.xlsx
+++ b/6node_spain/output_all.xlsx
@@ -14,6 +14,7 @@
     <sheet name="fij_level" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="solver_time" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="sh_level" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="mip_opt_gap" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,19 +460,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.957506279652943</v>
+        <v>0.5227848035737043</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3219984429901943</v>
+        <v>0.1360196946354306</v>
       </c>
       <c r="D2" t="n">
-        <v>1.245684889957986</v>
+        <v>0.2282864457862377</v>
       </c>
       <c r="E2" t="n">
-        <v>6.115042574241787e-08</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.656643958524995</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -558,16 +559,16 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1.964597279311804e-09</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1.455308137692222</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.200580695646784e-09</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8681712535801821</v>
+        <v>0.8713080059561737</v>
       </c>
     </row>
     <row r="4">
@@ -580,19 +581,19 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>1.964597279311804e-09</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6208333455715651</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1.549967327866147e-09</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2262353439614763</v>
+        <v>0.226699491059051</v>
       </c>
     </row>
     <row r="5">
@@ -605,10 +606,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>1.455308137692222</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6208333455715651</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -617,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.3804774096437295</v>
       </c>
     </row>
     <row r="6">
@@ -630,10 +631,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>1.200580695646784e-09</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1.549967327866147e-09</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -655,13 +656,13 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8681712535801821</v>
+        <v>0.8713080059561737</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2262353439614763</v>
+        <v>0.226699491059051</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.3804774096437295</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -757,13 +758,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1533211854451907</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1746731819131451</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -782,13 +783,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1732682923149792</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2973395180660651</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -801,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.151738315241142</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1717763677294855</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -813,7 +814,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>2.067326088095456e-09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -838,7 +839,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>9.714338222721608e-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -851,16 +852,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1762870596787873</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2887762466225903</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-6.828283494186849e-09</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.091150281240516e-09</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -922,19 +923,19 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -944,22 +945,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8466788145548093</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8253268180868549</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -969,22 +970,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8267317076850208</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7026604819339349</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -994,22 +995,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.848261684758858</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8282236322705145</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9999999979326739</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1019,22 +1020,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9999999990285662</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1044,19 +1045,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8237129403212127</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7112237533774097</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1.000000006828283</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9999999989088497</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1121,26 +1122,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>i2</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v/>
-      </c>
-      <c r="E2" t="n">
-        <v>6.999058060787945e-08</v>
-      </c>
-      <c r="F2" t="n">
-        <v>6.928830899745241e-11</v>
+          <t>i3</t>
+        </is>
       </c>
       <c r="G2" t="n">
-        <v>3.974360684676744e-11</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>5.158072893753792e-11</v>
-      </c>
-      <c r="I2" t="n">
-        <v>4.326298760763133e-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1156,26 +1145,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>i3</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v/>
-      </c>
-      <c r="E3" t="n">
-        <v>-8.517692356288191e-12</v>
+          <t>i4</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>9.167244382282194e-10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3.534099445956839e-11</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4.702407910399666e-11</v>
-      </c>
-      <c r="I3" t="n">
-        <v>3.84925830094839e-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1191,26 +1165,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>i4</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v/>
-      </c>
-      <c r="E4" t="n">
-        <v>1.297692133802654e-11</v>
-      </c>
-      <c r="F4" t="n">
-        <v>5.11799366249469e-11</v>
-      </c>
-      <c r="G4" t="n">
-        <v>5.592277644259414e-10</v>
-      </c>
-      <c r="H4" t="n">
-        <v>5.667653686536655e-11</v>
+          <t>i5</t>
+        </is>
       </c>
       <c r="I4" t="n">
-        <v>6.638373458011241e-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1226,26 +1185,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>i5</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v/>
+          <t>i6</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>4.248445427333001e-11</v>
-      </c>
-      <c r="F5" t="n">
-        <v>7.409721128955967e-12</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2.969710572324172e-11</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.981827410239557e-09</v>
-      </c>
-      <c r="I5" t="n">
-        <v>9.239380299570248e-12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1256,31 +1200,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v/>
-      </c>
-      <c r="E6" t="n">
-        <v>-2.532132872371463e-11</v>
+          <t>i3</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>-4.345964607504906e-12</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-3.26956801572254e-12</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-3.23459156768826e-12</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>2.102852451455637e-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1296,26 +1228,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>i1</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v/>
-      </c>
-      <c r="E7" t="n">
-        <v>-1.601317232917517e-11</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5.959150226130867e-12</v>
-      </c>
-      <c r="G7" t="n">
-        <v>6.341933088659929e-12</v>
+          <t>i5</t>
+        </is>
       </c>
       <c r="H7" t="n">
-        <v>4.80197797886277e-12</v>
-      </c>
-      <c r="I7" t="n">
-        <v>8.387211465641228e-12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1331,26 +1248,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>i3</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v/>
-      </c>
-      <c r="E8" t="n">
-        <v>-2.398790323814109e-11</v>
+          <t>i6</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>7.508594057698467e-11</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>2.605581044207033e-11</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2.625550513533907e-11</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2.159591187208599e-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1361,31 +1266,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>i4</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v/>
-      </c>
-      <c r="E9" t="n">
-        <v>-2.560450291038688e-11</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-1.250301784195878e-12</v>
+          <t>i2</t>
+        </is>
       </c>
       <c r="G9" t="n">
-        <v>2.383255484211595e-11</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.405983904694474e-12</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.094479851257352e-12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1396,31 +1286,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>i5</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v/>
-      </c>
-      <c r="E10" t="n">
-        <v>-2.524171739222478e-11</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-6.53354795162985e-12</v>
-      </c>
-      <c r="G10" t="n">
-        <v>6.593327105312834e-12</v>
+          <t>i4</t>
+        </is>
       </c>
       <c r="H10" t="n">
-        <v>4.289475409806861e-11</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.063167934603811e-12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1431,31 +1309,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v/>
+          <t>i5</t>
+        </is>
       </c>
       <c r="E11" t="n">
-        <v>-2.652385306480064e-11</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-1.347801608289485e-11</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-1.11837940841483e-11</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-1.180863341091301e-11</v>
-      </c>
-      <c r="I11" t="n">
-        <v>6.896623672783823e-12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1466,31 +1329,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>i1</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v/>
-      </c>
-      <c r="E12" t="n">
-        <v>-1.349631069680271e-11</v>
+          <t>i2</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>-3.442645605788137e-12</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4.699640858502962e-12</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>2.930320314507146e-12</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>6.533477415660082e-12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1501,31 +1355,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>i2</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v/>
+          <t>i3</t>
+        </is>
       </c>
       <c r="E13" t="n">
-        <v>-2.137967613877841e-11</v>
-      </c>
-      <c r="F13" t="n">
-        <v>4.159345762119093e-12</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2.390040238049258e-11</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2.278974652571581e-11</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1.846117574925373e-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1536,31 +1375,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>i4</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v/>
-      </c>
-      <c r="E14" t="n">
-        <v>-2.541296836343197e-11</v>
+          <t>i6</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>-6.593910520207246e-12</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2.619235415358592e-11</v>
-      </c>
-      <c r="H14" t="n">
-        <v>4.019534116066079e-12</v>
-      </c>
-      <c r="I14" t="n">
-        <v>3.757288928822035e-12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1571,31 +1395,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>i5</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v/>
+          <t>i6</t>
+        </is>
       </c>
       <c r="E15" t="n">
-        <v>-2.476580260311988e-11</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>-9.717717315927922e-12</v>
-      </c>
-      <c r="G15" t="n">
-        <v>8.710478816495473e-12</v>
-      </c>
-      <c r="H15" t="n">
-        <v>5.0503132749824e-11</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.965408547631892e-12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1606,31 +1421,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v/>
+          <t>i2</t>
+        </is>
       </c>
       <c r="E16" t="n">
-        <v>-2.615357392930178e-11</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.467427619293542e-11</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-1.063701612676422e-11</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-1.148093199285091e-11</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1.115122227137664e-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1641,31 +1444,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>i1</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v/>
+          <t>i4</t>
+        </is>
       </c>
       <c r="E17" t="n">
-        <v>1.333555246691729e-11</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>1.257801681570798e-11</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.678407406024111e-12</v>
-      </c>
-      <c r="H17" t="n">
-        <v>6.640279428968185e-12</v>
-      </c>
-      <c r="I17" t="n">
-        <v>7.270373152011178e-12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1676,42 +1470,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>i2</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v/>
-      </c>
-      <c r="E18" t="n">
-        <v>-2.531036904557456e-11</v>
+          <t>i5</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>3.845404188217079e-12</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-4.790806084144591e-12</v>
-      </c>
-      <c r="H18" t="n">
-        <v>4.059346884763075e-12</v>
-      </c>
-      <c r="I18" t="n">
-        <v>-1.322564548797459e-12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1719,274 +1498,154 @@
           <t>i3</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v/>
-      </c>
-      <c r="E19" t="n">
-        <v>-2.521931440510474e-11</v>
-      </c>
       <c r="F19" t="n">
-        <v>2.396590404045999e-11</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-3.890028350183149e-12</v>
-      </c>
-      <c r="H19" t="n">
-        <v>6.10422660192328e-12</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2.147404492661879e-13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>i5</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v/>
-      </c>
-      <c r="E20" t="n">
-        <v>-2.494080905260137e-11</v>
+          <t>i1</t>
+        </is>
       </c>
       <c r="F20" t="n">
-        <v>-4.984879779464657e-12</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-3.317333210056965e-12</v>
-      </c>
-      <c r="H20" t="n">
-        <v>4.565089213730729e-11</v>
-      </c>
-      <c r="I20" t="n">
-        <v>-5.417857837240488e-12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v/>
-      </c>
-      <c r="E21" t="n">
-        <v>-2.608047082408938e-11</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-7.153155569694226e-12</v>
+          <t>i3</t>
+        </is>
       </c>
       <c r="G21" t="n">
-        <v>-9.734806231061665e-12</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-5.777077470049302e-12</v>
-      </c>
-      <c r="I21" t="n">
-        <v>5.137158542891614e-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v/>
-      </c>
-      <c r="E22" t="n">
-        <v>4.163790774031392e-11</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-5.179228738662628e-12</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2.375227234854036e-12</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-3.625808840505989e-12</v>
-      </c>
-      <c r="I22" t="n">
-        <v>-4.569803176119799e-12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>i2</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v/>
-      </c>
-      <c r="E23" t="n">
-        <v>-2.45959100900128e-11</v>
-      </c>
-      <c r="F23" t="n">
-        <v>-5.244038420594909e-12</v>
-      </c>
-      <c r="G23" t="n">
-        <v>4.866236079404874e-12</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-1.114925771781769e-12</v>
+          <t>i6</t>
+        </is>
       </c>
       <c r="I23" t="n">
-        <v>-5.96246133064231e-12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>i3</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v/>
-      </c>
-      <c r="E24" t="n">
-        <v>-2.46352614361717e-11</v>
-      </c>
-      <c r="F24" t="n">
-        <v>3.524129394245783e-12</v>
+          <t>i4</t>
+        </is>
       </c>
       <c r="G24" t="n">
-        <v>7.200697324693422e-12</v>
-      </c>
-      <c r="H24" t="n">
-        <v>7.147330841935875e-13</v>
-      </c>
-      <c r="I24" t="n">
-        <v>-4.851387357838654e-12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v/>
-      </c>
-      <c r="E25" t="n">
-        <v>-2.491501054227165e-11</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-6.79068821080299e-12</v>
-      </c>
-      <c r="G25" t="n">
-        <v>2.654636761578175e-11</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-1.234899555323412e-12</v>
-      </c>
-      <c r="I25" t="n">
-        <v>-4.644452938013519e-12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v/>
-      </c>
-      <c r="E26" t="n">
-        <v>-2.643234658306321e-11</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-1.522472050670646e-11</v>
-      </c>
-      <c r="G26" t="n">
-        <v>-1.085641720278655e-11</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-1.309067500878875e-11</v>
-      </c>
-      <c r="I26" t="n">
-        <v>-2.378686948627146e-12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2000,553 +1659,319 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v/>
-      </c>
-      <c r="E27" t="n">
-        <v>-2.546243969591453e-11</v>
-      </c>
-      <c r="F27" t="n">
-        <v>-9.808985288979614e-12</v>
-      </c>
-      <c r="G27" t="n">
-        <v>-1.06501407245235e-11</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-1.066500308154121e-11</v>
-      </c>
-      <c r="I27" t="n">
-        <v>-1.750305279283975e-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>i2</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v/>
-      </c>
-      <c r="E28" t="n">
-        <v>-2.607294266530008e-11</v>
-      </c>
-      <c r="F28" t="n">
-        <v>-1.226579554278199e-11</v>
-      </c>
-      <c r="G28" t="n">
-        <v>-1.207960782850364e-11</v>
+          <t>i4</t>
+        </is>
       </c>
       <c r="H28" t="n">
-        <v>-1.176530887048781e-11</v>
-      </c>
-      <c r="I28" t="n">
-        <v>-1.852807855073953e-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>i3</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v/>
+          <t>i6</t>
+        </is>
       </c>
       <c r="E29" t="n">
-        <v>-2.644517413999881e-11</v>
-      </c>
-      <c r="F29" t="n">
-        <v>-9.53376148070472e-12</v>
-      </c>
-      <c r="G29" t="n">
-        <v>-1.184161379368201e-11</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-1.13367422113991e-11</v>
-      </c>
-      <c r="I29" t="n">
-        <v>-1.851409215618304e-11</v>
+        <v>-1.127737507781352e-10</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>i4</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v/>
-      </c>
-      <c r="E30" t="n">
-        <v>-2.610393496288255e-11</v>
-      </c>
-      <c r="F30" t="n">
-        <v>-8.293746414462299e-12</v>
-      </c>
-      <c r="G30" t="n">
-        <v>3.839055529988133e-13</v>
+          <t>i1</t>
+        </is>
       </c>
       <c r="H30" t="n">
-        <v>-6.189487749700572e-12</v>
-      </c>
-      <c r="I30" t="n">
-        <v>-1.647477377804845e-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>i5</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v/>
+          <t>i2</t>
+        </is>
       </c>
       <c r="E31" t="n">
-        <v>-2.647674613711317e-11</v>
-      </c>
-      <c r="F31" t="n">
-        <v>-1.507957936805244e-11</v>
-      </c>
-      <c r="G31" t="n">
-        <v>-1.155146738318009e-11</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-5.502174027914697e-12</v>
-      </c>
-      <c r="I31" t="n">
-        <v>-1.918695896312168e-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>i2</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>-2.246746265447055e-11</v>
-      </c>
-      <c r="E32" t="n">
-        <v/>
-      </c>
-      <c r="F32" t="n">
-        <v>-6.207004017356655e-12</v>
+          <t>i4</t>
+        </is>
       </c>
       <c r="G32" t="n">
-        <v>-2.261012074269936e-12</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1.771961344102814e-13</v>
-      </c>
-      <c r="I32" t="n">
-        <v>9.214262095099883e-13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-2.52541070637471e-11</v>
-      </c>
-      <c r="E33" t="n">
-        <v/>
-      </c>
-      <c r="F33" t="n">
-        <v>-2.780873296573271e-13</v>
-      </c>
-      <c r="G33" t="n">
-        <v>6.244916854562583e-11</v>
-      </c>
-      <c r="H33" t="n">
-        <v>3.204204497080095e-12</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>2.723321997475401e-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>i4</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>-2.492311828449002e-11</v>
-      </c>
-      <c r="E34" t="n">
-        <v/>
-      </c>
-      <c r="F34" t="n">
-        <v>-2.944199973576939e-12</v>
-      </c>
-      <c r="G34" t="n">
-        <v>8.490779196552646e-11</v>
+          <t>i5</t>
+        </is>
       </c>
       <c r="H34" t="n">
-        <v>8.600081624639062e-12</v>
-      </c>
-      <c r="I34" t="n">
-        <v>5.099367694226665e-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-2.496573138833164e-11</v>
-      </c>
-      <c r="E35" t="n">
-        <v/>
-      </c>
-      <c r="F35" t="n">
-        <v>-1.115459589445084e-11</v>
-      </c>
-      <c r="G35" t="n">
-        <v>2.052739067104875e-11</v>
-      </c>
-      <c r="H35" t="n">
-        <v>2.473316946899831e-11</v>
-      </c>
-      <c r="I35" t="n">
-        <v>2.378582200396776e-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>-2.621921380589665e-11</v>
+          <t>i1</t>
+        </is>
       </c>
       <c r="E36" t="n">
-        <v/>
-      </c>
-      <c r="F36" t="n">
-        <v>-1.183180771159139e-11</v>
-      </c>
-      <c r="G36" t="n">
-        <v>4.834359262927933e-11</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-9.527970371581851e-12</v>
-      </c>
-      <c r="I36" t="n">
-        <v>9.115337430624441e-11</v>
+        <v>-1.127737507781352e-10</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>7.149333214431222e-08</v>
-      </c>
-      <c r="E37" t="n">
-        <v/>
-      </c>
-      <c r="F37" t="n">
-        <v>1.760550464640016e-13</v>
-      </c>
-      <c r="G37" t="n">
-        <v>5.617993208727526e-11</v>
-      </c>
-      <c r="H37" t="n">
-        <v>2.666538278224646e-11</v>
-      </c>
-      <c r="I37" t="n">
-        <v>9.60319571309135e-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>9.171847876463956e-11</v>
-      </c>
-      <c r="E38" t="n">
-        <v/>
-      </c>
-      <c r="F38" t="n">
-        <v>4.779856838989358e-10</v>
-      </c>
-      <c r="G38" t="n">
-        <v>1.189354355816358e-09</v>
-      </c>
-      <c r="H38" t="n">
-        <v>9.502232252289786e-11</v>
-      </c>
-      <c r="I38" t="n">
-        <v>3.477754672947561e-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-1.976238226115868e-11</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v/>
-      </c>
-      <c r="F39" t="n">
-        <v>2.789273119478635e-11</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.1512976964335687</v>
-      </c>
-      <c r="H39" t="n">
-        <v>2.976570223705225e-11</v>
-      </c>
-      <c r="I39" t="n">
-        <v>2.677082496817983e-10</v>
+        <v>-1.127737507781352e-10</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>i5</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>-1.216530656933102e-11</v>
+          <t>i2</t>
+        </is>
       </c>
       <c r="E40" t="n">
-        <v/>
-      </c>
-      <c r="F40" t="n">
-        <v>2.589668727451095e-12</v>
-      </c>
-      <c r="G40" t="n">
-        <v>6.133868722836477e-11</v>
-      </c>
-      <c r="H40" t="n">
-        <v>2.901680246233684e-10</v>
-      </c>
-      <c r="I40" t="n">
-        <v>1.064434180176383e-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>-2.535932560259697e-11</v>
-      </c>
-      <c r="E41" t="n">
-        <v/>
+          <t>i3</t>
+        </is>
       </c>
       <c r="F41" t="n">
-        <v>-4.160862238367848e-12</v>
-      </c>
-      <c r="G41" t="n">
-        <v>1.777922993048335e-10</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-6.100497526861535e-12</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0.1748626584843367</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-2.212126158039726e-11</v>
-      </c>
-      <c r="E42" t="n">
-        <v/>
-      </c>
-      <c r="F42" t="n">
-        <v>-7.015983493198517e-12</v>
-      </c>
-      <c r="G42" t="n">
-        <v>5.25792932813211e-11</v>
-      </c>
-      <c r="H42" t="n">
-        <v>6.904439248577098e-12</v>
-      </c>
-      <c r="I42" t="n">
-        <v>4.591527411035112e-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2560,68 +1985,41 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>8.70678681950048e-11</v>
-      </c>
-      <c r="E43" t="n">
-        <v/>
-      </c>
-      <c r="F43" t="n">
-        <v>1.41366110366308e-11</v>
-      </c>
-      <c r="G43" t="n">
-        <v>7.279188165321847e-12</v>
-      </c>
-      <c r="H43" t="n">
-        <v>1.702258837665909e-11</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1.563391316109112e-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-2.452524993813465e-11</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v/>
-      </c>
-      <c r="F44" t="n">
-        <v>6.291270527295881e-12</v>
-      </c>
-      <c r="G44" t="n">
-        <v>1.328390603144198e-09</v>
-      </c>
-      <c r="H44" t="n">
-        <v>1.121577725038919e-11</v>
-      </c>
-      <c r="I44" t="n">
-        <v>9.69500067989253e-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2629,34 +2027,22 @@
           <t>i5</t>
         </is>
       </c>
-      <c r="D45" t="n">
-        <v>-2.358341492397804e-11</v>
-      </c>
-      <c r="E45" t="n">
-        <v/>
-      </c>
       <c r="F45" t="n">
-        <v>-4.670598792276939e-12</v>
-      </c>
-      <c r="G45" t="n">
-        <v>5.772923156528802e-11</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>6.575100982421754e-11</v>
-      </c>
-      <c r="I45" t="n">
-        <v>5.752833544446118e-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2664,34 +2050,19 @@
           <t>i6</t>
         </is>
       </c>
-      <c r="D46" t="n">
-        <v>-2.544742137154831e-11</v>
-      </c>
-      <c r="E46" t="n">
-        <v/>
-      </c>
-      <c r="F46" t="n">
-        <v>-8.242670997715776e-12</v>
-      </c>
-      <c r="G46" t="n">
-        <v>1.907358236569441e-10</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-9.063223507464176e-12</v>
-      </c>
       <c r="I46" t="n">
-        <v>2.202753335498146e-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2699,99 +2070,54 @@
           <t>i1</t>
         </is>
       </c>
-      <c r="D47" t="n">
-        <v>-2.298385262737955e-11</v>
-      </c>
-      <c r="E47" t="n">
-        <v/>
-      </c>
       <c r="F47" t="n">
-        <v>-2.894513402582874e-12</v>
-      </c>
-      <c r="G47" t="n">
-        <v>4.343283452489355e-11</v>
-      </c>
-      <c r="H47" t="n">
-        <v>6.780693368571739e-12</v>
-      </c>
-      <c r="I47" t="n">
-        <v>3.150001300299471e-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-2.174519845100084e-11</v>
-      </c>
-      <c r="E48" t="n">
-        <v/>
-      </c>
-      <c r="F48" t="n">
-        <v>5.882576838671305e-12</v>
-      </c>
-      <c r="G48" t="n">
-        <v>2.47463626252501e-12</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-3.929117678794021e-13</v>
-      </c>
-      <c r="I48" t="n">
-        <v>9.065769894363263e-13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>i3</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>-2.483802070178098e-11</v>
-      </c>
-      <c r="E49" t="n">
-        <v/>
-      </c>
-      <c r="F49" t="n">
-        <v>2.841431808774996e-11</v>
+          <t>i4</t>
+        </is>
       </c>
       <c r="G49" t="n">
-        <v>1.861514665300926e-10</v>
-      </c>
-      <c r="H49" t="n">
-        <v>4.893298672682964e-12</v>
-      </c>
-      <c r="I49" t="n">
-        <v>3.147478509978264e-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2801,67 +2127,40 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-2.417164179275057e-11</v>
-      </c>
-      <c r="E50" t="n">
-        <v/>
-      </c>
-      <c r="F50" t="n">
-        <v>-2.435618421820755e-12</v>
-      </c>
-      <c r="G50" t="n">
-        <v>4.342900622811758e-11</v>
-      </c>
-      <c r="H50" t="n">
-        <v>3.881679466407714e-11</v>
-      </c>
-      <c r="I50" t="n">
-        <v>3.123665509882629e-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>-2.563877688320901e-11</v>
-      </c>
-      <c r="E51" t="n">
-        <v/>
+          <t>i3</t>
+        </is>
       </c>
       <c r="F51" t="n">
-        <v>4.226598478008816e-13</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>1.451905002420831e-10</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-4.261893872740633e-12</v>
-      </c>
-      <c r="I51" t="n">
-        <v>3.776701326160373e-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2871,37 +2170,28 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>-2.262897176197638e-11</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v/>
-      </c>
-      <c r="F52" t="n">
-        <v>-1.113341576998017e-11</v>
-      </c>
-      <c r="G52" t="n">
-        <v>2.091350199863275e-11</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-3.491220280753358e-12</v>
+        <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>2.616751774908712e-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2909,139 +2199,79 @@
           <t>i2</t>
         </is>
       </c>
-      <c r="D53" t="n">
-        <v>-1.71665638966024e-11</v>
-      </c>
       <c r="E53" t="n">
-        <v/>
-      </c>
-      <c r="F53" t="n">
-        <v>-5.221235825431453e-12</v>
-      </c>
-      <c r="G53" t="n">
-        <v>-1.756038270450987e-12</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-4.543697468897777e-12</v>
-      </c>
-      <c r="I53" t="n">
-        <v>2.219204742066074e-12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-2.401043869703441e-11</v>
-      </c>
-      <c r="E54" t="n">
-        <v/>
-      </c>
-      <c r="F54" t="n">
-        <v>3.003456179814342e-12</v>
-      </c>
-      <c r="G54" t="n">
-        <v>6.642744599908534e-11</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-5.098315268338756e-13</v>
-      </c>
-      <c r="I54" t="n">
-        <v>3.587296472238284e-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>i4</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>-2.396148667700268e-11</v>
-      </c>
-      <c r="E55" t="n">
-        <v/>
-      </c>
-      <c r="F55" t="n">
-        <v>-2.327956271286725e-12</v>
-      </c>
-      <c r="G55" t="n">
-        <v>8.766396554607094e-11</v>
+          <t>i2</t>
+        </is>
       </c>
       <c r="H55" t="n">
-        <v>2.520498551433558e-13</v>
-      </c>
-      <c r="I55" t="n">
-        <v>5.637196398148653e-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>-2.60366545142928e-11</v>
-      </c>
-      <c r="E56" t="n">
-        <v/>
-      </c>
-      <c r="F56" t="n">
-        <v>-1.195193109402557e-11</v>
-      </c>
-      <c r="G56" t="n">
-        <v>4.785002689598492e-11</v>
+          <t>i3</t>
+        </is>
       </c>
       <c r="H56" t="n">
-        <v>-1.22364621269749e-11</v>
-      </c>
-      <c r="I56" t="n">
-        <v>9.237104422022118e-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3050,103 +2280,61 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>-2.514800715574353e-11</v>
-      </c>
-      <c r="E57" t="n">
-        <v/>
-      </c>
-      <c r="F57" t="n">
-        <v>-1.155594003589443e-11</v>
-      </c>
-      <c r="G57" t="n">
-        <v>4.086136984478308e-11</v>
+        <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>-9.672613765538966e-12</v>
-      </c>
-      <c r="I57" t="n">
-        <v>-5.527242560222088e-12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>i2</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>-2.568717630713048e-11</v>
-      </c>
-      <c r="E58" t="n">
-        <v/>
-      </c>
-      <c r="F58" t="n">
-        <v>-8.49699297865307e-12</v>
-      </c>
-      <c r="G58" t="n">
-        <v>2.007393770974105e-12</v>
+          <t>i1</t>
+        </is>
       </c>
       <c r="H58" t="n">
-        <v>-1.218178893932623e-11</v>
-      </c>
-      <c r="I58" t="n">
-        <v>-1.221671130008417e-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>-2.622539192077402e-11</v>
-      </c>
-      <c r="E59" t="n">
-        <v/>
-      </c>
-      <c r="F59" t="n">
-        <v>-4.238711155925126e-12</v>
-      </c>
-      <c r="G59" t="n">
-        <v>1.323317029222635e-10</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-1.077940297405817e-11</v>
-      </c>
-      <c r="I59" t="n">
-        <v>-6.053574026719726e-12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3154,554 +2342,326 @@
           <t>i4</t>
         </is>
       </c>
-      <c r="D60" t="n">
-        <v>-2.56913562468572e-11</v>
-      </c>
-      <c r="E60" t="n">
-        <v/>
-      </c>
-      <c r="F60" t="n">
-        <v>4.775774724781195e-13</v>
-      </c>
-      <c r="G60" t="n">
-        <v>3.966371897143478e-10</v>
-      </c>
       <c r="H60" t="n">
-        <v>-3.997629901407194e-12</v>
-      </c>
-      <c r="I60" t="n">
-        <v>7.642654030247045e-13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>i5</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>-2.610994410193399e-11</v>
-      </c>
-      <c r="E61" t="n">
-        <v/>
-      </c>
-      <c r="F61" t="n">
-        <v>-1.195725154005103e-11</v>
-      </c>
-      <c r="G61" t="n">
-        <v>3.807458647638946e-11</v>
+          <t>i3</t>
+        </is>
       </c>
       <c r="H61" t="n">
-        <v>-4.581190670061632e-12</v>
-      </c>
-      <c r="I61" t="n">
-        <v>-5.991535153775088e-12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>i2</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>-1.219565813894915e-11</v>
-      </c>
-      <c r="E62" t="n">
-        <v>6.322545319238239e-13</v>
-      </c>
-      <c r="F62" t="n">
-        <v/>
-      </c>
-      <c r="G62" t="n">
-        <v>2.530893639207546e-10</v>
+          <t>i5</t>
+        </is>
       </c>
       <c r="H62" t="n">
-        <v>3.874705064993068e-12</v>
-      </c>
-      <c r="I62" t="n">
-        <v>6.178898660418252e-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>i3</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>-1.224320329239846e-11</v>
+          <t>i2</t>
+        </is>
       </c>
       <c r="E63" t="n">
-        <v>-6.968433097729496e-12</v>
-      </c>
-      <c r="F63" t="n">
-        <v/>
-      </c>
-      <c r="G63" t="n">
-        <v>-1.609841727375064e-13</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-8.438009404712036e-13</v>
-      </c>
-      <c r="I63" t="n">
-        <v>1.35490364648446e-12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>-1.070936912701949e-11</v>
-      </c>
-      <c r="E64" t="n">
-        <v>-3.349905906593549e-12</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v/>
-      </c>
-      <c r="G64" t="n">
-        <v>2.891852122936442e-10</v>
-      </c>
-      <c r="H64" t="n">
-        <v>7.706271816357955e-12</v>
-      </c>
-      <c r="I64" t="n">
-        <v>7.953654233464686e-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>i5</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>-1.496373587753474e-11</v>
-      </c>
-      <c r="E65" t="n">
-        <v>-1.137759259493626e-11</v>
-      </c>
-      <c r="F65" t="n">
-        <v/>
+          <t>i4</t>
+        </is>
       </c>
       <c r="G65" t="n">
-        <v>1.061777031396214e-10</v>
+        <v>1</v>
       </c>
       <c r="H65" t="n">
-        <v>2.131538577219962e-11</v>
-      </c>
-      <c r="I65" t="n">
-        <v>4.384445770654197e-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>-1.643620808196607e-11</v>
+          <t>i2</t>
+        </is>
       </c>
       <c r="E66" t="n">
-        <v>-1.20409872712892e-11</v>
-      </c>
-      <c r="F66" t="n">
-        <v/>
-      </c>
-      <c r="G66" t="n">
-        <v>2.194144998546787e-10</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-1.020711327149125e-11</v>
-      </c>
-      <c r="I66" t="n">
-        <v>1.03029654212677e-09</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>i1</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>5.133860950255988e-11</v>
-      </c>
-      <c r="E67" t="n">
-        <v>-7.213340324440656e-12</v>
+          <t>i3</t>
+        </is>
       </c>
       <c r="F67" t="n">
-        <v/>
-      </c>
-      <c r="G67" t="n">
-        <v>1.91038335538023e-10</v>
-      </c>
-      <c r="H67" t="n">
-        <v>7.929557730697553e-12</v>
-      </c>
-      <c r="I67" t="n">
-        <v>7.055799883968218e-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>i3</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>2.986100651531016e-11</v>
-      </c>
-      <c r="E68" t="n">
-        <v>1.378095446403172e-11</v>
-      </c>
-      <c r="F68" t="n">
-        <v/>
+          <t>i4</t>
+        </is>
       </c>
       <c r="G68" t="n">
-        <v>2.99865255714681e-12</v>
-      </c>
-      <c r="H68" t="n">
-        <v>1.634230359218023e-11</v>
-      </c>
-      <c r="I68" t="n">
-        <v>2.484298601760688e-12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>i4</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>7.838282035482705e-12</v>
+          <t>i6</t>
+        </is>
       </c>
       <c r="E69" t="n">
-        <v>4.446656230586588e-12</v>
-      </c>
-      <c r="F69" t="n">
-        <v/>
-      </c>
-      <c r="G69" t="n">
-        <v>6.688005301227381e-09</v>
-      </c>
-      <c r="H69" t="n">
-        <v>7.337701225060303e-12</v>
-      </c>
-      <c r="I69" t="n">
-        <v>1.790069956089822e-09</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>i5</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>-3.475374532174636e-12</v>
+          <t>i1</t>
+        </is>
       </c>
       <c r="E70" t="n">
-        <v>-6.075646758845659e-12</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
-        <v/>
-      </c>
-      <c r="G70" t="n">
-        <v>2.027038772783739e-10</v>
-      </c>
-      <c r="H70" t="n">
-        <v>4.048202855866445e-11</v>
-      </c>
-      <c r="I70" t="n">
-        <v>7.385481096475596e-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>-1.093097913327097e-11</v>
+          <t>i3</t>
+        </is>
       </c>
       <c r="E71" t="n">
-        <v>-9.809635036282624e-12</v>
-      </c>
-      <c r="F71" t="n">
-        <v/>
-      </c>
-      <c r="G71" t="n">
-        <v>7.816055084061548e-10</v>
-      </c>
-      <c r="H71" t="n">
-        <v>-1.07554406746388e-11</v>
-      </c>
-      <c r="I71" t="n">
-        <v>2.742407033177936e-09</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>i1</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>9.580887343357152e-10</v>
-      </c>
-      <c r="E72" t="n">
-        <v>-1.515875987237702e-13</v>
-      </c>
-      <c r="F72" t="n">
-        <v/>
+          <t>i2</t>
+        </is>
       </c>
       <c r="G72" t="n">
-        <v>2.057580630445692e-10</v>
-      </c>
-      <c r="H72" t="n">
-        <v>1.980920742639763e-11</v>
-      </c>
-      <c r="I72" t="n">
-        <v>8.60754165722309e-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>i2</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>1.081219854790591e-10</v>
-      </c>
-      <c r="E73" t="n">
-        <v>4.934726991550212e-10</v>
-      </c>
-      <c r="F73" t="n">
-        <v/>
-      </c>
-      <c r="G73" t="n">
-        <v>5.431310875515554e-09</v>
-      </c>
-      <c r="H73" t="n">
-        <v>6.807480465339172e-11</v>
+          <t>i4</t>
+        </is>
       </c>
       <c r="I73" t="n">
-        <v>3.579281517466278e-09</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>i4</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>3.995291530660954e-11</v>
+          <t>i6</t>
+        </is>
       </c>
       <c r="E74" t="n">
-        <v>2.923770396170841e-11</v>
-      </c>
-      <c r="F74" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>0.1639645356674524</v>
-      </c>
-      <c r="H74" t="n">
-        <v>2.443171993681034e-11</v>
-      </c>
-      <c r="I74" t="n">
-        <v>3.60455121322542e-09</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>i5</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>9.931531605610744e-12</v>
-      </c>
-      <c r="E75" t="n">
-        <v>3.92911681919733e-12</v>
-      </c>
-      <c r="F75" t="n">
-        <v/>
+          <t>i1</t>
+        </is>
       </c>
       <c r="G75" t="n">
-        <v>2.182156087584199e-10</v>
-      </c>
-      <c r="H75" t="n">
-        <v>1.958708989706166e-10</v>
-      </c>
-      <c r="I75" t="n">
-        <v>9.767364083888732e-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3711,102 +2671,60 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>-4.528938369850443e-12</v>
-      </c>
-      <c r="E76" t="n">
-        <v>-2.518607543127918e-12</v>
-      </c>
-      <c r="F76" t="n">
-        <v/>
+          <t>i1</t>
+        </is>
       </c>
       <c r="G76" t="n">
-        <v>1.439025665086619e-09</v>
-      </c>
-      <c r="H76" t="n">
-        <v>-7.191055059384405e-12</v>
+        <v>1</v>
       </c>
       <c r="I76" t="n">
-        <v>0.2973394973009117</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>i1</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>3.761584943463705e-11</v>
+          <t>i4</t>
+        </is>
       </c>
       <c r="E77" t="n">
-        <v>-2.914762077448994e-12</v>
-      </c>
-      <c r="F77" t="n">
-        <v/>
-      </c>
-      <c r="G77" t="n">
-        <v>1.824051248289736e-10</v>
-      </c>
-      <c r="H77" t="n">
-        <v>6.700302787816376e-12</v>
-      </c>
-      <c r="I77" t="n">
-        <v>5.9795296081754e-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>i2</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>-1.175832110374955e-12</v>
-      </c>
-      <c r="E78" t="n">
-        <v>2.616676079150623e-11</v>
-      </c>
-      <c r="F78" t="n">
-        <v/>
+          <t>i6</t>
+        </is>
       </c>
       <c r="G78" t="n">
-        <v>9.6802172764193e-10</v>
-      </c>
-      <c r="H78" t="n">
-        <v>2.317816246126733e-12</v>
-      </c>
-      <c r="I78" t="n">
-        <v>8.225063552440428e-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3816,32 +2734,20 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1.141443842104217e-12</v>
+        <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>7.142772842583785e-12</v>
-      </c>
-      <c r="F79" t="n">
-        <v/>
-      </c>
-      <c r="G79" t="n">
-        <v>2.090495433094005e-12</v>
-      </c>
-      <c r="H79" t="n">
-        <v>-7.668549635568653e-14</v>
-      </c>
-      <c r="I79" t="n">
-        <v>1.731532588718119e-12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3851,67 +2757,37 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>i5</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>-5.953665352240586e-12</v>
-      </c>
-      <c r="E80" t="n">
-        <v>-2.651484514340792e-12</v>
-      </c>
-      <c r="F80" t="n">
-        <v/>
-      </c>
-      <c r="G80" t="n">
-        <v>1.819289120123292e-10</v>
-      </c>
-      <c r="H80" t="n">
-        <v>3.147547850860415e-11</v>
+          <t>i3</t>
+        </is>
       </c>
       <c r="I80" t="n">
-        <v>5.922934137284969e-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>-6.35679862582598e-12</v>
-      </c>
-      <c r="E81" t="n">
-        <v>1.717995307313529e-13</v>
-      </c>
-      <c r="F81" t="n">
-        <v/>
+          <t>i3</t>
+        </is>
       </c>
       <c r="G81" t="n">
-        <v>8.025335952940798e-10</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-5.446962883205999e-12</v>
-      </c>
-      <c r="I81" t="n">
-        <v>5.422931431787704e-09</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3921,32 +2797,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i4</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>2.849304214472199e-12</v>
-      </c>
-      <c r="E82" t="n">
-        <v>-1.118985580572481e-11</v>
-      </c>
-      <c r="F82" t="n">
-        <v/>
-      </c>
-      <c r="G82" t="n">
-        <v>1.071033872400481e-10</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-2.40425227281056e-12</v>
-      </c>
-      <c r="I82" t="n">
-        <v>4.554851923050948e-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3956,37 +2817,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>i2</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>-7.096260235564871e-12</v>
-      </c>
-      <c r="E83" t="n">
-        <v>2.323598195176411e-12</v>
-      </c>
-      <c r="F83" t="n">
-        <v/>
-      </c>
-      <c r="G83" t="n">
-        <v>2.598584313305191e-10</v>
-      </c>
-      <c r="H83" t="n">
-        <v>-1.144713173962718e-12</v>
+          <t>i6</t>
+        </is>
       </c>
       <c r="I83" t="n">
-        <v>6.591448992304301e-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3994,34 +2840,22 @@
           <t>i3</t>
         </is>
       </c>
-      <c r="D84" t="n">
-        <v>-5.796522732503674e-12</v>
-      </c>
       <c r="E84" t="n">
-        <v>-4.784709917676225e-12</v>
-      </c>
-      <c r="F84" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>4.786696020280699e-14</v>
-      </c>
-      <c r="H84" t="n">
-        <v>-2.784976110030855e-12</v>
-      </c>
-      <c r="I84" t="n">
-        <v>1.578862625958269e-12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4029,204 +2863,114 @@
           <t>i4</t>
         </is>
       </c>
-      <c r="D85" t="n">
-        <v>-4.936793824096268e-12</v>
-      </c>
-      <c r="E85" t="n">
-        <v>-2.557479716251279e-12</v>
-      </c>
-      <c r="F85" t="n">
-        <v/>
-      </c>
       <c r="G85" t="n">
-        <v>2.964078637128363e-10</v>
-      </c>
-      <c r="H85" t="n">
-        <v>7.342968474602742e-13</v>
-      </c>
-      <c r="I85" t="n">
-        <v>8.431828911545241e-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>i6</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>-1.444215303802371e-11</v>
-      </c>
-      <c r="E86" t="n">
-        <v>-1.209102943194886e-11</v>
-      </c>
-      <c r="F86" t="n">
-        <v/>
+          <t>i2</t>
+        </is>
       </c>
       <c r="G86" t="n">
-        <v>2.178475297743594e-10</v>
-      </c>
-      <c r="H86" t="n">
-        <v>-1.245109895629637e-11</v>
-      </c>
-      <c r="I86" t="n">
-        <v>1.042375188175938e-09</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>i1</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>-5.063067829997437e-12</v>
-      </c>
-      <c r="E87" t="n">
-        <v>-1.164415290130758e-11</v>
-      </c>
-      <c r="F87" t="n">
-        <v/>
+          <t>i3</t>
+        </is>
       </c>
       <c r="G87" t="n">
-        <v>1.814008843846664e-10</v>
-      </c>
-      <c r="H87" t="n">
-        <v>-1.018936723070362e-11</v>
-      </c>
-      <c r="I87" t="n">
-        <v>2.635790049854487e-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i2</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>i2</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>-1.3022690607186e-11</v>
-      </c>
-      <c r="E88" t="n">
-        <v>-3.585406637832523e-12</v>
-      </c>
-      <c r="F88" t="n">
-        <v/>
+          <t>i1</t>
+        </is>
       </c>
       <c r="G88" t="n">
-        <v>9.54071276598512e-10</v>
-      </c>
-      <c r="H88" t="n">
-        <v>-1.178646235923305e-11</v>
-      </c>
-      <c r="I88" t="n">
-        <v>3.002667479316e-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i3</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>i3</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>-1.289428976810786e-11</v>
-      </c>
-      <c r="E89" t="n">
-        <v>-9.083020814124178e-12</v>
-      </c>
-      <c r="F89" t="n">
-        <v/>
+          <t>i5</t>
+        </is>
       </c>
       <c r="G89" t="n">
-        <v>1.747072779967747e-12</v>
-      </c>
-      <c r="H89" t="n">
-        <v>-1.259445781208267e-11</v>
-      </c>
-      <c r="I89" t="n">
-        <v>-1.829216022214976e-13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>i5</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>i4</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>-6.874037202661255e-12</v>
-      </c>
-      <c r="E90" t="n">
-        <v>1.381120035388394e-13</v>
-      </c>
-      <c r="F90" t="n">
-        <v/>
+          <t>i1</t>
+        </is>
       </c>
       <c r="G90" t="n">
-        <v>2.150968586822984e-09</v>
-      </c>
-      <c r="H90" t="n">
-        <v>-5.240040661712158e-12</v>
-      </c>
-      <c r="I90" t="n">
-        <v>4.042462103497583e-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4236,37 +2980,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>i1</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>-1.495356861681892e-11</v>
-      </c>
-      <c r="E91" t="n">
-        <v>-1.212071406436196e-11</v>
-      </c>
-      <c r="F91" t="n">
-        <v/>
-      </c>
-      <c r="G91" t="n">
-        <v>1.722389778294714e-10</v>
-      </c>
-      <c r="H91" t="n">
-        <v>-6.303328191273513e-12</v>
-      </c>
-      <c r="I91" t="n">
-        <v>2.557445246617921e-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4274,34 +3003,19 @@
           <t>i2</t>
         </is>
       </c>
-      <c r="D92" t="n">
-        <v>-3.552230388838961e-12</v>
-      </c>
       <c r="E92" t="n">
-        <v>8.135731350593653e-11</v>
-      </c>
-      <c r="F92" t="n">
-        <v>2.661588604088594e-10</v>
-      </c>
-      <c r="G92" t="n">
-        <v/>
-      </c>
-      <c r="H92" t="n">
-        <v>1.075908936640099e-11</v>
-      </c>
-      <c r="I92" t="n">
-        <v>3.288940569855002e-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4309,34 +3023,19 @@
           <t>i3</t>
         </is>
       </c>
-      <c r="D93" t="n">
-        <v>-4.503345697068115e-12</v>
-      </c>
-      <c r="E93" t="n">
-        <v>6.743720385718219e-11</v>
-      </c>
       <c r="F93" t="n">
-        <v>2.777983892632817e-10</v>
-      </c>
-      <c r="G93" t="n">
-        <v/>
-      </c>
-      <c r="H93" t="n">
-        <v>8.887294964239147e-12</v>
-      </c>
-      <c r="I93" t="n">
-        <v>3.35042248125945e-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>i6</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4344,23 +3043,8 @@
           <t>i4</t>
         </is>
       </c>
-      <c r="D94" t="n">
-        <v>-4.040738801693473e-12</v>
-      </c>
-      <c r="E94" t="n">
-        <v>-2.172889850118085e-12</v>
-      </c>
-      <c r="F94" t="n">
-        <v>-1.612609077529268e-13</v>
-      </c>
       <c r="G94" t="n">
-        <v/>
-      </c>
-      <c r="H94" t="n">
-        <v>8.339817896929213e-12</v>
-      </c>
-      <c r="I94" t="n">
-        <v>-5.817940342594795e-13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -4388,9 +3072,6 @@
       <c r="F95" t="n">
         <v>1.050838559243662e-10</v>
       </c>
-      <c r="G95" t="n">
-        <v/>
-      </c>
       <c r="H95" t="n">
         <v>3.664563287944327e-11</v>
       </c>
@@ -4423,9 +3104,6 @@
       <c r="F96" t="n">
         <v>2.067864668593178e-10</v>
       </c>
-      <c r="G96" t="n">
-        <v/>
-      </c>
       <c r="H96" t="n">
         <v>-1.035903544912024e-11</v>
       </c>
@@ -4458,9 +3136,6 @@
       <c r="F97" t="n">
         <v>1.79284887862958e-10</v>
       </c>
-      <c r="G97" t="n">
-        <v/>
-      </c>
       <c r="H97" t="n">
         <v>7.776495502580512e-12</v>
       </c>
@@ -4493,9 +3168,6 @@
       <c r="F98" t="n">
         <v>7.056687462383032e-09</v>
       </c>
-      <c r="G98" t="n">
-        <v/>
-      </c>
       <c r="H98" t="n">
         <v>2.158655342424423e-11</v>
       </c>
@@ -4528,9 +3200,6 @@
       <c r="F99" t="n">
         <v>2.35442510609516e-12</v>
       </c>
-      <c r="G99" t="n">
-        <v/>
-      </c>
       <c r="H99" t="n">
         <v>-5.009535757666304e-13</v>
       </c>
@@ -4563,9 +3232,6 @@
       <c r="F100" t="n">
         <v>1.905463357161532e-10</v>
       </c>
-      <c r="G100" t="n">
-        <v/>
-      </c>
       <c r="H100" t="n">
         <v>2.854903675028034e-11</v>
       </c>
@@ -4598,9 +3264,6 @@
       <c r="F101" t="n">
         <v>5.822849826319701e-10</v>
       </c>
-      <c r="G101" t="n">
-        <v/>
-      </c>
       <c r="H101" t="n">
         <v>-1.309938064758448e-11</v>
       </c>
@@ -4633,9 +3296,6 @@
       <c r="F102" t="n">
         <v>1.764979418174182e-10</v>
       </c>
-      <c r="G102" t="n">
-        <v/>
-      </c>
       <c r="H102" t="n">
         <v>5.865492162939296e-12</v>
       </c>
@@ -4668,9 +3328,6 @@
       <c r="F103" t="n">
         <v>1.78446625651259e-09</v>
       </c>
-      <c r="G103" t="n">
-        <v/>
-      </c>
       <c r="H103" t="n">
         <v>2.092915755600953e-11</v>
       </c>
@@ -4703,9 +3360,6 @@
       <c r="F104" t="n">
         <v>2.132341052535778e-12</v>
       </c>
-      <c r="G104" t="n">
-        <v/>
-      </c>
       <c r="H104" t="n">
         <v>4.23978468464057e-13</v>
       </c>
@@ -4738,9 +3392,6 @@
       <c r="F105" t="n">
         <v>1.865210762973501e-10</v>
       </c>
-      <c r="G105" t="n">
-        <v/>
-      </c>
       <c r="H105" t="n">
         <v>3.521584551902487e-11</v>
       </c>
@@ -4773,9 +3424,6 @@
       <c r="F106" t="n">
         <v>6.6871097076556e-10</v>
       </c>
-      <c r="G106" t="n">
-        <v/>
-      </c>
       <c r="H106" t="n">
         <v>-1.279161384068078e-11</v>
       </c>
@@ -4808,9 +3456,6 @@
       <c r="F107" t="n">
         <v>2.09579617744234e-10</v>
       </c>
-      <c r="G107" t="n">
-        <v/>
-      </c>
       <c r="H107" t="n">
         <v>4.771105715621461e-11</v>
       </c>
@@ -4843,9 +3488,6 @@
       <c r="F108" t="n">
         <v>4.301216973596557e-09</v>
       </c>
-      <c r="G108" t="n">
-        <v/>
-      </c>
       <c r="H108" t="n">
         <v>2.207942010892821e-11</v>
       </c>
@@ -4878,9 +3520,6 @@
       <c r="F109" t="n">
         <v>0.162269023483914</v>
       </c>
-      <c r="G109" t="n">
-        <v/>
-      </c>
       <c r="H109" t="n">
         <v>2.604656249260268e-11</v>
       </c>
@@ -4913,9 +3552,6 @@
       <c r="F110" t="n">
         <v>2.10317547785359e-10</v>
       </c>
-      <c r="G110" t="n">
-        <v/>
-      </c>
       <c r="H110" t="n">
         <v>2.33072225995709e-10</v>
       </c>
@@ -4948,9 +3584,6 @@
       <c r="F111" t="n">
         <v>1.226110141488965e-09</v>
       </c>
-      <c r="G111" t="n">
-        <v/>
-      </c>
       <c r="H111" t="n">
         <v>-5.153609846446081e-13</v>
       </c>
@@ -4983,9 +3616,6 @@
       <c r="F112" t="n">
         <v>1.05413251484814e-10</v>
       </c>
-      <c r="G112" t="n">
-        <v/>
-      </c>
       <c r="H112" t="n">
         <v>2.998671987074423e-12</v>
       </c>
@@ -5018,9 +3648,6 @@
       <c r="F113" t="n">
         <v>2.722467513048244e-10</v>
       </c>
-      <c r="G113" t="n">
-        <v/>
-      </c>
       <c r="H113" t="n">
         <v>2.949234305601834e-12</v>
       </c>
@@ -5053,9 +3680,6 @@
       <c r="F114" t="n">
         <v>2.861752508308487e-10</v>
       </c>
-      <c r="G114" t="n">
-        <v/>
-      </c>
       <c r="H114" t="n">
         <v>5.12216660174276e-12</v>
       </c>
@@ -5088,9 +3712,6 @@
       <c r="F115" t="n">
         <v>1.870739525170177e-14</v>
       </c>
-      <c r="G115" t="n">
-        <v/>
-      </c>
       <c r="H115" t="n">
         <v>5.903081454496403e-13</v>
       </c>
@@ -5123,9 +3744,6 @@
       <c r="F116" t="n">
         <v>2.045616720324494e-10</v>
       </c>
-      <c r="G116" t="n">
-        <v/>
-      </c>
       <c r="H116" t="n">
         <v>-1.276250735524076e-11</v>
       </c>
@@ -5158,9 +3776,6 @@
       <c r="F117" t="n">
         <v>1.8489061263816e-10</v>
       </c>
-      <c r="G117" t="n">
-        <v/>
-      </c>
       <c r="H117" t="n">
         <v>-1.007891715091562e-11</v>
       </c>
@@ -5193,9 +3808,6 @@
       <c r="F118" t="n">
         <v>1.387069251877235e-09</v>
       </c>
-      <c r="G118" t="n">
-        <v/>
-      </c>
       <c r="H118" t="n">
         <v>-1.240514988318695e-11</v>
       </c>
@@ -5228,9 +3840,6 @@
       <c r="F119" t="n">
         <v>1.138174978323798e-09</v>
       </c>
-      <c r="G119" t="n">
-        <v/>
-      </c>
       <c r="H119" t="n">
         <v>-1.199971761707187e-11</v>
       </c>
@@ -5263,9 +3872,6 @@
       <c r="F120" t="n">
         <v>2.3725736137916e-12</v>
       </c>
-      <c r="G120" t="n">
-        <v/>
-      </c>
       <c r="H120" t="n">
         <v>-7.846880297898694e-12</v>
       </c>
@@ -5298,9 +3904,6 @@
       <c r="F121" t="n">
         <v>1.759468173252028e-10</v>
       </c>
-      <c r="G121" t="n">
-        <v/>
-      </c>
       <c r="H121" t="n">
         <v>-7.271716359120801e-12</v>
       </c>
@@ -5336,9 +3939,6 @@
       <c r="G122" t="n">
         <v>9.494342511730961e-12</v>
       </c>
-      <c r="H122" t="n">
-        <v/>
-      </c>
       <c r="I122" t="n">
         <v>1.718855212038178e-09</v>
       </c>
@@ -5371,9 +3971,6 @@
       <c r="G123" t="n">
         <v>7.439489516726069e-12</v>
       </c>
-      <c r="H123" t="n">
-        <v/>
-      </c>
       <c r="I123" t="n">
         <v>1.731261779069476e-09</v>
       </c>
@@ -5406,9 +4003,6 @@
       <c r="G124" t="n">
         <v>4.524069336401322e-11</v>
       </c>
-      <c r="H124" t="n">
-        <v/>
-      </c>
       <c r="I124" t="n">
         <v>1.784615315406774e-09</v>
       </c>
@@ -5441,9 +4035,6 @@
       <c r="G125" t="n">
         <v>5.065116142920972e-12</v>
       </c>
-      <c r="H125" t="n">
-        <v/>
-      </c>
       <c r="I125" t="n">
         <v>-2.061592268122756e-13</v>
       </c>
@@ -5476,9 +4067,6 @@
       <c r="G126" t="n">
         <v>-9.01246378639089e-12</v>
       </c>
-      <c r="H126" t="n">
-        <v/>
-      </c>
       <c r="I126" t="n">
         <v>1.93039667860613e-09</v>
       </c>
@@ -5511,9 +4099,6 @@
       <c r="G127" t="n">
         <v>1.253401755341473e-11</v>
       </c>
-      <c r="H127" t="n">
-        <v/>
-      </c>
       <c r="I127" t="n">
         <v>1.459655004123806e-09</v>
       </c>
@@ -5546,9 +4131,6 @@
       <c r="G128" t="n">
         <v>2.313052975440405e-11</v>
       </c>
-      <c r="H128" t="n">
-        <v/>
-      </c>
       <c r="I128" t="n">
         <v>2.229578980244085e-08</v>
       </c>
@@ -5581,9 +4163,6 @@
       <c r="G129" t="n">
         <v>2.167013736146798e-11</v>
       </c>
-      <c r="H129" t="n">
-        <v/>
-      </c>
       <c r="I129" t="n">
         <v>1.250061510394376e-08</v>
       </c>
@@ -5616,9 +4195,6 @@
       <c r="G130" t="n">
         <v>4.984192640565891e-12</v>
       </c>
-      <c r="H130" t="n">
-        <v/>
-      </c>
       <c r="I130" t="n">
         <v>1.831307637648858e-13</v>
       </c>
@@ -5651,9 +4227,6 @@
       <c r="G131" t="n">
         <v>-1.151280687618251e-11</v>
       </c>
-      <c r="H131" t="n">
-        <v/>
-      </c>
       <c r="I131" t="n">
         <v>1.424085037767381e-08</v>
       </c>
@@ -5686,9 +4259,6 @@
       <c r="G132" t="n">
         <v>1.063706544394696e-11</v>
       </c>
-      <c r="H132" t="n">
-        <v/>
-      </c>
       <c r="I132" t="n">
         <v>1.469140392636812e-09</v>
       </c>
@@ -5721,9 +4291,6 @@
       <c r="G133" t="n">
         <v>2.402924048845797e-11</v>
       </c>
-      <c r="H133" t="n">
-        <v/>
-      </c>
       <c r="I133" t="n">
         <v>1.308672937908933e-08</v>
       </c>
@@ -5756,9 +4323,6 @@
       <c r="G134" t="n">
         <v>2.549300736909365e-11</v>
       </c>
-      <c r="H134" t="n">
-        <v/>
-      </c>
       <c r="I134" t="n">
         <v>1.083998963815183e-08</v>
       </c>
@@ -5791,9 +4355,6 @@
       <c r="G135" t="n">
         <v>7.39480433640633e-12</v>
       </c>
-      <c r="H135" t="n">
-        <v/>
-      </c>
       <c r="I135" t="n">
         <v>1.862307210096395e-13</v>
       </c>
@@ -5826,9 +4387,6 @@
       <c r="G136" t="n">
         <v>-1.106789460315811e-11</v>
       </c>
-      <c r="H136" t="n">
-        <v/>
-      </c>
       <c r="I136" t="n">
         <v>4.108409987869431e-08</v>
       </c>
@@ -5861,9 +4419,6 @@
       <c r="G137" t="n">
         <v>4.132690808046113e-13</v>
       </c>
-      <c r="H137" t="n">
-        <v/>
-      </c>
       <c r="I137" t="n">
         <v>1.48372863877426e-09</v>
       </c>
@@ -5896,9 +4451,6 @@
       <c r="G138" t="n">
         <v>-5.054544221132892e-12</v>
       </c>
-      <c r="H138" t="n">
-        <v/>
-      </c>
       <c r="I138" t="n">
         <v>7.658867326969074e-09</v>
       </c>
@@ -5931,9 +4483,6 @@
       <c r="G139" t="n">
         <v>-4.467636695753713e-12</v>
       </c>
-      <c r="H139" t="n">
-        <v/>
-      </c>
       <c r="I139" t="n">
         <v>9.072509757175057e-09</v>
       </c>
@@ -5966,9 +4515,6 @@
       <c r="G140" t="n">
         <v>-4.027346480315157e-12</v>
       </c>
-      <c r="H140" t="n">
-        <v/>
-      </c>
       <c r="I140" t="n">
         <v>1.447228459762697e-13</v>
       </c>
@@ -6001,9 +4547,6 @@
       <c r="G141" t="n">
         <v>-1.000671566624388e-11</v>
       </c>
-      <c r="H141" t="n">
-        <v/>
-      </c>
       <c r="I141" t="n">
         <v>5.471080872321377e-08</v>
       </c>
@@ -6036,9 +4579,6 @@
       <c r="G142" t="n">
         <v>4.439782332002134e-11</v>
       </c>
-      <c r="H142" t="n">
-        <v/>
-      </c>
       <c r="I142" t="n">
         <v>1.629985236223137e-09</v>
       </c>
@@ -6071,9 +4611,6 @@
       <c r="G143" t="n">
         <v>3.489222585337271e-11</v>
       </c>
-      <c r="H143" t="n">
-        <v/>
-      </c>
       <c r="I143" t="n">
         <v>2.50994531561259e-08</v>
       </c>
@@ -6106,9 +4643,6 @@
       <c r="G144" t="n">
         <v>4.263270042659604e-11</v>
       </c>
-      <c r="H144" t="n">
-        <v/>
-      </c>
       <c r="I144" t="n">
         <v>3.073502175378298e-08</v>
       </c>
@@ -6141,9 +4675,6 @@
       <c r="G145" t="n">
         <v>2.399100581624925e-10</v>
       </c>
-      <c r="H145" t="n">
-        <v/>
-      </c>
       <c r="I145" t="n">
         <v>4.431234530524735e-08</v>
       </c>
@@ -6176,9 +4707,6 @@
       <c r="G146" t="n">
         <v>-5.524787950270351e-12</v>
       </c>
-      <c r="H146" t="n">
-        <v/>
-      </c>
       <c r="I146" t="n">
         <v>0.003112504153832382</v>
       </c>
@@ -6211,9 +4739,6 @@
       <c r="G147" t="n">
         <v>-9.754997649186309e-12</v>
       </c>
-      <c r="H147" t="n">
-        <v/>
-      </c>
       <c r="I147" t="n">
         <v>1.122413554135777e-09</v>
       </c>
@@ -6246,9 +4771,6 @@
       <c r="G148" t="n">
         <v>-1.255519419875925e-11</v>
       </c>
-      <c r="H148" t="n">
-        <v/>
-      </c>
       <c r="I148" t="n">
         <v>2.933188344723628e-09</v>
       </c>
@@ -6281,9 +4803,6 @@
       <c r="G149" t="n">
         <v>-1.22488599672255e-11</v>
       </c>
-      <c r="H149" t="n">
-        <v/>
-      </c>
       <c r="I149" t="n">
         <v>2.645562426825101e-09</v>
       </c>
@@ -6316,9 +4835,6 @@
       <c r="G150" t="n">
         <v>-5.535968639567732e-13</v>
       </c>
-      <c r="H150" t="n">
-        <v/>
-      </c>
       <c r="I150" t="n">
         <v>3.488493806228511e-09</v>
       </c>
@@ -6351,9 +4867,6 @@
       <c r="G151" t="n">
         <v>-1.207153979982942e-11</v>
       </c>
-      <c r="H151" t="n">
-        <v/>
-      </c>
       <c r="I151" t="n">
         <v>-1.230949818186465e-13</v>
       </c>
@@ -6389,9 +4902,6 @@
       <c r="H152" t="n">
         <v>1.719698442026227e-09</v>
       </c>
-      <c r="I152" t="n">
-        <v/>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6424,9 +4934,6 @@
       <c r="H153" t="n">
         <v>1.728425190046849e-09</v>
       </c>
-      <c r="I153" t="n">
-        <v/>
-      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6459,9 +4966,6 @@
       <c r="H154" t="n">
         <v>1.662966376097547e-09</v>
       </c>
-      <c r="I154" t="n">
-        <v/>
-      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6494,9 +4998,6 @@
       <c r="H155" t="n">
         <v>1.862283598484881e-09</v>
       </c>
-      <c r="I155" t="n">
-        <v/>
-      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6529,9 +5030,6 @@
       <c r="H156" t="n">
         <v>-1.800767709158529e-13</v>
       </c>
-      <c r="I156" t="n">
-        <v/>
-      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6564,9 +5062,6 @@
       <c r="H157" t="n">
         <v>1.46037000076649e-09</v>
       </c>
-      <c r="I157" t="n">
-        <v/>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6599,9 +5094,6 @@
       <c r="H158" t="n">
         <v>2.178012127989202e-08</v>
       </c>
-      <c r="I158" t="n">
-        <v/>
-      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6634,9 +5126,6 @@
       <c r="H159" t="n">
         <v>8.306562951711131e-09</v>
       </c>
-      <c r="I159" t="n">
-        <v/>
-      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6669,9 +5158,6 @@
       <c r="H160" t="n">
         <v>2.737793959970017e-08</v>
       </c>
-      <c r="I160" t="n">
-        <v/>
-      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6704,9 +5190,6 @@
       <c r="H161" t="n">
         <v>2.028003250719098e-13</v>
       </c>
-      <c r="I161" t="n">
-        <v/>
-      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6739,9 +5222,6 @@
       <c r="H162" t="n">
         <v>1.472004065906149e-09</v>
       </c>
-      <c r="I162" t="n">
-        <v/>
-      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6774,9 +5254,6 @@
       <c r="H163" t="n">
         <v>1.329457150938505e-08</v>
       </c>
-      <c r="I163" t="n">
-        <v/>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6809,9 +5286,6 @@
       <c r="H164" t="n">
         <v>7.601397106285743e-09</v>
       </c>
-      <c r="I164" t="n">
-        <v/>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6844,9 +5318,6 @@
       <c r="H165" t="n">
         <v>3.082116171080027e-08</v>
       </c>
-      <c r="I165" t="n">
-        <v/>
-      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6879,9 +5350,6 @@
       <c r="H166" t="n">
         <v>2.461237182975996e-13</v>
       </c>
-      <c r="I166" t="n">
-        <v/>
-      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6914,9 +5382,6 @@
       <c r="H167" t="n">
         <v>1.581421669355258e-09</v>
       </c>
-      <c r="I167" t="n">
-        <v/>
-      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6949,9 +5414,6 @@
       <c r="H168" t="n">
         <v>1.111368568120659e-08</v>
       </c>
-      <c r="I168" t="n">
-        <v/>
-      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6984,9 +5446,6 @@
       <c r="H169" t="n">
         <v>1.41188043443519e-08</v>
       </c>
-      <c r="I169" t="n">
-        <v/>
-      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7019,9 +5478,6 @@
       <c r="H170" t="n">
         <v>4.407536735837195e-08</v>
       </c>
-      <c r="I170" t="n">
-        <v/>
-      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -7054,9 +5510,6 @@
       <c r="H171" t="n">
         <v>2.90115890781308e-13</v>
       </c>
-      <c r="I171" t="n">
-        <v/>
-      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -7089,9 +5542,6 @@
       <c r="H172" t="n">
         <v>7.06744387757004e-10</v>
       </c>
-      <c r="I172" t="n">
-        <v/>
-      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -7124,9 +5574,6 @@
       <c r="H173" t="n">
         <v>1.226276354997859e-09</v>
       </c>
-      <c r="I173" t="n">
-        <v/>
-      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -7159,9 +5606,6 @@
       <c r="H174" t="n">
         <v>1.236014487965081e-09</v>
       </c>
-      <c r="I174" t="n">
-        <v/>
-      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -7194,9 +5638,6 @@
       <c r="H175" t="n">
         <v>1.191399521603229e-09</v>
       </c>
-      <c r="I175" t="n">
-        <v/>
-      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -7229,9 +5670,6 @@
       <c r="H176" t="n">
         <v>-3.752546872173415e-13</v>
       </c>
-      <c r="I176" t="n">
-        <v/>
-      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -7264,9 +5702,6 @@
       <c r="H177" t="n">
         <v>1.752653406099677e-09</v>
       </c>
-      <c r="I177" t="n">
-        <v/>
-      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -7299,9 +5734,6 @@
       <c r="H178" t="n">
         <v>3.157096464477926e-08</v>
       </c>
-      <c r="I178" t="n">
-        <v/>
-      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -7334,9 +5766,6 @@
       <c r="H179" t="n">
         <v>1.432601521383932e-08</v>
       </c>
-      <c r="I179" t="n">
-        <v/>
-      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -7369,9 +5798,6 @@
       <c r="H180" t="n">
         <v>5.212724321347923e-08</v>
       </c>
-      <c r="I180" t="n">
-        <v/>
-      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -7403,9 +5829,6 @@
       </c>
       <c r="H181" t="n">
         <v>0.003113491206743979</v>
-      </c>
-      <c r="I181" t="n">
-        <v/>
       </c>
     </row>
   </sheetData>
@@ -7423,8 +5846,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="n">
-        <v>0.02973639219999313</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -7478,10 +5903,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4365964458709515</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1862517895818428</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -7490,7 +5915,28 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.8870909439953725</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
   </sheetData>
